--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.3824</v>
+        <v>0.3792</v>
       </c>
       <c r="H3" t="n">
         <v>0.3901</v>
@@ -533,7 +533,7 @@
         <v>0.412</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4111</v>
+        <v>0.4002</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.7255</v>
+        <v>0.7408</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6036</v>
+        <v>0.6268</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +585,7 @@
         <v>0.5881999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.508</v>
+        <v>0.4907</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.8894</v>
+        <v>0.8495</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8421</v>
+        <v>0.8047</v>
       </c>
     </row>
     <row r="8">
@@ -625,19 +625,19 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.829</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7385</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="9">
@@ -660,10 +660,10 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.5937</v>
+        <v>0.5926</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5243</v>
+        <v>0.5224</v>
       </c>
     </row>
     <row r="10">
@@ -677,19 +677,19 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.7292</v>
+        <v>0.829</v>
       </c>
       <c r="H10" t="n">
-        <v>0.61</v>
+        <v>0.7385</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9198</v>
+        <v>0.9336</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9602000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.8389</v>
+        <v>0.884</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7911</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="13">
@@ -793,7 +793,7 @@
         <v>0.9550999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9704</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="15">
@@ -816,7 +816,7 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9444</v>
+        <v>0.945</v>
       </c>
       <c r="H15" t="n">
         <v>0.9536</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.16</v>
+        <v>0.1607</v>
       </c>
       <c r="H16" t="n">
         <v>0.1527</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>0.3247</v>
+        <v>0.3197</v>
       </c>
       <c r="H17" t="n">
         <v>0.3381</v>
@@ -894,10 +894,10 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0.4426</v>
+        <v>0.4475</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4197</v>
+        <v>0.4262</v>
       </c>
     </row>
     <row r="19">
@@ -920,10 +920,10 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>0.3744</v>
+        <v>0.4073</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4105</v>
+        <v>0.4292</v>
       </c>
     </row>
     <row r="20">
@@ -946,10 +946,10 @@
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
-        <v>0.6504</v>
+        <v>0.6625</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5954</v>
+        <v>0.6096</v>
       </c>
     </row>
     <row r="21">
@@ -975,7 +975,7 @@
         <v>0.6739000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6369</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="22">
@@ -1154,10 +1154,10 @@
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
-        <v>0.9438</v>
+        <v>0.9462</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9322</v>
+        <v>0.9386</v>
       </c>
     </row>
     <row r="29">
@@ -1183,7 +1183,7 @@
         <v>0.9437</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9555</v>
+        <v>0.9574</v>
       </c>
     </row>
     <row r="30">
@@ -1206,10 +1206,10 @@
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>0.9446</v>
+        <v>0.9456</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9462</v>
+        <v>0.9477</v>
       </c>
     </row>
     <row r="31">
@@ -1287,7 +1287,7 @@
         <v>0.5658</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5198</v>
       </c>
     </row>
     <row r="34">
@@ -1310,10 +1310,10 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.8269</v>
+        <v>0.8426</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7852</v>
+        <v>0.8083</v>
       </c>
     </row>
     <row r="35">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.9383</v>
+        <v>0.9196</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9412</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="37">
@@ -1379,19 +1379,19 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.9099</v>
+        <v>0.8133</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9084</v>
+        <v>0.8008999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1417,7 +1417,7 @@
         <v>0.6758999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6804</v>
+        <v>0.6823</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.8133</v>
+        <v>0.9113</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.9091</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.9696</v>
+        <v>0.9751</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9705</v>
+        <v>0.9752</v>
       </c>
     </row>
     <row r="41">
@@ -1492,10 +1492,10 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9437</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9246</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="42">
@@ -1570,10 +1570,10 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.979</v>
+        <v>0.9794</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9794</v>
+        <v>0.9797</v>
       </c>
     </row>
     <row r="45">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>0.4517</v>
+        <v>0.4522</v>
       </c>
       <c r="H46" t="n">
         <v>0.4618</v>
@@ -1648,10 +1648,10 @@
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
-        <v>0.6573</v>
+        <v>0.6697</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5561</v>
+        <v>0.5737</v>
       </c>
     </row>
     <row r="48">
@@ -1674,10 +1674,10 @@
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.6117</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5128</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="49">
@@ -1700,10 +1700,10 @@
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>0.7372</v>
+        <v>0.7728</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7506</v>
+        <v>0.7796</v>
       </c>
     </row>
     <row r="50">
@@ -1729,7 +1729,7 @@
         <v>0.7811</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8021</v>
+        <v>0.8008</v>
       </c>
     </row>
     <row r="51">
@@ -1807,7 +1807,7 @@
         <v>0.8899</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8966</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="54">
@@ -1833,7 +1833,7 @@
         <v>0.9085</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9101</v>
+        <v>0.9174</v>
       </c>
     </row>
     <row r="55">
@@ -1859,7 +1859,7 @@
         <v>0.9213</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9304</v>
+        <v>0.931</v>
       </c>
     </row>
     <row r="56">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>0.9685</v>
+        <v>0.9717</v>
       </c>
       <c r="H57" t="n">
         <v>0.9716</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>0.976</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="H59" t="n">
         <v>0.9745</v>
@@ -1989,7 +1989,7 @@
         <v>0.6099</v>
       </c>
       <c r="H60" t="n">
-        <v>0.6176</v>
+        <v>0.6208</v>
       </c>
     </row>
     <row r="61">
@@ -2041,7 +2041,7 @@
         <v>0.6159</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4943</v>
+        <v>0.4937</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.8266</v>
+        <v>0.8433</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7684</v>
+        <v>0.7892</v>
       </c>
     </row>
     <row r="64">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.9296</v>
+        <v>0.9113</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9536</v>
+        <v>0.9255</v>
       </c>
     </row>
     <row r="66">
@@ -2133,19 +2133,19 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.8984</v>
+        <v>0.8122</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8942</v>
+        <v>0.7879</v>
       </c>
     </row>
     <row r="67">
@@ -2171,7 +2171,7 @@
         <v>0.6869</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6077</v>
+        <v>0.6102</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.8122</v>
+        <v>0.8994</v>
       </c>
       <c r="H68" t="n">
-        <v>0.7879</v>
+        <v>0.8959</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.9621</v>
+        <v>0.9739</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9702</v>
+        <v>0.9752</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9347</v>
+        <v>0.9498</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8793</v>
+        <v>0.9298</v>
       </c>
     </row>
     <row r="71">
@@ -2301,7 +2301,7 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9832</v>
       </c>
     </row>
     <row r="73">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.974</v>
+        <v>0.9746</v>
       </c>
       <c r="H73" t="n">
         <v>0.9823</v>
@@ -2353,7 +2353,7 @@
         <v>0.3096</v>
       </c>
       <c r="H74" t="n">
-        <v>0.2424</v>
+        <v>0.2383</v>
       </c>
     </row>
     <row r="75">
@@ -2402,10 +2402,10 @@
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
-        <v>0.6283</v>
+        <v>0.6469</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5289</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -2428,10 +2428,10 @@
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>0.5474</v>
+        <v>0.611</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5164</v>
+        <v>0.5671</v>
       </c>
     </row>
     <row r="78">
@@ -2454,10 +2454,10 @@
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
-        <v>0.7376</v>
+        <v>0.7542</v>
       </c>
       <c r="H78" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7516</v>
       </c>
     </row>
     <row r="79">
@@ -2506,10 +2506,10 @@
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
-        <v>0.8659</v>
+        <v>0.8743</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8265</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="81">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
-        <v>0.7058</v>
+        <v>0.7077</v>
       </c>
       <c r="H81" t="n">
         <v>0.6726</v>
@@ -2639,7 +2639,7 @@
         <v>0.9661</v>
       </c>
       <c r="H85" t="n">
-        <v>0.9782</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="86">
@@ -2662,10 +2662,10 @@
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>0.9668</v>
+        <v>0.9679</v>
       </c>
       <c r="H86" t="n">
-        <v>0.9794</v>
+        <v>0.9802999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>0.9683</v>
+        <v>0.9695</v>
       </c>
       <c r="H88" t="n">
         <v>0.9821</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.5889</v>
+        <v>0.5998</v>
       </c>
       <c r="H89" t="n">
         <v>0.588</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.4814</v>
+        <v>0.4802</v>
       </c>
       <c r="H90" t="n">
         <v>0.4342</v>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.5057</v>
+        <v>0.5063</v>
       </c>
       <c r="H91" t="n">
         <v>0.3841</v>
@@ -2818,10 +2818,10 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.7988</v>
+        <v>0.8129</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7715</v>
+        <v>0.7922</v>
       </c>
     </row>
     <row r="93">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.9144</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>0.9324</v>
+        <v>0.922</v>
       </c>
     </row>
     <row r="95">
@@ -2887,19 +2887,19 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.8668</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8827</v>
+        <v>0.8098</v>
       </c>
     </row>
     <row r="96">
@@ -2922,10 +2922,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.6603</v>
+        <v>0.6625</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6015</v>
+        <v>0.6059</v>
       </c>
     </row>
     <row r="97">
@@ -2939,19 +2939,19 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.7991</v>
+        <v>0.8702</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.9663</v>
+        <v>0.9724</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9679</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9164</v>
+        <v>0.9336</v>
       </c>
       <c r="H99" t="n">
-        <v>0.907</v>
+        <v>0.9392</v>
       </c>
     </row>
     <row r="100">
@@ -3055,7 +3055,7 @@
         <v>0.9792</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9868</v>
+        <v>0.9866</v>
       </c>
     </row>
     <row r="102">
@@ -3081,7 +3081,7 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9815</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="103">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>0.4473</v>
+        <v>0.4577</v>
       </c>
       <c r="H104" t="n">
         <v>0.3817</v>
@@ -3156,10 +3156,10 @@
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>0.5873</v>
+        <v>0.5919</v>
       </c>
       <c r="H105" t="n">
-        <v>0.5085</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="106">
@@ -3182,10 +3182,10 @@
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>0.5424</v>
+        <v>0.5674</v>
       </c>
       <c r="H106" t="n">
-        <v>0.5091</v>
+        <v>0.5435</v>
       </c>
     </row>
     <row r="107">
@@ -3208,10 +3208,10 @@
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>0.7129</v>
+        <v>0.7343</v>
       </c>
       <c r="H107" t="n">
-        <v>0.6936</v>
+        <v>0.7294</v>
       </c>
     </row>
     <row r="108">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>0.7227</v>
+        <v>0.7269</v>
       </c>
       <c r="H108" t="n">
         <v>0.7566000000000001</v>
@@ -3263,7 +3263,7 @@
         <v>0.8106</v>
       </c>
       <c r="H109" t="n">
-        <v>0.8405</v>
+        <v>0.8518</v>
       </c>
     </row>
     <row r="110">
@@ -3312,10 +3312,10 @@
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.864</v>
       </c>
       <c r="H111" t="n">
-        <v>0.8905</v>
+        <v>0.8934</v>
       </c>
     </row>
     <row r="112">
@@ -3338,10 +3338,10 @@
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>0.8817</v>
+        <v>0.8827</v>
       </c>
       <c r="H112" t="n">
-        <v>0.9053</v>
+        <v>0.9046999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -3364,10 +3364,10 @@
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>0.9079</v>
+        <v>0.9087</v>
       </c>
       <c r="H113" t="n">
-        <v>0.9342</v>
+        <v>0.9354</v>
       </c>
     </row>
     <row r="114">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>0.9623</v>
+        <v>0.9637</v>
       </c>
       <c r="H114" t="n">
         <v>0.9778</v>
@@ -3416,10 +3416,10 @@
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="n">
-        <v>0.9653</v>
+        <v>0.9663</v>
       </c>
       <c r="H115" t="n">
-        <v>0.9729</v>
+        <v>0.9749</v>
       </c>
     </row>
     <row r="116">
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.3964</v>
+        <v>0.3732</v>
       </c>
       <c r="H118" t="n">
-        <v>0.2745</v>
+        <v>0.2592</v>
       </c>
     </row>
     <row r="119">
@@ -3520,10 +3520,10 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.2148</v>
+        <v>0.1917</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1731</v>
+        <v>0.1574</v>
       </c>
     </row>
     <row r="120">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.2316</v>
+        <v>0.2108</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1734</v>
+        <v>0.1567</v>
       </c>
     </row>
     <row r="121">
@@ -3572,10 +3572,10 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.2285</v>
+        <v>0.2078</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2012</v>
+        <v>0.1871</v>
       </c>
     </row>
     <row r="122">
@@ -3598,10 +3598,10 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0.3831</v>
+        <v>0.3748</v>
       </c>
       <c r="H122" t="n">
-        <v>0.3696</v>
+        <v>0.3603</v>
       </c>
     </row>
     <row r="123">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.774</v>
+        <v>0.7085</v>
       </c>
       <c r="H123" t="n">
-        <v>0.7337</v>
+        <v>0.6114000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -3641,19 +3641,19 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0.6639</v>
+        <v>0.4823</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6037</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="125">
@@ -3676,10 +3676,10 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>0.3443</v>
+        <v>0.3353</v>
       </c>
       <c r="H125" t="n">
-        <v>0.3733</v>
+        <v>0.3728</v>
       </c>
     </row>
     <row r="126">
@@ -3693,19 +3693,19 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>0.5107</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="H126" t="n">
-        <v>0.4389</v>
+        <v>0.5874</v>
       </c>
     </row>
     <row r="127">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.9092</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9064</v>
+        <v>0.9182</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.8005</v>
+        <v>0.8248</v>
       </c>
       <c r="H128" t="n">
-        <v>0.7088</v>
+        <v>0.7472</v>
       </c>
     </row>
     <row r="129">
@@ -3806,10 +3806,10 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.969</v>
+        <v>0.9683</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9767</v>
+        <v>0.9762999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -3832,10 +3832,10 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.9421</v>
+        <v>0.9383</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9529</v>
+        <v>0.9524</v>
       </c>
     </row>
     <row r="132">
@@ -3858,10 +3858,10 @@
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0815</v>
       </c>
       <c r="H132" t="n">
-        <v>0.0825</v>
+        <v>0.08069999999999999</v>
       </c>
     </row>
     <row r="133">
@@ -3884,10 +3884,10 @@
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>0.1909</v>
+        <v>0.1838</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1687</v>
+        <v>0.1594</v>
       </c>
     </row>
     <row r="134">
@@ -3910,10 +3910,10 @@
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="n">
-        <v>0.2778</v>
+        <v>0.2784</v>
       </c>
       <c r="H134" t="n">
-        <v>0.2787</v>
+        <v>0.2699</v>
       </c>
     </row>
     <row r="135">
@@ -3936,10 +3936,10 @@
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="n">
-        <v>0.1874</v>
+        <v>0.2343</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2448</v>
+        <v>0.2716</v>
       </c>
     </row>
     <row r="136">
@@ -3962,10 +3962,10 @@
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="n">
-        <v>0.4122</v>
+        <v>0.4219</v>
       </c>
       <c r="H136" t="n">
-        <v>0.3965</v>
+        <v>0.4064</v>
       </c>
     </row>
     <row r="137">
@@ -3988,10 +3988,10 @@
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="n">
-        <v>0.4641</v>
+        <v>0.4552</v>
       </c>
       <c r="H137" t="n">
-        <v>0.4314</v>
+        <v>0.4221</v>
       </c>
     </row>
     <row r="138">
@@ -4014,10 +4014,10 @@
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="n">
-        <v>0.5611</v>
+        <v>0.554</v>
       </c>
       <c r="H138" t="n">
-        <v>0.4826</v>
+        <v>0.4729</v>
       </c>
     </row>
     <row r="139">
@@ -4040,10 +4040,10 @@
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="n">
-        <v>0.3835</v>
+        <v>0.3752</v>
       </c>
       <c r="H139" t="n">
-        <v>0.3653</v>
+        <v>0.3619</v>
       </c>
     </row>
     <row r="140">
@@ -4066,10 +4066,10 @@
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6591</v>
       </c>
       <c r="H140" t="n">
-        <v>0.6185</v>
+        <v>0.6072</v>
       </c>
     </row>
     <row r="141">
@@ -4092,10 +4092,10 @@
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="n">
-        <v>0.6984</v>
+        <v>0.6916</v>
       </c>
       <c r="H141" t="n">
-        <v>0.5823</v>
+        <v>0.5725</v>
       </c>
     </row>
     <row r="142">
@@ -4118,10 +4118,10 @@
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>0.7993</v>
+        <v>0.7968</v>
       </c>
       <c r="H142" t="n">
-        <v>0.67</v>
+        <v>0.6618000000000001</v>
       </c>
     </row>
     <row r="143">
@@ -4144,10 +4144,10 @@
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="n">
-        <v>0.8958</v>
+        <v>0.8939</v>
       </c>
       <c r="H143" t="n">
-        <v>0.9127</v>
+        <v>0.9016</v>
       </c>
     </row>
     <row r="144">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.9038</v>
       </c>
       <c r="H144" t="n">
         <v>0.9169</v>
@@ -4196,10 +4196,10 @@
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="n">
-        <v>0.9411</v>
+        <v>0.9391</v>
       </c>
       <c r="H145" t="n">
-        <v>0.9291</v>
+        <v>0.9287</v>
       </c>
     </row>
     <row r="146">
@@ -4222,10 +4222,10 @@
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="n">
-        <v>0.9354</v>
+        <v>0.9265</v>
       </c>
       <c r="H146" t="n">
-        <v>0.9473</v>
+        <v>0.9465</v>
       </c>
     </row>
     <row r="147">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.492</v>
+        <v>0.5093</v>
       </c>
       <c r="H147" t="n">
         <v>0.4118</v>
@@ -4352,10 +4352,10 @@
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>0.6304</v>
+        <v>0.6397</v>
       </c>
       <c r="H151" t="n">
-        <v>0.6169</v>
+        <v>0.6252</v>
       </c>
     </row>
     <row r="152">
@@ -4378,10 +4378,10 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0.8517</v>
+        <v>0.8193</v>
       </c>
       <c r="H152" t="n">
-        <v>0.866</v>
+        <v>0.8157</v>
       </c>
     </row>
     <row r="153">
@@ -4395,19 +4395,19 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.7694</v>
+        <v>0.6283</v>
       </c>
       <c r="H153" t="n">
-        <v>0.7607</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="154">
@@ -4430,10 +4430,10 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.4603</v>
+        <v>0.4658</v>
       </c>
       <c r="H154" t="n">
-        <v>0.4265</v>
+        <v>0.4344</v>
       </c>
     </row>
     <row r="155">
@@ -4447,19 +4447,19 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.6283</v>
+        <v>0.7694</v>
       </c>
       <c r="H155" t="n">
-        <v>0.599</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="156">
@@ -4482,10 +4482,10 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.9026</v>
+        <v>0.9255</v>
       </c>
       <c r="H156" t="n">
-        <v>0.93</v>
+        <v>0.9406</v>
       </c>
     </row>
     <row r="157">
@@ -4508,10 +4508,10 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>0.8583</v>
+        <v>0.8832</v>
       </c>
       <c r="H157" t="n">
-        <v>0.85</v>
+        <v>0.8963</v>
       </c>
     </row>
     <row r="158">
@@ -4563,7 +4563,7 @@
         <v>0.9722</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9797</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="160">
@@ -4664,10 +4664,10 @@
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="n">
-        <v>0.3773</v>
+        <v>0.411</v>
       </c>
       <c r="H163" t="n">
-        <v>0.3681</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="164">
@@ -4690,10 +4690,10 @@
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>0.2747</v>
+        <v>0.3388</v>
       </c>
       <c r="H164" t="n">
-        <v>0.3242</v>
+        <v>0.3768</v>
       </c>
     </row>
     <row r="165">
@@ -4716,10 +4716,10 @@
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="n">
-        <v>0.5506</v>
+        <v>0.5904</v>
       </c>
       <c r="H165" t="n">
-        <v>0.5017</v>
+        <v>0.5393</v>
       </c>
     </row>
     <row r="166">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="n">
-        <v>0.5551</v>
+        <v>0.5601</v>
       </c>
       <c r="H166" t="n">
         <v>0.572</v>
@@ -4771,7 +4771,7 @@
         <v>0.6718</v>
       </c>
       <c r="H167" t="n">
-        <v>0.6966</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="168">
@@ -4823,7 +4823,7 @@
         <v>0.7645</v>
       </c>
       <c r="H169" t="n">
-        <v>0.7528</v>
+        <v>0.7513</v>
       </c>
     </row>
     <row r="170">
@@ -4846,10 +4846,10 @@
       </c>
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
-        <v>0.7788</v>
+        <v>0.7789</v>
       </c>
       <c r="H170" t="n">
-        <v>0.7843</v>
+        <v>0.7856</v>
       </c>
     </row>
     <row r="171">
@@ -4875,7 +4875,7 @@
         <v>0.8716</v>
       </c>
       <c r="H171" t="n">
-        <v>0.8417</v>
+        <v>0.8405</v>
       </c>
     </row>
     <row r="172">
@@ -4924,10 +4924,10 @@
       </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="n">
-        <v>0.9329</v>
+        <v>0.9358</v>
       </c>
       <c r="H173" t="n">
-        <v>0.9485</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="174">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
-        <v>0.9548</v>
+        <v>0.9585</v>
       </c>
       <c r="H174" t="n">
         <v>0.9693000000000001</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>0.9527</v>
+        <v>0.954</v>
       </c>
       <c r="H175" t="n">
         <v>0.9688</v>
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.1579</v>
+        <v>0.1953</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1106</v>
+        <v>0.1505</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.0588</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H177" t="n">
-        <v>0.0617</v>
+        <v>0.0804</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.0464</v>
+        <v>0.0745</v>
       </c>
       <c r="H178" t="n">
-        <v>0.0704</v>
+        <v>0.0887</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="H179" t="n">
-        <v>0.0856</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="180">
@@ -5106,10 +5106,10 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.2663</v>
+        <v>0.3886</v>
       </c>
       <c r="H180" t="n">
-        <v>0.226</v>
+        <v>0.2915</v>
       </c>
     </row>
     <row r="181">
@@ -5132,10 +5132,10 @@
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>0.134</v>
+        <v>0.1843</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1483</v>
+        <v>0.1807</v>
       </c>
     </row>
     <row r="182">
@@ -5149,19 +5149,19 @@
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.4229</v>
+        <v>0.3522</v>
       </c>
       <c r="H182" t="n">
-        <v>0.3531</v>
+        <v>0.2878</v>
       </c>
     </row>
     <row r="183">
@@ -5184,10 +5184,10 @@
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>0.1118</v>
+        <v>0.1637</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1335</v>
+        <v>0.163</v>
       </c>
     </row>
     <row r="184">
@@ -5201,19 +5201,19 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>0.2655</v>
+        <v>0.4698</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2227</v>
+        <v>0.4327</v>
       </c>
     </row>
     <row r="185">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.6987</v>
+        <v>0.7988</v>
       </c>
       <c r="H185" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.7894</v>
       </c>
     </row>
     <row r="186">
@@ -5262,10 +5262,10 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>0.5178</v>
+        <v>0.6337</v>
       </c>
       <c r="H186" t="n">
-        <v>0.4373</v>
+        <v>0.5858</v>
       </c>
     </row>
     <row r="187">
@@ -5288,10 +5288,10 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.9086</v>
+        <v>0.9312</v>
       </c>
       <c r="H187" t="n">
-        <v>0.8989</v>
+        <v>0.9337</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.9194</v>
+        <v>0.93</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9077</v>
+        <v>0.9484</v>
       </c>
     </row>
     <row r="189">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.8569</v>
+        <v>0.8848</v>
       </c>
       <c r="H189" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="190">
@@ -5366,10 +5366,10 @@
       </c>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="n">
-        <v>0.022</v>
+        <v>0.0253</v>
       </c>
       <c r="H190" t="n">
-        <v>0.0366</v>
+        <v>0.0493</v>
       </c>
     </row>
     <row r="191">
@@ -5392,10 +5392,10 @@
       </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>0.0378</v>
+        <v>0.0644</v>
       </c>
       <c r="H191" t="n">
-        <v>0.0608</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="192">
@@ -5418,10 +5418,10 @@
       </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="n">
-        <v>0.0911</v>
+        <v>0.1046</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1204</v>
+        <v>0.1516</v>
       </c>
     </row>
     <row r="193">
@@ -5444,10 +5444,10 @@
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0949</v>
       </c>
       <c r="H193" t="n">
-        <v>0.0813</v>
+        <v>0.1101</v>
       </c>
     </row>
     <row r="194">
@@ -5470,10 +5470,10 @@
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="n">
-        <v>0.1903</v>
+        <v>0.2913</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1774</v>
+        <v>0.2481</v>
       </c>
     </row>
     <row r="195">
@@ -5496,10 +5496,10 @@
       </c>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="n">
-        <v>0.2122</v>
+        <v>0.2893</v>
       </c>
       <c r="H195" t="n">
-        <v>0.2098</v>
+        <v>0.2504</v>
       </c>
     </row>
     <row r="196">
@@ -5522,10 +5522,10 @@
       </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="n">
-        <v>0.3689</v>
+        <v>0.4358</v>
       </c>
       <c r="H196" t="n">
-        <v>0.287</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="197">
@@ -5548,10 +5548,10 @@
       </c>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="n">
-        <v>0.1123</v>
+        <v>0.1552</v>
       </c>
       <c r="H197" t="n">
-        <v>0.158</v>
+        <v>0.1936</v>
       </c>
     </row>
     <row r="198">
@@ -5574,10 +5574,10 @@
       </c>
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
-        <v>0.4148</v>
+        <v>0.4757</v>
       </c>
       <c r="H198" t="n">
-        <v>0.3523</v>
+        <v>0.4195</v>
       </c>
     </row>
     <row r="199">
@@ -5600,10 +5600,10 @@
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="n">
-        <v>0.4517</v>
+        <v>0.493</v>
       </c>
       <c r="H199" t="n">
-        <v>0.3907</v>
+        <v>0.4526</v>
       </c>
     </row>
     <row r="200">
@@ -5626,10 +5626,10 @@
       </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="n">
-        <v>0.5441</v>
+        <v>0.5992</v>
       </c>
       <c r="H200" t="n">
-        <v>0.4858</v>
+        <v>0.5534</v>
       </c>
     </row>
     <row r="201">
@@ -5652,10 +5652,10 @@
       </c>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="n">
-        <v>0.7375</v>
+        <v>0.789</v>
       </c>
       <c r="H201" t="n">
-        <v>0.7056</v>
+        <v>0.7426</v>
       </c>
     </row>
     <row r="202">
@@ -5678,10 +5678,10 @@
       </c>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>0.7376</v>
+        <v>0.7899</v>
       </c>
       <c r="H202" t="n">
-        <v>0.7107</v>
+        <v>0.7755</v>
       </c>
     </row>
     <row r="203">
@@ -5704,10 +5704,10 @@
       </c>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8994</v>
       </c>
       <c r="H203" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.8277</v>
       </c>
     </row>
     <row r="204">
@@ -5730,19 +5730,19 @@
       </c>
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>0.8269</v>
+        <v>0.8806</v>
       </c>
       <c r="H204" t="n">
-        <v>0.7664</v>
+        <v>0.8371</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -5756,19 +5756,19 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.2615</v>
+        <v>0.39</v>
       </c>
       <c r="H205" t="n">
-        <v>0.171</v>
+        <v>0.2767</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -5782,19 +5782,19 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.0916</v>
+        <v>0.1991</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0901</v>
+        <v>0.1867</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -5808,19 +5808,19 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.1058</v>
+        <v>0.2121</v>
       </c>
       <c r="H207" t="n">
-        <v>0.1016</v>
+        <v>0.1878</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -5834,19 +5834,19 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.1173</v>
+        <v>0.1902</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1332</v>
+        <v>0.1981</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -5860,19 +5860,19 @@
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>0.3963</v>
+        <v>0.594</v>
       </c>
       <c r="H209" t="n">
-        <v>0.3361</v>
+        <v>0.5177</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -5886,19 +5886,19 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.2393</v>
+        <v>0.401</v>
       </c>
       <c r="H210" t="n">
-        <v>0.2306</v>
+        <v>0.3717</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -5912,19 +5912,19 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.6469</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="H211" t="n">
-        <v>0.5770999999999999</v>
+        <v>0.6478</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -5938,45 +5938,45 @@
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.235</v>
+        <v>0.3426</v>
       </c>
       <c r="H212" t="n">
-        <v>0.2139</v>
+        <v>0.3838</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>0.386</v>
+        <v>0.7209</v>
       </c>
       <c r="H213" t="n">
-        <v>0.2791</v>
+        <v>0.6177</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -5990,19 +5990,19 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.8324</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="H214" t="n">
-        <v>0.7986</v>
+        <v>0.9369</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -6016,19 +6016,19 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.6867</v>
+        <v>0.8319</v>
       </c>
       <c r="H215" t="n">
-        <v>0.5635</v>
+        <v>0.7512</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -6042,19 +6042,19 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.9423</v>
+        <v>0.9623</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9462</v>
+        <v>0.9696</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -6068,19 +6068,19 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.9436</v>
+        <v>0.9633</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9533</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -6094,19 +6094,19 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.9109</v>
+        <v>0.9402</v>
       </c>
       <c r="H218" t="n">
-        <v>0.8788</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -6120,19 +6120,19 @@
       </c>
       <c r="F219" t="inlineStr"/>
       <c r="G219" t="n">
-        <v>0.0454</v>
+        <v>0.0941</v>
       </c>
       <c r="H219" t="n">
-        <v>0.0464</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -6146,19 +6146,19 @@
       </c>
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>0.0852</v>
+        <v>0.1739</v>
       </c>
       <c r="H220" t="n">
-        <v>0.0886</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -6172,19 +6172,19 @@
       </c>
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="n">
-        <v>0.1568</v>
+        <v>0.2951</v>
       </c>
       <c r="H221" t="n">
-        <v>0.2025</v>
+        <v>0.2963</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -6198,19 +6198,19 @@
       </c>
       <c r="F222" t="inlineStr"/>
       <c r="G222" t="n">
-        <v>0.1468</v>
+        <v>0.2451</v>
       </c>
       <c r="H222" t="n">
-        <v>0.1601</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -6224,19 +6224,19 @@
       </c>
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="n">
-        <v>0.2932</v>
+        <v>0.4414</v>
       </c>
       <c r="H223" t="n">
-        <v>0.2415</v>
+        <v>0.4159</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -6250,19 +6250,19 @@
       </c>
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="n">
-        <v>0.3654</v>
+        <v>0.4965</v>
       </c>
       <c r="H224" t="n">
-        <v>0.3005</v>
+        <v>0.472</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -6276,19 +6276,19 @@
       </c>
       <c r="F225" t="inlineStr"/>
       <c r="G225" t="n">
-        <v>0.4892</v>
+        <v>0.609</v>
       </c>
       <c r="H225" t="n">
-        <v>0.3908</v>
+        <v>0.5245</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -6302,19 +6302,19 @@
       </c>
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="n">
-        <v>0.2216</v>
+        <v>0.4022</v>
       </c>
       <c r="H226" t="n">
-        <v>0.2659</v>
+        <v>0.3856</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -6328,19 +6328,19 @@
       </c>
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="n">
-        <v>0.5453</v>
+        <v>0.6722</v>
       </c>
       <c r="H227" t="n">
-        <v>0.5044</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -6354,19 +6354,19 @@
       </c>
       <c r="F228" t="inlineStr"/>
       <c r="G228" t="n">
-        <v>0.5644</v>
+        <v>0.6977</v>
       </c>
       <c r="H228" t="n">
-        <v>0.5093</v>
+        <v>0.6249</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -6380,19 +6380,19 @@
       </c>
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="n">
-        <v>0.6691</v>
+        <v>0.7965</v>
       </c>
       <c r="H229" t="n">
-        <v>0.5511</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -6406,19 +6406,19 @@
       </c>
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.911</v>
       </c>
       <c r="H230" t="n">
-        <v>0.8102</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -6432,19 +6432,19 @@
       </c>
       <c r="F231" t="inlineStr"/>
       <c r="G231" t="n">
-        <v>0.852</v>
+        <v>0.9173</v>
       </c>
       <c r="H231" t="n">
-        <v>0.7955</v>
+        <v>0.9244</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -6458,19 +6458,19 @@
       </c>
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="n">
-        <v>0.9058</v>
+        <v>0.9427</v>
       </c>
       <c r="H232" t="n">
-        <v>0.8585</v>
+        <v>0.9286</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -6484,10 +6484,10 @@
       </c>
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="n">
-        <v>0.8941</v>
+        <v>0.9321</v>
       </c>
       <c r="H233" t="n">
-        <v>0.834</v>
+        <v>0.9426</v>
       </c>
     </row>
     <row r="234">
@@ -6510,10 +6510,10 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.4757</v>
+        <v>0.4776</v>
       </c>
       <c r="H234" t="n">
-        <v>0.4063</v>
+        <v>0.4074</v>
       </c>
     </row>
     <row r="235">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.3196</v>
+        <v>0.3177</v>
       </c>
       <c r="H235" t="n">
         <v>0.3241</v>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.3923</v>
+        <v>0.3898</v>
       </c>
       <c r="H236" t="n">
         <v>0.3131</v>
@@ -6588,10 +6588,10 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.3985</v>
+        <v>0.3941</v>
       </c>
       <c r="H237" t="n">
-        <v>0.3397</v>
+        <v>0.3375</v>
       </c>
     </row>
     <row r="238">
@@ -6614,10 +6614,10 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>0.6267</v>
+        <v>0.6272</v>
       </c>
       <c r="H238" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6647</v>
       </c>
     </row>
     <row r="239">
@@ -6640,10 +6640,10 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.5735</v>
+        <v>0.5656</v>
       </c>
       <c r="H239" t="n">
-        <v>0.5397</v>
+        <v>0.5342</v>
       </c>
     </row>
     <row r="240">
@@ -6666,10 +6666,10 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>0.8665</v>
+        <v>0.837</v>
       </c>
       <c r="H240" t="n">
-        <v>0.8882</v>
+        <v>0.8363</v>
       </c>
     </row>
     <row r="241">
@@ -6683,19 +6683,19 @@
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.7861</v>
+        <v>0.6162</v>
       </c>
       <c r="H241" t="n">
-        <v>0.765</v>
+        <v>0.6574</v>
       </c>
     </row>
     <row r="242">
@@ -6709,19 +6709,19 @@
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.6162</v>
+        <v>0.7861</v>
       </c>
       <c r="H242" t="n">
-        <v>0.6574</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="243">
@@ -6744,10 +6744,10 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.9307</v>
+        <v>0.9486</v>
       </c>
       <c r="H243" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9575</v>
       </c>
     </row>
     <row r="244">
@@ -6770,10 +6770,10 @@
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>0.8617</v>
+        <v>0.9022</v>
       </c>
       <c r="H244" t="n">
-        <v>0.8323</v>
+        <v>0.8683</v>
       </c>
     </row>
     <row r="245">
@@ -6799,7 +6799,7 @@
         <v>0.9717</v>
       </c>
       <c r="H245" t="n">
-        <v>0.9848</v>
+        <v>0.9853</v>
       </c>
     </row>
     <row r="246">
@@ -6825,7 +6825,7 @@
         <v>0.9701</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9827</v>
+        <v>0.983</v>
       </c>
     </row>
     <row r="247">
@@ -6848,10 +6848,10 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.956</v>
+        <v>0.9581</v>
       </c>
       <c r="H247" t="n">
-        <v>0.9737</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="n">
-        <v>0.1752</v>
+        <v>0.1723</v>
       </c>
       <c r="H248" t="n">
         <v>0.1153</v>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="n">
-        <v>0.4355</v>
+        <v>0.4675</v>
       </c>
       <c r="H250" t="n">
         <v>0.4012</v>
@@ -6952,10 +6952,10 @@
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="n">
-        <v>0.3341</v>
+        <v>0.4089</v>
       </c>
       <c r="H251" t="n">
-        <v>0.3617</v>
+        <v>0.3966</v>
       </c>
     </row>
     <row r="252">
@@ -6978,10 +6978,10 @@
       </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="n">
-        <v>0.5865</v>
+        <v>0.6217</v>
       </c>
       <c r="H252" t="n">
-        <v>0.5574</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="253">
@@ -7059,7 +7059,7 @@
         <v>0.5725</v>
       </c>
       <c r="H255" t="n">
-        <v>0.4723</v>
+        <v>0.4698</v>
       </c>
     </row>
     <row r="256">
@@ -7137,7 +7137,7 @@
         <v>0.8651</v>
       </c>
       <c r="H258" t="n">
-        <v>0.8286</v>
+        <v>0.8347</v>
       </c>
     </row>
     <row r="259">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="n">
-        <v>0.9334</v>
+        <v>0.9343</v>
       </c>
       <c r="H259" t="n">
         <v>0.9422</v>
@@ -7186,10 +7186,10 @@
       </c>
       <c r="F260" t="inlineStr"/>
       <c r="G260" t="n">
-        <v>0.9398</v>
+        <v>0.9416</v>
       </c>
       <c r="H260" t="n">
-        <v>0.949</v>
+        <v>0.9563</v>
       </c>
     </row>
     <row r="261">
@@ -7212,10 +7212,10 @@
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="n">
-        <v>0.9594</v>
+        <v>0.9606</v>
       </c>
       <c r="H261" t="n">
-        <v>0.9757</v>
+        <v>0.9764</v>
       </c>
     </row>
     <row r="262">
@@ -7241,16 +7241,16 @@
         <v>0.9540999999999999</v>
       </c>
       <c r="H262" t="n">
-        <v>0.9709</v>
+        <v>0.9712</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -7264,19 +7264,19 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.39</v>
+        <v>0.2615</v>
       </c>
       <c r="H263" t="n">
-        <v>0.2708</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -7290,19 +7290,19 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.1991</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1867</v>
+        <v>0.0887</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -7316,19 +7316,19 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.2121</v>
+        <v>0.1041</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1878</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -7342,19 +7342,19 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.1941</v>
+        <v>0.116</v>
       </c>
       <c r="H266" t="n">
-        <v>0.2009</v>
+        <v>0.1298</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -7368,19 +7368,19 @@
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>0.5611</v>
+        <v>0.4126</v>
       </c>
       <c r="H267" t="n">
-        <v>0.4893</v>
+        <v>0.3553</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -7394,19 +7394,19 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.401</v>
+        <v>0.2393</v>
       </c>
       <c r="H268" t="n">
-        <v>0.3717</v>
+        <v>0.2306</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -7420,45 +7420,45 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>0.7773</v>
+        <v>0.5673</v>
       </c>
       <c r="H269" t="n">
-        <v>0.7345</v>
+        <v>0.5302</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="n">
-        <v>0.7209</v>
+        <v>0.3823</v>
       </c>
       <c r="H270" t="n">
-        <v>0.614</v>
+        <v>0.2791</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -7472,19 +7472,19 @@
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.3426</v>
+        <v>0.235</v>
       </c>
       <c r="H271" t="n">
-        <v>0.3838</v>
+        <v>0.2139</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -7498,19 +7498,19 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.8909</v>
+        <v>0.8708</v>
       </c>
       <c r="H272" t="n">
-        <v>0.9231</v>
+        <v>0.8638</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -7524,19 +7524,19 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.7965</v>
+        <v>0.7207</v>
       </c>
       <c r="H273" t="n">
-        <v>0.6978</v>
+        <v>0.6079</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -7550,19 +7550,19 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.9623</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H274" t="n">
-        <v>0.9696</v>
+        <v>0.9474</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -7576,19 +7576,19 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.9633</v>
+        <v>0.9447</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9745</v>
+        <v>0.954</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -7602,19 +7602,19 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.9402</v>
+        <v>0.9109</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9525</v>
+        <v>0.8788</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -7628,19 +7628,19 @@
       </c>
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="n">
-        <v>0.0941</v>
+        <v>0.0439</v>
       </c>
       <c r="H277" t="n">
-        <v>0.078</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -7654,19 +7654,19 @@
       </c>
       <c r="F278" t="inlineStr"/>
       <c r="G278" t="n">
-        <v>0.1739</v>
+        <v>0.0852</v>
       </c>
       <c r="H278" t="n">
-        <v>0.1648</v>
+        <v>0.0871</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -7680,19 +7680,19 @@
       </c>
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="n">
-        <v>0.2806</v>
+        <v>0.1579</v>
       </c>
       <c r="H279" t="n">
-        <v>0.2756</v>
+        <v>0.2137</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -7706,19 +7706,19 @@
       </c>
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="n">
-        <v>0.1998</v>
+        <v>0.156</v>
       </c>
       <c r="H280" t="n">
-        <v>0.2152</v>
+        <v>0.1782</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -7732,19 +7732,19 @@
       </c>
       <c r="F281" t="inlineStr"/>
       <c r="G281" t="n">
-        <v>0.4168</v>
+        <v>0.3423</v>
       </c>
       <c r="H281" t="n">
-        <v>0.3958</v>
+        <v>0.2827</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -7758,19 +7758,19 @@
       </c>
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="n">
-        <v>0.4965</v>
+        <v>0.3654</v>
       </c>
       <c r="H282" t="n">
-        <v>0.472</v>
+        <v>0.3005</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -7784,19 +7784,19 @@
       </c>
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="n">
-        <v>0.609</v>
+        <v>0.4892</v>
       </c>
       <c r="H283" t="n">
-        <v>0.5245</v>
+        <v>0.3908</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -7810,19 +7810,19 @@
       </c>
       <c r="F284" t="inlineStr"/>
       <c r="G284" t="n">
-        <v>0.4022</v>
+        <v>0.2172</v>
       </c>
       <c r="H284" t="n">
-        <v>0.3856</v>
+        <v>0.2659</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -7836,19 +7836,19 @@
       </c>
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="n">
-        <v>0.6722</v>
+        <v>0.5453</v>
       </c>
       <c r="H285" t="n">
-        <v>0.6333</v>
+        <v>0.5044</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -7862,19 +7862,19 @@
       </c>
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="n">
-        <v>0.6974</v>
+        <v>0.5644</v>
       </c>
       <c r="H286" t="n">
-        <v>0.6249</v>
+        <v>0.4911</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -7888,19 +7888,19 @@
       </c>
       <c r="F287" t="inlineStr"/>
       <c r="G287" t="n">
-        <v>0.7965</v>
+        <v>0.6691</v>
       </c>
       <c r="H287" t="n">
-        <v>0.6747</v>
+        <v>0.5511</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -7914,19 +7914,19 @@
       </c>
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="n">
-        <v>0.9104</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="H288" t="n">
-        <v>0.9029</v>
+        <v>0.8101</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -7940,19 +7940,19 @@
       </c>
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="n">
-        <v>0.9164</v>
+        <v>0.8548</v>
       </c>
       <c r="H289" t="n">
-        <v>0.9217</v>
+        <v>0.8004</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -7966,19 +7966,19 @@
       </c>
       <c r="F290" t="inlineStr"/>
       <c r="G290" t="n">
-        <v>0.9427</v>
+        <v>0.9062</v>
       </c>
       <c r="H290" t="n">
-        <v>0.9286</v>
+        <v>0.8585</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -7992,10 +7992,10 @@
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="n">
-        <v>0.9286</v>
+        <v>0.8954</v>
       </c>
       <c r="H291" t="n">
-        <v>0.9426</v>
+        <v>0.834</v>
       </c>
     </row>
     <row r="292">
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.0771</v>
+        <v>0.0398</v>
       </c>
       <c r="H292" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.0295</v>
+        <v>0.0248</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0304</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.0298</v>
+        <v>0.0248</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0379</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.0368</v>
+        <v>0.0321</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0337</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="296">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.0936</v>
+        <v>0.0818</v>
       </c>
       <c r="H296" t="n">
-        <v>0.1195</v>
+        <v>0.09080000000000001</v>
       </c>
     </row>
     <row r="297">
@@ -8148,10 +8148,10 @@
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0594</v>
       </c>
       <c r="H297" t="n">
-        <v>0.0974</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.3705</v>
+        <v>0.2106</v>
       </c>
       <c r="H298" t="n">
-        <v>0.3013</v>
+        <v>0.2012</v>
       </c>
     </row>
     <row r="299">
@@ -8191,19 +8191,19 @@
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.2014</v>
+        <v>0.0631</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1676</v>
+        <v>0.0771</v>
       </c>
     </row>
     <row r="300">
@@ -8226,10 +8226,10 @@
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.065</v>
+        <v>0.0425</v>
       </c>
       <c r="H300" t="n">
-        <v>0.0693</v>
+        <v>0.0514</v>
       </c>
     </row>
     <row r="301">
@@ -8243,19 +8243,19 @@
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.0769</v>
+        <v>0.1362</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1091</v>
+        <v>0.1292</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.3257</v>
+        <v>0.3005</v>
       </c>
       <c r="H302" t="n">
-        <v>0.3007</v>
+        <v>0.2918</v>
       </c>
     </row>
     <row r="303">
@@ -8304,10 +8304,10 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.79</v>
+        <v>0.7435</v>
       </c>
       <c r="H303" t="n">
-        <v>0.8092</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="304">
@@ -8330,10 +8330,10 @@
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.8414</v>
+        <v>0.7816</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7884</v>
+        <v>0.7514999999999999</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.6732</v>
+        <v>0.5966</v>
       </c>
       <c r="H305" t="n">
-        <v>0.6353</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="306">
@@ -8382,10 +8382,10 @@
       </c>
       <c r="F306" t="inlineStr"/>
       <c r="G306" t="n">
-        <v>0.0228</v>
+        <v>0.0209</v>
       </c>
       <c r="H306" t="n">
-        <v>0.0268</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="307">
@@ -8408,10 +8408,10 @@
       </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="n">
-        <v>0.0285</v>
+        <v>0.0234</v>
       </c>
       <c r="H307" t="n">
-        <v>0.0399</v>
+        <v>0.0313</v>
       </c>
     </row>
     <row r="308">
@@ -8434,10 +8434,10 @@
       </c>
       <c r="F308" t="inlineStr"/>
       <c r="G308" t="n">
-        <v>0.0495</v>
+        <v>0.0486</v>
       </c>
       <c r="H308" t="n">
-        <v>0.0431</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="309">
@@ -8460,10 +8460,10 @@
       </c>
       <c r="F309" t="inlineStr"/>
       <c r="G309" t="n">
-        <v>0.0374</v>
+        <v>0.0379</v>
       </c>
       <c r="H309" t="n">
-        <v>0.0384</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="310">
@@ -8486,10 +8486,10 @@
       </c>
       <c r="F310" t="inlineStr"/>
       <c r="G310" t="n">
-        <v>0.0682</v>
+        <v>0.0604</v>
       </c>
       <c r="H310" t="n">
-        <v>0.0793</v>
+        <v>0.0634</v>
       </c>
     </row>
     <row r="311">
@@ -8512,10 +8512,10 @@
       </c>
       <c r="F311" t="inlineStr"/>
       <c r="G311" t="n">
-        <v>0.0896</v>
+        <v>0.067</v>
       </c>
       <c r="H311" t="n">
-        <v>0.092</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="312">
@@ -8538,10 +8538,10 @@
       </c>
       <c r="F312" t="inlineStr"/>
       <c r="G312" t="n">
-        <v>0.148</v>
+        <v>0.0944</v>
       </c>
       <c r="H312" t="n">
-        <v>0.1242</v>
+        <v>0.1074</v>
       </c>
     </row>
     <row r="313">
@@ -8564,10 +8564,10 @@
       </c>
       <c r="F313" t="inlineStr"/>
       <c r="G313" t="n">
-        <v>0.0586</v>
+        <v>0.0505</v>
       </c>
       <c r="H313" t="n">
-        <v>0.0592</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="314">
@@ -8590,10 +8590,10 @@
       </c>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="n">
-        <v>0.2457</v>
+        <v>0.1721</v>
       </c>
       <c r="H314" t="n">
-        <v>0.2051</v>
+        <v>0.1739</v>
       </c>
     </row>
     <row r="315">
@@ -8616,10 +8616,10 @@
       </c>
       <c r="F315" t="inlineStr"/>
       <c r="G315" t="n">
-        <v>0.2508</v>
+        <v>0.1744</v>
       </c>
       <c r="H315" t="n">
-        <v>0.1857</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="316">
@@ -8642,10 +8642,10 @@
       </c>
       <c r="F316" t="inlineStr"/>
       <c r="G316" t="n">
-        <v>0.3076</v>
+        <v>0.2219</v>
       </c>
       <c r="H316" t="n">
-        <v>0.292</v>
+        <v>0.2612</v>
       </c>
     </row>
     <row r="317">
@@ -8668,10 +8668,10 @@
       </c>
       <c r="F317" t="inlineStr"/>
       <c r="G317" t="n">
-        <v>0.5646</v>
+        <v>0.4906</v>
       </c>
       <c r="H317" t="n">
-        <v>0.5246</v>
+        <v>0.4641</v>
       </c>
     </row>
     <row r="318">
@@ -8694,10 +8694,10 @@
       </c>
       <c r="F318" t="inlineStr"/>
       <c r="G318" t="n">
-        <v>0.5453</v>
+        <v>0.5004</v>
       </c>
       <c r="H318" t="n">
-        <v>0.5366</v>
+        <v>0.4826</v>
       </c>
     </row>
     <row r="319">
@@ -8720,10 +8720,10 @@
       </c>
       <c r="F319" t="inlineStr"/>
       <c r="G319" t="n">
-        <v>0.6751</v>
+        <v>0.5945</v>
       </c>
       <c r="H319" t="n">
-        <v>0.645</v>
+        <v>0.5873</v>
       </c>
     </row>
     <row r="320">
@@ -8746,10 +8746,10 @@
       </c>
       <c r="F320" t="inlineStr"/>
       <c r="G320" t="n">
-        <v>0.6661</v>
+        <v>0.5929</v>
       </c>
       <c r="H320" t="n">
-        <v>0.6623</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="321">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.2089</v>
+        <v>0.1538</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1611</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="322">
@@ -8798,10 +8798,10 @@
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.049</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0721</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="323">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.1207</v>
+        <v>0.0702</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0653</v>
+        <v>0.0502</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.093</v>
+        <v>0.0608</v>
       </c>
       <c r="H324" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.2912</v>
+        <v>0.2528</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1995</v>
+        <v>0.1752</v>
       </c>
     </row>
     <row r="326">
@@ -8902,10 +8902,10 @@
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="n">
-        <v>0.15</v>
+        <v>0.1037</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1417</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="327">
@@ -8928,10 +8928,10 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>0.5627</v>
+        <v>0.4142</v>
       </c>
       <c r="H327" t="n">
-        <v>0.4822</v>
+        <v>0.3663</v>
       </c>
     </row>
     <row r="328">
@@ -8945,19 +8945,19 @@
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.4365</v>
+        <v>0.2488</v>
       </c>
       <c r="H328" t="n">
-        <v>0.3133</v>
+        <v>0.1681</v>
       </c>
     </row>
     <row r="329">
@@ -8980,10 +8980,10 @@
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>0.1677</v>
+        <v>0.1317</v>
       </c>
       <c r="H329" t="n">
-        <v>0.1383</v>
+        <v>0.0978</v>
       </c>
     </row>
     <row r="330">
@@ -8997,19 +8997,19 @@
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.3022</v>
+        <v>0.3921</v>
       </c>
       <c r="H330" t="n">
-        <v>0.2035</v>
+        <v>0.2793</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.6993</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="H331" t="n">
-        <v>0.6743</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.8884</v>
+        <v>0.8752</v>
       </c>
       <c r="H332" t="n">
-        <v>0.9155</v>
+        <v>0.9043</v>
       </c>
     </row>
     <row r="333">
@@ -9084,10 +9084,10 @@
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.8983</v>
       </c>
       <c r="H333" t="n">
-        <v>0.9216</v>
+        <v>0.8999</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.8142</v>
+        <v>0.7943</v>
       </c>
       <c r="H334" t="n">
-        <v>0.8377</v>
+        <v>0.767</v>
       </c>
     </row>
     <row r="335">
@@ -9136,10 +9136,10 @@
       </c>
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="n">
-        <v>0.0418</v>
+        <v>0.0278</v>
       </c>
       <c r="H335" t="n">
-        <v>0.0511</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="336">
@@ -9162,10 +9162,10 @@
       </c>
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="n">
-        <v>0.099</v>
+        <v>0.0596</v>
       </c>
       <c r="H336" t="n">
-        <v>0.0769</v>
+        <v>0.0614</v>
       </c>
     </row>
     <row r="337">
@@ -9188,10 +9188,10 @@
       </c>
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="n">
-        <v>0.0772</v>
+        <v>0.0644</v>
       </c>
       <c r="H337" t="n">
-        <v>0.1024</v>
+        <v>0.07870000000000001</v>
       </c>
     </row>
     <row r="338">
@@ -9214,10 +9214,10 @@
       </c>
       <c r="F338" t="inlineStr"/>
       <c r="G338" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0733</v>
       </c>
       <c r="H338" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="339">
@@ -9240,10 +9240,10 @@
       </c>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
-        <v>0.2305</v>
+        <v>0.2112</v>
       </c>
       <c r="H339" t="n">
-        <v>0.1749</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="340">
@@ -9266,10 +9266,10 @@
       </c>
       <c r="F340" t="inlineStr"/>
       <c r="G340" t="n">
-        <v>0.2562</v>
+        <v>0.2195</v>
       </c>
       <c r="H340" t="n">
-        <v>0.2046</v>
+        <v>0.1579</v>
       </c>
     </row>
     <row r="341">
@@ -9292,10 +9292,10 @@
       </c>
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="n">
-        <v>0.3594</v>
+        <v>0.3082</v>
       </c>
       <c r="H341" t="n">
-        <v>0.2843</v>
+        <v>0.2191</v>
       </c>
     </row>
     <row r="342">
@@ -9318,10 +9318,10 @@
       </c>
       <c r="F342" t="inlineStr"/>
       <c r="G342" t="n">
-        <v>0.16</v>
+        <v>0.1169</v>
       </c>
       <c r="H342" t="n">
-        <v>0.132</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="343">
@@ -9344,10 +9344,10 @@
       </c>
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="n">
-        <v>0.39</v>
+        <v>0.3421</v>
       </c>
       <c r="H343" t="n">
-        <v>0.35</v>
+        <v>0.2944</v>
       </c>
     </row>
     <row r="344">
@@ -9370,10 +9370,10 @@
       </c>
       <c r="F344" t="inlineStr"/>
       <c r="G344" t="n">
-        <v>0.426</v>
+        <v>0.3886</v>
       </c>
       <c r="H344" t="n">
-        <v>0.3715</v>
+        <v>0.3191</v>
       </c>
     </row>
     <row r="345">
@@ -9396,10 +9396,10 @@
       </c>
       <c r="F345" t="inlineStr"/>
       <c r="G345" t="n">
-        <v>0.5324</v>
+        <v>0.4955</v>
       </c>
       <c r="H345" t="n">
-        <v>0.4737</v>
+        <v>0.4287</v>
       </c>
     </row>
     <row r="346">
@@ -9422,10 +9422,10 @@
       </c>
       <c r="F346" t="inlineStr"/>
       <c r="G346" t="n">
-        <v>0.7464</v>
+        <v>0.6984</v>
       </c>
       <c r="H346" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6106</v>
       </c>
     </row>
     <row r="347">
@@ -9448,10 +9448,10 @@
       </c>
       <c r="F347" t="inlineStr"/>
       <c r="G347" t="n">
-        <v>0.7043</v>
+        <v>0.66</v>
       </c>
       <c r="H347" t="n">
-        <v>0.7151</v>
+        <v>0.6493</v>
       </c>
     </row>
     <row r="348">
@@ -9474,10 +9474,10 @@
       </c>
       <c r="F348" t="inlineStr"/>
       <c r="G348" t="n">
-        <v>0.8495</v>
+        <v>0.8147</v>
       </c>
       <c r="H348" t="n">
-        <v>0.8031</v>
+        <v>0.7344000000000001</v>
       </c>
     </row>
     <row r="349">
@@ -9500,10 +9500,10 @@
       </c>
       <c r="F349" t="inlineStr"/>
       <c r="G349" t="n">
-        <v>0.8117</v>
+        <v>0.765</v>
       </c>
       <c r="H349" t="n">
-        <v>0.8055</v>
+        <v>0.7497</v>
       </c>
     </row>
     <row r="350">
@@ -9682,10 +9682,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.1011</v>
+        <v>0.0663</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0914</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="357">
@@ -9699,19 +9699,19 @@
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.0538</v>
+        <v>0.0304</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0577</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="358">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>0.0152</v>
+        <v>0.0147</v>
       </c>
       <c r="H358" t="n">
         <v>0.0283</v>
@@ -9751,19 +9751,19 @@
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.0304</v>
+        <v>0.0526</v>
       </c>
       <c r="H359" t="n">
-        <v>0.0377</v>
+        <v>0.0559</v>
       </c>
     </row>
     <row r="360">
@@ -9786,10 +9786,10 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.1908</v>
+        <v>0.2664</v>
       </c>
       <c r="H360" t="n">
-        <v>0.21</v>
+        <v>0.2565</v>
       </c>
     </row>
     <row r="361">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1116</v>
+        <v>0.1248</v>
       </c>
     </row>
     <row r="362">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="n">
-        <v>0.0153</v>
+        <v>0.0148</v>
       </c>
       <c r="H365" t="n">
         <v>0.0233</v>
@@ -9994,10 +9994,10 @@
       </c>
       <c r="F368" t="inlineStr"/>
       <c r="G368" t="n">
-        <v>0.0251</v>
+        <v>0.0266</v>
       </c>
       <c r="H368" t="n">
-        <v>0.0279</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="369">
@@ -10023,7 +10023,7 @@
         <v>0.0337</v>
       </c>
       <c r="H369" t="n">
-        <v>0.0352</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="370">
@@ -10046,10 +10046,10 @@
       </c>
       <c r="F370" t="inlineStr"/>
       <c r="G370" t="n">
-        <v>0.0341</v>
+        <v>0.0338</v>
       </c>
       <c r="H370" t="n">
-        <v>0.0444</v>
+        <v>0.0431</v>
       </c>
     </row>
     <row r="371">
@@ -10124,7 +10124,7 @@
       </c>
       <c r="F373" t="inlineStr"/>
       <c r="G373" t="n">
-        <v>0.0621</v>
+        <v>0.0616</v>
       </c>
       <c r="H373" t="n">
         <v>0.0609</v>
@@ -10176,7 +10176,7 @@
       </c>
       <c r="F375" t="inlineStr"/>
       <c r="G375" t="n">
-        <v>0.2367</v>
+        <v>0.2342</v>
       </c>
       <c r="H375" t="n">
         <v>0.2562</v>
@@ -10202,10 +10202,10 @@
       </c>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="n">
-        <v>0.26</v>
+        <v>0.2637</v>
       </c>
       <c r="H376" t="n">
-        <v>0.2472</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="377">
@@ -10231,7 +10231,7 @@
         <v>0.3792</v>
       </c>
       <c r="H377" t="n">
-        <v>0.3661</v>
+        <v>0.3649</v>
       </c>
     </row>
     <row r="378">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="F378" t="inlineStr"/>
       <c r="G378" t="n">
-        <v>0.3595</v>
+        <v>0.3613</v>
       </c>
       <c r="H378" t="n">
         <v>0.3205</v>
@@ -10280,7 +10280,7 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.0296</v>
+        <v>0.0291</v>
       </c>
       <c r="H379" t="n">
         <v>0.0449</v>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.0176</v>
+        <v>0.0168</v>
       </c>
       <c r="H381" t="n">
         <v>0.0186</v>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>0.0132</v>
+        <v>0.0134</v>
       </c>
       <c r="H382" t="n">
         <v>0.0208</v>
@@ -10384,10 +10384,10 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.0233</v>
+        <v>0.0237</v>
       </c>
       <c r="H383" t="n">
-        <v>0.031</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="384">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>0.0203</v>
+        <v>0.02</v>
       </c>
       <c r="H384" t="n">
         <v>0.0278</v>
@@ -10436,10 +10436,10 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0516</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0806</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="386">
@@ -10453,19 +10453,19 @@
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.0467</v>
+        <v>0.0255</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0564</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="387">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.0173</v>
+        <v>0.017</v>
       </c>
       <c r="H387" t="n">
         <v>0.0299</v>
@@ -10505,19 +10505,19 @@
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.0255</v>
+        <v>0.046</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0367</v>
+        <v>0.0553</v>
       </c>
     </row>
     <row r="389">
@@ -10540,10 +10540,10 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.2116</v>
+        <v>0.2485</v>
       </c>
       <c r="H389" t="n">
-        <v>0.1586</v>
+        <v>0.2184</v>
       </c>
     </row>
     <row r="390">
@@ -10566,10 +10566,10 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.0784</v>
+        <v>0.1001</v>
       </c>
       <c r="H390" t="n">
-        <v>0.0801</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="391">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>0.3738</v>
+        <v>0.3644</v>
       </c>
       <c r="H392" t="n">
         <v>0.2686</v>
@@ -10748,10 +10748,10 @@
       </c>
       <c r="F397" t="inlineStr"/>
       <c r="G397" t="n">
-        <v>0.0231</v>
+        <v>0.0253</v>
       </c>
       <c r="H397" t="n">
-        <v>0.0332</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="398">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="F399" t="inlineStr"/>
       <c r="G399" t="n">
-        <v>0.03</v>
+        <v>0.0283</v>
       </c>
       <c r="H399" t="n">
         <v>0.0353</v>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="F400" t="inlineStr"/>
       <c r="G400" t="n">
-        <v>0.0141</v>
+        <v>0.0136</v>
       </c>
       <c r="H400" t="n">
         <v>0.02</v>
@@ -10852,10 +10852,10 @@
       </c>
       <c r="F401" t="inlineStr"/>
       <c r="G401" t="n">
-        <v>0.05</v>
+        <v>0.049</v>
       </c>
       <c r="H401" t="n">
-        <v>0.0576</v>
+        <v>0.0558</v>
       </c>
     </row>
     <row r="402">
@@ -10881,7 +10881,7 @@
         <v>0.0511</v>
       </c>
       <c r="H402" t="n">
-        <v>0.0602</v>
+        <v>0.0575</v>
       </c>
     </row>
     <row r="403">
@@ -10904,10 +10904,10 @@
       </c>
       <c r="F403" t="inlineStr"/>
       <c r="G403" t="n">
-        <v>0.0732</v>
+        <v>0.0717</v>
       </c>
       <c r="H403" t="n">
-        <v>0.0759</v>
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="404">
@@ -10956,10 +10956,10 @@
       </c>
       <c r="F405" t="inlineStr"/>
       <c r="G405" t="n">
-        <v>0.2311</v>
+        <v>0.2509</v>
       </c>
       <c r="H405" t="n">
-        <v>0.1615</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="406">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="n">
-        <v>0.3104</v>
+        <v>0.3126</v>
       </c>
       <c r="H406" t="n">
         <v>0.3069</v>
@@ -11037,7 +11037,7 @@
         <v>0.0464</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0556</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="409">
@@ -11060,10 +11060,10 @@
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="H409" t="n">
         <v>0.0206</v>
-      </c>
-      <c r="H409" t="n">
-        <v>0.021</v>
       </c>
     </row>
     <row r="410">
@@ -11089,7 +11089,7 @@
         <v>0.0177</v>
       </c>
       <c r="H410" t="n">
-        <v>0.026</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="411">
@@ -11112,7 +11112,7 @@
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
-        <v>0.0185</v>
+        <v>0.0178</v>
       </c>
       <c r="H411" t="n">
         <v>0.0247</v>
@@ -11138,10 +11138,10 @@
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>0.0471</v>
+        <v>0.0476</v>
       </c>
       <c r="H412" t="n">
-        <v>0.0579</v>
+        <v>0.0617</v>
       </c>
     </row>
     <row r="413">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.2344</v>
+        <v>0.156</v>
       </c>
       <c r="H414" t="n">
-        <v>0.1431</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="415">
@@ -11207,19 +11207,19 @@
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.1212</v>
+        <v>0.047</v>
       </c>
       <c r="H415" t="n">
-        <v>0.0891</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="416">
@@ -11242,10 +11242,10 @@
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.0263</v>
+        <v>0.0257</v>
       </c>
       <c r="H416" t="n">
-        <v>0.044</v>
+        <v>0.0419</v>
       </c>
     </row>
     <row r="417">
@@ -11259,19 +11259,19 @@
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.0475</v>
+        <v>0.1212</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0598</v>
+        <v>0.0891</v>
       </c>
     </row>
     <row r="418">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.3647</v>
+        <v>0.4186</v>
       </c>
       <c r="H418" t="n">
-        <v>0.3268</v>
+        <v>0.4034</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.1623</v>
+        <v>0.233</v>
       </c>
       <c r="H419" t="n">
-        <v>0.1858</v>
+        <v>0.2057</v>
       </c>
     </row>
     <row r="420">
@@ -11375,7 +11375,7 @@
         <v>0.7314000000000001</v>
       </c>
       <c r="H421" t="n">
-        <v>0.6262</v>
+        <v>0.6356000000000001</v>
       </c>
     </row>
     <row r="422">
@@ -11427,7 +11427,7 @@
         <v>0.0188</v>
       </c>
       <c r="H423" t="n">
-        <v>0.0316</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="424">
@@ -11476,10 +11476,10 @@
       </c>
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="n">
-        <v>0.0193</v>
+        <v>0.0191</v>
       </c>
       <c r="H425" t="n">
-        <v>0.0255</v>
+        <v>0.0267</v>
       </c>
     </row>
     <row r="426">
@@ -11502,10 +11502,10 @@
       </c>
       <c r="F426" t="inlineStr"/>
       <c r="G426" t="n">
-        <v>0.0437</v>
+        <v>0.0483</v>
       </c>
       <c r="H426" t="n">
-        <v>0.0408</v>
+        <v>0.0515</v>
       </c>
     </row>
     <row r="427">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="n">
-        <v>0.052</v>
+        <v>0.0493</v>
       </c>
       <c r="H427" t="n">
         <v>0.0499</v>
@@ -11580,10 +11580,10 @@
       </c>
       <c r="F429" t="inlineStr"/>
       <c r="G429" t="n">
-        <v>0.0264</v>
+        <v>0.0258</v>
       </c>
       <c r="H429" t="n">
-        <v>0.0351</v>
+        <v>0.0347</v>
       </c>
     </row>
     <row r="430">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="F430" t="inlineStr"/>
       <c r="G430" t="n">
-        <v>0.1197</v>
+        <v>0.1156</v>
       </c>
       <c r="H430" t="n">
         <v>0.1057</v>
@@ -11635,7 +11635,7 @@
         <v>0.1285</v>
       </c>
       <c r="H431" t="n">
-        <v>0.1042</v>
+        <v>0.1035</v>
       </c>
     </row>
     <row r="432">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="F432" t="inlineStr"/>
       <c r="G432" t="n">
-        <v>0.1688</v>
+        <v>0.1664</v>
       </c>
       <c r="H432" t="n">
         <v>0.1853</v>
@@ -11710,10 +11710,10 @@
       </c>
       <c r="F434" t="inlineStr"/>
       <c r="G434" t="n">
-        <v>0.4171</v>
+        <v>0.4181</v>
       </c>
       <c r="H434" t="n">
-        <v>0.3154</v>
+        <v>0.3186</v>
       </c>
     </row>
     <row r="435">
@@ -11791,7 +11791,7 @@
         <v>0.8473000000000001</v>
       </c>
       <c r="H437" t="n">
-        <v>0.84</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="438">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="F439" t="inlineStr"/>
       <c r="G439" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7617</v>
       </c>
       <c r="H439" t="n">
         <v>0.6904</v>
@@ -11892,10 +11892,10 @@
       </c>
       <c r="F441" t="inlineStr"/>
       <c r="G441" t="n">
-        <v>0.9175</v>
+        <v>0.9193</v>
       </c>
       <c r="H441" t="n">
-        <v>0.9096</v>
+        <v>0.9185</v>
       </c>
     </row>
     <row r="442">
@@ -11944,10 +11944,10 @@
       </c>
       <c r="F443" t="inlineStr"/>
       <c r="G443" t="n">
-        <v>0.9634</v>
+        <v>0.9507</v>
       </c>
       <c r="H443" t="n">
-        <v>0.978</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="444">
@@ -11961,19 +11961,19 @@
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
       <c r="G444" t="n">
-        <v>0.9536</v>
+        <v>0.922</v>
       </c>
       <c r="H444" t="n">
-        <v>0.9546</v>
+        <v>0.9059</v>
       </c>
     </row>
     <row r="445">
@@ -11999,7 +11999,7 @@
         <v>0.8847</v>
       </c>
       <c r="H445" t="n">
-        <v>0.8248</v>
+        <v>0.8277</v>
       </c>
     </row>
     <row r="446">
@@ -12013,19 +12013,19 @@
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
       <c r="G446" t="n">
-        <v>0.922</v>
+        <v>0.9536</v>
       </c>
       <c r="H446" t="n">
-        <v>0.9059</v>
+        <v>0.9560999999999999</v>
       </c>
     </row>
     <row r="447">
@@ -12048,10 +12048,10 @@
       </c>
       <c r="F447" t="inlineStr"/>
       <c r="G447" t="n">
-        <v>0.9732</v>
+        <v>0.9748</v>
       </c>
       <c r="H447" t="n">
-        <v>0.9772</v>
+        <v>0.9791</v>
       </c>
     </row>
     <row r="448">
@@ -12074,10 +12074,10 @@
       </c>
       <c r="F448" t="inlineStr"/>
       <c r="G448" t="n">
-        <v>0.9489</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="H448" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="449">
@@ -12178,10 +12178,10 @@
       </c>
       <c r="F452" t="inlineStr"/>
       <c r="G452" t="n">
-        <v>0.7321</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="H452" t="n">
-        <v>0.6343</v>
+        <v>0.6397</v>
       </c>
     </row>
     <row r="453">
@@ -12204,10 +12204,10 @@
       </c>
       <c r="F453" t="inlineStr"/>
       <c r="G453" t="n">
-        <v>0.7657</v>
+        <v>0.7741</v>
       </c>
       <c r="H453" t="n">
-        <v>0.7311</v>
+        <v>0.7386</v>
       </c>
     </row>
     <row r="454">
@@ -12230,10 +12230,10 @@
       </c>
       <c r="F454" t="inlineStr"/>
       <c r="G454" t="n">
-        <v>0.725</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="H454" t="n">
-        <v>0.6601</v>
+        <v>0.7084</v>
       </c>
     </row>
     <row r="455">
@@ -12256,10 +12256,10 @@
       </c>
       <c r="F455" t="inlineStr"/>
       <c r="G455" t="n">
-        <v>0.9099</v>
+        <v>0.9196</v>
       </c>
       <c r="H455" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.9034</v>
       </c>
     </row>
     <row r="456">
@@ -12285,7 +12285,7 @@
         <v>0.9172</v>
       </c>
       <c r="H456" t="n">
-        <v>0.9022</v>
+        <v>0.9035</v>
       </c>
     </row>
     <row r="457">
@@ -12311,7 +12311,7 @@
         <v>0.927</v>
       </c>
       <c r="H457" t="n">
-        <v>0.9439</v>
+        <v>0.9442</v>
       </c>
     </row>
     <row r="458">
@@ -12360,10 +12360,10 @@
       </c>
       <c r="F459" t="inlineStr"/>
       <c r="G459" t="n">
-        <v>0.9372</v>
+        <v>0.9393</v>
       </c>
       <c r="H459" t="n">
-        <v>0.9515</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="460">
@@ -12412,10 +12412,10 @@
       </c>
       <c r="F461" t="inlineStr"/>
       <c r="G461" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H461" t="n">
-        <v>0.9627</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="462">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="F462" t="inlineStr"/>
       <c r="G462" t="n">
-        <v>0.9666</v>
+        <v>0.967</v>
       </c>
       <c r="H462" t="n">
         <v>0.9842</v>
@@ -12464,10 +12464,10 @@
       </c>
       <c r="F463" t="inlineStr"/>
       <c r="G463" t="n">
-        <v>0.9747</v>
+        <v>0.9778</v>
       </c>
       <c r="H463" t="n">
-        <v>0.985</v>
+        <v>0.9857</v>
       </c>
     </row>
     <row r="464">
@@ -12545,7 +12545,7 @@
         <v>0.6619</v>
       </c>
       <c r="H466" t="n">
-        <v>0.6753</v>
+        <v>0.6803</v>
       </c>
     </row>
     <row r="467">
@@ -12571,7 +12571,7 @@
         <v>0.5382</v>
       </c>
       <c r="H467" t="n">
-        <v>0.5483</v>
+        <v>0.5478</v>
       </c>
     </row>
     <row r="468">
@@ -12623,7 +12623,7 @@
         <v>0.6183</v>
       </c>
       <c r="H469" t="n">
-        <v>0.5527</v>
+        <v>0.5423</v>
       </c>
     </row>
     <row r="470">
@@ -12646,10 +12646,10 @@
       </c>
       <c r="F470" t="inlineStr"/>
       <c r="G470" t="n">
-        <v>0.8313</v>
+        <v>0.8406</v>
       </c>
       <c r="H470" t="n">
-        <v>0.8091</v>
+        <v>0.8162</v>
       </c>
     </row>
     <row r="471">
@@ -12698,10 +12698,10 @@
       </c>
       <c r="F472" t="inlineStr"/>
       <c r="G472" t="n">
-        <v>0.9392</v>
+        <v>0.9321</v>
       </c>
       <c r="H472" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="473">
@@ -12715,19 +12715,19 @@
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
       <c r="G473" t="n">
-        <v>0.9114</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="H473" t="n">
-        <v>0.9147999999999999</v>
+        <v>0.8260999999999999</v>
       </c>
     </row>
     <row r="474">
@@ -12767,19 +12767,19 @@
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
       <c r="G475" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.9129</v>
       </c>
       <c r="H475" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.9147999999999999</v>
       </c>
     </row>
     <row r="476">
@@ -12802,10 +12802,10 @@
       </c>
       <c r="F476" t="inlineStr"/>
       <c r="G476" t="n">
-        <v>0.9601</v>
+        <v>0.9687</v>
       </c>
       <c r="H476" t="n">
-        <v>0.9715</v>
+        <v>0.9766</v>
       </c>
     </row>
     <row r="477">
@@ -12828,10 +12828,10 @@
       </c>
       <c r="F477" t="inlineStr"/>
       <c r="G477" t="n">
-        <v>0.9231</v>
+        <v>0.9386</v>
       </c>
       <c r="H477" t="n">
-        <v>0.901</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="478">
@@ -12857,7 +12857,7 @@
         <v>0.9767</v>
       </c>
       <c r="H478" t="n">
-        <v>0.9847</v>
+        <v>0.9852</v>
       </c>
     </row>
     <row r="479">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="F480" t="inlineStr"/>
       <c r="G480" t="n">
-        <v>0.9684</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="H480" t="n">
         <v>0.9812</v>
@@ -12932,10 +12932,10 @@
       </c>
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="n">
-        <v>0.3657</v>
+        <v>0.3603</v>
       </c>
       <c r="H481" t="n">
-        <v>0.2679</v>
+        <v>0.2545</v>
       </c>
     </row>
     <row r="482">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="F482" t="inlineStr"/>
       <c r="G482" t="n">
-        <v>0.6679</v>
+        <v>0.6778</v>
       </c>
       <c r="H482" t="n">
         <v>0.5718</v>
@@ -12984,10 +12984,10 @@
       </c>
       <c r="F483" t="inlineStr"/>
       <c r="G483" t="n">
-        <v>0.5935</v>
+        <v>0.6489</v>
       </c>
       <c r="H483" t="n">
-        <v>0.5665</v>
+        <v>0.6052</v>
       </c>
     </row>
     <row r="484">
@@ -13010,10 +13010,10 @@
       </c>
       <c r="F484" t="inlineStr"/>
       <c r="G484" t="n">
-        <v>0.7834</v>
+        <v>0.8215</v>
       </c>
       <c r="H484" t="n">
-        <v>0.7575</v>
+        <v>0.7804</v>
       </c>
     </row>
     <row r="485">
@@ -13039,7 +13039,7 @@
         <v>0.8134</v>
       </c>
       <c r="H485" t="n">
-        <v>0.7951</v>
+        <v>0.7962</v>
       </c>
     </row>
     <row r="486">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="F486" t="inlineStr"/>
       <c r="G486" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8711</v>
       </c>
       <c r="H486" t="n">
         <v>0.8429</v>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="F487" t="inlineStr"/>
       <c r="G487" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7541</v>
       </c>
       <c r="H487" t="n">
         <v>0.6593</v>
@@ -13114,10 +13114,10 @@
       </c>
       <c r="F488" t="inlineStr"/>
       <c r="G488" t="n">
-        <v>0.8975</v>
+        <v>0.8982</v>
       </c>
       <c r="H488" t="n">
-        <v>0.857</v>
+        <v>0.8672</v>
       </c>
     </row>
     <row r="489">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="F489" t="inlineStr"/>
       <c r="G489" t="n">
-        <v>0.915</v>
+        <v>0.9157</v>
       </c>
       <c r="H489" t="n">
         <v>0.9069</v>
@@ -13218,10 +13218,10 @@
       </c>
       <c r="F492" t="inlineStr"/>
       <c r="G492" t="n">
-        <v>0.9623</v>
+        <v>0.965</v>
       </c>
       <c r="H492" t="n">
-        <v>0.9797</v>
+        <v>0.9812</v>
       </c>
     </row>
     <row r="493">
@@ -13270,10 +13270,10 @@
       </c>
       <c r="F494" t="inlineStr"/>
       <c r="G494" t="n">
-        <v>0.9654</v>
+        <v>0.966</v>
       </c>
       <c r="H494" t="n">
-        <v>0.98</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="495">
@@ -13296,10 +13296,10 @@
       </c>
       <c r="F495" t="inlineStr"/>
       <c r="G495" t="n">
-        <v>0.5803</v>
+        <v>0.5738</v>
       </c>
       <c r="H495" t="n">
-        <v>0.5574</v>
+        <v>0.5525</v>
       </c>
     </row>
     <row r="496">
@@ -13322,10 +13322,10 @@
       </c>
       <c r="F496" t="inlineStr"/>
       <c r="G496" t="n">
-        <v>0.4439</v>
+        <v>0.4263</v>
       </c>
       <c r="H496" t="n">
-        <v>0.3427</v>
+        <v>0.3303</v>
       </c>
     </row>
     <row r="497">
@@ -13348,10 +13348,10 @@
       </c>
       <c r="F497" t="inlineStr"/>
       <c r="G497" t="n">
-        <v>0.4711</v>
+        <v>0.44</v>
       </c>
       <c r="H497" t="n">
-        <v>0.3717</v>
+        <v>0.3531</v>
       </c>
     </row>
     <row r="498">
@@ -13374,10 +13374,10 @@
       </c>
       <c r="F498" t="inlineStr"/>
       <c r="G498" t="n">
-        <v>0.4915</v>
+        <v>0.4667</v>
       </c>
       <c r="H498" t="n">
-        <v>0.4127</v>
+        <v>0.4081</v>
       </c>
     </row>
     <row r="499">
@@ -13400,10 +13400,10 @@
       </c>
       <c r="F499" t="inlineStr"/>
       <c r="G499" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7301</v>
       </c>
       <c r="H499" t="n">
-        <v>0.7222</v>
+        <v>0.7216</v>
       </c>
     </row>
     <row r="500">
@@ -13426,10 +13426,10 @@
       </c>
       <c r="F500" t="inlineStr"/>
       <c r="G500" t="n">
-        <v>0.6319</v>
+        <v>0.609</v>
       </c>
       <c r="H500" t="n">
-        <v>0.6227</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="501">
@@ -13452,10 +13452,10 @@
       </c>
       <c r="F501" t="inlineStr"/>
       <c r="G501" t="n">
-        <v>0.8796</v>
+        <v>0.8484</v>
       </c>
       <c r="H501" t="n">
-        <v>0.9089</v>
+        <v>0.8954</v>
       </c>
     </row>
     <row r="502">
@@ -13469,19 +13469,19 @@
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="n">
-        <v>0.7975</v>
+        <v>0.7037</v>
       </c>
       <c r="H502" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.7049</v>
       </c>
     </row>
     <row r="503">
@@ -13507,7 +13507,7 @@
         <v>0.5988</v>
       </c>
       <c r="H503" t="n">
-        <v>0.5645</v>
+        <v>0.5325</v>
       </c>
     </row>
     <row r="504">
@@ -13521,19 +13521,19 @@
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
       <c r="G504" t="n">
-        <v>0.7244</v>
+        <v>0.7863</v>
       </c>
       <c r="H504" t="n">
-        <v>0.7194</v>
+        <v>0.8421</v>
       </c>
     </row>
     <row r="505">
@@ -13556,10 +13556,10 @@
       </c>
       <c r="F505" t="inlineStr"/>
       <c r="G505" t="n">
-        <v>0.9569</v>
+        <v>0.9587</v>
       </c>
       <c r="H505" t="n">
-        <v>0.9505</v>
+        <v>0.9514</v>
       </c>
     </row>
     <row r="506">
@@ -13582,10 +13582,10 @@
       </c>
       <c r="F506" t="inlineStr"/>
       <c r="G506" t="n">
-        <v>0.8976</v>
+        <v>0.9213</v>
       </c>
       <c r="H506" t="n">
-        <v>0.9228</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="507">
@@ -13686,10 +13686,10 @@
       </c>
       <c r="F510" t="inlineStr"/>
       <c r="G510" t="n">
-        <v>0.2689</v>
+        <v>0.2614</v>
       </c>
       <c r="H510" t="n">
-        <v>0.2343</v>
+        <v>0.2259</v>
       </c>
     </row>
     <row r="511">
@@ -13715,7 +13715,7 @@
         <v>0.4282</v>
       </c>
       <c r="H511" t="n">
-        <v>0.3321</v>
+        <v>0.3222</v>
       </c>
     </row>
     <row r="512">
@@ -13738,10 +13738,10 @@
       </c>
       <c r="F512" t="inlineStr"/>
       <c r="G512" t="n">
-        <v>0.4779</v>
+        <v>0.5081</v>
       </c>
       <c r="H512" t="n">
-        <v>0.4192</v>
+        <v>0.4608</v>
       </c>
     </row>
     <row r="513">
@@ -13764,10 +13764,10 @@
       </c>
       <c r="F513" t="inlineStr"/>
       <c r="G513" t="n">
-        <v>0.6846</v>
+        <v>0.6864</v>
       </c>
       <c r="H513" t="n">
-        <v>0.576</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="514">
@@ -13793,7 +13793,7 @@
         <v>0.7104</v>
       </c>
       <c r="H514" t="n">
-        <v>0.7214</v>
+        <v>0.6947</v>
       </c>
     </row>
     <row r="515">
@@ -13816,10 +13816,10 @@
       </c>
       <c r="F515" t="inlineStr"/>
       <c r="G515" t="n">
-        <v>0.7422</v>
+        <v>0.7375</v>
       </c>
       <c r="H515" t="n">
-        <v>0.7944</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="516">
@@ -13842,10 +13842,10 @@
       </c>
       <c r="F516" t="inlineStr"/>
       <c r="G516" t="n">
-        <v>0.6219</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="H516" t="n">
-        <v>0.5464</v>
+        <v>0.5385</v>
       </c>
     </row>
     <row r="517">
@@ -13868,10 +13868,10 @@
       </c>
       <c r="F517" t="inlineStr"/>
       <c r="G517" t="n">
-        <v>0.8415</v>
+        <v>0.831</v>
       </c>
       <c r="H517" t="n">
-        <v>0.8541</v>
+        <v>0.8481</v>
       </c>
     </row>
     <row r="518">
@@ -13894,10 +13894,10 @@
       </c>
       <c r="F518" t="inlineStr"/>
       <c r="G518" t="n">
-        <v>0.8162</v>
+        <v>0.8137</v>
       </c>
       <c r="H518" t="n">
-        <v>0.8975</v>
+        <v>0.8911</v>
       </c>
     </row>
     <row r="519">
@@ -13920,10 +13920,10 @@
       </c>
       <c r="F519" t="inlineStr"/>
       <c r="G519" t="n">
-        <v>0.8976</v>
+        <v>0.8899</v>
       </c>
       <c r="H519" t="n">
-        <v>0.9152</v>
+        <v>0.9095</v>
       </c>
     </row>
     <row r="520">
@@ -13946,10 +13946,10 @@
       </c>
       <c r="F520" t="inlineStr"/>
       <c r="G520" t="n">
-        <v>0.9643</v>
+        <v>0.963</v>
       </c>
       <c r="H520" t="n">
-        <v>0.9645</v>
+        <v>0.9628</v>
       </c>
     </row>
     <row r="521">
@@ -14024,10 +14024,10 @@
       </c>
       <c r="F523" t="inlineStr"/>
       <c r="G523" t="n">
-        <v>0.9739</v>
+        <v>0.9735</v>
       </c>
       <c r="H523" t="n">
-        <v>0.978</v>
+        <v>0.9772</v>
       </c>
     </row>
     <row r="524">
@@ -14050,10 +14050,10 @@
       </c>
       <c r="F524" t="inlineStr"/>
       <c r="G524" t="n">
-        <v>0.5895</v>
+        <v>0.5708</v>
       </c>
       <c r="H524" t="n">
-        <v>0.6256</v>
+        <v>0.5927</v>
       </c>
     </row>
     <row r="525">
@@ -14076,10 +14076,10 @@
       </c>
       <c r="F525" t="inlineStr"/>
       <c r="G525" t="n">
-        <v>0.4872</v>
+        <v>0.4545</v>
       </c>
       <c r="H525" t="n">
-        <v>0.4128</v>
+        <v>0.3883</v>
       </c>
     </row>
     <row r="526">
@@ -14102,10 +14102,10 @@
       </c>
       <c r="F526" t="inlineStr"/>
       <c r="G526" t="n">
-        <v>0.4836</v>
+        <v>0.4329</v>
       </c>
       <c r="H526" t="n">
-        <v>0.4526</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="527">
@@ -14128,10 +14128,10 @@
       </c>
       <c r="F527" t="inlineStr"/>
       <c r="G527" t="n">
-        <v>0.4909</v>
+        <v>0.4565</v>
       </c>
       <c r="H527" t="n">
-        <v>0.4576</v>
+        <v>0.4326</v>
       </c>
     </row>
     <row r="528">
@@ -14154,10 +14154,10 @@
       </c>
       <c r="F528" t="inlineStr"/>
       <c r="G528" t="n">
-        <v>0.7552</v>
+        <v>0.7284</v>
       </c>
       <c r="H528" t="n">
-        <v>0.8126</v>
+        <v>0.7657</v>
       </c>
     </row>
     <row r="529">
@@ -14180,10 +14180,10 @@
       </c>
       <c r="F529" t="inlineStr"/>
       <c r="G529" t="n">
-        <v>0.6758</v>
+        <v>0.6232</v>
       </c>
       <c r="H529" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.6612</v>
       </c>
     </row>
     <row r="530">
@@ -14206,10 +14206,10 @@
       </c>
       <c r="F530" t="inlineStr"/>
       <c r="G530" t="n">
-        <v>0.9187</v>
+        <v>0.8899</v>
       </c>
       <c r="H530" t="n">
-        <v>0.9271</v>
+        <v>0.9051</v>
       </c>
     </row>
     <row r="531">
@@ -14223,19 +14223,19 @@
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
       <c r="G531" t="n">
-        <v>0.8399</v>
+        <v>0.758</v>
       </c>
       <c r="H531" t="n">
-        <v>0.8532</v>
+        <v>0.7549</v>
       </c>
     </row>
     <row r="532">
@@ -14258,10 +14258,10 @@
       </c>
       <c r="F532" t="inlineStr"/>
       <c r="G532" t="n">
-        <v>0.6383</v>
+        <v>0.6034</v>
       </c>
       <c r="H532" t="n">
-        <v>0.6659</v>
+        <v>0.5911</v>
       </c>
     </row>
     <row r="533">
@@ -14275,19 +14275,19 @@
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
       <c r="G533" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.8218</v>
       </c>
       <c r="H533" t="n">
-        <v>0.8002</v>
+        <v>0.844</v>
       </c>
     </row>
     <row r="534">
@@ -14310,10 +14310,10 @@
       </c>
       <c r="F534" t="inlineStr"/>
       <c r="G534" t="n">
-        <v>0.9616</v>
+        <v>0.9633</v>
       </c>
       <c r="H534" t="n">
-        <v>0.9626</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="535">
@@ -14336,10 +14336,10 @@
       </c>
       <c r="F535" t="inlineStr"/>
       <c r="G535" t="n">
-        <v>0.93</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H535" t="n">
-        <v>0.9227</v>
+        <v>0.9267</v>
       </c>
     </row>
     <row r="536">
@@ -14414,10 +14414,10 @@
       </c>
       <c r="F538" t="inlineStr"/>
       <c r="G538" t="n">
-        <v>0.9745</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="H538" t="n">
-        <v>0.9807</v>
+        <v>0.9809</v>
       </c>
     </row>
     <row r="539">
@@ -14440,10 +14440,10 @@
       </c>
       <c r="F539" t="inlineStr"/>
       <c r="G539" t="n">
-        <v>0.3399</v>
+        <v>0.2916</v>
       </c>
       <c r="H539" t="n">
-        <v>0.275</v>
+        <v>0.2213</v>
       </c>
     </row>
     <row r="540">
@@ -14466,10 +14466,10 @@
       </c>
       <c r="F540" t="inlineStr"/>
       <c r="G540" t="n">
-        <v>0.4335</v>
+        <v>0.3948</v>
       </c>
       <c r="H540" t="n">
-        <v>0.4065</v>
+        <v>0.3511</v>
       </c>
     </row>
     <row r="541">
@@ -14492,10 +14492,10 @@
       </c>
       <c r="F541" t="inlineStr"/>
       <c r="G541" t="n">
-        <v>0.5808</v>
+        <v>0.5392</v>
       </c>
       <c r="H541" t="n">
-        <v>0.5221</v>
+        <v>0.4919</v>
       </c>
     </row>
     <row r="542">
@@ -14518,10 +14518,10 @@
       </c>
       <c r="F542" t="inlineStr"/>
       <c r="G542" t="n">
-        <v>0.6925</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H542" t="n">
-        <v>0.7482</v>
+        <v>0.7164</v>
       </c>
     </row>
     <row r="543">
@@ -14544,10 +14544,10 @@
       </c>
       <c r="F543" t="inlineStr"/>
       <c r="G543" t="n">
-        <v>0.7491</v>
+        <v>0.7258</v>
       </c>
       <c r="H543" t="n">
-        <v>0.7917</v>
+        <v>0.7275</v>
       </c>
     </row>
     <row r="544">
@@ -14570,10 +14570,10 @@
       </c>
       <c r="F544" t="inlineStr"/>
       <c r="G544" t="n">
-        <v>0.7944</v>
+        <v>0.7506</v>
       </c>
       <c r="H544" t="n">
-        <v>0.838</v>
+        <v>0.8221000000000001</v>
       </c>
     </row>
     <row r="545">
@@ -14596,10 +14596,10 @@
       </c>
       <c r="F545" t="inlineStr"/>
       <c r="G545" t="n">
-        <v>0.6812</v>
+        <v>0.6269</v>
       </c>
       <c r="H545" t="n">
-        <v>0.6752</v>
+        <v>0.6084000000000001</v>
       </c>
     </row>
     <row r="546">
@@ -14622,10 +14622,10 @@
       </c>
       <c r="F546" t="inlineStr"/>
       <c r="G546" t="n">
-        <v>0.8843</v>
+        <v>0.8524</v>
       </c>
       <c r="H546" t="n">
-        <v>0.8787</v>
+        <v>0.8573</v>
       </c>
     </row>
     <row r="547">
@@ -14648,10 +14648,10 @@
       </c>
       <c r="F547" t="inlineStr"/>
       <c r="G547" t="n">
-        <v>0.8758</v>
+        <v>0.8546</v>
       </c>
       <c r="H547" t="n">
-        <v>0.9051</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="548">
@@ -14674,10 +14674,10 @@
       </c>
       <c r="F548" t="inlineStr"/>
       <c r="G548" t="n">
-        <v>0.9191</v>
+        <v>0.8949</v>
       </c>
       <c r="H548" t="n">
-        <v>0.9315</v>
+        <v>0.9207</v>
       </c>
     </row>
     <row r="549">
@@ -14700,10 +14700,10 @@
       </c>
       <c r="F549" t="inlineStr"/>
       <c r="G549" t="n">
-        <v>0.9675</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="H549" t="n">
-        <v>0.975</v>
+        <v>0.9711</v>
       </c>
     </row>
     <row r="550">
@@ -14726,10 +14726,10 @@
       </c>
       <c r="F550" t="inlineStr"/>
       <c r="G550" t="n">
-        <v>0.964</v>
+        <v>0.9634</v>
       </c>
       <c r="H550" t="n">
-        <v>0.9718</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="551">
@@ -14755,7 +14755,7 @@
         <v>0.974</v>
       </c>
       <c r="H551" t="n">
-        <v>0.9777</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="552">
@@ -14778,10 +14778,10 @@
       </c>
       <c r="F552" t="inlineStr"/>
       <c r="G552" t="n">
-        <v>0.9696</v>
+        <v>0.9677</v>
       </c>
       <c r="H552" t="n">
-        <v>0.9747</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="553">
@@ -14804,10 +14804,10 @@
       </c>
       <c r="F553" t="inlineStr"/>
       <c r="G553" t="n">
-        <v>0.4046</v>
+        <v>0.3904</v>
       </c>
       <c r="H553" t="n">
-        <v>0.3496</v>
+        <v>0.3375</v>
       </c>
     </row>
     <row r="554">
@@ -14830,10 +14830,10 @@
       </c>
       <c r="F554" t="inlineStr"/>
       <c r="G554" t="n">
-        <v>0.2494</v>
+        <v>0.2204</v>
       </c>
       <c r="H554" t="n">
-        <v>0.2628</v>
+        <v>0.2272</v>
       </c>
     </row>
     <row r="555">
@@ -14856,10 +14856,10 @@
       </c>
       <c r="F555" t="inlineStr"/>
       <c r="G555" t="n">
-        <v>0.2707</v>
+        <v>0.2484</v>
       </c>
       <c r="H555" t="n">
-        <v>0.2624</v>
+        <v>0.2458</v>
       </c>
     </row>
     <row r="556">
@@ -14882,10 +14882,10 @@
       </c>
       <c r="F556" t="inlineStr"/>
       <c r="G556" t="n">
-        <v>0.3064</v>
+        <v>0.2706</v>
       </c>
       <c r="H556" t="n">
-        <v>0.2871</v>
+        <v>0.2657</v>
       </c>
     </row>
     <row r="557">
@@ -14908,10 +14908,10 @@
       </c>
       <c r="F557" t="inlineStr"/>
       <c r="G557" t="n">
-        <v>0.6035</v>
+        <v>0.5936</v>
       </c>
       <c r="H557" t="n">
-        <v>0.5878</v>
+        <v>0.5780999999999999</v>
       </c>
     </row>
     <row r="558">
@@ -14934,10 +14934,10 @@
       </c>
       <c r="F558" t="inlineStr"/>
       <c r="G558" t="n">
-        <v>0.4983</v>
+        <v>0.4607</v>
       </c>
       <c r="H558" t="n">
-        <v>0.4494</v>
+        <v>0.4096</v>
       </c>
     </row>
     <row r="559">
@@ -14960,10 +14960,10 @@
       </c>
       <c r="F559" t="inlineStr"/>
       <c r="G559" t="n">
-        <v>0.8226</v>
+        <v>0.7519</v>
       </c>
       <c r="H559" t="n">
-        <v>0.8097</v>
+        <v>0.7087</v>
       </c>
     </row>
     <row r="560">
@@ -14977,19 +14977,19 @@
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
       <c r="G560" t="n">
-        <v>0.7585</v>
+        <v>0.5841</v>
       </c>
       <c r="H560" t="n">
-        <v>0.7068</v>
+        <v>0.5586</v>
       </c>
     </row>
     <row r="561">
@@ -15012,10 +15012,10 @@
       </c>
       <c r="F561" t="inlineStr"/>
       <c r="G561" t="n">
-        <v>0.4426</v>
+        <v>0.409</v>
       </c>
       <c r="H561" t="n">
-        <v>0.4135</v>
+        <v>0.3783</v>
       </c>
     </row>
     <row r="562">
@@ -15029,19 +15029,19 @@
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
       <c r="G562" t="n">
-        <v>0.6042</v>
+        <v>0.7173</v>
       </c>
       <c r="H562" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.6577</v>
       </c>
     </row>
     <row r="563">
@@ -15064,10 +15064,10 @@
       </c>
       <c r="F563" t="inlineStr"/>
       <c r="G563" t="n">
-        <v>0.9207</v>
+        <v>0.9366</v>
       </c>
       <c r="H563" t="n">
-        <v>0.9318</v>
+        <v>0.9396</v>
       </c>
     </row>
     <row r="564">
@@ -15090,10 +15090,10 @@
       </c>
       <c r="F564" t="inlineStr"/>
       <c r="G564" t="n">
-        <v>0.8250999999999999</v>
+        <v>0.8573</v>
       </c>
       <c r="H564" t="n">
-        <v>0.7695</v>
+        <v>0.7887999999999999</v>
       </c>
     </row>
     <row r="565">
@@ -15116,10 +15116,10 @@
       </c>
       <c r="F565" t="inlineStr"/>
       <c r="G565" t="n">
-        <v>0.9721</v>
+        <v>0.9668</v>
       </c>
       <c r="H565" t="n">
-        <v>0.9749</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="566">
@@ -15142,10 +15142,10 @@
       </c>
       <c r="F566" t="inlineStr"/>
       <c r="G566" t="n">
-        <v>0.9668</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="H566" t="n">
-        <v>0.9769</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="567">
@@ -15168,10 +15168,10 @@
       </c>
       <c r="F567" t="inlineStr"/>
       <c r="G567" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9485</v>
       </c>
       <c r="H567" t="n">
-        <v>0.9563</v>
+        <v>0.9517</v>
       </c>
     </row>
     <row r="568">
@@ -15194,10 +15194,10 @@
       </c>
       <c r="F568" t="inlineStr"/>
       <c r="G568" t="n">
-        <v>0.1255</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="H568" t="n">
-        <v>0.0901</v>
+        <v>0.0804</v>
       </c>
     </row>
     <row r="569">
@@ -15220,10 +15220,10 @@
       </c>
       <c r="F569" t="inlineStr"/>
       <c r="G569" t="n">
-        <v>0.2425</v>
+        <v>0.2196</v>
       </c>
       <c r="H569" t="n">
-        <v>0.2166</v>
+        <v>0.1785</v>
       </c>
     </row>
     <row r="570">
@@ -15246,10 +15246,10 @@
       </c>
       <c r="F570" t="inlineStr"/>
       <c r="G570" t="n">
-        <v>0.424</v>
+        <v>0.365</v>
       </c>
       <c r="H570" t="n">
-        <v>0.3154</v>
+        <v>0.3136</v>
       </c>
     </row>
     <row r="571">
@@ -15272,10 +15272,10 @@
       </c>
       <c r="F571" t="inlineStr"/>
       <c r="G571" t="n">
-        <v>0.2518</v>
+        <v>0.2836</v>
       </c>
       <c r="H571" t="n">
-        <v>0.3075</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="572">
@@ -15298,10 +15298,10 @@
       </c>
       <c r="F572" t="inlineStr"/>
       <c r="G572" t="n">
-        <v>0.5675</v>
+        <v>0.5304</v>
       </c>
       <c r="H572" t="n">
-        <v>0.5289</v>
+        <v>0.4899</v>
       </c>
     </row>
     <row r="573">
@@ -15324,10 +15324,10 @@
       </c>
       <c r="F573" t="inlineStr"/>
       <c r="G573" t="n">
-        <v>0.6712</v>
+        <v>0.6339</v>
       </c>
       <c r="H573" t="n">
-        <v>0.6173999999999999</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="574">
@@ -15350,10 +15350,10 @@
       </c>
       <c r="F574" t="inlineStr"/>
       <c r="G574" t="n">
-        <v>0.5487</v>
+        <v>0.5051</v>
       </c>
       <c r="H574" t="n">
-        <v>0.4386</v>
+        <v>0.3818</v>
       </c>
     </row>
     <row r="575">
@@ -15376,10 +15376,10 @@
       </c>
       <c r="F575" t="inlineStr"/>
       <c r="G575" t="n">
-        <v>0.779</v>
+        <v>0.7337</v>
       </c>
       <c r="H575" t="n">
-        <v>0.7073</v>
+        <v>0.6788999999999999</v>
       </c>
     </row>
     <row r="576">
@@ -15402,10 +15402,10 @@
       </c>
       <c r="F576" t="inlineStr"/>
       <c r="G576" t="n">
-        <v>0.7387</v>
+        <v>0.7036</v>
       </c>
       <c r="H576" t="n">
-        <v>0.7071</v>
+        <v>0.6822</v>
       </c>
     </row>
     <row r="577">
@@ -15428,10 +15428,10 @@
       </c>
       <c r="F577" t="inlineStr"/>
       <c r="G577" t="n">
-        <v>0.8451</v>
+        <v>0.8016</v>
       </c>
       <c r="H577" t="n">
-        <v>0.7956</v>
+        <v>0.7748</v>
       </c>
     </row>
     <row r="578">
@@ -15454,10 +15454,10 @@
       </c>
       <c r="F578" t="inlineStr"/>
       <c r="G578" t="n">
-        <v>0.9291</v>
+        <v>0.9212</v>
       </c>
       <c r="H578" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9243</v>
       </c>
     </row>
     <row r="579">
@@ -15480,10 +15480,10 @@
       </c>
       <c r="F579" t="inlineStr"/>
       <c r="G579" t="n">
-        <v>0.9247</v>
+        <v>0.922</v>
       </c>
       <c r="H579" t="n">
-        <v>0.9385</v>
+        <v>0.9243</v>
       </c>
     </row>
     <row r="580">
@@ -15506,10 +15506,10 @@
       </c>
       <c r="F580" t="inlineStr"/>
       <c r="G580" t="n">
-        <v>0.9475</v>
+        <v>0.9412</v>
       </c>
       <c r="H580" t="n">
-        <v>0.9627</v>
+        <v>0.9585</v>
       </c>
     </row>
     <row r="581">
@@ -15532,10 +15532,10 @@
       </c>
       <c r="F581" t="inlineStr"/>
       <c r="G581" t="n">
-        <v>0.9423</v>
+        <v>0.9403</v>
       </c>
       <c r="H581" t="n">
-        <v>0.9588</v>
+        <v>0.9425</v>
       </c>
     </row>
     <row r="582">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="F582" t="inlineStr"/>
       <c r="G582" t="n">
-        <v>0.3631</v>
+        <v>0.3647</v>
       </c>
       <c r="H582" t="n">
         <v>0.3261</v>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="F583" t="inlineStr"/>
       <c r="G583" t="n">
-        <v>0.1979</v>
+        <v>0.1992</v>
       </c>
       <c r="H583" t="n">
         <v>0.2189</v>
@@ -15639,7 +15639,7 @@
         <v>0.2434</v>
       </c>
       <c r="H585" t="n">
-        <v>0.2773</v>
+        <v>0.2731</v>
       </c>
     </row>
     <row r="586">
@@ -15662,10 +15662,10 @@
       </c>
       <c r="F586" t="inlineStr"/>
       <c r="G586" t="n">
-        <v>0.5686</v>
+        <v>0.5779</v>
       </c>
       <c r="H586" t="n">
-        <v>0.5359</v>
+        <v>0.5448</v>
       </c>
     </row>
     <row r="587">
@@ -15691,7 +15691,7 @@
         <v>0.428</v>
       </c>
       <c r="H587" t="n">
-        <v>0.4449</v>
+        <v>0.4399</v>
       </c>
     </row>
     <row r="588">
@@ -15714,10 +15714,10 @@
       </c>
       <c r="F588" t="inlineStr"/>
       <c r="G588" t="n">
-        <v>0.7902</v>
+        <v>0.7496</v>
       </c>
       <c r="H588" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.7107</v>
       </c>
     </row>
     <row r="589">
@@ -15731,19 +15731,19 @@
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
       <c r="G589" t="n">
-        <v>0.6995</v>
+        <v>0.528</v>
       </c>
       <c r="H589" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.5034999999999999</v>
       </c>
     </row>
     <row r="590">
@@ -15783,19 +15783,19 @@
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
       <c r="G591" t="n">
-        <v>0.528</v>
+        <v>0.6995</v>
       </c>
       <c r="H591" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.6346000000000001</v>
       </c>
     </row>
     <row r="592">
@@ -15818,10 +15818,10 @@
       </c>
       <c r="F592" t="inlineStr"/>
       <c r="G592" t="n">
-        <v>0.908</v>
+        <v>0.9338</v>
       </c>
       <c r="H592" t="n">
-        <v>0.9104</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="593">
@@ -15844,10 +15844,10 @@
       </c>
       <c r="F593" t="inlineStr"/>
       <c r="G593" t="n">
-        <v>0.7954</v>
+        <v>0.8421</v>
       </c>
       <c r="H593" t="n">
-        <v>0.7438</v>
+        <v>0.7805</v>
       </c>
     </row>
     <row r="594">
@@ -15870,7 +15870,7 @@
       </c>
       <c r="F594" t="inlineStr"/>
       <c r="G594" t="n">
-        <v>0.9648</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="H594" t="n">
         <v>0.9663</v>
@@ -15925,7 +15925,7 @@
         <v>0.9500999999999999</v>
       </c>
       <c r="H596" t="n">
-        <v>0.948</v>
+        <v>0.9507</v>
       </c>
     </row>
     <row r="597">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="F597" t="inlineStr"/>
       <c r="G597" t="n">
-        <v>0.0978</v>
+        <v>0.0965</v>
       </c>
       <c r="H597" t="n">
         <v>0.0828</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="F598" t="inlineStr"/>
       <c r="G598" t="n">
-        <v>0.2049</v>
+        <v>0.2038</v>
       </c>
       <c r="H598" t="n">
         <v>0.1866</v>
@@ -16000,7 +16000,7 @@
       </c>
       <c r="F599" t="inlineStr"/>
       <c r="G599" t="n">
-        <v>0.2786</v>
+        <v>0.3053</v>
       </c>
       <c r="H599" t="n">
         <v>0.2896</v>
@@ -16026,10 +16026,10 @@
       </c>
       <c r="F600" t="inlineStr"/>
       <c r="G600" t="n">
-        <v>0.2083</v>
+        <v>0.2725</v>
       </c>
       <c r="H600" t="n">
-        <v>0.2509</v>
+        <v>0.2742</v>
       </c>
     </row>
     <row r="601">
@@ -16052,10 +16052,10 @@
       </c>
       <c r="F601" t="inlineStr"/>
       <c r="G601" t="n">
-        <v>0.4711</v>
+        <v>0.5101</v>
       </c>
       <c r="H601" t="n">
-        <v>0.4325</v>
+        <v>0.4696</v>
       </c>
     </row>
     <row r="602">
@@ -16081,7 +16081,7 @@
         <v>0.6567</v>
       </c>
       <c r="H602" t="n">
-        <v>0.5809</v>
+        <v>0.5825</v>
       </c>
     </row>
     <row r="603">
@@ -16104,10 +16104,10 @@
       </c>
       <c r="F603" t="inlineStr"/>
       <c r="G603" t="n">
-        <v>0.4572</v>
+        <v>0.4477</v>
       </c>
       <c r="H603" t="n">
-        <v>0.3822</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="604">
@@ -16211,7 +16211,7 @@
         <v>0.9207</v>
       </c>
       <c r="H607" t="n">
-        <v>0.9125</v>
+        <v>0.9137</v>
       </c>
     </row>
     <row r="608">
@@ -16234,10 +16234,10 @@
       </c>
       <c r="F608" t="inlineStr"/>
       <c r="G608" t="n">
-        <v>0.9207</v>
+        <v>0.9221</v>
       </c>
       <c r="H608" t="n">
-        <v>0.8962</v>
+        <v>0.9109</v>
       </c>
     </row>
     <row r="609">
@@ -16260,10 +16260,10 @@
       </c>
       <c r="F609" t="inlineStr"/>
       <c r="G609" t="n">
-        <v>0.9383</v>
+        <v>0.9401</v>
       </c>
       <c r="H609" t="n">
-        <v>0.946</v>
+        <v>0.9468</v>
       </c>
     </row>
     <row r="610">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="F610" t="inlineStr"/>
       <c r="G610" t="n">
-        <v>0.9355</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H610" t="n">
         <v>0.9428</v>
@@ -16364,10 +16364,10 @@
       </c>
       <c r="F613" t="inlineStr"/>
       <c r="G613" t="n">
-        <v>0.1735</v>
+        <v>0.17</v>
       </c>
       <c r="H613" t="n">
-        <v>0.1341</v>
+        <v>0.1257</v>
       </c>
     </row>
     <row r="614">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="F614" t="inlineStr"/>
       <c r="G614" t="n">
-        <v>0.1595</v>
+        <v>0.1482</v>
       </c>
       <c r="H614" t="n">
         <v>0.1894</v>
@@ -16416,10 +16416,10 @@
       </c>
       <c r="F615" t="inlineStr"/>
       <c r="G615" t="n">
-        <v>0.5174</v>
+        <v>0.5271</v>
       </c>
       <c r="H615" t="n">
-        <v>0.4389</v>
+        <v>0.446</v>
       </c>
     </row>
     <row r="616">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="F616" t="inlineStr"/>
       <c r="G616" t="n">
-        <v>0.3034</v>
+        <v>0.3005</v>
       </c>
       <c r="H616" t="n">
         <v>0.3282</v>
@@ -16468,10 +16468,10 @@
       </c>
       <c r="F617" t="inlineStr"/>
       <c r="G617" t="n">
-        <v>0.713</v>
+        <v>0.6443</v>
       </c>
       <c r="H617" t="n">
-        <v>0.6311</v>
+        <v>0.5642</v>
       </c>
     </row>
     <row r="618">
@@ -16485,19 +16485,19 @@
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
       <c r="G618" t="n">
-        <v>0.6092</v>
+        <v>0.4755</v>
       </c>
       <c r="H618" t="n">
-        <v>0.5108</v>
+        <v>0.391</v>
       </c>
     </row>
     <row r="619">
@@ -16537,19 +16537,19 @@
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
       <c r="G620" t="n">
-        <v>0.4755</v>
+        <v>0.6092</v>
       </c>
       <c r="H620" t="n">
-        <v>0.391</v>
+        <v>0.5108</v>
       </c>
     </row>
     <row r="621">
@@ -16572,10 +16572,10 @@
       </c>
       <c r="F621" t="inlineStr"/>
       <c r="G621" t="n">
-        <v>0.8758</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="H621" t="n">
-        <v>0.852</v>
+        <v>0.9056</v>
       </c>
     </row>
     <row r="622">
@@ -16598,10 +16598,10 @@
       </c>
       <c r="F622" t="inlineStr"/>
       <c r="G622" t="n">
-        <v>0.7157</v>
+        <v>0.7809</v>
       </c>
       <c r="H622" t="n">
-        <v>0.6405999999999999</v>
+        <v>0.6918</v>
       </c>
     </row>
     <row r="623">
@@ -16624,10 +16624,10 @@
       </c>
       <c r="F623" t="inlineStr"/>
       <c r="G623" t="n">
-        <v>0.9556</v>
+        <v>0.9569</v>
       </c>
       <c r="H623" t="n">
-        <v>0.9659</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="624">
@@ -16653,7 +16653,7 @@
         <v>0.9647</v>
       </c>
       <c r="H624" t="n">
-        <v>0.97</v>
+        <v>0.9717</v>
       </c>
     </row>
     <row r="625">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="F626" t="inlineStr"/>
       <c r="G626" t="n">
-        <v>0.0561</v>
+        <v>0.0558</v>
       </c>
       <c r="H626" t="n">
         <v>0.073</v>
@@ -16731,7 +16731,7 @@
         <v>0.1571</v>
       </c>
       <c r="H627" t="n">
-        <v>0.1316</v>
+        <v>0.1289</v>
       </c>
     </row>
     <row r="628">
@@ -16754,10 +16754,10 @@
       </c>
       <c r="F628" t="inlineStr"/>
       <c r="G628" t="n">
-        <v>0.2056</v>
+        <v>0.2125</v>
       </c>
       <c r="H628" t="n">
-        <v>0.2578</v>
+        <v>0.2625</v>
       </c>
     </row>
     <row r="629">
@@ -16780,10 +16780,10 @@
       </c>
       <c r="F629" t="inlineStr"/>
       <c r="G629" t="n">
-        <v>0.162</v>
+        <v>0.1779</v>
       </c>
       <c r="H629" t="n">
-        <v>0.2056</v>
+        <v>0.2494</v>
       </c>
     </row>
     <row r="630">
@@ -16806,10 +16806,10 @@
       </c>
       <c r="F630" t="inlineStr"/>
       <c r="G630" t="n">
-        <v>0.3826</v>
+        <v>0.3977</v>
       </c>
       <c r="H630" t="n">
-        <v>0.3288</v>
+        <v>0.3661</v>
       </c>
     </row>
     <row r="631">
@@ -16832,7 +16832,7 @@
       </c>
       <c r="F631" t="inlineStr"/>
       <c r="G631" t="n">
-        <v>0.4191</v>
+        <v>0.4175</v>
       </c>
       <c r="H631" t="n">
         <v>0.3433</v>
@@ -16861,7 +16861,7 @@
         <v>0.3083</v>
       </c>
       <c r="H632" t="n">
-        <v>0.328</v>
+        <v>0.3244</v>
       </c>
     </row>
     <row r="633">
@@ -16962,10 +16962,10 @@
       </c>
       <c r="F636" t="inlineStr"/>
       <c r="G636" t="n">
-        <v>0.8746</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="H636" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8712</v>
       </c>
     </row>
     <row r="637">
@@ -16991,7 +16991,7 @@
         <v>0.8974</v>
       </c>
       <c r="H637" t="n">
-        <v>0.8822</v>
+        <v>0.8855</v>
       </c>
     </row>
     <row r="638">
@@ -17014,10 +17014,10 @@
       </c>
       <c r="F638" t="inlineStr"/>
       <c r="G638" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9217</v>
       </c>
       <c r="H638" t="n">
-        <v>0.9218</v>
+        <v>0.9233</v>
       </c>
     </row>
     <row r="639">
@@ -17043,7 +17043,7 @@
         <v>0.9143</v>
       </c>
       <c r="H639" t="n">
-        <v>0.9256</v>
+        <v>0.9262</v>
       </c>
     </row>
     <row r="640">
@@ -17121,7 +17121,7 @@
         <v>0.3274</v>
       </c>
       <c r="H642" t="n">
-        <v>0.2942</v>
+        <v>0.2923</v>
       </c>
     </row>
     <row r="643">
@@ -17170,10 +17170,10 @@
       </c>
       <c r="F644" t="inlineStr"/>
       <c r="G644" t="n">
-        <v>0.6347</v>
+        <v>0.6381</v>
       </c>
       <c r="H644" t="n">
-        <v>0.6165</v>
+        <v>0.6248</v>
       </c>
     </row>
     <row r="645">
@@ -17222,10 +17222,10 @@
       </c>
       <c r="F646" t="inlineStr"/>
       <c r="G646" t="n">
-        <v>0.842</v>
+        <v>0.8064</v>
       </c>
       <c r="H646" t="n">
-        <v>0.8877</v>
+        <v>0.8448</v>
       </c>
     </row>
     <row r="647">
@@ -17239,19 +17239,19 @@
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
       <c r="G647" t="n">
-        <v>0.7341</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="H647" t="n">
-        <v>0.7784</v>
+        <v>0.5978</v>
       </c>
     </row>
     <row r="648">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="F648" t="inlineStr"/>
       <c r="G648" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.5302</v>
       </c>
       <c r="H648" t="n">
         <v>0.4275</v>
@@ -17291,19 +17291,19 @@
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
       <c r="G649" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.7341</v>
       </c>
       <c r="H649" t="n">
-        <v>0.5978</v>
+        <v>0.7828000000000001</v>
       </c>
     </row>
     <row r="650">
@@ -17326,10 +17326,10 @@
       </c>
       <c r="F650" t="inlineStr"/>
       <c r="G650" t="n">
-        <v>0.9408</v>
+        <v>0.9553</v>
       </c>
       <c r="H650" t="n">
-        <v>0.9414</v>
+        <v>0.9495</v>
       </c>
     </row>
     <row r="651">
@@ -17352,10 +17352,10 @@
       </c>
       <c r="F651" t="inlineStr"/>
       <c r="G651" t="n">
-        <v>0.868</v>
+        <v>0.8844</v>
       </c>
       <c r="H651" t="n">
-        <v>0.84</v>
+        <v>0.8831</v>
       </c>
     </row>
     <row r="652">
@@ -17407,7 +17407,7 @@
         <v>0.98</v>
       </c>
       <c r="H653" t="n">
-        <v>0.9859</v>
+        <v>0.9864000000000001</v>
       </c>
     </row>
     <row r="654">
@@ -17430,10 +17430,10 @@
       </c>
       <c r="F654" t="inlineStr"/>
       <c r="G654" t="n">
-        <v>0.9649</v>
+        <v>0.9653</v>
       </c>
       <c r="H654" t="n">
-        <v>0.9736</v>
+        <v>0.9742</v>
       </c>
     </row>
     <row r="655">
@@ -17485,7 +17485,7 @@
         <v>0.3407</v>
       </c>
       <c r="H656" t="n">
-        <v>0.2445</v>
+        <v>0.2459</v>
       </c>
     </row>
     <row r="657">
@@ -17508,10 +17508,10 @@
       </c>
       <c r="F657" t="inlineStr"/>
       <c r="G657" t="n">
-        <v>0.4536</v>
+        <v>0.4615</v>
       </c>
       <c r="H657" t="n">
-        <v>0.3781</v>
+        <v>0.3856</v>
       </c>
     </row>
     <row r="658">
@@ -17534,10 +17534,10 @@
       </c>
       <c r="F658" t="inlineStr"/>
       <c r="G658" t="n">
-        <v>0.3248</v>
+        <v>0.3916</v>
       </c>
       <c r="H658" t="n">
-        <v>0.3188</v>
+        <v>0.3731</v>
       </c>
     </row>
     <row r="659">
@@ -17560,10 +17560,10 @@
       </c>
       <c r="F659" t="inlineStr"/>
       <c r="G659" t="n">
-        <v>0.5614</v>
+        <v>0.6182</v>
       </c>
       <c r="H659" t="n">
-        <v>0.4513</v>
+        <v>0.4949</v>
       </c>
     </row>
     <row r="660">
@@ -17586,10 +17586,10 @@
       </c>
       <c r="F660" t="inlineStr"/>
       <c r="G660" t="n">
-        <v>0.6178</v>
+        <v>0.617</v>
       </c>
       <c r="H660" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.5523</v>
       </c>
     </row>
     <row r="661">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="F661" t="inlineStr"/>
       <c r="G661" t="n">
-        <v>0.672</v>
+        <v>0.6756</v>
       </c>
       <c r="H661" t="n">
         <v>0.6917</v>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="F662" t="inlineStr"/>
       <c r="G662" t="n">
-        <v>0.7585</v>
+        <v>0.7593</v>
       </c>
       <c r="H662" t="n">
         <v>0.7668</v>
@@ -17664,10 +17664,10 @@
       </c>
       <c r="F663" t="inlineStr"/>
       <c r="G663" t="n">
-        <v>0.7694</v>
+        <v>0.7764</v>
       </c>
       <c r="H663" t="n">
-        <v>0.8089</v>
+        <v>0.8085</v>
       </c>
     </row>
     <row r="664">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="F664" t="inlineStr"/>
       <c r="G664" t="n">
-        <v>0.8739</v>
+        <v>0.8744</v>
       </c>
       <c r="H664" t="n">
         <v>0.8487</v>
@@ -17716,10 +17716,10 @@
       </c>
       <c r="F665" t="inlineStr"/>
       <c r="G665" t="n">
-        <v>0.9434</v>
+        <v>0.9457</v>
       </c>
       <c r="H665" t="n">
-        <v>0.9594</v>
+        <v>0.9607</v>
       </c>
     </row>
     <row r="666">
@@ -17742,10 +17742,10 @@
       </c>
       <c r="F666" t="inlineStr"/>
       <c r="G666" t="n">
-        <v>0.9464</v>
+        <v>0.948</v>
       </c>
       <c r="H666" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9586</v>
       </c>
     </row>
     <row r="667">
@@ -17771,7 +17771,7 @@
         <v>0.9657</v>
       </c>
       <c r="H667" t="n">
-        <v>0.9663</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="668">
@@ -17846,7 +17846,7 @@
       </c>
       <c r="F670" t="inlineStr"/>
       <c r="G670" t="n">
-        <v>0.1034</v>
+        <v>0.1026</v>
       </c>
       <c r="H670" t="n">
         <v>0.1101</v>
@@ -17898,10 +17898,10 @@
       </c>
       <c r="F672" t="inlineStr"/>
       <c r="G672" t="n">
-        <v>0.1095</v>
+        <v>0.1066</v>
       </c>
       <c r="H672" t="n">
-        <v>0.1376</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="673">
@@ -17924,10 +17924,10 @@
       </c>
       <c r="F673" t="inlineStr"/>
       <c r="G673" t="n">
-        <v>0.3815</v>
+        <v>0.3928</v>
       </c>
       <c r="H673" t="n">
-        <v>0.3352</v>
+        <v>0.3409</v>
       </c>
     </row>
     <row r="674">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="F674" t="inlineStr"/>
       <c r="G674" t="n">
-        <v>0.2472</v>
+        <v>0.2487</v>
       </c>
       <c r="H674" t="n">
         <v>0.2355</v>
@@ -17976,10 +17976,10 @@
       </c>
       <c r="F675" t="inlineStr"/>
       <c r="G675" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.5805</v>
       </c>
       <c r="H675" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5243</v>
       </c>
     </row>
     <row r="676">
@@ -17993,19 +17993,19 @@
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
       <c r="G676" t="n">
-        <v>0.4956</v>
+        <v>0.3667</v>
       </c>
       <c r="H676" t="n">
-        <v>0.4547</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="677">
@@ -18045,19 +18045,19 @@
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
       <c r="G678" t="n">
-        <v>0.3667</v>
+        <v>0.4956</v>
       </c>
       <c r="H678" t="n">
-        <v>0.3278</v>
+        <v>0.4547</v>
       </c>
     </row>
     <row r="679">
@@ -18080,10 +18080,10 @@
       </c>
       <c r="F679" t="inlineStr"/>
       <c r="G679" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="H679" t="n">
-        <v>0.7543</v>
+        <v>0.8279</v>
       </c>
     </row>
     <row r="680">
@@ -18106,10 +18106,10 @@
       </c>
       <c r="F680" t="inlineStr"/>
       <c r="G680" t="n">
-        <v>0.65</v>
+        <v>0.7056</v>
       </c>
       <c r="H680" t="n">
-        <v>0.61</v>
+        <v>0.6579</v>
       </c>
     </row>
     <row r="681">
@@ -18158,10 +18158,10 @@
       </c>
       <c r="F682" t="inlineStr"/>
       <c r="G682" t="n">
-        <v>0.9424</v>
+        <v>0.9442</v>
       </c>
       <c r="H682" t="n">
-        <v>0.95</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="683">
@@ -18187,7 +18187,7 @@
         <v>0.8943</v>
       </c>
       <c r="H683" t="n">
-        <v>0.8803</v>
+        <v>0.8844</v>
       </c>
     </row>
     <row r="684">
@@ -18210,10 +18210,10 @@
       </c>
       <c r="F684" t="inlineStr"/>
       <c r="G684" t="n">
-        <v>0.0485</v>
+        <v>0.0479</v>
       </c>
       <c r="H684" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0607</v>
       </c>
     </row>
     <row r="685">
@@ -18236,10 +18236,10 @@
       </c>
       <c r="F685" t="inlineStr"/>
       <c r="G685" t="n">
-        <v>0.143</v>
+        <v>0.1328</v>
       </c>
       <c r="H685" t="n">
-        <v>0.1025</v>
+        <v>0.1018</v>
       </c>
     </row>
     <row r="686">
@@ -18262,10 +18262,10 @@
       </c>
       <c r="F686" t="inlineStr"/>
       <c r="G686" t="n">
-        <v>0.1459</v>
+        <v>0.1519</v>
       </c>
       <c r="H686" t="n">
-        <v>0.1585</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="687">
@@ -18288,10 +18288,10 @@
       </c>
       <c r="F687" t="inlineStr"/>
       <c r="G687" t="n">
-        <v>0.1213</v>
+        <v>0.1427</v>
       </c>
       <c r="H687" t="n">
-        <v>0.1157</v>
+        <v>0.1476</v>
       </c>
     </row>
     <row r="688">
@@ -18314,10 +18314,10 @@
       </c>
       <c r="F688" t="inlineStr"/>
       <c r="G688" t="n">
-        <v>0.2927</v>
+        <v>0.3211</v>
       </c>
       <c r="H688" t="n">
-        <v>0.221</v>
+        <v>0.2663</v>
       </c>
     </row>
     <row r="689">
@@ -18395,7 +18395,7 @@
         <v>0.2332</v>
       </c>
       <c r="H691" t="n">
-        <v>0.2415</v>
+        <v>0.2407</v>
       </c>
     </row>
     <row r="692">
@@ -18473,7 +18473,7 @@
         <v>0.8081</v>
       </c>
       <c r="H694" t="n">
-        <v>0.7669</v>
+        <v>0.7711</v>
       </c>
     </row>
     <row r="695">
@@ -18499,7 +18499,7 @@
         <v>0.8162</v>
       </c>
       <c r="H695" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.8182</v>
       </c>
     </row>
     <row r="696">
@@ -18551,7 +18551,7 @@
         <v>0.9</v>
       </c>
       <c r="H697" t="n">
-        <v>0.8686</v>
+        <v>0.8729</v>
       </c>
     </row>
     <row r="698">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="F699" t="inlineStr"/>
       <c r="G699" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H699" t="n">
         <v>0.0915</v>
@@ -18652,10 +18652,10 @@
       </c>
       <c r="F701" t="inlineStr"/>
       <c r="G701" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0953</v>
       </c>
       <c r="H701" t="n">
-        <v>0.1183</v>
+        <v>0.1173</v>
       </c>
     </row>
     <row r="702">
@@ -18678,10 +18678,10 @@
       </c>
       <c r="F702" t="inlineStr"/>
       <c r="G702" t="n">
-        <v>0.4177</v>
+        <v>0.4275</v>
       </c>
       <c r="H702" t="n">
-        <v>0.3016</v>
+        <v>0.3084</v>
       </c>
     </row>
     <row r="703">
@@ -18704,10 +18704,10 @@
       </c>
       <c r="F703" t="inlineStr"/>
       <c r="G703" t="n">
-        <v>0.2157</v>
+        <v>0.2144</v>
       </c>
       <c r="H703" t="n">
-        <v>0.2212</v>
+        <v>0.2211</v>
       </c>
     </row>
     <row r="704">
@@ -18730,10 +18730,10 @@
       </c>
       <c r="F704" t="inlineStr"/>
       <c r="G704" t="n">
-        <v>0.6093</v>
+        <v>0.5474</v>
       </c>
       <c r="H704" t="n">
-        <v>0.5483</v>
+        <v>0.507</v>
       </c>
     </row>
     <row r="705">
@@ -18747,19 +18747,19 @@
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
       <c r="G705" t="n">
-        <v>0.4907</v>
+        <v>0.3751</v>
       </c>
       <c r="H705" t="n">
-        <v>0.4356</v>
+        <v>0.3023</v>
       </c>
     </row>
     <row r="706">
@@ -18799,19 +18799,19 @@
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
       <c r="G707" t="n">
-        <v>0.3751</v>
+        <v>0.5089</v>
       </c>
       <c r="H707" t="n">
-        <v>0.3026</v>
+        <v>0.4356</v>
       </c>
     </row>
     <row r="708">
@@ -18834,10 +18834,10 @@
       </c>
       <c r="F708" t="inlineStr"/>
       <c r="G708" t="n">
-        <v>0.8143</v>
+        <v>0.8319</v>
       </c>
       <c r="H708" t="n">
-        <v>0.7492</v>
+        <v>0.8256</v>
       </c>
     </row>
     <row r="709">
@@ -18860,10 +18860,10 @@
       </c>
       <c r="F709" t="inlineStr"/>
       <c r="G709" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="H709" t="n">
-        <v>0.574</v>
+        <v>0.6114000000000001</v>
       </c>
     </row>
     <row r="710">
@@ -18889,7 +18889,7 @@
         <v>0.9391</v>
       </c>
       <c r="H710" t="n">
-        <v>0.9379</v>
+        <v>0.9384</v>
       </c>
     </row>
     <row r="711">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="F711" t="inlineStr"/>
       <c r="G711" t="n">
-        <v>0.9398</v>
+        <v>0.9425</v>
       </c>
       <c r="H711" t="n">
         <v>0.9489</v>
@@ -18938,7 +18938,7 @@
       </c>
       <c r="F712" t="inlineStr"/>
       <c r="G712" t="n">
-        <v>0.8958</v>
+        <v>0.8965</v>
       </c>
       <c r="H712" t="n">
         <v>0.8715000000000001</v>
@@ -18993,7 +18993,7 @@
         <v>0.0931</v>
       </c>
       <c r="H714" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.0843</v>
       </c>
     </row>
     <row r="715">
@@ -19016,10 +19016,10 @@
       </c>
       <c r="F715" t="inlineStr"/>
       <c r="G715" t="n">
-        <v>0.1025</v>
+        <v>0.1089</v>
       </c>
       <c r="H715" t="n">
-        <v>0.1838</v>
+        <v>0.1863</v>
       </c>
     </row>
     <row r="716">
@@ -19042,10 +19042,10 @@
       </c>
       <c r="F716" t="inlineStr"/>
       <c r="G716" t="n">
-        <v>0.0949</v>
+        <v>0.1097</v>
       </c>
       <c r="H716" t="n">
-        <v>0.1242</v>
+        <v>0.1454</v>
       </c>
     </row>
     <row r="717">
@@ -19068,10 +19068,10 @@
       </c>
       <c r="F717" t="inlineStr"/>
       <c r="G717" t="n">
-        <v>0.2929</v>
+        <v>0.3178</v>
       </c>
       <c r="H717" t="n">
-        <v>0.2613</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="718">
@@ -19146,10 +19146,10 @@
       </c>
       <c r="F720" t="inlineStr"/>
       <c r="G720" t="n">
-        <v>0.1911</v>
+        <v>0.1915</v>
       </c>
       <c r="H720" t="n">
-        <v>0.2306</v>
+        <v>0.2236</v>
       </c>
     </row>
     <row r="721">
@@ -19224,7 +19224,7 @@
       </c>
       <c r="F723" t="inlineStr"/>
       <c r="G723" t="n">
-        <v>0.7964</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="H723" t="n">
         <v>0.7924</v>
@@ -19250,10 +19250,10 @@
       </c>
       <c r="F724" t="inlineStr"/>
       <c r="G724" t="n">
-        <v>0.8134</v>
+        <v>0.8267</v>
       </c>
       <c r="H724" t="n">
-        <v>0.8046</v>
+        <v>0.8158</v>
       </c>
     </row>
     <row r="725">
@@ -19279,7 +19279,7 @@
         <v>0.8932</v>
       </c>
       <c r="H725" t="n">
-        <v>0.8504</v>
+        <v>0.8611</v>
       </c>
     </row>
     <row r="726">
@@ -19305,7 +19305,7 @@
         <v>0.8852</v>
       </c>
       <c r="H726" t="n">
-        <v>0.8627</v>
+        <v>0.8647</v>
       </c>
     </row>
     <row r="727">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F728" t="inlineStr"/>
       <c r="G728" t="n">
-        <v>0.0696</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H728" t="n">
         <v>0.07870000000000001</v>
@@ -19406,10 +19406,10 @@
       </c>
       <c r="F730" t="inlineStr"/>
       <c r="G730" t="n">
-        <v>0.0658</v>
+        <v>0.0646</v>
       </c>
       <c r="H730" t="n">
-        <v>0.0921</v>
+        <v>0.09130000000000001</v>
       </c>
     </row>
     <row r="731">
@@ -19432,10 +19432,10 @@
       </c>
       <c r="F731" t="inlineStr"/>
       <c r="G731" t="n">
-        <v>0.33</v>
+        <v>0.3382</v>
       </c>
       <c r="H731" t="n">
-        <v>0.2007</v>
+        <v>0.2032</v>
       </c>
     </row>
     <row r="732">
@@ -19458,7 +19458,7 @@
       </c>
       <c r="F732" t="inlineStr"/>
       <c r="G732" t="n">
-        <v>0.1583</v>
+        <v>0.1595</v>
       </c>
       <c r="H732" t="n">
         <v>0.1284</v>
@@ -19484,10 +19484,10 @@
       </c>
       <c r="F733" t="inlineStr"/>
       <c r="G733" t="n">
-        <v>0.5142</v>
+        <v>0.4466</v>
       </c>
       <c r="H733" t="n">
-        <v>0.4559</v>
+        <v>0.4008</v>
       </c>
     </row>
     <row r="734">
@@ -19501,19 +19501,19 @@
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
       <c r="G734" t="n">
-        <v>0.4489</v>
+        <v>0.323</v>
       </c>
       <c r="H734" t="n">
-        <v>0.3309</v>
+        <v>0.2035</v>
       </c>
     </row>
     <row r="735">
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F735" t="inlineStr"/>
       <c r="G735" t="n">
-        <v>0.1714</v>
+        <v>0.1653</v>
       </c>
       <c r="H735" t="n">
         <v>0.1349</v>
@@ -19553,19 +19553,19 @@
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
       <c r="G736" t="n">
-        <v>0.3253</v>
+        <v>0.4489</v>
       </c>
       <c r="H736" t="n">
-        <v>0.2035</v>
+        <v>0.3309</v>
       </c>
     </row>
     <row r="737">
@@ -19588,10 +19588,10 @@
       </c>
       <c r="F737" t="inlineStr"/>
       <c r="G737" t="n">
-        <v>0.708</v>
+        <v>0.7388</v>
       </c>
       <c r="H737" t="n">
-        <v>0.6924</v>
+        <v>0.7781</v>
       </c>
     </row>
     <row r="738">
@@ -19614,10 +19614,10 @@
       </c>
       <c r="F738" t="inlineStr"/>
       <c r="G738" t="n">
-        <v>0.5263</v>
+        <v>0.5713</v>
       </c>
       <c r="H738" t="n">
-        <v>0.4676</v>
+        <v>0.5044999999999999</v>
       </c>
     </row>
     <row r="739">
@@ -19666,10 +19666,10 @@
       </c>
       <c r="F740" t="inlineStr"/>
       <c r="G740" t="n">
-        <v>0.9241</v>
+        <v>0.9276</v>
       </c>
       <c r="H740" t="n">
-        <v>0.9268</v>
+        <v>0.9283</v>
       </c>
     </row>
     <row r="741">
@@ -19695,7 +19695,7 @@
         <v>0.8147</v>
       </c>
       <c r="H741" t="n">
-        <v>0.8312</v>
+        <v>0.8336</v>
       </c>
     </row>
     <row r="742">
@@ -19718,10 +19718,10 @@
       </c>
       <c r="F742" t="inlineStr"/>
       <c r="G742" t="n">
-        <v>0.0373</v>
+        <v>0.037</v>
       </c>
       <c r="H742" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="743">
@@ -19770,10 +19770,10 @@
       </c>
       <c r="F744" t="inlineStr"/>
       <c r="G744" t="n">
-        <v>0.0848</v>
+        <v>0.0905</v>
       </c>
       <c r="H744" t="n">
-        <v>0.1024</v>
+        <v>0.1101</v>
       </c>
     </row>
     <row r="745">
@@ -19796,10 +19796,10 @@
       </c>
       <c r="F745" t="inlineStr"/>
       <c r="G745" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0793</v>
       </c>
       <c r="H745" t="n">
-        <v>0.0809</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="746">
@@ -19822,10 +19822,10 @@
       </c>
       <c r="F746" t="inlineStr"/>
       <c r="G746" t="n">
-        <v>0.2044</v>
+        <v>0.2252</v>
       </c>
       <c r="H746" t="n">
-        <v>0.1549</v>
+        <v>0.1984</v>
       </c>
     </row>
     <row r="747">
@@ -19903,7 +19903,7 @@
         <v>0.1513</v>
       </c>
       <c r="H749" t="n">
-        <v>0.1261</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="750">
@@ -19981,7 +19981,7 @@
         <v>0.7071</v>
       </c>
       <c r="H752" t="n">
-        <v>0.703</v>
+        <v>0.7078</v>
       </c>
     </row>
     <row r="753">
@@ -20004,10 +20004,10 @@
       </c>
       <c r="F753" t="inlineStr"/>
       <c r="G753" t="n">
-        <v>0.7156</v>
+        <v>0.7199</v>
       </c>
       <c r="H753" t="n">
-        <v>0.7499</v>
+        <v>0.7585</v>
       </c>
     </row>
     <row r="754">
@@ -20033,7 +20033,7 @@
         <v>0.8184</v>
       </c>
       <c r="H754" t="n">
-        <v>0.8244</v>
+        <v>0.8283</v>
       </c>
     </row>
     <row r="755">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="F758" t="inlineStr"/>
       <c r="G758" t="n">
-        <v>0.0218</v>
+        <v>0.0217</v>
       </c>
       <c r="H758" t="n">
         <v>0.0339</v>
@@ -20163,7 +20163,7 @@
         <v>0.0222</v>
       </c>
       <c r="H759" t="n">
-        <v>0.0377</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="760">
@@ -20186,10 +20186,10 @@
       </c>
       <c r="F760" t="inlineStr"/>
       <c r="G760" t="n">
-        <v>0.0873</v>
+        <v>0.0984</v>
       </c>
       <c r="H760" t="n">
-        <v>0.1042</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="761">
@@ -20238,10 +20238,10 @@
       </c>
       <c r="F762" t="inlineStr"/>
       <c r="G762" t="n">
-        <v>0.2944</v>
+        <v>0.2574</v>
       </c>
       <c r="H762" t="n">
-        <v>0.2625</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="763">
@@ -20255,19 +20255,19 @@
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F763" t="inlineStr"/>
       <c r="G763" t="n">
-        <v>0.1898</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="H763" t="n">
-        <v>0.1436</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="764">
@@ -20293,7 +20293,7 @@
         <v>0.0578</v>
       </c>
       <c r="H764" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="765">
@@ -20307,19 +20307,19 @@
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
       <c r="G765" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1899</v>
       </c>
       <c r="H765" t="n">
-        <v>0.0896</v>
+        <v>0.1426</v>
       </c>
     </row>
     <row r="766">
@@ -20342,10 +20342,10 @@
       </c>
       <c r="F766" t="inlineStr"/>
       <c r="G766" t="n">
-        <v>0.4754</v>
+        <v>0.5359</v>
       </c>
       <c r="H766" t="n">
-        <v>0.4354</v>
+        <v>0.5094</v>
       </c>
     </row>
     <row r="767">
@@ -20368,10 +20368,10 @@
       </c>
       <c r="F767" t="inlineStr"/>
       <c r="G767" t="n">
-        <v>0.317</v>
+        <v>0.3894</v>
       </c>
       <c r="H767" t="n">
-        <v>0.2536</v>
+        <v>0.3016</v>
       </c>
     </row>
     <row r="768">
@@ -20397,7 +20397,7 @@
         <v>0.7438</v>
       </c>
       <c r="H768" t="n">
-        <v>0.7633</v>
+        <v>0.7658</v>
       </c>
     </row>
     <row r="769">
@@ -20475,7 +20475,7 @@
         <v>0.0158</v>
       </c>
       <c r="H771" t="n">
-        <v>0.0334</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="772">
@@ -20524,10 +20524,10 @@
       </c>
       <c r="F773" t="inlineStr"/>
       <c r="G773" t="n">
-        <v>0.0355</v>
+        <v>0.0372</v>
       </c>
       <c r="H773" t="n">
-        <v>0.0357</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="774">
@@ -20550,10 +20550,10 @@
       </c>
       <c r="F774" t="inlineStr"/>
       <c r="G774" t="n">
-        <v>0.025</v>
+        <v>0.0289</v>
       </c>
       <c r="H774" t="n">
-        <v>0.0325</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="775">
@@ -20576,10 +20576,10 @@
       </c>
       <c r="F775" t="inlineStr"/>
       <c r="G775" t="n">
-        <v>0.057</v>
+        <v>0.0757</v>
       </c>
       <c r="H775" t="n">
-        <v>0.0709</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="776">
@@ -20602,7 +20602,7 @@
       </c>
       <c r="F776" t="inlineStr"/>
       <c r="G776" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="H776" t="n">
         <v>0.0793</v>
@@ -20628,10 +20628,10 @@
       </c>
       <c r="F777" t="inlineStr"/>
       <c r="G777" t="n">
-        <v>0.1316</v>
+        <v>0.1288</v>
       </c>
       <c r="H777" t="n">
-        <v>0.1254</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="778">
@@ -20654,10 +20654,10 @@
       </c>
       <c r="F778" t="inlineStr"/>
       <c r="G778" t="n">
-        <v>0.0406</v>
+        <v>0.0393</v>
       </c>
       <c r="H778" t="n">
-        <v>0.0566</v>
+        <v>0.0543</v>
       </c>
     </row>
     <row r="779">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="F779" t="inlineStr"/>
       <c r="G779" t="n">
-        <v>0.2331</v>
+        <v>0.2289</v>
       </c>
       <c r="H779" t="n">
         <v>0.1919</v>
@@ -20709,7 +20709,7 @@
         <v>0.2076</v>
       </c>
       <c r="H780" t="n">
-        <v>0.2036</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="781">
@@ -20732,7 +20732,7 @@
       </c>
       <c r="F781" t="inlineStr"/>
       <c r="G781" t="n">
-        <v>0.297</v>
+        <v>0.2922</v>
       </c>
       <c r="H781" t="n">
         <v>0.2929</v>
@@ -20758,10 +20758,10 @@
       </c>
       <c r="F782" t="inlineStr"/>
       <c r="G782" t="n">
-        <v>0.5524</v>
+        <v>0.553</v>
       </c>
       <c r="H782" t="n">
-        <v>0.4879</v>
+        <v>0.4933</v>
       </c>
     </row>
     <row r="783">
@@ -20813,7 +20813,7 @@
         <v>0.6365</v>
       </c>
       <c r="H784" t="n">
-        <v>0.6072</v>
+        <v>0.6049</v>
       </c>
     </row>
     <row r="785">
@@ -20836,10 +20836,10 @@
       </c>
       <c r="F785" t="inlineStr"/>
       <c r="G785" t="n">
-        <v>0.0678</v>
+        <v>0.0614</v>
       </c>
       <c r="H785" t="n">
-        <v>0.0562</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="786">
@@ -20865,7 +20865,7 @@
         <v>0.0284</v>
       </c>
       <c r="H786" t="n">
-        <v>0.0315</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="787">
@@ -20888,10 +20888,10 @@
       </c>
       <c r="F787" t="inlineStr"/>
       <c r="G787" t="n">
-        <v>0.0206</v>
+        <v>0.0197</v>
       </c>
       <c r="H787" t="n">
-        <v>0.0332</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="788">
@@ -20914,10 +20914,10 @@
       </c>
       <c r="F788" t="inlineStr"/>
       <c r="G788" t="n">
-        <v>0.0271</v>
+        <v>0.0251</v>
       </c>
       <c r="H788" t="n">
-        <v>0.0347</v>
+        <v>0.0337</v>
       </c>
     </row>
     <row r="789">
@@ -20943,7 +20943,7 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="H789" t="n">
-        <v>0.0953</v>
+        <v>0.09619999999999999</v>
       </c>
     </row>
     <row r="790">
@@ -20966,10 +20966,10 @@
       </c>
       <c r="F790" t="inlineStr"/>
       <c r="G790" t="n">
-        <v>0.0515</v>
+        <v>0.049</v>
       </c>
       <c r="H790" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="791">
@@ -20992,10 +20992,10 @@
       </c>
       <c r="F791" t="inlineStr"/>
       <c r="G791" t="n">
-        <v>0.2893</v>
+        <v>0.2245</v>
       </c>
       <c r="H791" t="n">
-        <v>0.2624</v>
+        <v>0.2101</v>
       </c>
     </row>
     <row r="792">
@@ -21009,19 +21009,19 @@
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F792" t="inlineStr"/>
       <c r="G792" t="n">
-        <v>0.2045</v>
+        <v>0.0756</v>
       </c>
       <c r="H792" t="n">
-        <v>0.148</v>
+        <v>0.0827</v>
       </c>
     </row>
     <row r="793">
@@ -21044,10 +21044,10 @@
       </c>
       <c r="F793" t="inlineStr"/>
       <c r="G793" t="n">
-        <v>0.051</v>
+        <v>0.0437</v>
       </c>
       <c r="H793" t="n">
-        <v>0.0602</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="794">
@@ -21061,19 +21061,19 @@
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
       <c r="G794" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.1996</v>
       </c>
       <c r="H794" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.1452</v>
       </c>
     </row>
     <row r="795">
@@ -21096,10 +21096,10 @@
       </c>
       <c r="F795" t="inlineStr"/>
       <c r="G795" t="n">
-        <v>0.4634</v>
+        <v>0.5174</v>
       </c>
       <c r="H795" t="n">
-        <v>0.4547</v>
+        <v>0.4996</v>
       </c>
     </row>
     <row r="796">
@@ -21122,10 +21122,10 @@
       </c>
       <c r="F796" t="inlineStr"/>
       <c r="G796" t="n">
-        <v>0.2849</v>
+        <v>0.3507</v>
       </c>
       <c r="H796" t="n">
-        <v>0.2957</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="797">
@@ -21148,10 +21148,10 @@
       </c>
       <c r="F797" t="inlineStr"/>
       <c r="G797" t="n">
-        <v>0.7528</v>
+        <v>0.747</v>
       </c>
       <c r="H797" t="n">
-        <v>0.74</v>
+        <v>0.7363</v>
       </c>
     </row>
     <row r="798">
@@ -21174,10 +21174,10 @@
       </c>
       <c r="F798" t="inlineStr"/>
       <c r="G798" t="n">
-        <v>0.8385</v>
+        <v>0.836</v>
       </c>
       <c r="H798" t="n">
-        <v>0.7689</v>
+        <v>0.7491</v>
       </c>
     </row>
     <row r="799">
@@ -21200,10 +21200,10 @@
       </c>
       <c r="F799" t="inlineStr"/>
       <c r="G799" t="n">
-        <v>0.6846</v>
+        <v>0.6814</v>
       </c>
       <c r="H799" t="n">
-        <v>0.5829</v>
+        <v>0.5819</v>
       </c>
     </row>
     <row r="800">
@@ -21226,10 +21226,10 @@
       </c>
       <c r="F800" t="inlineStr"/>
       <c r="G800" t="n">
-        <v>0.015</v>
+        <v>0.0143</v>
       </c>
       <c r="H800" t="n">
-        <v>0.0253</v>
+        <v>0.0222</v>
       </c>
     </row>
     <row r="801">
@@ -21252,10 +21252,10 @@
       </c>
       <c r="F801" t="inlineStr"/>
       <c r="G801" t="n">
-        <v>0.0203</v>
+        <v>0.0188</v>
       </c>
       <c r="H801" t="n">
-        <v>0.0377</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="802">
@@ -21304,10 +21304,10 @@
       </c>
       <c r="F803" t="inlineStr"/>
       <c r="G803" t="n">
-        <v>0.0282</v>
+        <v>0.0311</v>
       </c>
       <c r="H803" t="n">
-        <v>0.036</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="804">
@@ -21330,10 +21330,10 @@
       </c>
       <c r="F804" t="inlineStr"/>
       <c r="G804" t="n">
-        <v>0.0615</v>
+        <v>0.0757</v>
       </c>
       <c r="H804" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="805">
@@ -21356,10 +21356,10 @@
       </c>
       <c r="F805" t="inlineStr"/>
       <c r="G805" t="n">
-        <v>0.1038</v>
+        <v>0.0891</v>
       </c>
       <c r="H805" t="n">
-        <v>0.0793</v>
+        <v>0.0779</v>
       </c>
     </row>
     <row r="806">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="F806" t="inlineStr"/>
       <c r="G806" t="n">
-        <v>0.1178</v>
+        <v>0.1145</v>
       </c>
       <c r="H806" t="n">
         <v>0.1026</v>
@@ -21408,10 +21408,10 @@
       </c>
       <c r="F807" t="inlineStr"/>
       <c r="G807" t="n">
-        <v>0.0418</v>
+        <v>0.0414</v>
       </c>
       <c r="H807" t="n">
-        <v>0.0536</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="808">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="F808" t="inlineStr"/>
       <c r="G808" t="n">
-        <v>0.189</v>
+        <v>0.1818</v>
       </c>
       <c r="H808" t="n">
         <v>0.1838</v>
@@ -21460,10 +21460,10 @@
       </c>
       <c r="F809" t="inlineStr"/>
       <c r="G809" t="n">
-        <v>0.1954</v>
+        <v>0.1842</v>
       </c>
       <c r="H809" t="n">
-        <v>0.1866</v>
+        <v>0.1733</v>
       </c>
     </row>
     <row r="810">
@@ -21486,10 +21486,10 @@
       </c>
       <c r="F810" t="inlineStr"/>
       <c r="G810" t="n">
-        <v>0.2501</v>
+        <v>0.2415</v>
       </c>
       <c r="H810" t="n">
-        <v>0.2844</v>
+        <v>0.2801</v>
       </c>
     </row>
     <row r="811">
@@ -21512,10 +21512,10 @@
       </c>
       <c r="F811" t="inlineStr"/>
       <c r="G811" t="n">
-        <v>0.5121</v>
+        <v>0.5067</v>
       </c>
       <c r="H811" t="n">
-        <v>0.4476</v>
+        <v>0.447</v>
       </c>
     </row>
     <row r="812">
@@ -21538,10 +21538,10 @@
       </c>
       <c r="F812" t="inlineStr"/>
       <c r="G812" t="n">
-        <v>0.6756</v>
+        <v>0.6745</v>
       </c>
       <c r="H812" t="n">
-        <v>0.5764</v>
+        <v>0.5718</v>
       </c>
     </row>
     <row r="813">
@@ -21564,10 +21564,10 @@
       </c>
       <c r="F813" t="inlineStr"/>
       <c r="G813" t="n">
-        <v>0.6711</v>
+        <v>0.6722</v>
       </c>
       <c r="H813" t="n">
-        <v>0.5377</v>
+        <v>0.5293</v>
       </c>
     </row>
     <row r="814">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="F814" t="inlineStr"/>
       <c r="G814" t="n">
-        <v>0.0445</v>
+        <v>0.0426</v>
       </c>
       <c r="H814" t="n">
         <v>0.0563</v>
@@ -21694,10 +21694,10 @@
       </c>
       <c r="F818" t="inlineStr"/>
       <c r="G818" t="n">
-        <v>0.0709</v>
+        <v>0.0713</v>
       </c>
       <c r="H818" t="n">
-        <v>0.0589</v>
+        <v>0.0609</v>
       </c>
     </row>
     <row r="819">
@@ -21723,7 +21723,7 @@
         <v>0.0307</v>
       </c>
       <c r="H819" t="n">
-        <v>0.0452</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="820">
@@ -21746,10 +21746,10 @@
       </c>
       <c r="F820" t="inlineStr"/>
       <c r="G820" t="n">
-        <v>0.2404</v>
+        <v>0.1723</v>
       </c>
       <c r="H820" t="n">
-        <v>0.1305</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="821">
@@ -21763,19 +21763,19 @@
       </c>
       <c r="C821" t="inlineStr"/>
       <c r="D821" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
       <c r="G821" t="n">
-        <v>0.1415</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H821" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0573</v>
       </c>
     </row>
     <row r="822">
@@ -21798,10 +21798,10 @@
       </c>
       <c r="F822" t="inlineStr"/>
       <c r="G822" t="n">
-        <v>0.0243</v>
+        <v>0.0236</v>
       </c>
       <c r="H822" t="n">
-        <v>0.0406</v>
+        <v>0.0394</v>
       </c>
     </row>
     <row r="823">
@@ -21815,19 +21815,19 @@
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
       <c r="G823" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1415</v>
       </c>
       <c r="H823" t="n">
-        <v>0.0573</v>
+        <v>0.09379999999999999</v>
       </c>
     </row>
     <row r="824">
@@ -21850,10 +21850,10 @@
       </c>
       <c r="F824" t="inlineStr"/>
       <c r="G824" t="n">
-        <v>0.355</v>
+        <v>0.4127</v>
       </c>
       <c r="H824" t="n">
-        <v>0.3249</v>
+        <v>0.4055</v>
       </c>
     </row>
     <row r="825">
@@ -21876,10 +21876,10 @@
       </c>
       <c r="F825" t="inlineStr"/>
       <c r="G825" t="n">
-        <v>0.1969</v>
+        <v>0.2656</v>
       </c>
       <c r="H825" t="n">
-        <v>0.1505</v>
+        <v>0.1853</v>
       </c>
     </row>
     <row r="826">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="F826" t="inlineStr"/>
       <c r="G826" t="n">
-        <v>0.6339</v>
+        <v>0.6351</v>
       </c>
       <c r="H826" t="n">
         <v>0.6208</v>
@@ -21931,7 +21931,7 @@
         <v>0.6931</v>
       </c>
       <c r="H827" t="n">
-        <v>0.6896</v>
+        <v>0.6874</v>
       </c>
     </row>
     <row r="828">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="F832" t="inlineStr"/>
       <c r="G832" t="n">
-        <v>0.0223</v>
+        <v>0.022</v>
       </c>
       <c r="H832" t="n">
         <v>0.026</v>
@@ -22084,10 +22084,10 @@
       </c>
       <c r="F833" t="inlineStr"/>
       <c r="G833" t="n">
-        <v>0.0373</v>
+        <v>0.0415</v>
       </c>
       <c r="H833" t="n">
-        <v>0.0525</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="834">
@@ -22110,10 +22110,10 @@
       </c>
       <c r="F834" t="inlineStr"/>
       <c r="G834" t="n">
-        <v>0.054</v>
+        <v>0.0532</v>
       </c>
       <c r="H834" t="n">
-        <v>0.0617</v>
+        <v>0.0599</v>
       </c>
     </row>
     <row r="835">
@@ -22136,10 +22136,10 @@
       </c>
       <c r="F835" t="inlineStr"/>
       <c r="G835" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="H835" t="n">
-        <v>0.0791</v>
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="836">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="F836" t="inlineStr"/>
       <c r="G836" t="n">
-        <v>0.0337</v>
+        <v>0.0322</v>
       </c>
       <c r="H836" t="n">
         <v>0.0343</v>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="F838" t="inlineStr"/>
       <c r="G838" t="n">
-        <v>0.1496</v>
+        <v>0.1389</v>
       </c>
       <c r="H838" t="n">
         <v>0.1068</v>
@@ -22240,7 +22240,7 @@
       </c>
       <c r="F839" t="inlineStr"/>
       <c r="G839" t="n">
-        <v>0.1756</v>
+        <v>0.1717</v>
       </c>
       <c r="H839" t="n">
         <v>0.1816</v>
@@ -22292,10 +22292,10 @@
       </c>
       <c r="F841" t="inlineStr"/>
       <c r="G841" t="n">
-        <v>0.4236</v>
+        <v>0.4282</v>
       </c>
       <c r="H841" t="n">
-        <v>0.3244</v>
+        <v>0.3255</v>
       </c>
     </row>
     <row r="842">
@@ -22321,7 +22321,7 @@
         <v>0.5235</v>
       </c>
       <c r="H842" t="n">
-        <v>0.5057</v>
+        <v>0.5016</v>
       </c>
     </row>
     <row r="843">
@@ -22344,10 +22344,10 @@
       </c>
       <c r="F843" t="inlineStr"/>
       <c r="G843" t="n">
-        <v>0.0538</v>
+        <v>0.0523</v>
       </c>
       <c r="H843" t="n">
-        <v>0.0554</v>
+        <v>0.0544</v>
       </c>
     </row>
     <row r="844">
@@ -22373,7 +22373,7 @@
         <v>0.0255</v>
       </c>
       <c r="H844" t="n">
-        <v>0.024</v>
+        <v>0.0237</v>
       </c>
     </row>
     <row r="845">
@@ -22399,7 +22399,7 @@
         <v>0.0179</v>
       </c>
       <c r="H845" t="n">
-        <v>0.0317</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="846">
@@ -22448,10 +22448,10 @@
       </c>
       <c r="F847" t="inlineStr"/>
       <c r="G847" t="n">
-        <v>0.0527</v>
+        <v>0.0535</v>
       </c>
       <c r="H847" t="n">
-        <v>0.0646</v>
+        <v>0.0735</v>
       </c>
     </row>
     <row r="848">
@@ -22477,7 +22477,7 @@
         <v>0.0312</v>
       </c>
       <c r="H848" t="n">
-        <v>0.0473</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="849">
@@ -22500,10 +22500,10 @@
       </c>
       <c r="F849" t="inlineStr"/>
       <c r="G849" t="n">
-        <v>0.2336</v>
+        <v>0.1629</v>
       </c>
       <c r="H849" t="n">
-        <v>0.1731</v>
+        <v>0.1194</v>
       </c>
     </row>
     <row r="850">
@@ -22517,19 +22517,19 @@
       </c>
       <c r="C850" t="inlineStr"/>
       <c r="D850" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F850" t="inlineStr"/>
       <c r="G850" t="n">
-        <v>0.166</v>
+        <v>0.0574</v>
       </c>
       <c r="H850" t="n">
-        <v>0.1059</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="851">
@@ -22552,7 +22552,7 @@
       </c>
       <c r="F851" t="inlineStr"/>
       <c r="G851" t="n">
-        <v>0.0291</v>
+        <v>0.0288</v>
       </c>
       <c r="H851" t="n">
         <v>0.0459</v>
@@ -22569,19 +22569,19 @@
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
       <c r="G852" t="n">
-        <v>0.0574</v>
+        <v>0.166</v>
       </c>
       <c r="H852" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1046</v>
       </c>
     </row>
     <row r="853">
@@ -22604,10 +22604,10 @@
       </c>
       <c r="F853" t="inlineStr"/>
       <c r="G853" t="n">
-        <v>0.3377</v>
+        <v>0.394</v>
       </c>
       <c r="H853" t="n">
-        <v>0.3339</v>
+        <v>0.4071</v>
       </c>
     </row>
     <row r="854">
@@ -22630,10 +22630,10 @@
       </c>
       <c r="F854" t="inlineStr"/>
       <c r="G854" t="n">
-        <v>0.1945</v>
+        <v>0.2503</v>
       </c>
       <c r="H854" t="n">
-        <v>0.1883</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="855">
@@ -22659,7 +22659,7 @@
         <v>0.6795</v>
       </c>
       <c r="H855" t="n">
-        <v>0.6405</v>
+        <v>0.6387</v>
       </c>
     </row>
     <row r="856">
@@ -22760,10 +22760,10 @@
       </c>
       <c r="F859" t="inlineStr"/>
       <c r="G859" t="n">
-        <v>0.02</v>
+        <v>0.0198</v>
       </c>
       <c r="H859" t="n">
-        <v>0.0346</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="860">
@@ -22786,10 +22786,10 @@
       </c>
       <c r="F860" t="inlineStr"/>
       <c r="G860" t="n">
-        <v>0.022</v>
+        <v>0.0228</v>
       </c>
       <c r="H860" t="n">
-        <v>0.0261</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="861">
@@ -22812,10 +22812,10 @@
       </c>
       <c r="F861" t="inlineStr"/>
       <c r="G861" t="n">
-        <v>0.0253</v>
+        <v>0.0266</v>
       </c>
       <c r="H861" t="n">
-        <v>0.0304</v>
+        <v>0.0323</v>
       </c>
     </row>
     <row r="862">
@@ -22838,10 +22838,10 @@
       </c>
       <c r="F862" t="inlineStr"/>
       <c r="G862" t="n">
-        <v>0.0412</v>
+        <v>0.0575</v>
       </c>
       <c r="H862" t="n">
-        <v>0.0577</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="863">
@@ -22867,7 +22867,7 @@
         <v>0.0572</v>
       </c>
       <c r="H863" t="n">
-        <v>0.0645</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="864">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="F864" t="inlineStr"/>
       <c r="G864" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.0738</v>
       </c>
       <c r="H864" t="n">
         <v>0.0857</v>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="F866" t="inlineStr"/>
       <c r="G866" t="n">
-        <v>0.1314</v>
+        <v>0.1271</v>
       </c>
       <c r="H866" t="n">
         <v>0.1</v>
@@ -22968,7 +22968,7 @@
       </c>
       <c r="F867" t="inlineStr"/>
       <c r="G867" t="n">
-        <v>0.1373</v>
+        <v>0.1353</v>
       </c>
       <c r="H867" t="n">
         <v>0.1148</v>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="F869" t="inlineStr"/>
       <c r="G869" t="n">
-        <v>0.3928</v>
+        <v>0.3951</v>
       </c>
       <c r="H869" t="n">
         <v>0.3635</v>
@@ -23046,10 +23046,10 @@
       </c>
       <c r="F870" t="inlineStr"/>
       <c r="G870" t="n">
-        <v>0.4623</v>
+        <v>0.4707</v>
       </c>
       <c r="H870" t="n">
-        <v>0.3289</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="871">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="F871" t="inlineStr"/>
       <c r="G871" t="n">
-        <v>0.4943</v>
+        <v>0.4984</v>
       </c>
       <c r="H871" t="n">
         <v>0.4765</v>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -625,11 +625,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -677,11 +677,11 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1431,11 +1431,11 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2185,11 +2185,11 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2887,11 +2887,11 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -2939,11 +2939,11 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -3693,11 +3693,11 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4395,11 +4395,11 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -4447,11 +4447,11 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5149,11 +5149,11 @@
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -5201,11 +5201,11 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -5738,11 +5738,11 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -5764,11 +5764,11 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -5790,11 +5790,11 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -5816,11 +5816,11 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -5842,11 +5842,11 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -5868,11 +5868,11 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -5894,11 +5894,11 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -5920,11 +5920,11 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -5946,20 +5946,20 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -5972,11 +5972,11 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -5998,11 +5998,11 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -6024,11 +6024,11 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -6050,11 +6050,11 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -6076,11 +6076,11 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -6102,11 +6102,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -6128,11 +6128,11 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -6154,11 +6154,11 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -6180,11 +6180,11 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -6206,11 +6206,11 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -6232,11 +6232,11 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -6258,11 +6258,11 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -6284,11 +6284,11 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -6310,11 +6310,11 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -6336,11 +6336,11 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -6362,11 +6362,11 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -6388,11 +6388,11 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -6414,11 +6414,11 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -6440,11 +6440,11 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -6466,11 +6466,11 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -6683,11 +6683,11 @@
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -6709,11 +6709,11 @@
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -7246,11 +7246,11 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -7272,11 +7272,11 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -7298,11 +7298,11 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -7324,11 +7324,11 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -7350,11 +7350,11 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -7376,11 +7376,11 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -7402,11 +7402,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -7428,20 +7428,20 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -7454,11 +7454,11 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -7480,11 +7480,11 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -7506,11 +7506,11 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -7532,11 +7532,11 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -7558,11 +7558,11 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -7584,11 +7584,11 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -7610,11 +7610,11 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -7636,11 +7636,11 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -7662,11 +7662,11 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -7688,11 +7688,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -7714,11 +7714,11 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -7766,11 +7766,11 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -7792,11 +7792,11 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -7818,11 +7818,11 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -7844,11 +7844,11 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -7870,11 +7870,11 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -7896,11 +7896,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -7922,11 +7922,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -7948,11 +7948,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -7974,11 +7974,11 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -8191,11 +8191,11 @@
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -8243,11 +8243,11 @@
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -8945,11 +8945,11 @@
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -8997,11 +8997,11 @@
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -9699,11 +9699,11 @@
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -9751,11 +9751,11 @@
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -10453,11 +10453,11 @@
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -10505,11 +10505,11 @@
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -11207,11 +11207,11 @@
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -11259,11 +11259,11 @@
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -11961,11 +11961,11 @@
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -12013,11 +12013,11 @@
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -12715,11 +12715,11 @@
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -12767,11 +12767,11 @@
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -13469,11 +13469,11 @@
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -13521,11 +13521,11 @@
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -14223,11 +14223,11 @@
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -14275,11 +14275,11 @@
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -14977,11 +14977,11 @@
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -15029,11 +15029,11 @@
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -15731,11 +15731,11 @@
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -15783,11 +15783,11 @@
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -16485,11 +16485,11 @@
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -16537,11 +16537,11 @@
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -17239,11 +17239,11 @@
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -17291,11 +17291,11 @@
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -17993,11 +17993,11 @@
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -18045,11 +18045,11 @@
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -18747,11 +18747,11 @@
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -18799,11 +18799,11 @@
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -19501,11 +19501,11 @@
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -19553,11 +19553,11 @@
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -20255,11 +20255,11 @@
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F763" t="inlineStr"/>
@@ -20307,11 +20307,11 @@
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -21009,11 +21009,11 @@
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F792" t="inlineStr"/>
@@ -21061,11 +21061,11 @@
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
@@ -21763,11 +21763,11 @@
       </c>
       <c r="C821" t="inlineStr"/>
       <c r="D821" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
@@ -21815,11 +21815,11 @@
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -22517,11 +22517,11 @@
       </c>
       <c r="C850" t="inlineStr"/>
       <c r="D850" t="n">
-        <v>1610612748</v>
+        <v>1610612753</v>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F850" t="inlineStr"/>
@@ -22569,11 +22569,11 @@
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -547,11 +547,11 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -573,11 +573,11 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -625,11 +625,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -651,11 +651,11 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1301,11 +1301,11 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1327,11 +1327,11 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1405,11 +1405,11 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -2055,11 +2055,11 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -2081,11 +2081,11 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2809,11 +2809,11 @@
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -2835,11 +2835,11 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -2887,11 +2887,11 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -3476,11 +3476,11 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -3502,11 +3502,11 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -3528,11 +3528,11 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -3554,11 +3554,11 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -3580,20 +3580,20 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -3606,11 +3606,11 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3632,20 +3632,20 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -3658,20 +3658,20 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -3684,11 +3684,11 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3710,11 +3710,11 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3736,11 +3736,11 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3762,11 +3762,11 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3788,11 +3788,11 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3814,11 +3814,11 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3840,11 +3840,11 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3866,11 +3866,11 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3892,11 +3892,11 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3918,11 +3918,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3944,11 +3944,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3970,11 +3970,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3996,11 +3996,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -4022,11 +4022,11 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -4048,11 +4048,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -4074,11 +4074,11 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -4100,11 +4100,11 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -4126,11 +4126,11 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -4152,11 +4152,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -4178,11 +4178,11 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -4204,11 +4204,11 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -4230,11 +4230,11 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -4256,11 +4256,11 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -4282,11 +4282,11 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -4308,11 +4308,11 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -4334,20 +4334,20 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
@@ -4360,11 +4360,11 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -4386,20 +4386,20 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -4412,20 +4412,20 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -4438,11 +4438,11 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -4464,11 +4464,11 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -4490,11 +4490,11 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -4516,11 +4516,11 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -4542,11 +4542,11 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -4568,11 +4568,11 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -4594,11 +4594,11 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -4620,11 +4620,11 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -4646,11 +4646,11 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -4672,11 +4672,11 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -4698,11 +4698,11 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -4724,11 +4724,11 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -4750,11 +4750,11 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -4776,11 +4776,11 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4802,11 +4802,11 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -4828,11 +4828,11 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -4854,11 +4854,11 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -4880,11 +4880,11 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -4906,11 +4906,11 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4932,11 +4932,11 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4958,11 +4958,11 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -5097,11 +5097,11 @@
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
@@ -5123,11 +5123,11 @@
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
@@ -5149,11 +5149,11 @@
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -5175,11 +5175,11 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -5738,11 +5738,11 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -5764,11 +5764,11 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -5790,11 +5790,11 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -5816,11 +5816,11 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -5842,20 +5842,20 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
@@ -5868,20 +5868,20 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
@@ -5894,11 +5894,11 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -5920,20 +5920,20 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -5946,11 +5946,11 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -5972,11 +5972,11 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -5998,11 +5998,11 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -6024,11 +6024,11 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -6050,11 +6050,11 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -6076,11 +6076,11 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -6102,11 +6102,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -6128,11 +6128,11 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -6154,11 +6154,11 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -6180,11 +6180,11 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -6206,11 +6206,11 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -6232,11 +6232,11 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -6258,11 +6258,11 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -6284,11 +6284,11 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -6310,11 +6310,11 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -6336,11 +6336,11 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -6362,11 +6362,11 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -6388,11 +6388,11 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -6414,11 +6414,11 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -6440,11 +6440,11 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -6466,11 +6466,11 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -6492,11 +6492,11 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -6518,11 +6518,11 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -6544,11 +6544,11 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -6570,11 +6570,11 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -6596,20 +6596,20 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
@@ -6622,20 +6622,20 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
@@ -6648,11 +6648,11 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -6674,20 +6674,20 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -6700,11 +6700,11 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -6726,11 +6726,11 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -6752,11 +6752,11 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -6778,11 +6778,11 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -6804,11 +6804,11 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -6830,11 +6830,11 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -6856,11 +6856,11 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -6882,11 +6882,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -6908,11 +6908,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -6934,11 +6934,11 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -6960,11 +6960,11 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -6986,11 +6986,11 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -7012,11 +7012,11 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -7038,11 +7038,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -7064,11 +7064,11 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -7090,11 +7090,11 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -7116,11 +7116,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -7142,11 +7142,11 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -7168,11 +7168,11 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -7194,11 +7194,11 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -7220,11 +7220,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -7359,11 +7359,11 @@
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
@@ -7437,11 +7437,11 @@
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -7463,11 +7463,11 @@
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -8113,11 +8113,11 @@
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
@@ -8139,11 +8139,11 @@
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
@@ -8191,11 +8191,11 @@
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -8867,11 +8867,11 @@
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
@@ -8893,11 +8893,11 @@
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
@@ -8945,11 +8945,11 @@
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -8971,11 +8971,11 @@
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -9621,11 +9621,11 @@
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
@@ -9699,11 +9699,11 @@
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -9725,11 +9725,11 @@
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -10375,11 +10375,11 @@
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
@@ -10401,11 +10401,11 @@
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
@@ -10453,11 +10453,11 @@
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -10479,11 +10479,11 @@
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -11129,11 +11129,11 @@
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
@@ -11155,11 +11155,11 @@
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
@@ -11207,11 +11207,11 @@
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -11233,11 +11233,11 @@
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -11883,11 +11883,11 @@
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -11909,11 +11909,11 @@
       </c>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -11961,11 +11961,11 @@
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -11987,11 +11987,11 @@
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -12637,11 +12637,11 @@
       </c>
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -12663,11 +12663,11 @@
       </c>
       <c r="C471" t="inlineStr"/>
       <c r="D471" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -12715,11 +12715,11 @@
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -12741,11 +12741,11 @@
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -13391,11 +13391,11 @@
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -13417,11 +13417,11 @@
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -13469,11 +13469,11 @@
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -13495,11 +13495,11 @@
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -14145,11 +14145,11 @@
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -14171,11 +14171,11 @@
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -14223,11 +14223,11 @@
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -14249,11 +14249,11 @@
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -14899,11 +14899,11 @@
       </c>
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -14925,11 +14925,11 @@
       </c>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -14977,11 +14977,11 @@
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -15003,11 +15003,11 @@
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -15653,11 +15653,11 @@
       </c>
       <c r="C586" t="inlineStr"/>
       <c r="D586" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -15679,11 +15679,11 @@
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -15731,11 +15731,11 @@
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -15757,11 +15757,11 @@
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -16407,11 +16407,11 @@
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -16433,11 +16433,11 @@
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -16485,11 +16485,11 @@
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -16511,11 +16511,11 @@
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -17161,11 +17161,11 @@
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -17187,11 +17187,11 @@
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -17239,11 +17239,11 @@
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -17265,11 +17265,11 @@
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -17915,11 +17915,11 @@
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -17941,11 +17941,11 @@
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -17993,11 +17993,11 @@
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -18019,11 +18019,11 @@
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -18669,11 +18669,11 @@
       </c>
       <c r="C702" t="inlineStr"/>
       <c r="D702" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -18695,11 +18695,11 @@
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -18747,11 +18747,11 @@
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -18773,11 +18773,11 @@
       </c>
       <c r="C706" t="inlineStr"/>
       <c r="D706" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -19423,11 +19423,11 @@
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -19449,11 +19449,11 @@
       </c>
       <c r="C732" t="inlineStr"/>
       <c r="D732" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -19501,11 +19501,11 @@
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -19527,11 +19527,11 @@
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -20177,11 +20177,11 @@
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -20203,11 +20203,11 @@
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -20255,11 +20255,11 @@
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F763" t="inlineStr"/>
@@ -20281,11 +20281,11 @@
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F764" t="inlineStr"/>
@@ -20931,11 +20931,11 @@
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F789" t="inlineStr"/>
@@ -20957,11 +20957,11 @@
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F790" t="inlineStr"/>
@@ -21009,11 +21009,11 @@
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F792" t="inlineStr"/>
@@ -21035,11 +21035,11 @@
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F793" t="inlineStr"/>
@@ -21685,11 +21685,11 @@
       </c>
       <c r="C818" t="inlineStr"/>
       <c r="D818" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F818" t="inlineStr"/>
@@ -21711,11 +21711,11 @@
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F819" t="inlineStr"/>
@@ -21763,11 +21763,11 @@
       </c>
       <c r="C821" t="inlineStr"/>
       <c r="D821" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
@@ -21789,11 +21789,11 @@
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F822" t="inlineStr"/>
@@ -22439,11 +22439,11 @@
       </c>
       <c r="C847" t="inlineStr"/>
       <c r="D847" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F847" t="inlineStr"/>
@@ -22465,11 +22465,11 @@
       </c>
       <c r="C848" t="inlineStr"/>
       <c r="D848" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F848" t="inlineStr"/>
@@ -22517,11 +22517,11 @@
       </c>
       <c r="C850" t="inlineStr"/>
       <c r="D850" t="n">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F850" t="inlineStr"/>
@@ -22543,11 +22543,11 @@
       </c>
       <c r="C851" t="inlineStr"/>
       <c r="D851" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F851" t="inlineStr"/>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -625,11 +625,11 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -651,11 +651,11 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -677,11 +677,11 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1119,11 +1119,11 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1379,11 +1379,11 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1405,11 +1405,11 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1431,11 +1431,11 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1873,11 +1873,11 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -2133,11 +2133,11 @@
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2159,11 +2159,11 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
@@ -2185,11 +2185,11 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2601,11 +2601,11 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -2887,11 +2887,11 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -2939,11 +2939,11 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -3355,11 +3355,11 @@
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -3381,11 +3381,11 @@
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F124" t="inlineStr"/>
@@ -3667,11 +3667,11 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
@@ -3693,11 +3693,11 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
@@ -4109,11 +4109,11 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -4135,11 +4135,11 @@
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -4395,11 +4395,11 @@
       </c>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
@@ -4421,11 +4421,11 @@
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
@@ -4447,11 +4447,11 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -4863,11 +4863,11 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -5149,11 +5149,11 @@
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F182" t="inlineStr"/>
@@ -5175,11 +5175,11 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
@@ -5201,11 +5201,11 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -5617,11 +5617,11 @@
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -5643,11 +5643,11 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -5738,11 +5738,11 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -5764,11 +5764,11 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -5790,11 +5790,11 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -5816,11 +5816,11 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -5842,11 +5842,11 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -5868,11 +5868,11 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -5894,11 +5894,11 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -5920,20 +5920,20 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
@@ -5946,20 +5946,20 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
@@ -5972,11 +5972,11 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -5998,11 +5998,11 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -6024,11 +6024,11 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -6050,11 +6050,11 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -6076,11 +6076,11 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -6102,11 +6102,11 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -6128,11 +6128,11 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -6154,11 +6154,11 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -6180,11 +6180,11 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -6206,11 +6206,11 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -6232,11 +6232,11 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -6258,11 +6258,11 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -6284,11 +6284,11 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -6310,11 +6310,11 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -6336,11 +6336,11 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -6362,20 +6362,20 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -6388,20 +6388,20 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -6414,11 +6414,11 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -6440,11 +6440,11 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -6466,11 +6466,11 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -6492,11 +6492,11 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -6518,11 +6518,11 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -6544,11 +6544,11 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -6570,11 +6570,11 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -6596,11 +6596,11 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -6622,11 +6622,11 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -6648,11 +6648,11 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -6674,20 +6674,20 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
@@ -6700,20 +6700,20 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
@@ -6726,11 +6726,11 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -6752,11 +6752,11 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -6778,11 +6778,11 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -6804,11 +6804,11 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -6830,11 +6830,11 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -6856,11 +6856,11 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -6882,11 +6882,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -6908,11 +6908,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -6934,11 +6934,11 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -6960,11 +6960,11 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -6986,11 +6986,11 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -7012,11 +7012,11 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -7038,11 +7038,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -7064,11 +7064,11 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -7090,11 +7090,11 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -7116,20 +7116,20 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -7142,20 +7142,20 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -7168,11 +7168,11 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -7194,11 +7194,11 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -7220,11 +7220,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -7246,11 +7246,11 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -7272,11 +7272,11 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -7298,11 +7298,11 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -7324,11 +7324,11 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -7350,11 +7350,11 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -7376,11 +7376,11 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -7402,11 +7402,11 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -7428,20 +7428,20 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F270" t="inlineStr"/>
@@ -7454,20 +7454,20 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
@@ -7480,11 +7480,11 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -7506,11 +7506,11 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -7532,11 +7532,11 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -7558,11 +7558,11 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -7584,11 +7584,11 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -7610,11 +7610,11 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -7636,11 +7636,11 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -7662,11 +7662,11 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -7688,11 +7688,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -7714,11 +7714,11 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -7766,11 +7766,11 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -7792,11 +7792,11 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -7818,11 +7818,11 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -7844,11 +7844,11 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -7870,20 +7870,20 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -7896,20 +7896,20 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -7922,11 +7922,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -7948,11 +7948,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -7974,11 +7974,11 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -8191,11 +8191,11 @@
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F299" t="inlineStr"/>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -8243,11 +8243,11 @@
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
@@ -8633,11 +8633,11 @@
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -8659,11 +8659,11 @@
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -8945,11 +8945,11 @@
       </c>
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
@@ -8971,11 +8971,11 @@
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
@@ -8997,11 +8997,11 @@
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
@@ -9387,11 +9387,11 @@
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -9413,11 +9413,11 @@
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -9699,11 +9699,11 @@
       </c>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F357" t="inlineStr"/>
@@ -9725,11 +9725,11 @@
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
@@ -9751,11 +9751,11 @@
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
@@ -10141,11 +10141,11 @@
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -10167,11 +10167,11 @@
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -10453,11 +10453,11 @@
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F386" t="inlineStr"/>
@@ -10479,11 +10479,11 @@
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
@@ -10505,11 +10505,11 @@
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
@@ -10895,11 +10895,11 @@
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -10921,11 +10921,11 @@
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -11207,11 +11207,11 @@
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F415" t="inlineStr"/>
@@ -11233,11 +11233,11 @@
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
@@ -11259,11 +11259,11 @@
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
@@ -11649,11 +11649,11 @@
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -11675,11 +11675,11 @@
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -11961,11 +11961,11 @@
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F444" t="inlineStr"/>
@@ -11987,11 +11987,11 @@
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -12013,11 +12013,11 @@
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -12403,11 +12403,11 @@
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -12429,11 +12429,11 @@
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -12715,11 +12715,11 @@
       </c>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
@@ -12741,11 +12741,11 @@
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -12767,11 +12767,11 @@
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -13157,11 +13157,11 @@
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -13183,11 +13183,11 @@
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -13469,11 +13469,11 @@
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
@@ -13495,11 +13495,11 @@
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -13521,11 +13521,11 @@
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -13911,11 +13911,11 @@
       </c>
       <c r="C519" t="inlineStr"/>
       <c r="D519" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -13937,11 +13937,11 @@
       </c>
       <c r="C520" t="inlineStr"/>
       <c r="D520" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -14223,11 +14223,11 @@
       </c>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F531" t="inlineStr"/>
@@ -14249,11 +14249,11 @@
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -14275,11 +14275,11 @@
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -14665,11 +14665,11 @@
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -14691,11 +14691,11 @@
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -14977,11 +14977,11 @@
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F560" t="inlineStr"/>
@@ -15003,11 +15003,11 @@
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -15029,11 +15029,11 @@
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -15419,11 +15419,11 @@
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -15445,11 +15445,11 @@
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -15731,11 +15731,11 @@
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F589" t="inlineStr"/>
@@ -15757,11 +15757,11 @@
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -15783,11 +15783,11 @@
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -16173,11 +16173,11 @@
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -16199,11 +16199,11 @@
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -16485,11 +16485,11 @@
       </c>
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F618" t="inlineStr"/>
@@ -16511,11 +16511,11 @@
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -16537,11 +16537,11 @@
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -16927,11 +16927,11 @@
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -16953,11 +16953,11 @@
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -17239,11 +17239,11 @@
       </c>
       <c r="C647" t="inlineStr"/>
       <c r="D647" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F647" t="inlineStr"/>
@@ -17265,11 +17265,11 @@
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -17291,11 +17291,11 @@
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -17681,11 +17681,11 @@
       </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -17707,11 +17707,11 @@
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -17993,11 +17993,11 @@
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F676" t="inlineStr"/>
@@ -18019,11 +18019,11 @@
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -18045,11 +18045,11 @@
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -18435,11 +18435,11 @@
       </c>
       <c r="C693" t="inlineStr"/>
       <c r="D693" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -18461,11 +18461,11 @@
       </c>
       <c r="C694" t="inlineStr"/>
       <c r="D694" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -18747,11 +18747,11 @@
       </c>
       <c r="C705" t="inlineStr"/>
       <c r="D705" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F705" t="inlineStr"/>
@@ -18773,11 +18773,11 @@
       </c>
       <c r="C706" t="inlineStr"/>
       <c r="D706" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -18799,11 +18799,11 @@
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -19189,11 +19189,11 @@
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -19215,11 +19215,11 @@
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -19310,11 +19310,11 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -19336,11 +19336,11 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -19362,11 +19362,11 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -19388,11 +19388,11 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -19414,11 +19414,11 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -19440,11 +19440,11 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -19466,11 +19466,11 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -19492,20 +19492,20 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
       <c r="D734" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F734" t="inlineStr"/>
@@ -19518,20 +19518,20 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -19544,20 +19544,20 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -19570,11 +19570,11 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -19596,11 +19596,11 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -19622,11 +19622,11 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -19648,11 +19648,11 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -19674,11 +19674,11 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -19700,11 +19700,11 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -19726,11 +19726,11 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -19752,11 +19752,11 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -19778,11 +19778,11 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -19804,11 +19804,11 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -19830,11 +19830,11 @@
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -19856,11 +19856,11 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
@@ -19882,11 +19882,11 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
@@ -19908,11 +19908,11 @@
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
@@ -19934,11 +19934,11 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
@@ -19960,20 +19960,20 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -19986,11 +19986,11 @@
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
@@ -20012,11 +20012,11 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
@@ -20038,11 +20038,11 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -20064,11 +20064,11 @@
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -20090,11 +20090,11 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
@@ -20116,11 +20116,11 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
@@ -20142,11 +20142,11 @@
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -20168,11 +20168,11 @@
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
@@ -20194,11 +20194,11 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
@@ -20220,11 +20220,11 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -20246,20 +20246,20 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
       <c r="D763" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E763" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F763" t="inlineStr"/>
@@ -20272,20 +20272,20 @@
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F764" t="inlineStr"/>
@@ -20298,20 +20298,20 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -20324,11 +20324,11 @@
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
@@ -20350,11 +20350,11 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
@@ -20376,11 +20376,11 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -20402,11 +20402,11 @@
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
@@ -20428,11 +20428,11 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
@@ -20454,11 +20454,11 @@
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
@@ -20480,11 +20480,11 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -20506,11 +20506,11 @@
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
@@ -20532,11 +20532,11 @@
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
@@ -20558,11 +20558,11 @@
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
@@ -20584,11 +20584,11 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -20610,11 +20610,11 @@
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -20636,11 +20636,11 @@
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
@@ -20662,11 +20662,11 @@
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
@@ -20688,11 +20688,11 @@
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -20714,20 +20714,20 @@
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
       <c r="D781" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F781" t="inlineStr"/>
@@ -20740,11 +20740,11 @@
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -20766,11 +20766,11 @@
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -20792,11 +20792,11 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -21009,11 +21009,11 @@
       </c>
       <c r="C792" t="inlineStr"/>
       <c r="D792" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F792" t="inlineStr"/>
@@ -21035,11 +21035,11 @@
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F793" t="inlineStr"/>
@@ -21061,11 +21061,11 @@
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
@@ -21477,11 +21477,11 @@
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F810" t="inlineStr"/>
@@ -21503,11 +21503,11 @@
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F811" t="inlineStr"/>
@@ -21763,11 +21763,11 @@
       </c>
       <c r="C821" t="inlineStr"/>
       <c r="D821" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E821" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F821" t="inlineStr"/>
@@ -21789,11 +21789,11 @@
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F822" t="inlineStr"/>
@@ -21815,11 +21815,11 @@
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -22231,11 +22231,11 @@
       </c>
       <c r="C839" t="inlineStr"/>
       <c r="D839" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F839" t="inlineStr"/>
@@ -22257,11 +22257,11 @@
       </c>
       <c r="C840" t="inlineStr"/>
       <c r="D840" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F840" t="inlineStr"/>
@@ -22517,11 +22517,11 @@
       </c>
       <c r="C850" t="inlineStr"/>
       <c r="D850" t="n">
-        <v>1610612766</v>
+        <v>1610612753</v>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="F850" t="inlineStr"/>
@@ -22543,11 +22543,11 @@
       </c>
       <c r="C851" t="inlineStr"/>
       <c r="D851" t="n">
-        <v>1610612753</v>
+        <v>1610612748</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Magic</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F851" t="inlineStr"/>
@@ -22569,11 +22569,11 @@
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -22985,11 +22985,11 @@
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F868" t="inlineStr"/>
@@ -23011,11 +23011,11 @@
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F869" t="inlineStr"/>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.5647</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.4603</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.4114</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0.535</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>0.4855</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.8073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.789</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.7237</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>0.6933</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.798</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.7703</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.8404</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.8169</v>
       </c>
     </row>
     <row r="9">
@@ -651,19 +651,19 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.6521</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.6197</v>
       </c>
     </row>
     <row r="10">
@@ -677,19 +677,19 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>0.778</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5</v>
+        <v>0.7417</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.9638</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5</v>
+        <v>0.9565</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.9135</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5</v>
+        <v>0.9013</v>
       </c>
     </row>
     <row r="13">
@@ -764,10 +764,10 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0.9653</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5</v>
+        <v>0.9594</v>
       </c>
     </row>
     <row r="14">
@@ -790,10 +790,10 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>0.9771</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5</v>
+        <v>0.9724</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.9388</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5</v>
+        <v>0.9316</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5</v>
+        <v>0.4353</v>
       </c>
     </row>
     <row r="32">
@@ -1258,10 +1258,10 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.5</v>
+        <v>0.449</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5</v>
+        <v>0.4119</v>
       </c>
     </row>
     <row r="33">
@@ -1284,10 +1284,10 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.5187</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5</v>
+        <v>0.4692</v>
       </c>
     </row>
     <row r="34">
@@ -1310,10 +1310,10 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.5</v>
+        <v>0.8222</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5</v>
+        <v>0.7961</v>
       </c>
     </row>
     <row r="35">
@@ -1336,10 +1336,10 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5</v>
+        <v>0.6542</v>
       </c>
     </row>
     <row r="36">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.5</v>
+        <v>0.803</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5</v>
+        <v>0.7785</v>
       </c>
     </row>
     <row r="37">
@@ -1388,10 +1388,10 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.5</v>
+        <v>0.8519</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.5</v>
+        <v>0.635</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5</v>
+        <v>0.6007</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.5</v>
+        <v>0.7759</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5</v>
+        <v>0.7389</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>0.975</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="41">
@@ -1492,10 +1492,10 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.5</v>
+        <v>0.9221</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5</v>
+        <v>0.912</v>
       </c>
     </row>
     <row r="42">
@@ -1518,10 +1518,10 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.5</v>
+        <v>0.9732</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5</v>
+        <v>0.9674</v>
       </c>
     </row>
     <row r="43">
@@ -1544,10 +1544,10 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>0.5</v>
+        <v>0.9805</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="44">
@@ -1570,10 +1570,10 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.5</v>
+        <v>0.9527</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5</v>
+        <v>0.9443</v>
       </c>
     </row>
     <row r="45">
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.5</v>
+        <v>0.5886</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5</v>
+        <v>0.5397</v>
       </c>
     </row>
     <row r="61">
@@ -2012,10 +2012,10 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>0.5</v>
+        <v>0.5881</v>
       </c>
       <c r="H61" t="n">
-        <v>0.5</v>
+        <v>0.551</v>
       </c>
     </row>
     <row r="62">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.5</v>
+        <v>0.5976</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5</v>
+        <v>0.5682</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.5</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5</v>
+        <v>0.8637</v>
       </c>
     </row>
     <row r="64">
@@ -2090,10 +2090,10 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0.5</v>
+        <v>0.778</v>
       </c>
       <c r="H64" t="n">
-        <v>0.5</v>
+        <v>0.7455000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.5</v>
+        <v>0.8729</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5</v>
+        <v>0.8528</v>
       </c>
     </row>
     <row r="66">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.5</v>
+        <v>0.9117</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5</v>
+        <v>0.8878</v>
       </c>
     </row>
     <row r="67">
@@ -2159,19 +2159,19 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.5</v>
+        <v>0.7056</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5</v>
+        <v>0.6721</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.5</v>
+        <v>0.8519</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.5</v>
+        <v>0.977</v>
       </c>
       <c r="H69" t="n">
-        <v>0.5</v>
+        <v>0.9738</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.5</v>
+        <v>0.9597</v>
       </c>
       <c r="H70" t="n">
-        <v>0.5</v>
+        <v>0.9516</v>
       </c>
     </row>
     <row r="71">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.5</v>
+        <v>0.9812</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2298,10 +2298,10 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>0.5</v>
+        <v>0.9811</v>
       </c>
       <c r="H72" t="n">
-        <v>0.5</v>
+        <v>0.9779</v>
       </c>
     </row>
     <row r="73">
@@ -2324,10 +2324,10 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.5</v>
+        <v>0.9719</v>
       </c>
       <c r="H73" t="n">
-        <v>0.5</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="74">
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.5</v>
+        <v>0.5145</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="90">
@@ -2766,10 +2766,10 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.5</v>
+        <v>0.5308</v>
       </c>
       <c r="H90" t="n">
-        <v>0.5</v>
+        <v>0.4813</v>
       </c>
     </row>
     <row r="91">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.5</v>
+        <v>0.4318</v>
       </c>
       <c r="H91" t="n">
-        <v>0.5</v>
+        <v>0.4024</v>
       </c>
     </row>
     <row r="92">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.5</v>
+        <v>0.8209</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="93">
@@ -2844,10 +2844,10 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0.5</v>
+        <v>0.7099</v>
       </c>
       <c r="H93" t="n">
-        <v>0.5</v>
+        <v>0.6675</v>
       </c>
     </row>
     <row r="94">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.5</v>
+        <v>0.8258</v>
       </c>
       <c r="H94" t="n">
-        <v>0.5</v>
+        <v>0.8013</v>
       </c>
     </row>
     <row r="95">
@@ -2896,10 +2896,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.5</v>
+        <v>0.8798</v>
       </c>
       <c r="H95" t="n">
-        <v>0.5</v>
+        <v>0.8483000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -2913,19 +2913,19 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.5</v>
+        <v>0.6345</v>
       </c>
       <c r="H96" t="n">
-        <v>0.5</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="97">
@@ -2939,19 +2939,19 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.5</v>
+        <v>0.8081</v>
       </c>
       <c r="H97" t="n">
-        <v>0.5</v>
+        <v>0.7653</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.5</v>
+        <v>0.9714</v>
       </c>
       <c r="H98" t="n">
-        <v>0.5</v>
+        <v>0.9669</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.5</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>0.5</v>
+        <v>0.9389</v>
       </c>
     </row>
     <row r="100">
@@ -3026,10 +3026,10 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>0.5</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="H100" t="n">
-        <v>0.5</v>
+        <v>0.9766</v>
       </c>
     </row>
     <row r="101">
@@ -3052,10 +3052,10 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0.5</v>
+        <v>0.9765</v>
       </c>
       <c r="H101" t="n">
-        <v>0.5</v>
+        <v>0.9722</v>
       </c>
     </row>
     <row r="102">
@@ -3078,10 +3078,10 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>0.5</v>
+        <v>0.9664</v>
       </c>
       <c r="H102" t="n">
-        <v>0.5</v>
+        <v>0.9612000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.5</v>
+        <v>0.211</v>
       </c>
       <c r="H118" t="n">
-        <v>0.5</v>
+        <v>0.1927</v>
       </c>
     </row>
     <row r="119">
@@ -3520,10 +3520,10 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.5</v>
+        <v>0.2039</v>
       </c>
       <c r="H119" t="n">
-        <v>0.5</v>
+        <v>0.1778</v>
       </c>
     </row>
     <row r="120">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.5</v>
+        <v>0.1363</v>
       </c>
       <c r="H120" t="n">
-        <v>0.5</v>
+        <v>0.1144</v>
       </c>
     </row>
     <row r="121">
@@ -3572,10 +3572,10 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.5</v>
+        <v>0.2134</v>
       </c>
       <c r="H121" t="n">
-        <v>0.5</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="122">
@@ -3598,10 +3598,10 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0.5</v>
+        <v>0.3986</v>
       </c>
       <c r="H122" t="n">
-        <v>0.5</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="123">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.5</v>
+        <v>0.5288</v>
       </c>
       <c r="H123" t="n">
-        <v>0.5</v>
+        <v>0.4934</v>
       </c>
     </row>
     <row r="124">
@@ -3650,10 +3650,10 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0.5</v>
+        <v>0.5677</v>
       </c>
       <c r="H124" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="125">
@@ -3667,19 +3667,19 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>0.5</v>
+        <v>0.329</v>
       </c>
       <c r="H125" t="n">
-        <v>0.5</v>
+        <v>0.2976</v>
       </c>
     </row>
     <row r="126">
@@ -3693,19 +3693,19 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>0.5</v>
+        <v>0.4872</v>
       </c>
       <c r="H126" t="n">
-        <v>0.5</v>
+        <v>0.4472</v>
       </c>
     </row>
     <row r="127">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.5</v>
+        <v>0.9182</v>
       </c>
       <c r="H127" t="n">
-        <v>0.5</v>
+        <v>0.8965</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.5</v>
+        <v>0.7765</v>
       </c>
       <c r="H128" t="n">
-        <v>0.5</v>
+        <v>0.7443</v>
       </c>
     </row>
     <row r="129">
@@ -3780,10 +3780,10 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.5</v>
+        <v>0.9473</v>
       </c>
       <c r="H129" t="n">
-        <v>0.5</v>
+        <v>0.9369</v>
       </c>
     </row>
     <row r="130">
@@ -3806,10 +3806,10 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.5</v>
+        <v>0.959</v>
       </c>
       <c r="H130" t="n">
-        <v>0.5</v>
+        <v>0.9489</v>
       </c>
     </row>
     <row r="131">
@@ -3832,10 +3832,10 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.5</v>
+        <v>0.8738</v>
       </c>
       <c r="H131" t="n">
-        <v>0.5</v>
+        <v>0.8554</v>
       </c>
     </row>
     <row r="132">
@@ -4248,10 +4248,10 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.5</v>
+        <v>0.3067</v>
       </c>
       <c r="H147" t="n">
-        <v>0.5</v>
+        <v>0.2763</v>
       </c>
     </row>
     <row r="148">
@@ -4274,10 +4274,10 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>0.5</v>
+        <v>0.3458</v>
       </c>
       <c r="H148" t="n">
-        <v>0.5</v>
+        <v>0.308</v>
       </c>
     </row>
     <row r="149">
@@ -4300,10 +4300,10 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>0.5</v>
+        <v>0.2545</v>
       </c>
       <c r="H149" t="n">
-        <v>0.5</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="150">
@@ -4326,10 +4326,10 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>0.5</v>
+        <v>0.3325</v>
       </c>
       <c r="H150" t="n">
-        <v>0.5</v>
+        <v>0.2901</v>
       </c>
     </row>
     <row r="151">
@@ -4352,10 +4352,10 @@
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>0.5</v>
+        <v>0.6409</v>
       </c>
       <c r="H151" t="n">
-        <v>0.5</v>
+        <v>0.6014</v>
       </c>
     </row>
     <row r="152">
@@ -4378,10 +4378,10 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="H152" t="n">
-        <v>0.5</v>
+        <v>0.624</v>
       </c>
     </row>
     <row r="153">
@@ -4404,10 +4404,10 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.5</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="H153" t="n">
-        <v>0.5</v>
+        <v>0.6762</v>
       </c>
     </row>
     <row r="154">
@@ -4421,19 +4421,19 @@
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="H154" t="n">
-        <v>0.5</v>
+        <v>0.4093</v>
       </c>
     </row>
     <row r="155">
@@ -4447,19 +4447,19 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.5</v>
+        <v>0.5782</v>
       </c>
       <c r="H155" t="n">
-        <v>0.5</v>
+        <v>0.5417999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -4482,10 +4482,10 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.5</v>
+        <v>0.9414</v>
       </c>
       <c r="H156" t="n">
-        <v>0.5</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="157">
@@ -4508,10 +4508,10 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>0.5</v>
+        <v>0.8823</v>
       </c>
       <c r="H157" t="n">
-        <v>0.5</v>
+        <v>0.8552</v>
       </c>
     </row>
     <row r="158">
@@ -4534,10 +4534,10 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.5</v>
+        <v>0.9698</v>
       </c>
       <c r="H158" t="n">
-        <v>0.5</v>
+        <v>0.9645</v>
       </c>
     </row>
     <row r="159">
@@ -4560,10 +4560,10 @@
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>0.5</v>
+        <v>0.9729</v>
       </c>
       <c r="H159" t="n">
-        <v>0.5</v>
+        <v>0.9661999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -4586,10 +4586,10 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>0.5</v>
+        <v>0.9324</v>
       </c>
       <c r="H160" t="n">
-        <v>0.5</v>
+        <v>0.9172</v>
       </c>
     </row>
     <row r="161">
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.5</v>
+        <v>0.2297</v>
       </c>
       <c r="H176" t="n">
-        <v>0.5</v>
+        <v>0.202</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.5</v>
+        <v>0.2215</v>
       </c>
       <c r="H177" t="n">
-        <v>0.5</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.5</v>
+        <v>0.1472</v>
       </c>
       <c r="H178" t="n">
-        <v>0.5</v>
+        <v>0.1271</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.5</v>
+        <v>0.1987</v>
       </c>
       <c r="H179" t="n">
-        <v>0.5</v>
+        <v>0.1742</v>
       </c>
     </row>
     <row r="180">
@@ -5106,10 +5106,10 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.5</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="H180" t="n">
-        <v>0.5</v>
+        <v>0.4712</v>
       </c>
     </row>
     <row r="181">
@@ -5132,10 +5132,10 @@
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>0.5</v>
+        <v>0.376</v>
       </c>
       <c r="H181" t="n">
-        <v>0.5</v>
+        <v>0.3439</v>
       </c>
     </row>
     <row r="182">
@@ -5158,10 +5158,10 @@
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.5</v>
+        <v>0.6011</v>
       </c>
       <c r="H182" t="n">
-        <v>0.5</v>
+        <v>0.5591</v>
       </c>
     </row>
     <row r="183">
@@ -5175,19 +5175,19 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>0.5</v>
+        <v>0.321</v>
       </c>
       <c r="H183" t="n">
-        <v>0.5</v>
+        <v>0.2804</v>
       </c>
     </row>
     <row r="184">
@@ -5201,19 +5201,19 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>0.5</v>
+        <v>0.4805</v>
       </c>
       <c r="H184" t="n">
-        <v>0.5</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="185">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.5</v>
+        <v>0.9216</v>
       </c>
       <c r="H185" t="n">
-        <v>0.5</v>
+        <v>0.9004</v>
       </c>
     </row>
     <row r="186">
@@ -5262,10 +5262,10 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>0.5</v>
+        <v>0.8035</v>
       </c>
       <c r="H186" t="n">
-        <v>0.5</v>
+        <v>0.7733</v>
       </c>
     </row>
     <row r="187">
@@ -5288,10 +5288,10 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.5</v>
+        <v>0.9543</v>
       </c>
       <c r="H187" t="n">
-        <v>0.5</v>
+        <v>0.9458</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.5</v>
+        <v>0.9573</v>
       </c>
       <c r="H188" t="n">
-        <v>0.5</v>
+        <v>0.9486</v>
       </c>
     </row>
     <row r="189">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.5</v>
+        <v>0.8935</v>
       </c>
       <c r="H189" t="n">
-        <v>0.5</v>
+        <v>0.8686</v>
       </c>
     </row>
     <row r="190">
@@ -5756,10 +5756,10 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.5</v>
+        <v>0.1831</v>
       </c>
       <c r="H205" t="n">
-        <v>0.5</v>
+        <v>0.1596</v>
       </c>
     </row>
     <row r="206">
@@ -5782,10 +5782,10 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.5</v>
+        <v>0.1769</v>
       </c>
       <c r="H206" t="n">
-        <v>0.5</v>
+        <v>0.1481</v>
       </c>
     </row>
     <row r="207">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.5</v>
+        <v>0.1122</v>
       </c>
       <c r="H207" t="n">
-        <v>0.5</v>
+        <v>0.0883</v>
       </c>
     </row>
     <row r="208">
@@ -5834,10 +5834,10 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.5</v>
+        <v>0.1517</v>
       </c>
       <c r="H208" t="n">
-        <v>0.5</v>
+        <v>0.1202</v>
       </c>
     </row>
     <row r="209">
@@ -5860,10 +5860,10 @@
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="H209" t="n">
-        <v>0.5</v>
+        <v>0.4323</v>
       </c>
     </row>
     <row r="210">
@@ -5886,10 +5886,10 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.5</v>
+        <v>0.3238</v>
       </c>
       <c r="H210" t="n">
-        <v>0.5</v>
+        <v>0.2858</v>
       </c>
     </row>
     <row r="211">
@@ -5912,10 +5912,10 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.5</v>
+        <v>0.4409</v>
       </c>
       <c r="H211" t="n">
-        <v>0.5</v>
+        <v>0.3989</v>
       </c>
     </row>
     <row r="212">
@@ -5929,19 +5929,19 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.5</v>
+        <v>0.2731</v>
       </c>
       <c r="H212" t="n">
-        <v>0.5</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="213">
@@ -5955,19 +5955,19 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>0.5</v>
+        <v>0.4158</v>
       </c>
       <c r="H213" t="n">
-        <v>0.5</v>
+        <v>0.3798</v>
       </c>
     </row>
     <row r="214">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.5</v>
+        <v>0.9023</v>
       </c>
       <c r="H214" t="n">
-        <v>0.5</v>
+        <v>0.8786</v>
       </c>
     </row>
     <row r="215">
@@ -6016,10 +6016,10 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.5</v>
+        <v>0.7381</v>
       </c>
       <c r="H215" t="n">
-        <v>0.5</v>
+        <v>0.7174</v>
       </c>
     </row>
     <row r="216">
@@ -6042,10 +6042,10 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.5</v>
+        <v>0.9373</v>
       </c>
       <c r="H216" t="n">
-        <v>0.5</v>
+        <v>0.9264</v>
       </c>
     </row>
     <row r="217">
@@ -6068,10 +6068,10 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.5</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H217" t="n">
-        <v>0.5</v>
+        <v>0.9335</v>
       </c>
     </row>
     <row r="218">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.5</v>
+        <v>0.839</v>
       </c>
       <c r="H218" t="n">
-        <v>0.5</v>
+        <v>0.8232</v>
       </c>
     </row>
     <row r="219">
@@ -6492,11 +6492,11 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -6510,19 +6510,19 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.5</v>
+        <v>0.3803</v>
       </c>
       <c r="H234" t="n">
-        <v>0.5</v>
+        <v>0.3479</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -6536,19 +6536,19 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.5</v>
+        <v>0.3993</v>
       </c>
       <c r="H235" t="n">
-        <v>0.5</v>
+        <v>0.365</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -6562,19 +6562,19 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.5</v>
+        <v>0.3279</v>
       </c>
       <c r="H236" t="n">
-        <v>0.5</v>
+        <v>0.2944</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -6588,19 +6588,19 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.5</v>
+        <v>0.407</v>
       </c>
       <c r="H237" t="n">
-        <v>0.5</v>
+        <v>0.3655</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -6614,19 +6614,19 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>0.5</v>
+        <v>0.7024</v>
       </c>
       <c r="H238" t="n">
-        <v>0.5</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -6640,19 +6640,19 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.5</v>
+        <v>0.5907</v>
       </c>
       <c r="H239" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -6666,19 +6666,19 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>0.5</v>
+        <v>0.7196</v>
       </c>
       <c r="H240" t="n">
-        <v>0.5</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -6692,45 +6692,45 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.5</v>
+        <v>0.761</v>
       </c>
       <c r="H241" t="n">
-        <v>0.5</v>
+        <v>0.7269</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.5</v>
+        <v>0.669</v>
       </c>
       <c r="H242" t="n">
-        <v>0.5</v>
+        <v>0.6303</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -6744,19 +6744,19 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.5</v>
+        <v>0.9633</v>
       </c>
       <c r="H243" t="n">
-        <v>0.5</v>
+        <v>0.9573</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -6770,19 +6770,19 @@
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>0.5</v>
+        <v>0.9126</v>
       </c>
       <c r="H244" t="n">
-        <v>0.5</v>
+        <v>0.8968</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -6796,19 +6796,19 @@
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
-        <v>0.5</v>
+        <v>0.973</v>
       </c>
       <c r="H245" t="n">
-        <v>0.5</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -6822,19 +6822,19 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.5</v>
+        <v>0.9781</v>
       </c>
       <c r="H246" t="n">
-        <v>0.5</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -6848,19 +6848,19 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.5</v>
+        <v>0.946</v>
       </c>
       <c r="H247" t="n">
-        <v>0.5</v>
+        <v>0.9362</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -6882,11 +6882,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -6908,11 +6908,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -6934,11 +6934,11 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -6960,11 +6960,11 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -6986,11 +6986,11 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -7012,11 +7012,11 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -7038,11 +7038,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -7064,11 +7064,11 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -7090,11 +7090,11 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -7116,11 +7116,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -7142,11 +7142,11 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -7168,11 +7168,11 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -7194,11 +7194,11 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -7220,11 +7220,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -7246,11 +7246,11 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -7264,19 +7264,19 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.5</v>
+        <v>0.2583</v>
       </c>
       <c r="H263" t="n">
-        <v>0.5</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -7290,19 +7290,19 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.5</v>
+        <v>0.2611</v>
       </c>
       <c r="H264" t="n">
-        <v>0.5</v>
+        <v>0.2241</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -7316,19 +7316,19 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.5</v>
+        <v>0.1835</v>
       </c>
       <c r="H265" t="n">
-        <v>0.5</v>
+        <v>0.1481</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -7342,19 +7342,19 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.5</v>
+        <v>0.2347</v>
       </c>
       <c r="H266" t="n">
-        <v>0.5</v>
+        <v>0.1919</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -7368,19 +7368,19 @@
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>0.5</v>
+        <v>0.5528</v>
       </c>
       <c r="H267" t="n">
-        <v>0.5</v>
+        <v>0.5128</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -7394,19 +7394,19 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.5</v>
+        <v>0.4582</v>
       </c>
       <c r="H268" t="n">
-        <v>0.5</v>
+        <v>0.4218</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -7420,19 +7420,19 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>0.5</v>
+        <v>0.552</v>
       </c>
       <c r="H269" t="n">
-        <v>0.5</v>
+        <v>0.5195</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -7446,45 +7446,45 @@
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="n">
-        <v>0.5</v>
+        <v>0.6202</v>
       </c>
       <c r="H270" t="n">
-        <v>0.5</v>
+        <v>0.5842000000000001</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.5</v>
+        <v>0.3697</v>
       </c>
       <c r="H271" t="n">
-        <v>0.5</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -7498,19 +7498,19 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.5</v>
+        <v>0.9379</v>
       </c>
       <c r="H272" t="n">
-        <v>0.5</v>
+        <v>0.9177999999999999</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -7524,19 +7524,19 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.5</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H273" t="n">
-        <v>0.5</v>
+        <v>0.7949000000000001</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -7550,19 +7550,19 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.5</v>
+        <v>0.9597</v>
       </c>
       <c r="H274" t="n">
-        <v>0.5</v>
+        <v>0.9522</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -7576,19 +7576,19 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.5</v>
+        <v>0.9641</v>
       </c>
       <c r="H275" t="n">
-        <v>0.5</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -7602,19 +7602,19 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.5</v>
+        <v>0.9112</v>
       </c>
       <c r="H276" t="n">
-        <v>0.5</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -7636,11 +7636,11 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -7662,11 +7662,11 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -7688,11 +7688,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -7714,11 +7714,11 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -7766,11 +7766,11 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -7792,11 +7792,11 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -7818,11 +7818,11 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -7844,11 +7844,11 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -7870,11 +7870,11 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -7896,11 +7896,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -7922,11 +7922,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -7948,11 +7948,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -7974,11 +7974,11 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.5</v>
+        <v>0.0435</v>
       </c>
       <c r="H292" t="n">
-        <v>0.5</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.5</v>
+        <v>0.0298</v>
       </c>
       <c r="H293" t="n">
-        <v>0.5</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.5</v>
+        <v>0.0262</v>
       </c>
       <c r="H294" t="n">
-        <v>0.5</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.5</v>
+        <v>0.0331</v>
       </c>
       <c r="H295" t="n">
-        <v>0.5</v>
+        <v>0.0286</v>
       </c>
     </row>
     <row r="296">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.5</v>
+        <v>0.1035</v>
       </c>
       <c r="H296" t="n">
-        <v>0.5</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="297">
@@ -8148,10 +8148,10 @@
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.5</v>
+        <v>0.0747</v>
       </c>
       <c r="H297" t="n">
-        <v>0.5</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.5</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="H298" t="n">
-        <v>0.5</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="299">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.5</v>
+        <v>0.1214</v>
       </c>
       <c r="H299" t="n">
-        <v>0.5</v>
+        <v>0.0977</v>
       </c>
     </row>
     <row r="300">
@@ -8217,19 +8217,19 @@
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.5</v>
+        <v>0.0427</v>
       </c>
       <c r="H300" t="n">
-        <v>0.5</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="301">
@@ -8243,19 +8243,19 @@
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.5</v>
+        <v>0.0822</v>
       </c>
       <c r="H301" t="n">
-        <v>0.5</v>
+        <v>0.0621</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.5</v>
+        <v>0.2904</v>
       </c>
       <c r="H302" t="n">
-        <v>0.5</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="303">
@@ -8304,10 +8304,10 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.5</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="H303" t="n">
-        <v>0.5</v>
+        <v>0.6286</v>
       </c>
     </row>
     <row r="304">
@@ -8330,10 +8330,10 @@
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.5</v>
+        <v>0.6796</v>
       </c>
       <c r="H304" t="n">
-        <v>0.5</v>
+        <v>0.6391</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.5</v>
+        <v>0.4494</v>
       </c>
       <c r="H305" t="n">
-        <v>0.5</v>
+        <v>0.3971</v>
       </c>
     </row>
     <row r="306">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.5</v>
+        <v>0.0987</v>
       </c>
       <c r="H321" t="n">
-        <v>0.5</v>
+        <v>0.08649999999999999</v>
       </c>
     </row>
     <row r="322">
@@ -8798,10 +8798,10 @@
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="n">
-        <v>0.5</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="H322" t="n">
-        <v>0.5</v>
+        <v>0.0779</v>
       </c>
     </row>
     <row r="323">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.5</v>
+        <v>0.0484</v>
       </c>
       <c r="H323" t="n">
-        <v>0.5</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.5</v>
+        <v>0.0611</v>
       </c>
       <c r="H324" t="n">
-        <v>0.5</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.5</v>
+        <v>0.2557</v>
       </c>
       <c r="H325" t="n">
-        <v>0.5</v>
+        <v>0.2235</v>
       </c>
     </row>
     <row r="326">
@@ -8902,10 +8902,10 @@
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="n">
-        <v>0.5</v>
+        <v>0.1448</v>
       </c>
       <c r="H326" t="n">
-        <v>0.5</v>
+        <v>0.1177</v>
       </c>
     </row>
     <row r="327">
@@ -8928,10 +8928,10 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>0.5</v>
+        <v>0.2267</v>
       </c>
       <c r="H327" t="n">
-        <v>0.5</v>
+        <v>0.1965</v>
       </c>
     </row>
     <row r="328">
@@ -8954,10 +8954,10 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.5</v>
+        <v>0.2826</v>
       </c>
       <c r="H328" t="n">
-        <v>0.5</v>
+        <v>0.2619</v>
       </c>
     </row>
     <row r="329">
@@ -8971,19 +8971,19 @@
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>0.5</v>
+        <v>0.1032</v>
       </c>
       <c r="H329" t="n">
-        <v>0.5</v>
+        <v>0.08740000000000001</v>
       </c>
     </row>
     <row r="330">
@@ -8997,19 +8997,19 @@
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.5</v>
+        <v>0.2051</v>
       </c>
       <c r="H330" t="n">
-        <v>0.5</v>
+        <v>0.186</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.5</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="H331" t="n">
-        <v>0.5</v>
+        <v>0.7096</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.5</v>
+        <v>0.8621</v>
       </c>
       <c r="H332" t="n">
-        <v>0.5</v>
+        <v>0.8342000000000001</v>
       </c>
     </row>
     <row r="333">
@@ -9084,10 +9084,10 @@
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.5</v>
+        <v>0.8739</v>
       </c>
       <c r="H333" t="n">
-        <v>0.5</v>
+        <v>0.8389</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.5</v>
+        <v>0.6834</v>
       </c>
       <c r="H334" t="n">
-        <v>0.5</v>
+        <v>0.6544</v>
       </c>
     </row>
     <row r="335">
@@ -9526,10 +9526,10 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>0.5</v>
+        <v>0.0406</v>
       </c>
       <c r="H350" t="n">
-        <v>0.5</v>
+        <v>0.0347</v>
       </c>
     </row>
     <row r="351">
@@ -9552,10 +9552,10 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.5</v>
+        <v>0.0326</v>
       </c>
       <c r="H351" t="n">
-        <v>0.5</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="352">
@@ -9578,10 +9578,10 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.5</v>
+        <v>0.0217</v>
       </c>
       <c r="H352" t="n">
-        <v>0.5</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="353">
@@ -9604,10 +9604,10 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>0.5</v>
+        <v>0.0234</v>
       </c>
       <c r="H353" t="n">
-        <v>0.5</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="354">
@@ -9630,10 +9630,10 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.5</v>
+        <v>0.0631</v>
       </c>
       <c r="H354" t="n">
-        <v>0.5</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="355">
@@ -9656,10 +9656,10 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.5</v>
+        <v>0.0355</v>
       </c>
       <c r="H355" t="n">
-        <v>0.5</v>
+        <v>0.0302</v>
       </c>
     </row>
     <row r="356">
@@ -9682,10 +9682,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.5</v>
+        <v>0.0542</v>
       </c>
       <c r="H356" t="n">
-        <v>0.5</v>
+        <v>0.0457</v>
       </c>
     </row>
     <row r="357">
@@ -9708,10 +9708,10 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.5</v>
+        <v>0.0736</v>
       </c>
       <c r="H357" t="n">
-        <v>0.5</v>
+        <v>0.06270000000000001</v>
       </c>
     </row>
     <row r="358">
@@ -9725,19 +9725,19 @@
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>0.5</v>
+        <v>0.0323</v>
       </c>
       <c r="H358" t="n">
-        <v>0.5</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="359">
@@ -9751,19 +9751,19 @@
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.5</v>
+        <v>0.0478</v>
       </c>
       <c r="H359" t="n">
-        <v>0.5</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="360">
@@ -9786,10 +9786,10 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.5</v>
+        <v>0.3714</v>
       </c>
       <c r="H360" t="n">
-        <v>0.5</v>
+        <v>0.3352</v>
       </c>
     </row>
     <row r="361">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.5</v>
+        <v>0.1658</v>
       </c>
       <c r="H361" t="n">
-        <v>0.5</v>
+        <v>0.1379</v>
       </c>
     </row>
     <row r="362">
@@ -9838,10 +9838,10 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>0.5</v>
+        <v>0.5409</v>
       </c>
       <c r="H362" t="n">
-        <v>0.5</v>
+        <v>0.4923</v>
       </c>
     </row>
     <row r="363">
@@ -9864,10 +9864,10 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>0.5</v>
+        <v>0.297</v>
       </c>
       <c r="H363" t="n">
-        <v>0.5</v>
+        <v>0.2735</v>
       </c>
     </row>
     <row r="364">
@@ -10280,10 +10280,10 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.5</v>
+        <v>0.0276</v>
       </c>
       <c r="H379" t="n">
-        <v>0.5</v>
+        <v>0.0229</v>
       </c>
     </row>
     <row r="380">
@@ -10306,10 +10306,10 @@
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
-        <v>0.5</v>
+        <v>0.0229</v>
       </c>
       <c r="H380" t="n">
-        <v>0.5</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="381">
@@ -10332,10 +10332,10 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.5</v>
+        <v>0.0221</v>
       </c>
       <c r="H381" t="n">
-        <v>0.5</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="382">
@@ -10358,10 +10358,10 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>0.5</v>
+        <v>0.0278</v>
       </c>
       <c r="H382" t="n">
-        <v>0.5</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="383">
@@ -10384,10 +10384,10 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.5</v>
+        <v>0.0511</v>
       </c>
       <c r="H383" t="n">
-        <v>0.5</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="384">
@@ -10410,10 +10410,10 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>0.5</v>
+        <v>0.0338</v>
       </c>
       <c r="H384" t="n">
-        <v>0.5</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="385">
@@ -10436,10 +10436,10 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.5</v>
+        <v>0.0514</v>
       </c>
       <c r="H385" t="n">
-        <v>0.5</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="386">
@@ -10462,10 +10462,10 @@
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.5</v>
+        <v>0.0665</v>
       </c>
       <c r="H386" t="n">
-        <v>0.5</v>
+        <v>0.0559</v>
       </c>
     </row>
     <row r="387">
@@ -10479,19 +10479,19 @@
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.5</v>
+        <v>0.0257</v>
       </c>
       <c r="H387" t="n">
-        <v>0.5</v>
+        <v>0.0219</v>
       </c>
     </row>
     <row r="388">
@@ -10505,19 +10505,19 @@
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.5</v>
+        <v>0.0433</v>
       </c>
       <c r="H388" t="n">
-        <v>0.5</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="389">
@@ -10540,10 +10540,10 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.5</v>
+        <v>0.3609</v>
       </c>
       <c r="H389" t="n">
-        <v>0.5</v>
+        <v>0.3204</v>
       </c>
     </row>
     <row r="390">
@@ -10566,10 +10566,10 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.5</v>
+        <v>0.1611</v>
       </c>
       <c r="H390" t="n">
-        <v>0.5</v>
+        <v>0.1261</v>
       </c>
     </row>
     <row r="391">
@@ -10592,10 +10592,10 @@
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>0.5</v>
+        <v>0.5077</v>
       </c>
       <c r="H391" t="n">
-        <v>0.5</v>
+        <v>0.4591</v>
       </c>
     </row>
     <row r="392">
@@ -10618,10 +10618,10 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>0.5</v>
+        <v>0.2787</v>
       </c>
       <c r="H392" t="n">
-        <v>0.5</v>
+        <v>0.2351</v>
       </c>
     </row>
     <row r="393">
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.5</v>
+        <v>0.0684</v>
       </c>
       <c r="H408" t="n">
-        <v>0.5</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="409">
@@ -11060,10 +11060,10 @@
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
-        <v>0.5</v>
+        <v>0.0557</v>
       </c>
       <c r="H409" t="n">
-        <v>0.5</v>
+        <v>0.0473</v>
       </c>
     </row>
     <row r="410">
@@ -11086,10 +11086,10 @@
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>0.5</v>
+        <v>0.0339</v>
       </c>
       <c r="H410" t="n">
-        <v>0.5</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="411">
@@ -11112,10 +11112,10 @@
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
-        <v>0.5</v>
+        <v>0.0388</v>
       </c>
       <c r="H411" t="n">
-        <v>0.5</v>
+        <v>0.0336</v>
       </c>
     </row>
     <row r="412">
@@ -11138,10 +11138,10 @@
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>0.5</v>
+        <v>0.1446</v>
       </c>
       <c r="H412" t="n">
-        <v>0.5</v>
+        <v>0.1262</v>
       </c>
     </row>
     <row r="413">
@@ -11164,10 +11164,10 @@
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>0.5</v>
+        <v>0.0828</v>
       </c>
       <c r="H413" t="n">
-        <v>0.5</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="414">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.5</v>
+        <v>0.1314</v>
       </c>
       <c r="H414" t="n">
-        <v>0.5</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="415">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.5</v>
+        <v>0.1768</v>
       </c>
       <c r="H415" t="n">
-        <v>0.5</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="416">
@@ -11233,19 +11233,19 @@
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.5</v>
+        <v>0.0638</v>
       </c>
       <c r="H416" t="n">
-        <v>0.5</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="417">
@@ -11259,19 +11259,19 @@
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.5</v>
+        <v>0.1061</v>
       </c>
       <c r="H417" t="n">
-        <v>0.5</v>
+        <v>0.0888</v>
       </c>
     </row>
     <row r="418">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.5</v>
+        <v>0.6029</v>
       </c>
       <c r="H418" t="n">
-        <v>0.5</v>
+        <v>0.5506</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.5</v>
+        <v>0.3456</v>
       </c>
       <c r="H419" t="n">
-        <v>0.5</v>
+        <v>0.3166</v>
       </c>
     </row>
     <row r="420">
@@ -11346,10 +11346,10 @@
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>0.5</v>
+        <v>0.7265</v>
       </c>
       <c r="H420" t="n">
-        <v>0.5</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="421">
@@ -11372,10 +11372,10 @@
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
-        <v>0.5</v>
+        <v>0.7649</v>
       </c>
       <c r="H421" t="n">
-        <v>0.5</v>
+        <v>0.7213000000000001</v>
       </c>
     </row>
     <row r="422">
@@ -11987,11 +11987,11 @@
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -12013,11 +12013,11 @@
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -12741,11 +12741,11 @@
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -12767,11 +12767,11 @@
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -13495,11 +13495,11 @@
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -13521,11 +13521,11 @@
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -14249,11 +14249,11 @@
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -14275,11 +14275,11 @@
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -15003,11 +15003,11 @@
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -15029,11 +15029,11 @@
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -15757,11 +15757,11 @@
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -15783,11 +15783,11 @@
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -16511,11 +16511,11 @@
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -16537,11 +16537,11 @@
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -17265,11 +17265,11 @@
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -17291,11 +17291,11 @@
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -18019,11 +18019,11 @@
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -18045,11 +18045,11 @@
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -18773,11 +18773,11 @@
       </c>
       <c r="C706" t="inlineStr"/>
       <c r="D706" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -18799,11 +18799,11 @@
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -19527,11 +19527,11 @@
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -19553,11 +19553,11 @@
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -20281,11 +20281,11 @@
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F764" t="inlineStr"/>
@@ -20307,11 +20307,11 @@
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -21035,11 +21035,11 @@
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F793" t="inlineStr"/>
@@ -21061,11 +21061,11 @@
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
@@ -21789,11 +21789,11 @@
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F822" t="inlineStr"/>
@@ -21815,11 +21815,11 @@
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -22543,11 +22543,11 @@
       </c>
       <c r="C851" t="inlineStr"/>
       <c r="D851" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F851" t="inlineStr"/>
@@ -22569,11 +22569,11 @@
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.5647</v>
+        <v>0.3982</v>
       </c>
       <c r="H2" t="n">
-        <v>0.519</v>
+        <v>0.3438</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.4603</v>
+        <v>0.4221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4114</v>
+        <v>0.3715</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.535</v>
+        <v>0.4473</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4855</v>
+        <v>0.4014</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.8073</v>
+        <v>0.6611</v>
       </c>
       <c r="H5" t="n">
-        <v>0.789</v>
+        <v>0.6244</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.7237</v>
+        <v>0.6176</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6933</v>
+        <v>0.5764</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.798</v>
+        <v>0.7118</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7703</v>
+        <v>0.6687</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.8404</v>
+        <v>0.8053</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8169</v>
+        <v>0.7723</v>
       </c>
     </row>
     <row r="9">
@@ -651,19 +651,19 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.6521</v>
+        <v>0.6906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6197</v>
+        <v>0.6339</v>
       </c>
     </row>
     <row r="10">
@@ -677,19 +677,19 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.778</v>
+        <v>0.5614</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7417</v>
+        <v>0.5159</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9638</v>
+        <v>0.9204</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9565</v>
+        <v>0.9102</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.9135</v>
+        <v>0.8662</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9013</v>
+        <v>0.8494</v>
       </c>
     </row>
     <row r="13">
@@ -755,19 +755,19 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.9653</v>
+        <v>0.9575</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9594</v>
+        <v>0.9475</v>
       </c>
     </row>
     <row r="14">
@@ -781,19 +781,19 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.9771</v>
+        <v>0.9529</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9724</v>
+        <v>0.9439</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9388</v>
+        <v>0.9212</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9316</v>
+        <v>0.9132</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.481</v>
+        <v>0.6562</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4353</v>
+        <v>0.6018</v>
       </c>
     </row>
     <row r="32">
@@ -1258,10 +1258,10 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.449</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4119</v>
+        <v>0.5379</v>
       </c>
     </row>
     <row r="33">
@@ -1284,10 +1284,10 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.5187</v>
+        <v>0.5894</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4692</v>
+        <v>0.5459000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1310,10 +1310,10 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.8222</v>
+        <v>0.8167</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7961</v>
+        <v>0.7873</v>
       </c>
     </row>
     <row r="35">
@@ -1336,10 +1336,10 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.7605</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6542</v>
+        <v>0.7299</v>
       </c>
     </row>
     <row r="36">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.803</v>
+        <v>0.8446</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7785</v>
+        <v>0.8275</v>
       </c>
     </row>
     <row r="37">
@@ -1388,10 +1388,10 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.8519</v>
+        <v>0.9201</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8231000000000001</v>
+        <v>0.8978</v>
       </c>
     </row>
     <row r="38">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.635</v>
+        <v>0.841</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6007</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="39">
@@ -1431,19 +1431,19 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.7759</v>
+        <v>0.7153</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7389</v>
+        <v>0.6808999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.975</v>
+        <v>0.9768</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9702</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="41">
@@ -1492,10 +1492,10 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.9221</v>
+        <v>0.9529</v>
       </c>
       <c r="H41" t="n">
-        <v>0.912</v>
+        <v>0.9437</v>
       </c>
     </row>
     <row r="42">
@@ -1509,19 +1509,19 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.9732</v>
+        <v>0.9813</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9674</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="43">
@@ -1535,19 +1535,19 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>0.9805</v>
+        <v>0.9822</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9771</v>
+        <v>0.9787</v>
       </c>
     </row>
     <row r="44">
@@ -1570,10 +1570,10 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.9527</v>
+        <v>0.9749</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9443</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="45">
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.5886</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5397</v>
+        <v>0.5779</v>
       </c>
     </row>
     <row r="61">
@@ -2012,10 +2012,10 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>0.5881</v>
+        <v>0.4621</v>
       </c>
       <c r="H61" t="n">
-        <v>0.551</v>
+        <v>0.4309</v>
       </c>
     </row>
     <row r="62">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.5976</v>
+        <v>0.5468</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5682</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.8856000000000001</v>
+        <v>0.7691</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8637</v>
+        <v>0.7387</v>
       </c>
     </row>
     <row r="64">
@@ -2090,10 +2090,10 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0.778</v>
+        <v>0.7247</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.6963</v>
       </c>
     </row>
     <row r="65">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.8729</v>
+        <v>0.8262</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8528</v>
+        <v>0.8084</v>
       </c>
     </row>
     <row r="66">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.9117</v>
+        <v>0.9096</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8878</v>
+        <v>0.8839</v>
       </c>
     </row>
     <row r="67">
@@ -2159,19 +2159,19 @@
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.7056</v>
+        <v>0.8167</v>
       </c>
       <c r="H67" t="n">
-        <v>0.6721</v>
+        <v>0.7794</v>
       </c>
     </row>
     <row r="68">
@@ -2185,19 +2185,19 @@
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.8519</v>
+        <v>0.6576</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8165</v>
+        <v>0.6277</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.977</v>
+        <v>0.9717</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9738</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9597</v>
+        <v>0.9463</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9516</v>
+        <v>0.9353</v>
       </c>
     </row>
     <row r="71">
@@ -2263,19 +2263,19 @@
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.9812</v>
+        <v>0.978</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -2289,19 +2289,19 @@
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>0.9811</v>
+        <v>0.9812</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9779</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="73">
@@ -2324,10 +2324,10 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.9719</v>
+        <v>0.9731</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9661</v>
+        <v>0.9679</v>
       </c>
     </row>
     <row r="74">
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.5145</v>
+        <v>0.5986</v>
       </c>
       <c r="H89" t="n">
-        <v>0.465</v>
+        <v>0.5527</v>
       </c>
     </row>
     <row r="90">
@@ -2766,10 +2766,10 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.5308</v>
+        <v>0.4541</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4813</v>
+        <v>0.4106</v>
       </c>
     </row>
     <row r="91">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.4318</v>
+        <v>0.49</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4024</v>
+        <v>0.4532</v>
       </c>
     </row>
     <row r="92">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.8209</v>
+        <v>0.771</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7866</v>
+        <v>0.7346</v>
       </c>
     </row>
     <row r="93">
@@ -2844,10 +2844,10 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0.7099</v>
+        <v>0.7149</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6675</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="94">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.8258</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="H94" t="n">
-        <v>0.8013</v>
+        <v>0.8043</v>
       </c>
     </row>
     <row r="95">
@@ -2896,10 +2896,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.8798</v>
+        <v>0.9142</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.8884</v>
       </c>
     </row>
     <row r="96">
@@ -2913,19 +2913,19 @@
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.6345</v>
+        <v>0.8316</v>
       </c>
       <c r="H96" t="n">
-        <v>0.593</v>
+        <v>0.7882</v>
       </c>
     </row>
     <row r="97">
@@ -2939,19 +2939,19 @@
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.8081</v>
+        <v>0.6523</v>
       </c>
       <c r="H97" t="n">
-        <v>0.7653</v>
+        <v>0.6097</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.9714</v>
+        <v>0.9702</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9669</v>
+        <v>0.9659</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9389</v>
+        <v>0.9409</v>
       </c>
     </row>
     <row r="100">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9746</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9766</v>
+        <v>0.9704</v>
       </c>
     </row>
     <row r="101">
@@ -3043,19 +3043,19 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0.9765</v>
+        <v>0.9813</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9722</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="102">
@@ -3078,10 +3078,10 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>0.9664</v>
+        <v>0.9732</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9703000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.211</v>
+        <v>0.3756</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1927</v>
+        <v>0.3389</v>
       </c>
     </row>
     <row r="119">
@@ -3520,10 +3520,10 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.2039</v>
+        <v>0.2127</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1778</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="120">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.1363</v>
+        <v>0.2613</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1144</v>
+        <v>0.2309</v>
       </c>
     </row>
     <row r="121">
@@ -3572,10 +3572,10 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.2134</v>
+        <v>0.2654</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1791</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="122">
@@ -3598,10 +3598,10 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0.3986</v>
+        <v>0.4516</v>
       </c>
       <c r="H122" t="n">
-        <v>0.3591</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="123">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.5288</v>
+        <v>0.5998</v>
       </c>
       <c r="H123" t="n">
-        <v>0.4934</v>
+        <v>0.5694</v>
       </c>
     </row>
     <row r="124">
@@ -3650,10 +3650,10 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0.5677</v>
+        <v>0.7055</v>
       </c>
       <c r="H124" t="n">
-        <v>0.54</v>
+        <v>0.6682</v>
       </c>
     </row>
     <row r="125">
@@ -3667,19 +3667,19 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>0.329</v>
+        <v>0.579</v>
       </c>
       <c r="H125" t="n">
-        <v>0.2976</v>
+        <v>0.5411</v>
       </c>
     </row>
     <row r="126">
@@ -3693,19 +3693,19 @@
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>0.4872</v>
+        <v>0.4036</v>
       </c>
       <c r="H126" t="n">
-        <v>0.4472</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="127">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.9182</v>
+        <v>0.9232</v>
       </c>
       <c r="H127" t="n">
-        <v>0.8965</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.7765</v>
+        <v>0.8394</v>
       </c>
       <c r="H128" t="n">
-        <v>0.7443</v>
+        <v>0.8073</v>
       </c>
     </row>
     <row r="129">
@@ -3771,19 +3771,19 @@
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.9473</v>
+        <v>0.9655</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9369</v>
+        <v>0.9579</v>
       </c>
     </row>
     <row r="130">
@@ -3797,19 +3797,19 @@
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.959</v>
+        <v>0.9688</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9489</v>
+        <v>0.9618</v>
       </c>
     </row>
     <row r="131">
@@ -3832,10 +3832,10 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.8738</v>
+        <v>0.9378</v>
       </c>
       <c r="H131" t="n">
-        <v>0.8554</v>
+        <v>0.9248</v>
       </c>
     </row>
     <row r="132">
@@ -4248,10 +4248,10 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.3067</v>
+        <v>0.4236</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2763</v>
+        <v>0.3824</v>
       </c>
     </row>
     <row r="148">
@@ -4274,10 +4274,10 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>0.3458</v>
+        <v>0.2701</v>
       </c>
       <c r="H148" t="n">
-        <v>0.308</v>
+        <v>0.2395</v>
       </c>
     </row>
     <row r="149">
@@ -4300,10 +4300,10 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>0.2545</v>
+        <v>0.3037</v>
       </c>
       <c r="H149" t="n">
-        <v>0.222</v>
+        <v>0.2753</v>
       </c>
     </row>
     <row r="150">
@@ -4326,10 +4326,10 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>0.3325</v>
+        <v>0.328</v>
       </c>
       <c r="H150" t="n">
-        <v>0.2901</v>
+        <v>0.2851</v>
       </c>
     </row>
     <row r="151">
@@ -4352,10 +4352,10 @@
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>0.6409</v>
+        <v>0.581</v>
       </c>
       <c r="H151" t="n">
-        <v>0.6014</v>
+        <v>0.5484</v>
       </c>
     </row>
     <row r="152">
@@ -4378,10 +4378,10 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0.6561</v>
+        <v>0.6574</v>
       </c>
       <c r="H152" t="n">
-        <v>0.624</v>
+        <v>0.6262</v>
       </c>
     </row>
     <row r="153">
@@ -4404,10 +4404,10 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7621</v>
       </c>
       <c r="H153" t="n">
-        <v>0.6762</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="154">
@@ -4421,19 +4421,19 @@
       </c>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.44</v>
+        <v>0.5969</v>
       </c>
       <c r="H154" t="n">
-        <v>0.4093</v>
+        <v>0.5577</v>
       </c>
     </row>
     <row r="155">
@@ -4447,19 +4447,19 @@
       </c>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.5782</v>
+        <v>0.4523</v>
       </c>
       <c r="H155" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="156">
@@ -4482,10 +4482,10 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.9414</v>
+        <v>0.9313</v>
       </c>
       <c r="H156" t="n">
-        <v>0.9253</v>
+        <v>0.911</v>
       </c>
     </row>
     <row r="157">
@@ -4508,10 +4508,10 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>0.8823</v>
+        <v>0.8844</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8552</v>
+        <v>0.8579</v>
       </c>
     </row>
     <row r="158">
@@ -4525,19 +4525,19 @@
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.9698</v>
+        <v>0.9716</v>
       </c>
       <c r="H158" t="n">
-        <v>0.9645</v>
+        <v>0.9648</v>
       </c>
     </row>
     <row r="159">
@@ -4551,19 +4551,19 @@
       </c>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>0.9729</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9718</v>
       </c>
     </row>
     <row r="160">
@@ -4586,10 +4586,10 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>0.9324</v>
+        <v>0.9513</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9172</v>
+        <v>0.9402</v>
       </c>
     </row>
     <row r="161">
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.2297</v>
+        <v>0.3313</v>
       </c>
       <c r="H176" t="n">
-        <v>0.202</v>
+        <v>0.2882</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.2215</v>
+        <v>0.1725</v>
       </c>
       <c r="H177" t="n">
-        <v>0.197</v>
+        <v>0.1554</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.1472</v>
+        <v>0.1916</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1271</v>
+        <v>0.1738</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.1987</v>
+        <v>0.1957</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1742</v>
+        <v>0.1709</v>
       </c>
     </row>
     <row r="180">
@@ -5106,10 +5106,10 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.4306</v>
       </c>
       <c r="H180" t="n">
-        <v>0.4712</v>
+        <v>0.4002</v>
       </c>
     </row>
     <row r="181">
@@ -5132,10 +5132,10 @@
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>0.376</v>
+        <v>0.3738</v>
       </c>
       <c r="H181" t="n">
-        <v>0.3439</v>
+        <v>0.3426</v>
       </c>
     </row>
     <row r="182">
@@ -5158,10 +5158,10 @@
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.6011</v>
+        <v>0.6546</v>
       </c>
       <c r="H182" t="n">
-        <v>0.5591</v>
+        <v>0.6143999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -5175,19 +5175,19 @@
       </c>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>0.321</v>
+        <v>0.4887</v>
       </c>
       <c r="H183" t="n">
-        <v>0.2804</v>
+        <v>0.4575</v>
       </c>
     </row>
     <row r="184">
@@ -5201,19 +5201,19 @@
       </c>
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>0.4805</v>
+        <v>0.3417</v>
       </c>
       <c r="H184" t="n">
-        <v>0.448</v>
+        <v>0.2991</v>
       </c>
     </row>
     <row r="185">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.9216</v>
+        <v>0.9006</v>
       </c>
       <c r="H185" t="n">
-        <v>0.9004</v>
+        <v>0.8728</v>
       </c>
     </row>
     <row r="186">
@@ -5262,10 +5262,10 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>0.8035</v>
+        <v>0.8071</v>
       </c>
       <c r="H186" t="n">
-        <v>0.7733</v>
+        <v>0.7774</v>
       </c>
     </row>
     <row r="187">
@@ -5279,19 +5279,19 @@
       </c>
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.9543</v>
+        <v>0.9509</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9458</v>
+        <v>0.9417</v>
       </c>
     </row>
     <row r="188">
@@ -5305,19 +5305,19 @@
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.9573</v>
+        <v>0.9613</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9486</v>
+        <v>0.9552</v>
       </c>
     </row>
     <row r="189">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.8935</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="H189" t="n">
-        <v>0.8686</v>
+        <v>0.8972</v>
       </c>
     </row>
     <row r="190">
@@ -5756,10 +5756,10 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.1831</v>
+        <v>0.2277</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1596</v>
+        <v>0.1947</v>
       </c>
     </row>
     <row r="206">
@@ -5782,10 +5782,10 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.1769</v>
+        <v>0.1022</v>
       </c>
       <c r="H206" t="n">
-        <v>0.1481</v>
+        <v>0.0799</v>
       </c>
     </row>
     <row r="207">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.1122</v>
+        <v>0.1161</v>
       </c>
       <c r="H207" t="n">
-        <v>0.0883</v>
+        <v>0.09039999999999999</v>
       </c>
     </row>
     <row r="208">
@@ -5834,10 +5834,10 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.1517</v>
+        <v>0.1116</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1202</v>
+        <v>0.0858</v>
       </c>
     </row>
     <row r="209">
@@ -5860,10 +5860,10 @@
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>0.46</v>
+        <v>0.3318</v>
       </c>
       <c r="H209" t="n">
-        <v>0.4323</v>
+        <v>0.2945</v>
       </c>
     </row>
     <row r="210">
@@ -5886,10 +5886,10 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.3238</v>
+        <v>0.2809</v>
       </c>
       <c r="H210" t="n">
-        <v>0.2858</v>
+        <v>0.2379</v>
       </c>
     </row>
     <row r="211">
@@ -5912,10 +5912,10 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.4409</v>
+        <v>0.3856</v>
       </c>
       <c r="H211" t="n">
-        <v>0.3989</v>
+        <v>0.3454</v>
       </c>
     </row>
     <row r="212">
@@ -5929,19 +5929,19 @@
       </c>
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.2731</v>
+        <v>0.3516</v>
       </c>
       <c r="H212" t="n">
-        <v>0.239</v>
+        <v>0.3175</v>
       </c>
     </row>
     <row r="213">
@@ -5955,19 +5955,19 @@
       </c>
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>0.4158</v>
+        <v>0.2237</v>
       </c>
       <c r="H213" t="n">
-        <v>0.3798</v>
+        <v>0.1849</v>
       </c>
     </row>
     <row r="214">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.9023</v>
+        <v>0.8371</v>
       </c>
       <c r="H214" t="n">
-        <v>0.8786</v>
+        <v>0.8062</v>
       </c>
     </row>
     <row r="215">
@@ -6016,10 +6016,10 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.7381</v>
+        <v>0.651</v>
       </c>
       <c r="H215" t="n">
-        <v>0.7174</v>
+        <v>0.6302</v>
       </c>
     </row>
     <row r="216">
@@ -6033,19 +6033,19 @@
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.9373</v>
+        <v>0.9115</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9264</v>
+        <v>0.8971</v>
       </c>
     </row>
     <row r="217">
@@ -6059,19 +6059,19 @@
       </c>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9273</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9335</v>
+        <v>0.9166</v>
       </c>
     </row>
     <row r="218">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.839</v>
+        <v>0.8259</v>
       </c>
       <c r="H218" t="n">
-        <v>0.8232</v>
+        <v>0.8058999999999999</v>
       </c>
     </row>
     <row r="219">
@@ -6492,11 +6492,11 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -6510,19 +6510,19 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.3803</v>
+        <v>0.3661</v>
       </c>
       <c r="H234" t="n">
-        <v>0.3479</v>
+        <v>0.3094</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -6536,19 +6536,19 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.3993</v>
+        <v>0.1918</v>
       </c>
       <c r="H235" t="n">
-        <v>0.365</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -6562,19 +6562,19 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.3279</v>
+        <v>0.2206</v>
       </c>
       <c r="H236" t="n">
-        <v>0.2944</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -6588,19 +6588,19 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.407</v>
+        <v>0.2118</v>
       </c>
       <c r="H237" t="n">
-        <v>0.3655</v>
+        <v>0.1684</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -6614,19 +6614,19 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>0.7024</v>
+        <v>0.4589</v>
       </c>
       <c r="H238" t="n">
-        <v>0.671</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -6640,19 +6640,19 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.5907</v>
+        <v>0.4423</v>
       </c>
       <c r="H239" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4031</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -6666,19 +6666,19 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>0.7196</v>
+        <v>0.5425</v>
       </c>
       <c r="H240" t="n">
-        <v>0.679</v>
+        <v>0.5113</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -6692,45 +6692,45 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.761</v>
+        <v>0.6825</v>
       </c>
       <c r="H241" t="n">
-        <v>0.7269</v>
+        <v>0.6484</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.669</v>
+        <v>0.3639</v>
       </c>
       <c r="H242" t="n">
-        <v>0.6303</v>
+        <v>0.3236</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -6744,19 +6744,19 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.9633</v>
+        <v>0.924</v>
       </c>
       <c r="H243" t="n">
-        <v>0.9573</v>
+        <v>0.8996</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -6770,71 +6770,71 @@
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>0.9126</v>
+        <v>0.8062</v>
       </c>
       <c r="H244" t="n">
-        <v>0.8968</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
-        <v>0.973</v>
+        <v>0.9529</v>
       </c>
       <c r="H245" t="n">
-        <v>0.9677</v>
+        <v>0.9444</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.9781</v>
+        <v>0.9623</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9556</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -6848,19 +6848,19 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.946</v>
+        <v>0.9267</v>
       </c>
       <c r="H247" t="n">
-        <v>0.9362</v>
+        <v>0.9119</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -6882,11 +6882,11 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -6908,11 +6908,11 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -6934,11 +6934,11 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -6960,11 +6960,11 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -6986,11 +6986,11 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -7012,11 +7012,11 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -7038,11 +7038,11 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -7064,11 +7064,11 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -7090,11 +7090,11 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -7116,11 +7116,11 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -7142,11 +7142,11 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -7168,11 +7168,11 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -7194,11 +7194,11 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -7220,11 +7220,11 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -7246,11 +7246,11 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -7264,19 +7264,19 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.2583</v>
+        <v>0.4841</v>
       </c>
       <c r="H263" t="n">
-        <v>0.222</v>
+        <v>0.4386</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -7290,19 +7290,19 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.2611</v>
+        <v>0.3191</v>
       </c>
       <c r="H264" t="n">
-        <v>0.2241</v>
+        <v>0.2847</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -7316,19 +7316,19 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.1835</v>
+        <v>0.3723</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1481</v>
+        <v>0.3424</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -7342,19 +7342,19 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.2347</v>
+        <v>0.3903</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1919</v>
+        <v>0.3477</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -7368,19 +7368,19 @@
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>0.5528</v>
+        <v>0.626</v>
       </c>
       <c r="H267" t="n">
-        <v>0.5128</v>
+        <v>0.5964</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -7394,19 +7394,19 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.4582</v>
+        <v>0.579</v>
       </c>
       <c r="H268" t="n">
-        <v>0.4218</v>
+        <v>0.5477</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -7420,19 +7420,19 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>0.552</v>
+        <v>0.7009</v>
       </c>
       <c r="H269" t="n">
-        <v>0.5195</v>
+        <v>0.6583</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -7446,45 +7446,45 @@
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="n">
-        <v>0.6202</v>
+        <v>0.8151</v>
       </c>
       <c r="H270" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.7763</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.3697</v>
+        <v>0.6764</v>
       </c>
       <c r="H271" t="n">
-        <v>0.331</v>
+        <v>0.6361</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -7498,19 +7498,19 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.9379</v>
+        <v>0.956</v>
       </c>
       <c r="H272" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9468</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -7524,71 +7524,71 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.9167</v>
       </c>
       <c r="H273" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.8994</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.9597</v>
+        <v>0.9754</v>
       </c>
       <c r="H274" t="n">
-        <v>0.9522</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.9641</v>
+        <v>0.977</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9567</v>
+        <v>0.9731</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -7602,19 +7602,19 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.9112</v>
+        <v>0.9619</v>
       </c>
       <c r="H276" t="n">
-        <v>0.8939</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -7636,11 +7636,11 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -7662,11 +7662,11 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -7688,11 +7688,11 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -7714,11 +7714,11 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -7740,11 +7740,11 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -7766,11 +7766,11 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -7792,11 +7792,11 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -7818,11 +7818,11 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -7844,11 +7844,11 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -7870,11 +7870,11 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -7896,11 +7896,11 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -7922,11 +7922,11 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -7948,11 +7948,11 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -7974,11 +7974,11 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.0435</v>
+        <v>0.0898</v>
       </c>
       <c r="H292" t="n">
-        <v>0.0362</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.0298</v>
+        <v>0.0275</v>
       </c>
       <c r="H293" t="n">
-        <v>0.025</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.0262</v>
+        <v>0.0329</v>
       </c>
       <c r="H294" t="n">
-        <v>0.023</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.0331</v>
+        <v>0.0341</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0286</v>
+        <v>0.0298</v>
       </c>
     </row>
     <row r="296">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.1035</v>
+        <v>0.097</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0818</v>
+        <v>0.07679999999999999</v>
       </c>
     </row>
     <row r="297">
@@ -8148,10 +8148,10 @@
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.0747</v>
+        <v>0.089</v>
       </c>
       <c r="H297" t="n">
-        <v>0.0586</v>
+        <v>0.0687</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.1272</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0784</v>
+        <v>0.0994</v>
       </c>
     </row>
     <row r="299">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.1214</v>
+        <v>0.1938</v>
       </c>
       <c r="H299" t="n">
-        <v>0.0977</v>
+        <v>0.1629</v>
       </c>
     </row>
     <row r="300">
@@ -8217,19 +8217,19 @@
       </c>
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.0427</v>
+        <v>0.1004</v>
       </c>
       <c r="H300" t="n">
-        <v>0.0367</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="301">
@@ -8243,19 +8243,19 @@
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.0822</v>
+        <v>0.0532</v>
       </c>
       <c r="H301" t="n">
-        <v>0.0621</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.2904</v>
+        <v>0.337</v>
       </c>
       <c r="H302" t="n">
-        <v>0.2495</v>
+        <v>0.2926</v>
       </c>
     </row>
     <row r="303">
@@ -8295,19 +8295,19 @@
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6947</v>
       </c>
       <c r="H303" t="n">
-        <v>0.6286</v>
+        <v>0.6478</v>
       </c>
     </row>
     <row r="304">
@@ -8321,19 +8321,19 @@
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.6796</v>
+        <v>0.7484</v>
       </c>
       <c r="H304" t="n">
-        <v>0.6391</v>
+        <v>0.7163</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.4494</v>
+        <v>0.5447</v>
       </c>
       <c r="H305" t="n">
-        <v>0.3971</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="306">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.0987</v>
+        <v>0.1506</v>
       </c>
       <c r="H321" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.1338</v>
       </c>
     </row>
     <row r="322">
@@ -8798,10 +8798,10 @@
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0563</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0779</v>
+        <v>0.0471</v>
       </c>
     </row>
     <row r="323">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.0484</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0403</v>
+        <v>0.0537</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.0611</v>
+        <v>0.0591</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0509</v>
+        <v>0.0489</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.2557</v>
+        <v>0.1927</v>
       </c>
       <c r="H325" t="n">
-        <v>0.2235</v>
+        <v>0.1606</v>
       </c>
     </row>
     <row r="326">
@@ -8902,10 +8902,10 @@
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="n">
-        <v>0.1448</v>
+        <v>0.1421</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1177</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="327">
@@ -8928,10 +8928,10 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>0.2267</v>
+        <v>0.2226</v>
       </c>
       <c r="H327" t="n">
-        <v>0.1965</v>
+        <v>0.1929</v>
       </c>
     </row>
     <row r="328">
@@ -8954,10 +8954,10 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.2826</v>
+        <v>0.3698</v>
       </c>
       <c r="H328" t="n">
-        <v>0.2619</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="329">
@@ -8971,19 +8971,19 @@
       </c>
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>0.1032</v>
+        <v>0.2155</v>
       </c>
       <c r="H329" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1938</v>
       </c>
     </row>
     <row r="330">
@@ -8997,19 +8997,19 @@
       </c>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.2051</v>
+        <v>0.1006</v>
       </c>
       <c r="H330" t="n">
-        <v>0.186</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7074</v>
       </c>
       <c r="H331" t="n">
-        <v>0.7096</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="332">
@@ -9049,19 +9049,19 @@
       </c>
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.8621</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="H332" t="n">
-        <v>0.8342000000000001</v>
+        <v>0.7988</v>
       </c>
     </row>
     <row r="333">
@@ -9075,19 +9075,19 @@
       </c>
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.8739</v>
+        <v>0.8808</v>
       </c>
       <c r="H333" t="n">
-        <v>0.8389</v>
+        <v>0.853</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.6834</v>
+        <v>0.7192</v>
       </c>
       <c r="H334" t="n">
-        <v>0.6544</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="335">
@@ -9508,11 +9508,11 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -9526,19 +9526,19 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>0.0406</v>
+        <v>0.0525</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0347</v>
+        <v>0.0425</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -9552,19 +9552,19 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.0326</v>
+        <v>0.022</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0268</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -9578,19 +9578,19 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.0217</v>
+        <v>0.0257</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0188</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -9604,19 +9604,19 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>0.0234</v>
+        <v>0.0296</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0207</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -9630,19 +9630,19 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.0631</v>
+        <v>0.0421</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0527</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C355" t="inlineStr"/>
@@ -9656,19 +9656,19 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.0355</v>
+        <v>0.0352</v>
       </c>
       <c r="H355" t="n">
-        <v>0.0302</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C356" t="inlineStr"/>
@@ -9682,19 +9682,19 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.0542</v>
+        <v>0.0583</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0457</v>
+        <v>0.0491</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C357" t="inlineStr"/>
@@ -9708,71 +9708,71 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.0736</v>
+        <v>0.1029</v>
       </c>
       <c r="H357" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0885</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>0.0323</v>
+        <v>0.0556</v>
       </c>
       <c r="H358" t="n">
-        <v>0.027</v>
+        <v>0.0471</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.0478</v>
+        <v>0.029</v>
       </c>
       <c r="H359" t="n">
-        <v>0.0403</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C360" t="inlineStr"/>
@@ -9786,19 +9786,19 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.3714</v>
+        <v>0.3522</v>
       </c>
       <c r="H360" t="n">
-        <v>0.3352</v>
+        <v>0.3053</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C361" t="inlineStr"/>
@@ -9812,45 +9812,45 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.1658</v>
+        <v>0.2012</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1379</v>
+        <v>0.1618</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>0.5409</v>
+        <v>0.5937</v>
       </c>
       <c r="H362" t="n">
-        <v>0.4923</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
@@ -9864,19 +9864,19 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>0.297</v>
+        <v>0.3825</v>
       </c>
       <c r="H363" t="n">
-        <v>0.2735</v>
+        <v>0.3353</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -9898,11 +9898,11 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -9924,11 +9924,11 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -9950,11 +9950,11 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -9976,11 +9976,11 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -10002,11 +10002,11 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -10028,11 +10028,11 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -10054,11 +10054,11 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -10080,11 +10080,11 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -10106,11 +10106,11 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -10132,11 +10132,11 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -10158,11 +10158,11 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -10184,11 +10184,11 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -10210,11 +10210,11 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -10236,11 +10236,11 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -10262,11 +10262,11 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -10280,19 +10280,19 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.0276</v>
+        <v>0.0561</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0229</v>
+        <v>0.0471</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -10306,19 +10306,19 @@
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
-        <v>0.0229</v>
+        <v>0.0213</v>
       </c>
       <c r="H380" t="n">
-        <v>0.0195</v>
+        <v>0.0178</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C381" t="inlineStr"/>
@@ -10332,19 +10332,19 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.0221</v>
+        <v>0.0216</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0189</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -10358,19 +10358,19 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>0.0278</v>
+        <v>0.0217</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0235</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -10384,19 +10384,19 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.0511</v>
+        <v>0.0382</v>
       </c>
       <c r="H383" t="n">
-        <v>0.041</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
@@ -10410,19 +10410,19 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>0.0338</v>
+        <v>0.0282</v>
       </c>
       <c r="H384" t="n">
-        <v>0.0271</v>
+        <v>0.0247</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
@@ -10436,19 +10436,19 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.0514</v>
+        <v>0.0448</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0427</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
@@ -10462,71 +10462,71 @@
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.0665</v>
+        <v>0.0834</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0559</v>
+        <v>0.0727</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.0257</v>
+        <v>0.0444</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0219</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.0433</v>
+        <v>0.0269</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0359</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
@@ -10540,19 +10540,19 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.3609</v>
+        <v>0.2837</v>
       </c>
       <c r="H389" t="n">
-        <v>0.3204</v>
+        <v>0.2516</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
@@ -10566,45 +10566,45 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.1611</v>
+        <v>0.147</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1261</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>0.5077</v>
+        <v>0.444</v>
       </c>
       <c r="H391" t="n">
-        <v>0.4591</v>
+        <v>0.4063</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
@@ -10618,19 +10618,19 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>0.2787</v>
+        <v>0.3076</v>
       </c>
       <c r="H392" t="n">
-        <v>0.2351</v>
+        <v>0.2801</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
@@ -10652,11 +10652,11 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
@@ -10678,11 +10678,11 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
@@ -10704,11 +10704,11 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C396" t="inlineStr"/>
@@ -10730,11 +10730,11 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C397" t="inlineStr"/>
@@ -10756,11 +10756,11 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
@@ -10782,11 +10782,11 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
@@ -10808,11 +10808,11 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -10834,11 +10834,11 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -10860,11 +10860,11 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
@@ -10886,11 +10886,11 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -10912,11 +10912,11 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -10938,11 +10938,11 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -10964,11 +10964,11 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -10990,11 +10990,11 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.0684</v>
+        <v>0.0868</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0612</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="409">
@@ -11060,10 +11060,10 @@
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
-        <v>0.0557</v>
+        <v>0.03</v>
       </c>
       <c r="H409" t="n">
-        <v>0.0473</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="410">
@@ -11086,10 +11086,10 @@
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>0.0339</v>
+        <v>0.0321</v>
       </c>
       <c r="H410" t="n">
-        <v>0.0281</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="411">
@@ -11112,10 +11112,10 @@
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
-        <v>0.0388</v>
+        <v>0.0297</v>
       </c>
       <c r="H411" t="n">
-        <v>0.0336</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="412">
@@ -11138,10 +11138,10 @@
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>0.1446</v>
+        <v>0.0752</v>
       </c>
       <c r="H412" t="n">
-        <v>0.1262</v>
+        <v>0.0622</v>
       </c>
     </row>
     <row r="413">
@@ -11164,10 +11164,10 @@
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>0.0828</v>
+        <v>0.0598</v>
       </c>
       <c r="H413" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0487</v>
       </c>
     </row>
     <row r="414">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.1314</v>
+        <v>0.1028</v>
       </c>
       <c r="H414" t="n">
-        <v>0.1065</v>
+        <v>0.0822</v>
       </c>
     </row>
     <row r="415">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.1768</v>
+        <v>0.1941</v>
       </c>
       <c r="H415" t="n">
-        <v>0.161</v>
+        <v>0.1741</v>
       </c>
     </row>
     <row r="416">
@@ -11233,19 +11233,19 @@
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.0638</v>
+        <v>0.0881</v>
       </c>
       <c r="H416" t="n">
-        <v>0.054</v>
+        <v>0.0733</v>
       </c>
     </row>
     <row r="417">
@@ -11259,19 +11259,19 @@
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.1061</v>
+        <v>0.0459</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0888</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="418">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.6029</v>
+        <v>0.496</v>
       </c>
       <c r="H418" t="n">
-        <v>0.5506</v>
+        <v>0.4553</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.3456</v>
+        <v>0.3146</v>
       </c>
       <c r="H419" t="n">
-        <v>0.3166</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="420">
@@ -11337,19 +11337,19 @@
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>0.7265</v>
+        <v>0.6647</v>
       </c>
       <c r="H420" t="n">
-        <v>0.703</v>
+        <v>0.6175</v>
       </c>
     </row>
     <row r="421">
@@ -11363,19 +11363,19 @@
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
-        <v>0.7649</v>
+        <v>0.7199</v>
       </c>
       <c r="H421" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.6924</v>
       </c>
     </row>
     <row r="422">
@@ -11987,11 +11987,11 @@
       </c>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F445" t="inlineStr"/>
@@ -12013,11 +12013,11 @@
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F446" t="inlineStr"/>
@@ -12091,11 +12091,11 @@
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F449" t="inlineStr"/>
@@ -12117,11 +12117,11 @@
       </c>
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F450" t="inlineStr"/>
@@ -12741,11 +12741,11 @@
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
@@ -12767,11 +12767,11 @@
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F475" t="inlineStr"/>
@@ -12845,11 +12845,11 @@
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F478" t="inlineStr"/>
@@ -12871,11 +12871,11 @@
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
@@ -13495,11 +13495,11 @@
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F503" t="inlineStr"/>
@@ -13521,11 +13521,11 @@
       </c>
       <c r="C504" t="inlineStr"/>
       <c r="D504" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F504" t="inlineStr"/>
@@ -13599,11 +13599,11 @@
       </c>
       <c r="C507" t="inlineStr"/>
       <c r="D507" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F507" t="inlineStr"/>
@@ -13625,11 +13625,11 @@
       </c>
       <c r="C508" t="inlineStr"/>
       <c r="D508" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F508" t="inlineStr"/>
@@ -14249,11 +14249,11 @@
       </c>
       <c r="C532" t="inlineStr"/>
       <c r="D532" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F532" t="inlineStr"/>
@@ -14275,11 +14275,11 @@
       </c>
       <c r="C533" t="inlineStr"/>
       <c r="D533" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F533" t="inlineStr"/>
@@ -14353,11 +14353,11 @@
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F536" t="inlineStr"/>
@@ -14379,11 +14379,11 @@
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F537" t="inlineStr"/>
@@ -15003,11 +15003,11 @@
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F561" t="inlineStr"/>
@@ -15029,11 +15029,11 @@
       </c>
       <c r="C562" t="inlineStr"/>
       <c r="D562" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F562" t="inlineStr"/>
@@ -15107,11 +15107,11 @@
       </c>
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F565" t="inlineStr"/>
@@ -15133,11 +15133,11 @@
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F566" t="inlineStr"/>
@@ -15757,11 +15757,11 @@
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F590" t="inlineStr"/>
@@ -15783,11 +15783,11 @@
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F591" t="inlineStr"/>
@@ -15861,11 +15861,11 @@
       </c>
       <c r="C594" t="inlineStr"/>
       <c r="D594" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F594" t="inlineStr"/>
@@ -15887,11 +15887,11 @@
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F595" t="inlineStr"/>
@@ -16511,11 +16511,11 @@
       </c>
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F619" t="inlineStr"/>
@@ -16537,11 +16537,11 @@
       </c>
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F620" t="inlineStr"/>
@@ -16615,11 +16615,11 @@
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F623" t="inlineStr"/>
@@ -16641,11 +16641,11 @@
       </c>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F624" t="inlineStr"/>
@@ -17265,11 +17265,11 @@
       </c>
       <c r="C648" t="inlineStr"/>
       <c r="D648" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F648" t="inlineStr"/>
@@ -17291,11 +17291,11 @@
       </c>
       <c r="C649" t="inlineStr"/>
       <c r="D649" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F649" t="inlineStr"/>
@@ -17369,11 +17369,11 @@
       </c>
       <c r="C652" t="inlineStr"/>
       <c r="D652" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F652" t="inlineStr"/>
@@ -17395,11 +17395,11 @@
       </c>
       <c r="C653" t="inlineStr"/>
       <c r="D653" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F653" t="inlineStr"/>
@@ -18019,11 +18019,11 @@
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F677" t="inlineStr"/>
@@ -18045,11 +18045,11 @@
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F678" t="inlineStr"/>
@@ -18123,11 +18123,11 @@
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F681" t="inlineStr"/>
@@ -18149,11 +18149,11 @@
       </c>
       <c r="C682" t="inlineStr"/>
       <c r="D682" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F682" t="inlineStr"/>
@@ -18773,11 +18773,11 @@
       </c>
       <c r="C706" t="inlineStr"/>
       <c r="D706" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F706" t="inlineStr"/>
@@ -18799,11 +18799,11 @@
       </c>
       <c r="C707" t="inlineStr"/>
       <c r="D707" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F707" t="inlineStr"/>
@@ -18877,11 +18877,11 @@
       </c>
       <c r="C710" t="inlineStr"/>
       <c r="D710" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F710" t="inlineStr"/>
@@ -18903,11 +18903,11 @@
       </c>
       <c r="C711" t="inlineStr"/>
       <c r="D711" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F711" t="inlineStr"/>
@@ -19527,11 +19527,11 @@
       </c>
       <c r="C735" t="inlineStr"/>
       <c r="D735" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F735" t="inlineStr"/>
@@ -19553,11 +19553,11 @@
       </c>
       <c r="C736" t="inlineStr"/>
       <c r="D736" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F736" t="inlineStr"/>
@@ -19631,11 +19631,11 @@
       </c>
       <c r="C739" t="inlineStr"/>
       <c r="D739" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F739" t="inlineStr"/>
@@ -19657,11 +19657,11 @@
       </c>
       <c r="C740" t="inlineStr"/>
       <c r="D740" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F740" t="inlineStr"/>
@@ -20281,11 +20281,11 @@
       </c>
       <c r="C764" t="inlineStr"/>
       <c r="D764" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E764" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F764" t="inlineStr"/>
@@ -20307,11 +20307,11 @@
       </c>
       <c r="C765" t="inlineStr"/>
       <c r="D765" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F765" t="inlineStr"/>
@@ -20385,11 +20385,11 @@
       </c>
       <c r="C768" t="inlineStr"/>
       <c r="D768" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F768" t="inlineStr"/>
@@ -20411,11 +20411,11 @@
       </c>
       <c r="C769" t="inlineStr"/>
       <c r="D769" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F769" t="inlineStr"/>
@@ -21035,11 +21035,11 @@
       </c>
       <c r="C793" t="inlineStr"/>
       <c r="D793" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F793" t="inlineStr"/>
@@ -21061,11 +21061,11 @@
       </c>
       <c r="C794" t="inlineStr"/>
       <c r="D794" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F794" t="inlineStr"/>
@@ -21139,11 +21139,11 @@
       </c>
       <c r="C797" t="inlineStr"/>
       <c r="D797" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F797" t="inlineStr"/>
@@ -21165,11 +21165,11 @@
       </c>
       <c r="C798" t="inlineStr"/>
       <c r="D798" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F798" t="inlineStr"/>
@@ -21789,11 +21789,11 @@
       </c>
       <c r="C822" t="inlineStr"/>
       <c r="D822" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E822" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F822" t="inlineStr"/>
@@ -21815,11 +21815,11 @@
       </c>
       <c r="C823" t="inlineStr"/>
       <c r="D823" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E823" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F823" t="inlineStr"/>
@@ -21893,11 +21893,11 @@
       </c>
       <c r="C826" t="inlineStr"/>
       <c r="D826" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F826" t="inlineStr"/>
@@ -21919,11 +21919,11 @@
       </c>
       <c r="C827" t="inlineStr"/>
       <c r="D827" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F827" t="inlineStr"/>
@@ -22543,11 +22543,11 @@
       </c>
       <c r="C851" t="inlineStr"/>
       <c r="D851" t="n">
-        <v>1610612766</v>
+        <v>1610612748</v>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>Hornets</t>
+          <t>Heat</t>
         </is>
       </c>
       <c r="F851" t="inlineStr"/>
@@ -22569,11 +22569,11 @@
       </c>
       <c r="C852" t="inlineStr"/>
       <c r="D852" t="n">
-        <v>1610612748</v>
+        <v>1610612766</v>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Hornets</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -22647,11 +22647,11 @@
       </c>
       <c r="C855" t="inlineStr"/>
       <c r="D855" t="n">
-        <v>1610612764</v>
+        <v>1610612751</v>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Wizards</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F855" t="inlineStr"/>
@@ -22673,11 +22673,11 @@
       </c>
       <c r="C856" t="inlineStr"/>
       <c r="D856" t="n">
-        <v>1610612751</v>
+        <v>1610612764</v>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Wizards</t>
         </is>
       </c>
       <c r="F856" t="inlineStr"/>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.3982</v>
+        <v>0.3785</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3438</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.4221</v>
+        <v>0.4215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3715</v>
+        <v>0.3772</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.4473</v>
+        <v>0.4127</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4014</v>
+        <v>0.394</v>
       </c>
     </row>
     <row r="5">
@@ -547,19 +547,19 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.6611</v>
+        <v>0.6137</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6244</v>
+        <v>0.5738</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.6176</v>
+        <v>0.7205</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5764</v>
+        <v>0.7042</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.7118</v>
+        <v>0.7534</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6687</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.8053</v>
+        <v>0.8115</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7723</v>
+        <v>0.7803</v>
       </c>
     </row>
     <row r="9">
@@ -660,10 +660,10 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.6906</v>
+        <v>0.7674</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6339</v>
+        <v>0.7326</v>
       </c>
     </row>
     <row r="10">
@@ -686,10 +686,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.5614</v>
+        <v>0.5475</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5159</v>
+        <v>0.5155999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9204</v>
+        <v>0.9251</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9102</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.8662</v>
+        <v>0.8764999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8494</v>
+        <v>0.8678</v>
       </c>
     </row>
     <row r="13">
@@ -764,10 +764,10 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.9575</v>
+        <v>0.9624</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9475</v>
+        <v>0.953</v>
       </c>
     </row>
     <row r="14">
@@ -790,10 +790,10 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.9529</v>
+        <v>0.9639</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9439</v>
+        <v>0.9559</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9212</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9132</v>
+        <v>0.9243</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.6562</v>
+        <v>0.665</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6018</v>
+        <v>0.6215000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1258,10 +1258,10 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.5589</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5379</v>
+        <v>0.533</v>
       </c>
     </row>
     <row r="33">
@@ -1284,10 +1284,10 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.5894</v>
+        <v>0.5261</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.4828</v>
       </c>
     </row>
     <row r="34">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.8167</v>
+        <v>0.7685</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7873</v>
+        <v>0.7335</v>
       </c>
     </row>
     <row r="35">
@@ -1327,19 +1327,19 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.7605</v>
+        <v>0.8708</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7299</v>
+        <v>0.8428</v>
       </c>
     </row>
     <row r="36">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.8446</v>
+        <v>0.8898</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8275</v>
+        <v>0.8704</v>
       </c>
     </row>
     <row r="37">
@@ -1388,10 +1388,10 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.9201</v>
+        <v>0.9291</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8978</v>
+        <v>0.9092</v>
       </c>
     </row>
     <row r="38">
@@ -1414,10 +1414,10 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.841</v>
+        <v>0.886</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8082</v>
+        <v>0.8567</v>
       </c>
     </row>
     <row r="39">
@@ -1440,10 +1440,10 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.7153</v>
+        <v>0.6574</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6235000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.9768</v>
+        <v>0.9752</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9725</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="41">
@@ -1492,10 +1492,10 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.9529</v>
+        <v>0.9674</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9437</v>
+        <v>0.9598</v>
       </c>
     </row>
     <row r="42">
@@ -1518,10 +1518,10 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.9813</v>
+        <v>0.9841</v>
       </c>
       <c r="H42" t="n">
-        <v>0.978</v>
+        <v>0.9816</v>
       </c>
     </row>
     <row r="43">
@@ -1544,10 +1544,10 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>0.9822</v>
+        <v>0.9835</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9787</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="44">
@@ -1570,10 +1570,10 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.9749</v>
+        <v>0.9744</v>
       </c>
       <c r="H44" t="n">
-        <v>0.97</v>
+        <v>0.9681</v>
       </c>
     </row>
     <row r="45">
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6228</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5779</v>
+        <v>0.5785</v>
       </c>
     </row>
     <row r="61">
@@ -2012,10 +2012,10 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>0.4621</v>
+        <v>0.467</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4309</v>
+        <v>0.4411</v>
       </c>
     </row>
     <row r="62">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.5468</v>
+        <v>0.4761</v>
       </c>
       <c r="H62" t="n">
-        <v>0.51</v>
+        <v>0.443</v>
       </c>
     </row>
     <row r="63">
@@ -2055,19 +2055,19 @@
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.7691</v>
+        <v>0.7265</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7387</v>
+        <v>0.6951000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2081,19 +2081,19 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0.7247</v>
+        <v>0.8374</v>
       </c>
       <c r="H64" t="n">
-        <v>0.6963</v>
+        <v>0.8105</v>
       </c>
     </row>
     <row r="65">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.8262</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8084</v>
+        <v>0.8334</v>
       </c>
     </row>
     <row r="66">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.9096</v>
+        <v>0.9121</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8839</v>
+        <v>0.8842</v>
       </c>
     </row>
     <row r="67">
@@ -2168,10 +2168,10 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.8167</v>
+        <v>0.867</v>
       </c>
       <c r="H67" t="n">
-        <v>0.7794</v>
+        <v>0.8306</v>
       </c>
     </row>
     <row r="68">
@@ -2194,10 +2194,10 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.6576</v>
+        <v>0.6251</v>
       </c>
       <c r="H68" t="n">
-        <v>0.6277</v>
+        <v>0.5946</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.9717</v>
+        <v>0.9686</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9671</v>
+        <v>0.9641999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9463</v>
+        <v>0.9608</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9353</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="71">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.978</v>
+        <v>0.9791</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9764</v>
       </c>
     </row>
     <row r="72">
@@ -2298,10 +2298,10 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>0.9812</v>
+        <v>0.9819</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9784</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="73">
@@ -2324,10 +2324,10 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.9731</v>
+        <v>0.9742</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9679</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="74">
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.5986</v>
+        <v>0.606</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5527</v>
+        <v>0.5873</v>
       </c>
     </row>
     <row r="90">
@@ -2766,10 +2766,10 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.4541</v>
+        <v>0.5172</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4106</v>
+        <v>0.4739</v>
       </c>
     </row>
     <row r="91">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.49</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4532</v>
+        <v>0.5239</v>
       </c>
     </row>
     <row r="92">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.771</v>
+        <v>0.7647</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7346</v>
+        <v>0.7319</v>
       </c>
     </row>
     <row r="93">
@@ -2835,19 +2835,19 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0.7149</v>
+        <v>0.8514</v>
       </c>
       <c r="H93" t="n">
-        <v>0.672</v>
+        <v>0.8286</v>
       </c>
     </row>
     <row r="94">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.8043</v>
+        <v>0.8484</v>
       </c>
     </row>
     <row r="95">
@@ -2896,10 +2896,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.9142</v>
+        <v>0.9185</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8884</v>
+        <v>0.8975</v>
       </c>
     </row>
     <row r="96">
@@ -2922,10 +2922,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.8316</v>
+        <v>0.88</v>
       </c>
       <c r="H96" t="n">
-        <v>0.7882</v>
+        <v>0.848</v>
       </c>
     </row>
     <row r="97">
@@ -2948,10 +2948,10 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.6523</v>
+        <v>0.6862</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6097</v>
+        <v>0.6497000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.9702</v>
+        <v>0.9731</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9659</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9644</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9409</v>
+        <v>0.9584</v>
       </c>
     </row>
     <row r="100">
@@ -3026,10 +3026,10 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>0.9746</v>
+        <v>0.9805</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9704</v>
+        <v>0.9774</v>
       </c>
     </row>
     <row r="101">
@@ -3052,10 +3052,10 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0.9813</v>
+        <v>0.9839</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9809</v>
       </c>
     </row>
     <row r="102">
@@ -3078,10 +3078,10 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>0.9732</v>
+        <v>0.9704</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.968</v>
       </c>
     </row>
     <row r="103">
@@ -3476,11 +3476,11 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -3494,19 +3494,19 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.3756</v>
+        <v>0.4262</v>
       </c>
       <c r="H118" t="n">
-        <v>0.3389</v>
+        <v>0.3863</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -3520,19 +3520,19 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.2127</v>
+        <v>0.2665</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1833</v>
+        <v>0.2315</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -3546,19 +3546,19 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.2613</v>
+        <v>0.3049</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2309</v>
+        <v>0.2735</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -3572,45 +3572,45 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.2654</v>
+        <v>0.2681</v>
       </c>
       <c r="H121" t="n">
-        <v>0.229</v>
+        <v>0.2353</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0.4516</v>
+        <v>0.6188</v>
       </c>
       <c r="H122" t="n">
-        <v>0.419</v>
+        <v>0.5783</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -3624,19 +3624,19 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.5998</v>
+        <v>0.6332</v>
       </c>
       <c r="H123" t="n">
-        <v>0.5694</v>
+        <v>0.6073</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3650,19 +3650,19 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0.7055</v>
+        <v>0.7741</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6682</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3676,19 +3676,19 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>0.579</v>
+        <v>0.6829</v>
       </c>
       <c r="H125" t="n">
-        <v>0.5411</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3702,19 +3702,19 @@
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>0.4036</v>
+        <v>0.4019</v>
       </c>
       <c r="H126" t="n">
-        <v>0.374</v>
+        <v>0.3743</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3728,19 +3728,19 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.9232</v>
+        <v>0.9113</v>
       </c>
       <c r="H127" t="n">
-        <v>0.903</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3754,19 +3754,19 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.8394</v>
+        <v>0.8996</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8073</v>
+        <v>0.8774999999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3780,19 +3780,19 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.9655</v>
+        <v>0.9696</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9579</v>
+        <v>0.9612000000000001</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3806,19 +3806,19 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.9688</v>
+        <v>0.9735</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9618</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3832,19 +3832,19 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.9378</v>
+        <v>0.9455</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9248</v>
+        <v>0.9354</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3866,11 +3866,11 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3892,11 +3892,11 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3918,11 +3918,11 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3944,11 +3944,11 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3970,11 +3970,11 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3996,11 +3996,11 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -4022,11 +4022,11 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -4048,11 +4048,11 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -4074,11 +4074,11 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -4100,11 +4100,11 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -4126,11 +4126,11 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -4152,11 +4152,11 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -4178,11 +4178,11 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -4204,11 +4204,11 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -4230,11 +4230,11 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -4248,19 +4248,19 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.4236</v>
+        <v>0.2958</v>
       </c>
       <c r="H147" t="n">
-        <v>0.3824</v>
+        <v>0.2795</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -4274,19 +4274,19 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>0.2701</v>
+        <v>0.1572</v>
       </c>
       <c r="H148" t="n">
-        <v>0.2395</v>
+        <v>0.1292</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -4300,19 +4300,19 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>0.3037</v>
+        <v>0.1895</v>
       </c>
       <c r="H149" t="n">
-        <v>0.2753</v>
+        <v>0.1626</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -4326,45 +4326,45 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>0.328</v>
+        <v>0.1714</v>
       </c>
       <c r="H150" t="n">
-        <v>0.2851</v>
+        <v>0.1486</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>0.581</v>
+        <v>0.4217</v>
       </c>
       <c r="H151" t="n">
-        <v>0.5484</v>
+        <v>0.3812</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -4378,19 +4378,19 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0.6574</v>
+        <v>0.5569</v>
       </c>
       <c r="H152" t="n">
-        <v>0.6262</v>
+        <v>0.5268</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -4404,19 +4404,19 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.7621</v>
+        <v>0.6573</v>
       </c>
       <c r="H153" t="n">
-        <v>0.7191</v>
+        <v>0.6224</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -4430,19 +4430,19 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.5969</v>
+        <v>0.6136</v>
       </c>
       <c r="H154" t="n">
-        <v>0.5577</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -4456,19 +4456,19 @@
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.4523</v>
+        <v>0.3038</v>
       </c>
       <c r="H155" t="n">
-        <v>0.421</v>
+        <v>0.2747</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -4482,19 +4482,19 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.9313</v>
+        <v>0.8818</v>
       </c>
       <c r="H156" t="n">
-        <v>0.911</v>
+        <v>0.8613</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -4508,19 +4508,19 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>0.8844</v>
+        <v>0.8368</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8579</v>
+        <v>0.8117</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -4534,19 +4534,19 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.9716</v>
+        <v>0.9585</v>
       </c>
       <c r="H158" t="n">
-        <v>0.9648</v>
+        <v>0.9515</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -4560,19 +4560,19 @@
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.967</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9718</v>
+        <v>0.9601</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -4586,19 +4586,19 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>0.9513</v>
+        <v>0.9167</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9402</v>
+        <v>0.8978</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -4620,11 +4620,11 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -4646,11 +4646,11 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -4672,11 +4672,11 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -4698,11 +4698,11 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -4724,11 +4724,11 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -4750,11 +4750,11 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -4776,11 +4776,11 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -4802,11 +4802,11 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -4828,11 +4828,11 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -4854,11 +4854,11 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -4880,11 +4880,11 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -4906,11 +4906,11 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -4932,11 +4932,11 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -4958,11 +4958,11 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.3313</v>
+        <v>0.283</v>
       </c>
       <c r="H176" t="n">
-        <v>0.2882</v>
+        <v>0.2466</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.1725</v>
+        <v>0.1296</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1554</v>
+        <v>0.1102</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.1916</v>
+        <v>0.1666</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1738</v>
+        <v>0.1436</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.1957</v>
+        <v>0.1516</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1709</v>
+        <v>0.1275</v>
       </c>
     </row>
     <row r="180">
@@ -5097,19 +5097,19 @@
       </c>
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.4306</v>
+        <v>0.3927</v>
       </c>
       <c r="H180" t="n">
-        <v>0.4002</v>
+        <v>0.3668</v>
       </c>
     </row>
     <row r="181">
@@ -5123,19 +5123,19 @@
       </c>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>0.3738</v>
+        <v>0.4732</v>
       </c>
       <c r="H181" t="n">
-        <v>0.3426</v>
+        <v>0.4431</v>
       </c>
     </row>
     <row r="182">
@@ -5158,10 +5158,10 @@
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.6546</v>
+        <v>0.6096</v>
       </c>
       <c r="H182" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.5715</v>
       </c>
     </row>
     <row r="183">
@@ -5184,10 +5184,10 @@
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>0.4887</v>
+        <v>0.5542</v>
       </c>
       <c r="H183" t="n">
-        <v>0.4575</v>
+        <v>0.5305</v>
       </c>
     </row>
     <row r="184">
@@ -5210,10 +5210,10 @@
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>0.3417</v>
+        <v>0.2837</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2991</v>
+        <v>0.2498</v>
       </c>
     </row>
     <row r="185">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.9006</v>
+        <v>0.8488</v>
       </c>
       <c r="H185" t="n">
-        <v>0.8728</v>
+        <v>0.8178</v>
       </c>
     </row>
     <row r="186">
@@ -5262,10 +5262,10 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>0.8071</v>
+        <v>0.804</v>
       </c>
       <c r="H186" t="n">
-        <v>0.7774</v>
+        <v>0.7714</v>
       </c>
     </row>
     <row r="187">
@@ -5288,10 +5288,10 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.9509</v>
+        <v>0.9398</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9417</v>
+        <v>0.9296</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.9613</v>
+        <v>0.9591</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9552</v>
+        <v>0.9546</v>
       </c>
     </row>
     <row r="189">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.8808</v>
       </c>
       <c r="H189" t="n">
-        <v>0.8972</v>
+        <v>0.8536</v>
       </c>
     </row>
     <row r="190">
@@ -5756,10 +5756,10 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.2277</v>
+        <v>0.2197</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1947</v>
+        <v>0.1885</v>
       </c>
     </row>
     <row r="206">
@@ -5782,10 +5782,10 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.1022</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0799</v>
+        <v>0.0709</v>
       </c>
     </row>
     <row r="207">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.1161</v>
+        <v>0.1158</v>
       </c>
       <c r="H207" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.08790000000000001</v>
       </c>
     </row>
     <row r="208">
@@ -5834,10 +5834,10 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.1116</v>
+        <v>0.1025</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0858</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="209">
@@ -5851,19 +5851,19 @@
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>0.3318</v>
+        <v>0.2685</v>
       </c>
       <c r="H209" t="n">
-        <v>0.2945</v>
+        <v>0.2259</v>
       </c>
     </row>
     <row r="210">
@@ -5877,19 +5877,19 @@
       </c>
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.2809</v>
+        <v>0.3776</v>
       </c>
       <c r="H210" t="n">
-        <v>0.2379</v>
+        <v>0.3427</v>
       </c>
     </row>
     <row r="211">
@@ -5912,10 +5912,10 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.3856</v>
+        <v>0.4285</v>
       </c>
       <c r="H211" t="n">
-        <v>0.3454</v>
+        <v>0.3904</v>
       </c>
     </row>
     <row r="212">
@@ -5938,10 +5938,10 @@
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.3516</v>
+        <v>0.4322</v>
       </c>
       <c r="H212" t="n">
-        <v>0.3175</v>
+        <v>0.4038</v>
       </c>
     </row>
     <row r="213">
@@ -5964,10 +5964,10 @@
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>0.2237</v>
+        <v>0.2184</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1849</v>
+        <v>0.1754</v>
       </c>
     </row>
     <row r="214">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.8371</v>
+        <v>0.7669</v>
       </c>
       <c r="H214" t="n">
-        <v>0.8062</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="215">
@@ -6016,10 +6016,10 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.651</v>
+        <v>0.6701</v>
       </c>
       <c r="H215" t="n">
-        <v>0.6302</v>
+        <v>0.6516999999999999</v>
       </c>
     </row>
     <row r="216">
@@ -6042,10 +6042,10 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.9115</v>
+        <v>0.9268</v>
       </c>
       <c r="H216" t="n">
-        <v>0.8971</v>
+        <v>0.9117</v>
       </c>
     </row>
     <row r="217">
@@ -6068,10 +6068,10 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.9273</v>
+        <v>0.9379</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9166</v>
+        <v>0.928</v>
       </c>
     </row>
     <row r="218">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.8259</v>
+        <v>0.8041</v>
       </c>
       <c r="H218" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7775</v>
       </c>
     </row>
     <row r="219">
@@ -6510,10 +6510,10 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.3661</v>
+        <v>0.2674</v>
       </c>
       <c r="H234" t="n">
-        <v>0.3094</v>
+        <v>0.2326</v>
       </c>
     </row>
     <row r="235">
@@ -6536,10 +6536,10 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.1918</v>
+        <v>0.1433</v>
       </c>
       <c r="H235" t="n">
-        <v>0.159</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="236">
@@ -6562,10 +6562,10 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.2206</v>
+        <v>0.1694</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1833</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="237">
@@ -6588,10 +6588,10 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.2118</v>
+        <v>0.152</v>
       </c>
       <c r="H237" t="n">
-        <v>0.1684</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="238">
@@ -6605,19 +6605,19 @@
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>0.4589</v>
+        <v>0.357</v>
       </c>
       <c r="H238" t="n">
-        <v>0.421</v>
+        <v>0.3171</v>
       </c>
     </row>
     <row r="239">
@@ -6631,19 +6631,19 @@
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.4423</v>
+        <v>0.43</v>
       </c>
       <c r="H239" t="n">
-        <v>0.4031</v>
+        <v>0.3864</v>
       </c>
     </row>
     <row r="240">
@@ -6666,10 +6666,10 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>0.5425</v>
+        <v>0.4695</v>
       </c>
       <c r="H240" t="n">
-        <v>0.5113</v>
+        <v>0.4458</v>
       </c>
     </row>
     <row r="241">
@@ -6692,10 +6692,10 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.6825</v>
+        <v>0.5962</v>
       </c>
       <c r="H241" t="n">
-        <v>0.6484</v>
+        <v>0.5678</v>
       </c>
     </row>
     <row r="242">
@@ -6718,10 +6718,10 @@
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.3639</v>
+        <v>0.2664</v>
       </c>
       <c r="H242" t="n">
-        <v>0.3236</v>
+        <v>0.2208</v>
       </c>
     </row>
     <row r="243">
@@ -6744,10 +6744,10 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.924</v>
+        <v>0.8578</v>
       </c>
       <c r="H243" t="n">
-        <v>0.8996</v>
+        <v>0.8183</v>
       </c>
     </row>
     <row r="244">
@@ -6770,10 +6770,10 @@
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>0.8062</v>
+        <v>0.7696</v>
       </c>
       <c r="H244" t="n">
-        <v>0.7845</v>
+        <v>0.7523</v>
       </c>
     </row>
     <row r="245">
@@ -6796,10 +6796,10 @@
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
-        <v>0.9529</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="H245" t="n">
-        <v>0.9444</v>
+        <v>0.9329</v>
       </c>
     </row>
     <row r="246">
@@ -6822,10 +6822,10 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.9623</v>
+        <v>0.9514</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9556</v>
+        <v>0.9437</v>
       </c>
     </row>
     <row r="247">
@@ -6848,10 +6848,10 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.9267</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="H247" t="n">
-        <v>0.9119</v>
+        <v>0.8707</v>
       </c>
     </row>
     <row r="248">
@@ -7264,10 +7264,10 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.4841</v>
+        <v>0.4844</v>
       </c>
       <c r="H263" t="n">
-        <v>0.4386</v>
+        <v>0.4525</v>
       </c>
     </row>
     <row r="264">
@@ -7290,10 +7290,10 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.3191</v>
+        <v>0.3765</v>
       </c>
       <c r="H264" t="n">
-        <v>0.2847</v>
+        <v>0.3426</v>
       </c>
     </row>
     <row r="265">
@@ -7316,10 +7316,10 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.3723</v>
+        <v>0.4054</v>
       </c>
       <c r="H265" t="n">
-        <v>0.3424</v>
+        <v>0.3749</v>
       </c>
     </row>
     <row r="266">
@@ -7342,10 +7342,10 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.3903</v>
+        <v>0.3503</v>
       </c>
       <c r="H266" t="n">
-        <v>0.3477</v>
+        <v>0.3138</v>
       </c>
     </row>
     <row r="267">
@@ -7359,19 +7359,19 @@
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>0.626</v>
+        <v>0.6257</v>
       </c>
       <c r="H267" t="n">
-        <v>0.5964</v>
+        <v>0.5981</v>
       </c>
     </row>
     <row r="268">
@@ -7385,19 +7385,19 @@
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.579</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="H268" t="n">
-        <v>0.5477</v>
+        <v>0.6962</v>
       </c>
     </row>
     <row r="269">
@@ -7420,10 +7420,10 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>0.7009</v>
+        <v>0.7502</v>
       </c>
       <c r="H269" t="n">
-        <v>0.6583</v>
+        <v>0.7163</v>
       </c>
     </row>
     <row r="270">
@@ -7446,10 +7446,10 @@
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="n">
-        <v>0.8151</v>
+        <v>0.8246</v>
       </c>
       <c r="H270" t="n">
-        <v>0.7763</v>
+        <v>0.7816</v>
       </c>
     </row>
     <row r="271">
@@ -7472,10 +7472,10 @@
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.6764</v>
+        <v>0.7792</v>
       </c>
       <c r="H271" t="n">
-        <v>0.6361</v>
+        <v>0.7336</v>
       </c>
     </row>
     <row r="272">
@@ -7498,10 +7498,10 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.956</v>
+        <v>0.9479</v>
       </c>
       <c r="H272" t="n">
-        <v>0.9468</v>
+        <v>0.9378</v>
       </c>
     </row>
     <row r="273">
@@ -7524,10 +7524,10 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.9167</v>
+        <v>0.9435</v>
       </c>
       <c r="H273" t="n">
-        <v>0.8994</v>
+        <v>0.9265</v>
       </c>
     </row>
     <row r="274">
@@ -7550,10 +7550,10 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.9754</v>
+        <v>0.9757</v>
       </c>
       <c r="H274" t="n">
-        <v>0.971</v>
+        <v>0.9718</v>
       </c>
     </row>
     <row r="275">
@@ -7576,10 +7576,10 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.977</v>
+        <v>0.9782</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9731</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="276">
@@ -7602,10 +7602,10 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.9619</v>
+        <v>0.969</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9623</v>
       </c>
     </row>
     <row r="277">
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.0898</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="H292" t="n">
-        <v>0.0796</v>
+        <v>0.07489999999999999</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.0275</v>
+        <v>0.028</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0232</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.0329</v>
+        <v>0.0358</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0283</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.0341</v>
+        <v>0.0311</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0298</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="296">
@@ -8113,19 +8113,19 @@
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.097</v>
+        <v>0.1125</v>
       </c>
       <c r="H296" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0887</v>
       </c>
     </row>
     <row r="297">
@@ -8139,19 +8139,19 @@
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.089</v>
+        <v>0.1387</v>
       </c>
       <c r="H297" t="n">
-        <v>0.0687</v>
+        <v>0.1182</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.1272</v>
+        <v>0.1822</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0994</v>
+        <v>0.1512</v>
       </c>
     </row>
     <row r="299">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.1938</v>
+        <v>0.267</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1629</v>
+        <v>0.2331</v>
       </c>
     </row>
     <row r="300">
@@ -8226,10 +8226,10 @@
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.1004</v>
+        <v>0.1817</v>
       </c>
       <c r="H300" t="n">
-        <v>0.076</v>
+        <v>0.1422</v>
       </c>
     </row>
     <row r="301">
@@ -8252,10 +8252,10 @@
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.0532</v>
+        <v>0.0622</v>
       </c>
       <c r="H301" t="n">
-        <v>0.044</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.337</v>
+        <v>0.4646</v>
       </c>
       <c r="H302" t="n">
-        <v>0.2926</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="303">
@@ -8304,10 +8304,10 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.6947</v>
+        <v>0.7713</v>
       </c>
       <c r="H303" t="n">
-        <v>0.6478</v>
+        <v>0.7373</v>
       </c>
     </row>
     <row r="304">
@@ -8330,10 +8330,10 @@
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.7484</v>
+        <v>0.8142</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7163</v>
+        <v>0.7884</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.5447</v>
+        <v>0.6253</v>
       </c>
       <c r="H305" t="n">
-        <v>0.504</v>
+        <v>0.5911</v>
       </c>
     </row>
     <row r="306">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.1506</v>
+        <v>0.1322</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1338</v>
+        <v>0.1235</v>
       </c>
     </row>
     <row r="322">
@@ -8798,10 +8798,10 @@
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="n">
-        <v>0.0563</v>
+        <v>0.0402</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0471</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="323">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0481</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0537</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.0591</v>
+        <v>0.0416</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0489</v>
+        <v>0.0356</v>
       </c>
     </row>
     <row r="325">
@@ -8867,19 +8867,19 @@
       </c>
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.1927</v>
+        <v>0.1225</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1606</v>
+        <v>0.1004</v>
       </c>
     </row>
     <row r="326">
@@ -8893,19 +8893,19 @@
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="n">
-        <v>0.1421</v>
+        <v>0.1883</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1156</v>
+        <v>0.1632</v>
       </c>
     </row>
     <row r="327">
@@ -8928,10 +8928,10 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>0.2226</v>
+        <v>0.2286</v>
       </c>
       <c r="H327" t="n">
-        <v>0.1929</v>
+        <v>0.196</v>
       </c>
     </row>
     <row r="328">
@@ -8954,10 +8954,10 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.3698</v>
+        <v>0.3483</v>
       </c>
       <c r="H328" t="n">
-        <v>0.349</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="329">
@@ -8980,10 +8980,10 @@
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>0.2155</v>
+        <v>0.2477</v>
       </c>
       <c r="H329" t="n">
-        <v>0.1938</v>
+        <v>0.2304</v>
       </c>
     </row>
     <row r="330">
@@ -9006,10 +9006,10 @@
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.1006</v>
+        <v>0.0735</v>
       </c>
       <c r="H330" t="n">
-        <v>0.0833</v>
+        <v>0.0565</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.7074</v>
+        <v>0.58</v>
       </c>
       <c r="H331" t="n">
-        <v>0.663</v>
+        <v>0.5354</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.8381999999999999</v>
+        <v>0.8236</v>
       </c>
       <c r="H332" t="n">
-        <v>0.7988</v>
+        <v>0.7769</v>
       </c>
     </row>
     <row r="333">
@@ -9084,10 +9084,10 @@
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.8808</v>
+        <v>0.8496</v>
       </c>
       <c r="H333" t="n">
-        <v>0.853</v>
+        <v>0.8224</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.7192</v>
+        <v>0.6585</v>
       </c>
       <c r="H334" t="n">
-        <v>0.6854</v>
+        <v>0.6327</v>
       </c>
     </row>
     <row r="335">
@@ -9526,10 +9526,10 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>0.0525</v>
+        <v>0.047</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0425</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="351">
@@ -9552,10 +9552,10 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.022</v>
+        <v>0.0184</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0187</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="352">
@@ -9578,10 +9578,10 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.0257</v>
+        <v>0.0236</v>
       </c>
       <c r="H352" t="n">
-        <v>0.022</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="353">
@@ -9604,10 +9604,10 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>0.0296</v>
+        <v>0.0226</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0254</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="354">
@@ -9621,19 +9621,19 @@
       </c>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.0421</v>
+        <v>0.0388</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0345</v>
+        <v>0.0304</v>
       </c>
     </row>
     <row r="355">
@@ -9647,19 +9647,19 @@
       </c>
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.0352</v>
+        <v>0.0485</v>
       </c>
       <c r="H355" t="n">
-        <v>0.0284</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="356">
@@ -9682,10 +9682,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.0583</v>
+        <v>0.0704</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0491</v>
+        <v>0.0602</v>
       </c>
     </row>
     <row r="357">
@@ -9708,10 +9708,10 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.1029</v>
+        <v>0.0883</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0885</v>
+        <v>0.0732</v>
       </c>
     </row>
     <row r="358">
@@ -9734,10 +9734,10 @@
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>0.0556</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H358" t="n">
-        <v>0.0471</v>
+        <v>0.0529</v>
       </c>
     </row>
     <row r="359">
@@ -9760,10 +9760,10 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.029</v>
+        <v>0.0282</v>
       </c>
       <c r="H359" t="n">
-        <v>0.0246</v>
+        <v>0.0243</v>
       </c>
     </row>
     <row r="360">
@@ -9786,10 +9786,10 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.3522</v>
+        <v>0.2627</v>
       </c>
       <c r="H360" t="n">
-        <v>0.3053</v>
+        <v>0.2287</v>
       </c>
     </row>
     <row r="361">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.2012</v>
+        <v>0.2231</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1618</v>
+        <v>0.1764</v>
       </c>
     </row>
     <row r="362">
@@ -9838,10 +9838,10 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>0.5937</v>
+        <v>0.5999</v>
       </c>
       <c r="H362" t="n">
-        <v>0.556</v>
+        <v>0.5663</v>
       </c>
     </row>
     <row r="363">
@@ -9864,10 +9864,10 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>0.3825</v>
+        <v>0.3669</v>
       </c>
       <c r="H363" t="n">
-        <v>0.3353</v>
+        <v>0.3196</v>
       </c>
     </row>
     <row r="364">
@@ -10280,10 +10280,10 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.0561</v>
+        <v>0.0441</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0471</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="380">
@@ -10306,10 +10306,10 @@
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
-        <v>0.0213</v>
+        <v>0.0194</v>
       </c>
       <c r="H380" t="n">
-        <v>0.0178</v>
+        <v>0.0165</v>
       </c>
     </row>
     <row r="381">
@@ -10332,10 +10332,10 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.0216</v>
+        <v>0.0217</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0188</v>
+        <v>0.0181</v>
       </c>
     </row>
     <row r="382">
@@ -10358,10 +10358,10 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>0.0217</v>
+        <v>0.0191</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0187</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="383">
@@ -10375,19 +10375,19 @@
       </c>
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.0382</v>
+        <v>0.03</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0312</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="384">
@@ -10401,19 +10401,19 @@
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>0.0282</v>
+        <v>0.0399</v>
       </c>
       <c r="H384" t="n">
-        <v>0.0247</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="385">
@@ -10436,10 +10436,10 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.0448</v>
+        <v>0.0454</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0387</v>
+        <v>0.0409</v>
       </c>
     </row>
     <row r="386">
@@ -10462,10 +10462,10 @@
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.0834</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0727</v>
+        <v>0.0621</v>
       </c>
     </row>
     <row r="387">
@@ -10488,10 +10488,10 @@
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.0444</v>
+        <v>0.0563</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0377</v>
+        <v>0.0486</v>
       </c>
     </row>
     <row r="388">
@@ -10514,10 +10514,10 @@
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.0269</v>
+        <v>0.0252</v>
       </c>
       <c r="H388" t="n">
-        <v>0.023</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="389">
@@ -10540,10 +10540,10 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.2837</v>
+        <v>0.2116</v>
       </c>
       <c r="H389" t="n">
-        <v>0.2516</v>
+        <v>0.1858</v>
       </c>
     </row>
     <row r="390">
@@ -10566,10 +10566,10 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.147</v>
+        <v>0.1776</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1192</v>
+        <v>0.1504</v>
       </c>
     </row>
     <row r="391">
@@ -10592,10 +10592,10 @@
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>0.444</v>
+        <v>0.4337</v>
       </c>
       <c r="H391" t="n">
-        <v>0.4063</v>
+        <v>0.4001</v>
       </c>
     </row>
     <row r="392">
@@ -10618,10 +10618,10 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>0.3076</v>
+        <v>0.2969</v>
       </c>
       <c r="H392" t="n">
-        <v>0.2801</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="393">
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.0868</v>
+        <v>0.0757</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0788</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="409">
@@ -11060,10 +11060,10 @@
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
-        <v>0.03</v>
+        <v>0.0319</v>
       </c>
       <c r="H409" t="n">
-        <v>0.0251</v>
+        <v>0.0256</v>
       </c>
     </row>
     <row r="410">
@@ -11086,10 +11086,10 @@
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>0.0321</v>
+        <v>0.0307</v>
       </c>
       <c r="H410" t="n">
-        <v>0.0269</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="411">
@@ -11112,10 +11112,10 @@
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
-        <v>0.0297</v>
+        <v>0.032</v>
       </c>
       <c r="H411" t="n">
-        <v>0.0268</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="412">
@@ -11129,19 +11129,19 @@
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>0.0752</v>
+        <v>0.0646</v>
       </c>
       <c r="H412" t="n">
-        <v>0.0622</v>
+        <v>0.0545</v>
       </c>
     </row>
     <row r="413">
@@ -11155,19 +11155,19 @@
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>0.0598</v>
+        <v>0.1022</v>
       </c>
       <c r="H413" t="n">
-        <v>0.0487</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="414">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.1028</v>
+        <v>0.1464</v>
       </c>
       <c r="H414" t="n">
-        <v>0.0822</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="415">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.1941</v>
+        <v>0.2225</v>
       </c>
       <c r="H415" t="n">
-        <v>0.1741</v>
+        <v>0.1959</v>
       </c>
     </row>
     <row r="416">
@@ -11242,10 +11242,10 @@
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.0881</v>
+        <v>0.1293</v>
       </c>
       <c r="H416" t="n">
-        <v>0.0733</v>
+        <v>0.1084</v>
       </c>
     </row>
     <row r="417">
@@ -11268,10 +11268,10 @@
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.0459</v>
+        <v>0.0377</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0381</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="418">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.496</v>
+        <v>0.4089</v>
       </c>
       <c r="H418" t="n">
-        <v>0.4553</v>
+        <v>0.3747</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.3146</v>
+        <v>0.3673</v>
       </c>
       <c r="H419" t="n">
-        <v>0.2808</v>
+        <v>0.3415</v>
       </c>
     </row>
     <row r="420">
@@ -11346,10 +11346,10 @@
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>0.6647</v>
+        <v>0.6804</v>
       </c>
       <c r="H420" t="n">
-        <v>0.6175</v>
+        <v>0.6331</v>
       </c>
     </row>
     <row r="421">
@@ -11372,10 +11372,10 @@
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
-        <v>0.7199</v>
+        <v>0.7333</v>
       </c>
       <c r="H421" t="n">
-        <v>0.6924</v>
+        <v>0.7030999999999999</v>
       </c>
     </row>
     <row r="422">
@@ -11883,11 +11883,11 @@
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
@@ -11909,11 +11909,11 @@
       </c>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
@@ -12637,11 +12637,11 @@
       </c>
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F470" t="inlineStr"/>
@@ -12663,11 +12663,11 @@
       </c>
       <c r="C471" t="inlineStr"/>
       <c r="D471" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F471" t="inlineStr"/>
@@ -13391,11 +13391,11 @@
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
@@ -13417,11 +13417,11 @@
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
@@ -14145,11 +14145,11 @@
       </c>
       <c r="C528" t="inlineStr"/>
       <c r="D528" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F528" t="inlineStr"/>
@@ -14171,11 +14171,11 @@
       </c>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F529" t="inlineStr"/>
@@ -14899,11 +14899,11 @@
       </c>
       <c r="C557" t="inlineStr"/>
       <c r="D557" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F557" t="inlineStr"/>
@@ -14925,11 +14925,11 @@
       </c>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F558" t="inlineStr"/>
@@ -15653,11 +15653,11 @@
       </c>
       <c r="C586" t="inlineStr"/>
       <c r="D586" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F586" t="inlineStr"/>
@@ -15679,11 +15679,11 @@
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F587" t="inlineStr"/>
@@ -16407,11 +16407,11 @@
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F615" t="inlineStr"/>
@@ -16433,11 +16433,11 @@
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F616" t="inlineStr"/>
@@ -17161,11 +17161,11 @@
       </c>
       <c r="C644" t="inlineStr"/>
       <c r="D644" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F644" t="inlineStr"/>
@@ -17187,11 +17187,11 @@
       </c>
       <c r="C645" t="inlineStr"/>
       <c r="D645" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F645" t="inlineStr"/>
@@ -17915,11 +17915,11 @@
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F673" t="inlineStr"/>
@@ -17941,11 +17941,11 @@
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F674" t="inlineStr"/>
@@ -18669,11 +18669,11 @@
       </c>
       <c r="C702" t="inlineStr"/>
       <c r="D702" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F702" t="inlineStr"/>
@@ -18695,11 +18695,11 @@
       </c>
       <c r="C703" t="inlineStr"/>
       <c r="D703" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F703" t="inlineStr"/>
@@ -19423,11 +19423,11 @@
       </c>
       <c r="C731" t="inlineStr"/>
       <c r="D731" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F731" t="inlineStr"/>
@@ -19449,11 +19449,11 @@
       </c>
       <c r="C732" t="inlineStr"/>
       <c r="D732" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F732" t="inlineStr"/>
@@ -20177,11 +20177,11 @@
       </c>
       <c r="C760" t="inlineStr"/>
       <c r="D760" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F760" t="inlineStr"/>
@@ -20203,11 +20203,11 @@
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F761" t="inlineStr"/>
@@ -20931,11 +20931,11 @@
       </c>
       <c r="C789" t="inlineStr"/>
       <c r="D789" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F789" t="inlineStr"/>
@@ -20957,11 +20957,11 @@
       </c>
       <c r="C790" t="inlineStr"/>
       <c r="D790" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F790" t="inlineStr"/>
@@ -21685,11 +21685,11 @@
       </c>
       <c r="C818" t="inlineStr"/>
       <c r="D818" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E818" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F818" t="inlineStr"/>
@@ -21711,11 +21711,11 @@
       </c>
       <c r="C819" t="inlineStr"/>
       <c r="D819" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F819" t="inlineStr"/>
@@ -22439,11 +22439,11 @@
       </c>
       <c r="C847" t="inlineStr"/>
       <c r="D847" t="n">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>Hawks</t>
         </is>
       </c>
       <c r="F847" t="inlineStr"/>
@@ -22465,11 +22465,11 @@
       </c>
       <c r="C848" t="inlineStr"/>
       <c r="D848" t="n">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>Hawks</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F848" t="inlineStr"/>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.3785</v>
+        <v>0.4496</v>
       </c>
       <c r="H2" t="n">
-        <v>0.335</v>
+        <v>0.3903</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.4215</v>
+        <v>0.4621</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3772</v>
+        <v>0.4084</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.4127</v>
+        <v>0.4897</v>
       </c>
       <c r="H4" t="n">
-        <v>0.394</v>
+        <v>0.4423</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.6137</v>
+        <v>0.679</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5738</v>
+        <v>0.6435999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.7205</v>
+        <v>0.706</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7042</v>
+        <v>0.6842</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.7534</v>
+        <v>0.7645</v>
       </c>
       <c r="H7" t="n">
-        <v>0.717</v>
+        <v>0.7363</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.8115</v>
+        <v>0.8312</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7803</v>
+        <v>0.8091</v>
       </c>
     </row>
     <row r="9">
@@ -660,10 +660,10 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.7674</v>
+        <v>0.7669</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7326</v>
+        <v>0.7364000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -686,10 +686,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.5475</v>
+        <v>0.5686</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5322</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9251</v>
+        <v>0.9382</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9154</v>
+        <v>0.9305</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.8764999999999999</v>
+        <v>0.8966</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8678</v>
+        <v>0.8881</v>
       </c>
     </row>
     <row r="13">
@@ -764,10 +764,10 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.9624</v>
+        <v>0.9681</v>
       </c>
       <c r="H13" t="n">
-        <v>0.953</v>
+        <v>0.9608</v>
       </c>
     </row>
     <row r="14">
@@ -790,10 +790,10 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.9639</v>
+        <v>0.9517</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9559</v>
+        <v>0.9446</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9261</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9243</v>
+        <v>0.9207</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.665</v>
+        <v>0.6097</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.5504</v>
       </c>
     </row>
     <row r="32">
@@ -1258,10 +1258,10 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.5589</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.533</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1284,10 +1284,10 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.5261</v>
+        <v>0.5837</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4828</v>
+        <v>0.5424</v>
       </c>
     </row>
     <row r="34">
@@ -1310,10 +1310,10 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.7685</v>
+        <v>0.7783</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7335</v>
+        <v>0.7426</v>
       </c>
     </row>
     <row r="35">
@@ -1336,10 +1336,10 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.8708</v>
+        <v>0.8419</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8428</v>
+        <v>0.8136</v>
       </c>
     </row>
     <row r="36">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.8898</v>
+        <v>0.8829</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8704</v>
+        <v>0.8646</v>
       </c>
     </row>
     <row r="37">
@@ -1388,10 +1388,10 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.9291</v>
+        <v>0.9267</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9092</v>
+        <v>0.9061</v>
       </c>
     </row>
     <row r="38">
@@ -1414,10 +1414,10 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.886</v>
+        <v>0.8764</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8567</v>
+        <v>0.8473000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1440,10 +1440,10 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.6574</v>
+        <v>0.6659</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6272</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.9752</v>
+        <v>0.9737</v>
       </c>
       <c r="H40" t="n">
-        <v>0.972</v>
+        <v>0.9688</v>
       </c>
     </row>
     <row r="41">
@@ -1492,10 +1492,10 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.9674</v>
+        <v>0.9634</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9598</v>
+        <v>0.9547</v>
       </c>
     </row>
     <row r="42">
@@ -1518,10 +1518,10 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.9841</v>
+        <v>0.9798</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9816</v>
+        <v>0.9771</v>
       </c>
     </row>
     <row r="43">
@@ -1544,10 +1544,10 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>0.9835</v>
+        <v>0.9812</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9806</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="44">
@@ -1570,10 +1570,10 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.9744</v>
+        <v>0.9716</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9681</v>
+        <v>0.9647</v>
       </c>
     </row>
     <row r="45">
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.6228</v>
+        <v>0.5916</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5785</v>
+        <v>0.5379</v>
       </c>
     </row>
     <row r="61">
@@ -2012,10 +2012,10 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>0.467</v>
+        <v>0.438</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4411</v>
+        <v>0.4148</v>
       </c>
     </row>
     <row r="62">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.4761</v>
+        <v>0.5258</v>
       </c>
       <c r="H62" t="n">
-        <v>0.443</v>
+        <v>0.4917</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.7265</v>
+        <v>0.7573</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7242</v>
       </c>
     </row>
     <row r="64">
@@ -2090,10 +2090,10 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0.8374</v>
+        <v>0.8151</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8105</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="65">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8521</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8334</v>
+        <v>0.8315</v>
       </c>
     </row>
     <row r="66">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.9121</v>
+        <v>0.9175</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8842</v>
+        <v>0.8918</v>
       </c>
     </row>
     <row r="67">
@@ -2168,10 +2168,10 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.867</v>
+        <v>0.8562</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8306</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="68">
@@ -2194,10 +2194,10 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.6251</v>
+        <v>0.6284</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5946</v>
+        <v>0.5955</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.9686</v>
+        <v>0.9674</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.9633</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9608</v>
+        <v>0.9574</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9519</v>
+        <v>0.9471000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.9791</v>
+        <v>0.9742</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9764</v>
+        <v>0.9715</v>
       </c>
     </row>
     <row r="72">
@@ -2298,10 +2298,10 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>0.9819</v>
+        <v>0.9822</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9792</v>
       </c>
     </row>
     <row r="73">
@@ -2324,10 +2324,10 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.9742</v>
+        <v>0.9725</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9673</v>
       </c>
     </row>
     <row r="74">
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.606</v>
+        <v>0.5577</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5873</v>
+        <v>0.5103</v>
       </c>
     </row>
     <row r="90">
@@ -2766,10 +2766,10 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.5172</v>
+        <v>0.4576</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4739</v>
+        <v>0.4163</v>
       </c>
     </row>
     <row r="91">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5083</v>
       </c>
       <c r="H91" t="n">
-        <v>0.5239</v>
+        <v>0.4742</v>
       </c>
     </row>
     <row r="92">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.7647</v>
+        <v>0.7479</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7319</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="93">
@@ -2844,10 +2844,10 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0.8514</v>
+        <v>0.7822</v>
       </c>
       <c r="H93" t="n">
-        <v>0.8286</v>
+        <v>0.7529</v>
       </c>
     </row>
     <row r="94">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8521</v>
       </c>
       <c r="H94" t="n">
-        <v>0.8484</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="95">
@@ -2896,10 +2896,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.9185</v>
+        <v>0.898</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8975</v>
+        <v>0.8712</v>
       </c>
     </row>
     <row r="96">
@@ -2922,10 +2922,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.88</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>0.848</v>
+        <v>0.8096</v>
       </c>
     </row>
     <row r="97">
@@ -2948,10 +2948,10 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.6862</v>
+        <v>0.6281</v>
       </c>
       <c r="H97" t="n">
-        <v>0.6497000000000001</v>
+        <v>0.5711000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.9731</v>
+        <v>0.9583</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9689</v>
+        <v>0.9519</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9644</v>
+        <v>0.9506</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9584</v>
+        <v>0.9421</v>
       </c>
     </row>
     <row r="100">
@@ -3026,10 +3026,10 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>0.9805</v>
+        <v>0.9694</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9774</v>
+        <v>0.9643</v>
       </c>
     </row>
     <row r="101">
@@ -3052,10 +3052,10 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0.9839</v>
+        <v>0.9796</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9809</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="102">
@@ -3078,10 +3078,10 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>0.9704</v>
+        <v>0.9661</v>
       </c>
       <c r="H102" t="n">
-        <v>0.968</v>
+        <v>0.9631999999999999</v>
       </c>
     </row>
     <row r="103">
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.4262</v>
+        <v>0.3564</v>
       </c>
       <c r="H118" t="n">
-        <v>0.3863</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="119">
@@ -3520,10 +3520,10 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.2665</v>
+        <v>0.2574</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2315</v>
+        <v>0.2217</v>
       </c>
     </row>
     <row r="120">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.3049</v>
+        <v>0.2758</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2735</v>
+        <v>0.2427</v>
       </c>
     </row>
     <row r="121">
@@ -3572,10 +3572,10 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.2681</v>
+        <v>0.294</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2353</v>
+        <v>0.2521</v>
       </c>
     </row>
     <row r="122">
@@ -3598,10 +3598,10 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0.6188</v>
+        <v>0.5684</v>
       </c>
       <c r="H122" t="n">
-        <v>0.5783</v>
+        <v>0.5369</v>
       </c>
     </row>
     <row r="123">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.6332</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="H123" t="n">
-        <v>0.6073</v>
+        <v>0.6119</v>
       </c>
     </row>
     <row r="124">
@@ -3650,10 +3650,10 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0.7741</v>
+        <v>0.7302</v>
       </c>
       <c r="H124" t="n">
-        <v>0.7315</v>
+        <v>0.6857</v>
       </c>
     </row>
     <row r="125">
@@ -3676,10 +3676,10 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>0.6829</v>
+        <v>0.6532</v>
       </c>
       <c r="H125" t="n">
-        <v>0.643</v>
+        <v>0.6099</v>
       </c>
     </row>
     <row r="126">
@@ -3702,10 +3702,10 @@
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>0.4019</v>
+        <v>0.3989</v>
       </c>
       <c r="H126" t="n">
-        <v>0.3743</v>
+        <v>0.3672</v>
       </c>
     </row>
     <row r="127">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.9113</v>
+        <v>0.9035</v>
       </c>
       <c r="H127" t="n">
-        <v>0.8875</v>
+        <v>0.8793</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.8996</v>
+        <v>0.8736</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8528</v>
       </c>
     </row>
     <row r="129">
@@ -3780,10 +3780,10 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.9696</v>
+        <v>0.9688</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9586</v>
       </c>
     </row>
     <row r="130">
@@ -3806,10 +3806,10 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.9735</v>
+        <v>0.9676</v>
       </c>
       <c r="H130" t="n">
-        <v>0.97</v>
+        <v>0.9617</v>
       </c>
     </row>
     <row r="131">
@@ -3832,10 +3832,10 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.9455</v>
+        <v>0.9389</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9354</v>
+        <v>0.9267</v>
       </c>
     </row>
     <row r="132">
@@ -4248,10 +4248,10 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.2958</v>
+        <v>0.3158</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2795</v>
+        <v>0.294</v>
       </c>
     </row>
     <row r="148">
@@ -4274,10 +4274,10 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>0.1572</v>
+        <v>0.1864</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1292</v>
+        <v>0.1581</v>
       </c>
     </row>
     <row r="149">
@@ -4300,10 +4300,10 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>0.1895</v>
+        <v>0.2155</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1626</v>
+        <v>0.1849</v>
       </c>
     </row>
     <row r="150">
@@ -4326,10 +4326,10 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>0.1714</v>
+        <v>0.2471</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1486</v>
+        <v>0.2178</v>
       </c>
     </row>
     <row r="151">
@@ -4352,10 +4352,10 @@
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>0.4217</v>
+        <v>0.4631</v>
       </c>
       <c r="H151" t="n">
-        <v>0.3812</v>
+        <v>0.4316</v>
       </c>
     </row>
     <row r="152">
@@ -4378,10 +4378,10 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0.5569</v>
+        <v>0.5839</v>
       </c>
       <c r="H152" t="n">
-        <v>0.5268</v>
+        <v>0.5582</v>
       </c>
     </row>
     <row r="153">
@@ -4404,10 +4404,10 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.6573</v>
+        <v>0.7036</v>
       </c>
       <c r="H153" t="n">
-        <v>0.6224</v>
+        <v>0.6636</v>
       </c>
     </row>
     <row r="154">
@@ -4430,10 +4430,10 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.6136</v>
+        <v>0.5927</v>
       </c>
       <c r="H154" t="n">
-        <v>0.57</v>
+        <v>0.556</v>
       </c>
     </row>
     <row r="155">
@@ -4456,10 +4456,10 @@
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.3038</v>
+        <v>0.3493</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2747</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="156">
@@ -4482,10 +4482,10 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.8818</v>
+        <v>0.8903</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8613</v>
+        <v>0.8677</v>
       </c>
     </row>
     <row r="157">
@@ -4508,10 +4508,10 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>0.8368</v>
+        <v>0.8414</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8117</v>
+        <v>0.8147</v>
       </c>
     </row>
     <row r="158">
@@ -4534,10 +4534,10 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.9585</v>
+        <v>0.9607</v>
       </c>
       <c r="H158" t="n">
-        <v>0.9515</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="159">
@@ -4560,10 +4560,10 @@
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>0.967</v>
+        <v>0.9646</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9601</v>
+        <v>0.956</v>
       </c>
     </row>
     <row r="160">
@@ -4586,10 +4586,10 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>0.9167</v>
+        <v>0.9253</v>
       </c>
       <c r="H160" t="n">
-        <v>0.8978</v>
+        <v>0.9108000000000001</v>
       </c>
     </row>
     <row r="161">
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.283</v>
+        <v>0.2637</v>
       </c>
       <c r="H176" t="n">
-        <v>0.2466</v>
+        <v>0.2355</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.1296</v>
+        <v>0.1354</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1102</v>
+        <v>0.1171</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.1666</v>
+        <v>0.1685</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1436</v>
+        <v>0.1479</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.1516</v>
+        <v>0.167</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1275</v>
+        <v>0.1479</v>
       </c>
     </row>
     <row r="180">
@@ -5106,10 +5106,10 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.3927</v>
+        <v>0.3881</v>
       </c>
       <c r="H180" t="n">
-        <v>0.3668</v>
+        <v>0.3604</v>
       </c>
     </row>
     <row r="181">
@@ -5132,10 +5132,10 @@
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>0.4732</v>
+        <v>0.4418</v>
       </c>
       <c r="H181" t="n">
-        <v>0.4431</v>
+        <v>0.4161</v>
       </c>
     </row>
     <row r="182">
@@ -5158,10 +5158,10 @@
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.6096</v>
+        <v>0.6123</v>
       </c>
       <c r="H182" t="n">
-        <v>0.5715</v>
+        <v>0.5784</v>
       </c>
     </row>
     <row r="183">
@@ -5184,10 +5184,10 @@
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>0.5542</v>
+        <v>0.5315</v>
       </c>
       <c r="H183" t="n">
-        <v>0.5305</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="184">
@@ -5210,10 +5210,10 @@
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>0.2837</v>
+        <v>0.2886</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2498</v>
+        <v>0.2519</v>
       </c>
     </row>
     <row r="185">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.8488</v>
+        <v>0.846</v>
       </c>
       <c r="H185" t="n">
-        <v>0.8178</v>
+        <v>0.8141</v>
       </c>
     </row>
     <row r="186">
@@ -5262,10 +5262,10 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>0.804</v>
+        <v>0.7844</v>
       </c>
       <c r="H186" t="n">
-        <v>0.7714</v>
+        <v>0.7549</v>
       </c>
     </row>
     <row r="187">
@@ -5288,10 +5288,10 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.9398</v>
+        <v>0.9369</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9296</v>
+        <v>0.9268999999999999</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.9591</v>
+        <v>0.9506</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9546</v>
+        <v>0.9441000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.8808</v>
+        <v>0.8747</v>
       </c>
       <c r="H189" t="n">
-        <v>0.8536</v>
+        <v>0.8518</v>
       </c>
     </row>
     <row r="190">
@@ -5756,10 +5756,10 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.2197</v>
+        <v>0.1909</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1885</v>
+        <v>0.1688</v>
       </c>
     </row>
     <row r="206">
@@ -5782,10 +5782,10 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0939</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0709</v>
+        <v>0.0733</v>
       </c>
     </row>
     <row r="207">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.1158</v>
+        <v>0.1082</v>
       </c>
       <c r="H207" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0825</v>
       </c>
     </row>
     <row r="208">
@@ -5834,10 +5834,10 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.1025</v>
+        <v>0.1288</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0815</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="209">
@@ -5860,10 +5860,10 @@
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>0.2685</v>
+        <v>0.3143</v>
       </c>
       <c r="H209" t="n">
-        <v>0.2259</v>
+        <v>0.2698</v>
       </c>
     </row>
     <row r="210">
@@ -5886,10 +5886,10 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.3776</v>
+        <v>0.3364</v>
       </c>
       <c r="H210" t="n">
-        <v>0.3427</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="211">
@@ -5912,10 +5912,10 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.4285</v>
+        <v>0.4216</v>
       </c>
       <c r="H211" t="n">
-        <v>0.3904</v>
+        <v>0.3877</v>
       </c>
     </row>
     <row r="212">
@@ -5938,10 +5938,10 @@
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.4322</v>
+        <v>0.3961</v>
       </c>
       <c r="H212" t="n">
-        <v>0.4038</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="213">
@@ -5964,10 +5964,10 @@
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>0.2184</v>
+        <v>0.2092</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1754</v>
+        <v>0.1735</v>
       </c>
     </row>
     <row r="214">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.7669</v>
+        <v>0.7606000000000001</v>
       </c>
       <c r="H214" t="n">
-        <v>0.733</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="215">
@@ -6016,10 +6016,10 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.6701</v>
+        <v>0.679</v>
       </c>
       <c r="H215" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6566</v>
       </c>
     </row>
     <row r="216">
@@ -6042,10 +6042,10 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.9268</v>
+        <v>0.9134</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9117</v>
+        <v>0.8968</v>
       </c>
     </row>
     <row r="217">
@@ -6068,10 +6068,10 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.9379</v>
+        <v>0.9124</v>
       </c>
       <c r="H217" t="n">
-        <v>0.928</v>
+        <v>0.9015</v>
       </c>
     </row>
     <row r="218">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.8041</v>
+        <v>0.8047</v>
       </c>
       <c r="H218" t="n">
-        <v>0.7775</v>
+        <v>0.7842</v>
       </c>
     </row>
     <row r="219">
@@ -6510,10 +6510,10 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.2674</v>
+        <v>0.2636</v>
       </c>
       <c r="H234" t="n">
-        <v>0.2326</v>
+        <v>0.2331</v>
       </c>
     </row>
     <row r="235">
@@ -6536,10 +6536,10 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.1433</v>
+        <v>0.1527</v>
       </c>
       <c r="H235" t="n">
-        <v>0.114</v>
+        <v>0.1236</v>
       </c>
     </row>
     <row r="236">
@@ -6562,10 +6562,10 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.1694</v>
+        <v>0.1763</v>
       </c>
       <c r="H236" t="n">
-        <v>0.133</v>
+        <v>0.1438</v>
       </c>
     </row>
     <row r="237">
@@ -6588,10 +6588,10 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.152</v>
+        <v>0.1904</v>
       </c>
       <c r="H237" t="n">
-        <v>0.12</v>
+        <v>0.1507</v>
       </c>
     </row>
     <row r="238">
@@ -6614,10 +6614,10 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>0.357</v>
+        <v>0.3901</v>
       </c>
       <c r="H238" t="n">
-        <v>0.3171</v>
+        <v>0.3468</v>
       </c>
     </row>
     <row r="239">
@@ -6640,10 +6640,10 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.43</v>
+        <v>0.444</v>
       </c>
       <c r="H239" t="n">
-        <v>0.3864</v>
+        <v>0.4073</v>
       </c>
     </row>
     <row r="240">
@@ -6666,10 +6666,10 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>0.4695</v>
+        <v>0.5</v>
       </c>
       <c r="H240" t="n">
-        <v>0.4458</v>
+        <v>0.4685</v>
       </c>
     </row>
     <row r="241">
@@ -6692,10 +6692,10 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.5962</v>
+        <v>0.6302</v>
       </c>
       <c r="H241" t="n">
-        <v>0.5678</v>
+        <v>0.6039</v>
       </c>
     </row>
     <row r="242">
@@ -6718,10 +6718,10 @@
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.2664</v>
+        <v>0.3263</v>
       </c>
       <c r="H242" t="n">
-        <v>0.2208</v>
+        <v>0.2808</v>
       </c>
     </row>
     <row r="243">
@@ -6744,10 +6744,10 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.8578</v>
+        <v>0.8762</v>
       </c>
       <c r="H243" t="n">
-        <v>0.8183</v>
+        <v>0.8418</v>
       </c>
     </row>
     <row r="244">
@@ -6770,10 +6770,10 @@
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>0.7696</v>
+        <v>0.7799</v>
       </c>
       <c r="H244" t="n">
-        <v>0.7523</v>
+        <v>0.7569</v>
       </c>
     </row>
     <row r="245">
@@ -6796,10 +6796,10 @@
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="H245" t="n">
-        <v>0.9329</v>
+        <v>0.9359</v>
       </c>
     </row>
     <row r="246">
@@ -6822,10 +6822,10 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.9514</v>
+        <v>0.9456</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9437</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="247">
@@ -6848,10 +6848,10 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8933</v>
       </c>
       <c r="H247" t="n">
-        <v>0.8707</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="248">
@@ -7264,10 +7264,10 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.4844</v>
+        <v>0.4678</v>
       </c>
       <c r="H263" t="n">
-        <v>0.4525</v>
+        <v>0.4314</v>
       </c>
     </row>
     <row r="264">
@@ -7290,10 +7290,10 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.3765</v>
+        <v>0.3728</v>
       </c>
       <c r="H264" t="n">
-        <v>0.3426</v>
+        <v>0.3341</v>
       </c>
     </row>
     <row r="265">
@@ -7316,10 +7316,10 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.4054</v>
+        <v>0.4045</v>
       </c>
       <c r="H265" t="n">
-        <v>0.3749</v>
+        <v>0.3716</v>
       </c>
     </row>
     <row r="266">
@@ -7342,10 +7342,10 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.3503</v>
+        <v>0.4289</v>
       </c>
       <c r="H266" t="n">
-        <v>0.3138</v>
+        <v>0.3719</v>
       </c>
     </row>
     <row r="267">
@@ -7368,10 +7368,10 @@
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>0.6257</v>
+        <v>0.6328</v>
       </c>
       <c r="H267" t="n">
-        <v>0.5981</v>
+        <v>0.6011</v>
       </c>
     </row>
     <row r="268">
@@ -7394,10 +7394,10 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.6832</v>
       </c>
       <c r="H268" t="n">
-        <v>0.6962</v>
+        <v>0.6506999999999999</v>
       </c>
     </row>
     <row r="269">
@@ -7420,10 +7420,10 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>0.7502</v>
+        <v>0.7481</v>
       </c>
       <c r="H269" t="n">
-        <v>0.7163</v>
+        <v>0.7114</v>
       </c>
     </row>
     <row r="270">
@@ -7446,10 +7446,10 @@
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="n">
-        <v>0.8246</v>
+        <v>0.8265</v>
       </c>
       <c r="H270" t="n">
-        <v>0.7816</v>
+        <v>0.7907999999999999</v>
       </c>
     </row>
     <row r="271">
@@ -7472,10 +7472,10 @@
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.7792</v>
+        <v>0.7192</v>
       </c>
       <c r="H271" t="n">
-        <v>0.7336</v>
+        <v>0.6737</v>
       </c>
     </row>
     <row r="272">
@@ -7498,10 +7498,10 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.9479</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="H272" t="n">
-        <v>0.9378</v>
+        <v>0.9399</v>
       </c>
     </row>
     <row r="273">
@@ -7524,10 +7524,10 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.9435</v>
+        <v>0.9281</v>
       </c>
       <c r="H273" t="n">
-        <v>0.9265</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="274">
@@ -7550,10 +7550,10 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.9757</v>
+        <v>0.9768</v>
       </c>
       <c r="H274" t="n">
-        <v>0.9718</v>
+        <v>0.9728</v>
       </c>
     </row>
     <row r="275">
@@ -7576,10 +7576,10 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.9782</v>
+        <v>0.9745</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9748</v>
+        <v>0.9694</v>
       </c>
     </row>
     <row r="276">
@@ -7602,10 +7602,10 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.969</v>
+        <v>0.9566</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9623</v>
+        <v>0.9482</v>
       </c>
     </row>
     <row r="277">
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="H292" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0618</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.028</v>
+        <v>0.0312</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0248</v>
+        <v>0.0263</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.0358</v>
+        <v>0.0367</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0314</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.0311</v>
+        <v>0.0481</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0269</v>
+        <v>0.0417</v>
       </c>
     </row>
     <row r="296">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.1125</v>
+        <v>0.1207</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0887</v>
+        <v>0.0965</v>
       </c>
     </row>
     <row r="297">
@@ -8148,10 +8148,10 @@
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.1387</v>
+        <v>0.1323</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1182</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.1822</v>
+        <v>0.1859</v>
       </c>
       <c r="H298" t="n">
-        <v>0.1512</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="299">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.267</v>
+        <v>0.269</v>
       </c>
       <c r="H299" t="n">
-        <v>0.2331</v>
+        <v>0.2394</v>
       </c>
     </row>
     <row r="300">
@@ -8226,10 +8226,10 @@
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.1817</v>
+        <v>0.1582</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1422</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="301">
@@ -8252,10 +8252,10 @@
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.0622</v>
+        <v>0.0601</v>
       </c>
       <c r="H301" t="n">
-        <v>0.0521</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.4646</v>
+        <v>0.465</v>
       </c>
       <c r="H302" t="n">
-        <v>0.42</v>
+        <v>0.4208</v>
       </c>
     </row>
     <row r="303">
@@ -8304,10 +8304,10 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.7713</v>
+        <v>0.7562</v>
       </c>
       <c r="H303" t="n">
-        <v>0.7373</v>
+        <v>0.7163</v>
       </c>
     </row>
     <row r="304">
@@ -8330,10 +8330,10 @@
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.8142</v>
+        <v>0.761</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7884</v>
+        <v>0.7261</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.6253</v>
+        <v>0.5885</v>
       </c>
       <c r="H305" t="n">
-        <v>0.5911</v>
+        <v>0.5501</v>
       </c>
     </row>
     <row r="306">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.1322</v>
+        <v>0.1119</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1235</v>
+        <v>0.1034</v>
       </c>
     </row>
     <row r="322">
@@ -8798,10 +8798,10 @@
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="n">
-        <v>0.0402</v>
+        <v>0.0453</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0326</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="323">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.0481</v>
+        <v>0.0529</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0392</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.0416</v>
+        <v>0.0579</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0356</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.1225</v>
+        <v>0.1472</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1004</v>
+        <v>0.1264</v>
       </c>
     </row>
     <row r="326">
@@ -8902,10 +8902,10 @@
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="n">
-        <v>0.1883</v>
+        <v>0.1853</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1632</v>
+        <v>0.1586</v>
       </c>
     </row>
     <row r="327">
@@ -8928,10 +8928,10 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>0.2286</v>
+        <v>0.2451</v>
       </c>
       <c r="H327" t="n">
-        <v>0.196</v>
+        <v>0.2156</v>
       </c>
     </row>
     <row r="328">
@@ -8954,10 +8954,10 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.3483</v>
+        <v>0.3434</v>
       </c>
       <c r="H328" t="n">
-        <v>0.3299</v>
+        <v>0.321</v>
       </c>
     </row>
     <row r="329">
@@ -8980,10 +8980,10 @@
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>0.2477</v>
+        <v>0.2431</v>
       </c>
       <c r="H329" t="n">
-        <v>0.2304</v>
+        <v>0.2201</v>
       </c>
     </row>
     <row r="330">
@@ -9006,10 +9006,10 @@
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.0735</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H330" t="n">
-        <v>0.0565</v>
+        <v>0.07190000000000001</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.58</v>
+        <v>0.5792</v>
       </c>
       <c r="H331" t="n">
-        <v>0.5354</v>
+        <v>0.535</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.8236</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="H332" t="n">
-        <v>0.7769</v>
+        <v>0.7707000000000001</v>
       </c>
     </row>
     <row r="333">
@@ -9084,10 +9084,10 @@
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.8496</v>
+        <v>0.8308</v>
       </c>
       <c r="H333" t="n">
-        <v>0.8224</v>
+        <v>0.8036</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.6585</v>
+        <v>0.677</v>
       </c>
       <c r="H334" t="n">
-        <v>0.6327</v>
+        <v>0.6504</v>
       </c>
     </row>
     <row r="335">
@@ -9526,10 +9526,10 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>0.047</v>
+        <v>0.0392</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0376</v>
+        <v>0.0319</v>
       </c>
     </row>
     <row r="351">
@@ -9552,10 +9552,10 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.0184</v>
+        <v>0.0229</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0159</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="352">
@@ -9578,10 +9578,10 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.0236</v>
+        <v>0.0285</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0209</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="353">
@@ -9604,10 +9604,10 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>0.0226</v>
+        <v>0.0357</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0195</v>
+        <v>0.0306</v>
       </c>
     </row>
     <row r="354">
@@ -9630,10 +9630,10 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.0388</v>
+        <v>0.0414</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0304</v>
+        <v>0.0312</v>
       </c>
     </row>
     <row r="355">
@@ -9656,10 +9656,10 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.0485</v>
+        <v>0.0474</v>
       </c>
       <c r="H355" t="n">
-        <v>0.0415</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="356">
@@ -9682,10 +9682,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.0704</v>
+        <v>0.0731</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0602</v>
+        <v>0.0631</v>
       </c>
     </row>
     <row r="357">
@@ -9708,10 +9708,10 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.0883</v>
+        <v>0.1032</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0732</v>
+        <v>0.0866</v>
       </c>
     </row>
     <row r="358">
@@ -9734,10 +9734,10 @@
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="H358" t="n">
-        <v>0.0529</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="359">
@@ -9760,10 +9760,10 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.0282</v>
+        <v>0.0272</v>
       </c>
       <c r="H359" t="n">
-        <v>0.0243</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="360">
@@ -9786,10 +9786,10 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.2627</v>
+        <v>0.2837</v>
       </c>
       <c r="H360" t="n">
-        <v>0.2287</v>
+        <v>0.2438</v>
       </c>
     </row>
     <row r="361">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.2231</v>
+        <v>0.2293</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1764</v>
+        <v>0.1789</v>
       </c>
     </row>
     <row r="362">
@@ -9838,10 +9838,10 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>0.5999</v>
+        <v>0.5609</v>
       </c>
       <c r="H362" t="n">
-        <v>0.5663</v>
+        <v>0.5123</v>
       </c>
     </row>
     <row r="363">
@@ -9864,10 +9864,10 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>0.3669</v>
+        <v>0.3415</v>
       </c>
       <c r="H363" t="n">
-        <v>0.3196</v>
+        <v>0.2893</v>
       </c>
     </row>
     <row r="364">
@@ -10280,10 +10280,10 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.0441</v>
+        <v>0.0554</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0361</v>
+        <v>0.0483</v>
       </c>
     </row>
     <row r="380">
@@ -10306,10 +10306,10 @@
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
-        <v>0.0194</v>
+        <v>0.0223</v>
       </c>
       <c r="H380" t="n">
-        <v>0.0165</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="381">
@@ -10332,10 +10332,10 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.0217</v>
+        <v>0.0208</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0181</v>
+        <v>0.0178</v>
       </c>
     </row>
     <row r="382">
@@ -10358,10 +10358,10 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>0.0191</v>
+        <v>0.0235</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0161</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="383">
@@ -10384,10 +10384,10 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.03</v>
+        <v>0.0383</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0265</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="384">
@@ -10410,10 +10410,10 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>0.0399</v>
+        <v>0.044</v>
       </c>
       <c r="H384" t="n">
-        <v>0.033</v>
+        <v>0.0354</v>
       </c>
     </row>
     <row r="385">
@@ -10436,10 +10436,10 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.0454</v>
+        <v>0.0559</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0409</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="386">
@@ -10462,10 +10462,10 @@
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0985</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0621</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="387">
@@ -10488,10 +10488,10 @@
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.0563</v>
+        <v>0.064</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0486</v>
+        <v>0.0544</v>
       </c>
     </row>
     <row r="388">
@@ -10514,10 +10514,10 @@
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.0252</v>
+        <v>0.0306</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0218</v>
+        <v>0.0255</v>
       </c>
     </row>
     <row r="389">
@@ -10540,10 +10540,10 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.2116</v>
+        <v>0.2739</v>
       </c>
       <c r="H389" t="n">
-        <v>0.1858</v>
+        <v>0.239</v>
       </c>
     </row>
     <row r="390">
@@ -10566,10 +10566,10 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.1776</v>
+        <v>0.1964</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1504</v>
+        <v>0.1692</v>
       </c>
     </row>
     <row r="391">
@@ -10592,10 +10592,10 @@
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>0.4337</v>
+        <v>0.4877</v>
       </c>
       <c r="H391" t="n">
-        <v>0.4001</v>
+        <v>0.4391</v>
       </c>
     </row>
     <row r="392">
@@ -10618,10 +10618,10 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>0.2969</v>
+        <v>0.2993</v>
       </c>
       <c r="H392" t="n">
-        <v>0.2667</v>
+        <v>0.2779</v>
       </c>
     </row>
     <row r="393">
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.0757</v>
+        <v>0.0793</v>
       </c>
       <c r="H408" t="n">
-        <v>0.067</v>
+        <v>0.07389999999999999</v>
       </c>
     </row>
     <row r="409">
@@ -11060,10 +11060,10 @@
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
-        <v>0.0319</v>
+        <v>0.0353</v>
       </c>
       <c r="H409" t="n">
-        <v>0.0256</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="410">
@@ -11086,10 +11086,10 @@
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>0.0307</v>
+        <v>0.0327</v>
       </c>
       <c r="H410" t="n">
-        <v>0.0258</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="411">
@@ -11112,10 +11112,10 @@
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
-        <v>0.032</v>
+        <v>0.0368</v>
       </c>
       <c r="H411" t="n">
-        <v>0.0296</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="412">
@@ -11138,10 +11138,10 @@
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>0.0646</v>
+        <v>0.0733</v>
       </c>
       <c r="H412" t="n">
-        <v>0.0545</v>
+        <v>0.0611</v>
       </c>
     </row>
     <row r="413">
@@ -11164,10 +11164,10 @@
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>0.1022</v>
+        <v>0.0892</v>
       </c>
       <c r="H413" t="n">
-        <v>0.0833</v>
+        <v>0.0747</v>
       </c>
     </row>
     <row r="414">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.1464</v>
+        <v>0.1482</v>
       </c>
       <c r="H414" t="n">
-        <v>0.1192</v>
+        <v>0.1253</v>
       </c>
     </row>
     <row r="415">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.2225</v>
+        <v>0.2158</v>
       </c>
       <c r="H415" t="n">
-        <v>0.1959</v>
+        <v>0.1953</v>
       </c>
     </row>
     <row r="416">
@@ -11242,10 +11242,10 @@
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.1293</v>
+        <v>0.1251</v>
       </c>
       <c r="H416" t="n">
-        <v>0.1084</v>
+        <v>0.1067</v>
       </c>
     </row>
     <row r="417">
@@ -11268,10 +11268,10 @@
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.0377</v>
+        <v>0.0518</v>
       </c>
       <c r="H417" t="n">
-        <v>0.031</v>
+        <v>0.0434</v>
       </c>
     </row>
     <row r="418">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.4089</v>
+        <v>0.4499</v>
       </c>
       <c r="H418" t="n">
-        <v>0.3747</v>
+        <v>0.4115</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.3673</v>
+        <v>0.3496</v>
       </c>
       <c r="H419" t="n">
-        <v>0.3415</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="420">
@@ -11346,10 +11346,10 @@
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>0.6804</v>
+        <v>0.7107</v>
       </c>
       <c r="H420" t="n">
-        <v>0.6331</v>
+        <v>0.6585</v>
       </c>
     </row>
     <row r="421">
@@ -11372,10 +11372,10 @@
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
-        <v>0.7333</v>
+        <v>0.7221</v>
       </c>
       <c r="H421" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7007</v>
       </c>
     </row>
     <row r="422">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.4496</v>
+        <v>0.4125</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3903</v>
+        <v>0.3548</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.4621</v>
+        <v>0.4437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4084</v>
+        <v>0.3902</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.4897</v>
+        <v>0.4313</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4423</v>
+        <v>0.3917</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.679</v>
+        <v>0.6355</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.5836</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.706</v>
+        <v>0.7075</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6842</v>
+        <v>0.6714</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.7645</v>
+        <v>0.7294</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7363</v>
+        <v>0.6921</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.8312</v>
+        <v>0.8573</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8091</v>
+        <v>0.829</v>
       </c>
     </row>
     <row r="9">
@@ -660,10 +660,10 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.7669</v>
+        <v>0.7518</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7364000000000001</v>
+        <v>0.7114</v>
       </c>
     </row>
     <row r="10">
@@ -686,10 +686,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.5686</v>
+        <v>0.5329</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5322</v>
+        <v>0.4872</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9382</v>
+        <v>0.9414</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9305</v>
+        <v>0.9288999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.8966</v>
+        <v>0.9025</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8881</v>
+        <v>0.8888</v>
       </c>
     </row>
     <row r="13">
@@ -764,10 +764,10 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.9681</v>
+        <v>0.971</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9608</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="14">
@@ -790,10 +790,10 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.9517</v>
+        <v>0.9588</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9446</v>
+        <v>0.9484</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9261</v>
+        <v>0.9402</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9207</v>
+        <v>0.9304</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.6097</v>
+        <v>0.6452</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5504</v>
+        <v>0.5875</v>
       </c>
     </row>
     <row r="32">
@@ -1258,10 +1258,10 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5658</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5397999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1284,10 +1284,10 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.5837</v>
+        <v>0.5792</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5424</v>
+        <v>0.5381</v>
       </c>
     </row>
     <row r="34">
@@ -1310,10 +1310,10 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.7783</v>
+        <v>0.7964</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7426</v>
+        <v>0.7435</v>
       </c>
     </row>
     <row r="35">
@@ -1336,10 +1336,10 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.8419</v>
+        <v>0.8558</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8136</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.8829</v>
+        <v>0.8909</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8646</v>
+        <v>0.8686</v>
       </c>
     </row>
     <row r="37">
@@ -1388,10 +1388,10 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.9267</v>
+        <v>0.9329</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9061</v>
+        <v>0.9094</v>
       </c>
     </row>
     <row r="38">
@@ -1414,10 +1414,10 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.8764</v>
+        <v>0.8878</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8521</v>
       </c>
     </row>
     <row r="39">
@@ -1440,10 +1440,10 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.6659</v>
+        <v>0.6886</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6272</v>
+        <v>0.6506</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.9737</v>
+        <v>0.978</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9688</v>
+        <v>0.9709</v>
       </c>
     </row>
     <row r="41">
@@ -1492,10 +1492,10 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.9634</v>
+        <v>0.9638</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9547</v>
+        <v>0.9539</v>
       </c>
     </row>
     <row r="42">
@@ -1518,10 +1518,10 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.9798</v>
+        <v>0.9869</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9771</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="43">
@@ -1544,10 +1544,10 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>0.9812</v>
+        <v>0.9855</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9777</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="44">
@@ -1570,10 +1570,10 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.9716</v>
+        <v>0.9761</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9647</v>
+        <v>0.9692</v>
       </c>
     </row>
     <row r="45">
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.5916</v>
+        <v>0.6098</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5379</v>
+        <v>0.5563</v>
       </c>
     </row>
     <row r="61">
@@ -2012,10 +2012,10 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>0.438</v>
+        <v>0.4602</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4148</v>
+        <v>0.4342</v>
       </c>
     </row>
     <row r="62">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.5258</v>
+        <v>0.5189</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4917</v>
+        <v>0.4773</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.7573</v>
+        <v>0.7756</v>
       </c>
       <c r="H63" t="n">
-        <v>0.7242</v>
+        <v>0.7228</v>
       </c>
     </row>
     <row r="64">
@@ -2090,10 +2090,10 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0.8151</v>
+        <v>0.8365</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7845</v>
+        <v>0.8038</v>
       </c>
     </row>
     <row r="65">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.8521</v>
+        <v>0.8525</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8315</v>
+        <v>0.8293</v>
       </c>
     </row>
     <row r="66">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.9175</v>
+        <v>0.9164</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8918</v>
+        <v>0.8912</v>
       </c>
     </row>
     <row r="67">
@@ -2168,10 +2168,10 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.8562</v>
+        <v>0.8607</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8237</v>
+        <v>0.8201000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2194,10 +2194,10 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.6284</v>
+        <v>0.6822</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5955</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.9674</v>
+        <v>0.9761</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9633</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9574</v>
+        <v>0.957</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9453</v>
       </c>
     </row>
     <row r="71">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.9742</v>
+        <v>0.9841</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9715</v>
+        <v>0.9814000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -2298,10 +2298,10 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>0.9822</v>
+        <v>0.9847</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9792</v>
+        <v>0.9802</v>
       </c>
     </row>
     <row r="73">
@@ -2324,10 +2324,10 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.9725</v>
+        <v>0.9741</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9673</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="74">
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.5577</v>
+        <v>0.6083</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5103</v>
+        <v>0.5687</v>
       </c>
     </row>
     <row r="90">
@@ -2766,10 +2766,10 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.4576</v>
+        <v>0.4619</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4163</v>
+        <v>0.4208</v>
       </c>
     </row>
     <row r="91">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.5083</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4742</v>
+        <v>0.4811</v>
       </c>
     </row>
     <row r="92">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.7479</v>
+        <v>0.8015</v>
       </c>
       <c r="H92" t="n">
-        <v>0.706</v>
+        <v>0.7494</v>
       </c>
     </row>
     <row r="93">
@@ -2844,10 +2844,10 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0.7822</v>
+        <v>0.8093</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7529</v>
+        <v>0.775</v>
       </c>
     </row>
     <row r="94">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.8521</v>
+        <v>0.869</v>
       </c>
       <c r="H94" t="n">
-        <v>0.833</v>
+        <v>0.8445</v>
       </c>
     </row>
     <row r="95">
@@ -2896,10 +2896,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.898</v>
+        <v>0.9176</v>
       </c>
       <c r="H95" t="n">
-        <v>0.8712</v>
+        <v>0.8953</v>
       </c>
     </row>
     <row r="96">
@@ -2922,10 +2922,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.8698</v>
       </c>
       <c r="H96" t="n">
-        <v>0.8096</v>
+        <v>0.8347</v>
       </c>
     </row>
     <row r="97">
@@ -2948,10 +2948,10 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.6281</v>
+        <v>0.6631</v>
       </c>
       <c r="H97" t="n">
-        <v>0.5711000000000001</v>
+        <v>0.6109</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.9583</v>
+        <v>0.9759</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9519</v>
+        <v>0.9699</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9506</v>
+        <v>0.953</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9421</v>
+        <v>0.944</v>
       </c>
     </row>
     <row r="100">
@@ -3026,10 +3026,10 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>0.9694</v>
+        <v>0.9794</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9643</v>
+        <v>0.9755</v>
       </c>
     </row>
     <row r="101">
@@ -3052,10 +3052,10 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0.9796</v>
+        <v>0.9857</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9765</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="102">
@@ -3078,10 +3078,10 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>0.9661</v>
+        <v>0.9745</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9698</v>
       </c>
     </row>
     <row r="103">
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.3564</v>
+        <v>0.4164</v>
       </c>
       <c r="H118" t="n">
-        <v>0.321</v>
+        <v>0.3645</v>
       </c>
     </row>
     <row r="119">
@@ -3520,10 +3520,10 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.2574</v>
+        <v>0.2565</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2217</v>
+        <v>0.2036</v>
       </c>
     </row>
     <row r="120">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.2758</v>
+        <v>0.2772</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2427</v>
+        <v>0.2244</v>
       </c>
     </row>
     <row r="121">
@@ -3572,10 +3572,10 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.294</v>
+        <v>0.2506</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2521</v>
+        <v>0.1985</v>
       </c>
     </row>
     <row r="122">
@@ -3598,10 +3598,10 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0.5684</v>
+        <v>0.576</v>
       </c>
       <c r="H122" t="n">
-        <v>0.5369</v>
+        <v>0.5394</v>
       </c>
     </row>
     <row r="123">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="H123" t="n">
-        <v>0.6119</v>
+        <v>0.6428</v>
       </c>
     </row>
     <row r="124">
@@ -3650,10 +3650,10 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0.7302</v>
+        <v>0.7582</v>
       </c>
       <c r="H124" t="n">
-        <v>0.6857</v>
+        <v>0.7036</v>
       </c>
     </row>
     <row r="125">
@@ -3676,10 +3676,10 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>0.6532</v>
+        <v>0.6292</v>
       </c>
       <c r="H125" t="n">
-        <v>0.6099</v>
+        <v>0.5849</v>
       </c>
     </row>
     <row r="126">
@@ -3702,10 +3702,10 @@
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>0.3989</v>
+        <v>0.4316</v>
       </c>
       <c r="H126" t="n">
-        <v>0.3672</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="127">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.9035</v>
+        <v>0.923</v>
       </c>
       <c r="H127" t="n">
-        <v>0.8793</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.8736</v>
+        <v>0.8963</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8528</v>
+        <v>0.8635</v>
       </c>
     </row>
     <row r="129">
@@ -3780,10 +3780,10 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.9688</v>
+        <v>0.9728</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9586</v>
+        <v>0.9631</v>
       </c>
     </row>
     <row r="130">
@@ -3806,10 +3806,10 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.9676</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9617</v>
+        <v>0.9637</v>
       </c>
     </row>
     <row r="131">
@@ -3832,10 +3832,10 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.9389</v>
+        <v>0.9469</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9267</v>
+        <v>0.9303</v>
       </c>
     </row>
     <row r="132">
@@ -4248,10 +4248,10 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.3158</v>
+        <v>0.3286</v>
       </c>
       <c r="H147" t="n">
-        <v>0.294</v>
+        <v>0.2925</v>
       </c>
     </row>
     <row r="148">
@@ -4274,10 +4274,10 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>0.1864</v>
+        <v>0.1769</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1581</v>
+        <v>0.1442</v>
       </c>
     </row>
     <row r="149">
@@ -4300,10 +4300,10 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>0.2155</v>
+        <v>0.1962</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1849</v>
+        <v>0.1635</v>
       </c>
     </row>
     <row r="150">
@@ -4326,10 +4326,10 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>0.2471</v>
+        <v>0.225</v>
       </c>
       <c r="H150" t="n">
-        <v>0.2178</v>
+        <v>0.1907</v>
       </c>
     </row>
     <row r="151">
@@ -4352,10 +4352,10 @@
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>0.4631</v>
+        <v>0.4606</v>
       </c>
       <c r="H151" t="n">
-        <v>0.4316</v>
+        <v>0.424</v>
       </c>
     </row>
     <row r="152">
@@ -4378,10 +4378,10 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0.5839</v>
+        <v>0.5583</v>
       </c>
       <c r="H152" t="n">
-        <v>0.5582</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="153">
@@ -4404,10 +4404,10 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.7036</v>
+        <v>0.7144</v>
       </c>
       <c r="H153" t="n">
-        <v>0.6636</v>
+        <v>0.6716</v>
       </c>
     </row>
     <row r="154">
@@ -4430,10 +4430,10 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.5927</v>
+        <v>0.5848</v>
       </c>
       <c r="H154" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
     </row>
     <row r="155">
@@ -4456,10 +4456,10 @@
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.3493</v>
+        <v>0.3464</v>
       </c>
       <c r="H155" t="n">
-        <v>0.3168</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="156">
@@ -4482,10 +4482,10 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.8903</v>
+        <v>0.9085</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8677</v>
+        <v>0.8826000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -4508,10 +4508,10 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>0.8414</v>
+        <v>0.8492</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8147</v>
+        <v>0.8177</v>
       </c>
     </row>
     <row r="158">
@@ -4534,10 +4534,10 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.9607</v>
+        <v>0.9647</v>
       </c>
       <c r="H158" t="n">
-        <v>0.9526</v>
+        <v>0.9564</v>
       </c>
     </row>
     <row r="159">
@@ -4560,10 +4560,10 @@
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>0.9646</v>
+        <v>0.9636</v>
       </c>
       <c r="H159" t="n">
-        <v>0.956</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -4586,10 +4586,10 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>0.9253</v>
+        <v>0.9282</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9129</v>
       </c>
     </row>
     <row r="161">
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.2637</v>
+        <v>0.3079</v>
       </c>
       <c r="H176" t="n">
-        <v>0.2355</v>
+        <v>0.2706</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.1354</v>
+        <v>0.1314</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1171</v>
+        <v>0.1091</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.1685</v>
+        <v>0.1707</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1479</v>
+        <v>0.1475</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.167</v>
+        <v>0.1555</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1479</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="180">
@@ -5106,10 +5106,10 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.3881</v>
+        <v>0.3572</v>
       </c>
       <c r="H180" t="n">
-        <v>0.3604</v>
+        <v>0.335</v>
       </c>
     </row>
     <row r="181">
@@ -5132,10 +5132,10 @@
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>0.4418</v>
+        <v>0.466</v>
       </c>
       <c r="H181" t="n">
-        <v>0.4161</v>
+        <v>0.4417</v>
       </c>
     </row>
     <row r="182">
@@ -5158,10 +5158,10 @@
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.6123</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="H182" t="n">
-        <v>0.5784</v>
+        <v>0.6183999999999999</v>
       </c>
     </row>
     <row r="183">
@@ -5184,10 +5184,10 @@
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>0.5315</v>
+        <v>0.5425</v>
       </c>
       <c r="H183" t="n">
-        <v>0.5</v>
+        <v>0.4978</v>
       </c>
     </row>
     <row r="184">
@@ -5210,10 +5210,10 @@
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>0.2886</v>
+        <v>0.3104</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2519</v>
+        <v>0.2653</v>
       </c>
     </row>
     <row r="185">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.846</v>
+        <v>0.8563</v>
       </c>
       <c r="H185" t="n">
-        <v>0.8141</v>
+        <v>0.8317</v>
       </c>
     </row>
     <row r="186">
@@ -5262,10 +5262,10 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>0.7844</v>
+        <v>0.8026</v>
       </c>
       <c r="H186" t="n">
-        <v>0.7549</v>
+        <v>0.7614</v>
       </c>
     </row>
     <row r="187">
@@ -5288,10 +5288,10 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.9369</v>
+        <v>0.9475</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9385</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.9506</v>
+        <v>0.9544</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9461000000000001</v>
       </c>
     </row>
     <row r="189">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.8747</v>
+        <v>0.8888</v>
       </c>
       <c r="H189" t="n">
-        <v>0.8518</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="190">
@@ -5756,10 +5756,10 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.1909</v>
+        <v>0.171</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1688</v>
+        <v>0.1427</v>
       </c>
     </row>
     <row r="206">
@@ -5782,10 +5782,10 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.0939</v>
+        <v>0.0906</v>
       </c>
       <c r="H206" t="n">
-        <v>0.0733</v>
+        <v>0.06710000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.1082</v>
+        <v>0.1088</v>
       </c>
       <c r="H207" t="n">
-        <v>0.0825</v>
+        <v>0.08359999999999999</v>
       </c>
     </row>
     <row r="208">
@@ -5834,10 +5834,10 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.1288</v>
+        <v>0.1047</v>
       </c>
       <c r="H208" t="n">
-        <v>0.102</v>
+        <v>0.0824</v>
       </c>
     </row>
     <row r="209">
@@ -5860,10 +5860,10 @@
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>0.3143</v>
+        <v>0.2964</v>
       </c>
       <c r="H209" t="n">
-        <v>0.2698</v>
+        <v>0.2418</v>
       </c>
     </row>
     <row r="210">
@@ -5886,10 +5886,10 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.3364</v>
+        <v>0.3284</v>
       </c>
       <c r="H210" t="n">
-        <v>0.2964</v>
+        <v>0.2856</v>
       </c>
     </row>
     <row r="211">
@@ -5912,10 +5912,10 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.4216</v>
+        <v>0.3816</v>
       </c>
       <c r="H211" t="n">
-        <v>0.3877</v>
+        <v>0.3332</v>
       </c>
     </row>
     <row r="212">
@@ -5938,10 +5938,10 @@
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.3961</v>
+        <v>0.3802</v>
       </c>
       <c r="H212" t="n">
-        <v>0.3698</v>
+        <v>0.3461</v>
       </c>
     </row>
     <row r="213">
@@ -5967,7 +5967,7 @@
         <v>0.2092</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1735</v>
+        <v>0.1713</v>
       </c>
     </row>
     <row r="214">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.7606000000000001</v>
+        <v>0.8008</v>
       </c>
       <c r="H214" t="n">
-        <v>0.731</v>
+        <v>0.7597</v>
       </c>
     </row>
     <row r="215">
@@ -6016,10 +6016,10 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.679</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H215" t="n">
-        <v>0.6566</v>
+        <v>0.6581</v>
       </c>
     </row>
     <row r="216">
@@ -6042,10 +6042,10 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.9134</v>
+        <v>0.917</v>
       </c>
       <c r="H216" t="n">
-        <v>0.8968</v>
+        <v>0.9025</v>
       </c>
     </row>
     <row r="217">
@@ -6068,10 +6068,10 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.9124</v>
+        <v>0.9163</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9015</v>
+        <v>0.8974</v>
       </c>
     </row>
     <row r="218">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.8047</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="H218" t="n">
-        <v>0.7842</v>
+        <v>0.7836</v>
       </c>
     </row>
     <row r="219">
@@ -6510,10 +6510,10 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.2636</v>
+        <v>0.2886</v>
       </c>
       <c r="H234" t="n">
-        <v>0.2331</v>
+        <v>0.2482</v>
       </c>
     </row>
     <row r="235">
@@ -6536,10 +6536,10 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.1527</v>
+        <v>0.1479</v>
       </c>
       <c r="H235" t="n">
-        <v>0.1236</v>
+        <v>0.1122</v>
       </c>
     </row>
     <row r="236">
@@ -6562,10 +6562,10 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.1763</v>
+        <v>0.1799</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1438</v>
+        <v>0.1393</v>
       </c>
     </row>
     <row r="237">
@@ -6588,10 +6588,10 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.1904</v>
+        <v>0.1653</v>
       </c>
       <c r="H237" t="n">
-        <v>0.1507</v>
+        <v>0.1302</v>
       </c>
     </row>
     <row r="238">
@@ -6614,10 +6614,10 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>0.3901</v>
+        <v>0.4151</v>
       </c>
       <c r="H238" t="n">
-        <v>0.3468</v>
+        <v>0.3708</v>
       </c>
     </row>
     <row r="239">
@@ -6640,10 +6640,10 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.444</v>
+        <v>0.452</v>
       </c>
       <c r="H239" t="n">
-        <v>0.4073</v>
+        <v>0.4152</v>
       </c>
     </row>
     <row r="240">
@@ -6666,10 +6666,10 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>0.5</v>
+        <v>0.5022</v>
       </c>
       <c r="H240" t="n">
-        <v>0.4685</v>
+        <v>0.4575</v>
       </c>
     </row>
     <row r="241">
@@ -6692,10 +6692,10 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.6302</v>
+        <v>0.6539</v>
       </c>
       <c r="H241" t="n">
-        <v>0.6039</v>
+        <v>0.6198</v>
       </c>
     </row>
     <row r="242">
@@ -6718,10 +6718,10 @@
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.3263</v>
+        <v>0.2837</v>
       </c>
       <c r="H242" t="n">
-        <v>0.2808</v>
+        <v>0.2437</v>
       </c>
     </row>
     <row r="243">
@@ -6744,10 +6744,10 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.8762</v>
+        <v>0.8871</v>
       </c>
       <c r="H243" t="n">
-        <v>0.8418</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="244">
@@ -6770,10 +6770,10 @@
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>0.7799</v>
+        <v>0.8173</v>
       </c>
       <c r="H244" t="n">
-        <v>0.7569</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="245">
@@ -6796,10 +6796,10 @@
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9497</v>
       </c>
       <c r="H245" t="n">
-        <v>0.9359</v>
+        <v>0.9367</v>
       </c>
     </row>
     <row r="246">
@@ -6822,10 +6822,10 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.9456</v>
+        <v>0.9463</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9337</v>
       </c>
     </row>
     <row r="247">
@@ -6848,10 +6848,10 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.8933</v>
+        <v>0.8939</v>
       </c>
       <c r="H247" t="n">
-        <v>0.8749</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="248">
@@ -7264,10 +7264,10 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.4678</v>
+        <v>0.5128</v>
       </c>
       <c r="H263" t="n">
-        <v>0.4314</v>
+        <v>0.4671</v>
       </c>
     </row>
     <row r="264">
@@ -7290,10 +7290,10 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.3728</v>
+        <v>0.3494</v>
       </c>
       <c r="H264" t="n">
-        <v>0.3341</v>
+        <v>0.3114</v>
       </c>
     </row>
     <row r="265">
@@ -7316,10 +7316,10 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.4045</v>
+        <v>0.354</v>
       </c>
       <c r="H265" t="n">
-        <v>0.3716</v>
+        <v>0.3178</v>
       </c>
     </row>
     <row r="266">
@@ -7342,10 +7342,10 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.4289</v>
+        <v>0.3891</v>
       </c>
       <c r="H266" t="n">
-        <v>0.3719</v>
+        <v>0.3369</v>
       </c>
     </row>
     <row r="267">
@@ -7368,10 +7368,10 @@
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>0.6328</v>
+        <v>0.602</v>
       </c>
       <c r="H267" t="n">
-        <v>0.6011</v>
+        <v>0.5684</v>
       </c>
     </row>
     <row r="268">
@@ -7394,10 +7394,10 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.6832</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H268" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6536</v>
       </c>
     </row>
     <row r="269">
@@ -7420,10 +7420,10 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>0.7481</v>
+        <v>0.7347</v>
       </c>
       <c r="H269" t="n">
-        <v>0.7114</v>
+        <v>0.6896</v>
       </c>
     </row>
     <row r="270">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="n">
-        <v>0.8265</v>
+        <v>0.8287</v>
       </c>
       <c r="H270" t="n">
         <v>0.7907999999999999</v>
@@ -7472,10 +7472,10 @@
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.7192</v>
+        <v>0.7563</v>
       </c>
       <c r="H271" t="n">
-        <v>0.6737</v>
+        <v>0.7163</v>
       </c>
     </row>
     <row r="272">
@@ -7498,10 +7498,10 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9473</v>
       </c>
       <c r="H272" t="n">
-        <v>0.9399</v>
+        <v>0.9322</v>
       </c>
     </row>
     <row r="273">
@@ -7524,10 +7524,10 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.9281</v>
+        <v>0.9224</v>
       </c>
       <c r="H273" t="n">
-        <v>0.914</v>
+        <v>0.8997000000000001</v>
       </c>
     </row>
     <row r="274">
@@ -7550,10 +7550,10 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.9768</v>
+        <v>0.9811</v>
       </c>
       <c r="H274" t="n">
-        <v>0.9728</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="275">
@@ -7576,10 +7576,10 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.9745</v>
+        <v>0.9755</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9694</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="276">
@@ -7602,10 +7602,10 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.9566</v>
+        <v>0.9574</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9482</v>
+        <v>0.9456</v>
       </c>
     </row>
     <row r="277">
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.0711</v>
       </c>
       <c r="H292" t="n">
-        <v>0.0618</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.0312</v>
+        <v>0.0291</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0263</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.0367</v>
+        <v>0.0307</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0326</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.0481</v>
+        <v>0.0301</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0417</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="296">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.1207</v>
+        <v>0.104</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0965</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="297">
@@ -8148,10 +8148,10 @@
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.1323</v>
+        <v>0.1174</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1097</v>
+        <v>0.0915</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.1859</v>
+        <v>0.1683</v>
       </c>
       <c r="H298" t="n">
-        <v>0.154</v>
+        <v>0.1437</v>
       </c>
     </row>
     <row r="299">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.269</v>
+        <v>0.2403</v>
       </c>
       <c r="H299" t="n">
-        <v>0.2394</v>
+        <v>0.1992</v>
       </c>
     </row>
     <row r="300">
@@ -8226,10 +8226,10 @@
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.1582</v>
+        <v>0.148</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1238</v>
+        <v>0.1129</v>
       </c>
     </row>
     <row r="301">
@@ -8252,10 +8252,10 @@
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.0601</v>
+        <v>0.0678</v>
       </c>
       <c r="H301" t="n">
-        <v>0.0519</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.465</v>
+        <v>0.4174</v>
       </c>
       <c r="H302" t="n">
-        <v>0.4208</v>
+        <v>0.3817</v>
       </c>
     </row>
     <row r="303">
@@ -8304,10 +8304,10 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.7562</v>
+        <v>0.7749</v>
       </c>
       <c r="H303" t="n">
-        <v>0.7163</v>
+        <v>0.7369</v>
       </c>
     </row>
     <row r="304">
@@ -8330,10 +8330,10 @@
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.761</v>
+        <v>0.7887</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7261</v>
+        <v>0.7538</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.5885</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H305" t="n">
-        <v>0.5501</v>
+        <v>0.5213</v>
       </c>
     </row>
     <row r="306">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.1119</v>
+        <v>0.1112</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1034</v>
+        <v>0.0975</v>
       </c>
     </row>
     <row r="322">
@@ -8798,10 +8798,10 @@
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="n">
-        <v>0.0453</v>
+        <v>0.0461</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0366</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="323">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.0529</v>
+        <v>0.0547</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0426</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.0579</v>
+        <v>0.056</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0494</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.1472</v>
+        <v>0.1365</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1264</v>
+        <v>0.1037</v>
       </c>
     </row>
     <row r="326">
@@ -8902,10 +8902,10 @@
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="n">
-        <v>0.1853</v>
+        <v>0.1823</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1586</v>
+        <v>0.1508</v>
       </c>
     </row>
     <row r="327">
@@ -8928,10 +8928,10 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>0.2451</v>
+        <v>0.2386</v>
       </c>
       <c r="H327" t="n">
-        <v>0.2156</v>
+        <v>0.1974</v>
       </c>
     </row>
     <row r="328">
@@ -8954,10 +8954,10 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.3434</v>
+        <v>0.3419</v>
       </c>
       <c r="H328" t="n">
-        <v>0.321</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="329">
@@ -8980,10 +8980,10 @@
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>0.2431</v>
+        <v>0.2188</v>
       </c>
       <c r="H329" t="n">
-        <v>0.2201</v>
+        <v>0.1827</v>
       </c>
     </row>
     <row r="330">
@@ -9006,10 +9006,10 @@
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1003</v>
       </c>
       <c r="H330" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.5792</v>
+        <v>0.6183</v>
       </c>
       <c r="H331" t="n">
-        <v>0.535</v>
+        <v>0.5826</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="H332" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.8116</v>
       </c>
     </row>
     <row r="333">
@@ -9084,10 +9084,10 @@
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.8308</v>
+        <v>0.8596</v>
       </c>
       <c r="H333" t="n">
-        <v>0.8036</v>
+        <v>0.8287</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.677</v>
+        <v>0.6899</v>
       </c>
       <c r="H334" t="n">
-        <v>0.6504</v>
+        <v>0.6542</v>
       </c>
     </row>
     <row r="335">
@@ -9526,10 +9526,10 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>0.0392</v>
+        <v>0.0373</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0319</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="351">
@@ -9552,10 +9552,10 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.0229</v>
+        <v>0.0159</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0202</v>
+        <v>0.0131</v>
       </c>
     </row>
     <row r="352">
@@ -9578,10 +9578,10 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.0285</v>
+        <v>0.0186</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0258</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="353">
@@ -9604,10 +9604,10 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>0.0357</v>
+        <v>0.0245</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0306</v>
+        <v>0.0206</v>
       </c>
     </row>
     <row r="354">
@@ -9630,10 +9630,10 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.0414</v>
+        <v>0.0369</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0312</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="355">
@@ -9656,10 +9656,10 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.0474</v>
+        <v>0.0436</v>
       </c>
       <c r="H355" t="n">
-        <v>0.0393</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="356">
@@ -9682,10 +9682,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.0731</v>
+        <v>0.0615</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0631</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="357">
@@ -9708,10 +9708,10 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.1032</v>
+        <v>0.0975</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0866</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="358">
@@ -9734,10 +9734,10 @@
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>0.0641</v>
+        <v>0.0633</v>
       </c>
       <c r="H358" t="n">
-        <v>0.0519</v>
+        <v>0.0503</v>
       </c>
     </row>
     <row r="359">
@@ -9760,10 +9760,10 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.0272</v>
+        <v>0.0235</v>
       </c>
       <c r="H359" t="n">
-        <v>0.0232</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="360">
@@ -9786,10 +9786,10 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.2837</v>
+        <v>0.2631</v>
       </c>
       <c r="H360" t="n">
-        <v>0.2438</v>
+        <v>0.2251</v>
       </c>
     </row>
     <row r="361">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.2293</v>
+        <v>0.1884</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1789</v>
+        <v>0.1578</v>
       </c>
     </row>
     <row r="362">
@@ -9838,10 +9838,10 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>0.5609</v>
+        <v>0.5571</v>
       </c>
       <c r="H362" t="n">
-        <v>0.5123</v>
+        <v>0.5153</v>
       </c>
     </row>
     <row r="363">
@@ -9864,10 +9864,10 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>0.3415</v>
+        <v>0.2912</v>
       </c>
       <c r="H363" t="n">
-        <v>0.2893</v>
+        <v>0.2513</v>
       </c>
     </row>
     <row r="364">
@@ -10280,10 +10280,10 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.0554</v>
+        <v>0.0516</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0483</v>
+        <v>0.0412</v>
       </c>
     </row>
     <row r="380">
@@ -10306,10 +10306,10 @@
       </c>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
-        <v>0.0223</v>
+        <v>0.0198</v>
       </c>
       <c r="H380" t="n">
-        <v>0.0188</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="381">
@@ -10332,10 +10332,10 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.0208</v>
+        <v>0.0198</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0178</v>
+        <v>0.0153</v>
       </c>
     </row>
     <row r="382">
@@ -10358,10 +10358,10 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>0.0235</v>
+        <v>0.018</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0204</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="383">
@@ -10384,10 +10384,10 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.0383</v>
+        <v>0.0363</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0324</v>
+        <v>0.0277</v>
       </c>
     </row>
     <row r="384">
@@ -10410,10 +10410,10 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>0.044</v>
+        <v>0.0469</v>
       </c>
       <c r="H384" t="n">
-        <v>0.0354</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="385">
@@ -10436,10 +10436,10 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.0559</v>
+        <v>0.0539</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0494</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="386">
@@ -10462,10 +10462,10 @@
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.0985</v>
+        <v>0.1026</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0876</v>
+        <v>0.0837</v>
       </c>
     </row>
     <row r="387">
@@ -10488,10 +10488,10 @@
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.064</v>
+        <v>0.0663</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0544</v>
+        <v>0.0537</v>
       </c>
     </row>
     <row r="388">
@@ -10514,10 +10514,10 @@
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.0306</v>
+        <v>0.0322</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0255</v>
+        <v>0.0245</v>
       </c>
     </row>
     <row r="389">
@@ -10540,10 +10540,10 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.2739</v>
+        <v>0.2462</v>
       </c>
       <c r="H389" t="n">
-        <v>0.239</v>
+        <v>0.2113</v>
       </c>
     </row>
     <row r="390">
@@ -10566,10 +10566,10 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.1964</v>
+        <v>0.1713</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1692</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="391">
@@ -10592,10 +10592,10 @@
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>0.4877</v>
+        <v>0.4847</v>
       </c>
       <c r="H391" t="n">
-        <v>0.4391</v>
+        <v>0.4429</v>
       </c>
     </row>
     <row r="392">
@@ -10618,10 +10618,10 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>0.2993</v>
+        <v>0.2976</v>
       </c>
       <c r="H392" t="n">
-        <v>0.2779</v>
+        <v>0.2664</v>
       </c>
     </row>
     <row r="393">
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.0793</v>
+        <v>0.0696</v>
       </c>
       <c r="H408" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="409">
@@ -11060,10 +11060,10 @@
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
-        <v>0.0353</v>
+        <v>0.0308</v>
       </c>
       <c r="H409" t="n">
-        <v>0.0284</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="410">
@@ -11086,10 +11086,10 @@
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>0.0327</v>
+        <v>0.033</v>
       </c>
       <c r="H410" t="n">
-        <v>0.0275</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="411">
@@ -11112,10 +11112,10 @@
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
-        <v>0.0368</v>
+        <v>0.0302</v>
       </c>
       <c r="H411" t="n">
-        <v>0.0339</v>
+        <v>0.0255</v>
       </c>
     </row>
     <row r="412">
@@ -11138,10 +11138,10 @@
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>0.0733</v>
+        <v>0.0697</v>
       </c>
       <c r="H412" t="n">
-        <v>0.0611</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="413">
@@ -11164,10 +11164,10 @@
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>0.0892</v>
+        <v>0.0871</v>
       </c>
       <c r="H413" t="n">
-        <v>0.0747</v>
+        <v>0.0718</v>
       </c>
     </row>
     <row r="414">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.1482</v>
+        <v>0.135</v>
       </c>
       <c r="H414" t="n">
-        <v>0.1253</v>
+        <v>0.1112</v>
       </c>
     </row>
     <row r="415">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.2158</v>
+        <v>0.2164</v>
       </c>
       <c r="H415" t="n">
-        <v>0.1953</v>
+        <v>0.1809</v>
       </c>
     </row>
     <row r="416">
@@ -11242,10 +11242,10 @@
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.1251</v>
+        <v>0.131</v>
       </c>
       <c r="H416" t="n">
-        <v>0.1067</v>
+        <v>0.1061</v>
       </c>
     </row>
     <row r="417">
@@ -11268,10 +11268,10 @@
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.0518</v>
+        <v>0.0544</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0434</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="418">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.4499</v>
+        <v>0.4787</v>
       </c>
       <c r="H418" t="n">
-        <v>0.4115</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.3496</v>
+        <v>0.3458</v>
       </c>
       <c r="H419" t="n">
-        <v>0.323</v>
+        <v>0.3101</v>
       </c>
     </row>
     <row r="420">
@@ -11346,10 +11346,10 @@
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>0.7107</v>
+        <v>0.7487</v>
       </c>
       <c r="H420" t="n">
-        <v>0.6585</v>
+        <v>0.7088</v>
       </c>
     </row>
     <row r="421">
@@ -11372,10 +11372,10 @@
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
-        <v>0.7221</v>
+        <v>0.7336</v>
       </c>
       <c r="H421" t="n">
-        <v>0.7007</v>
+        <v>0.7024</v>
       </c>
     </row>
     <row r="422">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.42</v>
+        <v>0.4085</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3616</v>
+        <v>0.3506</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.4352</v>
+        <v>0.4387</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3884</v>
+        <v>0.3921</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.4389</v>
+        <v>0.4217</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4017</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.6061</v>
+        <v>0.6259</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5496</v>
+        <v>0.5822000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.7275</v>
+        <v>0.7482</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6958</v>
+        <v>0.7115</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.6994</v>
+        <v>0.6859</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6633</v>
+        <v>0.6447000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.5395</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4951</v>
+        <v>0.5205</v>
       </c>
     </row>
     <row r="9">
@@ -660,10 +660,10 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.8295</v>
+        <v>0.8304</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7964</v>
+        <v>0.7974</v>
       </c>
     </row>
     <row r="10">
@@ -686,10 +686,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.7758</v>
+        <v>0.7762</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7309</v>
+        <v>0.7343</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9407</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9278</v>
+        <v>0.9436</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.9019</v>
+        <v>0.9043</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8871</v>
+        <v>0.8895</v>
       </c>
     </row>
     <row r="13">
@@ -764,10 +764,10 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.9421</v>
+        <v>0.9315</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9335</v>
+        <v>0.9192</v>
       </c>
     </row>
     <row r="14">
@@ -790,10 +790,10 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.9688</v>
+        <v>0.9701</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9603</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9669</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.958</v>
+        <v>0.9599</v>
       </c>
     </row>
     <row r="16">
@@ -1015,11 +1015,11 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1041,11 +1041,11 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1093,11 +1093,11 @@
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1119,11 +1119,11 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.6384</v>
+        <v>0.6494</v>
       </c>
       <c r="H31" t="n">
-        <v>0.58</v>
+        <v>0.5915</v>
       </c>
     </row>
     <row r="32">
@@ -1284,10 +1284,10 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.5749</v>
+        <v>0.5665</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.5227000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1310,10 +1310,10 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.7982</v>
+        <v>0.7992</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7471</v>
+        <v>0.7479</v>
       </c>
     </row>
     <row r="35">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.87</v>
+        <v>0.8685</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8367</v>
+        <v>0.8353</v>
       </c>
     </row>
     <row r="37">
@@ -1388,10 +1388,10 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.7143</v>
+        <v>0.7509</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6771</v>
+        <v>0.7062</v>
       </c>
     </row>
     <row r="38">
@@ -1414,10 +1414,10 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.9427</v>
+        <v>0.9409</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9218</v>
       </c>
     </row>
     <row r="39">
@@ -1440,10 +1440,10 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.8986</v>
+        <v>0.8992</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8672</v>
+        <v>0.8683</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9827</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9718</v>
+        <v>0.9775</v>
       </c>
     </row>
     <row r="41">
@@ -1518,10 +1518,10 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.9769</v>
+        <v>0.9751</v>
       </c>
       <c r="H42" t="n">
-        <v>0.97</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="43">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1795,11 +1795,11 @@
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1847,11 +1847,11 @@
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1873,11 +1873,11 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.6116</v>
+        <v>0.6079</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5648</v>
+        <v>0.5613</v>
       </c>
     </row>
     <row r="61">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.5079</v>
+        <v>0.514</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4677</v>
+        <v>0.4749</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.7451</v>
+        <v>0.7483</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6973</v>
+        <v>0.6999</v>
       </c>
     </row>
     <row r="64">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.6626</v>
+        <v>0.6838</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6227</v>
+        <v>0.6419</v>
       </c>
     </row>
     <row r="67">
@@ -2168,10 +2168,10 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.9266</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9033</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="68">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.9727</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>0.965</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9595</v>
+        <v>0.9597</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9481000000000001</v>
+        <v>0.9485</v>
       </c>
     </row>
     <row r="71">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.9726</v>
+        <v>0.9709</v>
       </c>
       <c r="H71" t="n">
-        <v>0.965</v>
+        <v>0.9629</v>
       </c>
     </row>
     <row r="72">
@@ -2523,11 +2523,11 @@
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -2549,11 +2549,11 @@
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -2601,11 +2601,11 @@
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -2627,11 +2627,11 @@
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.5983000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5611</v>
+        <v>0.5783</v>
       </c>
     </row>
     <row r="90">
@@ -2766,10 +2766,10 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.4733</v>
+        <v>0.4773</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4251</v>
+        <v>0.4335</v>
       </c>
     </row>
     <row r="91">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.5323</v>
+        <v>0.5251</v>
       </c>
       <c r="H91" t="n">
-        <v>0.4921</v>
+        <v>0.486</v>
       </c>
     </row>
     <row r="92">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.7877</v>
+        <v>0.7806</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7333</v>
+        <v>0.7287</v>
       </c>
     </row>
     <row r="93">
@@ -2844,10 +2844,10 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0.86</v>
+        <v>0.8623</v>
       </c>
       <c r="H93" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8326</v>
       </c>
     </row>
     <row r="94">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.8012</v>
+        <v>0.8188</v>
       </c>
       <c r="H94" t="n">
-        <v>0.7692</v>
+        <v>0.7826</v>
       </c>
     </row>
     <row r="95">
@@ -2896,10 +2896,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.6614</v>
+        <v>0.6681</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6095</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.9149</v>
+        <v>0.9153</v>
       </c>
       <c r="H96" t="n">
         <v>0.8929</v>
@@ -2948,10 +2948,10 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.8883</v>
+        <v>0.8917</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8602</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9761</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9685</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9582000000000001</v>
+        <v>0.9565</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9498</v>
+        <v>0.9453</v>
       </c>
     </row>
     <row r="100">
@@ -3026,10 +3026,10 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>0.9727</v>
+        <v>0.9718</v>
       </c>
       <c r="H100" t="n">
-        <v>0.968</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="101">
@@ -3052,10 +3052,10 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>0.9794</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9755</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="102">
@@ -3078,10 +3078,10 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9863</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9816</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="103">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
@@ -3303,11 +3303,11 @@
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
@@ -3355,11 +3355,11 @@
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
@@ -3381,11 +3381,11 @@
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.4504</v>
+        <v>0.4178</v>
       </c>
       <c r="H118" t="n">
-        <v>0.3939</v>
+        <v>0.3741</v>
       </c>
     </row>
     <row r="119">
@@ -3520,10 +3520,10 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.2529</v>
+        <v>0.2521</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2018</v>
+        <v>0.2008</v>
       </c>
     </row>
     <row r="120">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.3027</v>
+        <v>0.3001</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2549</v>
+        <v>0.2517</v>
       </c>
     </row>
     <row r="121">
@@ -3572,10 +3572,10 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.2667</v>
+        <v>0.2713</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2123</v>
+        <v>0.2194</v>
       </c>
     </row>
     <row r="122">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.6166</v>
+        <v>0.5929</v>
       </c>
       <c r="H123" t="n">
-        <v>0.5748</v>
+        <v>0.5557</v>
       </c>
     </row>
     <row r="124">
@@ -3650,10 +3650,10 @@
       </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
-        <v>0.4578</v>
+        <v>0.467</v>
       </c>
       <c r="H124" t="n">
-        <v>0.4252</v>
+        <v>0.4254</v>
       </c>
     </row>
     <row r="125">
@@ -3676,10 +3676,10 @@
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="n">
-        <v>0.7716</v>
+        <v>0.7677</v>
       </c>
       <c r="H125" t="n">
-        <v>0.7278</v>
+        <v>0.7246</v>
       </c>
     </row>
     <row r="126">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.9338</v>
+        <v>0.9411</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9083</v>
+        <v>0.9191</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.9096</v>
+        <v>0.9059</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8814</v>
+        <v>0.8772</v>
       </c>
     </row>
     <row r="129">
@@ -3780,10 +3780,10 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9411</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9318</v>
+        <v>0.9263</v>
       </c>
     </row>
     <row r="130">
@@ -3806,10 +3806,10 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.9768</v>
+        <v>0.9764</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9697</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -4031,11 +4031,11 @@
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -4109,11 +4109,11 @@
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
@@ -4135,11 +4135,11 @@
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
@@ -4248,10 +4248,10 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.3042</v>
+        <v>0.2885</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2725</v>
+        <v>0.2518</v>
       </c>
     </row>
     <row r="148">
@@ -4326,10 +4326,10 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>0.1689</v>
+        <v>0.1674</v>
       </c>
       <c r="H150" t="n">
-        <v>0.14</v>
+        <v>0.1377</v>
       </c>
     </row>
     <row r="151">
@@ -4404,10 +4404,10 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.3303</v>
+        <v>0.3466</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2884</v>
+        <v>0.3001</v>
       </c>
     </row>
     <row r="154">
@@ -4430,10 +4430,10 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.6605</v>
+        <v>0.6543</v>
       </c>
       <c r="H154" t="n">
-        <v>0.606</v>
+        <v>0.6011</v>
       </c>
     </row>
     <row r="155">
@@ -4482,10 +4482,10 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.8768</v>
+        <v>0.8973</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8485</v>
+        <v>0.8725000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -4534,10 +4534,10 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.8952</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8693</v>
+        <v>0.8616</v>
       </c>
     </row>
     <row r="159">
@@ -4785,11 +4785,11 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
@@ -4811,11 +4811,11 @@
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
@@ -4863,11 +4863,11 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F171" t="inlineStr"/>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.3367</v>
+        <v>0.3553</v>
       </c>
       <c r="H176" t="n">
-        <v>0.3006</v>
+        <v>0.3141</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.1633</v>
+        <v>0.1647</v>
       </c>
       <c r="H177" t="n">
-        <v>0.13</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="178">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.2308</v>
+        <v>0.2174</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1988</v>
+        <v>0.1812</v>
       </c>
     </row>
     <row r="180">
@@ -5106,10 +5106,10 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.4252</v>
+        <v>0.4443</v>
       </c>
       <c r="H180" t="n">
-        <v>0.3834</v>
+        <v>0.4071</v>
       </c>
     </row>
     <row r="181">
@@ -5158,10 +5158,10 @@
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.3457</v>
+        <v>0.3684</v>
       </c>
       <c r="H182" t="n">
-        <v>0.3154</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="183">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.9099</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="H185" t="n">
-        <v>0.8848</v>
+        <v>0.9061</v>
       </c>
     </row>
     <row r="186">
@@ -5288,10 +5288,10 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.9111</v>
+        <v>0.9052</v>
       </c>
       <c r="H187" t="n">
-        <v>0.8915</v>
+        <v>0.8832</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.962</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9533</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="189">
@@ -5539,11 +5539,11 @@
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -5565,11 +5565,11 @@
       </c>
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F198" t="inlineStr"/>
@@ -5617,11 +5617,11 @@
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
@@ -5643,11 +5643,11 @@
       </c>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F201" t="inlineStr"/>
@@ -5756,10 +5756,10 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.5049</v>
+        <v>0.4795</v>
       </c>
       <c r="H205" t="n">
-        <v>0.4605</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="206">
@@ -5782,10 +5782,10 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.3229</v>
+        <v>0.2938</v>
       </c>
       <c r="H206" t="n">
-        <v>0.2857</v>
+        <v>0.2491</v>
       </c>
     </row>
     <row r="207">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.3773</v>
+        <v>0.3581</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3374</v>
+        <v>0.3162</v>
       </c>
     </row>
     <row r="208">
@@ -5834,10 +5834,10 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.3905</v>
+        <v>0.3735</v>
       </c>
       <c r="H208" t="n">
-        <v>0.3386</v>
+        <v>0.3319</v>
       </c>
     </row>
     <row r="209">
@@ -5860,10 +5860,10 @@
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="n">
-        <v>0.5748</v>
+        <v>0.5746</v>
       </c>
       <c r="H209" t="n">
-        <v>0.5422</v>
+        <v>0.533</v>
       </c>
     </row>
     <row r="210">
@@ -5886,10 +5886,10 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.7116</v>
+        <v>0.6999</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6697</v>
+        <v>0.6534</v>
       </c>
     </row>
     <row r="211">
@@ -5912,10 +5912,10 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.6846</v>
+        <v>0.6722</v>
       </c>
       <c r="H211" t="n">
-        <v>0.6543</v>
+        <v>0.6316000000000001</v>
       </c>
     </row>
     <row r="212">
@@ -5938,10 +5938,10 @@
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.8295</v>
+        <v>0.8307</v>
       </c>
       <c r="H212" t="n">
-        <v>0.7933</v>
+        <v>0.7976</v>
       </c>
     </row>
     <row r="213">
@@ -5964,10 +5964,10 @@
       </c>
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>0.762</v>
+        <v>0.7339</v>
       </c>
       <c r="H213" t="n">
-        <v>0.7249</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="214">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.9465</v>
+        <v>0.956</v>
       </c>
       <c r="H214" t="n">
-        <v>0.9318</v>
+        <v>0.9429</v>
       </c>
     </row>
     <row r="215">
@@ -6016,10 +6016,10 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.9211</v>
+        <v>0.9135</v>
       </c>
       <c r="H215" t="n">
-        <v>0.8996</v>
+        <v>0.8913</v>
       </c>
     </row>
     <row r="216">
@@ -6042,10 +6042,10 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.957</v>
+        <v>0.9465</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9452</v>
+        <v>0.9329</v>
       </c>
     </row>
     <row r="217">
@@ -6068,10 +6068,10 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.9802</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9751</v>
+        <v>0.9737</v>
       </c>
     </row>
     <row r="218">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.9799</v>
+        <v>0.9787</v>
       </c>
       <c r="H218" t="n">
-        <v>0.9735</v>
+        <v>0.9724</v>
       </c>
     </row>
     <row r="219">
@@ -6293,11 +6293,11 @@
       </c>
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F226" t="inlineStr"/>
@@ -6319,11 +6319,11 @@
       </c>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F227" t="inlineStr"/>
@@ -6371,11 +6371,11 @@
       </c>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F229" t="inlineStr"/>
@@ -6397,11 +6397,11 @@
       </c>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F230" t="inlineStr"/>
@@ -6510,10 +6510,10 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.2036</v>
+        <v>0.2026</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1705</v>
+        <v>0.1696</v>
       </c>
     </row>
     <row r="235">
@@ -6536,10 +6536,10 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.0761</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0573</v>
+        <v>0.0591</v>
       </c>
     </row>
     <row r="236">
@@ -6562,10 +6562,10 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="H236" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0731</v>
       </c>
     </row>
     <row r="237">
@@ -6591,7 +6591,7 @@
         <v>0.1071</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0851</v>
+        <v>0.0847</v>
       </c>
     </row>
     <row r="238">
@@ -6614,10 +6614,10 @@
       </c>
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="n">
-        <v>0.2722</v>
+        <v>0.2754</v>
       </c>
       <c r="H238" t="n">
-        <v>0.2284</v>
+        <v>0.2323</v>
       </c>
     </row>
     <row r="239">
@@ -6640,10 +6640,10 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.394</v>
+        <v>0.3989</v>
       </c>
       <c r="H239" t="n">
-        <v>0.3395</v>
+        <v>0.3457</v>
       </c>
     </row>
     <row r="240">
@@ -6692,10 +6692,10 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.2067</v>
+        <v>0.2024</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1705</v>
+        <v>0.1693</v>
       </c>
     </row>
     <row r="242">
@@ -6718,10 +6718,10 @@
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.4358</v>
+        <v>0.4385</v>
       </c>
       <c r="H242" t="n">
-        <v>0.4077</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="243">
@@ -6744,10 +6744,10 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.7899</v>
+        <v>0.8292</v>
       </c>
       <c r="H243" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="244">
@@ -6796,10 +6796,10 @@
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="n">
-        <v>0.8264</v>
+        <v>0.8143</v>
       </c>
       <c r="H245" t="n">
-        <v>0.7885</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="246">
@@ -6822,10 +6822,10 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.9156</v>
+        <v>0.9166</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9014</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="247">
@@ -7047,11 +7047,11 @@
       </c>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
@@ -7073,11 +7073,11 @@
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F256" t="inlineStr"/>
@@ -7125,11 +7125,11 @@
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
@@ -7151,11 +7151,11 @@
       </c>
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
@@ -7264,10 +7264,10 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.2691</v>
+        <v>0.2657</v>
       </c>
       <c r="H263" t="n">
-        <v>0.2242</v>
+        <v>0.2238</v>
       </c>
     </row>
     <row r="264">
@@ -7290,10 +7290,10 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.1328</v>
+        <v>0.1317</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1014</v>
+        <v>0.1008</v>
       </c>
     </row>
     <row r="265">
@@ -7342,10 +7342,10 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.1426</v>
+        <v>0.1398</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1117</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="267">
@@ -7446,10 +7446,10 @@
       </c>
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="n">
-        <v>0.2751</v>
+        <v>0.3077</v>
       </c>
       <c r="H270" t="n">
-        <v>0.238</v>
+        <v>0.2661</v>
       </c>
     </row>
     <row r="271">
@@ -7472,10 +7472,10 @@
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.5923</v>
+        <v>0.5888</v>
       </c>
       <c r="H271" t="n">
-        <v>0.5642</v>
+        <v>0.5615</v>
       </c>
     </row>
     <row r="272">
@@ -7498,10 +7498,10 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8963</v>
       </c>
       <c r="H272" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.8633</v>
       </c>
     </row>
     <row r="273">
@@ -7524,10 +7524,10 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.8024</v>
+        <v>0.7985</v>
       </c>
       <c r="H273" t="n">
-        <v>0.7663</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="274">
@@ -7550,10 +7550,10 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.8547</v>
+        <v>0.8494</v>
       </c>
       <c r="H274" t="n">
-        <v>0.8242</v>
+        <v>0.8177</v>
       </c>
     </row>
     <row r="275">
@@ -7576,10 +7576,10 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.9392</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9212</v>
+        <v>0.9228</v>
       </c>
     </row>
     <row r="276">
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F284" t="inlineStr"/>
@@ -7827,11 +7827,11 @@
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F285" t="inlineStr"/>
@@ -7879,11 +7879,11 @@
       </c>
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F287" t="inlineStr"/>
@@ -7905,11 +7905,11 @@
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F288" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.0722</v>
+        <v>0.0564</v>
       </c>
       <c r="H292" t="n">
-        <v>0.0593</v>
+        <v>0.0469</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.0282</v>
+        <v>0.0225</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0217</v>
+        <v>0.0173</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.035</v>
+        <v>0.0266</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0273</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.0315</v>
+        <v>0.0307</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0247</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="296">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.0917</v>
+        <v>0.0809</v>
       </c>
       <c r="H296" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row r="297">
@@ -8148,10 +8148,10 @@
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.1515</v>
+        <v>0.1275</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1232</v>
+        <v>0.1027</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.1152</v>
+        <v>0.0939</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0901</v>
+        <v>0.0721</v>
       </c>
     </row>
     <row r="299">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.0682</v>
+        <v>0.0571</v>
       </c>
       <c r="H299" t="n">
-        <v>0.0535</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="300">
@@ -8226,10 +8226,10 @@
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.2455</v>
+        <v>0.1995</v>
       </c>
       <c r="H300" t="n">
-        <v>0.2101</v>
+        <v>0.1708</v>
       </c>
     </row>
     <row r="301">
@@ -8252,10 +8252,10 @@
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.1628</v>
+        <v>0.1367</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1245</v>
+        <v>0.1037</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.4167</v>
+        <v>0.36</v>
       </c>
       <c r="H302" t="n">
-        <v>0.379</v>
+        <v>0.3224</v>
       </c>
     </row>
     <row r="303">
@@ -8304,10 +8304,10 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.5162</v>
+        <v>0.4378</v>
       </c>
       <c r="H303" t="n">
-        <v>0.4788</v>
+        <v>0.3928</v>
       </c>
     </row>
     <row r="304">
@@ -8330,10 +8330,10 @@
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.7592</v>
+        <v>0.6926</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6599</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.8472</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="H305" t="n">
-        <v>0.8102</v>
+        <v>0.7533</v>
       </c>
     </row>
     <row r="306">
@@ -8555,11 +8555,11 @@
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F313" t="inlineStr"/>
@@ -8581,11 +8581,11 @@
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
@@ -8633,11 +8633,11 @@
       </c>
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F316" t="inlineStr"/>
@@ -8659,11 +8659,11 @@
       </c>
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.1129</v>
+        <v>0.1105</v>
       </c>
       <c r="H321" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.09569999999999999</v>
       </c>
     </row>
     <row r="322">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.0519</v>
+        <v>0.0515</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0405</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.0502</v>
+        <v>0.0547</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0418</v>
+        <v>0.0435</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.1186</v>
+        <v>0.1228</v>
       </c>
       <c r="H325" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="326">
@@ -8954,10 +8954,10 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.1004</v>
+        <v>0.1087</v>
       </c>
       <c r="H328" t="n">
-        <v>0.0789</v>
+        <v>0.08649999999999999</v>
       </c>
     </row>
     <row r="329">
@@ -9006,10 +9006,10 @@
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.2337</v>
+        <v>0.237</v>
       </c>
       <c r="H330" t="n">
-        <v>0.1976</v>
+        <v>0.2015</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.621</v>
+        <v>0.6776</v>
       </c>
       <c r="H331" t="n">
-        <v>0.5833</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.6571</v>
+        <v>0.6437</v>
       </c>
       <c r="H332" t="n">
-        <v>0.6218</v>
+        <v>0.6105</v>
       </c>
     </row>
     <row r="333">
@@ -9084,10 +9084,10 @@
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8305</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7947</v>
+        <v>0.8012</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.8891</v>
+        <v>0.8925</v>
       </c>
       <c r="H334" t="n">
-        <v>0.8642</v>
+        <v>0.8681</v>
       </c>
     </row>
     <row r="335">
@@ -9309,11 +9309,11 @@
       </c>
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F342" t="inlineStr"/>
@@ -9335,11 +9335,11 @@
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F343" t="inlineStr"/>
@@ -9387,11 +9387,11 @@
       </c>
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F345" t="inlineStr"/>
@@ -9413,11 +9413,11 @@
       </c>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F346" t="inlineStr"/>
@@ -9526,10 +9526,10 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>0.0665</v>
+        <v>0.0808</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0579</v>
+        <v>0.06850000000000001</v>
       </c>
     </row>
     <row r="351">
@@ -9552,10 +9552,10 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.03</v>
+        <v>0.0323</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0231</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="352">
@@ -9578,10 +9578,10 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.035</v>
+        <v>0.0371</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0274</v>
+        <v>0.0291</v>
       </c>
     </row>
     <row r="353">
@@ -9604,10 +9604,10 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>0.032</v>
+        <v>0.0329</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0273</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="354">
@@ -9630,10 +9630,10 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.0682</v>
+        <v>0.0737</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0539</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row r="355">
@@ -9656,10 +9656,10 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.1307</v>
+        <v>0.1384</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1048</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="356">
@@ -9682,10 +9682,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.1085</v>
+        <v>0.1168</v>
       </c>
       <c r="H356" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0948</v>
       </c>
     </row>
     <row r="357">
@@ -9708,10 +9708,10 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.0548</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H357" t="n">
-        <v>0.043</v>
+        <v>0.0535</v>
       </c>
     </row>
     <row r="358">
@@ -9734,10 +9734,10 @@
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>0.2115</v>
+        <v>0.221</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1736</v>
+        <v>0.1857</v>
       </c>
     </row>
     <row r="359">
@@ -9760,10 +9760,10 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.1758</v>
+        <v>0.1823</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1453</v>
+        <v>0.1506</v>
       </c>
     </row>
     <row r="360">
@@ -9786,10 +9786,10 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.5212</v>
+        <v>0.6072</v>
       </c>
       <c r="H360" t="n">
-        <v>0.4838</v>
+        <v>0.5622</v>
       </c>
     </row>
     <row r="361">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.3782</v>
+        <v>0.3895</v>
       </c>
       <c r="H361" t="n">
-        <v>0.3429</v>
+        <v>0.3563</v>
       </c>
     </row>
     <row r="362">
@@ -9838,10 +9838,10 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>0.7438</v>
+        <v>0.7725</v>
       </c>
       <c r="H362" t="n">
-        <v>0.7024</v>
+        <v>0.7262</v>
       </c>
     </row>
     <row r="363">
@@ -9864,10 +9864,10 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>0.7983</v>
+        <v>0.8205</v>
       </c>
       <c r="H363" t="n">
-        <v>0.7693</v>
+        <v>0.7914</v>
       </c>
     </row>
     <row r="364">
@@ -10063,11 +10063,11 @@
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F371" t="inlineStr"/>
@@ -10089,11 +10089,11 @@
       </c>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F372" t="inlineStr"/>
@@ -10141,11 +10141,11 @@
       </c>
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F374" t="inlineStr"/>
@@ -10167,11 +10167,11 @@
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F375" t="inlineStr"/>
@@ -10280,10 +10280,10 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.0397</v>
+        <v>0.0385</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0312</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="380">
@@ -10358,10 +10358,10 @@
       </c>
       <c r="F382" t="inlineStr"/>
       <c r="G382" t="n">
-        <v>0.0245</v>
+        <v>0.0223</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0206</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="383">
@@ -10384,10 +10384,10 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.0303</v>
+        <v>0.0307</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0232</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="384">
@@ -10436,10 +10436,10 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.0467</v>
+        <v>0.0465</v>
       </c>
       <c r="H385" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
     </row>
     <row r="386">
@@ -10462,10 +10462,10 @@
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.0249</v>
+        <v>0.0263</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0198</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="387">
@@ -10488,10 +10488,10 @@
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0844</v>
+        <v>0.0834</v>
       </c>
     </row>
     <row r="388">
@@ -10514,10 +10514,10 @@
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.0788</v>
+        <v>0.0772</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0608</v>
+        <v>0.059</v>
       </c>
     </row>
     <row r="389">
@@ -10540,10 +10540,10 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.2807</v>
+        <v>0.3401</v>
       </c>
       <c r="H389" t="n">
-        <v>0.2408</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="390">
@@ -10566,10 +10566,10 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.2053</v>
+        <v>0.1988</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1739</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="391">
@@ -10592,10 +10592,10 @@
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>0.2976</v>
+        <v>0.2738</v>
       </c>
       <c r="H391" t="n">
-        <v>0.2562</v>
+        <v>0.2275</v>
       </c>
     </row>
     <row r="392">
@@ -10817,11 +10817,11 @@
       </c>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F400" t="inlineStr"/>
@@ -10843,11 +10843,11 @@
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F401" t="inlineStr"/>
@@ -10895,11 +10895,11 @@
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F403" t="inlineStr"/>
@@ -10921,11 +10921,11 @@
       </c>
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F404" t="inlineStr"/>
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.042</v>
+        <v>0.0401</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0331</v>
+        <v>0.0318</v>
       </c>
     </row>
     <row r="409">
@@ -11112,10 +11112,10 @@
       </c>
       <c r="F411" t="inlineStr"/>
       <c r="G411" t="n">
-        <v>0.0184</v>
+        <v>0.0175</v>
       </c>
       <c r="H411" t="n">
-        <v>0.0146</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="412">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.0265</v>
+        <v>0.0276</v>
       </c>
       <c r="H415" t="n">
-        <v>0.0201</v>
+        <v>0.0213</v>
       </c>
     </row>
     <row r="416">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.1898</v>
+        <v>0.2467</v>
       </c>
       <c r="H418" t="n">
-        <v>0.1528</v>
+        <v>0.2092</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.1358</v>
+        <v>0.1319</v>
       </c>
       <c r="H419" t="n">
-        <v>0.1109</v>
+        <v>0.1075</v>
       </c>
     </row>
     <row r="420">
@@ -11346,10 +11346,10 @@
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>0.2307</v>
+        <v>0.2086</v>
       </c>
       <c r="H420" t="n">
-        <v>0.2017</v>
+        <v>0.1795</v>
       </c>
     </row>
     <row r="421">
@@ -11571,11 +11571,11 @@
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F429" t="inlineStr"/>
@@ -11597,11 +11597,11 @@
       </c>
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F430" t="inlineStr"/>
@@ -11649,11 +11649,11 @@
       </c>
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F432" t="inlineStr"/>
@@ -11675,11 +11675,11 @@
       </c>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F433" t="inlineStr"/>
@@ -12325,11 +12325,11 @@
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F458" t="inlineStr"/>
@@ -12351,11 +12351,11 @@
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F459" t="inlineStr"/>
@@ -12403,11 +12403,11 @@
       </c>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F461" t="inlineStr"/>
@@ -12429,11 +12429,11 @@
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F462" t="inlineStr"/>
@@ -13079,11 +13079,11 @@
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
@@ -13105,11 +13105,11 @@
       </c>
       <c r="C488" t="inlineStr"/>
       <c r="D488" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
@@ -13157,11 +13157,11 @@
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
@@ -13183,11 +13183,11 @@
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
@@ -13833,11 +13833,11 @@
       </c>
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
@@ -13859,11 +13859,11 @@
       </c>
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F517" t="inlineStr"/>
@@ -13911,11 +13911,11 @@
       </c>
       <c r="C519" t="inlineStr"/>
       <c r="D519" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F519" t="inlineStr"/>
@@ -13937,11 +13937,11 @@
       </c>
       <c r="C520" t="inlineStr"/>
       <c r="D520" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F520" t="inlineStr"/>
@@ -14587,11 +14587,11 @@
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F545" t="inlineStr"/>
@@ -14613,11 +14613,11 @@
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F546" t="inlineStr"/>
@@ -14665,11 +14665,11 @@
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F548" t="inlineStr"/>
@@ -14691,11 +14691,11 @@
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F549" t="inlineStr"/>
@@ -15341,11 +15341,11 @@
       </c>
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F574" t="inlineStr"/>
@@ -15367,11 +15367,11 @@
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F575" t="inlineStr"/>
@@ -15419,11 +15419,11 @@
       </c>
       <c r="C577" t="inlineStr"/>
       <c r="D577" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F577" t="inlineStr"/>
@@ -15445,11 +15445,11 @@
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F578" t="inlineStr"/>
@@ -16095,11 +16095,11 @@
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F603" t="inlineStr"/>
@@ -16121,11 +16121,11 @@
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F604" t="inlineStr"/>
@@ -16173,11 +16173,11 @@
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F606" t="inlineStr"/>
@@ -16199,11 +16199,11 @@
       </c>
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F607" t="inlineStr"/>
@@ -16849,11 +16849,11 @@
       </c>
       <c r="C632" t="inlineStr"/>
       <c r="D632" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F632" t="inlineStr"/>
@@ -16875,11 +16875,11 @@
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F633" t="inlineStr"/>
@@ -16927,11 +16927,11 @@
       </c>
       <c r="C635" t="inlineStr"/>
       <c r="D635" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F635" t="inlineStr"/>
@@ -16953,11 +16953,11 @@
       </c>
       <c r="C636" t="inlineStr"/>
       <c r="D636" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F636" t="inlineStr"/>
@@ -17048,11 +17048,11 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -17074,11 +17074,11 @@
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -17100,11 +17100,11 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -17126,11 +17126,11 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C643" t="inlineStr"/>
@@ -17152,11 +17152,11 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -17178,11 +17178,11 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
@@ -17204,11 +17204,11 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C646" t="inlineStr"/>
@@ -17230,11 +17230,11 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C647" t="inlineStr"/>
@@ -17256,11 +17256,11 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -17282,11 +17282,11 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -17308,11 +17308,11 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -17334,11 +17334,11 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -17360,11 +17360,11 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -17386,11 +17386,11 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C653" t="inlineStr"/>
@@ -17412,11 +17412,11 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -17438,11 +17438,11 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -17464,11 +17464,11 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -17490,11 +17490,11 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
@@ -17516,11 +17516,11 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
@@ -17542,11 +17542,11 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
@@ -17568,11 +17568,11 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -17594,11 +17594,11 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -17620,20 +17620,20 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F662" t="inlineStr"/>
@@ -17646,11 +17646,11 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C663" t="inlineStr"/>
@@ -17672,20 +17672,20 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C664" t="inlineStr"/>
       <c r="D664" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F664" t="inlineStr"/>
@@ -17698,20 +17698,20 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C665" t="inlineStr"/>
       <c r="D665" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F665" t="inlineStr"/>
@@ -17724,11 +17724,11 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C666" t="inlineStr"/>
@@ -17750,11 +17750,11 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C667" t="inlineStr"/>
@@ -17776,11 +17776,11 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -17802,11 +17802,11 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -17828,11 +17828,11 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
@@ -17854,11 +17854,11 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
@@ -17880,11 +17880,11 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
@@ -17906,11 +17906,11 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
@@ -17932,11 +17932,11 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
@@ -17958,11 +17958,11 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
@@ -17984,11 +17984,11 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
@@ -18010,11 +18010,11 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
@@ -18036,11 +18036,11 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
@@ -18062,11 +18062,11 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
@@ -18088,11 +18088,11 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
@@ -18114,11 +18114,11 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
@@ -18140,11 +18140,11 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C682" t="inlineStr"/>
@@ -18166,11 +18166,11 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
@@ -18192,11 +18192,11 @@
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
@@ -18218,11 +18218,11 @@
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C685" t="inlineStr"/>
@@ -18244,11 +18244,11 @@
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C686" t="inlineStr"/>
@@ -18270,11 +18270,11 @@
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C687" t="inlineStr"/>
@@ -18296,11 +18296,11 @@
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C688" t="inlineStr"/>
@@ -18322,11 +18322,11 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C689" t="inlineStr"/>
@@ -18348,11 +18348,11 @@
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C690" t="inlineStr"/>
@@ -18374,20 +18374,20 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C691" t="inlineStr"/>
       <c r="D691" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F691" t="inlineStr"/>
@@ -18400,11 +18400,11 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C692" t="inlineStr"/>
@@ -18426,20 +18426,20 @@
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C693" t="inlineStr"/>
       <c r="D693" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F693" t="inlineStr"/>
@@ -18452,20 +18452,20 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C694" t="inlineStr"/>
       <c r="D694" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F694" t="inlineStr"/>
@@ -18478,11 +18478,11 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C695" t="inlineStr"/>
@@ -18504,11 +18504,11 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C696" t="inlineStr"/>
@@ -18530,11 +18530,11 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="C697" t="inlineStr"/>
@@ -19137,11 +19137,11 @@
       </c>
       <c r="C720" t="inlineStr"/>
       <c r="D720" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F720" t="inlineStr"/>
@@ -19163,11 +19163,11 @@
       </c>
       <c r="C721" t="inlineStr"/>
       <c r="D721" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F721" t="inlineStr"/>
@@ -19189,11 +19189,11 @@
       </c>
       <c r="C722" t="inlineStr"/>
       <c r="D722" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F722" t="inlineStr"/>
@@ -19215,11 +19215,11 @@
       </c>
       <c r="C723" t="inlineStr"/>
       <c r="D723" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F723" t="inlineStr"/>
@@ -19310,11 +19310,11 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C727" t="inlineStr"/>
@@ -19336,11 +19336,11 @@
     </row>
     <row r="728">
       <c r="A728" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C728" t="inlineStr"/>
@@ -19362,11 +19362,11 @@
     </row>
     <row r="729">
       <c r="A729" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C729" t="inlineStr"/>
@@ -19388,11 +19388,11 @@
     </row>
     <row r="730">
       <c r="A730" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C730" t="inlineStr"/>
@@ -19414,11 +19414,11 @@
     </row>
     <row r="731">
       <c r="A731" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C731" t="inlineStr"/>
@@ -19440,11 +19440,11 @@
     </row>
     <row r="732">
       <c r="A732" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C732" t="inlineStr"/>
@@ -19466,11 +19466,11 @@
     </row>
     <row r="733">
       <c r="A733" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C733" t="inlineStr"/>
@@ -19492,11 +19492,11 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C734" t="inlineStr"/>
@@ -19518,11 +19518,11 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C735" t="inlineStr"/>
@@ -19544,11 +19544,11 @@
     </row>
     <row r="736">
       <c r="A736" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C736" t="inlineStr"/>
@@ -19570,11 +19570,11 @@
     </row>
     <row r="737">
       <c r="A737" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C737" t="inlineStr"/>
@@ -19596,11 +19596,11 @@
     </row>
     <row r="738">
       <c r="A738" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C738" t="inlineStr"/>
@@ -19622,11 +19622,11 @@
     </row>
     <row r="739">
       <c r="A739" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C739" t="inlineStr"/>
@@ -19648,11 +19648,11 @@
     </row>
     <row r="740">
       <c r="A740" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C740" t="inlineStr"/>
@@ -19674,11 +19674,11 @@
     </row>
     <row r="741">
       <c r="A741" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C741" t="inlineStr"/>
@@ -19700,11 +19700,11 @@
     </row>
     <row r="742">
       <c r="A742" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C742" t="inlineStr"/>
@@ -19726,11 +19726,11 @@
     </row>
     <row r="743">
       <c r="A743" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C743" t="inlineStr"/>
@@ -19752,11 +19752,11 @@
     </row>
     <row r="744">
       <c r="A744" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -19778,11 +19778,11 @@
     </row>
     <row r="745">
       <c r="A745" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -19804,11 +19804,11 @@
     </row>
     <row r="746">
       <c r="A746" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -19830,11 +19830,11 @@
     </row>
     <row r="747">
       <c r="A747" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -19856,11 +19856,11 @@
     </row>
     <row r="748">
       <c r="A748" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
@@ -19882,20 +19882,20 @@
     </row>
     <row r="749">
       <c r="A749" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
       <c r="D749" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F749" t="inlineStr"/>
@@ -19908,20 +19908,20 @@
     </row>
     <row r="750">
       <c r="A750" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
       <c r="D750" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F750" t="inlineStr"/>
@@ -19934,11 +19934,11 @@
     </row>
     <row r="751">
       <c r="A751" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
@@ -19960,20 +19960,20 @@
     </row>
     <row r="752">
       <c r="A752" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
       <c r="D752" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F752" t="inlineStr"/>
@@ -19986,11 +19986,11 @@
     </row>
     <row r="753">
       <c r="A753" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
@@ -20012,11 +20012,11 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
@@ -20038,11 +20038,11 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -20064,11 +20064,11 @@
     </row>
     <row r="756">
       <c r="A756" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
@@ -20090,11 +20090,11 @@
     </row>
     <row r="757">
       <c r="A757" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
@@ -20116,11 +20116,11 @@
     </row>
     <row r="758">
       <c r="A758" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
@@ -20142,11 +20142,11 @@
     </row>
     <row r="759">
       <c r="A759" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -20168,11 +20168,11 @@
     </row>
     <row r="760">
       <c r="A760" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
@@ -20194,11 +20194,11 @@
     </row>
     <row r="761">
       <c r="A761" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
@@ -20220,11 +20220,11 @@
     </row>
     <row r="762">
       <c r="A762" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -20246,11 +20246,11 @@
     </row>
     <row r="763">
       <c r="A763" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -20272,11 +20272,11 @@
     </row>
     <row r="764">
       <c r="A764" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -20298,11 +20298,11 @@
     </row>
     <row r="765">
       <c r="A765" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
@@ -20324,11 +20324,11 @@
     </row>
     <row r="766">
       <c r="A766" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
@@ -20350,11 +20350,11 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
@@ -20376,11 +20376,11 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -20402,11 +20402,11 @@
     </row>
     <row r="769">
       <c r="A769" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
@@ -20428,11 +20428,11 @@
     </row>
     <row r="770">
       <c r="A770" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
@@ -20454,11 +20454,11 @@
     </row>
     <row r="771">
       <c r="A771" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
@@ -20480,11 +20480,11 @@
     </row>
     <row r="772">
       <c r="A772" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -20506,11 +20506,11 @@
     </row>
     <row r="773">
       <c r="A773" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
@@ -20532,11 +20532,11 @@
     </row>
     <row r="774">
       <c r="A774" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
@@ -20558,11 +20558,11 @@
     </row>
     <row r="775">
       <c r="A775" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
@@ -20584,11 +20584,11 @@
     </row>
     <row r="776">
       <c r="A776" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -20610,11 +20610,11 @@
     </row>
     <row r="777">
       <c r="A777" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -20636,20 +20636,20 @@
     </row>
     <row r="778">
       <c r="A778" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
       <c r="D778" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E778" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F778" t="inlineStr"/>
@@ -20662,20 +20662,20 @@
     </row>
     <row r="779">
       <c r="A779" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
       <c r="D779" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E779" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F779" t="inlineStr"/>
@@ -20688,11 +20688,11 @@
     </row>
     <row r="780">
       <c r="A780" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
@@ -20714,20 +20714,20 @@
     </row>
     <row r="781">
       <c r="A781" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
       <c r="D781" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F781" t="inlineStr"/>
@@ -20740,11 +20740,11 @@
     </row>
     <row r="782">
       <c r="A782" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -20766,11 +20766,11 @@
     </row>
     <row r="783">
       <c r="A783" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -20792,11 +20792,11 @@
     </row>
     <row r="784">
       <c r="A784" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -21399,11 +21399,11 @@
       </c>
       <c r="C807" t="inlineStr"/>
       <c r="D807" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E807" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F807" t="inlineStr"/>
@@ -21425,11 +21425,11 @@
       </c>
       <c r="C808" t="inlineStr"/>
       <c r="D808" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F808" t="inlineStr"/>
@@ -21477,11 +21477,11 @@
       </c>
       <c r="C810" t="inlineStr"/>
       <c r="D810" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F810" t="inlineStr"/>
@@ -21503,11 +21503,11 @@
       </c>
       <c r="C811" t="inlineStr"/>
       <c r="D811" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F811" t="inlineStr"/>
@@ -22153,11 +22153,11 @@
       </c>
       <c r="C836" t="inlineStr"/>
       <c r="D836" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F836" t="inlineStr"/>
@@ -22179,11 +22179,11 @@
       </c>
       <c r="C837" t="inlineStr"/>
       <c r="D837" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F837" t="inlineStr"/>
@@ -22231,11 +22231,11 @@
       </c>
       <c r="C839" t="inlineStr"/>
       <c r="D839" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F839" t="inlineStr"/>
@@ -22257,11 +22257,11 @@
       </c>
       <c r="C840" t="inlineStr"/>
       <c r="D840" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F840" t="inlineStr"/>
@@ -22907,11 +22907,11 @@
       </c>
       <c r="C865" t="inlineStr"/>
       <c r="D865" t="n">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>Clippers</t>
+          <t>Trail Blazers</t>
         </is>
       </c>
       <c r="F865" t="inlineStr"/>
@@ -22933,11 +22933,11 @@
       </c>
       <c r="C866" t="inlineStr"/>
       <c r="D866" t="n">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>Trail Blazers</t>
+          <t>Clippers</t>
         </is>
       </c>
       <c r="F866" t="inlineStr"/>
@@ -22985,11 +22985,11 @@
       </c>
       <c r="C868" t="inlineStr"/>
       <c r="D868" t="n">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>Pelicans</t>
+          <t>Grizzlies</t>
         </is>
       </c>
       <c r="F868" t="inlineStr"/>
@@ -23011,11 +23011,11 @@
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="n">
-        <v>1610612763</v>
+        <v>1610612740</v>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>Grizzlies</t>
+          <t>Pelicans</t>
         </is>
       </c>
       <c r="F869" t="inlineStr"/>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.4085</v>
+        <v>0.4061</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3506</v>
+        <v>0.3472</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.4387</v>
+        <v>0.4821</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3921</v>
+        <v>0.442</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.4217</v>
+        <v>0.4187</v>
       </c>
       <c r="H4" t="n">
-        <v>0.384</v>
+        <v>0.3819</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.6259</v>
+        <v>0.622</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.5768</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.7482</v>
+        <v>0.7338</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7115</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9529</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9436</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="12">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9599</v>
+        <v>0.9608</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.6494</v>
+        <v>0.6528</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5915</v>
+        <v>0.5939</v>
       </c>
     </row>
     <row r="32">
@@ -1258,10 +1258,10 @@
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>0.5849</v>
+        <v>0.649</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5622</v>
+        <v>0.617</v>
       </c>
     </row>
     <row r="33">
@@ -1336,10 +1336,10 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.8864</v>
+        <v>0.8883</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8641</v>
+        <v>0.8657</v>
       </c>
     </row>
     <row r="36">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.8685</v>
+        <v>0.87</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8353</v>
+        <v>0.8367</v>
       </c>
     </row>
     <row r="37">
@@ -1414,10 +1414,10 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.9409</v>
+        <v>0.9427</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9218</v>
+        <v>0.9239000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1440,10 +1440,10 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.8992</v>
+        <v>0.9003</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8683</v>
+        <v>0.8693</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.9827</v>
+        <v>0.9832</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9775</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="41">
@@ -1518,10 +1518,10 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.9751</v>
+        <v>0.9758</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9677</v>
+        <v>0.9683</v>
       </c>
     </row>
     <row r="43">
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.6079</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5613</v>
+        <v>0.5179</v>
       </c>
     </row>
     <row r="61">
@@ -2012,10 +2012,10 @@
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>0.4378</v>
+        <v>0.383</v>
       </c>
       <c r="H61" t="n">
-        <v>0.4151</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="62">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.514</v>
+        <v>0.446</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4749</v>
+        <v>0.3982</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.7483</v>
+        <v>0.6866</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6999</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="64">
@@ -2090,10 +2090,10 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0.8576</v>
+        <v>0.8033</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8354</v>
+        <v>0.7856</v>
       </c>
     </row>
     <row r="65">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.8471</v>
+        <v>0.7958</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.7617</v>
       </c>
     </row>
     <row r="66">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.6838</v>
+        <v>0.6177</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6419</v>
+        <v>0.5786</v>
       </c>
     </row>
     <row r="67">
@@ -2168,10 +2168,10 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9073</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9038</v>
+        <v>0.8834</v>
       </c>
     </row>
     <row r="68">
@@ -2194,10 +2194,10 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8487</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8478</v>
+        <v>0.8118</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9727</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9734</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9597</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9485</v>
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.9709</v>
+        <v>0.9609</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9629</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -2298,10 +2298,10 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>0.9848</v>
+        <v>0.9812</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9827</v>
+        <v>0.9782</v>
       </c>
     </row>
     <row r="73">
@@ -2324,10 +2324,10 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.9866</v>
+        <v>0.9831</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9828</v>
+        <v>0.9782999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.616</v>
+        <v>0.6181</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5783</v>
+        <v>0.5813</v>
       </c>
     </row>
     <row r="90">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.5251</v>
+        <v>0.6018</v>
       </c>
       <c r="H91" t="n">
-        <v>0.486</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="92">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.8188</v>
+        <v>0.8215</v>
       </c>
       <c r="H94" t="n">
-        <v>0.7826</v>
+        <v>0.7849</v>
       </c>
     </row>
     <row r="95">
@@ -2922,10 +2922,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.9153</v>
+        <v>0.9161</v>
       </c>
       <c r="H96" t="n">
-        <v>0.8929</v>
+        <v>0.8935999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9565</v>
+        <v>0.9576</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9453</v>
+        <v>0.9469</v>
       </c>
     </row>
     <row r="100">
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.4178</v>
+        <v>0.4232</v>
       </c>
       <c r="H118" t="n">
-        <v>0.3741</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="119">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.3001</v>
+        <v>0.36</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2517</v>
+        <v>0.3134</v>
       </c>
     </row>
     <row r="121">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.9411</v>
+        <v>0.9427</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9191</v>
+        <v>0.9218</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.9059</v>
+        <v>0.9073</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8772</v>
+        <v>0.8794999999999999</v>
       </c>
     </row>
     <row r="129">
@@ -3780,10 +3780,10 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.9411</v>
+        <v>0.9418</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9263</v>
+        <v>0.9268999999999999</v>
       </c>
     </row>
     <row r="130">
@@ -3806,10 +3806,10 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.9764</v>
+        <v>0.9768</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9697</v>
       </c>
     </row>
     <row r="131">
@@ -4248,10 +4248,10 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.2885</v>
+        <v>0.3</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2518</v>
+        <v>0.2662</v>
       </c>
     </row>
     <row r="148">
@@ -4274,10 +4274,10 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>0.1359</v>
+        <v>0.1343</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1136</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="149">
@@ -4300,10 +4300,10 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>0.1646</v>
+        <v>0.2144</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1424</v>
+        <v>0.1967</v>
       </c>
     </row>
     <row r="150">
@@ -4404,10 +4404,10 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.3466</v>
+        <v>0.3641</v>
       </c>
       <c r="H153" t="n">
-        <v>0.3001</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="154">
@@ -4430,10 +4430,10 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.6543</v>
+        <v>0.6605</v>
       </c>
       <c r="H154" t="n">
-        <v>0.6011</v>
+        <v>0.606</v>
       </c>
     </row>
     <row r="155">
@@ -4456,10 +4456,10 @@
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.5747</v>
+        <v>0.5794</v>
       </c>
       <c r="H155" t="n">
-        <v>0.5249</v>
+        <v>0.5313</v>
       </c>
     </row>
     <row r="156">
@@ -4534,10 +4534,10 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8931</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8616</v>
+        <v>0.8668</v>
       </c>
     </row>
     <row r="159">
@@ -4586,10 +4586,10 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>0.9683</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9601</v>
+        <v>0.9617</v>
       </c>
     </row>
     <row r="161">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.1647</v>
+        <v>0.1633</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1315</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.188</v>
+        <v>0.2383</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1529</v>
+        <v>0.2042</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.2174</v>
+        <v>0.2151</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1812</v>
+        <v>0.1785</v>
       </c>
     </row>
     <row r="180">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.9696</v>
+        <v>0.971</v>
       </c>
       <c r="H189" t="n">
-        <v>0.9596</v>
+        <v>0.9613</v>
       </c>
     </row>
     <row r="190">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.3581</v>
+        <v>0.4214</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3162</v>
+        <v>0.3823</v>
       </c>
     </row>
     <row r="208">
@@ -5886,10 +5886,10 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.6999</v>
+        <v>0.6875</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6534</v>
+        <v>0.6359</v>
       </c>
     </row>
     <row r="211">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.956</v>
+        <v>0.9573</v>
       </c>
       <c r="H214" t="n">
-        <v>0.9429</v>
+        <v>0.9442</v>
       </c>
     </row>
     <row r="215">
@@ -6042,10 +6042,10 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.9465</v>
+        <v>0.948</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9329</v>
+        <v>0.9347</v>
       </c>
     </row>
     <row r="217">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.9787</v>
+        <v>0.9796</v>
       </c>
       <c r="H218" t="n">
-        <v>0.9724</v>
+        <v>0.9739</v>
       </c>
     </row>
     <row r="219">
@@ -6536,10 +6536,10 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0761</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0591</v>
+        <v>0.0573</v>
       </c>
     </row>
     <row r="236">
@@ -6562,10 +6562,10 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1166</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0731</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="237">
@@ -6588,10 +6588,10 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.1071</v>
+        <v>0.1064</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0847</v>
+        <v>0.0839</v>
       </c>
     </row>
     <row r="238">
@@ -6640,10 +6640,10 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.3989</v>
+        <v>0.394</v>
       </c>
       <c r="H239" t="n">
-        <v>0.3457</v>
+        <v>0.3395</v>
       </c>
     </row>
     <row r="240">
@@ -6744,10 +6744,10 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.8292</v>
+        <v>0.8312</v>
       </c>
       <c r="H243" t="n">
-        <v>0.8005</v>
+        <v>0.8034</v>
       </c>
     </row>
     <row r="244">
@@ -6822,10 +6822,10 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.9166</v>
+        <v>0.9175</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9029</v>
+        <v>0.9042</v>
       </c>
     </row>
     <row r="247">
@@ -6848,10 +6848,10 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.9364</v>
+        <v>0.9374</v>
       </c>
       <c r="H247" t="n">
-        <v>0.9212</v>
+        <v>0.9221</v>
       </c>
     </row>
     <row r="248">
@@ -7290,10 +7290,10 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.1317</v>
+        <v>0.1307</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1008</v>
+        <v>0.0997</v>
       </c>
     </row>
     <row r="265">
@@ -7316,10 +7316,10 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.1522</v>
+        <v>0.1882</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1195</v>
+        <v>0.1513</v>
       </c>
     </row>
     <row r="266">
@@ -7394,10 +7394,10 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.4751</v>
+        <v>0.4687</v>
       </c>
       <c r="H268" t="n">
-        <v>0.4253</v>
+        <v>0.4206</v>
       </c>
     </row>
     <row r="269">
@@ -7602,10 +7602,10 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9574</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9465</v>
+        <v>0.9483</v>
       </c>
     </row>
     <row r="277">
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.0564</v>
+        <v>0.0567</v>
       </c>
       <c r="H292" t="n">
-        <v>0.0469</v>
+        <v>0.0471</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.0225</v>
+        <v>0.0218</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0173</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.0266</v>
+        <v>0.035</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0207</v>
+        <v>0.0273</v>
       </c>
     </row>
     <row r="295">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.0809</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0589</v>
+        <v>0.0573</v>
       </c>
     </row>
     <row r="297">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.0571</v>
+        <v>0.0558</v>
       </c>
       <c r="H299" t="n">
-        <v>0.044</v>
+        <v>0.0427</v>
       </c>
     </row>
     <row r="300">
@@ -8226,10 +8226,10 @@
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.1995</v>
+        <v>0.1966</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1708</v>
+        <v>0.1688</v>
       </c>
     </row>
     <row r="301">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.36</v>
+        <v>0.3566</v>
       </c>
       <c r="H302" t="n">
-        <v>0.3224</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="303">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.0515</v>
+        <v>0.068</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0403</v>
+        <v>0.0529</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.0547</v>
+        <v>0.0531</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0435</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.1228</v>
+        <v>0.1205</v>
       </c>
       <c r="H325" t="n">
-        <v>0.0941</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="326">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.6776</v>
+        <v>0.68</v>
       </c>
       <c r="H331" t="n">
-        <v>0.64</v>
+        <v>0.6434</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.6437</v>
+        <v>0.6454</v>
       </c>
       <c r="H332" t="n">
-        <v>0.6105</v>
+        <v>0.613</v>
       </c>
     </row>
     <row r="333">
@@ -9552,10 +9552,10 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.0323</v>
+        <v>0.0317</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0249</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="352">
@@ -9578,10 +9578,10 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.0371</v>
+        <v>0.0479</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0291</v>
+        <v>0.0391</v>
       </c>
     </row>
     <row r="353">
@@ -9630,10 +9630,10 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.0737</v>
+        <v>0.0731</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0589</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="355">
@@ -9656,10 +9656,10 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.1384</v>
+        <v>0.1332</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1104</v>
+        <v>0.1069</v>
       </c>
     </row>
     <row r="356">
@@ -9708,10 +9708,10 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0653</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0535</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="358">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.3895</v>
+        <v>0.387</v>
       </c>
       <c r="H361" t="n">
-        <v>0.3563</v>
+        <v>0.3546</v>
       </c>
     </row>
     <row r="362">
@@ -10332,10 +10332,10 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.0173</v>
+        <v>0.0218</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0152</v>
+        <v>0.0188</v>
       </c>
     </row>
     <row r="382">
@@ -10384,10 +10384,10 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.0307</v>
+        <v>0.0303</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0236</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="384">
@@ -10488,10 +10488,10 @@
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0958</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0834</v>
+        <v>0.0825</v>
       </c>
     </row>
     <row r="388">
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.0401</v>
+        <v>0.0392</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0318</v>
+        <v>0.0307</v>
       </c>
     </row>
     <row r="409">
@@ -11086,10 +11086,10 @@
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>0.0172</v>
+        <v>0.0217</v>
       </c>
       <c r="H410" t="n">
-        <v>0.0134</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="411">
@@ -11164,10 +11164,10 @@
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>0.0399</v>
+        <v>0.0383</v>
       </c>
       <c r="H413" t="n">
-        <v>0.0317</v>
+        <v>0.0307</v>
       </c>
     </row>
     <row r="414">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.0404</v>
+        <v>0.0387</v>
       </c>
       <c r="H414" t="n">
-        <v>0.0304</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="415">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.0276</v>
+        <v>0.0261</v>
       </c>
       <c r="H415" t="n">
-        <v>0.0213</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="416">
@@ -11242,10 +11242,10 @@
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.0788</v>
+        <v>0.0779</v>
       </c>
       <c r="H416" t="n">
-        <v>0.0636</v>
+        <v>0.0626</v>
       </c>
     </row>
     <row r="417">
@@ -11268,10 +11268,10 @@
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.0535</v>
+        <v>0.0517</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0439</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="418">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -478,10 +478,10 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.4061</v>
+        <v>0.4864</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3472</v>
+        <v>0.4346</v>
       </c>
     </row>
     <row r="3">
@@ -504,10 +504,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.4821</v>
+        <v>0.5587</v>
       </c>
       <c r="H3" t="n">
-        <v>0.442</v>
+        <v>0.5245</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +530,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.4187</v>
+        <v>0.5062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3819</v>
+        <v>0.4658</v>
       </c>
     </row>
     <row r="5">
@@ -556,10 +556,10 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>0.622</v>
+        <v>0.7338</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5768</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.7338</v>
+        <v>0.8373</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>0.8173</v>
       </c>
     </row>
     <row r="7">
@@ -608,10 +608,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.6859</v>
+        <v>0.7385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.7084</v>
       </c>
     </row>
     <row r="8">
@@ -634,10 +634,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.6661</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5205</v>
+        <v>0.6318</v>
       </c>
     </row>
     <row r="9">
@@ -660,10 +660,10 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>0.8304</v>
+        <v>0.9161</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7974</v>
+        <v>0.8928</v>
       </c>
     </row>
     <row r="10">
@@ -686,10 +686,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.7762</v>
+        <v>0.8596</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7343</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="11">
@@ -712,10 +712,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.9529</v>
+        <v>0.9503</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9433</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="12">
@@ -738,10 +738,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.9043</v>
+        <v>0.9613</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8895</v>
+        <v>0.9518</v>
       </c>
     </row>
     <row r="13">
@@ -764,10 +764,10 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.9315</v>
+        <v>0.9576</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9192</v>
+        <v>0.9495</v>
       </c>
     </row>
     <row r="14">
@@ -790,10 +790,10 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.9701</v>
+        <v>0.984</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9615</v>
+        <v>0.9795</v>
       </c>
     </row>
     <row r="15">
@@ -816,10 +816,10 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9766</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9608</v>
+        <v>0.9696</v>
       </c>
     </row>
     <row r="16">
@@ -1232,10 +1232,10 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>0.6528</v>
+        <v>0.5654</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5939</v>
+        <v>0.5135999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1284,10 +1284,10 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>0.5665</v>
+        <v>0.5934</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5572</v>
       </c>
     </row>
     <row r="34">
@@ -1310,10 +1310,10 @@
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.7992</v>
+        <v>0.8264</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7479</v>
+        <v>0.7815</v>
       </c>
     </row>
     <row r="35">
@@ -1336,10 +1336,10 @@
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>0.8883</v>
+        <v>0.9092</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8657</v>
+        <v>0.889</v>
       </c>
     </row>
     <row r="36">
@@ -1362,10 +1362,10 @@
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
-        <v>0.87</v>
+        <v>0.8609</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8367</v>
+        <v>0.8293</v>
       </c>
     </row>
     <row r="37">
@@ -1388,10 +1388,10 @@
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.7509</v>
+        <v>0.7748</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7062</v>
+        <v>0.7342</v>
       </c>
     </row>
     <row r="38">
@@ -1414,10 +1414,10 @@
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
-        <v>0.9427</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="39">
@@ -1440,10 +1440,10 @@
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
-        <v>0.9003</v>
+        <v>0.9055</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8693</v>
+        <v>0.8767</v>
       </c>
     </row>
     <row r="40">
@@ -1466,10 +1466,10 @@
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.9832</v>
+        <v>0.9756</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9782</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1492,10 +1492,10 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0.9694</v>
+        <v>0.9792</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9595</v>
+        <v>0.9718</v>
       </c>
     </row>
     <row r="42">
@@ -1518,10 +1518,10 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>0.9758</v>
+        <v>0.9795</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9683</v>
+        <v>0.9734</v>
       </c>
     </row>
     <row r="43">
@@ -1570,10 +1570,10 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>0.9881</v>
+        <v>0.9878</v>
       </c>
       <c r="H44" t="n">
-        <v>0.984</v>
+        <v>0.9834000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1986,10 +1986,10 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.4755</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5179</v>
+        <v>0.4413</v>
       </c>
     </row>
     <row r="61">
@@ -2038,10 +2038,10 @@
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>0.446</v>
+        <v>0.4937</v>
       </c>
       <c r="H62" t="n">
-        <v>0.3982</v>
+        <v>0.4492</v>
       </c>
     </row>
     <row r="63">
@@ -2064,10 +2064,10 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.6866</v>
+        <v>0.7247</v>
       </c>
       <c r="H63" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="64">
@@ -2090,10 +2090,10 @@
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>0.8033</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>0.7856</v>
+        <v>0.8283</v>
       </c>
     </row>
     <row r="65">
@@ -2116,10 +2116,10 @@
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
-        <v>0.7958</v>
+        <v>0.789</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7617</v>
+        <v>0.7537</v>
       </c>
     </row>
     <row r="66">
@@ -2142,10 +2142,10 @@
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
-        <v>0.6177</v>
+        <v>0.6566</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5786</v>
+        <v>0.6133999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2168,10 +2168,10 @@
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
-        <v>0.9073</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8834</v>
+        <v>0.899</v>
       </c>
     </row>
     <row r="68">
@@ -2194,10 +2194,10 @@
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>0.8487</v>
+        <v>0.8648</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8118</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="69">
@@ -2220,10 +2220,10 @@
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>0.9727</v>
+        <v>0.9608</v>
       </c>
       <c r="H69" t="n">
-        <v>0.965</v>
+        <v>0.9499</v>
       </c>
     </row>
     <row r="70">
@@ -2246,10 +2246,10 @@
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.962</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9508</v>
       </c>
     </row>
     <row r="71">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>0.9609</v>
+        <v>0.967</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9588</v>
       </c>
     </row>
     <row r="72">
@@ -2298,10 +2298,10 @@
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
-        <v>0.9812</v>
+        <v>0.9848</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9782</v>
+        <v>0.9827</v>
       </c>
     </row>
     <row r="73">
@@ -2324,10 +2324,10 @@
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>0.9831</v>
+        <v>0.9816</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="74">
@@ -2740,10 +2740,10 @@
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
-        <v>0.6181</v>
+        <v>0.5342</v>
       </c>
       <c r="H89" t="n">
-        <v>0.5813</v>
+        <v>0.4938</v>
       </c>
     </row>
     <row r="90">
@@ -2766,10 +2766,10 @@
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>0.4773</v>
+        <v>0.4428</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4335</v>
+        <v>0.4066</v>
       </c>
     </row>
     <row r="91">
@@ -2792,10 +2792,10 @@
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
-        <v>0.6018</v>
+        <v>0.5508</v>
       </c>
       <c r="H91" t="n">
-        <v>0.554</v>
+        <v>0.5063</v>
       </c>
     </row>
     <row r="92">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.7806</v>
+        <v>0.7874</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7287</v>
+        <v>0.7366</v>
       </c>
     </row>
     <row r="93">
@@ -2844,10 +2844,10 @@
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
-        <v>0.8623</v>
+        <v>0.8686</v>
       </c>
       <c r="H93" t="n">
-        <v>0.8326</v>
+        <v>0.8408</v>
       </c>
     </row>
     <row r="94">
@@ -2870,10 +2870,10 @@
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
-        <v>0.8215</v>
+        <v>0.7996</v>
       </c>
       <c r="H94" t="n">
-        <v>0.7849</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="95">
@@ -2896,10 +2896,10 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0.6681</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6264999999999999</v>
+        <v>0.6336000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -2922,10 +2922,10 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0.9161</v>
+        <v>0.9181</v>
       </c>
       <c r="H96" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.8966</v>
       </c>
     </row>
     <row r="97">
@@ -2948,10 +2948,10 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0.8917</v>
+        <v>0.8895</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8602</v>
+        <v>0.8567</v>
       </c>
     </row>
     <row r="98">
@@ -2974,10 +2974,10 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>0.9761</v>
+        <v>0.9668</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9578</v>
       </c>
     </row>
     <row r="99">
@@ -3000,10 +3000,10 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>0.9576</v>
+        <v>0.9629</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9469</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="100">
@@ -3026,10 +3026,10 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>0.9718</v>
+        <v>0.9731</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9671</v>
+        <v>0.9681999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -3494,10 +3494,10 @@
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="n">
-        <v>0.4232</v>
+        <v>0.296</v>
       </c>
       <c r="H118" t="n">
-        <v>0.378</v>
+        <v>0.2662</v>
       </c>
     </row>
     <row r="119">
@@ -3520,10 +3520,10 @@
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>0.2521</v>
+        <v>0.2185</v>
       </c>
       <c r="H119" t="n">
-        <v>0.2008</v>
+        <v>0.1736</v>
       </c>
     </row>
     <row r="120">
@@ -3546,10 +3546,10 @@
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H120" t="n">
-        <v>0.3134</v>
+        <v>0.2753</v>
       </c>
     </row>
     <row r="121">
@@ -3572,10 +3572,10 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.2713</v>
+        <v>0.2634</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2194</v>
+        <v>0.2126</v>
       </c>
     </row>
     <row r="122">
@@ -3598,10 +3598,10 @@
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="n">
-        <v>0.6733</v>
+        <v>0.6754</v>
       </c>
       <c r="H122" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6553</v>
       </c>
     </row>
     <row r="123">
@@ -3624,10 +3624,10 @@
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="n">
-        <v>0.5929</v>
+        <v>0.539</v>
       </c>
       <c r="H123" t="n">
-        <v>0.5557</v>
+        <v>0.4989</v>
       </c>
     </row>
     <row r="124">
@@ -3702,10 +3702,10 @@
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="n">
-        <v>0.7055</v>
+        <v>0.6885</v>
       </c>
       <c r="H126" t="n">
-        <v>0.6586</v>
+        <v>0.6442</v>
       </c>
     </row>
     <row r="127">
@@ -3728,10 +3728,10 @@
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="n">
-        <v>0.9427</v>
+        <v>0.9133</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9218</v>
+        <v>0.8843</v>
       </c>
     </row>
     <row r="128">
@@ -3754,10 +3754,10 @@
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="n">
-        <v>0.9073</v>
+        <v>0.923</v>
       </c>
       <c r="H128" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.9001</v>
       </c>
     </row>
     <row r="129">
@@ -3780,10 +3780,10 @@
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="n">
-        <v>0.9418</v>
+        <v>0.9411</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9263</v>
       </c>
     </row>
     <row r="130">
@@ -3806,10 +3806,10 @@
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="n">
-        <v>0.9768</v>
+        <v>0.9798</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9697</v>
+        <v>0.9742</v>
       </c>
     </row>
     <row r="131">
@@ -3832,10 +3832,10 @@
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="n">
-        <v>0.9769</v>
+        <v>0.9721</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9699</v>
+        <v>0.9635</v>
       </c>
     </row>
     <row r="132">
@@ -4248,10 +4248,10 @@
       </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="n">
-        <v>0.3</v>
+        <v>0.1827</v>
       </c>
       <c r="H147" t="n">
-        <v>0.2662</v>
+        <v>0.1627</v>
       </c>
     </row>
     <row r="148">
@@ -4274,10 +4274,10 @@
       </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="n">
-        <v>0.1343</v>
+        <v>0.111</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1117</v>
+        <v>0.09080000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -4300,10 +4300,10 @@
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="n">
-        <v>0.2144</v>
+        <v>0.1717</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1967</v>
+        <v>0.1497</v>
       </c>
     </row>
     <row r="150">
@@ -4326,10 +4326,10 @@
       </c>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>0.1674</v>
+        <v>0.1592</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1377</v>
+        <v>0.1314</v>
       </c>
     </row>
     <row r="151">
@@ -4352,10 +4352,10 @@
       </c>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>0.3463</v>
+        <v>0.3447</v>
       </c>
       <c r="H151" t="n">
-        <v>0.3267</v>
+        <v>0.3246</v>
       </c>
     </row>
     <row r="152">
@@ -4378,10 +4378,10 @@
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>0.4647</v>
+        <v>0.3991</v>
       </c>
       <c r="H152" t="n">
-        <v>0.4388</v>
+        <v>0.3746</v>
       </c>
     </row>
     <row r="153">
@@ -4404,10 +4404,10 @@
       </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="n">
-        <v>0.3641</v>
+        <v>0.3394</v>
       </c>
       <c r="H153" t="n">
-        <v>0.3125</v>
+        <v>0.2974</v>
       </c>
     </row>
     <row r="154">
@@ -4430,10 +4430,10 @@
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
-        <v>0.6605</v>
+        <v>0.649</v>
       </c>
       <c r="H154" t="n">
-        <v>0.606</v>
+        <v>0.5956</v>
       </c>
     </row>
     <row r="155">
@@ -4456,10 +4456,10 @@
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="n">
-        <v>0.5794</v>
+        <v>0.5429</v>
       </c>
       <c r="H155" t="n">
-        <v>0.5313</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
@@ -4482,10 +4482,10 @@
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>0.8973</v>
+        <v>0.8464</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -4508,10 +4508,10 @@
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="n">
-        <v>0.8273</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="H157" t="n">
-        <v>0.7914</v>
+        <v>0.8087</v>
       </c>
     </row>
     <row r="158">
@@ -4534,10 +4534,10 @@
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="n">
-        <v>0.8931</v>
+        <v>0.8875</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8668</v>
+        <v>0.8598</v>
       </c>
     </row>
     <row r="159">
@@ -4560,10 +4560,10 @@
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="n">
-        <v>0.9506</v>
+        <v>0.9526</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9424</v>
+        <v>0.9441000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -4586,10 +4586,10 @@
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9624</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9617</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="161">
@@ -5002,10 +5002,10 @@
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="n">
-        <v>0.3553</v>
+        <v>0.2916</v>
       </c>
       <c r="H176" t="n">
-        <v>0.3141</v>
+        <v>0.2615</v>
       </c>
     </row>
     <row r="177">
@@ -5028,10 +5028,10 @@
       </c>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="n">
-        <v>0.1633</v>
+        <v>0.1707</v>
       </c>
       <c r="H177" t="n">
-        <v>0.13</v>
+        <v>0.1391</v>
       </c>
     </row>
     <row r="178">
@@ -5054,10 +5054,10 @@
       </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="n">
-        <v>0.2383</v>
+        <v>0.2463</v>
       </c>
       <c r="H178" t="n">
-        <v>0.2042</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="179">
@@ -5080,10 +5080,10 @@
       </c>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>0.2151</v>
+        <v>0.24</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1785</v>
+        <v>0.2004</v>
       </c>
     </row>
     <row r="180">
@@ -5106,10 +5106,10 @@
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>0.4443</v>
+        <v>0.5011</v>
       </c>
       <c r="H180" t="n">
-        <v>0.4071</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="181">
@@ -5132,10 +5132,10 @@
       </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
-        <v>0.5612</v>
+        <v>0.6254</v>
       </c>
       <c r="H181" t="n">
-        <v>0.5353</v>
+        <v>0.6009</v>
       </c>
     </row>
     <row r="182">
@@ -5158,10 +5158,10 @@
       </c>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="n">
-        <v>0.3684</v>
+        <v>0.4121</v>
       </c>
       <c r="H182" t="n">
-        <v>0.3278</v>
+        <v>0.3611</v>
       </c>
     </row>
     <row r="183">
@@ -5184,10 +5184,10 @@
       </c>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="n">
-        <v>0.7336</v>
+        <v>0.7688</v>
       </c>
       <c r="H183" t="n">
-        <v>0.6855</v>
+        <v>0.7241</v>
       </c>
     </row>
     <row r="184">
@@ -5210,10 +5210,10 @@
       </c>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="n">
-        <v>0.6271</v>
+        <v>0.6684</v>
       </c>
       <c r="H184" t="n">
-        <v>0.5879</v>
+        <v>0.6234</v>
       </c>
     </row>
     <row r="185">
@@ -5236,10 +5236,10 @@
       </c>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9045</v>
       </c>
       <c r="H185" t="n">
-        <v>0.9061</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="186">
@@ -5262,10 +5262,10 @@
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.9032</v>
       </c>
       <c r="H186" t="n">
-        <v>0.8246</v>
+        <v>0.8754999999999999</v>
       </c>
     </row>
     <row r="187">
@@ -5288,10 +5288,10 @@
       </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>0.9052</v>
+        <v>0.9181</v>
       </c>
       <c r="H187" t="n">
-        <v>0.8832</v>
+        <v>0.8999</v>
       </c>
     </row>
     <row r="188">
@@ -5314,10 +5314,10 @@
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9724</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9535</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="189">
@@ -5340,10 +5340,10 @@
       </c>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>0.971</v>
+        <v>0.9696</v>
       </c>
       <c r="H189" t="n">
-        <v>0.9613</v>
+        <v>0.9596</v>
       </c>
     </row>
     <row r="190">
@@ -5756,10 +5756,10 @@
       </c>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>0.4795</v>
+        <v>0.3682</v>
       </c>
       <c r="H205" t="n">
-        <v>0.442</v>
+        <v>0.3339</v>
       </c>
     </row>
     <row r="206">
@@ -5782,10 +5782,10 @@
       </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="n">
-        <v>0.2938</v>
+        <v>0.2658</v>
       </c>
       <c r="H206" t="n">
-        <v>0.2491</v>
+        <v>0.2252</v>
       </c>
     </row>
     <row r="207">
@@ -5808,10 +5808,10 @@
       </c>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>0.4214</v>
+        <v>0.3866</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3823</v>
+        <v>0.3434</v>
       </c>
     </row>
     <row r="208">
@@ -5834,10 +5834,10 @@
       </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>0.3735</v>
+        <v>0.3664</v>
       </c>
       <c r="H208" t="n">
-        <v>0.3319</v>
+        <v>0.3251</v>
       </c>
     </row>
     <row r="209">
@@ -5886,10 +5886,10 @@
       </c>
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="n">
-        <v>0.6875</v>
+        <v>0.7026</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6359</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="211">
@@ -5912,10 +5912,10 @@
       </c>
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="n">
-        <v>0.6722</v>
+        <v>0.6389</v>
       </c>
       <c r="H211" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.5879</v>
       </c>
     </row>
     <row r="212">
@@ -5938,10 +5938,10 @@
       </c>
       <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>0.8307</v>
+        <v>0.8329</v>
       </c>
       <c r="H212" t="n">
-        <v>0.7976</v>
+        <v>0.7994</v>
       </c>
     </row>
     <row r="213">
@@ -5990,10 +5990,10 @@
       </c>
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>0.9573</v>
+        <v>0.9295</v>
       </c>
       <c r="H214" t="n">
-        <v>0.9442</v>
+        <v>0.9104</v>
       </c>
     </row>
     <row r="215">
@@ -6016,10 +6016,10 @@
       </c>
       <c r="F215" t="inlineStr"/>
       <c r="G215" t="n">
-        <v>0.9135</v>
+        <v>0.9352</v>
       </c>
       <c r="H215" t="n">
-        <v>0.8913</v>
+        <v>0.9154</v>
       </c>
     </row>
     <row r="216">
@@ -6042,10 +6042,10 @@
       </c>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="n">
-        <v>0.948</v>
+        <v>0.9479</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9347</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="217">
@@ -6068,10 +6068,10 @@
       </c>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>0.9792999999999999</v>
+        <v>0.9821</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9737</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="218">
@@ -6094,10 +6094,10 @@
       </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="n">
-        <v>0.9796</v>
+        <v>0.9727</v>
       </c>
       <c r="H218" t="n">
-        <v>0.9739</v>
+        <v>0.9654</v>
       </c>
     </row>
     <row r="219">
@@ -6510,10 +6510,10 @@
       </c>
       <c r="F234" t="inlineStr"/>
       <c r="G234" t="n">
-        <v>0.2026</v>
+        <v>0.1072</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1696</v>
+        <v>0.0839</v>
       </c>
     </row>
     <row r="235">
@@ -6536,10 +6536,10 @@
       </c>
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="n">
-        <v>0.0761</v>
+        <v>0.0689</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0573</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="236">
@@ -6562,10 +6562,10 @@
       </c>
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="n">
-        <v>0.1166</v>
+        <v>0.101</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0927</v>
+        <v>0.0771</v>
       </c>
     </row>
     <row r="237">
@@ -6588,10 +6588,10 @@
       </c>
       <c r="F237" t="inlineStr"/>
       <c r="G237" t="n">
-        <v>0.1064</v>
+        <v>0.1034</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0839</v>
+        <v>0.0819</v>
       </c>
     </row>
     <row r="238">
@@ -6640,10 +6640,10 @@
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="n">
-        <v>0.394</v>
+        <v>0.4044</v>
       </c>
       <c r="H239" t="n">
-        <v>0.3395</v>
+        <v>0.351</v>
       </c>
     </row>
     <row r="240">
@@ -6666,10 +6666,10 @@
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="n">
-        <v>0.3145</v>
+        <v>0.2759</v>
       </c>
       <c r="H240" t="n">
-        <v>0.2664</v>
+        <v>0.2312</v>
       </c>
     </row>
     <row r="241">
@@ -6692,10 +6692,10 @@
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="n">
-        <v>0.2024</v>
+        <v>0.2006</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1693</v>
+        <v>0.1671</v>
       </c>
     </row>
     <row r="242">
@@ -6718,10 +6718,10 @@
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="n">
-        <v>0.4385</v>
+        <v>0.4107</v>
       </c>
       <c r="H242" t="n">
-        <v>0.4112</v>
+        <v>0.3847</v>
       </c>
     </row>
     <row r="243">
@@ -6744,10 +6744,10 @@
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="n">
-        <v>0.8312</v>
+        <v>0.7381</v>
       </c>
       <c r="H243" t="n">
-        <v>0.8034</v>
+        <v>0.7009</v>
       </c>
     </row>
     <row r="244">
@@ -6770,10 +6770,10 @@
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="n">
-        <v>0.7167</v>
+        <v>0.7549</v>
       </c>
       <c r="H244" t="n">
-        <v>0.6804</v>
+        <v>0.714</v>
       </c>
     </row>
     <row r="245">
@@ -6822,10 +6822,10 @@
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>0.9175</v>
+        <v>0.9252</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9042</v>
+        <v>0.9119</v>
       </c>
     </row>
     <row r="247">
@@ -6848,10 +6848,10 @@
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="n">
-        <v>0.9374</v>
+        <v>0.923</v>
       </c>
       <c r="H247" t="n">
-        <v>0.9221</v>
+        <v>0.9028</v>
       </c>
     </row>
     <row r="248">
@@ -7264,10 +7264,10 @@
       </c>
       <c r="F263" t="inlineStr"/>
       <c r="G263" t="n">
-        <v>0.2657</v>
+        <v>0.1756</v>
       </c>
       <c r="H263" t="n">
-        <v>0.2238</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="264">
@@ -7290,10 +7290,10 @@
       </c>
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="n">
-        <v>0.1307</v>
+        <v>0.1233</v>
       </c>
       <c r="H264" t="n">
-        <v>0.0997</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="265">
@@ -7316,10 +7316,10 @@
       </c>
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>0.1882</v>
+        <v>0.1665</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1513</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="266">
@@ -7342,10 +7342,10 @@
       </c>
       <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>0.1398</v>
+        <v>0.1433</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1083</v>
+        <v>0.1105</v>
       </c>
     </row>
     <row r="267">
@@ -7368,10 +7368,10 @@
       </c>
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>0.3414</v>
+        <v>0.3558</v>
       </c>
       <c r="H267" t="n">
-        <v>0.2945</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="268">
@@ -7394,10 +7394,10 @@
       </c>
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="n">
-        <v>0.4687</v>
+        <v>0.5</v>
       </c>
       <c r="H268" t="n">
-        <v>0.4206</v>
+        <v>0.4571</v>
       </c>
     </row>
     <row r="269">
@@ -7420,10 +7420,10 @@
       </c>
       <c r="F269" t="inlineStr"/>
       <c r="G269" t="n">
-        <v>0.4121</v>
+        <v>0.3766</v>
       </c>
       <c r="H269" t="n">
-        <v>0.3729</v>
+        <v>0.3316</v>
       </c>
     </row>
     <row r="270">
@@ -7472,10 +7472,10 @@
       </c>
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>0.5888</v>
+        <v>0.6153</v>
       </c>
       <c r="H271" t="n">
-        <v>0.5615</v>
+        <v>0.5893</v>
       </c>
     </row>
     <row r="272">
@@ -7498,10 +7498,10 @@
       </c>
       <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>0.8963</v>
+        <v>0.8416</v>
       </c>
       <c r="H272" t="n">
-        <v>0.8633</v>
+        <v>0.7959000000000001</v>
       </c>
     </row>
     <row r="273">
@@ -7524,10 +7524,10 @@
       </c>
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>0.7985</v>
+        <v>0.8426</v>
       </c>
       <c r="H273" t="n">
-        <v>0.763</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="274">
@@ -7550,10 +7550,10 @@
       </c>
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="n">
-        <v>0.8494</v>
+        <v>0.8529</v>
       </c>
       <c r="H274" t="n">
-        <v>0.8177</v>
+        <v>0.8229</v>
       </c>
     </row>
     <row r="275">
@@ -7576,10 +7576,10 @@
       </c>
       <c r="F275" t="inlineStr"/>
       <c r="G275" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9489</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9228</v>
+        <v>0.9337</v>
       </c>
     </row>
     <row r="276">
@@ -7602,10 +7602,10 @@
       </c>
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="n">
-        <v>0.9574</v>
+        <v>0.9495</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9483</v>
+        <v>0.9395</v>
       </c>
     </row>
     <row r="277">
@@ -8018,10 +8018,10 @@
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
-        <v>0.0567</v>
+        <v>0.0596</v>
       </c>
       <c r="H292" t="n">
-        <v>0.0471</v>
+        <v>0.0497</v>
       </c>
     </row>
     <row r="293">
@@ -8044,10 +8044,10 @@
       </c>
       <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
-        <v>0.0218</v>
+        <v>0.0318</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0168</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="294">
@@ -8070,10 +8070,10 @@
       </c>
       <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
-        <v>0.035</v>
+        <v>0.0501</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0273</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="295">
@@ -8096,10 +8096,10 @@
       </c>
       <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>0.0307</v>
+        <v>0.0422</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0239</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="296">
@@ -8122,10 +8122,10 @@
       </c>
       <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.1157</v>
       </c>
       <c r="H296" t="n">
-        <v>0.0573</v>
+        <v>0.0867</v>
       </c>
     </row>
     <row r="297">
@@ -8148,10 +8148,10 @@
       </c>
       <c r="F297" t="inlineStr"/>
       <c r="G297" t="n">
-        <v>0.1275</v>
+        <v>0.19</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1027</v>
+        <v>0.1536</v>
       </c>
     </row>
     <row r="298">
@@ -8174,10 +8174,10 @@
       </c>
       <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>0.0939</v>
+        <v>0.122</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0721</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="299">
@@ -8200,10 +8200,10 @@
       </c>
       <c r="F299" t="inlineStr"/>
       <c r="G299" t="n">
-        <v>0.0558</v>
+        <v>0.0896</v>
       </c>
       <c r="H299" t="n">
-        <v>0.0427</v>
+        <v>0.07049999999999999</v>
       </c>
     </row>
     <row r="300">
@@ -8226,10 +8226,10 @@
       </c>
       <c r="F300" t="inlineStr"/>
       <c r="G300" t="n">
-        <v>0.1966</v>
+        <v>0.2991</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1688</v>
+        <v>0.2619</v>
       </c>
     </row>
     <row r="301">
@@ -8252,10 +8252,10 @@
       </c>
       <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>0.1367</v>
+        <v>0.2041</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1037</v>
+        <v>0.1584</v>
       </c>
     </row>
     <row r="302">
@@ -8278,10 +8278,10 @@
       </c>
       <c r="F302" t="inlineStr"/>
       <c r="G302" t="n">
-        <v>0.3566</v>
+        <v>0.5285</v>
       </c>
       <c r="H302" t="n">
-        <v>0.32</v>
+        <v>0.4995</v>
       </c>
     </row>
     <row r="303">
@@ -8304,10 +8304,10 @@
       </c>
       <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>0.4378</v>
+        <v>0.5675</v>
       </c>
       <c r="H303" t="n">
-        <v>0.3928</v>
+        <v>0.5322</v>
       </c>
     </row>
     <row r="304">
@@ -8330,10 +8330,10 @@
       </c>
       <c r="F304" t="inlineStr"/>
       <c r="G304" t="n">
-        <v>0.6926</v>
+        <v>0.8305</v>
       </c>
       <c r="H304" t="n">
-        <v>0.6599</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="305">
@@ -8356,10 +8356,10 @@
       </c>
       <c r="F305" t="inlineStr"/>
       <c r="G305" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.8507</v>
       </c>
       <c r="H305" t="n">
-        <v>0.7533</v>
+        <v>0.8131</v>
       </c>
     </row>
     <row r="306">
@@ -8772,10 +8772,10 @@
       </c>
       <c r="F321" t="inlineStr"/>
       <c r="G321" t="n">
-        <v>0.1105</v>
+        <v>0.0482</v>
       </c>
       <c r="H321" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="322">
@@ -8798,10 +8798,10 @@
       </c>
       <c r="F322" t="inlineStr"/>
       <c r="G322" t="n">
-        <v>0.0405</v>
+        <v>0.0282</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0306</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="323">
@@ -8824,10 +8824,10 @@
       </c>
       <c r="F323" t="inlineStr"/>
       <c r="G323" t="n">
-        <v>0.068</v>
+        <v>0.0492</v>
       </c>
       <c r="H323" t="n">
-        <v>0.0529</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="324">
@@ -8850,10 +8850,10 @@
       </c>
       <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>0.0531</v>
+        <v>0.0458</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0424</v>
+        <v>0.0371</v>
       </c>
     </row>
     <row r="325">
@@ -8876,10 +8876,10 @@
       </c>
       <c r="F325" t="inlineStr"/>
       <c r="G325" t="n">
-        <v>0.1205</v>
+        <v>0.0999</v>
       </c>
       <c r="H325" t="n">
-        <v>0.0927</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="326">
@@ -8902,10 +8902,10 @@
       </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="n">
-        <v>0.2086</v>
+        <v>0.1913</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1727</v>
+        <v>0.1568</v>
       </c>
     </row>
     <row r="327">
@@ -8928,10 +8928,10 @@
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>0.1754</v>
+        <v>0.1245</v>
       </c>
       <c r="H327" t="n">
-        <v>0.1416</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="328">
@@ -8954,10 +8954,10 @@
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="n">
-        <v>0.1087</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="H328" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="329">
@@ -8980,10 +8980,10 @@
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>0.3196</v>
+        <v>0.286</v>
       </c>
       <c r="H329" t="n">
-        <v>0.2833</v>
+        <v>0.2451</v>
       </c>
     </row>
     <row r="330">
@@ -9006,10 +9006,10 @@
       </c>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="n">
-        <v>0.237</v>
+        <v>0.1925</v>
       </c>
       <c r="H330" t="n">
-        <v>0.2015</v>
+        <v>0.1574</v>
       </c>
     </row>
     <row r="331">
@@ -9032,10 +9032,10 @@
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>0.68</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="H331" t="n">
-        <v>0.6434</v>
+        <v>0.4715</v>
       </c>
     </row>
     <row r="332">
@@ -9058,10 +9058,10 @@
       </c>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>0.6454</v>
+        <v>0.5757</v>
       </c>
       <c r="H332" t="n">
-        <v>0.613</v>
+        <v>0.5522</v>
       </c>
     </row>
     <row r="333">
@@ -9084,10 +9084,10 @@
       </c>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="n">
-        <v>0.8305</v>
+        <v>0.8196</v>
       </c>
       <c r="H333" t="n">
-        <v>0.8012</v>
+        <v>0.7895</v>
       </c>
     </row>
     <row r="334">
@@ -9110,10 +9110,10 @@
       </c>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>0.8925</v>
+        <v>0.836</v>
       </c>
       <c r="H334" t="n">
-        <v>0.8681</v>
+        <v>0.8036</v>
       </c>
     </row>
     <row r="335">
@@ -9526,10 +9526,10 @@
       </c>
       <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>0.0808</v>
+        <v>0.0505</v>
       </c>
       <c r="H350" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="351">
@@ -9552,10 +9552,10 @@
       </c>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="n">
-        <v>0.0317</v>
+        <v>0.0266</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0242</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="352">
@@ -9578,10 +9578,10 @@
       </c>
       <c r="F352" t="inlineStr"/>
       <c r="G352" t="n">
-        <v>0.0479</v>
+        <v>0.0412</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0391</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="353">
@@ -9604,10 +9604,10 @@
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>0.0329</v>
+        <v>0.0318</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0282</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="354">
@@ -9630,10 +9630,10 @@
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>0.0731</v>
+        <v>0.0737</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0582</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row r="355">
@@ -9656,10 +9656,10 @@
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>0.1332</v>
+        <v>0.1402</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1069</v>
+        <v>0.1125</v>
       </c>
     </row>
     <row r="356">
@@ -9682,10 +9682,10 @@
       </c>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>0.1168</v>
+        <v>0.1001</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0948</v>
+        <v>0.0819</v>
       </c>
     </row>
     <row r="357">
@@ -9708,10 +9708,10 @@
       </c>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="n">
-        <v>0.0653</v>
+        <v>0.0654</v>
       </c>
       <c r="H357" t="n">
-        <v>0.052</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="358">
@@ -9760,10 +9760,10 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>0.1823</v>
+        <v>0.1771</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1506</v>
+        <v>0.1471</v>
       </c>
     </row>
     <row r="360">
@@ -9786,10 +9786,10 @@
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>0.6072</v>
+        <v>0.4678</v>
       </c>
       <c r="H360" t="n">
-        <v>0.5622</v>
+        <v>0.4325</v>
       </c>
     </row>
     <row r="361">
@@ -9812,10 +9812,10 @@
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>0.387</v>
+        <v>0.4478</v>
       </c>
       <c r="H361" t="n">
-        <v>0.3546</v>
+        <v>0.4243</v>
       </c>
     </row>
     <row r="362">
@@ -9838,10 +9838,10 @@
       </c>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>0.7725</v>
+        <v>0.7852</v>
       </c>
       <c r="H362" t="n">
-        <v>0.7262</v>
+        <v>0.7431</v>
       </c>
     </row>
     <row r="363">
@@ -9864,10 +9864,10 @@
       </c>
       <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>0.8205</v>
+        <v>0.77</v>
       </c>
       <c r="H363" t="n">
-        <v>0.7914</v>
+        <v>0.7423999999999999</v>
       </c>
     </row>
     <row r="364">
@@ -10280,10 +10280,10 @@
       </c>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="n">
-        <v>0.0385</v>
+        <v>0.0205</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0299</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="380">
@@ -10332,10 +10332,10 @@
       </c>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>0.0218</v>
+        <v>0.0173</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0188</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="382">
@@ -10384,10 +10384,10 @@
       </c>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>0.0303</v>
+        <v>0.0258</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0232</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="384">
@@ -10410,10 +10410,10 @@
       </c>
       <c r="F384" t="inlineStr"/>
       <c r="G384" t="n">
-        <v>0.0576</v>
+        <v>0.0559</v>
       </c>
       <c r="H384" t="n">
-        <v>0.0494</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="385">
@@ -10436,10 +10436,10 @@
       </c>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>0.0465</v>
+        <v>0.0339</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0378</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="386">
@@ -10462,10 +10462,10 @@
       </c>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>0.0263</v>
+        <v>0.0224</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0207</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="387">
@@ -10488,10 +10488,10 @@
       </c>
       <c r="F387" t="inlineStr"/>
       <c r="G387" t="n">
-        <v>0.0958</v>
+        <v>0.0881</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0825</v>
+        <v>0.07480000000000001</v>
       </c>
     </row>
     <row r="388">
@@ -10514,10 +10514,10 @@
       </c>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="n">
-        <v>0.0772</v>
+        <v>0.0663</v>
       </c>
       <c r="H388" t="n">
-        <v>0.059</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="389">
@@ -10540,10 +10540,10 @@
       </c>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>0.3401</v>
+        <v>0.2052</v>
       </c>
       <c r="H389" t="n">
-        <v>0.3074</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="390">
@@ -10566,10 +10566,10 @@
       </c>
       <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>0.1988</v>
+        <v>0.2105</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1695</v>
+        <v>0.1804</v>
       </c>
     </row>
     <row r="391">
@@ -10592,10 +10592,10 @@
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>0.2738</v>
+        <v>0.2569</v>
       </c>
       <c r="H391" t="n">
-        <v>0.2275</v>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="392">
@@ -10618,10 +10618,10 @@
       </c>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>0.6125</v>
+        <v>0.519</v>
       </c>
       <c r="H392" t="n">
-        <v>0.5823</v>
+        <v>0.4764</v>
       </c>
     </row>
     <row r="393">
@@ -11034,10 +11034,10 @@
       </c>
       <c r="F408" t="inlineStr"/>
       <c r="G408" t="n">
-        <v>0.0392</v>
+        <v>0.0304</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0307</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="409">
@@ -11060,10 +11060,10 @@
       </c>
       <c r="F409" t="inlineStr"/>
       <c r="G409" t="n">
-        <v>0.016</v>
+        <v>0.0166</v>
       </c>
       <c r="H409" t="n">
-        <v>0.0119</v>
+        <v>0.0122</v>
       </c>
     </row>
     <row r="410">
@@ -11086,10 +11086,10 @@
       </c>
       <c r="F410" t="inlineStr"/>
       <c r="G410" t="n">
-        <v>0.0217</v>
+        <v>0.0235</v>
       </c>
       <c r="H410" t="n">
-        <v>0.0169</v>
+        <v>0.0184</v>
       </c>
     </row>
     <row r="411">
@@ -11138,10 +11138,10 @@
       </c>
       <c r="F412" t="inlineStr"/>
       <c r="G412" t="n">
-        <v>0.0301</v>
+        <v>0.0365</v>
       </c>
       <c r="H412" t="n">
-        <v>0.0231</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="413">
@@ -11164,10 +11164,10 @@
       </c>
       <c r="F413" t="inlineStr"/>
       <c r="G413" t="n">
-        <v>0.0383</v>
+        <v>0.0474</v>
       </c>
       <c r="H413" t="n">
-        <v>0.0307</v>
+        <v>0.0376</v>
       </c>
     </row>
     <row r="414">
@@ -11190,10 +11190,10 @@
       </c>
       <c r="F414" t="inlineStr"/>
       <c r="G414" t="n">
-        <v>0.0387</v>
+        <v>0.0404</v>
       </c>
       <c r="H414" t="n">
-        <v>0.029</v>
+        <v>0.0304</v>
       </c>
     </row>
     <row r="415">
@@ -11216,10 +11216,10 @@
       </c>
       <c r="F415" t="inlineStr"/>
       <c r="G415" t="n">
-        <v>0.0261</v>
+        <v>0.0346</v>
       </c>
       <c r="H415" t="n">
-        <v>0.0204</v>
+        <v>0.0273</v>
       </c>
     </row>
     <row r="416">
@@ -11242,10 +11242,10 @@
       </c>
       <c r="F416" t="inlineStr"/>
       <c r="G416" t="n">
-        <v>0.0779</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="H416" t="n">
-        <v>0.0626</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="417">
@@ -11268,10 +11268,10 @@
       </c>
       <c r="F417" t="inlineStr"/>
       <c r="G417" t="n">
-        <v>0.0517</v>
+        <v>0.0605</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0426</v>
+        <v>0.0505</v>
       </c>
     </row>
     <row r="418">
@@ -11294,10 +11294,10 @@
       </c>
       <c r="F418" t="inlineStr"/>
       <c r="G418" t="n">
-        <v>0.2467</v>
+        <v>0.1869</v>
       </c>
       <c r="H418" t="n">
-        <v>0.2092</v>
+        <v>0.1493</v>
       </c>
     </row>
     <row r="419">
@@ -11320,10 +11320,10 @@
       </c>
       <c r="F419" t="inlineStr"/>
       <c r="G419" t="n">
-        <v>0.1319</v>
+        <v>0.1964</v>
       </c>
       <c r="H419" t="n">
-        <v>0.1075</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="420">
@@ -11346,10 +11346,10 @@
       </c>
       <c r="F420" t="inlineStr"/>
       <c r="G420" t="n">
-        <v>0.2086</v>
+        <v>0.2576</v>
       </c>
       <c r="H420" t="n">
-        <v>0.1795</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="421">
@@ -11372,10 +11372,10 @@
       </c>
       <c r="F421" t="inlineStr"/>
       <c r="G421" t="n">
-        <v>0.4177</v>
+        <v>0.5236</v>
       </c>
       <c r="H421" t="n">
-        <v>0.3875</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="422">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6661</v>
+        <v>0.6595</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6318</v>
+        <v>0.6266</v>
       </c>
     </row>
     <row r="9">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.9576</v>
+        <v>0.9594</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9495</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="14">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.984</v>
+        <v>0.9845</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9795</v>
+        <v>0.9799</v>
       </c>
     </row>
     <row r="15">
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7748</v>
+        <v>0.7627</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7342</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="38">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.9795</v>
+        <v>0.9808</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9734</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="43">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.6566</v>
+        <v>0.6434</v>
       </c>
       <c r="H66" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.5995</v>
       </c>
     </row>
     <row r="67">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.967</v>
+        <v>0.9701</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9588</v>
+        <v>0.9616</v>
       </c>
     </row>
     <row r="72">
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.6749000000000001</v>
+        <v>0.6631</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6188</v>
       </c>
     </row>
     <row r="96">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.9731</v>
+        <v>0.9735</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9686</v>
       </c>
     </row>
     <row r="101">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.467</v>
+        <v>0.4491</v>
       </c>
       <c r="H124" t="n">
-        <v>0.4254</v>
+        <v>0.4112</v>
       </c>
     </row>
     <row r="125">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.9411</v>
+        <v>0.9432</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9263</v>
+        <v>0.9287</v>
       </c>
     </row>
     <row r="130">
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.3394</v>
+        <v>0.331</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2974</v>
+        <v>0.2898</v>
       </c>
     </row>
     <row r="154">
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.8875</v>
+        <v>0.8931</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8598</v>
+        <v>0.8668</v>
       </c>
     </row>
     <row r="159">
@@ -6606,10 +6606,10 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.4121</v>
+        <v>0.4021</v>
       </c>
       <c r="H182" t="n">
-        <v>0.3611</v>
+        <v>0.3539</v>
       </c>
     </row>
     <row r="183">
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.9181</v>
+        <v>0.9193</v>
       </c>
       <c r="H187" t="n">
-        <v>0.8999</v>
+        <v>0.9009</v>
       </c>
     </row>
     <row r="188">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.3682</v>
+        <v>0.3734</v>
       </c>
       <c r="H205" t="n">
-        <v>0.3339</v>
+        <v>0.3405</v>
       </c>
     </row>
     <row r="206">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.2658</v>
+        <v>0.28</v>
       </c>
       <c r="H206" t="n">
-        <v>0.2252</v>
+        <v>0.2373</v>
       </c>
     </row>
     <row r="207">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.3866</v>
+        <v>0.4005</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3434</v>
+        <v>0.3566</v>
       </c>
     </row>
     <row r="208">
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.3664</v>
+        <v>0.3812</v>
       </c>
       <c r="H208" t="n">
-        <v>0.3251</v>
+        <v>0.3369</v>
       </c>
     </row>
     <row r="209">
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.5746</v>
+        <v>0.5888</v>
       </c>
       <c r="H209" t="n">
-        <v>0.533</v>
+        <v>0.5508999999999999</v>
       </c>
     </row>
     <row r="210">
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.7026</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="H210" t="n">
-        <v>0.6606</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="211">
@@ -7592,10 +7592,10 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.6389</v>
+        <v>0.6461</v>
       </c>
       <c r="H211" t="n">
-        <v>0.5879</v>
+        <v>0.5979</v>
       </c>
     </row>
     <row r="212">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.8329</v>
+        <v>0.8419</v>
       </c>
       <c r="H212" t="n">
-        <v>0.7994</v>
+        <v>0.8083</v>
       </c>
     </row>
     <row r="213">
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.7339</v>
+        <v>0.7357</v>
       </c>
       <c r="H213" t="n">
-        <v>0.6923</v>
+        <v>0.6938</v>
       </c>
     </row>
     <row r="214">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.9295</v>
+        <v>0.93</v>
       </c>
       <c r="H214" t="n">
-        <v>0.9104</v>
+        <v>0.9111</v>
       </c>
     </row>
     <row r="215">
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.9352</v>
+        <v>0.9381</v>
       </c>
       <c r="H215" t="n">
-        <v>0.9154</v>
+        <v>0.9194</v>
       </c>
     </row>
     <row r="216">
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.9479</v>
+        <v>0.9534</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9346</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="217">
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.9821</v>
+        <v>0.983</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9776</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="218">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.9727</v>
+        <v>0.9747</v>
       </c>
       <c r="H218" t="n">
-        <v>0.9654</v>
+        <v>0.9674</v>
       </c>
     </row>
     <row r="219">
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.2006</v>
+        <v>0.1917</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1671</v>
+        <v>0.1581</v>
       </c>
     </row>
     <row r="242">
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.8143</v>
+        <v>0.8177</v>
       </c>
       <c r="H245" t="n">
-        <v>0.779</v>
+        <v>0.7818000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.9252</v>
+        <v>0.9268</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9119</v>
+        <v>0.9143</v>
       </c>
     </row>
     <row r="247">
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.3077</v>
+        <v>0.3062</v>
       </c>
       <c r="H270" t="n">
-        <v>0.2661</v>
+        <v>0.2643</v>
       </c>
     </row>
     <row r="271">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.8529</v>
+        <v>0.8622</v>
       </c>
       <c r="H274" t="n">
-        <v>0.8229</v>
+        <v>0.8317</v>
       </c>
     </row>
     <row r="275">
@@ -9802,10 +9802,10 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.9495</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9395</v>
+        <v>0.9401</v>
       </c>
     </row>
     <row r="277">
@@ -10584,10 +10584,10 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.0896</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H299" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="300">
@@ -10720,10 +10720,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0.5675</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="H303" t="n">
-        <v>0.5322</v>
+        <v>0.5564</v>
       </c>
     </row>
     <row r="304">
@@ -11570,10 +11570,10 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0806</v>
       </c>
       <c r="H328" t="n">
-        <v>0.0648</v>
+        <v>0.0619</v>
       </c>
     </row>
     <row r="329">
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.5757</v>
+        <v>0.5936</v>
       </c>
       <c r="H332" t="n">
-        <v>0.5522</v>
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="333">
@@ -12318,10 +12318,10 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.0505</v>
+        <v>0.049</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0424</v>
+        <v>0.0406</v>
       </c>
     </row>
     <row r="351">
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>0.0266</v>
+        <v>0.0255</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0205</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="352">
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0.0412</v>
+        <v>0.0384</v>
       </c>
       <c r="H352" t="n">
-        <v>0.033</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="353">
@@ -12420,10 +12420,10 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>0.0318</v>
+        <v>0.0314</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0269</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="354">
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>0.0737</v>
+        <v>0.0713</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0589</v>
+        <v>0.0568</v>
       </c>
     </row>
     <row r="355">
@@ -12488,10 +12488,10 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.1402</v>
+        <v>0.1332</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1125</v>
+        <v>0.1069</v>
       </c>
     </row>
     <row r="356">
@@ -12522,10 +12522,10 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.1001</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0819</v>
+        <v>0.08069999999999999</v>
       </c>
     </row>
     <row r="357">
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>0.0654</v>
+        <v>0.0585</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0521</v>
+        <v>0.0466</v>
       </c>
     </row>
     <row r="358">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>0.221</v>
+        <v>0.2182</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1857</v>
+        <v>0.1823</v>
       </c>
     </row>
     <row r="359">
@@ -12624,10 +12624,10 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.1771</v>
+        <v>0.1683</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1471</v>
+        <v>0.1378</v>
       </c>
     </row>
     <row r="360">
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.4678</v>
+        <v>0.4436</v>
       </c>
       <c r="H360" t="n">
-        <v>0.4325</v>
+        <v>0.4078</v>
       </c>
     </row>
     <row r="361">
@@ -12692,10 +12692,10 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.4478</v>
+        <v>0.434</v>
       </c>
       <c r="H361" t="n">
-        <v>0.4243</v>
+        <v>0.4064</v>
       </c>
     </row>
     <row r="362">
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.7852</v>
+        <v>0.7829</v>
       </c>
       <c r="H362" t="n">
-        <v>0.7431</v>
+        <v>0.7401</v>
       </c>
     </row>
     <row r="363">
@@ -12760,10 +12760,10 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.77</v>
+        <v>0.7654</v>
       </c>
       <c r="H363" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7387</v>
       </c>
     </row>
     <row r="364">
@@ -13304,10 +13304,10 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.0205</v>
+        <v>0.0201</v>
       </c>
       <c r="H379" t="n">
-        <v>0.016</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="380">
@@ -13542,10 +13542,10 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0.0224</v>
+        <v>0.0216</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0179</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="387">
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0.0881</v>
+        <v>0.0857</v>
       </c>
       <c r="H387" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0732</v>
       </c>
     </row>
     <row r="388">
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>0.2569</v>
+        <v>0.2599</v>
       </c>
       <c r="H391" t="n">
-        <v>0.2148</v>
+        <v>0.2171</v>
       </c>
     </row>
     <row r="392">
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>0.0346</v>
+        <v>0.0326</v>
       </c>
       <c r="H415" t="n">
-        <v>0.0273</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="416">
@@ -14596,10 +14596,10 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>0.0605</v>
+        <v>0.0599</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0505</v>
+        <v>0.0499</v>
       </c>
     </row>
     <row r="418">
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>0.2576</v>
+        <v>0.2613</v>
       </c>
       <c r="H420" t="n">
-        <v>0.23</v>
+        <v>0.2346</v>
       </c>
     </row>
     <row r="421">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -847,23 +847,23 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.9594</v>
+        <v>0.9845</v>
       </c>
       <c r="H13" t="n">
-        <v>0.951</v>
+        <v>0.9799</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.9845</v>
+        <v>0.9594</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9799</v>
+        <v>0.951</v>
       </c>
     </row>
     <row r="15">
@@ -1833,23 +1833,23 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.9808</v>
+        <v>0.987</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9745</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="43">
@@ -1867,23 +1867,23 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.987</v>
+        <v>0.9808</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9841</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="44">
@@ -2819,23 +2819,23 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.9701</v>
+        <v>0.9848</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9616</v>
+        <v>0.9827</v>
       </c>
     </row>
     <row r="72">
@@ -2853,23 +2853,23 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.9848</v>
+        <v>0.9701</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9827</v>
+        <v>0.9616</v>
       </c>
     </row>
     <row r="73">
@@ -3805,23 +3805,23 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.9735</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9686</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="101">
@@ -3839,23 +3839,23 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9735</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9777</v>
+        <v>0.9686</v>
       </c>
     </row>
     <row r="102">
@@ -4791,23 +4791,23 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.9432</v>
+        <v>0.9798</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9287</v>
+        <v>0.9742</v>
       </c>
     </row>
     <row r="130">
@@ -4825,23 +4825,23 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.9798</v>
+        <v>0.9432</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9742</v>
+        <v>0.9287</v>
       </c>
     </row>
     <row r="131">
@@ -5777,23 +5777,23 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.8931</v>
+        <v>0.9526</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8668</v>
+        <v>0.9441000000000001</v>
       </c>
     </row>
     <row r="159">
@@ -5811,23 +5811,23 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.9526</v>
+        <v>0.8931</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8668</v>
       </c>
     </row>
     <row r="160">
@@ -6763,23 +6763,23 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.9193</v>
+        <v>0.9724</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9009</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="188">
@@ -6797,23 +6797,23 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.9724</v>
+        <v>0.9193</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9661</v>
+        <v>0.9009</v>
       </c>
     </row>
     <row r="189">
@@ -7749,23 +7749,23 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.9534</v>
+        <v>0.983</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9415</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="217">
@@ -7783,23 +7783,23 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.983</v>
+        <v>0.9534</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9784</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="218">
@@ -8735,23 +8735,23 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.8177</v>
+        <v>0.9268</v>
       </c>
       <c r="H245" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.9143</v>
       </c>
     </row>
     <row r="246">
@@ -8769,23 +8769,23 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.9268</v>
+        <v>0.8177</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9143</v>
+        <v>0.7818000000000001</v>
       </c>
     </row>
     <row r="247">
@@ -9721,23 +9721,23 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.8622</v>
+        <v>0.9489</v>
       </c>
       <c r="H274" t="n">
-        <v>0.8317</v>
+        <v>0.9337</v>
       </c>
     </row>
     <row r="275">
@@ -9755,23 +9755,23 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.9489</v>
+        <v>0.8622</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9337</v>
+        <v>0.8317</v>
       </c>
     </row>
     <row r="276">
@@ -10707,23 +10707,23 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.8305</v>
       </c>
       <c r="H303" t="n">
-        <v>0.5564</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="304">
@@ -10741,23 +10741,23 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.8305</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7948</v>
+        <v>0.5564</v>
       </c>
     </row>
     <row r="305">
@@ -11693,23 +11693,23 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.5936</v>
+        <v>0.8196</v>
       </c>
       <c r="H332" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.7895</v>
       </c>
     </row>
     <row r="333">
@@ -11727,23 +11727,23 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.8196</v>
+        <v>0.5936</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7895</v>
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="334">
@@ -12292,16 +12292,16 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -12318,24 +12318,24 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.049</v>
+        <v>0.0201</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0406</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -12352,24 +12352,24 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>0.0255</v>
+        <v>0.0159</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0192</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -12386,24 +12386,24 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0.0384</v>
+        <v>0.0173</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0299</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -12420,24 +12420,24 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>0.0314</v>
+        <v>0.0223</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0265</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -12454,24 +12454,24 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>0.0713</v>
+        <v>0.0258</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0568</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -12488,24 +12488,24 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.1332</v>
+        <v>0.0559</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1069</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -12522,24 +12522,24 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0339</v>
       </c>
       <c r="H356" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -12556,24 +12556,24 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>0.0585</v>
+        <v>0.0216</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0466</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -12590,24 +12590,24 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>0.2182</v>
+        <v>0.0857</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1823</v>
+        <v>0.0732</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -12624,24 +12624,24 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.1683</v>
+        <v>0.0663</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1378</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -12658,24 +12658,24 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.4436</v>
+        <v>0.2052</v>
       </c>
       <c r="H360" t="n">
-        <v>0.4078</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -12692,58 +12692,58 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.434</v>
+        <v>0.2105</v>
       </c>
       <c r="H361" t="n">
-        <v>0.4064</v>
+        <v>0.1804</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
+        <v>1610612751</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Nets</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
         <v>1610612754</v>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="E362" t="inlineStr">
         <is>
           <t>Pacers</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="F362" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="D362" t="n">
-        <v>1610612751</v>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>Nets</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
       <c r="G362" t="n">
-        <v>0.7829</v>
+        <v>0.2599</v>
       </c>
       <c r="H362" t="n">
-        <v>0.7401</v>
+        <v>0.2171</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D363" t="n">
@@ -12760,24 +12760,24 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.7654</v>
+        <v>0.519</v>
       </c>
       <c r="H363" t="n">
-        <v>0.7387</v>
+        <v>0.4764</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -12802,16 +12802,16 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -12836,16 +12836,16 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -12870,16 +12870,16 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -12904,16 +12904,16 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -12938,16 +12938,16 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -12972,16 +12972,16 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -13006,16 +13006,16 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -13040,16 +13040,16 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -13074,16 +13074,16 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -13108,16 +13108,16 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -13142,16 +13142,16 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -13176,16 +13176,16 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -13210,16 +13210,16 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -13244,16 +13244,16 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -13278,16 +13278,16 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -13304,24 +13304,24 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.0201</v>
+        <v>0.049</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0155</v>
+        <v>0.0406</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -13338,24 +13338,24 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0.0159</v>
+        <v>0.0255</v>
       </c>
       <c r="H380" t="n">
-        <v>0.013</v>
+        <v>0.0192</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -13372,24 +13372,24 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.0173</v>
+        <v>0.0384</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0152</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -13406,24 +13406,24 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>0.0223</v>
+        <v>0.0314</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0186</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -13440,24 +13440,24 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>0.0258</v>
+        <v>0.0713</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0202</v>
+        <v>0.0568</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D384" t="n">
@@ -13474,24 +13474,24 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>0.0559</v>
+        <v>0.1332</v>
       </c>
       <c r="H384" t="n">
-        <v>0.0474</v>
+        <v>0.1069</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -13508,24 +13508,24 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0.0339</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0276</v>
+        <v>0.08069999999999999</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -13542,24 +13542,24 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0.0216</v>
+        <v>0.0585</v>
       </c>
       <c r="H386" t="n">
-        <v>0.017</v>
+        <v>0.0466</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -13576,24 +13576,24 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0.0857</v>
+        <v>0.2182</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0732</v>
+        <v>0.1823</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -13610,24 +13610,24 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.0663</v>
+        <v>0.1683</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0511</v>
+        <v>0.1378</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -13644,24 +13644,24 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0.2052</v>
+        <v>0.4436</v>
       </c>
       <c r="H389" t="n">
-        <v>0.1695</v>
+        <v>0.4078</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -13678,58 +13678,58 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>0.2105</v>
+        <v>0.434</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1804</v>
+        <v>0.4064</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
+        <v>1610612754</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Pacers</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
         <v>1610612751</v>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="E391" t="inlineStr">
         <is>
           <t>Nets</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="F391" t="inlineStr">
         <is>
           <t>BKN</t>
         </is>
       </c>
-      <c r="D391" t="n">
-        <v>1610612754</v>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>Pacers</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
       <c r="G391" t="n">
-        <v>0.2599</v>
+        <v>0.7829</v>
       </c>
       <c r="H391" t="n">
-        <v>0.2171</v>
+        <v>0.7401</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D392" t="n">
@@ -13746,24 +13746,24 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0.519</v>
+        <v>0.7654</v>
       </c>
       <c r="H392" t="n">
-        <v>0.4764</v>
+        <v>0.7387</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D393" t="n">
@@ -13788,16 +13788,16 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D394" t="n">
@@ -13822,16 +13822,16 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -13856,16 +13856,16 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -13890,16 +13890,16 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -13924,16 +13924,16 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -13958,16 +13958,16 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -13992,16 +13992,16 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -14026,16 +14026,16 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -14060,16 +14060,16 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -14094,16 +14094,16 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -14128,16 +14128,16 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -14162,16 +14162,16 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -14196,16 +14196,16 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D406" t="n">
@@ -14230,16 +14230,16 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D407" t="n">
@@ -14685,23 +14685,23 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G420" t="n">
-        <v>0.2613</v>
+        <v>0.5236</v>
       </c>
       <c r="H420" t="n">
-        <v>0.2346</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="421">
@@ -14719,23 +14719,23 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0.5236</v>
+        <v>0.2613</v>
       </c>
       <c r="H421" t="n">
-        <v>0.481</v>
+        <v>0.2346</v>
       </c>
     </row>
     <row r="422">
@@ -15671,16 +15671,16 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G449" t="n">
@@ -15705,16 +15705,16 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G450" t="n">
@@ -16657,16 +16657,16 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -16691,16 +16691,16 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -17643,16 +17643,16 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G507" t="n">
@@ -17677,16 +17677,16 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G508" t="n">
@@ -18629,16 +18629,16 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G536" t="n">
@@ -18663,16 +18663,16 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G537" t="n">
@@ -19615,16 +19615,16 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G565" t="n">
@@ -19649,16 +19649,16 @@
         </is>
       </c>
       <c r="D566" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G566" t="n">
@@ -20601,16 +20601,16 @@
         </is>
       </c>
       <c r="D594" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -20635,16 +20635,16 @@
         </is>
       </c>
       <c r="D595" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -21587,16 +21587,16 @@
         </is>
       </c>
       <c r="D623" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G623" t="n">
@@ -21621,16 +21621,16 @@
         </is>
       </c>
       <c r="D624" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G624" t="n">
@@ -22573,16 +22573,16 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G652" t="n">
@@ -22607,16 +22607,16 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G653" t="n">
@@ -23559,16 +23559,16 @@
         </is>
       </c>
       <c r="D681" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -23593,16 +23593,16 @@
         </is>
       </c>
       <c r="D682" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G682" t="n">
@@ -24545,16 +24545,16 @@
         </is>
       </c>
       <c r="D710" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G710" t="n">
@@ -24579,16 +24579,16 @@
         </is>
       </c>
       <c r="D711" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G711" t="n">
@@ -25531,16 +25531,16 @@
         </is>
       </c>
       <c r="D739" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -25565,16 +25565,16 @@
         </is>
       </c>
       <c r="D740" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -26517,16 +26517,16 @@
         </is>
       </c>
       <c r="D768" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G768" t="n">
@@ -26551,16 +26551,16 @@
         </is>
       </c>
       <c r="D769" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G769" t="n">
@@ -27503,16 +27503,16 @@
         </is>
       </c>
       <c r="D797" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G797" t="n">
@@ -27537,16 +27537,16 @@
         </is>
       </c>
       <c r="D798" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -28489,16 +28489,16 @@
         </is>
       </c>
       <c r="D826" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G826" t="n">
@@ -28523,16 +28523,16 @@
         </is>
       </c>
       <c r="D827" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G827" t="n">
@@ -29475,16 +29475,16 @@
         </is>
       </c>
       <c r="D855" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G855" t="n">
@@ -29509,16 +29509,16 @@
         </is>
       </c>
       <c r="D856" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G856" t="n">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.9594</v>
+        <v>0.9617</v>
       </c>
       <c r="H14" t="n">
-        <v>0.951</v>
+        <v>0.9537</v>
       </c>
     </row>
     <row r="15">
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7627</v>
+        <v>0.7647</v>
       </c>
       <c r="H37" t="n">
-        <v>0.72</v>
+        <v>0.7216</v>
       </c>
     </row>
     <row r="38">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.9808</v>
+        <v>0.9811</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9745</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="44">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.9701</v>
+        <v>0.9718</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9616</v>
+        <v>0.9643</v>
       </c>
     </row>
     <row r="73">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.8895</v>
+        <v>0.8917</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8567</v>
+        <v>0.8602</v>
       </c>
     </row>
     <row r="98">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.9629</v>
+        <v>0.9639</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9542</v>
+        <v>0.9559</v>
       </c>
     </row>
     <row r="100">
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.9735</v>
+        <v>0.9768</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9686</v>
+        <v>0.9731</v>
       </c>
     </row>
     <row r="102">
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.9432</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9287</v>
+        <v>0.9318</v>
       </c>
     </row>
     <row r="131">
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.5429</v>
+        <v>0.543</v>
       </c>
       <c r="H155" t="n">
         <v>0.5</v>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.8931</v>
+        <v>0.8937</v>
       </c>
       <c r="H159" t="n">
-        <v>0.8668</v>
+        <v>0.8671</v>
       </c>
     </row>
     <row r="160">
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.9045</v>
+        <v>0.9059</v>
       </c>
       <c r="H185" t="n">
-        <v>0.878</v>
+        <v>0.8791</v>
       </c>
     </row>
     <row r="186">
@@ -6810,10 +6810,10 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.9193</v>
+        <v>0.9235</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9009</v>
+        <v>0.9058</v>
       </c>
     </row>
     <row r="189">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.28</v>
+        <v>0.2784</v>
       </c>
       <c r="H206" t="n">
-        <v>0.2373</v>
+        <v>0.2353</v>
       </c>
     </row>
     <row r="207">
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.9534</v>
+        <v>0.9552</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9415</v>
+        <v>0.9438</v>
       </c>
     </row>
     <row r="218">
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.8177</v>
+        <v>0.8305</v>
       </c>
       <c r="H246" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7911</v>
       </c>
     </row>
     <row r="247">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.1433</v>
+        <v>0.1398</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1105</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="267">
@@ -9533,7 +9533,7 @@
         <v>0.5</v>
       </c>
       <c r="H268" t="n">
-        <v>0.4571</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="269">
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.8622</v>
+        <v>0.8663</v>
       </c>
       <c r="H275" t="n">
-        <v>0.8317</v>
+        <v>0.8362000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -10550,10 +10550,10 @@
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.122</v>
+        <v>0.1209</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0955</v>
+        <v>0.0941</v>
       </c>
     </row>
     <row r="299">
@@ -10754,10 +10754,10 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.6239</v>
       </c>
       <c r="H304" t="n">
-        <v>0.5564</v>
+        <v>0.5816</v>
       </c>
     </row>
     <row r="305">
@@ -11434,10 +11434,10 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>0.0458</v>
+        <v>0.0441</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0371</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="325">
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.8196</v>
+        <v>0.8208</v>
       </c>
       <c r="H332" t="n">
-        <v>0.7895</v>
+        <v>0.7904</v>
       </c>
     </row>
     <row r="333">
@@ -11740,10 +11740,10 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.5936</v>
+        <v>0.6286</v>
       </c>
       <c r="H333" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5989</v>
       </c>
     </row>
     <row r="334">
@@ -12692,10 +12692,10 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.2105</v>
+        <v>0.2096</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1804</v>
+        <v>0.1792</v>
       </c>
     </row>
     <row r="362">
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.2599</v>
+        <v>0.2724</v>
       </c>
       <c r="H362" t="n">
-        <v>0.2171</v>
+        <v>0.2266</v>
       </c>
     </row>
     <row r="363">
@@ -13304,10 +13304,10 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.049</v>
+        <v>0.0463</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0406</v>
+        <v>0.0383</v>
       </c>
     </row>
     <row r="380">
@@ -13338,10 +13338,10 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0.0255</v>
+        <v>0.0252</v>
       </c>
       <c r="H380" t="n">
-        <v>0.0192</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="381">
@@ -13372,10 +13372,10 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.0384</v>
+        <v>0.0357</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0299</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="382">
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>0.0314</v>
+        <v>0.0269</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0265</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="383">
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>0.0713</v>
+        <v>0.0682</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0568</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="384">
@@ -13474,10 +13474,10 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>0.1332</v>
+        <v>0.1329</v>
       </c>
       <c r="H384" t="n">
-        <v>0.1069</v>
+        <v>0.1063</v>
       </c>
     </row>
     <row r="385">
@@ -13508,10 +13508,10 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H385" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="386">
@@ -13542,10 +13542,10 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0.0585</v>
+        <v>0.0562</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0466</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="387">
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0.2182</v>
+        <v>0.2089</v>
       </c>
       <c r="H387" t="n">
-        <v>0.1823</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="388">
@@ -13610,10 +13610,10 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.1683</v>
+        <v>0.1638</v>
       </c>
       <c r="H388" t="n">
-        <v>0.1378</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="389">
@@ -13644,10 +13644,10 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0.4436</v>
+        <v>0.4184</v>
       </c>
       <c r="H389" t="n">
-        <v>0.4078</v>
+        <v>0.3761</v>
       </c>
     </row>
     <row r="390">
@@ -13678,10 +13678,10 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>0.434</v>
+        <v>0.4011</v>
       </c>
       <c r="H390" t="n">
-        <v>0.4064</v>
+        <v>0.3714</v>
       </c>
     </row>
     <row r="391">
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>0.7829</v>
+        <v>0.7734</v>
       </c>
       <c r="H391" t="n">
-        <v>0.7401</v>
+        <v>0.7276</v>
       </c>
     </row>
     <row r="392">
@@ -13746,10 +13746,10 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0.7654</v>
+        <v>0.7459</v>
       </c>
       <c r="H392" t="n">
-        <v>0.7387</v>
+        <v>0.7225</v>
       </c>
     </row>
     <row r="393">
@@ -14732,10 +14732,10 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0.2613</v>
+        <v>0.2775</v>
       </c>
       <c r="H421" t="n">
-        <v>0.2346</v>
+        <v>0.2541</v>
       </c>
     </row>
     <row r="422">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -847,23 +847,23 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.9845</v>
+        <v>0.9617</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9799</v>
+        <v>0.9537</v>
       </c>
     </row>
     <row r="14">
@@ -881,23 +881,23 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.9617</v>
+        <v>0.9845</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9537</v>
+        <v>0.9799</v>
       </c>
     </row>
     <row r="15">
@@ -1833,23 +1833,23 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.987</v>
+        <v>0.9811</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9841</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="43">
@@ -1867,23 +1867,23 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.9811</v>
+        <v>0.987</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9748</v>
+        <v>0.9841</v>
       </c>
     </row>
     <row r="44">
@@ -2819,23 +2819,23 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.9848</v>
+        <v>0.9718</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9827</v>
+        <v>0.9643</v>
       </c>
     </row>
     <row r="72">
@@ -2853,23 +2853,23 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.9718</v>
+        <v>0.9848</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9643</v>
+        <v>0.9827</v>
       </c>
     </row>
     <row r="73">
@@ -3805,23 +3805,23 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9768</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9777</v>
+        <v>0.9731</v>
       </c>
     </row>
     <row r="101">
@@ -3839,23 +3839,23 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.9768</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9731</v>
+        <v>0.9777</v>
       </c>
     </row>
     <row r="102">
@@ -4791,23 +4791,23 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.9798</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9742</v>
+        <v>0.9318</v>
       </c>
     </row>
     <row r="130">
@@ -4825,23 +4825,23 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9318</v>
+        <v>0.9742</v>
       </c>
     </row>
     <row r="131">
@@ -5777,23 +5777,23 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.9526</v>
+        <v>0.8937</v>
       </c>
       <c r="H158" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.8671</v>
       </c>
     </row>
     <row r="159">
@@ -5811,23 +5811,23 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.8937</v>
+        <v>0.9526</v>
       </c>
       <c r="H159" t="n">
-        <v>0.8671</v>
+        <v>0.9441000000000001</v>
       </c>
     </row>
     <row r="160">
@@ -6763,23 +6763,23 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.9724</v>
+        <v>0.9235</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9661</v>
+        <v>0.9058</v>
       </c>
     </row>
     <row r="188">
@@ -6797,23 +6797,23 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.9235</v>
+        <v>0.9724</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9058</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="189">
@@ -7749,23 +7749,23 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.983</v>
+        <v>0.9552</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9784</v>
+        <v>0.9438</v>
       </c>
     </row>
     <row r="217">
@@ -7783,23 +7783,23 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.9552</v>
+        <v>0.983</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9438</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="218">
@@ -8735,23 +8735,23 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.9268</v>
+        <v>0.8305</v>
       </c>
       <c r="H245" t="n">
-        <v>0.9143</v>
+        <v>0.7911</v>
       </c>
     </row>
     <row r="246">
@@ -8769,23 +8769,23 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.8305</v>
+        <v>0.9268</v>
       </c>
       <c r="H246" t="n">
-        <v>0.7911</v>
+        <v>0.9143</v>
       </c>
     </row>
     <row r="247">
@@ -9721,23 +9721,23 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.9489</v>
+        <v>0.8663</v>
       </c>
       <c r="H274" t="n">
-        <v>0.9337</v>
+        <v>0.8362000000000001</v>
       </c>
     </row>
     <row r="275">
@@ -9755,23 +9755,23 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.8663</v>
+        <v>0.9489</v>
       </c>
       <c r="H275" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.9337</v>
       </c>
     </row>
     <row r="276">
@@ -10707,23 +10707,23 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0.8305</v>
+        <v>0.6239</v>
       </c>
       <c r="H303" t="n">
-        <v>0.7948</v>
+        <v>0.5816</v>
       </c>
     </row>
     <row r="304">
@@ -10741,23 +10741,23 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.6239</v>
+        <v>0.8305</v>
       </c>
       <c r="H304" t="n">
-        <v>0.5816</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="305">
@@ -11693,23 +11693,23 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.8208</v>
+        <v>0.6286</v>
       </c>
       <c r="H332" t="n">
-        <v>0.7904</v>
+        <v>0.5989</v>
       </c>
     </row>
     <row r="333">
@@ -11727,23 +11727,23 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.6286</v>
+        <v>0.8208</v>
       </c>
       <c r="H333" t="n">
-        <v>0.5989</v>
+        <v>0.7904</v>
       </c>
     </row>
     <row r="334">
@@ -12292,16 +12292,16 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D350" t="n">
@@ -12318,24 +12318,24 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.0201</v>
+        <v>0.0463</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0155</v>
+        <v>0.0383</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D351" t="n">
@@ -12352,24 +12352,24 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>0.0159</v>
+        <v>0.0252</v>
       </c>
       <c r="H351" t="n">
-        <v>0.013</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D352" t="n">
@@ -12386,24 +12386,24 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0.0173</v>
+        <v>0.0357</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0152</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -12420,24 +12420,24 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>0.0223</v>
+        <v>0.0269</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0186</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D354" t="n">
@@ -12454,24 +12454,24 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>0.0258</v>
+        <v>0.0682</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0202</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D355" t="n">
@@ -12488,24 +12488,24 @@
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.0559</v>
+        <v>0.1329</v>
       </c>
       <c r="H355" t="n">
-        <v>0.0474</v>
+        <v>0.1063</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -12522,24 +12522,24 @@
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.0339</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0276</v>
+        <v>0.0765</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D357" t="n">
@@ -12556,24 +12556,24 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>0.0216</v>
+        <v>0.0562</v>
       </c>
       <c r="H357" t="n">
-        <v>0.017</v>
+        <v>0.0448</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D358" t="n">
@@ -12590,24 +12590,24 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>0.0857</v>
+        <v>0.2089</v>
       </c>
       <c r="H358" t="n">
-        <v>0.0732</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D359" t="n">
@@ -12624,24 +12624,24 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.0663</v>
+        <v>0.1638</v>
       </c>
       <c r="H359" t="n">
-        <v>0.0511</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D360" t="n">
@@ -12658,24 +12658,24 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.2052</v>
+        <v>0.4184</v>
       </c>
       <c r="H360" t="n">
-        <v>0.1695</v>
+        <v>0.3761</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D361" t="n">
@@ -12692,58 +12692,58 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.2096</v>
+        <v>0.4011</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1792</v>
+        <v>0.3714</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
+        <v>1610612754</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Pacers</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
         <v>1610612751</v>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="E362" t="inlineStr">
         <is>
           <t>Nets</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
+      <c r="F362" t="inlineStr">
         <is>
           <t>BKN</t>
         </is>
       </c>
-      <c r="D362" t="n">
-        <v>1610612754</v>
-      </c>
-      <c r="E362" t="inlineStr">
-        <is>
-          <t>Pacers</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>IND</t>
-        </is>
-      </c>
       <c r="G362" t="n">
-        <v>0.2724</v>
+        <v>0.7734</v>
       </c>
       <c r="H362" t="n">
-        <v>0.2266</v>
+        <v>0.7276</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D363" t="n">
@@ -12760,24 +12760,24 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.519</v>
+        <v>0.7459</v>
       </c>
       <c r="H363" t="n">
-        <v>0.4764</v>
+        <v>0.7225</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -12802,16 +12802,16 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -12836,16 +12836,16 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -12870,16 +12870,16 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D367" t="n">
@@ -12904,16 +12904,16 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -12938,16 +12938,16 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -12972,16 +12972,16 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -13006,16 +13006,16 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -13040,16 +13040,16 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D372" t="n">
@@ -13074,16 +13074,16 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D373" t="n">
@@ -13108,16 +13108,16 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D374" t="n">
@@ -13142,16 +13142,16 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D375" t="n">
@@ -13176,16 +13176,16 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -13210,16 +13210,16 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D377" t="n">
@@ -13244,16 +13244,16 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -13278,16 +13278,16 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -13304,24 +13304,24 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.0463</v>
+        <v>0.0201</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0383</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D380" t="n">
@@ -13338,24 +13338,24 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0.0252</v>
+        <v>0.0159</v>
       </c>
       <c r="H380" t="n">
-        <v>0.0189</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D381" t="n">
@@ -13372,24 +13372,24 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.0357</v>
+        <v>0.0173</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0282</v>
+        <v>0.0152</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D382" t="n">
@@ -13406,24 +13406,24 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>0.0269</v>
+        <v>0.0223</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0232</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D383" t="n">
@@ -13440,24 +13440,24 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>0.0682</v>
+        <v>0.0258</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0539</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D384" t="n">
@@ -13474,24 +13474,24 @@
         </is>
       </c>
       <c r="G384" t="n">
-        <v>0.1329</v>
+        <v>0.0559</v>
       </c>
       <c r="H384" t="n">
-        <v>0.1063</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -13508,24 +13508,24 @@
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0339</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0765</v>
+        <v>0.0276</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D386" t="n">
@@ -13542,24 +13542,24 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0.0562</v>
+        <v>0.0216</v>
       </c>
       <c r="H386" t="n">
-        <v>0.0448</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D387" t="n">
@@ -13576,24 +13576,24 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0.2089</v>
+        <v>0.0857</v>
       </c>
       <c r="H387" t="n">
-        <v>0.1695</v>
+        <v>0.0732</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -13610,24 +13610,24 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.1638</v>
+        <v>0.0663</v>
       </c>
       <c r="H388" t="n">
-        <v>0.1337</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D389" t="n">
@@ -13644,24 +13644,24 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0.4184</v>
+        <v>0.2052</v>
       </c>
       <c r="H389" t="n">
-        <v>0.3761</v>
+        <v>0.1695</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -13678,58 +13678,58 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>0.4011</v>
+        <v>0.2096</v>
       </c>
       <c r="H390" t="n">
-        <v>0.3714</v>
+        <v>0.1792</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
+        <v>1610612751</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Nets</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
         <v>1610612754</v>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="E391" t="inlineStr">
         <is>
           <t>Pacers</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
+      <c r="F391" t="inlineStr">
         <is>
           <t>IND</t>
         </is>
       </c>
-      <c r="D391" t="n">
-        <v>1610612751</v>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>Nets</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
       <c r="G391" t="n">
-        <v>0.7734</v>
+        <v>0.2724</v>
       </c>
       <c r="H391" t="n">
-        <v>0.7276</v>
+        <v>0.2266</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D392" t="n">
@@ -13746,24 +13746,24 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0.7459</v>
+        <v>0.519</v>
       </c>
       <c r="H392" t="n">
-        <v>0.7225</v>
+        <v>0.4764</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D393" t="n">
@@ -13788,16 +13788,16 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D394" t="n">
@@ -13822,16 +13822,16 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D395" t="n">
@@ -13856,16 +13856,16 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -13890,16 +13890,16 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -13924,16 +13924,16 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D398" t="n">
@@ -13958,16 +13958,16 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -13992,16 +13992,16 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D400" t="n">
@@ -14026,16 +14026,16 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D401" t="n">
@@ -14060,16 +14060,16 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D402" t="n">
@@ -14094,16 +14094,16 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -14128,16 +14128,16 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D404" t="n">
@@ -14162,16 +14162,16 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -14196,16 +14196,16 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D406" t="n">
@@ -14230,16 +14230,16 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D407" t="n">
@@ -14685,23 +14685,23 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G420" t="n">
-        <v>0.5236</v>
+        <v>0.2775</v>
       </c>
       <c r="H420" t="n">
-        <v>0.481</v>
+        <v>0.2541</v>
       </c>
     </row>
     <row r="421">
@@ -14719,23 +14719,23 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0.2775</v>
+        <v>0.5236</v>
       </c>
       <c r="H421" t="n">
-        <v>0.2541</v>
+        <v>0.481</v>
       </c>
     </row>
     <row r="422">
@@ -15671,16 +15671,16 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G449" t="n">
@@ -15705,16 +15705,16 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G450" t="n">
@@ -16657,16 +16657,16 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G478" t="n">
@@ -16691,16 +16691,16 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G479" t="n">
@@ -17643,16 +17643,16 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G507" t="n">
@@ -17677,16 +17677,16 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G508" t="n">
@@ -18629,16 +18629,16 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G536" t="n">
@@ -18663,16 +18663,16 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G537" t="n">
@@ -19615,16 +19615,16 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G565" t="n">
@@ -19649,16 +19649,16 @@
         </is>
       </c>
       <c r="D566" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G566" t="n">
@@ -20601,16 +20601,16 @@
         </is>
       </c>
       <c r="D594" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G594" t="n">
@@ -20635,16 +20635,16 @@
         </is>
       </c>
       <c r="D595" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G595" t="n">
@@ -21587,16 +21587,16 @@
         </is>
       </c>
       <c r="D623" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G623" t="n">
@@ -21621,16 +21621,16 @@
         </is>
       </c>
       <c r="D624" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G624" t="n">
@@ -22573,16 +22573,16 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G652" t="n">
@@ -22607,16 +22607,16 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G653" t="n">
@@ -23559,16 +23559,16 @@
         </is>
       </c>
       <c r="D681" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G681" t="n">
@@ -23593,16 +23593,16 @@
         </is>
       </c>
       <c r="D682" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G682" t="n">
@@ -24545,16 +24545,16 @@
         </is>
       </c>
       <c r="D710" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G710" t="n">
@@ -24579,16 +24579,16 @@
         </is>
       </c>
       <c r="D711" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G711" t="n">
@@ -25531,16 +25531,16 @@
         </is>
       </c>
       <c r="D739" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G739" t="n">
@@ -25565,16 +25565,16 @@
         </is>
       </c>
       <c r="D740" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G740" t="n">
@@ -26517,16 +26517,16 @@
         </is>
       </c>
       <c r="D768" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E768" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G768" t="n">
@@ -26551,16 +26551,16 @@
         </is>
       </c>
       <c r="D769" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E769" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G769" t="n">
@@ -27503,16 +27503,16 @@
         </is>
       </c>
       <c r="D797" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G797" t="n">
@@ -27537,16 +27537,16 @@
         </is>
       </c>
       <c r="D798" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G798" t="n">
@@ -28489,16 +28489,16 @@
         </is>
       </c>
       <c r="D826" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E826" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G826" t="n">
@@ -28523,16 +28523,16 @@
         </is>
       </c>
       <c r="D827" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G827" t="n">
@@ -29475,16 +29475,16 @@
         </is>
       </c>
       <c r="D855" t="n">
-        <v>1610612751</v>
+        <v>1610612754</v>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>Nets</t>
+          <t>Pacers</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="G855" t="n">
@@ -29509,16 +29509,16 @@
         </is>
       </c>
       <c r="D856" t="n">
-        <v>1610612754</v>
+        <v>1610612751</v>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>Pacers</t>
+          <t>Nets</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="G856" t="n">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.4864</v>
+        <v>0.4757</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4346</v>
+        <v>0.4282</v>
       </c>
     </row>
     <row r="3">
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5587</v>
+        <v>0.5536</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5245</v>
+        <v>0.5238</v>
       </c>
     </row>
     <row r="4">
@@ -554,10 +554,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5062</v>
+        <v>0.5279</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4658</v>
+        <v>0.4847</v>
       </c>
     </row>
     <row r="5">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.7338</v>
+        <v>0.7634</v>
       </c>
       <c r="H5" t="n">
-        <v>0.704</v>
+        <v>0.7402</v>
       </c>
     </row>
     <row r="6">
@@ -609,23 +609,23 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8373</v>
+        <v>0.7444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8173</v>
+        <v>0.7229</v>
       </c>
     </row>
     <row r="7">
@@ -643,23 +643,23 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.7385</v>
+        <v>0.834</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7084</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="8">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.6595</v>
+        <v>0.6929</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6266</v>
+        <v>0.6594</v>
       </c>
     </row>
     <row r="9">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.9161</v>
+        <v>0.9206</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8928</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="10">
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8596</v>
+        <v>0.8703</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8244</v>
+        <v>0.8373</v>
       </c>
     </row>
     <row r="11">
@@ -792,10 +792,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.9503</v>
+        <v>0.9496</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9404</v>
+        <v>0.9395</v>
       </c>
     </row>
     <row r="12">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.9613</v>
+        <v>0.9629</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9518</v>
+        <v>0.955</v>
       </c>
     </row>
     <row r="13">
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.9617</v>
+        <v>0.9674</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9537</v>
+        <v>0.9601</v>
       </c>
     </row>
     <row r="14">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.9845</v>
+        <v>0.9855</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9799</v>
+        <v>0.9811</v>
       </c>
     </row>
     <row r="15">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.9766</v>
+        <v>0.9778</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9696</v>
+        <v>0.9717</v>
       </c>
     </row>
     <row r="16">
@@ -1391,16 +1391,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1425,16 +1425,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.5654</v>
+        <v>0.5718</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5243</v>
       </c>
     </row>
     <row r="32">
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.649</v>
+        <v>0.6887</v>
       </c>
       <c r="H32" t="n">
-        <v>0.617</v>
+        <v>0.6644</v>
       </c>
     </row>
     <row r="33">
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.5934</v>
+        <v>0.6181</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5572</v>
+        <v>0.5800999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8264</v>
+        <v>0.8283</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7815</v>
+        <v>0.7827</v>
       </c>
     </row>
     <row r="35">
@@ -1595,23 +1595,23 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.9092</v>
+        <v>0.8825</v>
       </c>
       <c r="H35" t="n">
-        <v>0.889</v>
+        <v>0.8568</v>
       </c>
     </row>
     <row r="36">
@@ -1629,23 +1629,23 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8609</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8293</v>
+        <v>0.9035</v>
       </c>
     </row>
     <row r="37">
@@ -1676,10 +1676,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.7647</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7216</v>
+        <v>0.7296</v>
       </c>
     </row>
     <row r="38">
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9311</v>
+        <v>0.9383</v>
       </c>
     </row>
     <row r="39">
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.9055</v>
+        <v>0.921</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8767</v>
+        <v>0.8925999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.9756</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9674</v>
       </c>
     </row>
     <row r="41">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.9792</v>
+        <v>0.9823</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9718</v>
+        <v>0.9762999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.9811</v>
+        <v>0.9821</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9748</v>
+        <v>0.9756</v>
       </c>
     </row>
     <row r="43">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.987</v>
+        <v>0.9881</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9841</v>
+        <v>0.9857</v>
       </c>
     </row>
     <row r="44">
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.9878</v>
+        <v>0.9876</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9833</v>
       </c>
     </row>
     <row r="45">
@@ -2377,16 +2377,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -2411,16 +2411,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.4755</v>
+        <v>0.4762</v>
       </c>
       <c r="H60" t="n">
-        <v>0.4413</v>
+        <v>0.4464</v>
       </c>
     </row>
     <row r="61">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.383</v>
+        <v>0.3356</v>
       </c>
       <c r="H61" t="n">
-        <v>0.351</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="62">
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.4937</v>
+        <v>0.5092</v>
       </c>
       <c r="H62" t="n">
-        <v>0.4492</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="63">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.7247</v>
+        <v>0.7275</v>
       </c>
       <c r="H63" t="n">
-        <v>0.68</v>
+        <v>0.6784</v>
       </c>
     </row>
     <row r="64">
@@ -2581,23 +2581,23 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8283</v>
+        <v>0.7654</v>
       </c>
     </row>
     <row r="65">
@@ -2615,23 +2615,23 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.789</v>
+        <v>0.885</v>
       </c>
       <c r="H65" t="n">
-        <v>0.7537</v>
+        <v>0.8673999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.6434</v>
+        <v>0.6539</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5995</v>
+        <v>0.6092</v>
       </c>
     </row>
     <row r="67">
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.9229000000000001</v>
+        <v>0.9321</v>
       </c>
       <c r="H67" t="n">
-        <v>0.899</v>
+        <v>0.9092</v>
       </c>
     </row>
     <row r="68">
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8648</v>
+        <v>0.8739</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8335</v>
+        <v>0.8383</v>
       </c>
     </row>
     <row r="69">
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.9608</v>
+        <v>0.9604</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9499</v>
+        <v>0.9489</v>
       </c>
     </row>
     <row r="70">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.962</v>
+        <v>0.9729</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9508</v>
+        <v>0.9631999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.9718</v>
+        <v>0.9708</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9643</v>
+        <v>0.9622000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.9848</v>
+        <v>0.9867</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9827</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="73">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.9816</v>
+        <v>0.9826</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9765</v>
+        <v>0.9778</v>
       </c>
     </row>
     <row r="74">
@@ -3363,16 +3363,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>0.5342</v>
+        <v>0.5153</v>
       </c>
       <c r="H89" t="n">
-        <v>0.4938</v>
+        <v>0.4721</v>
       </c>
     </row>
     <row r="90">
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.4428</v>
+        <v>0.4199</v>
       </c>
       <c r="H90" t="n">
-        <v>0.4066</v>
+        <v>0.3819</v>
       </c>
     </row>
     <row r="91">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>0.5508</v>
+        <v>0.5375</v>
       </c>
       <c r="H91" t="n">
-        <v>0.5063</v>
+        <v>0.4908</v>
       </c>
     </row>
     <row r="92">
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0.7874</v>
+        <v>0.7724</v>
       </c>
       <c r="H92" t="n">
-        <v>0.7366</v>
+        <v>0.7201</v>
       </c>
     </row>
     <row r="93">
@@ -3567,23 +3567,23 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.8686</v>
+        <v>0.7622</v>
       </c>
       <c r="H93" t="n">
-        <v>0.8408</v>
+        <v>0.7233000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -3601,23 +3601,23 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.7996</v>
+        <v>0.8733</v>
       </c>
       <c r="H94" t="n">
-        <v>0.76</v>
+        <v>0.8493000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -3648,10 +3648,10 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>0.6631</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6188</v>
+        <v>0.6253</v>
       </c>
     </row>
     <row r="96">
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0.9181</v>
+        <v>0.9312</v>
       </c>
       <c r="H96" t="n">
-        <v>0.8966</v>
+        <v>0.9107</v>
       </c>
     </row>
     <row r="97">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0.8917</v>
+        <v>0.891</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8602</v>
+        <v>0.8585</v>
       </c>
     </row>
     <row r="98">
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>0.9668</v>
+        <v>0.9695</v>
       </c>
       <c r="H98" t="n">
-        <v>0.9578</v>
+        <v>0.9609</v>
       </c>
     </row>
     <row r="99">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0.9639</v>
+        <v>0.9766</v>
       </c>
       <c r="H99" t="n">
-        <v>0.9559</v>
+        <v>0.9705</v>
       </c>
     </row>
     <row r="100">
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0.9768</v>
+        <v>0.9749</v>
       </c>
       <c r="H100" t="n">
-        <v>0.9731</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="101">
@@ -3852,10 +3852,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.9814000000000001</v>
+        <v>0.9839</v>
       </c>
       <c r="H101" t="n">
-        <v>0.9777</v>
+        <v>0.9797</v>
       </c>
     </row>
     <row r="102">
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.9863</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="H102" t="n">
-        <v>0.9825</v>
+        <v>0.9812</v>
       </c>
     </row>
     <row r="103">
@@ -4349,16 +4349,16 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -4383,16 +4383,16 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0.296</v>
+        <v>0.2598</v>
       </c>
       <c r="H118" t="n">
-        <v>0.2662</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="119">
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.2185</v>
+        <v>0.2173</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1736</v>
+        <v>0.1717</v>
       </c>
     </row>
     <row r="120">
@@ -4498,10 +4498,10 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.32</v>
+        <v>0.3216</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2753</v>
+        <v>0.2725</v>
       </c>
     </row>
     <row r="121">
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.2634</v>
+        <v>0.2799</v>
       </c>
       <c r="H121" t="n">
-        <v>0.2126</v>
+        <v>0.2276</v>
       </c>
     </row>
     <row r="122">
@@ -4553,23 +4553,23 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.6754</v>
+        <v>0.5626</v>
       </c>
       <c r="H122" t="n">
-        <v>0.6553</v>
+        <v>0.5261</v>
       </c>
     </row>
     <row r="123">
@@ -4587,23 +4587,23 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0.539</v>
+        <v>0.6808</v>
       </c>
       <c r="H123" t="n">
-        <v>0.4989</v>
+        <v>0.6526999999999999</v>
       </c>
     </row>
     <row r="124">
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.4491</v>
+        <v>0.4447</v>
       </c>
       <c r="H124" t="n">
-        <v>0.4112</v>
+        <v>0.4093</v>
       </c>
     </row>
     <row r="125">
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0.7677</v>
+        <v>0.8156</v>
       </c>
       <c r="H125" t="n">
-        <v>0.7246</v>
+        <v>0.7752</v>
       </c>
     </row>
     <row r="126">
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>0.6885</v>
+        <v>0.7049</v>
       </c>
       <c r="H126" t="n">
-        <v>0.6442</v>
+        <v>0.6561</v>
       </c>
     </row>
     <row r="127">
@@ -4739,7 +4739,7 @@
         <v>0.9133</v>
       </c>
       <c r="H127" t="n">
-        <v>0.8843</v>
+        <v>0.883</v>
       </c>
     </row>
     <row r="128">
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.923</v>
+        <v>0.9406</v>
       </c>
       <c r="H128" t="n">
-        <v>0.9001</v>
+        <v>0.9215</v>
       </c>
     </row>
     <row r="129">
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9489</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9318</v>
+        <v>0.9352</v>
       </c>
     </row>
     <row r="130">
@@ -4838,10 +4838,10 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.9798</v>
+        <v>0.9818</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9742</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="131">
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0.9721</v>
+        <v>0.9728</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9635</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="132">
@@ -5335,16 +5335,16 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -5369,16 +5369,16 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -5390,16 +5390,16 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5416,24 +5416,24 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.1827</v>
+        <v>0.2771</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1627</v>
+        <v>0.2556</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5450,24 +5450,24 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.111</v>
+        <v>0.1432</v>
       </c>
       <c r="H148" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.1175</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5484,24 +5484,24 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.1717</v>
+        <v>0.2346</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1497</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5518,24 +5518,24 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.1592</v>
+        <v>0.2767</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1314</v>
+        <v>0.2378</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5552,58 +5552,58 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.3447</v>
+        <v>0.4739</v>
       </c>
       <c r="H151" t="n">
-        <v>0.3246</v>
+        <v>0.4374</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
+        <v>1610612761</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Raptors</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TOR</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
         <v>1610612755</v>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>76ers</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>1610612761</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Raptors</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>TOR</t>
-        </is>
-      </c>
       <c r="G152" t="n">
-        <v>0.3991</v>
+        <v>0.63</v>
       </c>
       <c r="H152" t="n">
-        <v>0.3746</v>
+        <v>0.6133999999999999</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5620,24 +5620,24 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>0.331</v>
+        <v>0.3977</v>
       </c>
       <c r="H153" t="n">
-        <v>0.2898</v>
+        <v>0.3514</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5654,24 +5654,24 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>0.649</v>
+        <v>0.7978</v>
       </c>
       <c r="H154" t="n">
-        <v>0.5956</v>
+        <v>0.7514999999999999</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5688,24 +5688,24 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.543</v>
+        <v>0.6686</v>
       </c>
       <c r="H155" t="n">
-        <v>0.5</v>
+        <v>0.6239</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5722,24 +5722,24 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>0.8464</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="H156" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8821</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5756,24 +5756,24 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.9343</v>
       </c>
       <c r="H157" t="n">
-        <v>0.8087</v>
+        <v>0.9099</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5790,24 +5790,24 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>0.8937</v>
+        <v>0.9383</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8671</v>
+        <v>0.9224</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5824,24 +5824,24 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>0.9526</v>
+        <v>0.9775</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9721</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -5858,24 +5858,24 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>0.9624</v>
+        <v>0.9708</v>
       </c>
       <c r="H160" t="n">
-        <v>0.9526</v>
+        <v>0.9619</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -5900,16 +5900,16 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -5934,16 +5934,16 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -5968,16 +5968,16 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6002,16 +6002,16 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6036,16 +6036,16 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6070,16 +6070,16 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6104,16 +6104,16 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6138,16 +6138,16 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6172,16 +6172,16 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6206,16 +6206,16 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6240,16 +6240,16 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6274,16 +6274,16 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6308,29 +6308,29 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -6342,29 +6342,29 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -6376,16 +6376,16 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6402,24 +6402,24 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.2916</v>
+        <v>0.1873</v>
       </c>
       <c r="H176" t="n">
-        <v>0.2615</v>
+        <v>0.166</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6436,24 +6436,24 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0.1707</v>
+        <v>0.0965</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1391</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6470,24 +6470,24 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.2463</v>
+        <v>0.1326</v>
       </c>
       <c r="H178" t="n">
-        <v>0.211</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6504,24 +6504,24 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.24</v>
+        <v>0.1507</v>
       </c>
       <c r="H179" t="n">
-        <v>0.2004</v>
+        <v>0.1267</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6538,58 +6538,58 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>0.5011</v>
+        <v>0.3473</v>
       </c>
       <c r="H180" t="n">
-        <v>0.461</v>
+        <v>0.3192</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
+        <v>1610612755</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>76ers</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
         <v>1610612761</v>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>Raptors</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D181" t="n">
-        <v>1610612755</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>76ers</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="G181" t="n">
-        <v>0.6254</v>
+        <v>0.3866</v>
       </c>
       <c r="H181" t="n">
-        <v>0.6009</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6606,24 +6606,24 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>0.4021</v>
+        <v>0.3162</v>
       </c>
       <c r="H182" t="n">
-        <v>0.3539</v>
+        <v>0.2728</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6640,24 +6640,24 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.7688</v>
+        <v>0.6501</v>
       </c>
       <c r="H183" t="n">
-        <v>0.7241</v>
+        <v>0.6101</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6674,24 +6674,24 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>0.6684</v>
+        <v>0.5527</v>
       </c>
       <c r="H184" t="n">
-        <v>0.6234</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6708,24 +6708,24 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.9059</v>
+        <v>0.839</v>
       </c>
       <c r="H185" t="n">
-        <v>0.8791</v>
+        <v>0.8001</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6742,24 +6742,24 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.9032</v>
+        <v>0.8744</v>
       </c>
       <c r="H186" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8481</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6776,24 +6776,24 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.9235</v>
+        <v>0.8861</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9058</v>
+        <v>0.861</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6810,24 +6810,24 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>0.9724</v>
+        <v>0.9701</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9661</v>
+        <v>0.9634</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -6844,24 +6844,24 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>0.9696</v>
+        <v>0.9627</v>
       </c>
       <c r="H189" t="n">
-        <v>0.9596</v>
+        <v>0.9525</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -6886,16 +6886,16 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -6920,16 +6920,16 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -6954,16 +6954,16 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -6988,16 +6988,16 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7022,16 +7022,16 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7056,16 +7056,16 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7090,16 +7090,16 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7124,16 +7124,16 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7158,16 +7158,16 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7192,16 +7192,16 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7226,16 +7226,16 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7260,16 +7260,16 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7294,29 +7294,29 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -7328,29 +7328,29 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0.3734</v>
+        <v>0.3406</v>
       </c>
       <c r="H205" t="n">
-        <v>0.3405</v>
+        <v>0.3071</v>
       </c>
     </row>
     <row r="206">
@@ -7422,10 +7422,10 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>0.2784</v>
+        <v>0.2704</v>
       </c>
       <c r="H206" t="n">
-        <v>0.2353</v>
+        <v>0.2283</v>
       </c>
     </row>
     <row r="207">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0.4005</v>
+        <v>0.3908</v>
       </c>
       <c r="H207" t="n">
-        <v>0.3566</v>
+        <v>0.3461</v>
       </c>
     </row>
     <row r="208">
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>0.3812</v>
+        <v>0.3747</v>
       </c>
       <c r="H208" t="n">
-        <v>0.3369</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="209">
@@ -7524,10 +7524,10 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>0.5888</v>
+        <v>0.5907</v>
       </c>
       <c r="H209" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5553</v>
       </c>
     </row>
     <row r="210">
@@ -7545,23 +7545,23 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.6486</v>
       </c>
       <c r="H210" t="n">
-        <v>0.669</v>
+        <v>0.6022999999999999</v>
       </c>
     </row>
     <row r="211">
@@ -7579,23 +7579,23 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>0.6461</v>
+        <v>0.7272</v>
       </c>
       <c r="H211" t="n">
-        <v>0.5979</v>
+        <v>0.6838</v>
       </c>
     </row>
     <row r="212">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0.8419</v>
+        <v>0.8444</v>
       </c>
       <c r="H212" t="n">
-        <v>0.8083</v>
+        <v>0.8093</v>
       </c>
     </row>
     <row r="213">
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>0.7357</v>
+        <v>0.7287</v>
       </c>
       <c r="H213" t="n">
-        <v>0.6938</v>
+        <v>0.6894</v>
       </c>
     </row>
     <row r="214">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>0.93</v>
+        <v>0.9287</v>
       </c>
       <c r="H214" t="n">
-        <v>0.9111</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="215">
@@ -7728,10 +7728,10 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.9381</v>
+        <v>0.9476</v>
       </c>
       <c r="H215" t="n">
-        <v>0.9194</v>
+        <v>0.9304</v>
       </c>
     </row>
     <row r="216">
@@ -7762,10 +7762,10 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>0.9552</v>
+        <v>0.9543</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9438</v>
+        <v>0.9411</v>
       </c>
     </row>
     <row r="217">
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>0.983</v>
+        <v>0.9872</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9784</v>
+        <v>0.9837</v>
       </c>
     </row>
     <row r="218">
@@ -7830,10 +7830,10 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0.9747</v>
+        <v>0.9732</v>
       </c>
       <c r="H218" t="n">
-        <v>0.9674</v>
+        <v>0.9657</v>
       </c>
     </row>
     <row r="219">
@@ -8293,16 +8293,16 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -8327,16 +8327,16 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0.1072</v>
+        <v>0.104</v>
       </c>
       <c r="H234" t="n">
-        <v>0.0839</v>
+        <v>0.0794</v>
       </c>
     </row>
     <row r="235">
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>0.0689</v>
+        <v>0.0617</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0509</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="236">
@@ -8442,10 +8442,10 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0.101</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="H236" t="n">
-        <v>0.0771</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="237">
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>0.1034</v>
+        <v>0.0893</v>
       </c>
       <c r="H237" t="n">
-        <v>0.0819</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="238">
@@ -8510,10 +8510,10 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>0.2754</v>
+        <v>0.2248</v>
       </c>
       <c r="H238" t="n">
-        <v>0.2323</v>
+        <v>0.1844</v>
       </c>
     </row>
     <row r="239">
@@ -8531,23 +8531,23 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>0.4044</v>
+        <v>0.2485</v>
       </c>
       <c r="H239" t="n">
-        <v>0.351</v>
+        <v>0.2022</v>
       </c>
     </row>
     <row r="240">
@@ -8565,23 +8565,23 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.2759</v>
+        <v>0.3899</v>
       </c>
       <c r="H240" t="n">
-        <v>0.2312</v>
+        <v>0.3499</v>
       </c>
     </row>
     <row r="241">
@@ -8612,10 +8612,10 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.1917</v>
+        <v>0.1907</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1581</v>
+        <v>0.1556</v>
       </c>
     </row>
     <row r="242">
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0.4107</v>
+        <v>0.3803</v>
       </c>
       <c r="H242" t="n">
-        <v>0.3847</v>
+        <v>0.3518</v>
       </c>
     </row>
     <row r="243">
@@ -8680,10 +8680,10 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>0.7381</v>
+        <v>0.7685</v>
       </c>
       <c r="H243" t="n">
-        <v>0.7009</v>
+        <v>0.7288</v>
       </c>
     </row>
     <row r="244">
@@ -8714,10 +8714,10 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.7549</v>
+        <v>0.7944</v>
       </c>
       <c r="H244" t="n">
-        <v>0.714</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="245">
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>0.8305</v>
+        <v>0.8182</v>
       </c>
       <c r="H245" t="n">
-        <v>0.7911</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="246">
@@ -8782,10 +8782,10 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>0.9268</v>
+        <v>0.9418</v>
       </c>
       <c r="H246" t="n">
-        <v>0.9143</v>
+        <v>0.9298</v>
       </c>
     </row>
     <row r="247">
@@ -8816,10 +8816,10 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.923</v>
+        <v>0.9204</v>
       </c>
       <c r="H247" t="n">
-        <v>0.9028</v>
+        <v>0.9021</v>
       </c>
     </row>
     <row r="248">
@@ -9279,16 +9279,16 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -9313,16 +9313,16 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -9360,10 +9360,10 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>0.1756</v>
+        <v>0.1627</v>
       </c>
       <c r="H263" t="n">
-        <v>0.1404</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="264">
@@ -9394,10 +9394,10 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>0.1233</v>
+        <v>0.1074</v>
       </c>
       <c r="H264" t="n">
-        <v>0.0945</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="265">
@@ -9428,10 +9428,10 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>0.1665</v>
+        <v>0.1617</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1352</v>
+        <v>0.1261</v>
       </c>
     </row>
     <row r="266">
@@ -9462,10 +9462,10 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>0.1398</v>
+        <v>0.1415</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1083</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="267">
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="G267" t="n">
-        <v>0.3558</v>
+        <v>0.3439</v>
       </c>
       <c r="H267" t="n">
-        <v>0.3115</v>
+        <v>0.2951</v>
       </c>
     </row>
     <row r="268">
@@ -9517,23 +9517,23 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>0.5</v>
+        <v>0.3761</v>
       </c>
       <c r="H268" t="n">
-        <v>0.457</v>
+        <v>0.3314</v>
       </c>
     </row>
     <row r="269">
@@ -9551,23 +9551,23 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>0.3766</v>
+        <v>0.501</v>
       </c>
       <c r="H269" t="n">
-        <v>0.3316</v>
+        <v>0.4473</v>
       </c>
     </row>
     <row r="270">
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>0.3062</v>
+        <v>0.3106</v>
       </c>
       <c r="H270" t="n">
-        <v>0.2643</v>
+        <v>0.2713</v>
       </c>
     </row>
     <row r="271">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="G271" t="n">
-        <v>0.6153</v>
+        <v>0.6482</v>
       </c>
       <c r="H271" t="n">
-        <v>0.5893</v>
+        <v>0.6197</v>
       </c>
     </row>
     <row r="272">
@@ -9666,10 +9666,10 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>0.8416</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="H272" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.8021</v>
       </c>
     </row>
     <row r="273">
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="G273" t="n">
-        <v>0.8426</v>
+        <v>0.8578</v>
       </c>
       <c r="H273" t="n">
-        <v>0.8075</v>
+        <v>0.8273</v>
       </c>
     </row>
     <row r="274">
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="G274" t="n">
-        <v>0.8663</v>
+        <v>0.8711</v>
       </c>
       <c r="H274" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.843</v>
       </c>
     </row>
     <row r="275">
@@ -9768,10 +9768,10 @@
         </is>
       </c>
       <c r="G275" t="n">
-        <v>0.9489</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="H275" t="n">
-        <v>0.9337</v>
+        <v>0.9535</v>
       </c>
     </row>
     <row r="276">
@@ -9802,10 +9802,10 @@
         </is>
       </c>
       <c r="G276" t="n">
-        <v>0.9500999999999999</v>
+        <v>0.9527</v>
       </c>
       <c r="H276" t="n">
-        <v>0.9401</v>
+        <v>0.9429</v>
       </c>
     </row>
     <row r="277">
@@ -10265,16 +10265,16 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -10299,16 +10299,16 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -10346,10 +10346,10 @@
         </is>
       </c>
       <c r="G292" t="n">
-        <v>0.0596</v>
+        <v>0.0605</v>
       </c>
       <c r="H292" t="n">
-        <v>0.0497</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="293">
@@ -10380,10 +10380,10 @@
         </is>
       </c>
       <c r="G293" t="n">
-        <v>0.0318</v>
+        <v>0.0326</v>
       </c>
       <c r="H293" t="n">
-        <v>0.0244</v>
+        <v>0.0247</v>
       </c>
     </row>
     <row r="294">
@@ -10414,10 +10414,10 @@
         </is>
       </c>
       <c r="G294" t="n">
-        <v>0.0501</v>
+        <v>0.0511</v>
       </c>
       <c r="H294" t="n">
-        <v>0.0392</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="295">
@@ -10448,10 +10448,10 @@
         </is>
       </c>
       <c r="G295" t="n">
-        <v>0.0422</v>
+        <v>0.0391</v>
       </c>
       <c r="H295" t="n">
-        <v>0.0332</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="296">
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="G296" t="n">
-        <v>0.1157</v>
+        <v>0.117</v>
       </c>
       <c r="H296" t="n">
         <v>0.0867</v>
@@ -10503,23 +10503,23 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>0.19</v>
+        <v>0.1179</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1536</v>
+        <v>0.0892</v>
       </c>
     </row>
     <row r="298">
@@ -10537,23 +10537,23 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>0.1209</v>
+        <v>0.1999</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0941</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="299">
@@ -10584,10 +10584,10 @@
         </is>
       </c>
       <c r="G299" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="H299" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="300">
@@ -10618,10 +10618,10 @@
         </is>
       </c>
       <c r="G300" t="n">
-        <v>0.2991</v>
+        <v>0.2712</v>
       </c>
       <c r="H300" t="n">
-        <v>0.2619</v>
+        <v>0.2315</v>
       </c>
     </row>
     <row r="301">
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="G301" t="n">
-        <v>0.2041</v>
+        <v>0.1979</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1584</v>
+        <v>0.1568</v>
       </c>
     </row>
     <row r="302">
@@ -10686,10 +10686,10 @@
         </is>
       </c>
       <c r="G302" t="n">
-        <v>0.5285</v>
+        <v>0.5619</v>
       </c>
       <c r="H302" t="n">
-        <v>0.4995</v>
+        <v>0.5381</v>
       </c>
     </row>
     <row r="303">
@@ -10720,10 +10720,10 @@
         </is>
       </c>
       <c r="G303" t="n">
-        <v>0.6239</v>
+        <v>0.6152</v>
       </c>
       <c r="H303" t="n">
-        <v>0.5816</v>
+        <v>0.5748</v>
       </c>
     </row>
     <row r="304">
@@ -10754,10 +10754,10 @@
         </is>
       </c>
       <c r="G304" t="n">
-        <v>0.8305</v>
+        <v>0.867</v>
       </c>
       <c r="H304" t="n">
-        <v>0.7948</v>
+        <v>0.8337</v>
       </c>
     </row>
     <row r="305">
@@ -10788,10 +10788,10 @@
         </is>
       </c>
       <c r="G305" t="n">
-        <v>0.8507</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="H305" t="n">
-        <v>0.8131</v>
+        <v>0.8005</v>
       </c>
     </row>
     <row r="306">
@@ -11251,16 +11251,16 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -11285,16 +11285,16 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="G321" t="n">
-        <v>0.0482</v>
+        <v>0.045</v>
       </c>
       <c r="H321" t="n">
-        <v>0.0387</v>
+        <v>0.0371</v>
       </c>
     </row>
     <row r="322">
@@ -11366,10 +11366,10 @@
         </is>
       </c>
       <c r="G322" t="n">
-        <v>0.0282</v>
+        <v>0.0237</v>
       </c>
       <c r="H322" t="n">
-        <v>0.0208</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="323">
@@ -11400,10 +11400,10 @@
         </is>
       </c>
       <c r="G323" t="n">
-        <v>0.0492</v>
+        <v>0.0368</v>
       </c>
       <c r="H323" t="n">
-        <v>0.038</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="324">
@@ -11434,10 +11434,10 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>0.0441</v>
+        <v>0.0295</v>
       </c>
       <c r="H324" t="n">
-        <v>0.0361</v>
+        <v>0.0234</v>
       </c>
     </row>
     <row r="325">
@@ -11468,10 +11468,10 @@
         </is>
       </c>
       <c r="G325" t="n">
-        <v>0.0999</v>
+        <v>0.0785</v>
       </c>
       <c r="H325" t="n">
-        <v>0.077</v>
+        <v>0.0594</v>
       </c>
     </row>
     <row r="326">
@@ -11489,23 +11489,23 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G326" t="n">
-        <v>0.1913</v>
+        <v>0.0901</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1568</v>
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="327">
@@ -11523,23 +11523,23 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G327" t="n">
-        <v>0.1245</v>
+        <v>0.1519</v>
       </c>
       <c r="H327" t="n">
-        <v>0.0968</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="328">
@@ -11570,10 +11570,10 @@
         </is>
       </c>
       <c r="G328" t="n">
-        <v>0.0806</v>
+        <v>0.0696</v>
       </c>
       <c r="H328" t="n">
-        <v>0.0619</v>
+        <v>0.0524</v>
       </c>
     </row>
     <row r="329">
@@ -11604,10 +11604,10 @@
         </is>
       </c>
       <c r="G329" t="n">
-        <v>0.286</v>
+        <v>0.2445</v>
       </c>
       <c r="H329" t="n">
-        <v>0.2451</v>
+        <v>0.2056</v>
       </c>
     </row>
     <row r="330">
@@ -11638,10 +11638,10 @@
         </is>
       </c>
       <c r="G330" t="n">
-        <v>0.1925</v>
+        <v>0.1727</v>
       </c>
       <c r="H330" t="n">
-        <v>0.1574</v>
+        <v>0.1422</v>
       </c>
     </row>
     <row r="331">
@@ -11672,10 +11672,10 @@
         </is>
       </c>
       <c r="G331" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4619</v>
       </c>
       <c r="H331" t="n">
-        <v>0.4715</v>
+        <v>0.4381</v>
       </c>
     </row>
     <row r="332">
@@ -11706,10 +11706,10 @@
         </is>
       </c>
       <c r="G332" t="n">
-        <v>0.6286</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="H332" t="n">
-        <v>0.5989</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="333">
@@ -11740,10 +11740,10 @@
         </is>
       </c>
       <c r="G333" t="n">
-        <v>0.8208</v>
+        <v>0.8296</v>
       </c>
       <c r="H333" t="n">
-        <v>0.7904</v>
+        <v>0.7973</v>
       </c>
     </row>
     <row r="334">
@@ -11774,10 +11774,10 @@
         </is>
       </c>
       <c r="G334" t="n">
-        <v>0.836</v>
+        <v>0.8008</v>
       </c>
       <c r="H334" t="n">
-        <v>0.8036</v>
+        <v>0.7673</v>
       </c>
     </row>
     <row r="335">
@@ -12237,16 +12237,16 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -12271,16 +12271,16 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -12318,10 +12318,10 @@
         </is>
       </c>
       <c r="G350" t="n">
-        <v>0.0463</v>
+        <v>0.0399</v>
       </c>
       <c r="H350" t="n">
-        <v>0.0383</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="351">
@@ -12352,10 +12352,10 @@
         </is>
       </c>
       <c r="G351" t="n">
-        <v>0.0252</v>
+        <v>0.0244</v>
       </c>
       <c r="H351" t="n">
-        <v>0.0189</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="352">
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="G352" t="n">
-        <v>0.0357</v>
+        <v>0.0378</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0282</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="353">
@@ -12420,10 +12420,10 @@
         </is>
       </c>
       <c r="G353" t="n">
-        <v>0.0269</v>
+        <v>0.03</v>
       </c>
       <c r="H353" t="n">
-        <v>0.0232</v>
+        <v>0.0251</v>
       </c>
     </row>
     <row r="354">
@@ -12454,10 +12454,10 @@
         </is>
       </c>
       <c r="G354" t="n">
-        <v>0.0682</v>
+        <v>0.0648</v>
       </c>
       <c r="H354" t="n">
-        <v>0.0539</v>
+        <v>0.0511</v>
       </c>
     </row>
     <row r="355">
@@ -12475,23 +12475,23 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G355" t="n">
-        <v>0.1329</v>
+        <v>0.0776</v>
       </c>
       <c r="H355" t="n">
-        <v>0.1063</v>
+        <v>0.0617</v>
       </c>
     </row>
     <row r="356">
@@ -12509,23 +12509,23 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.139</v>
       </c>
       <c r="H356" t="n">
-        <v>0.0765</v>
+        <v>0.1139</v>
       </c>
     </row>
     <row r="357">
@@ -12556,10 +12556,10 @@
         </is>
       </c>
       <c r="G357" t="n">
-        <v>0.0562</v>
+        <v>0.0589</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0448</v>
+        <v>0.0457</v>
       </c>
     </row>
     <row r="358">
@@ -12590,10 +12590,10 @@
         </is>
       </c>
       <c r="G358" t="n">
-        <v>0.2089</v>
+        <v>0.22</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1695</v>
+        <v>0.1818</v>
       </c>
     </row>
     <row r="359">
@@ -12624,10 +12624,10 @@
         </is>
       </c>
       <c r="G359" t="n">
-        <v>0.1638</v>
+        <v>0.157</v>
       </c>
       <c r="H359" t="n">
-        <v>0.1337</v>
+        <v>0.1289</v>
       </c>
     </row>
     <row r="360">
@@ -12658,10 +12658,10 @@
         </is>
       </c>
       <c r="G360" t="n">
-        <v>0.4184</v>
+        <v>0.4252</v>
       </c>
       <c r="H360" t="n">
-        <v>0.3761</v>
+        <v>0.3848</v>
       </c>
     </row>
     <row r="361">
@@ -12692,10 +12692,10 @@
         </is>
       </c>
       <c r="G361" t="n">
-        <v>0.4011</v>
+        <v>0.482</v>
       </c>
       <c r="H361" t="n">
-        <v>0.3714</v>
+        <v>0.4551</v>
       </c>
     </row>
     <row r="362">
@@ -12726,10 +12726,10 @@
         </is>
       </c>
       <c r="G362" t="n">
-        <v>0.7734</v>
+        <v>0.8095</v>
       </c>
       <c r="H362" t="n">
-        <v>0.7276</v>
+        <v>0.7773</v>
       </c>
     </row>
     <row r="363">
@@ -12760,10 +12760,10 @@
         </is>
       </c>
       <c r="G363" t="n">
-        <v>0.7459</v>
+        <v>0.7718</v>
       </c>
       <c r="H363" t="n">
-        <v>0.7225</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="364">
@@ -13223,16 +13223,16 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -13257,16 +13257,16 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -13304,10 +13304,10 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>0.0201</v>
+        <v>0.0189</v>
       </c>
       <c r="H379" t="n">
-        <v>0.0155</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="380">
@@ -13338,10 +13338,10 @@
         </is>
       </c>
       <c r="G380" t="n">
-        <v>0.0159</v>
+        <v>0.0143</v>
       </c>
       <c r="H380" t="n">
-        <v>0.013</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="381">
@@ -13372,10 +13372,10 @@
         </is>
       </c>
       <c r="G381" t="n">
-        <v>0.0173</v>
+        <v>0.0153</v>
       </c>
       <c r="H381" t="n">
-        <v>0.0152</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="382">
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="G382" t="n">
-        <v>0.0223</v>
+        <v>0.0203</v>
       </c>
       <c r="H382" t="n">
-        <v>0.0186</v>
+        <v>0.0161</v>
       </c>
     </row>
     <row r="383">
@@ -13440,10 +13440,10 @@
         </is>
       </c>
       <c r="G383" t="n">
-        <v>0.0258</v>
+        <v>0.0238</v>
       </c>
       <c r="H383" t="n">
-        <v>0.0202</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="384">
@@ -13461,23 +13461,23 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>0.0559</v>
+        <v>0.0279</v>
       </c>
       <c r="H384" t="n">
-        <v>0.0474</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="385">
@@ -13495,23 +13495,23 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G385" t="n">
-        <v>0.0339</v>
+        <v>0.0366</v>
       </c>
       <c r="H385" t="n">
-        <v>0.0276</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="386">
@@ -13542,10 +13542,10 @@
         </is>
       </c>
       <c r="G386" t="n">
-        <v>0.0216</v>
+        <v>0.0163</v>
       </c>
       <c r="H386" t="n">
-        <v>0.017</v>
+        <v>0.0128</v>
       </c>
     </row>
     <row r="387">
@@ -13576,10 +13576,10 @@
         </is>
       </c>
       <c r="G387" t="n">
-        <v>0.0857</v>
+        <v>0.0702</v>
       </c>
       <c r="H387" t="n">
-        <v>0.0732</v>
+        <v>0.0582</v>
       </c>
     </row>
     <row r="388">
@@ -13610,10 +13610,10 @@
         </is>
       </c>
       <c r="G388" t="n">
-        <v>0.0663</v>
+        <v>0.0465</v>
       </c>
       <c r="H388" t="n">
-        <v>0.0511</v>
+        <v>0.0358</v>
       </c>
     </row>
     <row r="389">
@@ -13644,10 +13644,10 @@
         </is>
       </c>
       <c r="G389" t="n">
-        <v>0.2052</v>
+        <v>0.1663</v>
       </c>
       <c r="H389" t="n">
-        <v>0.1695</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="390">
@@ -13678,10 +13678,10 @@
         </is>
       </c>
       <c r="G390" t="n">
-        <v>0.2096</v>
+        <v>0.2027</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1792</v>
+        <v>0.1704</v>
       </c>
     </row>
     <row r="391">
@@ -13712,10 +13712,10 @@
         </is>
       </c>
       <c r="G391" t="n">
-        <v>0.2724</v>
+        <v>0.2227</v>
       </c>
       <c r="H391" t="n">
-        <v>0.2266</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="392">
@@ -13746,10 +13746,10 @@
         </is>
       </c>
       <c r="G392" t="n">
-        <v>0.519</v>
+        <v>0.462</v>
       </c>
       <c r="H392" t="n">
-        <v>0.4764</v>
+        <v>0.4153</v>
       </c>
     </row>
     <row r="393">
@@ -14209,16 +14209,16 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G406" t="n">
@@ -14243,16 +14243,16 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G407" t="n">
@@ -14290,10 +14290,10 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>0.0304</v>
+        <v>0.0283</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0234</v>
+        <v>0.0222</v>
       </c>
     </row>
     <row r="409">
@@ -14324,10 +14324,10 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>0.0166</v>
+        <v>0.0167</v>
       </c>
       <c r="H409" t="n">
-        <v>0.0122</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="410">
@@ -14358,10 +14358,10 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>0.0235</v>
+        <v>0.0222</v>
       </c>
       <c r="H410" t="n">
-        <v>0.0184</v>
+        <v>0.0174</v>
       </c>
     </row>
     <row r="411">
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>0.0175</v>
+        <v>0.0188</v>
       </c>
       <c r="H411" t="n">
-        <v>0.0137</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="412">
@@ -14426,10 +14426,10 @@
         </is>
       </c>
       <c r="G412" t="n">
-        <v>0.0365</v>
+        <v>0.035</v>
       </c>
       <c r="H412" t="n">
-        <v>0.0279</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="413">
@@ -14447,23 +14447,23 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>0.0474</v>
+        <v>0.0381</v>
       </c>
       <c r="H413" t="n">
-        <v>0.0376</v>
+        <v>0.0292</v>
       </c>
     </row>
     <row r="414">
@@ -14481,23 +14481,23 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G414" t="n">
-        <v>0.0404</v>
+        <v>0.0475</v>
       </c>
       <c r="H414" t="n">
-        <v>0.0304</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="415">
@@ -14528,10 +14528,10 @@
         </is>
       </c>
       <c r="G415" t="n">
-        <v>0.0326</v>
+        <v>0.0343</v>
       </c>
       <c r="H415" t="n">
-        <v>0.0253</v>
+        <v>0.0268</v>
       </c>
     </row>
     <row r="416">
@@ -14562,10 +14562,10 @@
         </is>
       </c>
       <c r="G416" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0979</v>
       </c>
       <c r="H416" t="n">
-        <v>0.077</v>
+        <v>0.0796</v>
       </c>
     </row>
     <row r="417">
@@ -14596,10 +14596,10 @@
         </is>
       </c>
       <c r="G417" t="n">
-        <v>0.0599</v>
+        <v>0.0571</v>
       </c>
       <c r="H417" t="n">
-        <v>0.0499</v>
+        <v>0.0473</v>
       </c>
     </row>
     <row r="418">
@@ -14630,10 +14630,10 @@
         </is>
       </c>
       <c r="G418" t="n">
-        <v>0.1869</v>
+        <v>0.1995</v>
       </c>
       <c r="H418" t="n">
-        <v>0.1493</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="419">
@@ -14664,10 +14664,10 @@
         </is>
       </c>
       <c r="G419" t="n">
-        <v>0.1964</v>
+        <v>0.2327</v>
       </c>
       <c r="H419" t="n">
-        <v>0.164</v>
+        <v>0.1992</v>
       </c>
     </row>
     <row r="420">
@@ -14698,10 +14698,10 @@
         </is>
       </c>
       <c r="G420" t="n">
-        <v>0.2775</v>
+        <v>0.254</v>
       </c>
       <c r="H420" t="n">
-        <v>0.2541</v>
+        <v>0.2282</v>
       </c>
     </row>
     <row r="421">
@@ -14732,10 +14732,10 @@
         </is>
       </c>
       <c r="G421" t="n">
-        <v>0.5236</v>
+        <v>0.5847</v>
       </c>
       <c r="H421" t="n">
-        <v>0.481</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="422">
@@ -15195,16 +15195,16 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G435" t="n">
@@ -15229,16 +15229,16 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G436" t="n">
@@ -15433,16 +15433,16 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G442" t="n">
@@ -15467,16 +15467,16 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G443" t="n">
@@ -16181,16 +16181,16 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G464" t="n">
@@ -16215,16 +16215,16 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G465" t="n">
@@ -16419,16 +16419,16 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G471" t="n">
@@ -16453,16 +16453,16 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G472" t="n">
@@ -17167,16 +17167,16 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G493" t="n">
@@ -17201,16 +17201,16 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G494" t="n">
@@ -17405,16 +17405,16 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G500" t="n">
@@ -17439,16 +17439,16 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G501" t="n">
@@ -18153,16 +18153,16 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G522" t="n">
@@ -18187,16 +18187,16 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G523" t="n">
@@ -18391,16 +18391,16 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G529" t="n">
@@ -18425,16 +18425,16 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G530" t="n">
@@ -19139,16 +19139,16 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G551" t="n">
@@ -19173,16 +19173,16 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G552" t="n">
@@ -19377,16 +19377,16 @@
         </is>
       </c>
       <c r="D558" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G558" t="n">
@@ -19411,16 +19411,16 @@
         </is>
       </c>
       <c r="D559" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G559" t="n">
@@ -20125,16 +20125,16 @@
         </is>
       </c>
       <c r="D580" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G580" t="n">
@@ -20159,16 +20159,16 @@
         </is>
       </c>
       <c r="D581" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G581" t="n">
@@ -20363,16 +20363,16 @@
         </is>
       </c>
       <c r="D587" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G587" t="n">
@@ -20397,16 +20397,16 @@
         </is>
       </c>
       <c r="D588" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G588" t="n">
@@ -21111,16 +21111,16 @@
         </is>
       </c>
       <c r="D609" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G609" t="n">
@@ -21145,16 +21145,16 @@
         </is>
       </c>
       <c r="D610" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G610" t="n">
@@ -21349,16 +21349,16 @@
         </is>
       </c>
       <c r="D616" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G616" t="n">
@@ -21383,16 +21383,16 @@
         </is>
       </c>
       <c r="D617" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G617" t="n">
@@ -22097,16 +22097,16 @@
         </is>
       </c>
       <c r="D638" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G638" t="n">
@@ -22131,16 +22131,16 @@
         </is>
       </c>
       <c r="D639" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G639" t="n">
@@ -22335,16 +22335,16 @@
         </is>
       </c>
       <c r="D645" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G645" t="n">
@@ -22369,16 +22369,16 @@
         </is>
       </c>
       <c r="D646" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G646" t="n">
@@ -23083,16 +23083,16 @@
         </is>
       </c>
       <c r="D667" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G667" t="n">
@@ -23117,16 +23117,16 @@
         </is>
       </c>
       <c r="D668" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G668" t="n">
@@ -23321,16 +23321,16 @@
         </is>
       </c>
       <c r="D674" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G674" t="n">
@@ -23355,16 +23355,16 @@
         </is>
       </c>
       <c r="D675" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G675" t="n">
@@ -24069,16 +24069,16 @@
         </is>
       </c>
       <c r="D696" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G696" t="n">
@@ -24103,16 +24103,16 @@
         </is>
       </c>
       <c r="D697" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G697" t="n">
@@ -24307,16 +24307,16 @@
         </is>
       </c>
       <c r="D703" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G703" t="n">
@@ -24341,16 +24341,16 @@
         </is>
       </c>
       <c r="D704" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G704" t="n">
@@ -25055,16 +25055,16 @@
         </is>
       </c>
       <c r="D725" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G725" t="n">
@@ -25089,16 +25089,16 @@
         </is>
       </c>
       <c r="D726" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G726" t="n">
@@ -25293,16 +25293,16 @@
         </is>
       </c>
       <c r="D732" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G732" t="n">
@@ -25327,16 +25327,16 @@
         </is>
       </c>
       <c r="D733" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G733" t="n">
@@ -26041,16 +26041,16 @@
         </is>
       </c>
       <c r="D754" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G754" t="n">
@@ -26075,16 +26075,16 @@
         </is>
       </c>
       <c r="D755" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G755" t="n">
@@ -26279,16 +26279,16 @@
         </is>
       </c>
       <c r="D761" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E761" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G761" t="n">
@@ -26313,16 +26313,16 @@
         </is>
       </c>
       <c r="D762" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E762" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G762" t="n">
@@ -27027,16 +27027,16 @@
         </is>
       </c>
       <c r="D783" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G783" t="n">
@@ -27061,16 +27061,16 @@
         </is>
       </c>
       <c r="D784" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G784" t="n">
@@ -27265,16 +27265,16 @@
         </is>
       </c>
       <c r="D790" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G790" t="n">
@@ -27299,16 +27299,16 @@
         </is>
       </c>
       <c r="D791" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G791" t="n">
@@ -28013,16 +28013,16 @@
         </is>
       </c>
       <c r="D812" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="G812" t="n">
@@ -28047,16 +28047,16 @@
         </is>
       </c>
       <c r="D813" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="G813" t="n">
@@ -28068,16 +28068,16 @@
     </row>
     <row r="814">
       <c r="A814" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D814" t="n">
@@ -28102,16 +28102,16 @@
     </row>
     <row r="815">
       <c r="A815" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D815" t="n">
@@ -28136,16 +28136,16 @@
     </row>
     <row r="816">
       <c r="A816" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D816" t="n">
@@ -28170,16 +28170,16 @@
     </row>
     <row r="817">
       <c r="A817" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D817" t="n">
@@ -28204,16 +28204,16 @@
     </row>
     <row r="818">
       <c r="A818" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D818" t="n">
@@ -28238,29 +28238,29 @@
     </row>
     <row r="819">
       <c r="A819" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D819" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E819" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G819" t="n">
@@ -28272,29 +28272,29 @@
     </row>
     <row r="820">
       <c r="A820" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D820" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E820" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G820" t="n">
@@ -28306,16 +28306,16 @@
     </row>
     <row r="821">
       <c r="A821" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D821" t="n">
@@ -28340,16 +28340,16 @@
     </row>
     <row r="822">
       <c r="A822" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D822" t="n">
@@ -28374,16 +28374,16 @@
     </row>
     <row r="823">
       <c r="A823" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D823" t="n">
@@ -28408,16 +28408,16 @@
     </row>
     <row r="824">
       <c r="A824" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D824" t="n">
@@ -28442,16 +28442,16 @@
     </row>
     <row r="825">
       <c r="A825" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D825" t="n">
@@ -28476,16 +28476,16 @@
     </row>
     <row r="826">
       <c r="A826" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D826" t="n">
@@ -28510,16 +28510,16 @@
     </row>
     <row r="827">
       <c r="A827" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D827" t="n">
@@ -28544,16 +28544,16 @@
     </row>
     <row r="828">
       <c r="A828" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D828" t="n">
@@ -28578,16 +28578,16 @@
     </row>
     <row r="829">
       <c r="A829" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D829" t="n">
@@ -28612,16 +28612,16 @@
     </row>
     <row r="830">
       <c r="A830" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D830" t="n">
@@ -28646,16 +28646,16 @@
     </row>
     <row r="831">
       <c r="A831" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D831" t="n">
@@ -28680,16 +28680,16 @@
     </row>
     <row r="832">
       <c r="A832" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D832" t="n">
@@ -28714,16 +28714,16 @@
     </row>
     <row r="833">
       <c r="A833" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D833" t="n">
@@ -28748,16 +28748,16 @@
     </row>
     <row r="834">
       <c r="A834" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D834" t="n">
@@ -28782,16 +28782,16 @@
     </row>
     <row r="835">
       <c r="A835" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D835" t="n">
@@ -28816,16 +28816,16 @@
     </row>
     <row r="836">
       <c r="A836" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D836" t="n">
@@ -28850,16 +28850,16 @@
     </row>
     <row r="837">
       <c r="A837" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D837" t="n">
@@ -28884,16 +28884,16 @@
     </row>
     <row r="838">
       <c r="A838" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D838" t="n">
@@ -28918,16 +28918,16 @@
     </row>
     <row r="839">
       <c r="A839" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D839" t="n">
@@ -28952,16 +28952,16 @@
     </row>
     <row r="840">
       <c r="A840" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D840" t="n">
@@ -28986,16 +28986,16 @@
     </row>
     <row r="841">
       <c r="A841" t="n">
-        <v>1610612762</v>
+        <v>1610612758</v>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Jazz</t>
+          <t>Kings</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="D841" t="n">
@@ -29020,29 +29020,29 @@
     </row>
     <row r="842">
       <c r="A842" t="n">
+        <v>1610612758</v>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Kings</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="D842" t="n">
         <v>1610612762</v>
       </c>
-      <c r="B842" t="inlineStr">
+      <c r="E842" t="inlineStr">
         <is>
           <t>Jazz</t>
         </is>
       </c>
-      <c r="C842" t="inlineStr">
+      <c r="F842" t="inlineStr">
         <is>
           <t>UTA</t>
-        </is>
-      </c>
-      <c r="D842" t="n">
-        <v>1610612758</v>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>Kings</t>
-        </is>
-      </c>
-      <c r="F842" t="inlineStr">
-        <is>
-          <t>SAC</t>
         </is>
       </c>
       <c r="G842" t="n">
@@ -29054,16 +29054,16 @@
     </row>
     <row r="843">
       <c r="A843" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D843" t="n">
@@ -29088,16 +29088,16 @@
     </row>
     <row r="844">
       <c r="A844" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D844" t="n">
@@ -29122,16 +29122,16 @@
     </row>
     <row r="845">
       <c r="A845" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D845" t="n">
@@ -29156,16 +29156,16 @@
     </row>
     <row r="846">
       <c r="A846" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D846" t="n">
@@ -29190,16 +29190,16 @@
     </row>
     <row r="847">
       <c r="A847" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D847" t="n">
@@ -29224,29 +29224,29 @@
     </row>
     <row r="848">
       <c r="A848" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D848" t="n">
-        <v>1610612755</v>
+        <v>1610612761</v>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>76ers</t>
+          <t>Raptors</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="G848" t="n">
@@ -29258,29 +29258,29 @@
     </row>
     <row r="849">
       <c r="A849" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D849" t="n">
-        <v>1610612761</v>
+        <v>1610612755</v>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>Raptors</t>
+          <t>76ers</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="G849" t="n">
@@ -29292,16 +29292,16 @@
     </row>
     <row r="850">
       <c r="A850" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D850" t="n">
@@ -29326,16 +29326,16 @@
     </row>
     <row r="851">
       <c r="A851" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D851" t="n">
@@ -29360,16 +29360,16 @@
     </row>
     <row r="852">
       <c r="A852" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D852" t="n">
@@ -29394,16 +29394,16 @@
     </row>
     <row r="853">
       <c r="A853" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D853" t="n">
@@ -29428,16 +29428,16 @@
     </row>
     <row r="854">
       <c r="A854" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D854" t="n">
@@ -29462,16 +29462,16 @@
     </row>
     <row r="855">
       <c r="A855" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D855" t="n">
@@ -29496,16 +29496,16 @@
     </row>
     <row r="856">
       <c r="A856" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D856" t="n">
@@ -29530,16 +29530,16 @@
     </row>
     <row r="857">
       <c r="A857" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D857" t="n">
@@ -29564,16 +29564,16 @@
     </row>
     <row r="858">
       <c r="A858" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D858" t="n">
@@ -29598,16 +29598,16 @@
     </row>
     <row r="859">
       <c r="A859" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D859" t="n">
@@ -29632,16 +29632,16 @@
     </row>
     <row r="860">
       <c r="A860" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D860" t="n">
@@ -29666,16 +29666,16 @@
     </row>
     <row r="861">
       <c r="A861" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D861" t="n">
@@ -29700,16 +29700,16 @@
     </row>
     <row r="862">
       <c r="A862" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D862" t="n">
@@ -29734,16 +29734,16 @@
     </row>
     <row r="863">
       <c r="A863" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D863" t="n">
@@ -29768,16 +29768,16 @@
     </row>
     <row r="864">
       <c r="A864" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D864" t="n">
@@ -29802,16 +29802,16 @@
     </row>
     <row r="865">
       <c r="A865" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D865" t="n">
@@ -29836,16 +29836,16 @@
     </row>
     <row r="866">
       <c r="A866" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D866" t="n">
@@ -29870,16 +29870,16 @@
     </row>
     <row r="867">
       <c r="A867" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D867" t="n">
@@ -29904,16 +29904,16 @@
     </row>
     <row r="868">
       <c r="A868" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D868" t="n">
@@ -29938,16 +29938,16 @@
     </row>
     <row r="869">
       <c r="A869" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D869" t="n">
@@ -29972,16 +29972,16 @@
     </row>
     <row r="870">
       <c r="A870" t="n">
-        <v>1610612758</v>
+        <v>1610612762</v>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Kings</t>
+          <t>Jazz</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="D870" t="n">
@@ -30006,29 +30006,29 @@
     </row>
     <row r="871">
       <c r="A871" t="n">
+        <v>1610612762</v>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Jazz</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="D871" t="n">
         <v>1610612758</v>
       </c>
-      <c r="B871" t="inlineStr">
+      <c r="E871" t="inlineStr">
         <is>
           <t>Kings</t>
         </is>
       </c>
-      <c r="C871" t="inlineStr">
+      <c r="F871" t="inlineStr">
         <is>
           <t>SAC</t>
-        </is>
-      </c>
-      <c r="D871" t="n">
-        <v>1610612762</v>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>Jazz</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>UTA</t>
         </is>
       </c>
       <c r="G871" t="n">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4428</v>
+        <v>0.4563</v>
       </c>
       <c r="H2">
-        <v>0.3947</v>
+        <v>0.4037</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5048</v>
+        <v>0.5087</v>
       </c>
       <c r="H4">
-        <v>0.461</v>
+        <v>0.4679</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -728,10 +728,10 @@
         <v>43</v>
       </c>
       <c r="G6">
-        <v>0.7476</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="H6">
-        <v>0.7239</v>
+        <v>0.7594</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.6833</v>
+        <v>0.6501</v>
       </c>
       <c r="H8">
-        <v>0.6505</v>
+        <v>0.6223</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -832,10 +832,10 @@
         <v>47</v>
       </c>
       <c r="G10">
-        <v>0.8637</v>
+        <v>0.8568</v>
       </c>
       <c r="H10">
-        <v>0.833</v>
+        <v>0.8243</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -858,10 +858,10 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>0.9588</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="H11">
-        <v>0.9493</v>
+        <v>0.9466</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -884,10 +884,10 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>0.967</v>
+        <v>0.965</v>
       </c>
       <c r="H12">
-        <v>0.9591</v>
+        <v>0.9567</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.9578</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="H14">
-        <v>0.9488</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -962,10 +962,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>0.9791</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="H15">
-        <v>0.9733000000000001</v>
+        <v>0.9712</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.6052999999999999</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="H31">
-        <v>0.5572</v>
+        <v>0.5437</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="G32">
-        <v>0.6704</v>
+        <v>0.6693</v>
       </c>
       <c r="H32">
-        <v>0.6482</v>
+        <v>0.6474</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.8424</v>
+        <v>0.8403</v>
       </c>
       <c r="H34">
-        <v>0.8015</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1482,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="G35">
-        <v>0.8823</v>
+        <v>0.8976</v>
       </c>
       <c r="H35">
-        <v>0.8545</v>
+        <v>0.8699</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1508,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="G36">
-        <v>0.9236</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="H36">
-        <v>0.9042</v>
+        <v>0.9018</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.7484</v>
+        <v>0.7346</v>
       </c>
       <c r="H37">
-        <v>0.7085</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.9492</v>
+        <v>0.9473</v>
       </c>
       <c r="H38">
-        <v>0.9319</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1586,10 +1586,10 @@
         <v>47</v>
       </c>
       <c r="G39">
-        <v>0.9287</v>
+        <v>0.9232</v>
       </c>
       <c r="H39">
-        <v>0.9029</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1612,10 +1612,10 @@
         <v>48</v>
       </c>
       <c r="G40">
-        <v>0.9781</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="H40">
-        <v>0.9715</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1638,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="G41">
-        <v>0.9844000000000001</v>
+        <v>0.9837</v>
       </c>
       <c r="H41">
-        <v>0.9782999999999999</v>
+        <v>0.9776</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1690,10 +1690,10 @@
         <v>51</v>
       </c>
       <c r="G43">
-        <v>0.9802</v>
+        <v>0.9789</v>
       </c>
       <c r="H43">
-        <v>0.974</v>
+        <v>0.9717</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2158,10 +2158,10 @@
         <v>39</v>
       </c>
       <c r="G61">
-        <v>0.3518</v>
+        <v>0.3526</v>
       </c>
       <c r="H61">
-        <v>0.3296</v>
+        <v>0.3307</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2210,10 +2210,10 @@
         <v>42</v>
       </c>
       <c r="G63">
-        <v>0.7336</v>
+        <v>0.7291</v>
       </c>
       <c r="H63">
-        <v>0.6903</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2236,10 +2236,10 @@
         <v>43</v>
       </c>
       <c r="G64">
-        <v>0.785</v>
+        <v>0.8086</v>
       </c>
       <c r="H64">
-        <v>0.7521</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2262,10 +2262,10 @@
         <v>44</v>
       </c>
       <c r="G65">
-        <v>0.8794</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="H65">
-        <v>0.8598</v>
+        <v>0.8579</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.6282</v>
+        <v>0.62</v>
       </c>
       <c r="H66">
-        <v>0.5807</v>
+        <v>0.5744</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2314,10 +2314,10 @@
         <v>46</v>
       </c>
       <c r="G67">
-        <v>0.9225</v>
+        <v>0.9206</v>
       </c>
       <c r="H67">
-        <v>0.8974</v>
+        <v>0.8943</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2366,10 +2366,10 @@
         <v>48</v>
       </c>
       <c r="G69">
-        <v>0.9693000000000001</v>
+        <v>0.9663</v>
       </c>
       <c r="H69">
-        <v>0.9599</v>
+        <v>0.9563</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="G70">
-        <v>0.9777</v>
+        <v>0.9769</v>
       </c>
       <c r="H70">
-        <v>0.9703000000000001</v>
+        <v>0.9691</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2444,10 +2444,10 @@
         <v>51</v>
       </c>
       <c r="G72">
-        <v>0.9701</v>
+        <v>0.9678</v>
       </c>
       <c r="H72">
-        <v>0.9611</v>
+        <v>0.9585</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2470,10 +2470,10 @@
         <v>52</v>
       </c>
       <c r="G73">
-        <v>0.9871</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="H73">
-        <v>0.9835</v>
+        <v>0.9808</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.539</v>
+        <v>0.5321</v>
       </c>
       <c r="H89">
-        <v>0.4952</v>
+        <v>0.4913</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.7753</v>
+        <v>0.7671</v>
       </c>
       <c r="H92">
-        <v>0.7289</v>
+        <v>0.7227</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2990,10 +2990,10 @@
         <v>43</v>
       </c>
       <c r="G93">
-        <v>0.7999000000000001</v>
+        <v>0.8097</v>
       </c>
       <c r="H93">
-        <v>0.7651</v>
+        <v>0.7772</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3016,10 +3016,10 @@
         <v>44</v>
       </c>
       <c r="G94">
-        <v>0.8768</v>
+        <v>0.872</v>
       </c>
       <c r="H94">
-        <v>0.8515</v>
+        <v>0.8457</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.6634</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="H95">
-        <v>0.6145</v>
+        <v>0.5993000000000001</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3068,10 +3068,10 @@
         <v>46</v>
       </c>
       <c r="G96">
-        <v>0.9127</v>
+        <v>0.907</v>
       </c>
       <c r="H96">
-        <v>0.8895</v>
+        <v>0.8845</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3094,10 +3094,10 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.8941</v>
+        <v>0.8919</v>
       </c>
       <c r="H97">
-        <v>0.8625</v>
+        <v>0.8596</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3120,10 +3120,10 @@
         <v>48</v>
       </c>
       <c r="G98">
-        <v>0.9714</v>
+        <v>0.9701</v>
       </c>
       <c r="H98">
-        <v>0.9631999999999999</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3146,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="G99">
-        <v>0.9795</v>
+        <v>0.9765</v>
       </c>
       <c r="H99">
-        <v>0.9746</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3198,10 +3198,10 @@
         <v>51</v>
       </c>
       <c r="G101">
-        <v>0.9728</v>
+        <v>0.9715</v>
       </c>
       <c r="H101">
-        <v>0.9684</v>
+        <v>0.9673</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3666,10 +3666,10 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.1985</v>
+        <v>0.2023</v>
       </c>
       <c r="H119">
-        <v>0.1576</v>
+        <v>0.1597</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3692,10 +3692,10 @@
         <v>40</v>
       </c>
       <c r="G120">
-        <v>0.3097</v>
+        <v>0.316</v>
       </c>
       <c r="H120">
-        <v>0.2664</v>
+        <v>0.2709</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3718,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2711</v>
+        <v>0.2773</v>
       </c>
       <c r="H121">
-        <v>0.2247</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3744,10 +3744,10 @@
         <v>43</v>
       </c>
       <c r="G122">
-        <v>0.5741000000000001</v>
+        <v>0.6007</v>
       </c>
       <c r="H122">
-        <v>0.5385</v>
+        <v>0.5661</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3770,7 +3770,7 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.6889999999999999</v>
+        <v>0.6885</v>
       </c>
       <c r="H123">
         <v>0.6629</v>
@@ -3796,10 +3796,10 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.4313</v>
+        <v>0.4073</v>
       </c>
       <c r="H124">
-        <v>0.3914</v>
+        <v>0.3729</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3822,10 +3822,10 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.7983</v>
+        <v>0.7974</v>
       </c>
       <c r="H125">
-        <v>0.7596000000000001</v>
+        <v>0.7583</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3848,10 +3848,10 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.7092000000000001</v>
+        <v>0.7081</v>
       </c>
       <c r="H126">
-        <v>0.6593</v>
+        <v>0.6558</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3874,10 +3874,10 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.925</v>
+        <v>0.9233</v>
       </c>
       <c r="H127">
-        <v>0.8991</v>
+        <v>0.8967000000000001</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3900,10 +3900,10 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9446</v>
+        <v>0.9434</v>
       </c>
       <c r="H128">
-        <v>0.9268</v>
+        <v>0.9253</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3952,10 +3952,10 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9453</v>
+        <v>0.9449</v>
       </c>
       <c r="H130">
-        <v>0.9313</v>
+        <v>0.9308999999999999</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3978,10 +3978,10 @@
         <v>52</v>
       </c>
       <c r="G131">
-        <v>0.9777</v>
+        <v>0.9758</v>
       </c>
       <c r="H131">
-        <v>0.9713000000000001</v>
+        <v>0.9691</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4394,10 +4394,10 @@
         <v>38</v>
       </c>
       <c r="G147">
-        <v>0.2761</v>
+        <v>0.2406</v>
       </c>
       <c r="H147">
-        <v>0.2524</v>
+        <v>0.2213</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4420,10 +4420,10 @@
         <v>39</v>
       </c>
       <c r="G148">
-        <v>0.1455</v>
+        <v>0.1301</v>
       </c>
       <c r="H148">
-        <v>0.1177</v>
+        <v>0.1024</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4446,10 +4446,10 @@
         <v>40</v>
       </c>
       <c r="G149">
-        <v>0.2479</v>
+        <v>0.228</v>
       </c>
       <c r="H149">
-        <v>0.215</v>
+        <v>0.1914</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4472,10 +4472,10 @@
         <v>41</v>
       </c>
       <c r="G150">
-        <v>0.2349</v>
+        <v>0.2228</v>
       </c>
       <c r="H150">
-        <v>0.2001</v>
+        <v>0.1903</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4498,10 +4498,10 @@
         <v>42</v>
       </c>
       <c r="G151">
-        <v>0.4615</v>
+        <v>0.4339</v>
       </c>
       <c r="H151">
-        <v>0.4259</v>
+        <v>0.3993</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4524,10 +4524,10 @@
         <v>44</v>
       </c>
       <c r="G152">
-        <v>0.6193</v>
+        <v>0.5827</v>
       </c>
       <c r="H152">
-        <v>0.6</v>
+        <v>0.5623</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4550,10 +4550,10 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.3922</v>
+        <v>0.3419</v>
       </c>
       <c r="H153">
-        <v>0.3417</v>
+        <v>0.2996</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4576,10 +4576,10 @@
         <v>46</v>
       </c>
       <c r="G154">
-        <v>0.7425</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="H154">
-        <v>0.6978</v>
+        <v>0.6733</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4602,10 +4602,10 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>0.6793</v>
+        <v>0.6482</v>
       </c>
       <c r="H155">
-        <v>0.6297</v>
+        <v>0.5978</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4628,10 +4628,10 @@
         <v>48</v>
       </c>
       <c r="G156">
-        <v>0.913</v>
+        <v>0.9019</v>
       </c>
       <c r="H156">
-        <v>0.8877</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4654,10 +4654,10 @@
         <v>49</v>
       </c>
       <c r="G157">
-        <v>0.9298</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="H157">
-        <v>0.9083</v>
+        <v>0.8995</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4680,10 +4680,10 @@
         <v>50</v>
       </c>
       <c r="G158">
-        <v>0.9782999999999999</v>
+        <v>0.9778</v>
       </c>
       <c r="H158">
-        <v>0.9734</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -4706,10 +4706,10 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9319</v>
+        <v>0.9231</v>
       </c>
       <c r="H159">
-        <v>0.9177999999999999</v>
+        <v>0.9083</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4732,10 +4732,10 @@
         <v>52</v>
       </c>
       <c r="G160">
-        <v>0.9736</v>
+        <v>0.969</v>
       </c>
       <c r="H160">
-        <v>0.9657</v>
+        <v>0.9594</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5174,10 +5174,10 @@
         <v>39</v>
       </c>
       <c r="G177">
-        <v>0.0958</v>
+        <v>0.0982</v>
       </c>
       <c r="H177">
-        <v>0.0764</v>
+        <v>0.0791</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5200,10 +5200,10 @@
         <v>40</v>
       </c>
       <c r="G178">
-        <v>0.1402</v>
+        <v>0.1421</v>
       </c>
       <c r="H178">
-        <v>0.1206</v>
+        <v>0.1225</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5226,10 +5226,10 @@
         <v>41</v>
       </c>
       <c r="G179">
-        <v>0.1485</v>
+        <v>0.1543</v>
       </c>
       <c r="H179">
-        <v>0.1232</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5255,7 +5255,7 @@
         <v>0.3371</v>
       </c>
       <c r="H180">
-        <v>0.311</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5278,10 +5278,10 @@
         <v>43</v>
       </c>
       <c r="G181">
-        <v>0.4</v>
+        <v>0.4377</v>
       </c>
       <c r="H181">
-        <v>0.3807</v>
+        <v>0.4173</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5304,10 +5304,10 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.2988</v>
+        <v>0.2862</v>
       </c>
       <c r="H182">
-        <v>0.2514</v>
+        <v>0.2401</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5330,10 +5330,10 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.623</v>
+        <v>0.6147</v>
       </c>
       <c r="H183">
-        <v>0.5844</v>
+        <v>0.5749</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5356,10 +5356,10 @@
         <v>47</v>
       </c>
       <c r="G184">
-        <v>0.5613</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H184">
-        <v>0.5128</v>
+        <v>0.5127</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5382,10 +5382,10 @@
         <v>48</v>
       </c>
       <c r="G185">
-        <v>0.841</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="H185">
-        <v>0.8142</v>
+        <v>0.8091</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5408,10 +5408,10 @@
         <v>49</v>
       </c>
       <c r="G186">
-        <v>0.8786</v>
+        <v>0.8754</v>
       </c>
       <c r="H186">
-        <v>0.8497</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5434,10 +5434,10 @@
         <v>50</v>
       </c>
       <c r="G187">
-        <v>0.9575</v>
+        <v>0.9563</v>
       </c>
       <c r="H187">
-        <v>0.9506</v>
+        <v>0.9496</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5460,10 +5460,10 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.8828</v>
+        <v>0.8773</v>
       </c>
       <c r="H188">
-        <v>0.857</v>
+        <v>0.8501</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5486,10 +5486,10 @@
         <v>52</v>
       </c>
       <c r="G189">
-        <v>0.9615</v>
+        <v>0.9604</v>
       </c>
       <c r="H189">
-        <v>0.9528</v>
+        <v>0.9512</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -5902,10 +5902,10 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.3495</v>
+        <v>0.3777</v>
       </c>
       <c r="H205">
-        <v>0.3167</v>
+        <v>0.3499</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5928,10 +5928,10 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.2915</v>
+        <v>0.307</v>
       </c>
       <c r="H206">
-        <v>0.2516</v>
+        <v>0.2654</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -5954,10 +5954,10 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.4193</v>
+        <v>0.4256</v>
       </c>
       <c r="H207">
-        <v>0.3718</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5980,10 +5980,10 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.3855</v>
+        <v>0.4007</v>
       </c>
       <c r="H208">
-        <v>0.3366</v>
+        <v>0.3493</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6006,10 +6006,10 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.6086</v>
+        <v>0.6271</v>
       </c>
       <c r="H209">
-        <v>0.5687</v>
+        <v>0.5927</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6032,10 +6032,10 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.6583</v>
+        <v>0.7004</v>
       </c>
       <c r="H210">
-        <v>0.6078</v>
+        <v>0.6581</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6058,10 +6058,10 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.7486</v>
+        <v>0.7599</v>
       </c>
       <c r="H211">
-        <v>0.7012</v>
+        <v>0.7138</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -6084,10 +6084,10 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.8383</v>
+        <v>0.8519</v>
       </c>
       <c r="H212">
-        <v>0.7995</v>
+        <v>0.8183</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -6110,10 +6110,10 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.7762</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="H213">
-        <v>0.7355</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -6136,10 +6136,10 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.9399999999999999</v>
+        <v>0.9422</v>
       </c>
       <c r="H214">
-        <v>0.9239000000000001</v>
+        <v>0.9273</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -6162,10 +6162,10 @@
         <v>49</v>
       </c>
       <c r="G215">
-        <v>0.9560999999999999</v>
+        <v>0.9593</v>
       </c>
       <c r="H215">
-        <v>0.9423</v>
+        <v>0.9464</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -6214,10 +6214,10 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.9527</v>
+        <v>0.9545</v>
       </c>
       <c r="H217">
-        <v>0.9389</v>
+        <v>0.9418</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -6682,10 +6682,10 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.06809999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="H235">
-        <v>0.0508</v>
+        <v>0.0527</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -6708,10 +6708,10 @@
         <v>40</v>
       </c>
       <c r="G236">
-        <v>0.1026</v>
+        <v>0.1057</v>
       </c>
       <c r="H236">
-        <v>0.0775</v>
+        <v>0.0794</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -6734,10 +6734,10 @@
         <v>41</v>
       </c>
       <c r="G237">
-        <v>0.1105</v>
+        <v>0.1155</v>
       </c>
       <c r="H237">
-        <v>0.0873</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -6760,10 +6760,10 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.2404</v>
+        <v>0.2417</v>
       </c>
       <c r="H238">
-        <v>0.2017</v>
+        <v>0.2026</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -6786,10 +6786,10 @@
         <v>43</v>
       </c>
       <c r="G239">
-        <v>0.3022</v>
+        <v>0.3267</v>
       </c>
       <c r="H239">
-        <v>0.2575</v>
+        <v>0.2868</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -6812,10 +6812,10 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.4156</v>
+        <v>0.4251</v>
       </c>
       <c r="H240">
-        <v>0.377</v>
+        <v>0.3853</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -6838,10 +6838,10 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.2005</v>
+        <v>0.1817</v>
       </c>
       <c r="H241">
-        <v>0.1617</v>
+        <v>0.1481</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -6864,10 +6864,10 @@
         <v>47</v>
       </c>
       <c r="G242">
-        <v>0.424</v>
+        <v>0.4268</v>
       </c>
       <c r="H242">
-        <v>0.3984</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -6916,10 +6916,10 @@
         <v>49</v>
       </c>
       <c r="G244">
-        <v>0.8227</v>
+        <v>0.8156</v>
       </c>
       <c r="H244">
-        <v>0.7907999999999999</v>
+        <v>0.7804</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -6942,10 +6942,10 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9493</v>
+        <v>0.9462</v>
       </c>
       <c r="H245">
-        <v>0.9375</v>
+        <v>0.9342</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -6994,10 +6994,10 @@
         <v>52</v>
       </c>
       <c r="G247">
-        <v>0.9361</v>
+        <v>0.9348</v>
       </c>
       <c r="H247">
-        <v>0.9219000000000001</v>
+        <v>0.9207</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7410,10 +7410,10 @@
         <v>38</v>
       </c>
       <c r="G263">
-        <v>0.167</v>
+        <v>0.1757</v>
       </c>
       <c r="H263">
-        <v>0.1363</v>
+        <v>0.1432</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -7436,10 +7436,10 @@
         <v>39</v>
       </c>
       <c r="G264">
-        <v>0.09710000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="H264">
-        <v>0.0713</v>
+        <v>0.07679999999999999</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7488,10 +7488,10 @@
         <v>41</v>
       </c>
       <c r="G266">
-        <v>0.1375</v>
+        <v>0.1404</v>
       </c>
       <c r="H266">
-        <v>0.1059</v>
+        <v>0.1081</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3407</v>
+        <v>0.3442</v>
       </c>
       <c r="H267">
-        <v>0.2908</v>
+        <v>0.2919</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7540,10 +7540,10 @@
         <v>43</v>
       </c>
       <c r="G268">
-        <v>0.3703</v>
+        <v>0.4022</v>
       </c>
       <c r="H268">
-        <v>0.3207</v>
+        <v>0.3518</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -7566,10 +7566,10 @@
         <v>44</v>
       </c>
       <c r="G269">
-        <v>0.4872</v>
+        <v>0.4873</v>
       </c>
       <c r="H269">
-        <v>0.4387</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.2645</v>
+        <v>0.26</v>
       </c>
       <c r="H270">
-        <v>0.2238</v>
+        <v>0.2182</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7618,10 +7618,10 @@
         <v>46</v>
       </c>
       <c r="G271">
-        <v>0.6016</v>
+        <v>0.598</v>
       </c>
       <c r="H271">
-        <v>0.576</v>
+        <v>0.5732</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -7644,10 +7644,10 @@
         <v>48</v>
       </c>
       <c r="G272">
-        <v>0.8442</v>
+        <v>0.8386</v>
       </c>
       <c r="H272">
-        <v>0.7991</v>
+        <v>0.7952</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7670,10 +7670,10 @@
         <v>49</v>
       </c>
       <c r="G273">
-        <v>0.8614000000000001</v>
+        <v>0.8587</v>
       </c>
       <c r="H273">
-        <v>0.8346</v>
+        <v>0.8306</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7696,10 +7696,10 @@
         <v>50</v>
       </c>
       <c r="G274">
-        <v>0.9559</v>
+        <v>0.9524</v>
       </c>
       <c r="H274">
-        <v>0.9454</v>
+        <v>0.9416</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7722,10 +7722,10 @@
         <v>51</v>
       </c>
       <c r="G275">
-        <v>0.8529</v>
+        <v>0.8474</v>
       </c>
       <c r="H275">
-        <v>0.8235</v>
+        <v>0.8197</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -7748,10 +7748,10 @@
         <v>52</v>
       </c>
       <c r="G276">
-        <v>0.9581</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="H276">
-        <v>0.9481000000000001</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -8164,10 +8164,10 @@
         <v>38</v>
       </c>
       <c r="G292">
-        <v>0.0507</v>
+        <v>0.0534</v>
       </c>
       <c r="H292">
-        <v>0.0412</v>
+        <v>0.0439</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8190,10 +8190,10 @@
         <v>39</v>
       </c>
       <c r="G293">
-        <v>0.0285</v>
+        <v>0.0298</v>
       </c>
       <c r="H293">
-        <v>0.0219</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -8216,10 +8216,10 @@
         <v>40</v>
       </c>
       <c r="G294">
-        <v>0.0401</v>
+        <v>0.0437</v>
       </c>
       <c r="H294">
-        <v>0.0307</v>
+        <v>0.0337</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -8242,10 +8242,10 @@
         <v>41</v>
       </c>
       <c r="G295">
-        <v>0.0368</v>
+        <v>0.0379</v>
       </c>
       <c r="H295">
-        <v>0.0286</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.1009</v>
+        <v>0.1033</v>
       </c>
       <c r="H296">
-        <v>0.075</v>
+        <v>0.0767</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8294,10 +8294,10 @@
         <v>43</v>
       </c>
       <c r="G297">
-        <v>0.1123</v>
+        <v>0.1251</v>
       </c>
       <c r="H297">
-        <v>0.08699999999999999</v>
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -8320,10 +8320,10 @@
         <v>44</v>
       </c>
       <c r="G298">
-        <v>0.1858</v>
+        <v>0.1909</v>
       </c>
       <c r="H298">
-        <v>0.159</v>
+        <v>0.1628</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.0761</v>
+        <v>0.0727</v>
       </c>
       <c r="H299">
-        <v>0.06</v>
+        <v>0.0578</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8398,10 +8398,10 @@
         <v>47</v>
       </c>
       <c r="G301">
-        <v>0.2009</v>
+        <v>0.2048</v>
       </c>
       <c r="H301">
-        <v>0.1558</v>
+        <v>0.1614</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8450,10 +8450,10 @@
         <v>50</v>
       </c>
       <c r="G303">
-        <v>0.8304</v>
+        <v>0.8295</v>
       </c>
       <c r="H303">
-        <v>0.7938</v>
+        <v>0.7934</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -8502,10 +8502,10 @@
         <v>52</v>
       </c>
       <c r="G305">
-        <v>0.8683</v>
+        <v>0.8629</v>
       </c>
       <c r="H305">
-        <v>0.8337</v>
+        <v>0.8292</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -8918,10 +8918,10 @@
         <v>38</v>
       </c>
       <c r="G321">
-        <v>0.0409</v>
+        <v>0.0433</v>
       </c>
       <c r="H321">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8944,10 +8944,10 @@
         <v>39</v>
       </c>
       <c r="G322">
-        <v>0.0217</v>
+        <v>0.0224</v>
       </c>
       <c r="H322">
-        <v>0.0156</v>
+        <v>0.0163</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8970,10 +8970,10 @@
         <v>40</v>
       </c>
       <c r="G323">
-        <v>0.0297</v>
+        <v>0.0309</v>
       </c>
       <c r="H323">
-        <v>0.0223</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8996,10 +8996,10 @@
         <v>41</v>
       </c>
       <c r="G324">
-        <v>0.0254</v>
+        <v>0.0298</v>
       </c>
       <c r="H324">
-        <v>0.0205</v>
+        <v>0.0235</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.0732</v>
+        <v>0.0747</v>
       </c>
       <c r="H325">
-        <v>0.0554</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9048,10 +9048,10 @@
         <v>43</v>
       </c>
       <c r="G326">
-        <v>0.0917</v>
+        <v>0.1005</v>
       </c>
       <c r="H326">
-        <v>0.0702</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -9074,10 +9074,10 @@
         <v>44</v>
       </c>
       <c r="G327">
-        <v>0.1503</v>
+        <v>0.1538</v>
       </c>
       <c r="H327">
-        <v>0.1214</v>
+        <v>0.1246</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -9100,10 +9100,10 @@
         <v>45</v>
       </c>
       <c r="G328">
-        <v>0.0577</v>
+        <v>0.0536</v>
       </c>
       <c r="H328">
-        <v>0.0439</v>
+        <v>0.0407</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9126,10 +9126,10 @@
         <v>46</v>
       </c>
       <c r="G329">
-        <v>0.2092</v>
+        <v>0.2196</v>
       </c>
       <c r="H329">
-        <v>0.1773</v>
+        <v>0.1844</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9152,10 +9152,10 @@
         <v>47</v>
       </c>
       <c r="G330">
-        <v>0.1654</v>
+        <v>0.1694</v>
       </c>
       <c r="H330">
-        <v>0.1386</v>
+        <v>0.1413</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.8008999999999999</v>
+        <v>0.793</v>
       </c>
       <c r="H332">
-        <v>0.7655</v>
+        <v>0.7556</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9230,10 +9230,10 @@
         <v>51</v>
       </c>
       <c r="G333">
-        <v>0.4939</v>
+        <v>0.4956</v>
       </c>
       <c r="H333">
-        <v>0.4664</v>
+        <v>0.4688</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -9256,10 +9256,10 @@
         <v>52</v>
       </c>
       <c r="G334">
-        <v>0.8205</v>
+        <v>0.8163</v>
       </c>
       <c r="H334">
-        <v>0.7858000000000001</v>
+        <v>0.7824</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -9802,10 +9802,10 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>0.0266</v>
+        <v>0.0275</v>
       </c>
       <c r="H355">
-        <v>0.0217</v>
+        <v>0.0222</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -9828,10 +9828,10 @@
         <v>44</v>
       </c>
       <c r="G356">
-        <v>0.0494</v>
+        <v>0.0504</v>
       </c>
       <c r="H356">
-        <v>0.0425</v>
+        <v>0.0437</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
-        <v>0.0625</v>
+        <v>0.0658</v>
       </c>
       <c r="H358">
-        <v>0.0507</v>
+        <v>0.0538</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9906,10 +9906,10 @@
         <v>47</v>
       </c>
       <c r="G359">
-        <v>0.0546</v>
+        <v>0.0584</v>
       </c>
       <c r="H359">
-        <v>0.0441</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -9932,10 +9932,10 @@
         <v>48</v>
       </c>
       <c r="G360">
-        <v>0.2062</v>
+        <v>0.2066</v>
       </c>
       <c r="H360">
-        <v>0.1696</v>
+        <v>0.1705</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.2345</v>
+        <v>0.2444</v>
       </c>
       <c r="H361">
-        <v>0.1991</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -9984,10 +9984,10 @@
         <v>51</v>
       </c>
       <c r="G362">
-        <v>0.2278</v>
+        <v>0.2268</v>
       </c>
       <c r="H362">
-        <v>0.195</v>
+        <v>0.1943</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -10010,10 +10010,10 @@
         <v>52</v>
       </c>
       <c r="G363">
-        <v>0.5407999999999999</v>
+        <v>0.5531</v>
       </c>
       <c r="H363">
-        <v>0.4923</v>
+        <v>0.505</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.0512</v>
+        <v>0.054</v>
       </c>
       <c r="H379">
-        <v>0.0422</v>
+        <v>0.0449</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10452,10 +10452,10 @@
         <v>39</v>
       </c>
       <c r="G380">
-        <v>0.026</v>
+        <v>0.0283</v>
       </c>
       <c r="H380">
-        <v>0.0198</v>
+        <v>0.0211</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -10478,10 +10478,10 @@
         <v>40</v>
       </c>
       <c r="G381">
-        <v>0.0389</v>
+        <v>0.0415</v>
       </c>
       <c r="H381">
-        <v>0.0299</v>
+        <v>0.0322</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -10504,10 +10504,10 @@
         <v>41</v>
       </c>
       <c r="G382">
-        <v>0.0316</v>
+        <v>0.0327</v>
       </c>
       <c r="H382">
-        <v>0.0272</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.0687</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H383">
-        <v>0.0547</v>
+        <v>0.0551</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.0822</v>
+        <v>0.0917</v>
       </c>
       <c r="H384">
-        <v>0.06809999999999999</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.143</v>
+        <v>0.1499</v>
       </c>
       <c r="H385">
-        <v>0.1172</v>
+        <v>0.1227</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.0611</v>
+        <v>0.0582</v>
       </c>
       <c r="H386">
-        <v>0.0473</v>
+        <v>0.0455</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10660,10 +10660,10 @@
         <v>47</v>
       </c>
       <c r="G388">
-        <v>0.1765</v>
+        <v>0.1803</v>
       </c>
       <c r="H388">
-        <v>0.1471</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -10712,10 +10712,10 @@
         <v>49</v>
       </c>
       <c r="G390">
-        <v>0.5336</v>
+        <v>0.5312</v>
       </c>
       <c r="H390">
-        <v>0.5061</v>
+        <v>0.5044</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -10738,10 +10738,10 @@
         <v>50</v>
       </c>
       <c r="G391">
-        <v>0.805</v>
+        <v>0.8057</v>
       </c>
       <c r="H391">
-        <v>0.7722</v>
+        <v>0.7732</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -11180,10 +11180,10 @@
         <v>38</v>
       </c>
       <c r="G408">
-        <v>0.0267</v>
+        <v>0.0288</v>
       </c>
       <c r="H408">
-        <v>0.0209</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11232,10 +11232,10 @@
         <v>40</v>
       </c>
       <c r="G410">
-        <v>0.0165</v>
+        <v>0.0192</v>
       </c>
       <c r="H410">
-        <v>0.0129</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -11284,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="G412">
-        <v>0.0287</v>
+        <v>0.0309</v>
       </c>
       <c r="H412">
-        <v>0.0223</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11310,10 +11310,10 @@
         <v>43</v>
       </c>
       <c r="G413">
-        <v>0.0343</v>
+        <v>0.0406</v>
       </c>
       <c r="H413">
-        <v>0.0264</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -11336,10 +11336,10 @@
         <v>44</v>
       </c>
       <c r="G414">
-        <v>0.0472</v>
+        <v>0.0488</v>
       </c>
       <c r="H414">
-        <v>0.0385</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -11388,10 +11388,10 @@
         <v>46</v>
       </c>
       <c r="G416">
-        <v>0.0781</v>
+        <v>0.0793</v>
       </c>
       <c r="H416">
-        <v>0.0639</v>
+        <v>0.06519999999999999</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -11414,10 +11414,10 @@
         <v>47</v>
       </c>
       <c r="G417">
-        <v>0.0519</v>
+        <v>0.054</v>
       </c>
       <c r="H417">
-        <v>0.0419</v>
+        <v>0.0439</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -11440,10 +11440,10 @@
         <v>48</v>
       </c>
       <c r="G418">
-        <v>0.1663</v>
+        <v>0.1708</v>
       </c>
       <c r="H418">
-        <v>0.1317</v>
+        <v>0.1371</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -11466,10 +11466,10 @@
         <v>49</v>
       </c>
       <c r="G419">
-        <v>0.2142</v>
+        <v>0.2176</v>
       </c>
       <c r="H419">
-        <v>0.1795</v>
+        <v>0.1837</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -11492,10 +11492,10 @@
         <v>50</v>
       </c>
       <c r="G420">
-        <v>0.5077</v>
+        <v>0.495</v>
       </c>
       <c r="H420">
-        <v>0.4592</v>
+        <v>0.4469</v>
       </c>
     </row>
     <row r="421" spans="1:8">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -52,19 +52,19 @@
     <t>Cavaliers</t>
   </si>
   <si>
+    <t>Raptors</t>
+  </si>
+  <si>
     <t>Hawks</t>
   </si>
   <si>
-    <t>Raptors</t>
+    <t>Magic</t>
   </si>
   <si>
     <t>76ers</t>
   </si>
   <si>
     <t>Hornets</t>
-  </si>
-  <si>
-    <t>Magic</t>
   </si>
   <si>
     <t>Heat</t>
@@ -115,13 +115,13 @@
     <t>Warriors</t>
   </si>
   <si>
-    <t>Mavericks</t>
-  </si>
-  <si>
     <t>Pelicans</t>
   </si>
   <si>
     <t>Grizzlies</t>
+  </si>
+  <si>
+    <t>Mavericks</t>
   </si>
   <si>
     <t>Kings</t>
@@ -142,19 +142,19 @@
     <t>CLE</t>
   </si>
   <si>
+    <t>TOR</t>
+  </si>
+  <si>
     <t>ATL</t>
   </si>
   <si>
-    <t>TOR</t>
+    <t>ORL</t>
   </si>
   <si>
     <t>PHI</t>
   </si>
   <si>
     <t>CHA</t>
-  </si>
-  <si>
-    <t>ORL</t>
   </si>
   <si>
     <t>MIA</t>
@@ -205,13 +205,13 @@
     <t>GSW</t>
   </si>
   <si>
-    <t>DAL</t>
-  </si>
-  <si>
     <t>NOP</t>
   </si>
   <si>
     <t>MEM</t>
+  </si>
+  <si>
+    <t>DAL</t>
   </si>
   <si>
     <t>SAC</t>
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4563</v>
+        <v>0.4706</v>
       </c>
       <c r="H2">
-        <v>0.4037</v>
+        <v>0.4157</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,10 +650,10 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>0.5543</v>
+        <v>0.5359</v>
       </c>
       <c r="H3">
-        <v>0.5171</v>
+        <v>0.4921</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5087</v>
+        <v>0.5181</v>
       </c>
       <c r="H4">
-        <v>0.4679</v>
+        <v>0.4799</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -693,7 +693,7 @@
         <v>38</v>
       </c>
       <c r="D5">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -702,10 +702,10 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>0.7475000000000001</v>
+        <v>0.7623</v>
       </c>
       <c r="H5">
-        <v>0.7192</v>
+        <v>0.7457</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -719,7 +719,7 @@
         <v>38</v>
       </c>
       <c r="D6">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -728,10 +728,10 @@
         <v>43</v>
       </c>
       <c r="G6">
-        <v>0.7786999999999999</v>
+        <v>0.7467</v>
       </c>
       <c r="H6">
-        <v>0.7594</v>
+        <v>0.7086</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -745,7 +745,7 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -754,10 +754,10 @@
         <v>44</v>
       </c>
       <c r="G7">
-        <v>0.8354</v>
+        <v>0.907</v>
       </c>
       <c r="H7">
-        <v>0.8135</v>
+        <v>0.8798</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -771,7 +771,7 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.6501</v>
+        <v>0.8467</v>
       </c>
       <c r="H8">
-        <v>0.6223</v>
+        <v>0.8175</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -797,7 +797,7 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -806,10 +806,10 @@
         <v>46</v>
       </c>
       <c r="G9">
-        <v>0.9065</v>
+        <v>0.6642</v>
       </c>
       <c r="H9">
-        <v>0.8798</v>
+        <v>0.6382</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -832,10 +832,10 @@
         <v>47</v>
       </c>
       <c r="G10">
-        <v>0.8568</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="H10">
-        <v>0.8243</v>
+        <v>0.8401999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -858,10 +858,10 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>0.9560999999999999</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="H11">
-        <v>0.9466</v>
+        <v>0.9373</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -884,10 +884,10 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>0.965</v>
+        <v>0.9657</v>
       </c>
       <c r="H12">
-        <v>0.9567</v>
+        <v>0.9569</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -910,10 +910,10 @@
         <v>50</v>
       </c>
       <c r="G13">
-        <v>0.9845</v>
+        <v>0.9849</v>
       </c>
       <c r="H13">
-        <v>0.9799</v>
+        <v>0.9802999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.9550999999999999</v>
+        <v>0.966</v>
       </c>
       <c r="H14">
-        <v>0.946</v>
+        <v>0.9605</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -962,10 +962,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>0.9772999999999999</v>
+        <v>0.9791</v>
       </c>
       <c r="H15">
-        <v>0.9712</v>
+        <v>0.9729</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1239,7 +1239,7 @@
         <v>38</v>
       </c>
       <c r="D26">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
@@ -1265,7 +1265,7 @@
         <v>38</v>
       </c>
       <c r="D27">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E27" t="s">
         <v>34</v>
@@ -1291,7 +1291,7 @@
         <v>38</v>
       </c>
       <c r="D28">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E28" t="s">
         <v>35</v>
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.5963000000000001</v>
+        <v>0.5843</v>
       </c>
       <c r="H31">
-        <v>0.5437</v>
+        <v>0.5294</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="G32">
-        <v>0.6693</v>
+        <v>0.6526</v>
       </c>
       <c r="H32">
-        <v>0.6474</v>
+        <v>0.6325</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1430,10 +1430,10 @@
         <v>41</v>
       </c>
       <c r="G33">
-        <v>0.6467000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="H33">
-        <v>0.6196</v>
+        <v>0.5883</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1447,7 +1447,7 @@
         <v>39</v>
       </c>
       <c r="D34">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E34" t="s">
         <v>12</v>
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.8403</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="H34">
-        <v>0.7977</v>
+        <v>0.8337</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1473,7 +1473,7 @@
         <v>39</v>
       </c>
       <c r="D35">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E35" t="s">
         <v>13</v>
@@ -1482,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="G35">
-        <v>0.8976</v>
+        <v>0.83</v>
       </c>
       <c r="H35">
-        <v>0.8699</v>
+        <v>0.787</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1499,7 +1499,7 @@
         <v>39</v>
       </c>
       <c r="D36">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
@@ -1508,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="G36">
-        <v>0.9209000000000001</v>
+        <v>0.9384</v>
       </c>
       <c r="H36">
-        <v>0.9018</v>
+        <v>0.9204</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1525,7 +1525,7 @@
         <v>39</v>
       </c>
       <c r="D37">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.7346</v>
+        <v>0.9163</v>
       </c>
       <c r="H37">
-        <v>0.6929999999999999</v>
+        <v>0.8971</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1551,7 +1551,7 @@
         <v>39</v>
       </c>
       <c r="D38">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E38" t="s">
         <v>16</v>
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.9473</v>
+        <v>0.7496</v>
       </c>
       <c r="H38">
-        <v>0.9292</v>
+        <v>0.7053</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1586,10 +1586,10 @@
         <v>47</v>
       </c>
       <c r="G39">
-        <v>0.9232</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="H39">
-        <v>0.896</v>
+        <v>0.9031</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1612,10 +1612,10 @@
         <v>48</v>
       </c>
       <c r="G40">
-        <v>0.9772999999999999</v>
+        <v>0.9728</v>
       </c>
       <c r="H40">
-        <v>0.9702</v>
+        <v>0.9635</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1638,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="G41">
-        <v>0.9837</v>
+        <v>0.9828</v>
       </c>
       <c r="H41">
-        <v>0.9776</v>
+        <v>0.9767</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1664,10 +1664,10 @@
         <v>50</v>
       </c>
       <c r="G42">
-        <v>0.9883</v>
+        <v>0.9875</v>
       </c>
       <c r="H42">
-        <v>0.9859</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1690,10 +1690,10 @@
         <v>51</v>
       </c>
       <c r="G43">
-        <v>0.9789</v>
+        <v>0.9786</v>
       </c>
       <c r="H43">
-        <v>0.9717</v>
+        <v>0.9713000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1716,10 +1716,10 @@
         <v>52</v>
       </c>
       <c r="G44">
-        <v>0.9881</v>
+        <v>0.9892</v>
       </c>
       <c r="H44">
-        <v>0.9842</v>
+        <v>0.9859</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1993,7 +1993,7 @@
         <v>39</v>
       </c>
       <c r="D55">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E55" t="s">
         <v>33</v>
@@ -2019,7 +2019,7 @@
         <v>39</v>
       </c>
       <c r="D56">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E56" t="s">
         <v>34</v>
@@ -2045,7 +2045,7 @@
         <v>39</v>
       </c>
       <c r="D57">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E57" t="s">
         <v>35</v>
@@ -2132,10 +2132,10 @@
         <v>38</v>
       </c>
       <c r="G60">
-        <v>0.4829</v>
+        <v>0.5079</v>
       </c>
       <c r="H60">
-        <v>0.4457</v>
+        <v>0.4641</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2158,10 +2158,10 @@
         <v>39</v>
       </c>
       <c r="G61">
-        <v>0.3526</v>
+        <v>0.3675</v>
       </c>
       <c r="H61">
-        <v>0.3307</v>
+        <v>0.3474</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2184,10 +2184,10 @@
         <v>41</v>
       </c>
       <c r="G62">
-        <v>0.536</v>
+        <v>0.5139</v>
       </c>
       <c r="H62">
-        <v>0.497</v>
+        <v>0.4731</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2201,7 +2201,7 @@
         <v>40</v>
       </c>
       <c r="D63">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E63" t="s">
         <v>12</v>
@@ -2210,10 +2210,10 @@
         <v>42</v>
       </c>
       <c r="G63">
-        <v>0.7291</v>
+        <v>0.805</v>
       </c>
       <c r="H63">
-        <v>0.6840000000000001</v>
+        <v>0.7696</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2227,7 +2227,7 @@
         <v>40</v>
       </c>
       <c r="D64">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E64" t="s">
         <v>13</v>
@@ -2236,10 +2236,10 @@
         <v>43</v>
       </c>
       <c r="G64">
-        <v>0.8086</v>
+        <v>0.7507</v>
       </c>
       <c r="H64">
-        <v>0.772</v>
+        <v>0.7094</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2253,7 +2253,7 @@
         <v>40</v>
       </c>
       <c r="D65">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E65" t="s">
         <v>14</v>
@@ -2262,10 +2262,10 @@
         <v>44</v>
       </c>
       <c r="G65">
-        <v>0.8774999999999999</v>
+        <v>0.9134</v>
       </c>
       <c r="H65">
-        <v>0.8579</v>
+        <v>0.8893</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2279,7 +2279,7 @@
         <v>40</v>
       </c>
       <c r="D66">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.62</v>
+        <v>0.8835</v>
       </c>
       <c r="H66">
-        <v>0.5744</v>
+        <v>0.8651</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2305,7 +2305,7 @@
         <v>40</v>
       </c>
       <c r="D67">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E67" t="s">
         <v>16</v>
@@ -2314,10 +2314,10 @@
         <v>46</v>
       </c>
       <c r="G67">
-        <v>0.9206</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="H67">
-        <v>0.8943</v>
+        <v>0.6151</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2340,10 +2340,10 @@
         <v>47</v>
       </c>
       <c r="G68">
-        <v>0.8804999999999999</v>
+        <v>0.9041</v>
       </c>
       <c r="H68">
-        <v>0.8427</v>
+        <v>0.8716</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2366,10 +2366,10 @@
         <v>48</v>
       </c>
       <c r="G69">
-        <v>0.9663</v>
+        <v>0.9613</v>
       </c>
       <c r="H69">
-        <v>0.9563</v>
+        <v>0.9514</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="G70">
-        <v>0.9769</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="H70">
-        <v>0.9691</v>
+        <v>0.9653</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2418,10 +2418,10 @@
         <v>50</v>
       </c>
       <c r="G71">
-        <v>0.9863</v>
+        <v>0.9849</v>
       </c>
       <c r="H71">
-        <v>0.9841</v>
+        <v>0.9829</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2444,10 +2444,10 @@
         <v>51</v>
       </c>
       <c r="G72">
-        <v>0.9678</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="H72">
-        <v>0.9585</v>
+        <v>0.9631999999999999</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2470,10 +2470,10 @@
         <v>52</v>
       </c>
       <c r="G73">
-        <v>0.9854000000000001</v>
+        <v>0.9881</v>
       </c>
       <c r="H73">
-        <v>0.9808</v>
+        <v>0.9846</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2747,7 +2747,7 @@
         <v>40</v>
       </c>
       <c r="D84">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E84" t="s">
         <v>33</v>
@@ -2773,7 +2773,7 @@
         <v>40</v>
       </c>
       <c r="D85">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E85" t="s">
         <v>34</v>
@@ -2799,7 +2799,7 @@
         <v>40</v>
       </c>
       <c r="D86">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E86" t="s">
         <v>35</v>
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.5321</v>
+        <v>0.5201</v>
       </c>
       <c r="H89">
-        <v>0.4913</v>
+        <v>0.4819</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2912,10 +2912,10 @@
         <v>39</v>
       </c>
       <c r="G90">
-        <v>0.3804</v>
+        <v>0.4117</v>
       </c>
       <c r="H90">
-        <v>0.3533</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2938,10 +2938,10 @@
         <v>40</v>
       </c>
       <c r="G91">
-        <v>0.503</v>
+        <v>0.5269</v>
       </c>
       <c r="H91">
-        <v>0.464</v>
+        <v>0.4861</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2955,7 +2955,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E92" t="s">
         <v>12</v>
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.7671</v>
+        <v>0.7845</v>
       </c>
       <c r="H92">
-        <v>0.7227</v>
+        <v>0.7493</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2981,7 +2981,7 @@
         <v>41</v>
       </c>
       <c r="D93">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E93" t="s">
         <v>13</v>
@@ -2990,10 +2990,10 @@
         <v>43</v>
       </c>
       <c r="G93">
-        <v>0.8097</v>
+        <v>0.7811</v>
       </c>
       <c r="H93">
-        <v>0.7772</v>
+        <v>0.7391</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3007,7 +3007,7 @@
         <v>41</v>
       </c>
       <c r="D94">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E94" t="s">
         <v>14</v>
@@ -3016,10 +3016,10 @@
         <v>44</v>
       </c>
       <c r="G94">
-        <v>0.872</v>
+        <v>0.9021</v>
       </c>
       <c r="H94">
-        <v>0.8457</v>
+        <v>0.8742</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3033,7 +3033,7 @@
         <v>41</v>
       </c>
       <c r="D95">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.6506999999999999</v>
+        <v>0.8892</v>
       </c>
       <c r="H95">
-        <v>0.5993000000000001</v>
+        <v>0.8665</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3059,7 +3059,7 @@
         <v>41</v>
       </c>
       <c r="D96">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E96" t="s">
         <v>16</v>
@@ -3068,10 +3068,10 @@
         <v>46</v>
       </c>
       <c r="G96">
-        <v>0.907</v>
+        <v>0.6498</v>
       </c>
       <c r="H96">
-        <v>0.8845</v>
+        <v>0.6116</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3094,10 +3094,10 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.8919</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="H97">
-        <v>0.8596</v>
+        <v>0.8595</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3120,10 +3120,10 @@
         <v>48</v>
       </c>
       <c r="G98">
-        <v>0.9701</v>
+        <v>0.9677</v>
       </c>
       <c r="H98">
-        <v>0.9621</v>
+        <v>0.9581</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3146,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="G99">
-        <v>0.9765</v>
+        <v>0.9739</v>
       </c>
       <c r="H99">
-        <v>0.9702</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3172,10 +3172,10 @@
         <v>50</v>
       </c>
       <c r="G100">
-        <v>0.9817</v>
+        <v>0.9832</v>
       </c>
       <c r="H100">
-        <v>0.9776</v>
+        <v>0.9792999999999999</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3198,10 +3198,10 @@
         <v>51</v>
       </c>
       <c r="G101">
-        <v>0.9715</v>
+        <v>0.9704</v>
       </c>
       <c r="H101">
-        <v>0.9673</v>
+        <v>0.9657</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3224,10 +3224,10 @@
         <v>52</v>
       </c>
       <c r="G102">
-        <v>0.9855</v>
+        <v>0.9863</v>
       </c>
       <c r="H102">
-        <v>0.9816</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3501,7 +3501,7 @@
         <v>41</v>
       </c>
       <c r="D113">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E113" t="s">
         <v>33</v>
@@ -3527,7 +3527,7 @@
         <v>41</v>
       </c>
       <c r="D114">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E114" t="s">
         <v>34</v>
@@ -3553,7 +3553,7 @@
         <v>41</v>
       </c>
       <c r="D115">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E115" t="s">
         <v>35</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B118" t="s">
         <v>12</v>
@@ -3640,15 +3640,15 @@
         <v>38</v>
       </c>
       <c r="G118">
-        <v>0.2808</v>
+        <v>0.2543</v>
       </c>
       <c r="H118">
-        <v>0.2525</v>
+        <v>0.2377</v>
       </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B119" t="s">
         <v>12</v>
@@ -3666,15 +3666,15 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.2023</v>
+        <v>0.1663</v>
       </c>
       <c r="H119">
-        <v>0.1597</v>
+        <v>0.1356</v>
       </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B120" t="s">
         <v>12</v>
@@ -3692,15 +3692,15 @@
         <v>40</v>
       </c>
       <c r="G120">
-        <v>0.316</v>
+        <v>0.2304</v>
       </c>
       <c r="H120">
-        <v>0.2709</v>
+        <v>0.195</v>
       </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B121" t="s">
         <v>12</v>
@@ -3718,15 +3718,15 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2773</v>
+        <v>0.2507</v>
       </c>
       <c r="H121">
-        <v>0.2329</v>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B122" t="s">
         <v>12</v>
@@ -3735,7 +3735,7 @@
         <v>42</v>
       </c>
       <c r="D122">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E122" t="s">
         <v>13</v>
@@ -3744,15 +3744,15 @@
         <v>43</v>
       </c>
       <c r="G122">
-        <v>0.6007</v>
+        <v>0.4518</v>
       </c>
       <c r="H122">
-        <v>0.5661</v>
+        <v>0.4201</v>
       </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B123" t="s">
         <v>12</v>
@@ -3761,7 +3761,7 @@
         <v>42</v>
       </c>
       <c r="D123">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E123" t="s">
         <v>14</v>
@@ -3770,15 +3770,15 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.6885</v>
+        <v>0.7047</v>
       </c>
       <c r="H123">
-        <v>0.6629</v>
+        <v>0.6568000000000001</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B124" t="s">
         <v>12</v>
@@ -3787,7 +3787,7 @@
         <v>42</v>
       </c>
       <c r="D124">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E124" t="s">
         <v>15</v>
@@ -3796,15 +3796,15 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.4073</v>
+        <v>0.6297</v>
       </c>
       <c r="H124">
-        <v>0.3729</v>
+        <v>0.5998</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B125" t="s">
         <v>12</v>
@@ -3813,7 +3813,7 @@
         <v>42</v>
       </c>
       <c r="D125">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
@@ -3822,15 +3822,15 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.7974</v>
+        <v>0.4013</v>
       </c>
       <c r="H125">
-        <v>0.7583</v>
+        <v>0.3598</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B126" t="s">
         <v>12</v>
@@ -3848,15 +3848,15 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.7081</v>
+        <v>0.6661</v>
       </c>
       <c r="H126">
-        <v>0.6558</v>
+        <v>0.6219</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B127" t="s">
         <v>12</v>
@@ -3874,15 +3874,15 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.9233</v>
+        <v>0.9025</v>
       </c>
       <c r="H127">
-        <v>0.8967000000000001</v>
+        <v>0.8696</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B128" t="s">
         <v>12</v>
@@ -3900,15 +3900,15 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9434</v>
+        <v>0.9184</v>
       </c>
       <c r="H128">
-        <v>0.9253</v>
+        <v>0.8948</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B129" t="s">
         <v>12</v>
@@ -3926,15 +3926,15 @@
         <v>50</v>
       </c>
       <c r="G129">
-        <v>0.9804</v>
+        <v>0.979</v>
       </c>
       <c r="H129">
-        <v>0.9739</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B130" t="s">
         <v>12</v>
@@ -3952,15 +3952,15 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9449</v>
+        <v>0.9327</v>
       </c>
       <c r="H130">
-        <v>0.9308999999999999</v>
+        <v>0.9179</v>
       </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B131" t="s">
         <v>12</v>
@@ -3978,15 +3978,15 @@
         <v>52</v>
       </c>
       <c r="G131">
-        <v>0.9758</v>
+        <v>0.9731</v>
       </c>
       <c r="H131">
-        <v>0.9691</v>
+        <v>0.9645</v>
       </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B132" t="s">
         <v>12</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B133" t="s">
         <v>12</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B134" t="s">
         <v>12</v>
@@ -4064,7 +4064,7 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B135" t="s">
         <v>12</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B136" t="s">
         <v>12</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B137" t="s">
         <v>12</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B138" t="s">
         <v>12</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B139" t="s">
         <v>12</v>
@@ -4194,7 +4194,7 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B140" t="s">
         <v>12</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B141" t="s">
         <v>12</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B142" t="s">
         <v>12</v>
@@ -4255,7 +4255,7 @@
         <v>42</v>
       </c>
       <c r="D142">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E142" t="s">
         <v>33</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B143" t="s">
         <v>12</v>
@@ -4281,7 +4281,7 @@
         <v>42</v>
       </c>
       <c r="D143">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E143" t="s">
         <v>34</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B144" t="s">
         <v>12</v>
@@ -4307,7 +4307,7 @@
         <v>42</v>
       </c>
       <c r="D144">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E144" t="s">
         <v>35</v>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B145" t="s">
         <v>12</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="B146" t="s">
         <v>12</v>
@@ -4376,7 +4376,7 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B147" t="s">
         <v>13</v>
@@ -4394,15 +4394,15 @@
         <v>38</v>
       </c>
       <c r="G147">
-        <v>0.2406</v>
+        <v>0.2914</v>
       </c>
       <c r="H147">
-        <v>0.2213</v>
+        <v>0.2533</v>
       </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B148" t="s">
         <v>13</v>
@@ -4420,15 +4420,15 @@
         <v>39</v>
       </c>
       <c r="G148">
-        <v>0.1301</v>
+        <v>0.213</v>
       </c>
       <c r="H148">
-        <v>0.1024</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B149" t="s">
         <v>13</v>
@@ -4446,15 +4446,15 @@
         <v>40</v>
       </c>
       <c r="G149">
-        <v>0.228</v>
+        <v>0.2906</v>
       </c>
       <c r="H149">
-        <v>0.1914</v>
+        <v>0.2493</v>
       </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B150" t="s">
         <v>13</v>
@@ -4472,15 +4472,15 @@
         <v>41</v>
       </c>
       <c r="G150">
-        <v>0.2228</v>
+        <v>0.2609</v>
       </c>
       <c r="H150">
-        <v>0.1903</v>
+        <v>0.2189</v>
       </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B151" t="s">
         <v>13</v>
@@ -4489,7 +4489,7 @@
         <v>43</v>
       </c>
       <c r="D151">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E151" t="s">
         <v>12</v>
@@ -4498,15 +4498,15 @@
         <v>42</v>
       </c>
       <c r="G151">
-        <v>0.4339</v>
+        <v>0.5799</v>
       </c>
       <c r="H151">
-        <v>0.3993</v>
+        <v>0.5482</v>
       </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B152" t="s">
         <v>13</v>
@@ -4515,7 +4515,7 @@
         <v>43</v>
       </c>
       <c r="D152">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E152" t="s">
         <v>14</v>
@@ -4524,15 +4524,15 @@
         <v>44</v>
       </c>
       <c r="G152">
-        <v>0.5827</v>
+        <v>0.7261</v>
       </c>
       <c r="H152">
-        <v>0.5623</v>
+        <v>0.6808999999999999</v>
       </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B153" t="s">
         <v>13</v>
@@ -4541,7 +4541,7 @@
         <v>43</v>
       </c>
       <c r="D153">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -4550,15 +4550,15 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.3419</v>
+        <v>0.6996</v>
       </c>
       <c r="H153">
-        <v>0.2996</v>
+        <v>0.6652</v>
       </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B154" t="s">
         <v>13</v>
@@ -4567,7 +4567,7 @@
         <v>43</v>
       </c>
       <c r="D154">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E154" t="s">
         <v>16</v>
@@ -4576,15 +4576,15 @@
         <v>46</v>
       </c>
       <c r="G154">
-        <v>0.7131999999999999</v>
+        <v>0.4515</v>
       </c>
       <c r="H154">
-        <v>0.6733</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B155" t="s">
         <v>13</v>
@@ -4602,15 +4602,15 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>0.6482</v>
+        <v>0.7079</v>
       </c>
       <c r="H155">
-        <v>0.5978</v>
+        <v>0.6646</v>
       </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B156" t="s">
         <v>13</v>
@@ -4628,15 +4628,15 @@
         <v>48</v>
       </c>
       <c r="G156">
-        <v>0.9019</v>
+        <v>0.9146</v>
       </c>
       <c r="H156">
-        <v>0.8749</v>
+        <v>0.8835</v>
       </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B157" t="s">
         <v>13</v>
@@ -4654,15 +4654,15 @@
         <v>49</v>
       </c>
       <c r="G157">
-        <v>0.9219000000000001</v>
+        <v>0.9349</v>
       </c>
       <c r="H157">
-        <v>0.8995</v>
+        <v>0.9152</v>
       </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B158" t="s">
         <v>13</v>
@@ -4680,15 +4680,15 @@
         <v>50</v>
       </c>
       <c r="G158">
-        <v>0.9778</v>
+        <v>0.9799</v>
       </c>
       <c r="H158">
-        <v>0.9725</v>
+        <v>0.9731</v>
       </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B159" t="s">
         <v>13</v>
@@ -4706,15 +4706,15 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9231</v>
+        <v>0.9427</v>
       </c>
       <c r="H159">
-        <v>0.9083</v>
+        <v>0.9291</v>
       </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B160" t="s">
         <v>13</v>
@@ -4732,15 +4732,15 @@
         <v>52</v>
       </c>
       <c r="G160">
-        <v>0.969</v>
+        <v>0.9784</v>
       </c>
       <c r="H160">
-        <v>0.9594</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B161" t="s">
         <v>13</v>
@@ -4766,7 +4766,7 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B162" t="s">
         <v>13</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B163" t="s">
         <v>13</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B164" t="s">
         <v>13</v>
@@ -4844,7 +4844,7 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B165" t="s">
         <v>13</v>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B166" t="s">
         <v>13</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B167" t="s">
         <v>13</v>
@@ -4922,7 +4922,7 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B168" t="s">
         <v>13</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B169" t="s">
         <v>13</v>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B170" t="s">
         <v>13</v>
@@ -5000,7 +5000,7 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B171" t="s">
         <v>13</v>
@@ -5009,7 +5009,7 @@
         <v>43</v>
       </c>
       <c r="D171">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E171" t="s">
         <v>33</v>
@@ -5026,7 +5026,7 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B172" t="s">
         <v>13</v>
@@ -5035,7 +5035,7 @@
         <v>43</v>
       </c>
       <c r="D172">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E172" t="s">
         <v>34</v>
@@ -5052,7 +5052,7 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B173" t="s">
         <v>13</v>
@@ -5061,7 +5061,7 @@
         <v>43</v>
       </c>
       <c r="D173">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E173" t="s">
         <v>35</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B174" t="s">
         <v>13</v>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="B175" t="s">
         <v>13</v>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B176" t="s">
         <v>14</v>
@@ -5148,15 +5148,15 @@
         <v>38</v>
       </c>
       <c r="G176">
-        <v>0.1865</v>
+        <v>0.1202</v>
       </c>
       <c r="H176">
-        <v>0.1646</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B177" t="s">
         <v>14</v>
@@ -5174,15 +5174,15 @@
         <v>39</v>
       </c>
       <c r="G177">
-        <v>0.0982</v>
+        <v>0.0796</v>
       </c>
       <c r="H177">
-        <v>0.0791</v>
+        <v>0.0616</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B178" t="s">
         <v>14</v>
@@ -5200,15 +5200,15 @@
         <v>40</v>
       </c>
       <c r="G178">
-        <v>0.1421</v>
+        <v>0.1107</v>
       </c>
       <c r="H178">
-        <v>0.1225</v>
+        <v>0.0866</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B179" t="s">
         <v>14</v>
@@ -5226,15 +5226,15 @@
         <v>41</v>
       </c>
       <c r="G179">
-        <v>0.1543</v>
+        <v>0.1258</v>
       </c>
       <c r="H179">
-        <v>0.128</v>
+        <v>0.0979</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B180" t="s">
         <v>14</v>
@@ -5243,7 +5243,7 @@
         <v>44</v>
       </c>
       <c r="D180">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E180" t="s">
         <v>12</v>
@@ -5252,15 +5252,15 @@
         <v>42</v>
       </c>
       <c r="G180">
-        <v>0.3371</v>
+        <v>0.3432</v>
       </c>
       <c r="H180">
-        <v>0.3115</v>
+        <v>0.2953</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B181" t="s">
         <v>14</v>
@@ -5269,7 +5269,7 @@
         <v>44</v>
       </c>
       <c r="D181">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E181" t="s">
         <v>13</v>
@@ -5278,15 +5278,15 @@
         <v>43</v>
       </c>
       <c r="G181">
-        <v>0.4377</v>
+        <v>0.3191</v>
       </c>
       <c r="H181">
-        <v>0.4173</v>
+        <v>0.2739</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B182" t="s">
         <v>14</v>
@@ -5295,7 +5295,7 @@
         <v>44</v>
       </c>
       <c r="D182">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E182" t="s">
         <v>15</v>
@@ -5304,15 +5304,15 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.2862</v>
+        <v>0.4539</v>
       </c>
       <c r="H182">
-        <v>0.2401</v>
+        <v>0.421</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B183" t="s">
         <v>14</v>
@@ -5321,7 +5321,7 @@
         <v>44</v>
       </c>
       <c r="D183">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E183" t="s">
         <v>16</v>
@@ -5330,15 +5330,15 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.6147</v>
+        <v>0.2276</v>
       </c>
       <c r="H183">
-        <v>0.5749</v>
+        <v>0.1819</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B184" t="s">
         <v>14</v>
@@ -5356,15 +5356,15 @@
         <v>47</v>
       </c>
       <c r="G184">
-        <v>0.5600000000000001</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="H184">
-        <v>0.5127</v>
+        <v>0.5092</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B185" t="s">
         <v>14</v>
@@ -5382,15 +5382,15 @@
         <v>48</v>
       </c>
       <c r="G185">
-        <v>0.8372000000000001</v>
+        <v>0.792</v>
       </c>
       <c r="H185">
-        <v>0.8091</v>
+        <v>0.7546</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B186" t="s">
         <v>14</v>
@@ -5408,15 +5408,15 @@
         <v>49</v>
       </c>
       <c r="G186">
-        <v>0.8754</v>
+        <v>0.8245</v>
       </c>
       <c r="H186">
-        <v>0.8462</v>
+        <v>0.7945</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B187" t="s">
         <v>14</v>
@@ -5434,15 +5434,15 @@
         <v>50</v>
       </c>
       <c r="G187">
-        <v>0.9563</v>
+        <v>0.9464</v>
       </c>
       <c r="H187">
-        <v>0.9496</v>
+        <v>0.9357</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B188" t="s">
         <v>14</v>
@@ -5460,15 +5460,15 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.8773</v>
+        <v>0.8444</v>
       </c>
       <c r="H188">
-        <v>0.8501</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B189" t="s">
         <v>14</v>
@@ -5486,15 +5486,15 @@
         <v>52</v>
       </c>
       <c r="G189">
-        <v>0.9604</v>
+        <v>0.9482</v>
       </c>
       <c r="H189">
-        <v>0.9512</v>
+        <v>0.9352</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B190" t="s">
         <v>14</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B191" t="s">
         <v>14</v>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B192" t="s">
         <v>14</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B193" t="s">
         <v>14</v>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B194" t="s">
         <v>14</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B195" t="s">
         <v>14</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B196" t="s">
         <v>14</v>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B197" t="s">
         <v>14</v>
@@ -5702,7 +5702,7 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B198" t="s">
         <v>14</v>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B199" t="s">
         <v>14</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B200" t="s">
         <v>14</v>
@@ -5763,7 +5763,7 @@
         <v>44</v>
       </c>
       <c r="D200">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E200" t="s">
         <v>33</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B201" t="s">
         <v>14</v>
@@ -5789,7 +5789,7 @@
         <v>44</v>
       </c>
       <c r="D201">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E201" t="s">
         <v>34</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B202" t="s">
         <v>14</v>
@@ -5815,7 +5815,7 @@
         <v>44</v>
       </c>
       <c r="D202">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E202" t="s">
         <v>35</v>
@@ -5832,7 +5832,7 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B203" t="s">
         <v>14</v>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B204" t="s">
         <v>14</v>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B205" t="s">
         <v>15</v>
@@ -5902,15 +5902,15 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.3777</v>
+        <v>0.1825</v>
       </c>
       <c r="H205">
-        <v>0.3499</v>
+        <v>0.1533</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B206" t="s">
         <v>15</v>
@@ -5928,15 +5928,15 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.307</v>
+        <v>0.1029</v>
       </c>
       <c r="H206">
-        <v>0.2654</v>
+        <v>0.0837</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B207" t="s">
         <v>15</v>
@@ -5954,15 +5954,15 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.4256</v>
+        <v>0.1349</v>
       </c>
       <c r="H207">
-        <v>0.38</v>
+        <v>0.1165</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B208" t="s">
         <v>15</v>
@@ -5980,15 +5980,15 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.4007</v>
+        <v>0.1335</v>
       </c>
       <c r="H208">
-        <v>0.3493</v>
+        <v>0.1108</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B209" t="s">
         <v>15</v>
@@ -5997,7 +5997,7 @@
         <v>45</v>
       </c>
       <c r="D209">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E209" t="s">
         <v>12</v>
@@ -6006,15 +6006,15 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.6271</v>
+        <v>0.4002</v>
       </c>
       <c r="H209">
-        <v>0.5927</v>
+        <v>0.3703</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B210" t="s">
         <v>15</v>
@@ -6023,7 +6023,7 @@
         <v>45</v>
       </c>
       <c r="D210">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E210" t="s">
         <v>13</v>
@@ -6032,15 +6032,15 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.7004</v>
+        <v>0.3348</v>
       </c>
       <c r="H210">
-        <v>0.6581</v>
+        <v>0.3004</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B211" t="s">
         <v>15</v>
@@ -6049,7 +6049,7 @@
         <v>45</v>
       </c>
       <c r="D211">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E211" t="s">
         <v>14</v>
@@ -6058,15 +6058,15 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.7599</v>
+        <v>0.579</v>
       </c>
       <c r="H211">
-        <v>0.7138</v>
+        <v>0.5461</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B212" t="s">
         <v>15</v>
@@ -6075,7 +6075,7 @@
         <v>45</v>
       </c>
       <c r="D212">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E212" t="s">
         <v>16</v>
@@ -6084,15 +6084,15 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.8519</v>
+        <v>0.3045</v>
       </c>
       <c r="H212">
-        <v>0.8183</v>
+        <v>0.2567</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B213" t="s">
         <v>15</v>
@@ -6110,15 +6110,15 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.7818000000000001</v>
+        <v>0.5521</v>
       </c>
       <c r="H213">
-        <v>0.74</v>
+        <v>0.5068</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B214" t="s">
         <v>15</v>
@@ -6136,15 +6136,15 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.9422</v>
+        <v>0.8397</v>
       </c>
       <c r="H214">
-        <v>0.9273</v>
+        <v>0.8068</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B215" t="s">
         <v>15</v>
@@ -6162,15 +6162,15 @@
         <v>49</v>
       </c>
       <c r="G215">
-        <v>0.9593</v>
+        <v>0.8565</v>
       </c>
       <c r="H215">
-        <v>0.9464</v>
+        <v>0.8235</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B216" t="s">
         <v>15</v>
@@ -6188,15 +6188,15 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>0.9867</v>
+        <v>0.9536</v>
       </c>
       <c r="H216">
-        <v>0.9831</v>
+        <v>0.9457</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B217" t="s">
         <v>15</v>
@@ -6214,15 +6214,15 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.9545</v>
+        <v>0.8767</v>
       </c>
       <c r="H217">
-        <v>0.9418</v>
+        <v>0.8401999999999999</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B218" t="s">
         <v>15</v>
@@ -6240,15 +6240,15 @@
         <v>52</v>
       </c>
       <c r="G218">
-        <v>0.98</v>
+        <v>0.9666</v>
       </c>
       <c r="H218">
-        <v>0.9739</v>
+        <v>0.9571</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B219" t="s">
         <v>15</v>
@@ -6274,7 +6274,7 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B220" t="s">
         <v>15</v>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B221" t="s">
         <v>15</v>
@@ -6326,7 +6326,7 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B222" t="s">
         <v>15</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B223" t="s">
         <v>15</v>
@@ -6378,7 +6378,7 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B224" t="s">
         <v>15</v>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B225" t="s">
         <v>15</v>
@@ -6430,7 +6430,7 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B226" t="s">
         <v>15</v>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B227" t="s">
         <v>15</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B228" t="s">
         <v>15</v>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="229" spans="1:8">
       <c r="A229">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B229" t="s">
         <v>15</v>
@@ -6517,7 +6517,7 @@
         <v>45</v>
       </c>
       <c r="D229">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E229" t="s">
         <v>33</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="230" spans="1:8">
       <c r="A230">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B230" t="s">
         <v>15</v>
@@ -6543,7 +6543,7 @@
         <v>45</v>
       </c>
       <c r="D230">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E230" t="s">
         <v>34</v>
@@ -6560,7 +6560,7 @@
     </row>
     <row r="231" spans="1:8">
       <c r="A231">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B231" t="s">
         <v>15</v>
@@ -6569,7 +6569,7 @@
         <v>45</v>
       </c>
       <c r="D231">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E231" t="s">
         <v>35</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B232" t="s">
         <v>15</v>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="B233" t="s">
         <v>15</v>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B234" t="s">
         <v>16</v>
@@ -6656,15 +6656,15 @@
         <v>38</v>
       </c>
       <c r="G234">
-        <v>0.1202</v>
+        <v>0.3618</v>
       </c>
       <c r="H234">
-        <v>0.0935</v>
+        <v>0.3358</v>
       </c>
     </row>
     <row r="235" spans="1:8">
       <c r="A235">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B235" t="s">
         <v>16</v>
@@ -6682,15 +6682,15 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.0708</v>
+        <v>0.2947</v>
       </c>
       <c r="H235">
-        <v>0.0527</v>
+        <v>0.2504</v>
       </c>
     </row>
     <row r="236" spans="1:8">
       <c r="A236">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B236" t="s">
         <v>16</v>
@@ -6708,15 +6708,15 @@
         <v>40</v>
       </c>
       <c r="G236">
-        <v>0.1057</v>
+        <v>0.3849</v>
       </c>
       <c r="H236">
-        <v>0.0794</v>
+        <v>0.3463</v>
       </c>
     </row>
     <row r="237" spans="1:8">
       <c r="A237">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B237" t="s">
         <v>16</v>
@@ -6734,15 +6734,15 @@
         <v>41</v>
       </c>
       <c r="G237">
-        <v>0.1155</v>
+        <v>0.3884</v>
       </c>
       <c r="H237">
-        <v>0.093</v>
+        <v>0.3502</v>
       </c>
     </row>
     <row r="238" spans="1:8">
       <c r="A238">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B238" t="s">
         <v>16</v>
@@ -6751,7 +6751,7 @@
         <v>46</v>
       </c>
       <c r="D238">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E238" t="s">
         <v>12</v>
@@ -6760,15 +6760,15 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.2417</v>
+        <v>0.6402</v>
       </c>
       <c r="H238">
-        <v>0.2026</v>
+        <v>0.5987</v>
       </c>
     </row>
     <row r="239" spans="1:8">
       <c r="A239">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B239" t="s">
         <v>16</v>
@@ -6777,7 +6777,7 @@
         <v>46</v>
       </c>
       <c r="D239">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E239" t="s">
         <v>13</v>
@@ -6786,15 +6786,15 @@
         <v>43</v>
       </c>
       <c r="G239">
-        <v>0.3267</v>
+        <v>0.587</v>
       </c>
       <c r="H239">
-        <v>0.2868</v>
+        <v>0.5485</v>
       </c>
     </row>
     <row r="240" spans="1:8">
       <c r="A240">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B240" t="s">
         <v>16</v>
@@ -6803,7 +6803,7 @@
         <v>46</v>
       </c>
       <c r="D240">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E240" t="s">
         <v>14</v>
@@ -6812,15 +6812,15 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.4251</v>
+        <v>0.8181</v>
       </c>
       <c r="H240">
-        <v>0.3853</v>
+        <v>0.7724</v>
       </c>
     </row>
     <row r="241" spans="1:8">
       <c r="A241">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B241" t="s">
         <v>16</v>
@@ -6829,7 +6829,7 @@
         <v>46</v>
       </c>
       <c r="D241">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E241" t="s">
         <v>15</v>
@@ -6838,15 +6838,15 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.1817</v>
+        <v>0.7433</v>
       </c>
       <c r="H241">
-        <v>0.1481</v>
+        <v>0.6955</v>
       </c>
     </row>
     <row r="242" spans="1:8">
       <c r="A242">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B242" t="s">
         <v>16</v>
@@ -6864,15 +6864,15 @@
         <v>47</v>
       </c>
       <c r="G242">
-        <v>0.4268</v>
+        <v>0.787</v>
       </c>
       <c r="H242">
-        <v>0.402</v>
+        <v>0.7422</v>
       </c>
     </row>
     <row r="243" spans="1:8">
       <c r="A243">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B243" t="s">
         <v>16</v>
@@ -6890,15 +6890,15 @@
         <v>48</v>
       </c>
       <c r="G243">
-        <v>0.7685</v>
+        <v>0.9321</v>
       </c>
       <c r="H243">
-        <v>0.7274</v>
+        <v>0.9123</v>
       </c>
     </row>
     <row r="244" spans="1:8">
       <c r="A244">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B244" t="s">
         <v>16</v>
@@ -6916,15 +6916,15 @@
         <v>49</v>
       </c>
       <c r="G244">
-        <v>0.8156</v>
+        <v>0.9535</v>
       </c>
       <c r="H244">
-        <v>0.7804</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="245" spans="1:8">
       <c r="A245">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B245" t="s">
         <v>16</v>
@@ -6942,15 +6942,15 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9462</v>
+        <v>0.9856</v>
       </c>
       <c r="H245">
-        <v>0.9342</v>
+        <v>0.9821</v>
       </c>
     </row>
     <row r="246" spans="1:8">
       <c r="A246">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B246" t="s">
         <v>16</v>
@@ -6968,15 +6968,15 @@
         <v>51</v>
       </c>
       <c r="G246">
-        <v>0.8173</v>
+        <v>0.9545</v>
       </c>
       <c r="H246">
-        <v>0.7854</v>
+        <v>0.9442</v>
       </c>
     </row>
     <row r="247" spans="1:8">
       <c r="A247">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B247" t="s">
         <v>16</v>
@@ -6994,15 +6994,15 @@
         <v>52</v>
       </c>
       <c r="G247">
-        <v>0.9348</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="H247">
-        <v>0.9207</v>
+        <v>0.9743000000000001</v>
       </c>
     </row>
     <row r="248" spans="1:8">
       <c r="A248">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B248" t="s">
         <v>16</v>
@@ -7028,7 +7028,7 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B249" t="s">
         <v>16</v>
@@ -7054,7 +7054,7 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B250" t="s">
         <v>16</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B251" t="s">
         <v>16</v>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B252" t="s">
         <v>16</v>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B253" t="s">
         <v>16</v>
@@ -7158,7 +7158,7 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B254" t="s">
         <v>16</v>
@@ -7184,7 +7184,7 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B255" t="s">
         <v>16</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B256" t="s">
         <v>16</v>
@@ -7236,7 +7236,7 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B257" t="s">
         <v>16</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B258" t="s">
         <v>16</v>
@@ -7271,7 +7271,7 @@
         <v>46</v>
       </c>
       <c r="D258">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E258" t="s">
         <v>33</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B259" t="s">
         <v>16</v>
@@ -7297,7 +7297,7 @@
         <v>46</v>
       </c>
       <c r="D259">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E259" t="s">
         <v>34</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B260" t="s">
         <v>16</v>
@@ -7323,7 +7323,7 @@
         <v>46</v>
       </c>
       <c r="D260">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E260" t="s">
         <v>35</v>
@@ -7340,7 +7340,7 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B261" t="s">
         <v>16</v>
@@ -7366,7 +7366,7 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="B262" t="s">
         <v>16</v>
@@ -7410,10 +7410,10 @@
         <v>38</v>
       </c>
       <c r="G263">
-        <v>0.1757</v>
+        <v>0.1598</v>
       </c>
       <c r="H263">
-        <v>0.1432</v>
+        <v>0.1255</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -7436,10 +7436,10 @@
         <v>39</v>
       </c>
       <c r="G264">
-        <v>0.104</v>
+        <v>0.0969</v>
       </c>
       <c r="H264">
-        <v>0.07679999999999999</v>
+        <v>0.0711</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7462,10 +7462,10 @@
         <v>40</v>
       </c>
       <c r="G265">
-        <v>0.1573</v>
+        <v>0.1284</v>
       </c>
       <c r="H265">
-        <v>0.1195</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7488,10 +7488,10 @@
         <v>41</v>
       </c>
       <c r="G266">
-        <v>0.1404</v>
+        <v>0.1405</v>
       </c>
       <c r="H266">
-        <v>0.1081</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7505,7 +7505,7 @@
         <v>47</v>
       </c>
       <c r="D267">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E267" t="s">
         <v>12</v>
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3442</v>
+        <v>0.3781</v>
       </c>
       <c r="H267">
-        <v>0.2919</v>
+        <v>0.3339</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7531,7 +7531,7 @@
         <v>47</v>
       </c>
       <c r="D268">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E268" t="s">
         <v>13</v>
@@ -7540,10 +7540,10 @@
         <v>43</v>
       </c>
       <c r="G268">
-        <v>0.4022</v>
+        <v>0.3354</v>
       </c>
       <c r="H268">
-        <v>0.3518</v>
+        <v>0.2921</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -7557,7 +7557,7 @@
         <v>47</v>
       </c>
       <c r="D269">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E269" t="s">
         <v>14</v>
@@ -7566,10 +7566,10 @@
         <v>44</v>
       </c>
       <c r="G269">
-        <v>0.4873</v>
+        <v>0.4908</v>
       </c>
       <c r="H269">
-        <v>0.44</v>
+        <v>0.4652</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7583,7 +7583,7 @@
         <v>47</v>
       </c>
       <c r="D270">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E270" t="s">
         <v>15</v>
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.26</v>
+        <v>0.4932</v>
       </c>
       <c r="H270">
-        <v>0.2182</v>
+        <v>0.4479</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7609,7 +7609,7 @@
         <v>47</v>
       </c>
       <c r="D271">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E271" t="s">
         <v>16</v>
@@ -7618,10 +7618,10 @@
         <v>46</v>
       </c>
       <c r="G271">
-        <v>0.598</v>
+        <v>0.2578</v>
       </c>
       <c r="H271">
-        <v>0.5732</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -7644,10 +7644,10 @@
         <v>48</v>
       </c>
       <c r="G272">
-        <v>0.8386</v>
+        <v>0.8008</v>
       </c>
       <c r="H272">
-        <v>0.7952</v>
+        <v>0.7536</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7670,10 +7670,10 @@
         <v>49</v>
       </c>
       <c r="G273">
-        <v>0.8587</v>
+        <v>0.8259</v>
       </c>
       <c r="H273">
-        <v>0.8306</v>
+        <v>0.7911</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7696,10 +7696,10 @@
         <v>50</v>
       </c>
       <c r="G274">
-        <v>0.9524</v>
+        <v>0.9518</v>
       </c>
       <c r="H274">
-        <v>0.9416</v>
+        <v>0.9383</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7722,10 +7722,10 @@
         <v>51</v>
       </c>
       <c r="G275">
-        <v>0.8474</v>
+        <v>0.8693</v>
       </c>
       <c r="H275">
-        <v>0.8197</v>
+        <v>0.8315</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -7748,10 +7748,10 @@
         <v>52</v>
       </c>
       <c r="G276">
-        <v>0.9560999999999999</v>
+        <v>0.9469</v>
       </c>
       <c r="H276">
-        <v>0.946</v>
+        <v>0.9360000000000001</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -8025,7 +8025,7 @@
         <v>47</v>
       </c>
       <c r="D287">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E287" t="s">
         <v>33</v>
@@ -8051,7 +8051,7 @@
         <v>47</v>
       </c>
       <c r="D288">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E288" t="s">
         <v>34</v>
@@ -8077,7 +8077,7 @@
         <v>47</v>
       </c>
       <c r="D289">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E289" t="s">
         <v>35</v>
@@ -8164,10 +8164,10 @@
         <v>38</v>
       </c>
       <c r="G292">
-        <v>0.0534</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="H292">
-        <v>0.0439</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8190,10 +8190,10 @@
         <v>39</v>
       </c>
       <c r="G293">
-        <v>0.0298</v>
+        <v>0.0365</v>
       </c>
       <c r="H293">
-        <v>0.0227</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -8216,10 +8216,10 @@
         <v>40</v>
       </c>
       <c r="G294">
-        <v>0.0437</v>
+        <v>0.0486</v>
       </c>
       <c r="H294">
-        <v>0.0337</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -8242,10 +8242,10 @@
         <v>41</v>
       </c>
       <c r="G295">
-        <v>0.0379</v>
+        <v>0.0419</v>
       </c>
       <c r="H295">
-        <v>0.0299</v>
+        <v>0.0323</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -8259,7 +8259,7 @@
         <v>48</v>
       </c>
       <c r="D296">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E296" t="s">
         <v>12</v>
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.1033</v>
+        <v>0.1304</v>
       </c>
       <c r="H296">
-        <v>0.0767</v>
+        <v>0.0975</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8285,7 +8285,7 @@
         <v>48</v>
       </c>
       <c r="D297">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E297" t="s">
         <v>13</v>
@@ -8294,10 +8294,10 @@
         <v>43</v>
       </c>
       <c r="G297">
-        <v>0.1251</v>
+        <v>0.1165</v>
       </c>
       <c r="H297">
-        <v>0.09810000000000001</v>
+        <v>0.0854</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -8311,7 +8311,7 @@
         <v>48</v>
       </c>
       <c r="D298">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E298" t="s">
         <v>14</v>
@@ -8320,10 +8320,10 @@
         <v>44</v>
       </c>
       <c r="G298">
-        <v>0.1909</v>
+        <v>0.2454</v>
       </c>
       <c r="H298">
-        <v>0.1628</v>
+        <v>0.208</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8337,7 +8337,7 @@
         <v>48</v>
       </c>
       <c r="D299">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E299" t="s">
         <v>15</v>
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.0727</v>
+        <v>0.1932</v>
       </c>
       <c r="H299">
-        <v>0.0578</v>
+        <v>0.1603</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8363,7 +8363,7 @@
         <v>48</v>
       </c>
       <c r="D300">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E300" t="s">
         <v>16</v>
@@ -8372,10 +8372,10 @@
         <v>46</v>
       </c>
       <c r="G300">
-        <v>0.2726</v>
+        <v>0.0877</v>
       </c>
       <c r="H300">
-        <v>0.2315</v>
+        <v>0.0679</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -8398,10 +8398,10 @@
         <v>47</v>
       </c>
       <c r="G301">
-        <v>0.2048</v>
+        <v>0.2464</v>
       </c>
       <c r="H301">
-        <v>0.1614</v>
+        <v>0.1992</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8424,10 +8424,10 @@
         <v>49</v>
       </c>
       <c r="G302">
-        <v>0.5512</v>
+        <v>0.5688</v>
       </c>
       <c r="H302">
-        <v>0.5252</v>
+        <v>0.5351</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -8450,10 +8450,10 @@
         <v>50</v>
       </c>
       <c r="G303">
-        <v>0.8295</v>
+        <v>0.8351</v>
       </c>
       <c r="H303">
-        <v>0.7934</v>
+        <v>0.7971</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -8476,10 +8476,10 @@
         <v>51</v>
       </c>
       <c r="G304">
-        <v>0.5637</v>
+        <v>0.6052</v>
       </c>
       <c r="H304">
-        <v>0.5274</v>
+        <v>0.5494</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -8502,10 +8502,10 @@
         <v>52</v>
       </c>
       <c r="G305">
-        <v>0.8629</v>
+        <v>0.8701</v>
       </c>
       <c r="H305">
-        <v>0.8292</v>
+        <v>0.8346</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -8779,7 +8779,7 @@
         <v>48</v>
       </c>
       <c r="D316">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E316" t="s">
         <v>33</v>
@@ -8805,7 +8805,7 @@
         <v>48</v>
       </c>
       <c r="D317">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E317" t="s">
         <v>34</v>
@@ -8831,7 +8831,7 @@
         <v>48</v>
       </c>
       <c r="D318">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E318" t="s">
         <v>35</v>
@@ -8918,10 +8918,10 @@
         <v>38</v>
       </c>
       <c r="G321">
-        <v>0.0433</v>
+        <v>0.0431</v>
       </c>
       <c r="H321">
-        <v>0.035</v>
+        <v>0.0343</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8944,10 +8944,10 @@
         <v>39</v>
       </c>
       <c r="G322">
-        <v>0.0224</v>
+        <v>0.0233</v>
       </c>
       <c r="H322">
-        <v>0.0163</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8970,10 +8970,10 @@
         <v>40</v>
       </c>
       <c r="G323">
-        <v>0.0309</v>
+        <v>0.0347</v>
       </c>
       <c r="H323">
-        <v>0.0231</v>
+        <v>0.0267</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8996,10 +8996,10 @@
         <v>41</v>
       </c>
       <c r="G324">
-        <v>0.0298</v>
+        <v>0.031</v>
       </c>
       <c r="H324">
-        <v>0.0235</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -9013,7 +9013,7 @@
         <v>49</v>
       </c>
       <c r="D325">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E325" t="s">
         <v>12</v>
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.0747</v>
+        <v>0.1052</v>
       </c>
       <c r="H325">
-        <v>0.0566</v>
+        <v>0.08160000000000001</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9039,7 +9039,7 @@
         <v>49</v>
       </c>
       <c r="D326">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E326" t="s">
         <v>13</v>
@@ -9048,10 +9048,10 @@
         <v>43</v>
       </c>
       <c r="G326">
-        <v>0.1005</v>
+        <v>0.0848</v>
       </c>
       <c r="H326">
-        <v>0.0781</v>
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -9065,7 +9065,7 @@
         <v>49</v>
       </c>
       <c r="D327">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E327" t="s">
         <v>14</v>
@@ -9074,10 +9074,10 @@
         <v>44</v>
       </c>
       <c r="G327">
-        <v>0.1538</v>
+        <v>0.2055</v>
       </c>
       <c r="H327">
-        <v>0.1246</v>
+        <v>0.1755</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -9091,7 +9091,7 @@
         <v>49</v>
       </c>
       <c r="D328">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E328" t="s">
         <v>15</v>
@@ -9100,10 +9100,10 @@
         <v>45</v>
       </c>
       <c r="G328">
-        <v>0.0536</v>
+        <v>0.1765</v>
       </c>
       <c r="H328">
-        <v>0.0407</v>
+        <v>0.1435</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9117,7 +9117,7 @@
         <v>49</v>
       </c>
       <c r="D329">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E329" t="s">
         <v>16</v>
@@ -9126,10 +9126,10 @@
         <v>46</v>
       </c>
       <c r="G329">
-        <v>0.2196</v>
+        <v>0.062</v>
       </c>
       <c r="H329">
-        <v>0.1844</v>
+        <v>0.0465</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9152,10 +9152,10 @@
         <v>47</v>
       </c>
       <c r="G330">
-        <v>0.1694</v>
+        <v>0.2089</v>
       </c>
       <c r="H330">
-        <v>0.1413</v>
+        <v>0.1741</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9178,10 +9178,10 @@
         <v>48</v>
       </c>
       <c r="G331">
-        <v>0.4748</v>
+        <v>0.4649</v>
       </c>
       <c r="H331">
-        <v>0.4488</v>
+        <v>0.4312</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.793</v>
+        <v>0.8284</v>
       </c>
       <c r="H332">
-        <v>0.7556</v>
+        <v>0.798</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9230,10 +9230,10 @@
         <v>51</v>
       </c>
       <c r="G333">
-        <v>0.4956</v>
+        <v>0.5482</v>
       </c>
       <c r="H333">
-        <v>0.4688</v>
+        <v>0.5189</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -9256,10 +9256,10 @@
         <v>52</v>
       </c>
       <c r="G334">
-        <v>0.8163</v>
+        <v>0.8461</v>
       </c>
       <c r="H334">
-        <v>0.7824</v>
+        <v>0.8135</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -9533,7 +9533,7 @@
         <v>49</v>
       </c>
       <c r="D345">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E345" t="s">
         <v>33</v>
@@ -9559,7 +9559,7 @@
         <v>49</v>
       </c>
       <c r="D346">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E346" t="s">
         <v>34</v>
@@ -9585,7 +9585,7 @@
         <v>49</v>
       </c>
       <c r="D347">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E347" t="s">
         <v>35</v>
@@ -9672,10 +9672,10 @@
         <v>38</v>
       </c>
       <c r="G350">
-        <v>0.0201</v>
+        <v>0.0197</v>
       </c>
       <c r="H350">
-        <v>0.0155</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -9698,10 +9698,10 @@
         <v>39</v>
       </c>
       <c r="G351">
-        <v>0.0141</v>
+        <v>0.015</v>
       </c>
       <c r="H351">
-        <v>0.0117</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -9724,10 +9724,10 @@
         <v>40</v>
       </c>
       <c r="G352">
-        <v>0.0159</v>
+        <v>0.0171</v>
       </c>
       <c r="H352">
-        <v>0.0137</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -9750,10 +9750,10 @@
         <v>41</v>
       </c>
       <c r="G353">
-        <v>0.0224</v>
+        <v>0.0207</v>
       </c>
       <c r="H353">
-        <v>0.0183</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -9767,7 +9767,7 @@
         <v>50</v>
       </c>
       <c r="D354">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E354" t="s">
         <v>12</v>
@@ -9776,10 +9776,10 @@
         <v>42</v>
       </c>
       <c r="G354">
-        <v>0.0261</v>
+        <v>0.026</v>
       </c>
       <c r="H354">
-        <v>0.0196</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -9793,7 +9793,7 @@
         <v>50</v>
       </c>
       <c r="D355">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E355" t="s">
         <v>13</v>
@@ -9802,10 +9802,10 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>0.0275</v>
+        <v>0.0269</v>
       </c>
       <c r="H355">
-        <v>0.0222</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -9819,7 +9819,7 @@
         <v>50</v>
       </c>
       <c r="D356">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E356" t="s">
         <v>14</v>
@@ -9828,10 +9828,10 @@
         <v>44</v>
       </c>
       <c r="G356">
-        <v>0.0504</v>
+        <v>0.0643</v>
       </c>
       <c r="H356">
-        <v>0.0437</v>
+        <v>0.0536</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9845,7 +9845,7 @@
         <v>50</v>
       </c>
       <c r="D357">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E357" t="s">
         <v>15</v>
@@ -9854,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="G357">
-        <v>0.0169</v>
+        <v>0.0543</v>
       </c>
       <c r="H357">
-        <v>0.0133</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9871,7 +9871,7 @@
         <v>50</v>
       </c>
       <c r="D358">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E358" t="s">
         <v>16</v>
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
-        <v>0.0658</v>
+        <v>0.0179</v>
       </c>
       <c r="H358">
-        <v>0.0538</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9906,10 +9906,10 @@
         <v>47</v>
       </c>
       <c r="G359">
-        <v>0.0584</v>
+        <v>0.0617</v>
       </c>
       <c r="H359">
-        <v>0.0476</v>
+        <v>0.0482</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -9932,10 +9932,10 @@
         <v>48</v>
       </c>
       <c r="G360">
-        <v>0.2066</v>
+        <v>0.2029</v>
       </c>
       <c r="H360">
-        <v>0.1705</v>
+        <v>0.1649</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.2444</v>
+        <v>0.202</v>
       </c>
       <c r="H361">
-        <v>0.207</v>
+        <v>0.1716</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -9984,10 +9984,10 @@
         <v>51</v>
       </c>
       <c r="G362">
-        <v>0.2268</v>
+        <v>0.2372</v>
       </c>
       <c r="H362">
-        <v>0.1943</v>
+        <v>0.1991</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -10010,10 +10010,10 @@
         <v>52</v>
       </c>
       <c r="G363">
-        <v>0.5531</v>
+        <v>0.5383</v>
       </c>
       <c r="H363">
-        <v>0.505</v>
+        <v>0.5001</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -10287,7 +10287,7 @@
         <v>50</v>
       </c>
       <c r="D374">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E374" t="s">
         <v>33</v>
@@ -10313,7 +10313,7 @@
         <v>50</v>
       </c>
       <c r="D375">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E375" t="s">
         <v>34</v>
@@ -10339,7 +10339,7 @@
         <v>50</v>
       </c>
       <c r="D376">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E376" t="s">
         <v>35</v>
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.054</v>
+        <v>0.0395</v>
       </c>
       <c r="H379">
-        <v>0.0449</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10452,10 +10452,10 @@
         <v>39</v>
       </c>
       <c r="G380">
-        <v>0.0283</v>
+        <v>0.0287</v>
       </c>
       <c r="H380">
-        <v>0.0211</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -10478,10 +10478,10 @@
         <v>40</v>
       </c>
       <c r="G381">
-        <v>0.0415</v>
+        <v>0.0368</v>
       </c>
       <c r="H381">
-        <v>0.0322</v>
+        <v>0.0287</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -10504,10 +10504,10 @@
         <v>41</v>
       </c>
       <c r="G382">
-        <v>0.0327</v>
+        <v>0.0343</v>
       </c>
       <c r="H382">
-        <v>0.0285</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -10521,7 +10521,7 @@
         <v>51</v>
       </c>
       <c r="D383">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E383" t="s">
         <v>12</v>
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.06909999999999999</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="H383">
-        <v>0.0551</v>
+        <v>0.0673</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10547,7 +10547,7 @@
         <v>51</v>
       </c>
       <c r="D384">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E384" t="s">
         <v>13</v>
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.0917</v>
+        <v>0.0709</v>
       </c>
       <c r="H384">
-        <v>0.0769</v>
+        <v>0.0573</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10573,7 +10573,7 @@
         <v>51</v>
       </c>
       <c r="D385">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E385" t="s">
         <v>14</v>
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.1499</v>
+        <v>0.1918</v>
       </c>
       <c r="H385">
-        <v>0.1227</v>
+        <v>0.1556</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10599,7 +10599,7 @@
         <v>51</v>
       </c>
       <c r="D386">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E386" t="s">
         <v>15</v>
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.0582</v>
+        <v>0.1598</v>
       </c>
       <c r="H386">
-        <v>0.0455</v>
+        <v>0.1233</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10625,7 +10625,7 @@
         <v>51</v>
       </c>
       <c r="D387">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E387" t="s">
         <v>16</v>
@@ -10634,10 +10634,10 @@
         <v>46</v>
       </c>
       <c r="G387">
-        <v>0.2146</v>
+        <v>0.0558</v>
       </c>
       <c r="H387">
-        <v>0.1827</v>
+        <v>0.0455</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -10660,10 +10660,10 @@
         <v>47</v>
       </c>
       <c r="G388">
-        <v>0.1803</v>
+        <v>0.1685</v>
       </c>
       <c r="H388">
-        <v>0.1526</v>
+        <v>0.1307</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -10686,10 +10686,10 @@
         <v>48</v>
       </c>
       <c r="G389">
-        <v>0.4726</v>
+        <v>0.4506</v>
       </c>
       <c r="H389">
-        <v>0.4363</v>
+        <v>0.3948</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -10712,10 +10712,10 @@
         <v>49</v>
       </c>
       <c r="G390">
-        <v>0.5312</v>
+        <v>0.4811</v>
       </c>
       <c r="H390">
-        <v>0.5044</v>
+        <v>0.4518</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -10738,10 +10738,10 @@
         <v>50</v>
       </c>
       <c r="G391">
-        <v>0.8057</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="H391">
-        <v>0.7732</v>
+        <v>0.7628</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -10764,10 +10764,10 @@
         <v>52</v>
       </c>
       <c r="G392">
-        <v>0.8061</v>
+        <v>0.8313</v>
       </c>
       <c r="H392">
-        <v>0.7796999999999999</v>
+        <v>0.7979000000000001</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -11041,7 +11041,7 @@
         <v>51</v>
       </c>
       <c r="D403">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E403" t="s">
         <v>33</v>
@@ -11067,7 +11067,7 @@
         <v>51</v>
       </c>
       <c r="D404">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E404" t="s">
         <v>34</v>
@@ -11093,7 +11093,7 @@
         <v>51</v>
       </c>
       <c r="D405">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E405" t="s">
         <v>35</v>
@@ -11180,10 +11180,10 @@
         <v>38</v>
       </c>
       <c r="G408">
-        <v>0.0288</v>
+        <v>0.0271</v>
       </c>
       <c r="H408">
-        <v>0.0227</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11206,10 +11206,10 @@
         <v>39</v>
       </c>
       <c r="G409">
-        <v>0.0158</v>
+        <v>0.0141</v>
       </c>
       <c r="H409">
-        <v>0.0119</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -11232,10 +11232,10 @@
         <v>40</v>
       </c>
       <c r="G410">
-        <v>0.0192</v>
+        <v>0.0154</v>
       </c>
       <c r="H410">
-        <v>0.0146</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -11258,10 +11258,10 @@
         <v>41</v>
       </c>
       <c r="G411">
-        <v>0.0184</v>
+        <v>0.0175</v>
       </c>
       <c r="H411">
-        <v>0.0145</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -11275,7 +11275,7 @@
         <v>52</v>
       </c>
       <c r="D412">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E412" t="s">
         <v>12</v>
@@ -11284,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="G412">
-        <v>0.0309</v>
+        <v>0.0355</v>
       </c>
       <c r="H412">
-        <v>0.0242</v>
+        <v>0.0269</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11301,7 +11301,7 @@
         <v>52</v>
       </c>
       <c r="D413">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E413" t="s">
         <v>13</v>
@@ -11310,10 +11310,10 @@
         <v>43</v>
       </c>
       <c r="G413">
-        <v>0.0406</v>
+        <v>0.0275</v>
       </c>
       <c r="H413">
-        <v>0.031</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -11327,7 +11327,7 @@
         <v>52</v>
       </c>
       <c r="D414">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E414" t="s">
         <v>14</v>
@@ -11336,10 +11336,10 @@
         <v>44</v>
       </c>
       <c r="G414">
-        <v>0.0488</v>
+        <v>0.0648</v>
       </c>
       <c r="H414">
-        <v>0.0396</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -11353,7 +11353,7 @@
         <v>52</v>
       </c>
       <c r="D415">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E415" t="s">
         <v>15</v>
@@ -11362,10 +11362,10 @@
         <v>45</v>
       </c>
       <c r="G415">
-        <v>0.0261</v>
+        <v>0.0429</v>
       </c>
       <c r="H415">
-        <v>0.02</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -11379,7 +11379,7 @@
         <v>52</v>
       </c>
       <c r="D416">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E416" t="s">
         <v>16</v>
@@ -11388,10 +11388,10 @@
         <v>46</v>
       </c>
       <c r="G416">
-        <v>0.0793</v>
+        <v>0.0257</v>
       </c>
       <c r="H416">
-        <v>0.06519999999999999</v>
+        <v>0.0197</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -11414,10 +11414,10 @@
         <v>47</v>
       </c>
       <c r="G417">
-        <v>0.054</v>
+        <v>0.064</v>
       </c>
       <c r="H417">
-        <v>0.0439</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -11440,10 +11440,10 @@
         <v>48</v>
       </c>
       <c r="G418">
-        <v>0.1708</v>
+        <v>0.1654</v>
       </c>
       <c r="H418">
-        <v>0.1371</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -11466,10 +11466,10 @@
         <v>49</v>
       </c>
       <c r="G419">
-        <v>0.2176</v>
+        <v>0.1865</v>
       </c>
       <c r="H419">
-        <v>0.1837</v>
+        <v>0.1539</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -11492,10 +11492,10 @@
         <v>50</v>
       </c>
       <c r="G420">
-        <v>0.495</v>
+        <v>0.4999</v>
       </c>
       <c r="H420">
-        <v>0.4469</v>
+        <v>0.4617</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -11518,10 +11518,10 @@
         <v>51</v>
       </c>
       <c r="G421">
-        <v>0.2203</v>
+        <v>0.2021</v>
       </c>
       <c r="H421">
-        <v>0.1939</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -11795,7 +11795,7 @@
         <v>52</v>
       </c>
       <c r="D432">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E432" t="s">
         <v>33</v>
@@ -11821,7 +11821,7 @@
         <v>52</v>
       </c>
       <c r="D433">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E433" t="s">
         <v>34</v>
@@ -11847,7 +11847,7 @@
         <v>52</v>
       </c>
       <c r="D434">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E434" t="s">
         <v>35</v>
@@ -12029,7 +12029,7 @@
         <v>53</v>
       </c>
       <c r="D441">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E441" t="s">
         <v>12</v>
@@ -12055,7 +12055,7 @@
         <v>53</v>
       </c>
       <c r="D442">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E442" t="s">
         <v>13</v>
@@ -12081,7 +12081,7 @@
         <v>53</v>
       </c>
       <c r="D443">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E443" t="s">
         <v>14</v>
@@ -12107,7 +12107,7 @@
         <v>53</v>
       </c>
       <c r="D444">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E444" t="s">
         <v>15</v>
@@ -12133,7 +12133,7 @@
         <v>53</v>
       </c>
       <c r="D445">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E445" t="s">
         <v>16</v>
@@ -12549,7 +12549,7 @@
         <v>53</v>
       </c>
       <c r="D461">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E461" t="s">
         <v>33</v>
@@ -12575,7 +12575,7 @@
         <v>53</v>
       </c>
       <c r="D462">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E462" t="s">
         <v>34</v>
@@ -12601,7 +12601,7 @@
         <v>53</v>
       </c>
       <c r="D463">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E463" t="s">
         <v>35</v>
@@ -12783,7 +12783,7 @@
         <v>54</v>
       </c>
       <c r="D470">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E470" t="s">
         <v>12</v>
@@ -12809,7 +12809,7 @@
         <v>54</v>
       </c>
       <c r="D471">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E471" t="s">
         <v>13</v>
@@ -12835,7 +12835,7 @@
         <v>54</v>
       </c>
       <c r="D472">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E472" t="s">
         <v>14</v>
@@ -12861,7 +12861,7 @@
         <v>54</v>
       </c>
       <c r="D473">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E473" t="s">
         <v>15</v>
@@ -12887,7 +12887,7 @@
         <v>54</v>
       </c>
       <c r="D474">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E474" t="s">
         <v>16</v>
@@ -13303,7 +13303,7 @@
         <v>54</v>
       </c>
       <c r="D490">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E490" t="s">
         <v>33</v>
@@ -13329,7 +13329,7 @@
         <v>54</v>
       </c>
       <c r="D491">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E491" t="s">
         <v>34</v>
@@ -13355,7 +13355,7 @@
         <v>54</v>
       </c>
       <c r="D492">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E492" t="s">
         <v>35</v>
@@ -13537,7 +13537,7 @@
         <v>55</v>
       </c>
       <c r="D499">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E499" t="s">
         <v>12</v>
@@ -13563,7 +13563,7 @@
         <v>55</v>
       </c>
       <c r="D500">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E500" t="s">
         <v>13</v>
@@ -13589,7 +13589,7 @@
         <v>55</v>
       </c>
       <c r="D501">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E501" t="s">
         <v>14</v>
@@ -13615,7 +13615,7 @@
         <v>55</v>
       </c>
       <c r="D502">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E502" t="s">
         <v>15</v>
@@ -13641,7 +13641,7 @@
         <v>55</v>
       </c>
       <c r="D503">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E503" t="s">
         <v>16</v>
@@ -14057,7 +14057,7 @@
         <v>55</v>
       </c>
       <c r="D519">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E519" t="s">
         <v>33</v>
@@ -14083,7 +14083,7 @@
         <v>55</v>
       </c>
       <c r="D520">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E520" t="s">
         <v>34</v>
@@ -14109,7 +14109,7 @@
         <v>55</v>
       </c>
       <c r="D521">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E521" t="s">
         <v>35</v>
@@ -14291,7 +14291,7 @@
         <v>56</v>
       </c>
       <c r="D528">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E528" t="s">
         <v>12</v>
@@ -14317,7 +14317,7 @@
         <v>56</v>
       </c>
       <c r="D529">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E529" t="s">
         <v>13</v>
@@ -14343,7 +14343,7 @@
         <v>56</v>
       </c>
       <c r="D530">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E530" t="s">
         <v>14</v>
@@ -14369,7 +14369,7 @@
         <v>56</v>
       </c>
       <c r="D531">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E531" t="s">
         <v>15</v>
@@ -14395,7 +14395,7 @@
         <v>56</v>
       </c>
       <c r="D532">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E532" t="s">
         <v>16</v>
@@ -14811,7 +14811,7 @@
         <v>56</v>
       </c>
       <c r="D548">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E548" t="s">
         <v>33</v>
@@ -14837,7 +14837,7 @@
         <v>56</v>
       </c>
       <c r="D549">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E549" t="s">
         <v>34</v>
@@ -14863,7 +14863,7 @@
         <v>56</v>
       </c>
       <c r="D550">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E550" t="s">
         <v>35</v>
@@ -15045,7 +15045,7 @@
         <v>57</v>
       </c>
       <c r="D557">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E557" t="s">
         <v>12</v>
@@ -15071,7 +15071,7 @@
         <v>57</v>
       </c>
       <c r="D558">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E558" t="s">
         <v>13</v>
@@ -15097,7 +15097,7 @@
         <v>57</v>
       </c>
       <c r="D559">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E559" t="s">
         <v>14</v>
@@ -15123,7 +15123,7 @@
         <v>57</v>
       </c>
       <c r="D560">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E560" t="s">
         <v>15</v>
@@ -15149,7 +15149,7 @@
         <v>57</v>
       </c>
       <c r="D561">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E561" t="s">
         <v>16</v>
@@ -15565,7 +15565,7 @@
         <v>57</v>
       </c>
       <c r="D577">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E577" t="s">
         <v>33</v>
@@ -15591,7 +15591,7 @@
         <v>57</v>
       </c>
       <c r="D578">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E578" t="s">
         <v>34</v>
@@ -15617,7 +15617,7 @@
         <v>57</v>
       </c>
       <c r="D579">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E579" t="s">
         <v>35</v>
@@ -15799,7 +15799,7 @@
         <v>58</v>
       </c>
       <c r="D586">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E586" t="s">
         <v>12</v>
@@ -15825,7 +15825,7 @@
         <v>58</v>
       </c>
       <c r="D587">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E587" t="s">
         <v>13</v>
@@ -15851,7 +15851,7 @@
         <v>58</v>
       </c>
       <c r="D588">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E588" t="s">
         <v>14</v>
@@ -15877,7 +15877,7 @@
         <v>58</v>
       </c>
       <c r="D589">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E589" t="s">
         <v>15</v>
@@ -15903,7 +15903,7 @@
         <v>58</v>
       </c>
       <c r="D590">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E590" t="s">
         <v>16</v>
@@ -16319,7 +16319,7 @@
         <v>58</v>
       </c>
       <c r="D606">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E606" t="s">
         <v>33</v>
@@ -16345,7 +16345,7 @@
         <v>58</v>
       </c>
       <c r="D607">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E607" t="s">
         <v>34</v>
@@ -16371,7 +16371,7 @@
         <v>58</v>
       </c>
       <c r="D608">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E608" t="s">
         <v>35</v>
@@ -16553,7 +16553,7 @@
         <v>59</v>
       </c>
       <c r="D615">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E615" t="s">
         <v>12</v>
@@ -16579,7 +16579,7 @@
         <v>59</v>
       </c>
       <c r="D616">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E616" t="s">
         <v>13</v>
@@ -16605,7 +16605,7 @@
         <v>59</v>
       </c>
       <c r="D617">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E617" t="s">
         <v>14</v>
@@ -16631,7 +16631,7 @@
         <v>59</v>
       </c>
       <c r="D618">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E618" t="s">
         <v>15</v>
@@ -16657,7 +16657,7 @@
         <v>59</v>
       </c>
       <c r="D619">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E619" t="s">
         <v>16</v>
@@ -17073,7 +17073,7 @@
         <v>59</v>
       </c>
       <c r="D635">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E635" t="s">
         <v>33</v>
@@ -17099,7 +17099,7 @@
         <v>59</v>
       </c>
       <c r="D636">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E636" t="s">
         <v>34</v>
@@ -17125,7 +17125,7 @@
         <v>59</v>
       </c>
       <c r="D637">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E637" t="s">
         <v>35</v>
@@ -17307,7 +17307,7 @@
         <v>60</v>
       </c>
       <c r="D644">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E644" t="s">
         <v>12</v>
@@ -17333,7 +17333,7 @@
         <v>60</v>
       </c>
       <c r="D645">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E645" t="s">
         <v>13</v>
@@ -17359,7 +17359,7 @@
         <v>60</v>
       </c>
       <c r="D646">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E646" t="s">
         <v>14</v>
@@ -17385,7 +17385,7 @@
         <v>60</v>
       </c>
       <c r="D647">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E647" t="s">
         <v>15</v>
@@ -17411,7 +17411,7 @@
         <v>60</v>
       </c>
       <c r="D648">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E648" t="s">
         <v>16</v>
@@ -17827,7 +17827,7 @@
         <v>60</v>
       </c>
       <c r="D664">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E664" t="s">
         <v>33</v>
@@ -17853,7 +17853,7 @@
         <v>60</v>
       </c>
       <c r="D665">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E665" t="s">
         <v>34</v>
@@ -17879,7 +17879,7 @@
         <v>60</v>
       </c>
       <c r="D666">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E666" t="s">
         <v>35</v>
@@ -18061,7 +18061,7 @@
         <v>61</v>
       </c>
       <c r="D673">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E673" t="s">
         <v>12</v>
@@ -18087,7 +18087,7 @@
         <v>61</v>
       </c>
       <c r="D674">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E674" t="s">
         <v>13</v>
@@ -18113,7 +18113,7 @@
         <v>61</v>
       </c>
       <c r="D675">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E675" t="s">
         <v>14</v>
@@ -18139,7 +18139,7 @@
         <v>61</v>
       </c>
       <c r="D676">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E676" t="s">
         <v>15</v>
@@ -18165,7 +18165,7 @@
         <v>61</v>
       </c>
       <c r="D677">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E677" t="s">
         <v>16</v>
@@ -18581,7 +18581,7 @@
         <v>61</v>
       </c>
       <c r="D693">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E693" t="s">
         <v>33</v>
@@ -18607,7 +18607,7 @@
         <v>61</v>
       </c>
       <c r="D694">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E694" t="s">
         <v>34</v>
@@ -18633,7 +18633,7 @@
         <v>61</v>
       </c>
       <c r="D695">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E695" t="s">
         <v>35</v>
@@ -18815,7 +18815,7 @@
         <v>62</v>
       </c>
       <c r="D702">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E702" t="s">
         <v>12</v>
@@ -18841,7 +18841,7 @@
         <v>62</v>
       </c>
       <c r="D703">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E703" t="s">
         <v>13</v>
@@ -18867,7 +18867,7 @@
         <v>62</v>
       </c>
       <c r="D704">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E704" t="s">
         <v>14</v>
@@ -18893,7 +18893,7 @@
         <v>62</v>
       </c>
       <c r="D705">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E705" t="s">
         <v>15</v>
@@ -18919,7 +18919,7 @@
         <v>62</v>
       </c>
       <c r="D706">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E706" t="s">
         <v>16</v>
@@ -19335,7 +19335,7 @@
         <v>62</v>
       </c>
       <c r="D722">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E722" t="s">
         <v>33</v>
@@ -19361,7 +19361,7 @@
         <v>62</v>
       </c>
       <c r="D723">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E723" t="s">
         <v>34</v>
@@ -19387,7 +19387,7 @@
         <v>62</v>
       </c>
       <c r="D724">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E724" t="s">
         <v>35</v>
@@ -19456,7 +19456,7 @@
     </row>
     <row r="727" spans="1:8">
       <c r="A727">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B727" t="s">
         <v>33</v>
@@ -19482,7 +19482,7 @@
     </row>
     <row r="728" spans="1:8">
       <c r="A728">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B728" t="s">
         <v>33</v>
@@ -19508,7 +19508,7 @@
     </row>
     <row r="729" spans="1:8">
       <c r="A729">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B729" t="s">
         <v>33</v>
@@ -19534,7 +19534,7 @@
     </row>
     <row r="730" spans="1:8">
       <c r="A730">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B730" t="s">
         <v>33</v>
@@ -19560,7 +19560,7 @@
     </row>
     <row r="731" spans="1:8">
       <c r="A731">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B731" t="s">
         <v>33</v>
@@ -19569,7 +19569,7 @@
         <v>63</v>
       </c>
       <c r="D731">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E731" t="s">
         <v>12</v>
@@ -19586,7 +19586,7 @@
     </row>
     <row r="732" spans="1:8">
       <c r="A732">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B732" t="s">
         <v>33</v>
@@ -19595,7 +19595,7 @@
         <v>63</v>
       </c>
       <c r="D732">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E732" t="s">
         <v>13</v>
@@ -19612,7 +19612,7 @@
     </row>
     <row r="733" spans="1:8">
       <c r="A733">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B733" t="s">
         <v>33</v>
@@ -19621,7 +19621,7 @@
         <v>63</v>
       </c>
       <c r="D733">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E733" t="s">
         <v>14</v>
@@ -19638,7 +19638,7 @@
     </row>
     <row r="734" spans="1:8">
       <c r="A734">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B734" t="s">
         <v>33</v>
@@ -19647,7 +19647,7 @@
         <v>63</v>
       </c>
       <c r="D734">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E734" t="s">
         <v>15</v>
@@ -19664,7 +19664,7 @@
     </row>
     <row r="735" spans="1:8">
       <c r="A735">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B735" t="s">
         <v>33</v>
@@ -19673,7 +19673,7 @@
         <v>63</v>
       </c>
       <c r="D735">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E735" t="s">
         <v>16</v>
@@ -19690,7 +19690,7 @@
     </row>
     <row r="736" spans="1:8">
       <c r="A736">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B736" t="s">
         <v>33</v>
@@ -19716,7 +19716,7 @@
     </row>
     <row r="737" spans="1:8">
       <c r="A737">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B737" t="s">
         <v>33</v>
@@ -19742,7 +19742,7 @@
     </row>
     <row r="738" spans="1:8">
       <c r="A738">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B738" t="s">
         <v>33</v>
@@ -19768,7 +19768,7 @@
     </row>
     <row r="739" spans="1:8">
       <c r="A739">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B739" t="s">
         <v>33</v>
@@ -19794,7 +19794,7 @@
     </row>
     <row r="740" spans="1:8">
       <c r="A740">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B740" t="s">
         <v>33</v>
@@ -19820,7 +19820,7 @@
     </row>
     <row r="741" spans="1:8">
       <c r="A741">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B741" t="s">
         <v>33</v>
@@ -19846,7 +19846,7 @@
     </row>
     <row r="742" spans="1:8">
       <c r="A742">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B742" t="s">
         <v>33</v>
@@ -19872,7 +19872,7 @@
     </row>
     <row r="743" spans="1:8">
       <c r="A743">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B743" t="s">
         <v>33</v>
@@ -19898,7 +19898,7 @@
     </row>
     <row r="744" spans="1:8">
       <c r="A744">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B744" t="s">
         <v>33</v>
@@ -19924,7 +19924,7 @@
     </row>
     <row r="745" spans="1:8">
       <c r="A745">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B745" t="s">
         <v>33</v>
@@ -19950,7 +19950,7 @@
     </row>
     <row r="746" spans="1:8">
       <c r="A746">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B746" t="s">
         <v>33</v>
@@ -19976,7 +19976,7 @@
     </row>
     <row r="747" spans="1:8">
       <c r="A747">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B747" t="s">
         <v>33</v>
@@ -20002,7 +20002,7 @@
     </row>
     <row r="748" spans="1:8">
       <c r="A748">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B748" t="s">
         <v>33</v>
@@ -20028,7 +20028,7 @@
     </row>
     <row r="749" spans="1:8">
       <c r="A749">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B749" t="s">
         <v>33</v>
@@ -20054,7 +20054,7 @@
     </row>
     <row r="750" spans="1:8">
       <c r="A750">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B750" t="s">
         <v>33</v>
@@ -20080,7 +20080,7 @@
     </row>
     <row r="751" spans="1:8">
       <c r="A751">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B751" t="s">
         <v>33</v>
@@ -20106,7 +20106,7 @@
     </row>
     <row r="752" spans="1:8">
       <c r="A752">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B752" t="s">
         <v>33</v>
@@ -20115,7 +20115,7 @@
         <v>63</v>
       </c>
       <c r="D752">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E752" t="s">
         <v>34</v>
@@ -20132,7 +20132,7 @@
     </row>
     <row r="753" spans="1:8">
       <c r="A753">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B753" t="s">
         <v>33</v>
@@ -20141,7 +20141,7 @@
         <v>63</v>
       </c>
       <c r="D753">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E753" t="s">
         <v>35</v>
@@ -20158,7 +20158,7 @@
     </row>
     <row r="754" spans="1:8">
       <c r="A754">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B754" t="s">
         <v>33</v>
@@ -20184,7 +20184,7 @@
     </row>
     <row r="755" spans="1:8">
       <c r="A755">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="B755" t="s">
         <v>33</v>
@@ -20210,7 +20210,7 @@
     </row>
     <row r="756" spans="1:8">
       <c r="A756">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B756" t="s">
         <v>34</v>
@@ -20236,7 +20236,7 @@
     </row>
     <row r="757" spans="1:8">
       <c r="A757">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B757" t="s">
         <v>34</v>
@@ -20262,7 +20262,7 @@
     </row>
     <row r="758" spans="1:8">
       <c r="A758">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B758" t="s">
         <v>34</v>
@@ -20288,7 +20288,7 @@
     </row>
     <row r="759" spans="1:8">
       <c r="A759">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B759" t="s">
         <v>34</v>
@@ -20314,7 +20314,7 @@
     </row>
     <row r="760" spans="1:8">
       <c r="A760">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B760" t="s">
         <v>34</v>
@@ -20323,7 +20323,7 @@
         <v>64</v>
       </c>
       <c r="D760">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E760" t="s">
         <v>12</v>
@@ -20340,7 +20340,7 @@
     </row>
     <row r="761" spans="1:8">
       <c r="A761">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B761" t="s">
         <v>34</v>
@@ -20349,7 +20349,7 @@
         <v>64</v>
       </c>
       <c r="D761">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E761" t="s">
         <v>13</v>
@@ -20366,7 +20366,7 @@
     </row>
     <row r="762" spans="1:8">
       <c r="A762">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B762" t="s">
         <v>34</v>
@@ -20375,7 +20375,7 @@
         <v>64</v>
       </c>
       <c r="D762">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E762" t="s">
         <v>14</v>
@@ -20392,7 +20392,7 @@
     </row>
     <row r="763" spans="1:8">
       <c r="A763">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B763" t="s">
         <v>34</v>
@@ -20401,7 +20401,7 @@
         <v>64</v>
       </c>
       <c r="D763">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E763" t="s">
         <v>15</v>
@@ -20418,7 +20418,7 @@
     </row>
     <row r="764" spans="1:8">
       <c r="A764">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B764" t="s">
         <v>34</v>
@@ -20427,7 +20427,7 @@
         <v>64</v>
       </c>
       <c r="D764">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E764" t="s">
         <v>16</v>
@@ -20444,7 +20444,7 @@
     </row>
     <row r="765" spans="1:8">
       <c r="A765">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B765" t="s">
         <v>34</v>
@@ -20470,7 +20470,7 @@
     </row>
     <row r="766" spans="1:8">
       <c r="A766">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B766" t="s">
         <v>34</v>
@@ -20496,7 +20496,7 @@
     </row>
     <row r="767" spans="1:8">
       <c r="A767">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B767" t="s">
         <v>34</v>
@@ -20522,7 +20522,7 @@
     </row>
     <row r="768" spans="1:8">
       <c r="A768">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B768" t="s">
         <v>34</v>
@@ -20548,7 +20548,7 @@
     </row>
     <row r="769" spans="1:8">
       <c r="A769">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B769" t="s">
         <v>34</v>
@@ -20574,7 +20574,7 @@
     </row>
     <row r="770" spans="1:8">
       <c r="A770">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B770" t="s">
         <v>34</v>
@@ -20600,7 +20600,7 @@
     </row>
     <row r="771" spans="1:8">
       <c r="A771">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B771" t="s">
         <v>34</v>
@@ -20626,7 +20626,7 @@
     </row>
     <row r="772" spans="1:8">
       <c r="A772">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B772" t="s">
         <v>34</v>
@@ -20652,7 +20652,7 @@
     </row>
     <row r="773" spans="1:8">
       <c r="A773">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B773" t="s">
         <v>34</v>
@@ -20678,7 +20678,7 @@
     </row>
     <row r="774" spans="1:8">
       <c r="A774">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B774" t="s">
         <v>34</v>
@@ -20704,7 +20704,7 @@
     </row>
     <row r="775" spans="1:8">
       <c r="A775">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B775" t="s">
         <v>34</v>
@@ -20730,7 +20730,7 @@
     </row>
     <row r="776" spans="1:8">
       <c r="A776">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B776" t="s">
         <v>34</v>
@@ -20756,7 +20756,7 @@
     </row>
     <row r="777" spans="1:8">
       <c r="A777">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B777" t="s">
         <v>34</v>
@@ -20782,7 +20782,7 @@
     </row>
     <row r="778" spans="1:8">
       <c r="A778">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B778" t="s">
         <v>34</v>
@@ -20808,7 +20808,7 @@
     </row>
     <row r="779" spans="1:8">
       <c r="A779">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B779" t="s">
         <v>34</v>
@@ -20834,7 +20834,7 @@
     </row>
     <row r="780" spans="1:8">
       <c r="A780">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B780" t="s">
         <v>34</v>
@@ -20860,7 +20860,7 @@
     </row>
     <row r="781" spans="1:8">
       <c r="A781">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B781" t="s">
         <v>34</v>
@@ -20869,7 +20869,7 @@
         <v>64</v>
       </c>
       <c r="D781">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E781" t="s">
         <v>33</v>
@@ -20886,7 +20886,7 @@
     </row>
     <row r="782" spans="1:8">
       <c r="A782">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B782" t="s">
         <v>34</v>
@@ -20895,7 +20895,7 @@
         <v>64</v>
       </c>
       <c r="D782">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E782" t="s">
         <v>35</v>
@@ -20912,7 +20912,7 @@
     </row>
     <row r="783" spans="1:8">
       <c r="A783">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B783" t="s">
         <v>34</v>
@@ -20938,7 +20938,7 @@
     </row>
     <row r="784" spans="1:8">
       <c r="A784">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="B784" t="s">
         <v>34</v>
@@ -20964,7 +20964,7 @@
     </row>
     <row r="785" spans="1:8">
       <c r="A785">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B785" t="s">
         <v>35</v>
@@ -20990,7 +20990,7 @@
     </row>
     <row r="786" spans="1:8">
       <c r="A786">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B786" t="s">
         <v>35</v>
@@ -21016,7 +21016,7 @@
     </row>
     <row r="787" spans="1:8">
       <c r="A787">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B787" t="s">
         <v>35</v>
@@ -21042,7 +21042,7 @@
     </row>
     <row r="788" spans="1:8">
       <c r="A788">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B788" t="s">
         <v>35</v>
@@ -21068,7 +21068,7 @@
     </row>
     <row r="789" spans="1:8">
       <c r="A789">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B789" t="s">
         <v>35</v>
@@ -21077,7 +21077,7 @@
         <v>65</v>
       </c>
       <c r="D789">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E789" t="s">
         <v>12</v>
@@ -21094,7 +21094,7 @@
     </row>
     <row r="790" spans="1:8">
       <c r="A790">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B790" t="s">
         <v>35</v>
@@ -21103,7 +21103,7 @@
         <v>65</v>
       </c>
       <c r="D790">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E790" t="s">
         <v>13</v>
@@ -21120,7 +21120,7 @@
     </row>
     <row r="791" spans="1:8">
       <c r="A791">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B791" t="s">
         <v>35</v>
@@ -21129,7 +21129,7 @@
         <v>65</v>
       </c>
       <c r="D791">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E791" t="s">
         <v>14</v>
@@ -21146,7 +21146,7 @@
     </row>
     <row r="792" spans="1:8">
       <c r="A792">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B792" t="s">
         <v>35</v>
@@ -21155,7 +21155,7 @@
         <v>65</v>
       </c>
       <c r="D792">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E792" t="s">
         <v>15</v>
@@ -21172,7 +21172,7 @@
     </row>
     <row r="793" spans="1:8">
       <c r="A793">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B793" t="s">
         <v>35</v>
@@ -21181,7 +21181,7 @@
         <v>65</v>
       </c>
       <c r="D793">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E793" t="s">
         <v>16</v>
@@ -21198,7 +21198,7 @@
     </row>
     <row r="794" spans="1:8">
       <c r="A794">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B794" t="s">
         <v>35</v>
@@ -21224,7 +21224,7 @@
     </row>
     <row r="795" spans="1:8">
       <c r="A795">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B795" t="s">
         <v>35</v>
@@ -21250,7 +21250,7 @@
     </row>
     <row r="796" spans="1:8">
       <c r="A796">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B796" t="s">
         <v>35</v>
@@ -21276,7 +21276,7 @@
     </row>
     <row r="797" spans="1:8">
       <c r="A797">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B797" t="s">
         <v>35</v>
@@ -21302,7 +21302,7 @@
     </row>
     <row r="798" spans="1:8">
       <c r="A798">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B798" t="s">
         <v>35</v>
@@ -21328,7 +21328,7 @@
     </row>
     <row r="799" spans="1:8">
       <c r="A799">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B799" t="s">
         <v>35</v>
@@ -21354,7 +21354,7 @@
     </row>
     <row r="800" spans="1:8">
       <c r="A800">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B800" t="s">
         <v>35</v>
@@ -21380,7 +21380,7 @@
     </row>
     <row r="801" spans="1:8">
       <c r="A801">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B801" t="s">
         <v>35</v>
@@ -21406,7 +21406,7 @@
     </row>
     <row r="802" spans="1:8">
       <c r="A802">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B802" t="s">
         <v>35</v>
@@ -21432,7 +21432,7 @@
     </row>
     <row r="803" spans="1:8">
       <c r="A803">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B803" t="s">
         <v>35</v>
@@ -21458,7 +21458,7 @@
     </row>
     <row r="804" spans="1:8">
       <c r="A804">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B804" t="s">
         <v>35</v>
@@ -21484,7 +21484,7 @@
     </row>
     <row r="805" spans="1:8">
       <c r="A805">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B805" t="s">
         <v>35</v>
@@ -21510,7 +21510,7 @@
     </row>
     <row r="806" spans="1:8">
       <c r="A806">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B806" t="s">
         <v>35</v>
@@ -21536,7 +21536,7 @@
     </row>
     <row r="807" spans="1:8">
       <c r="A807">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B807" t="s">
         <v>35</v>
@@ -21562,7 +21562,7 @@
     </row>
     <row r="808" spans="1:8">
       <c r="A808">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B808" t="s">
         <v>35</v>
@@ -21588,7 +21588,7 @@
     </row>
     <row r="809" spans="1:8">
       <c r="A809">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B809" t="s">
         <v>35</v>
@@ -21614,7 +21614,7 @@
     </row>
     <row r="810" spans="1:8">
       <c r="A810">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B810" t="s">
         <v>35</v>
@@ -21623,7 +21623,7 @@
         <v>65</v>
       </c>
       <c r="D810">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E810" t="s">
         <v>33</v>
@@ -21640,7 +21640,7 @@
     </row>
     <row r="811" spans="1:8">
       <c r="A811">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B811" t="s">
         <v>35</v>
@@ -21649,7 +21649,7 @@
         <v>65</v>
       </c>
       <c r="D811">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E811" t="s">
         <v>34</v>
@@ -21666,7 +21666,7 @@
     </row>
     <row r="812" spans="1:8">
       <c r="A812">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B812" t="s">
         <v>35</v>
@@ -21692,7 +21692,7 @@
     </row>
     <row r="813" spans="1:8">
       <c r="A813">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B813" t="s">
         <v>35</v>
@@ -21831,7 +21831,7 @@
         <v>66</v>
       </c>
       <c r="D818">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E818" t="s">
         <v>12</v>
@@ -21857,7 +21857,7 @@
         <v>66</v>
       </c>
       <c r="D819">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E819" t="s">
         <v>13</v>
@@ -21883,7 +21883,7 @@
         <v>66</v>
       </c>
       <c r="D820">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E820" t="s">
         <v>14</v>
@@ -21909,7 +21909,7 @@
         <v>66</v>
       </c>
       <c r="D821">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E821" t="s">
         <v>15</v>
@@ -21935,7 +21935,7 @@
         <v>66</v>
       </c>
       <c r="D822">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E822" t="s">
         <v>16</v>
@@ -22377,7 +22377,7 @@
         <v>66</v>
       </c>
       <c r="D839">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E839" t="s">
         <v>33</v>
@@ -22403,7 +22403,7 @@
         <v>66</v>
       </c>
       <c r="D840">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E840" t="s">
         <v>34</v>
@@ -22429,7 +22429,7 @@
         <v>66</v>
       </c>
       <c r="D841">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E841" t="s">
         <v>35</v>
@@ -22585,7 +22585,7 @@
         <v>67</v>
       </c>
       <c r="D847">
-        <v>1610612737</v>
+        <v>1610612761</v>
       </c>
       <c r="E847" t="s">
         <v>12</v>
@@ -22611,7 +22611,7 @@
         <v>67</v>
       </c>
       <c r="D848">
-        <v>1610612761</v>
+        <v>1610612737</v>
       </c>
       <c r="E848" t="s">
         <v>13</v>
@@ -22637,7 +22637,7 @@
         <v>67</v>
       </c>
       <c r="D849">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E849" t="s">
         <v>14</v>
@@ -22663,7 +22663,7 @@
         <v>67</v>
       </c>
       <c r="D850">
-        <v>1610612766</v>
+        <v>1610612755</v>
       </c>
       <c r="E850" t="s">
         <v>15</v>
@@ -22689,7 +22689,7 @@
         <v>67</v>
       </c>
       <c r="D851">
-        <v>1610612753</v>
+        <v>1610612766</v>
       </c>
       <c r="E851" t="s">
         <v>16</v>
@@ -23131,7 +23131,7 @@
         <v>67</v>
       </c>
       <c r="D868">
-        <v>1610612742</v>
+        <v>1610612740</v>
       </c>
       <c r="E868" t="s">
         <v>33</v>
@@ -23157,7 +23157,7 @@
         <v>67</v>
       </c>
       <c r="D869">
-        <v>1610612740</v>
+        <v>1610612763</v>
       </c>
       <c r="E869" t="s">
         <v>34</v>
@@ -23183,7 +23183,7 @@
         <v>67</v>
       </c>
       <c r="D870">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E870" t="s">
         <v>35</v>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -58,10 +58,10 @@
     <t>Hawks</t>
   </si>
   <si>
-    <t>Magic</t>
+    <t>76ers</t>
   </si>
   <si>
-    <t>76ers</t>
+    <t>Magic</t>
   </si>
   <si>
     <t>Hornets</t>
@@ -106,10 +106,10 @@
     <t>Suns</t>
   </si>
   <si>
-    <t>Clippers</t>
+    <t>Trail Blazers</t>
   </si>
   <si>
-    <t>Trail Blazers</t>
+    <t>Clippers</t>
   </si>
   <si>
     <t>Warriors</t>
@@ -118,10 +118,10 @@
     <t>Pelicans</t>
   </si>
   <si>
-    <t>Grizzlies</t>
+    <t>Mavericks</t>
   </si>
   <si>
-    <t>Mavericks</t>
+    <t>Grizzlies</t>
   </si>
   <si>
     <t>Kings</t>
@@ -148,10 +148,10 @@
     <t>ATL</t>
   </si>
   <si>
-    <t>ORL</t>
+    <t>PHI</t>
   </si>
   <si>
-    <t>PHI</t>
+    <t>ORL</t>
   </si>
   <si>
     <t>CHA</t>
@@ -196,10 +196,10 @@
     <t>PHX</t>
   </si>
   <si>
-    <t>LAC</t>
+    <t>POR</t>
   </si>
   <si>
-    <t>POR</t>
+    <t>LAC</t>
   </si>
   <si>
     <t>GSW</t>
@@ -208,10 +208,10 @@
     <t>NOP</t>
   </si>
   <si>
-    <t>MEM</t>
+    <t>DAL</t>
   </si>
   <si>
-    <t>DAL</t>
+    <t>MEM</t>
   </si>
   <si>
     <t>SAC</t>
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4706</v>
+        <v>0.4274</v>
       </c>
       <c r="H2">
-        <v>0.4157</v>
+        <v>0.3739</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,10 +650,10 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>0.5359</v>
+        <v>0.5937</v>
       </c>
       <c r="H3">
-        <v>0.4921</v>
+        <v>0.5558999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5181</v>
+        <v>0.5325</v>
       </c>
       <c r="H4">
-        <v>0.4799</v>
+        <v>0.4917</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -702,10 +702,10 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>0.7623</v>
+        <v>0.7864</v>
       </c>
       <c r="H5">
-        <v>0.7457</v>
+        <v>0.7712</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -728,10 +728,10 @@
         <v>43</v>
       </c>
       <c r="G6">
-        <v>0.7467</v>
+        <v>0.8082</v>
       </c>
       <c r="H6">
-        <v>0.7086</v>
+        <v>0.7793</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -745,7 +745,7 @@
         <v>38</v>
       </c>
       <c r="D7">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -754,10 +754,10 @@
         <v>44</v>
       </c>
       <c r="G7">
-        <v>0.907</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="H7">
-        <v>0.8798</v>
+        <v>0.8804999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -771,7 +771,7 @@
         <v>38</v>
       </c>
       <c r="D8">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.8467</v>
+        <v>0.927</v>
       </c>
       <c r="H8">
-        <v>0.8175</v>
+        <v>0.9061</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -806,10 +806,10 @@
         <v>46</v>
       </c>
       <c r="G9">
-        <v>0.6642</v>
+        <v>0.7487</v>
       </c>
       <c r="H9">
-        <v>0.6382</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -835,7 +835,7 @@
         <v>0.8745000000000001</v>
       </c>
       <c r="H10">
-        <v>0.8401999999999999</v>
+        <v>0.8475</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -858,10 +858,10 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>0.9481000000000001</v>
+        <v>0.9798</v>
       </c>
       <c r="H11">
-        <v>0.9373</v>
+        <v>0.9752</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -884,10 +884,10 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>0.9657</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="H12">
-        <v>0.9569</v>
+        <v>0.976</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -910,10 +910,10 @@
         <v>50</v>
       </c>
       <c r="G13">
-        <v>0.9849</v>
+        <v>0.9855</v>
       </c>
       <c r="H13">
-        <v>0.9802999999999999</v>
+        <v>0.9811</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.966</v>
+        <v>0.9797</v>
       </c>
       <c r="H14">
-        <v>0.9605</v>
+        <v>0.9765</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -962,10 +962,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>0.9791</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="H15">
-        <v>0.9729</v>
+        <v>0.9809</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1161,7 +1161,7 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E23" t="s">
         <v>30</v>
@@ -1187,7 +1187,7 @@
         <v>38</v>
       </c>
       <c r="D24">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E24" t="s">
         <v>31</v>
@@ -1265,7 +1265,7 @@
         <v>38</v>
       </c>
       <c r="D27">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E27" t="s">
         <v>34</v>
@@ -1291,7 +1291,7 @@
         <v>38</v>
       </c>
       <c r="D28">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E28" t="s">
         <v>35</v>
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.5843</v>
+        <v>0.6261</v>
       </c>
       <c r="H31">
-        <v>0.5294</v>
+        <v>0.5726</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="G32">
-        <v>0.6526</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="H32">
-        <v>0.6325</v>
+        <v>0.6698</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1430,10 +1430,10 @@
         <v>41</v>
       </c>
       <c r="G33">
-        <v>0.625</v>
+        <v>0.6828</v>
       </c>
       <c r="H33">
-        <v>0.5883</v>
+        <v>0.6556999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.8643999999999999</v>
+        <v>0.8879</v>
       </c>
       <c r="H34">
-        <v>0.8337</v>
+        <v>0.8594000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1482,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="G35">
-        <v>0.83</v>
+        <v>0.8995</v>
       </c>
       <c r="H35">
-        <v>0.787</v>
+        <v>0.8692</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1499,7 +1499,7 @@
         <v>39</v>
       </c>
       <c r="D36">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E36" t="s">
         <v>14</v>
@@ -1508,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="G36">
-        <v>0.9384</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="H36">
-        <v>0.9204</v>
+        <v>0.9366</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1525,7 +1525,7 @@
         <v>39</v>
       </c>
       <c r="D37">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.9163</v>
+        <v>0.9589</v>
       </c>
       <c r="H37">
-        <v>0.8971</v>
+        <v>0.9471000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.7496</v>
+        <v>0.8406</v>
       </c>
       <c r="H38">
-        <v>0.7053</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1586,10 +1586,10 @@
         <v>47</v>
       </c>
       <c r="G39">
-        <v>0.9288999999999999</v>
+        <v>0.9337</v>
       </c>
       <c r="H39">
-        <v>0.9031</v>
+        <v>0.9113</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1612,10 +1612,10 @@
         <v>48</v>
       </c>
       <c r="G40">
-        <v>0.9728</v>
+        <v>0.9856</v>
       </c>
       <c r="H40">
-        <v>0.9635</v>
+        <v>0.9814000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1638,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="G41">
-        <v>0.9828</v>
+        <v>0.9881</v>
       </c>
       <c r="H41">
-        <v>0.9767</v>
+        <v>0.9838</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1664,10 +1664,10 @@
         <v>50</v>
       </c>
       <c r="G42">
-        <v>0.9875</v>
+        <v>0.9886</v>
       </c>
       <c r="H42">
-        <v>0.985</v>
+        <v>0.9862</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1690,10 +1690,10 @@
         <v>51</v>
       </c>
       <c r="G43">
-        <v>0.9786</v>
+        <v>0.9856</v>
       </c>
       <c r="H43">
-        <v>0.9713000000000001</v>
+        <v>0.981</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1716,10 +1716,10 @@
         <v>52</v>
       </c>
       <c r="G44">
-        <v>0.9892</v>
+        <v>0.989</v>
       </c>
       <c r="H44">
-        <v>0.9859</v>
+        <v>0.9852</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1915,7 +1915,7 @@
         <v>39</v>
       </c>
       <c r="D52">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
@@ -1941,7 +1941,7 @@
         <v>39</v>
       </c>
       <c r="D53">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E53" t="s">
         <v>31</v>
@@ -2019,7 +2019,7 @@
         <v>39</v>
       </c>
       <c r="D56">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E56" t="s">
         <v>34</v>
@@ -2045,7 +2045,7 @@
         <v>39</v>
       </c>
       <c r="D57">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E57" t="s">
         <v>35</v>
@@ -2132,10 +2132,10 @@
         <v>38</v>
       </c>
       <c r="G60">
-        <v>0.5079</v>
+        <v>0.4441</v>
       </c>
       <c r="H60">
-        <v>0.4641</v>
+        <v>0.4063</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2158,10 +2158,10 @@
         <v>39</v>
       </c>
       <c r="G61">
-        <v>0.3675</v>
+        <v>0.3302</v>
       </c>
       <c r="H61">
-        <v>0.3474</v>
+        <v>0.3049</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2184,10 +2184,10 @@
         <v>41</v>
       </c>
       <c r="G62">
-        <v>0.5139</v>
+        <v>0.5058</v>
       </c>
       <c r="H62">
-        <v>0.4731</v>
+        <v>0.4677</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2210,10 +2210,10 @@
         <v>42</v>
       </c>
       <c r="G63">
-        <v>0.805</v>
+        <v>0.78</v>
       </c>
       <c r="H63">
-        <v>0.7696</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2236,10 +2236,10 @@
         <v>43</v>
       </c>
       <c r="G64">
-        <v>0.7507</v>
+        <v>0.7732</v>
       </c>
       <c r="H64">
-        <v>0.7094</v>
+        <v>0.7217</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2253,7 +2253,7 @@
         <v>40</v>
       </c>
       <c r="D65">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E65" t="s">
         <v>14</v>
@@ -2262,10 +2262,10 @@
         <v>44</v>
       </c>
       <c r="G65">
-        <v>0.9134</v>
+        <v>0.8932</v>
       </c>
       <c r="H65">
-        <v>0.8893</v>
+        <v>0.8738</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2279,7 +2279,7 @@
         <v>40</v>
       </c>
       <c r="D66">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E66" t="s">
         <v>15</v>
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.8835</v>
+        <v>0.9086</v>
       </c>
       <c r="H66">
-        <v>0.8651</v>
+        <v>0.884</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2314,10 +2314,10 @@
         <v>46</v>
       </c>
       <c r="G67">
-        <v>0.6536999999999999</v>
+        <v>0.6823</v>
       </c>
       <c r="H67">
-        <v>0.6151</v>
+        <v>0.6371</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2340,10 +2340,10 @@
         <v>47</v>
       </c>
       <c r="G68">
-        <v>0.9041</v>
+        <v>0.8704</v>
       </c>
       <c r="H68">
-        <v>0.8716</v>
+        <v>0.8302</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2366,10 +2366,10 @@
         <v>48</v>
       </c>
       <c r="G69">
-        <v>0.9613</v>
+        <v>0.9818</v>
       </c>
       <c r="H69">
-        <v>0.9514</v>
+        <v>0.9768</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="G70">
-        <v>0.9733000000000001</v>
+        <v>0.9863</v>
       </c>
       <c r="H70">
-        <v>0.9653</v>
+        <v>0.9818</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2418,10 +2418,10 @@
         <v>50</v>
       </c>
       <c r="G71">
-        <v>0.9849</v>
+        <v>0.9868</v>
       </c>
       <c r="H71">
-        <v>0.9829</v>
+        <v>0.9848</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2444,10 +2444,10 @@
         <v>51</v>
       </c>
       <c r="G72">
-        <v>0.9713000000000001</v>
+        <v>0.9797</v>
       </c>
       <c r="H72">
-        <v>0.9631999999999999</v>
+        <v>0.9741</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2470,10 +2470,10 @@
         <v>52</v>
       </c>
       <c r="G73">
-        <v>0.9881</v>
+        <v>0.9875</v>
       </c>
       <c r="H73">
-        <v>0.9846</v>
+        <v>0.9835</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2669,7 +2669,7 @@
         <v>40</v>
       </c>
       <c r="D81">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E81" t="s">
         <v>30</v>
@@ -2695,7 +2695,7 @@
         <v>40</v>
       </c>
       <c r="D82">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E82" t="s">
         <v>31</v>
@@ -2773,7 +2773,7 @@
         <v>40</v>
       </c>
       <c r="D85">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E85" t="s">
         <v>34</v>
@@ -2799,7 +2799,7 @@
         <v>40</v>
       </c>
       <c r="D86">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E86" t="s">
         <v>35</v>
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.5201</v>
+        <v>0.5083</v>
       </c>
       <c r="H89">
-        <v>0.4819</v>
+        <v>0.4675</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2912,10 +2912,10 @@
         <v>39</v>
       </c>
       <c r="G90">
-        <v>0.4117</v>
+        <v>0.3443</v>
       </c>
       <c r="H90">
-        <v>0.375</v>
+        <v>0.3172</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2938,10 +2938,10 @@
         <v>40</v>
       </c>
       <c r="G91">
-        <v>0.5269</v>
+        <v>0.5323</v>
       </c>
       <c r="H91">
-        <v>0.4861</v>
+        <v>0.4942</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.7845</v>
+        <v>0.8031</v>
       </c>
       <c r="H92">
-        <v>0.7493</v>
+        <v>0.7664</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2990,10 +2990,10 @@
         <v>43</v>
       </c>
       <c r="G93">
-        <v>0.7811</v>
+        <v>0.8207</v>
       </c>
       <c r="H93">
-        <v>0.7391</v>
+        <v>0.7829</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3007,7 +3007,7 @@
         <v>41</v>
       </c>
       <c r="D94">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E94" t="s">
         <v>14</v>
@@ -3016,10 +3016,10 @@
         <v>44</v>
       </c>
       <c r="G94">
-        <v>0.9021</v>
+        <v>0.889</v>
       </c>
       <c r="H94">
-        <v>0.8742</v>
+        <v>0.8676</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3033,7 +3033,7 @@
         <v>41</v>
       </c>
       <c r="D95">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E95" t="s">
         <v>15</v>
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.8892</v>
+        <v>0.9024</v>
       </c>
       <c r="H95">
-        <v>0.8665</v>
+        <v>0.8764</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3068,10 +3068,10 @@
         <v>46</v>
       </c>
       <c r="G96">
-        <v>0.6498</v>
+        <v>0.6977</v>
       </c>
       <c r="H96">
-        <v>0.6116</v>
+        <v>0.6609</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3094,10 +3094,10 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.8947000000000001</v>
+        <v>0.886</v>
       </c>
       <c r="H97">
-        <v>0.8595</v>
+        <v>0.8525</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3120,10 +3120,10 @@
         <v>48</v>
       </c>
       <c r="G98">
-        <v>0.9677</v>
+        <v>0.9759</v>
       </c>
       <c r="H98">
-        <v>0.9581</v>
+        <v>0.9687</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3146,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="G99">
-        <v>0.9739</v>
+        <v>0.9792</v>
       </c>
       <c r="H99">
-        <v>0.969</v>
+        <v>0.9752999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3175,7 +3175,7 @@
         <v>0.9832</v>
       </c>
       <c r="H100">
-        <v>0.9792999999999999</v>
+        <v>0.9792</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3198,10 +3198,10 @@
         <v>51</v>
       </c>
       <c r="G101">
-        <v>0.9704</v>
+        <v>0.9691</v>
       </c>
       <c r="H101">
-        <v>0.9657</v>
+        <v>0.9654</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3224,7 +3224,7 @@
         <v>52</v>
       </c>
       <c r="G102">
-        <v>0.9863</v>
+        <v>0.9861</v>
       </c>
       <c r="H102">
         <v>0.9825</v>
@@ -3423,7 +3423,7 @@
         <v>41</v>
       </c>
       <c r="D110">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E110" t="s">
         <v>30</v>
@@ -3449,7 +3449,7 @@
         <v>41</v>
       </c>
       <c r="D111">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E111" t="s">
         <v>31</v>
@@ -3527,7 +3527,7 @@
         <v>41</v>
       </c>
       <c r="D114">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E114" t="s">
         <v>34</v>
@@ -3553,7 +3553,7 @@
         <v>41</v>
       </c>
       <c r="D115">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E115" t="s">
         <v>35</v>
@@ -3640,10 +3640,10 @@
         <v>38</v>
       </c>
       <c r="G118">
-        <v>0.2543</v>
+        <v>0.2288</v>
       </c>
       <c r="H118">
-        <v>0.2377</v>
+        <v>0.2136</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3666,10 +3666,10 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.1663</v>
+        <v>0.1406</v>
       </c>
       <c r="H119">
-        <v>0.1356</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3692,10 +3692,10 @@
         <v>40</v>
       </c>
       <c r="G120">
-        <v>0.2304</v>
+        <v>0.2605</v>
       </c>
       <c r="H120">
-        <v>0.195</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3718,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2507</v>
+        <v>0.2336</v>
       </c>
       <c r="H121">
-        <v>0.2155</v>
+        <v>0.1969</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3744,10 +3744,10 @@
         <v>43</v>
       </c>
       <c r="G122">
-        <v>0.4518</v>
+        <v>0.4891</v>
       </c>
       <c r="H122">
-        <v>0.4201</v>
+        <v>0.4544</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3761,7 +3761,7 @@
         <v>42</v>
       </c>
       <c r="D123">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E123" t="s">
         <v>14</v>
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.7047</v>
+        <v>0.6917</v>
       </c>
       <c r="H123">
-        <v>0.6568000000000001</v>
+        <v>0.6713</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -3787,7 +3787,7 @@
         <v>42</v>
       </c>
       <c r="D124">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E124" t="s">
         <v>15</v>
@@ -3796,10 +3796,10 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.6297</v>
+        <v>0.7459</v>
       </c>
       <c r="H124">
-        <v>0.5998</v>
+        <v>0.7054</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3822,10 +3822,10 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.4013</v>
+        <v>0.455</v>
       </c>
       <c r="H125">
-        <v>0.3598</v>
+        <v>0.4118</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3848,10 +3848,10 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.6661</v>
+        <v>0.6748</v>
       </c>
       <c r="H126">
-        <v>0.6219</v>
+        <v>0.6284999999999999</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3874,10 +3874,10 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.9025</v>
+        <v>0.9606</v>
       </c>
       <c r="H127">
-        <v>0.8696</v>
+        <v>0.946</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3900,10 +3900,10 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9184</v>
+        <v>0.9589</v>
       </c>
       <c r="H128">
-        <v>0.8948</v>
+        <v>0.9403</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3926,10 +3926,10 @@
         <v>50</v>
       </c>
       <c r="G129">
-        <v>0.979</v>
+        <v>0.9806</v>
       </c>
       <c r="H129">
-        <v>0.974</v>
+        <v>0.9759</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -3952,10 +3952,10 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9327</v>
+        <v>0.9554</v>
       </c>
       <c r="H130">
-        <v>0.9179</v>
+        <v>0.9445</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3978,10 +3978,10 @@
         <v>52</v>
       </c>
       <c r="G131">
-        <v>0.9731</v>
+        <v>0.9811</v>
       </c>
       <c r="H131">
-        <v>0.9645</v>
+        <v>0.9752999999999999</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4177,7 +4177,7 @@
         <v>42</v>
       </c>
       <c r="D139">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E139" t="s">
         <v>30</v>
@@ -4203,7 +4203,7 @@
         <v>42</v>
       </c>
       <c r="D140">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E140" t="s">
         <v>31</v>
@@ -4281,7 +4281,7 @@
         <v>42</v>
       </c>
       <c r="D143">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E143" t="s">
         <v>34</v>
@@ -4307,7 +4307,7 @@
         <v>42</v>
       </c>
       <c r="D144">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E144" t="s">
         <v>35</v>
@@ -4394,10 +4394,10 @@
         <v>38</v>
       </c>
       <c r="G147">
-        <v>0.2914</v>
+        <v>0.2207</v>
       </c>
       <c r="H147">
-        <v>0.2533</v>
+        <v>0.1918</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4420,10 +4420,10 @@
         <v>39</v>
       </c>
       <c r="G148">
-        <v>0.213</v>
+        <v>0.1308</v>
       </c>
       <c r="H148">
-        <v>0.17</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4446,10 +4446,10 @@
         <v>40</v>
       </c>
       <c r="G149">
-        <v>0.2906</v>
+        <v>0.2783</v>
       </c>
       <c r="H149">
-        <v>0.2493</v>
+        <v>0.2268</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4472,10 +4472,10 @@
         <v>41</v>
       </c>
       <c r="G150">
-        <v>0.2609</v>
+        <v>0.2171</v>
       </c>
       <c r="H150">
-        <v>0.2189</v>
+        <v>0.1793</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4498,10 +4498,10 @@
         <v>42</v>
       </c>
       <c r="G151">
-        <v>0.5799</v>
+        <v>0.5456</v>
       </c>
       <c r="H151">
-        <v>0.5482</v>
+        <v>0.5109</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4515,7 +4515,7 @@
         <v>43</v>
       </c>
       <c r="D152">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E152" t="s">
         <v>14</v>
@@ -4524,10 +4524,10 @@
         <v>44</v>
       </c>
       <c r="G152">
-        <v>0.7261</v>
+        <v>0.6984</v>
       </c>
       <c r="H152">
-        <v>0.6808999999999999</v>
+        <v>0.6777</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4541,7 +4541,7 @@
         <v>43</v>
       </c>
       <c r="D153">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E153" t="s">
         <v>15</v>
@@ -4550,10 +4550,10 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.6996</v>
+        <v>0.7249</v>
       </c>
       <c r="H153">
-        <v>0.6652</v>
+        <v>0.6774</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4576,10 +4576,10 @@
         <v>46</v>
       </c>
       <c r="G154">
-        <v>0.4515</v>
+        <v>0.4563</v>
       </c>
       <c r="H154">
-        <v>0.413</v>
+        <v>0.4238</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4602,10 +4602,10 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>0.7079</v>
+        <v>0.6725</v>
       </c>
       <c r="H155">
-        <v>0.6646</v>
+        <v>0.6354</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4628,10 +4628,10 @@
         <v>48</v>
       </c>
       <c r="G156">
-        <v>0.9146</v>
+        <v>0.9594</v>
       </c>
       <c r="H156">
-        <v>0.8835</v>
+        <v>0.9434</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4654,10 +4654,10 @@
         <v>49</v>
       </c>
       <c r="G157">
-        <v>0.9349</v>
+        <v>0.9578</v>
       </c>
       <c r="H157">
-        <v>0.9152</v>
+        <v>0.9437</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4680,10 +4680,10 @@
         <v>50</v>
       </c>
       <c r="G158">
-        <v>0.9799</v>
+        <v>0.9802</v>
       </c>
       <c r="H158">
-        <v>0.9731</v>
+        <v>0.9737</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -4706,10 +4706,10 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9427</v>
+        <v>0.9544</v>
       </c>
       <c r="H159">
-        <v>0.9291</v>
+        <v>0.9434</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4732,10 +4732,10 @@
         <v>52</v>
       </c>
       <c r="G160">
-        <v>0.9784</v>
+        <v>0.9828</v>
       </c>
       <c r="H160">
-        <v>0.9725</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -4931,7 +4931,7 @@
         <v>43</v>
       </c>
       <c r="D168">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E168" t="s">
         <v>30</v>
@@ -4957,7 +4957,7 @@
         <v>43</v>
       </c>
       <c r="D169">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E169" t="s">
         <v>31</v>
@@ -5035,7 +5035,7 @@
         <v>43</v>
       </c>
       <c r="D172">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E172" t="s">
         <v>34</v>
@@ -5061,7 +5061,7 @@
         <v>43</v>
       </c>
       <c r="D173">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E173" t="s">
         <v>35</v>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B176" t="s">
         <v>14</v>
@@ -5148,15 +5148,15 @@
         <v>38</v>
       </c>
       <c r="G176">
-        <v>0.1202</v>
+        <v>0.1195</v>
       </c>
       <c r="H176">
-        <v>0.093</v>
+        <v>0.0993</v>
       </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B177" t="s">
         <v>14</v>
@@ -5174,15 +5174,15 @@
         <v>39</v>
       </c>
       <c r="G177">
-        <v>0.0796</v>
+        <v>0.0634</v>
       </c>
       <c r="H177">
-        <v>0.0616</v>
+        <v>0.0499</v>
       </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B178" t="s">
         <v>14</v>
@@ -5200,15 +5200,15 @@
         <v>40</v>
       </c>
       <c r="G178">
-        <v>0.1107</v>
+        <v>0.1262</v>
       </c>
       <c r="H178">
-        <v>0.0866</v>
+        <v>0.1068</v>
       </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B179" t="s">
         <v>14</v>
@@ -5226,15 +5226,15 @@
         <v>41</v>
       </c>
       <c r="G179">
-        <v>0.1258</v>
+        <v>0.1324</v>
       </c>
       <c r="H179">
-        <v>0.0979</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B180" t="s">
         <v>14</v>
@@ -5252,15 +5252,15 @@
         <v>42</v>
       </c>
       <c r="G180">
-        <v>0.3432</v>
+        <v>0.3287</v>
       </c>
       <c r="H180">
-        <v>0.2953</v>
+        <v>0.3083</v>
       </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B181" t="s">
         <v>14</v>
@@ -5278,15 +5278,15 @@
         <v>43</v>
       </c>
       <c r="G181">
-        <v>0.3191</v>
+        <v>0.3223</v>
       </c>
       <c r="H181">
-        <v>0.2739</v>
+        <v>0.3016</v>
       </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B182" t="s">
         <v>14</v>
@@ -5295,7 +5295,7 @@
         <v>44</v>
       </c>
       <c r="D182">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E182" t="s">
         <v>15</v>
@@ -5304,15 +5304,15 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.4539</v>
+        <v>0.5443</v>
       </c>
       <c r="H182">
-        <v>0.421</v>
+        <v>0.4948</v>
       </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B183" t="s">
         <v>14</v>
@@ -5330,15 +5330,15 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.2276</v>
+        <v>0.2444</v>
       </c>
       <c r="H183">
-        <v>0.1819</v>
+        <v>0.2074</v>
       </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B184" t="s">
         <v>14</v>
@@ -5356,15 +5356,15 @@
         <v>47</v>
       </c>
       <c r="G184">
-        <v>0.5348000000000001</v>
+        <v>0.4789</v>
       </c>
       <c r="H184">
-        <v>0.5092</v>
+        <v>0.4236</v>
       </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B185" t="s">
         <v>14</v>
@@ -5382,15 +5382,15 @@
         <v>48</v>
       </c>
       <c r="G185">
-        <v>0.792</v>
+        <v>0.9111</v>
       </c>
       <c r="H185">
-        <v>0.7546</v>
+        <v>0.8863</v>
       </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B186" t="s">
         <v>14</v>
@@ -5408,15 +5408,15 @@
         <v>49</v>
       </c>
       <c r="G186">
-        <v>0.8245</v>
+        <v>0.8988</v>
       </c>
       <c r="H186">
-        <v>0.7945</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B187" t="s">
         <v>14</v>
@@ -5434,15 +5434,15 @@
         <v>50</v>
       </c>
       <c r="G187">
-        <v>0.9464</v>
+        <v>0.9719</v>
       </c>
       <c r="H187">
-        <v>0.9357</v>
+        <v>0.9646</v>
       </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B188" t="s">
         <v>14</v>
@@ -5460,15 +5460,15 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.8444</v>
+        <v>0.9055</v>
       </c>
       <c r="H188">
-        <v>0.8082</v>
+        <v>0.8824</v>
       </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B189" t="s">
         <v>14</v>
@@ -5486,15 +5486,15 @@
         <v>52</v>
       </c>
       <c r="G189">
-        <v>0.9482</v>
+        <v>0.9691</v>
       </c>
       <c r="H189">
-        <v>0.9352</v>
+        <v>0.9622000000000001</v>
       </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B190" t="s">
         <v>14</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B191" t="s">
         <v>14</v>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B192" t="s">
         <v>14</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B193" t="s">
         <v>14</v>
@@ -5598,7 +5598,7 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B194" t="s">
         <v>14</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B195" t="s">
         <v>14</v>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B196" t="s">
         <v>14</v>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B197" t="s">
         <v>14</v>
@@ -5685,7 +5685,7 @@
         <v>44</v>
       </c>
       <c r="D197">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E197" t="s">
         <v>30</v>
@@ -5702,7 +5702,7 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B198" t="s">
         <v>14</v>
@@ -5711,7 +5711,7 @@
         <v>44</v>
       </c>
       <c r="D198">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E198" t="s">
         <v>31</v>
@@ -5728,7 +5728,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B199" t="s">
         <v>14</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B200" t="s">
         <v>14</v>
@@ -5780,7 +5780,7 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B201" t="s">
         <v>14</v>
@@ -5789,7 +5789,7 @@
         <v>44</v>
       </c>
       <c r="D201">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E201" t="s">
         <v>34</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B202" t="s">
         <v>14</v>
@@ -5815,7 +5815,7 @@
         <v>44</v>
       </c>
       <c r="D202">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E202" t="s">
         <v>35</v>
@@ -5832,7 +5832,7 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B203" t="s">
         <v>14</v>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="B204" t="s">
         <v>14</v>
@@ -5884,7 +5884,7 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B205" t="s">
         <v>15</v>
@@ -5902,15 +5902,15 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.1825</v>
+        <v>0.0939</v>
       </c>
       <c r="H205">
-        <v>0.1533</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B206" t="s">
         <v>15</v>
@@ -5928,15 +5928,15 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.1029</v>
+        <v>0.0529</v>
       </c>
       <c r="H206">
-        <v>0.0837</v>
+        <v>0.0411</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B207" t="s">
         <v>15</v>
@@ -5954,15 +5954,15 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.1349</v>
+        <v>0.116</v>
       </c>
       <c r="H207">
-        <v>0.1165</v>
+        <v>0.0914</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B208" t="s">
         <v>15</v>
@@ -5980,15 +5980,15 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.1335</v>
+        <v>0.1236</v>
       </c>
       <c r="H208">
-        <v>0.1108</v>
+        <v>0.09760000000000001</v>
       </c>
     </row>
     <row r="209" spans="1:8">
       <c r="A209">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B209" t="s">
         <v>15</v>
@@ -6006,15 +6006,15 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.4002</v>
+        <v>0.2946</v>
       </c>
       <c r="H209">
-        <v>0.3703</v>
+        <v>0.2541</v>
       </c>
     </row>
     <row r="210" spans="1:8">
       <c r="A210">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B210" t="s">
         <v>15</v>
@@ -6032,15 +6032,15 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.3348</v>
+        <v>0.3226</v>
       </c>
       <c r="H210">
-        <v>0.3004</v>
+        <v>0.2751</v>
       </c>
     </row>
     <row r="211" spans="1:8">
       <c r="A211">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B211" t="s">
         <v>15</v>
@@ -6049,7 +6049,7 @@
         <v>45</v>
       </c>
       <c r="D211">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E211" t="s">
         <v>14</v>
@@ -6058,15 +6058,15 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.579</v>
+        <v>0.5052</v>
       </c>
       <c r="H211">
-        <v>0.5461</v>
+        <v>0.4557</v>
       </c>
     </row>
     <row r="212" spans="1:8">
       <c r="A212">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B212" t="s">
         <v>15</v>
@@ -6084,15 +6084,15 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.3045</v>
+        <v>0.239</v>
       </c>
       <c r="H212">
-        <v>0.2567</v>
+        <v>0.2024</v>
       </c>
     </row>
     <row r="213" spans="1:8">
       <c r="A213">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B213" t="s">
         <v>15</v>
@@ -6110,15 +6110,15 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.5521</v>
+        <v>0.4469</v>
       </c>
       <c r="H213">
-        <v>0.5068</v>
+        <v>0.4072</v>
       </c>
     </row>
     <row r="214" spans="1:8">
       <c r="A214">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B214" t="s">
         <v>15</v>
@@ -6136,15 +6136,15 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.8397</v>
+        <v>0.915</v>
       </c>
       <c r="H214">
-        <v>0.8068</v>
+        <v>0.8887</v>
       </c>
     </row>
     <row r="215" spans="1:8">
       <c r="A215">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B215" t="s">
         <v>15</v>
@@ -6162,15 +6162,15 @@
         <v>49</v>
       </c>
       <c r="G215">
-        <v>0.8565</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="H215">
-        <v>0.8235</v>
+        <v>0.8715000000000001</v>
       </c>
     </row>
     <row r="216" spans="1:8">
       <c r="A216">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B216" t="s">
         <v>15</v>
@@ -6188,15 +6188,15 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>0.9536</v>
+        <v>0.9734</v>
       </c>
       <c r="H216">
-        <v>0.9457</v>
+        <v>0.9669</v>
       </c>
     </row>
     <row r="217" spans="1:8">
       <c r="A217">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B217" t="s">
         <v>15</v>
@@ -6214,15 +6214,15 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.8767</v>
+        <v>0.8931</v>
       </c>
       <c r="H217">
-        <v>0.8401999999999999</v>
+        <v>0.8707</v>
       </c>
     </row>
     <row r="218" spans="1:8">
       <c r="A218">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B218" t="s">
         <v>15</v>
@@ -6240,15 +6240,15 @@
         <v>52</v>
       </c>
       <c r="G218">
-        <v>0.9666</v>
+        <v>0.9585</v>
       </c>
       <c r="H218">
-        <v>0.9571</v>
+        <v>0.9487</v>
       </c>
     </row>
     <row r="219" spans="1:8">
       <c r="A219">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B219" t="s">
         <v>15</v>
@@ -6274,7 +6274,7 @@
     </row>
     <row r="220" spans="1:8">
       <c r="A220">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B220" t="s">
         <v>15</v>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="221" spans="1:8">
       <c r="A221">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B221" t="s">
         <v>15</v>
@@ -6326,7 +6326,7 @@
     </row>
     <row r="222" spans="1:8">
       <c r="A222">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B222" t="s">
         <v>15</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="223" spans="1:8">
       <c r="A223">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B223" t="s">
         <v>15</v>
@@ -6378,7 +6378,7 @@
     </row>
     <row r="224" spans="1:8">
       <c r="A224">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B224" t="s">
         <v>15</v>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="225" spans="1:8">
       <c r="A225">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B225" t="s">
         <v>15</v>
@@ -6430,7 +6430,7 @@
     </row>
     <row r="226" spans="1:8">
       <c r="A226">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B226" t="s">
         <v>15</v>
@@ -6439,7 +6439,7 @@
         <v>45</v>
       </c>
       <c r="D226">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E226" t="s">
         <v>30</v>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="227" spans="1:8">
       <c r="A227">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B227" t="s">
         <v>15</v>
@@ -6465,7 +6465,7 @@
         <v>45</v>
       </c>
       <c r="D227">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E227" t="s">
         <v>31</v>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="228" spans="1:8">
       <c r="A228">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B228" t="s">
         <v>15</v>
@@ -6508,7 +6508,7 @@
     </row>
     <row r="229" spans="1:8">
       <c r="A229">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B229" t="s">
         <v>15</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="230" spans="1:8">
       <c r="A230">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B230" t="s">
         <v>15</v>
@@ -6543,7 +6543,7 @@
         <v>45</v>
       </c>
       <c r="D230">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E230" t="s">
         <v>34</v>
@@ -6560,7 +6560,7 @@
     </row>
     <row r="231" spans="1:8">
       <c r="A231">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B231" t="s">
         <v>15</v>
@@ -6569,7 +6569,7 @@
         <v>45</v>
       </c>
       <c r="D231">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E231" t="s">
         <v>35</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B232" t="s">
         <v>15</v>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="B233" t="s">
         <v>15</v>
@@ -6656,10 +6656,10 @@
         <v>38</v>
       </c>
       <c r="G234">
-        <v>0.3618</v>
+        <v>0.288</v>
       </c>
       <c r="H234">
-        <v>0.3358</v>
+        <v>0.2513</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -6682,10 +6682,10 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.2947</v>
+        <v>0.189</v>
       </c>
       <c r="H235">
-        <v>0.2504</v>
+        <v>0.1594</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -6708,10 +6708,10 @@
         <v>40</v>
       </c>
       <c r="G236">
-        <v>0.3849</v>
+        <v>0.3629</v>
       </c>
       <c r="H236">
-        <v>0.3463</v>
+        <v>0.3177</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -6734,10 +6734,10 @@
         <v>41</v>
       </c>
       <c r="G237">
-        <v>0.3884</v>
+        <v>0.3391</v>
       </c>
       <c r="H237">
-        <v>0.3502</v>
+        <v>0.3023</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -6760,10 +6760,10 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.6402</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="H238">
-        <v>0.5987</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -6786,10 +6786,10 @@
         <v>43</v>
       </c>
       <c r="G239">
-        <v>0.587</v>
+        <v>0.5762</v>
       </c>
       <c r="H239">
-        <v>0.5485</v>
+        <v>0.5437</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -6803,7 +6803,7 @@
         <v>46</v>
       </c>
       <c r="D240">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E240" t="s">
         <v>14</v>
@@ -6812,10 +6812,10 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.8181</v>
+        <v>0.7926</v>
       </c>
       <c r="H240">
-        <v>0.7724</v>
+        <v>0.7556</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -6829,7 +6829,7 @@
         <v>46</v>
       </c>
       <c r="D241">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E241" t="s">
         <v>15</v>
@@ -6838,10 +6838,10 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.7433</v>
+        <v>0.7976</v>
       </c>
       <c r="H241">
-        <v>0.6955</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -6864,10 +6864,10 @@
         <v>47</v>
       </c>
       <c r="G242">
-        <v>0.787</v>
+        <v>0.7279</v>
       </c>
       <c r="H242">
-        <v>0.7422</v>
+        <v>0.6855</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -6890,10 +6890,10 @@
         <v>48</v>
       </c>
       <c r="G243">
-        <v>0.9321</v>
+        <v>0.9717</v>
       </c>
       <c r="H243">
-        <v>0.9123</v>
+        <v>0.963</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -6916,10 +6916,10 @@
         <v>49</v>
       </c>
       <c r="G244">
-        <v>0.9535</v>
+        <v>0.9649</v>
       </c>
       <c r="H244">
-        <v>0.9379999999999999</v>
+        <v>0.9517</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -6942,10 +6942,10 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9856</v>
+        <v>0.9865</v>
       </c>
       <c r="H245">
-        <v>0.9821</v>
+        <v>0.9827</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -6968,10 +6968,10 @@
         <v>51</v>
       </c>
       <c r="G246">
-        <v>0.9545</v>
+        <v>0.9678</v>
       </c>
       <c r="H246">
-        <v>0.9442</v>
+        <v>0.9603</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -6994,10 +6994,10 @@
         <v>52</v>
       </c>
       <c r="G247">
-        <v>0.9802999999999999</v>
+        <v>0.9859</v>
       </c>
       <c r="H247">
-        <v>0.9743000000000001</v>
+        <v>0.9818</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7193,7 +7193,7 @@
         <v>46</v>
       </c>
       <c r="D255">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E255" t="s">
         <v>30</v>
@@ -7219,7 +7219,7 @@
         <v>46</v>
       </c>
       <c r="D256">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E256" t="s">
         <v>31</v>
@@ -7297,7 +7297,7 @@
         <v>46</v>
       </c>
       <c r="D259">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E259" t="s">
         <v>34</v>
@@ -7323,7 +7323,7 @@
         <v>46</v>
       </c>
       <c r="D260">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E260" t="s">
         <v>35</v>
@@ -7410,7 +7410,7 @@
         <v>38</v>
       </c>
       <c r="G263">
-        <v>0.1598</v>
+        <v>0.1525</v>
       </c>
       <c r="H263">
         <v>0.1255</v>
@@ -7436,10 +7436,10 @@
         <v>39</v>
       </c>
       <c r="G264">
-        <v>0.0969</v>
+        <v>0.0887</v>
       </c>
       <c r="H264">
-        <v>0.0711</v>
+        <v>0.0663</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7462,10 +7462,10 @@
         <v>40</v>
       </c>
       <c r="G265">
-        <v>0.1284</v>
+        <v>0.1698</v>
       </c>
       <c r="H265">
-        <v>0.0959</v>
+        <v>0.1296</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7488,10 +7488,10 @@
         <v>41</v>
       </c>
       <c r="G266">
-        <v>0.1405</v>
+        <v>0.1475</v>
       </c>
       <c r="H266">
-        <v>0.1053</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3781</v>
+        <v>0.3715</v>
       </c>
       <c r="H267">
-        <v>0.3339</v>
+        <v>0.3252</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7540,10 +7540,10 @@
         <v>43</v>
       </c>
       <c r="G268">
-        <v>0.3354</v>
+        <v>0.3646</v>
       </c>
       <c r="H268">
-        <v>0.2921</v>
+        <v>0.3275</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -7557,7 +7557,7 @@
         <v>47</v>
       </c>
       <c r="D269">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E269" t="s">
         <v>14</v>
@@ -7566,10 +7566,10 @@
         <v>44</v>
       </c>
       <c r="G269">
-        <v>0.4908</v>
+        <v>0.5764</v>
       </c>
       <c r="H269">
-        <v>0.4652</v>
+        <v>0.5211</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7583,7 +7583,7 @@
         <v>47</v>
       </c>
       <c r="D270">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E270" t="s">
         <v>15</v>
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.4932</v>
+        <v>0.5928</v>
       </c>
       <c r="H270">
-        <v>0.4479</v>
+        <v>0.5531</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7618,10 +7618,10 @@
         <v>46</v>
       </c>
       <c r="G271">
-        <v>0.2578</v>
+        <v>0.3145</v>
       </c>
       <c r="H271">
-        <v>0.213</v>
+        <v>0.2721</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -7644,10 +7644,10 @@
         <v>48</v>
       </c>
       <c r="G272">
-        <v>0.8008</v>
+        <v>0.9352</v>
       </c>
       <c r="H272">
-        <v>0.7536</v>
+        <v>0.9121</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7670,10 +7670,10 @@
         <v>49</v>
       </c>
       <c r="G273">
-        <v>0.8259</v>
+        <v>0.9141</v>
       </c>
       <c r="H273">
-        <v>0.7911</v>
+        <v>0.8925</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7696,10 +7696,10 @@
         <v>50</v>
       </c>
       <c r="G274">
-        <v>0.9518</v>
+        <v>0.972</v>
       </c>
       <c r="H274">
-        <v>0.9383</v>
+        <v>0.9655</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7722,10 +7722,10 @@
         <v>51</v>
       </c>
       <c r="G275">
-        <v>0.8693</v>
+        <v>0.9172</v>
       </c>
       <c r="H275">
-        <v>0.8315</v>
+        <v>0.8998</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -7748,10 +7748,10 @@
         <v>52</v>
       </c>
       <c r="G276">
-        <v>0.9469</v>
+        <v>0.9697</v>
       </c>
       <c r="H276">
-        <v>0.9360000000000001</v>
+        <v>0.9626</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -7947,7 +7947,7 @@
         <v>47</v>
       </c>
       <c r="D284">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E284" t="s">
         <v>30</v>
@@ -7973,7 +7973,7 @@
         <v>47</v>
       </c>
       <c r="D285">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E285" t="s">
         <v>31</v>
@@ -8051,7 +8051,7 @@
         <v>47</v>
       </c>
       <c r="D288">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E288" t="s">
         <v>34</v>
@@ -8077,7 +8077,7 @@
         <v>47</v>
       </c>
       <c r="D289">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E289" t="s">
         <v>35</v>
@@ -8164,10 +8164,10 @@
         <v>38</v>
       </c>
       <c r="G292">
-        <v>0.06270000000000001</v>
+        <v>0.0248</v>
       </c>
       <c r="H292">
-        <v>0.0519</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8190,10 +8190,10 @@
         <v>39</v>
       </c>
       <c r="G293">
-        <v>0.0365</v>
+        <v>0.0186</v>
       </c>
       <c r="H293">
-        <v>0.0272</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -8216,10 +8216,10 @@
         <v>40</v>
       </c>
       <c r="G294">
-        <v>0.0486</v>
+        <v>0.0232</v>
       </c>
       <c r="H294">
-        <v>0.0387</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -8242,10 +8242,10 @@
         <v>41</v>
       </c>
       <c r="G295">
-        <v>0.0419</v>
+        <v>0.0313</v>
       </c>
       <c r="H295">
-        <v>0.0323</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.1304</v>
+        <v>0.054</v>
       </c>
       <c r="H296">
-        <v>0.0975</v>
+        <v>0.0394</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8294,10 +8294,10 @@
         <v>43</v>
       </c>
       <c r="G297">
-        <v>0.1165</v>
+        <v>0.0566</v>
       </c>
       <c r="H297">
-        <v>0.0854</v>
+        <v>0.0406</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -8311,7 +8311,7 @@
         <v>48</v>
       </c>
       <c r="D298">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E298" t="s">
         <v>14</v>
@@ -8320,10 +8320,10 @@
         <v>44</v>
       </c>
       <c r="G298">
-        <v>0.2454</v>
+        <v>0.1137</v>
       </c>
       <c r="H298">
-        <v>0.208</v>
+        <v>0.08890000000000001</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8337,7 +8337,7 @@
         <v>48</v>
       </c>
       <c r="D299">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E299" t="s">
         <v>15</v>
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.1932</v>
+        <v>0.1113</v>
       </c>
       <c r="H299">
-        <v>0.1603</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8372,10 +8372,10 @@
         <v>46</v>
       </c>
       <c r="G300">
-        <v>0.0877</v>
+        <v>0.037</v>
       </c>
       <c r="H300">
-        <v>0.0679</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -8398,10 +8398,10 @@
         <v>47</v>
       </c>
       <c r="G301">
-        <v>0.2464</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="H301">
-        <v>0.1992</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8424,10 +8424,10 @@
         <v>49</v>
       </c>
       <c r="G302">
-        <v>0.5688</v>
+        <v>0.4346</v>
       </c>
       <c r="H302">
-        <v>0.5351</v>
+        <v>0.4027</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -8450,10 +8450,10 @@
         <v>50</v>
       </c>
       <c r="G303">
-        <v>0.8351</v>
+        <v>0.7849</v>
       </c>
       <c r="H303">
-        <v>0.7971</v>
+        <v>0.7489</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -8476,10 +8476,10 @@
         <v>51</v>
       </c>
       <c r="G304">
-        <v>0.6052</v>
+        <v>0.453</v>
       </c>
       <c r="H304">
-        <v>0.5494</v>
+        <v>0.4098</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -8502,10 +8502,10 @@
         <v>52</v>
       </c>
       <c r="G305">
-        <v>0.8701</v>
+        <v>0.7548</v>
       </c>
       <c r="H305">
-        <v>0.8346</v>
+        <v>0.7157</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -8701,7 +8701,7 @@
         <v>48</v>
       </c>
       <c r="D313">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E313" t="s">
         <v>30</v>
@@ -8727,7 +8727,7 @@
         <v>48</v>
       </c>
       <c r="D314">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E314" t="s">
         <v>31</v>
@@ -8805,7 +8805,7 @@
         <v>48</v>
       </c>
       <c r="D317">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E317" t="s">
         <v>34</v>
@@ -8831,7 +8831,7 @@
         <v>48</v>
       </c>
       <c r="D318">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E318" t="s">
         <v>35</v>
@@ -8918,10 +8918,10 @@
         <v>38</v>
       </c>
       <c r="G321">
-        <v>0.0431</v>
+        <v>0.024</v>
       </c>
       <c r="H321">
-        <v>0.0343</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8944,10 +8944,10 @@
         <v>39</v>
       </c>
       <c r="G322">
-        <v>0.0233</v>
+        <v>0.0162</v>
       </c>
       <c r="H322">
-        <v>0.0172</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8970,10 +8970,10 @@
         <v>40</v>
       </c>
       <c r="G323">
-        <v>0.0347</v>
+        <v>0.0182</v>
       </c>
       <c r="H323">
-        <v>0.0267</v>
+        <v>0.0137</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8996,10 +8996,10 @@
         <v>41</v>
       </c>
       <c r="G324">
-        <v>0.031</v>
+        <v>0.0247</v>
       </c>
       <c r="H324">
-        <v>0.0261</v>
+        <v>0.0208</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.1052</v>
+        <v>0.0597</v>
       </c>
       <c r="H325">
-        <v>0.08160000000000001</v>
+        <v>0.0411</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9048,10 +9048,10 @@
         <v>43</v>
       </c>
       <c r="G326">
-        <v>0.0848</v>
+        <v>0.0563</v>
       </c>
       <c r="H326">
-        <v>0.06510000000000001</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -9065,7 +9065,7 @@
         <v>49</v>
       </c>
       <c r="D327">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E327" t="s">
         <v>14</v>
@@ -9074,10 +9074,10 @@
         <v>44</v>
       </c>
       <c r="G327">
-        <v>0.2055</v>
+        <v>0.126</v>
       </c>
       <c r="H327">
-        <v>0.1755</v>
+        <v>0.1012</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -9091,7 +9091,7 @@
         <v>49</v>
       </c>
       <c r="D328">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E328" t="s">
         <v>15</v>
@@ -9100,10 +9100,10 @@
         <v>45</v>
       </c>
       <c r="G328">
-        <v>0.1765</v>
+        <v>0.1285</v>
       </c>
       <c r="H328">
-        <v>0.1435</v>
+        <v>0.1053</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9126,10 +9126,10 @@
         <v>46</v>
       </c>
       <c r="G329">
-        <v>0.062</v>
+        <v>0.0483</v>
       </c>
       <c r="H329">
-        <v>0.0465</v>
+        <v>0.0351</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9152,10 +9152,10 @@
         <v>47</v>
       </c>
       <c r="G330">
-        <v>0.2089</v>
+        <v>0.1075</v>
       </c>
       <c r="H330">
-        <v>0.1741</v>
+        <v>0.0859</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9178,10 +9178,10 @@
         <v>48</v>
       </c>
       <c r="G331">
-        <v>0.4649</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="H331">
-        <v>0.4312</v>
+        <v>0.5654</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.8284</v>
+        <v>0.8369</v>
       </c>
       <c r="H332">
-        <v>0.798</v>
+        <v>0.7994</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9230,10 +9230,10 @@
         <v>51</v>
       </c>
       <c r="G333">
-        <v>0.5482</v>
+        <v>0.5364</v>
       </c>
       <c r="H333">
-        <v>0.5189</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -9256,10 +9256,10 @@
         <v>52</v>
       </c>
       <c r="G334">
-        <v>0.8461</v>
+        <v>0.8195</v>
       </c>
       <c r="H334">
-        <v>0.8135</v>
+        <v>0.7851</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -9455,7 +9455,7 @@
         <v>49</v>
       </c>
       <c r="D342">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E342" t="s">
         <v>30</v>
@@ -9481,7 +9481,7 @@
         <v>49</v>
       </c>
       <c r="D343">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E343" t="s">
         <v>31</v>
@@ -9559,7 +9559,7 @@
         <v>49</v>
       </c>
       <c r="D346">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E346" t="s">
         <v>34</v>
@@ -9585,7 +9585,7 @@
         <v>49</v>
       </c>
       <c r="D347">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E347" t="s">
         <v>35</v>
@@ -9672,10 +9672,10 @@
         <v>38</v>
       </c>
       <c r="G350">
-        <v>0.0197</v>
+        <v>0.0189</v>
       </c>
       <c r="H350">
-        <v>0.0151</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -9698,10 +9698,10 @@
         <v>39</v>
       </c>
       <c r="G351">
-        <v>0.015</v>
+        <v>0.0138</v>
       </c>
       <c r="H351">
-        <v>0.0125</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -9724,10 +9724,10 @@
         <v>40</v>
       </c>
       <c r="G352">
-        <v>0.0171</v>
+        <v>0.0152</v>
       </c>
       <c r="H352">
-        <v>0.0151</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -9750,7 +9750,7 @@
         <v>41</v>
       </c>
       <c r="G353">
-        <v>0.0207</v>
+        <v>0.0208</v>
       </c>
       <c r="H353">
         <v>0.0168</v>
@@ -9776,10 +9776,10 @@
         <v>42</v>
       </c>
       <c r="G354">
-        <v>0.026</v>
+        <v>0.0241</v>
       </c>
       <c r="H354">
-        <v>0.021</v>
+        <v>0.0194</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -9802,10 +9802,10 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>0.0269</v>
+        <v>0.0263</v>
       </c>
       <c r="H355">
-        <v>0.0201</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -9819,7 +9819,7 @@
         <v>50</v>
       </c>
       <c r="D356">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E356" t="s">
         <v>14</v>
@@ -9828,10 +9828,10 @@
         <v>44</v>
       </c>
       <c r="G356">
-        <v>0.0643</v>
+        <v>0.0354</v>
       </c>
       <c r="H356">
-        <v>0.0536</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9845,7 +9845,7 @@
         <v>50</v>
       </c>
       <c r="D357">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E357" t="s">
         <v>15</v>
@@ -9854,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="G357">
-        <v>0.0543</v>
+        <v>0.0331</v>
       </c>
       <c r="H357">
-        <v>0.0464</v>
+        <v>0.0266</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
-        <v>0.0179</v>
+        <v>0.0173</v>
       </c>
       <c r="H358">
-        <v>0.0144</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9906,10 +9906,10 @@
         <v>47</v>
       </c>
       <c r="G359">
-        <v>0.0617</v>
+        <v>0.0345</v>
       </c>
       <c r="H359">
-        <v>0.0482</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -9932,10 +9932,10 @@
         <v>48</v>
       </c>
       <c r="G360">
-        <v>0.2029</v>
+        <v>0.2511</v>
       </c>
       <c r="H360">
-        <v>0.1649</v>
+        <v>0.2151</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.202</v>
+        <v>0.2006</v>
       </c>
       <c r="H361">
-        <v>0.1716</v>
+        <v>0.1631</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -9984,10 +9984,10 @@
         <v>51</v>
       </c>
       <c r="G362">
-        <v>0.2372</v>
+        <v>0.21</v>
       </c>
       <c r="H362">
-        <v>0.1991</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -10010,10 +10010,10 @@
         <v>52</v>
       </c>
       <c r="G363">
-        <v>0.5383</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="H363">
-        <v>0.5001</v>
+        <v>0.4669</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -10209,7 +10209,7 @@
         <v>50</v>
       </c>
       <c r="D371">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E371" t="s">
         <v>30</v>
@@ -10235,7 +10235,7 @@
         <v>50</v>
       </c>
       <c r="D372">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E372" t="s">
         <v>31</v>
@@ -10313,7 +10313,7 @@
         <v>50</v>
       </c>
       <c r="D375">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E375" t="s">
         <v>34</v>
@@ -10339,7 +10339,7 @@
         <v>50</v>
       </c>
       <c r="D376">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E376" t="s">
         <v>35</v>
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.0395</v>
+        <v>0.0235</v>
       </c>
       <c r="H379">
-        <v>0.034</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10452,10 +10452,10 @@
         <v>39</v>
       </c>
       <c r="G380">
-        <v>0.0287</v>
+        <v>0.019</v>
       </c>
       <c r="H380">
-        <v>0.0214</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -10478,10 +10478,10 @@
         <v>40</v>
       </c>
       <c r="G381">
-        <v>0.0368</v>
+        <v>0.0259</v>
       </c>
       <c r="H381">
-        <v>0.0287</v>
+        <v>0.0203</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -10504,10 +10504,10 @@
         <v>41</v>
       </c>
       <c r="G382">
-        <v>0.0343</v>
+        <v>0.0346</v>
       </c>
       <c r="H382">
-        <v>0.0296</v>
+        <v>0.0309</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.08210000000000001</v>
+        <v>0.0555</v>
       </c>
       <c r="H383">
-        <v>0.0673</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.0709</v>
+        <v>0.0566</v>
       </c>
       <c r="H384">
-        <v>0.0573</v>
+        <v>0.0456</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10573,7 +10573,7 @@
         <v>51</v>
       </c>
       <c r="D385">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E385" t="s">
         <v>14</v>
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.1918</v>
+        <v>0.1176</v>
       </c>
       <c r="H385">
-        <v>0.1556</v>
+        <v>0.0945</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10599,7 +10599,7 @@
         <v>51</v>
       </c>
       <c r="D386">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E386" t="s">
         <v>15</v>
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.1598</v>
+        <v>0.1293</v>
       </c>
       <c r="H386">
-        <v>0.1233</v>
+        <v>0.1069</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10634,10 +10634,10 @@
         <v>46</v>
       </c>
       <c r="G387">
-        <v>0.0558</v>
+        <v>0.0397</v>
       </c>
       <c r="H387">
-        <v>0.0455</v>
+        <v>0.0322</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -10660,10 +10660,10 @@
         <v>47</v>
       </c>
       <c r="G388">
-        <v>0.1685</v>
+        <v>0.1002</v>
       </c>
       <c r="H388">
-        <v>0.1307</v>
+        <v>0.0828</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -10686,10 +10686,10 @@
         <v>48</v>
       </c>
       <c r="G389">
-        <v>0.4506</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="H389">
-        <v>0.3948</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -10712,10 +10712,10 @@
         <v>49</v>
       </c>
       <c r="G390">
-        <v>0.4811</v>
+        <v>0.501</v>
       </c>
       <c r="H390">
-        <v>0.4518</v>
+        <v>0.4636</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -10738,10 +10738,10 @@
         <v>50</v>
       </c>
       <c r="G391">
-        <v>0.8008999999999999</v>
+        <v>0.8337</v>
       </c>
       <c r="H391">
-        <v>0.7628</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -10764,10 +10764,10 @@
         <v>52</v>
       </c>
       <c r="G392">
-        <v>0.8313</v>
+        <v>0.7915</v>
       </c>
       <c r="H392">
-        <v>0.7979000000000001</v>
+        <v>0.7614</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -10963,7 +10963,7 @@
         <v>51</v>
       </c>
       <c r="D400">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E400" t="s">
         <v>30</v>
@@ -10989,7 +10989,7 @@
         <v>51</v>
       </c>
       <c r="D401">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E401" t="s">
         <v>31</v>
@@ -11067,7 +11067,7 @@
         <v>51</v>
       </c>
       <c r="D404">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E404" t="s">
         <v>34</v>
@@ -11093,7 +11093,7 @@
         <v>51</v>
       </c>
       <c r="D405">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E405" t="s">
         <v>35</v>
@@ -11180,10 +11180,10 @@
         <v>38</v>
       </c>
       <c r="G408">
-        <v>0.0271</v>
+        <v>0.0191</v>
       </c>
       <c r="H408">
-        <v>0.0209</v>
+        <v>0.0146</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11206,10 +11206,10 @@
         <v>39</v>
       </c>
       <c r="G409">
-        <v>0.0141</v>
+        <v>0.0148</v>
       </c>
       <c r="H409">
-        <v>0.0108</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -11232,10 +11232,10 @@
         <v>40</v>
       </c>
       <c r="G410">
-        <v>0.0154</v>
+        <v>0.0165</v>
       </c>
       <c r="H410">
-        <v>0.0119</v>
+        <v>0.0125</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -11261,7 +11261,7 @@
         <v>0.0175</v>
       </c>
       <c r="H411">
-        <v>0.0137</v>
+        <v>0.0139</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -11284,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="G412">
-        <v>0.0355</v>
+        <v>0.0247</v>
       </c>
       <c r="H412">
-        <v>0.0269</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11310,10 +11310,10 @@
         <v>43</v>
       </c>
       <c r="G413">
-        <v>0.0275</v>
+        <v>0.022</v>
       </c>
       <c r="H413">
-        <v>0.0216</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -11327,7 +11327,7 @@
         <v>52</v>
       </c>
       <c r="D414">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E414" t="s">
         <v>14</v>
@@ -11336,10 +11336,10 @@
         <v>44</v>
       </c>
       <c r="G414">
-        <v>0.0648</v>
+        <v>0.0378</v>
       </c>
       <c r="H414">
-        <v>0.0518</v>
+        <v>0.0309</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -11353,7 +11353,7 @@
         <v>52</v>
       </c>
       <c r="D415">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E415" t="s">
         <v>15</v>
@@ -11362,10 +11362,10 @@
         <v>45</v>
       </c>
       <c r="G415">
-        <v>0.0429</v>
+        <v>0.0513</v>
       </c>
       <c r="H415">
-        <v>0.0334</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -11388,10 +11388,10 @@
         <v>46</v>
       </c>
       <c r="G416">
-        <v>0.0257</v>
+        <v>0.0182</v>
       </c>
       <c r="H416">
-        <v>0.0197</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -11414,10 +11414,10 @@
         <v>47</v>
       </c>
       <c r="G417">
-        <v>0.064</v>
+        <v>0.0374</v>
       </c>
       <c r="H417">
-        <v>0.0531</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -11440,10 +11440,10 @@
         <v>48</v>
       </c>
       <c r="G418">
-        <v>0.1654</v>
+        <v>0.2843</v>
       </c>
       <c r="H418">
-        <v>0.1299</v>
+        <v>0.2452</v>
       </c>
     </row>
     <row r="419" spans="1:8">
@@ -11466,10 +11466,10 @@
         <v>49</v>
       </c>
       <c r="G419">
-        <v>0.1865</v>
+        <v>0.2149</v>
       </c>
       <c r="H419">
-        <v>0.1539</v>
+        <v>0.1805</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -11492,10 +11492,10 @@
         <v>50</v>
       </c>
       <c r="G420">
-        <v>0.4999</v>
+        <v>0.5331</v>
       </c>
       <c r="H420">
-        <v>0.4617</v>
+        <v>0.4874</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -11518,10 +11518,10 @@
         <v>51</v>
       </c>
       <c r="G421">
-        <v>0.2021</v>
+        <v>0.2386</v>
       </c>
       <c r="H421">
-        <v>0.1687</v>
+        <v>0.2085</v>
       </c>
     </row>
     <row r="422" spans="1:8">
@@ -11717,7 +11717,7 @@
         <v>52</v>
       </c>
       <c r="D429">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E429" t="s">
         <v>30</v>
@@ -11743,7 +11743,7 @@
         <v>52</v>
       </c>
       <c r="D430">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E430" t="s">
         <v>31</v>
@@ -11821,7 +11821,7 @@
         <v>52</v>
       </c>
       <c r="D433">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E433" t="s">
         <v>34</v>
@@ -11847,7 +11847,7 @@
         <v>52</v>
       </c>
       <c r="D434">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E434" t="s">
         <v>35</v>
@@ -12081,7 +12081,7 @@
         <v>53</v>
       </c>
       <c r="D443">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E443" t="s">
         <v>14</v>
@@ -12107,7 +12107,7 @@
         <v>53</v>
       </c>
       <c r="D444">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E444" t="s">
         <v>15</v>
@@ -12471,7 +12471,7 @@
         <v>53</v>
       </c>
       <c r="D458">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E458" t="s">
         <v>30</v>
@@ -12497,7 +12497,7 @@
         <v>53</v>
       </c>
       <c r="D459">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E459" t="s">
         <v>31</v>
@@ -12575,7 +12575,7 @@
         <v>53</v>
       </c>
       <c r="D462">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E462" t="s">
         <v>34</v>
@@ -12601,7 +12601,7 @@
         <v>53</v>
       </c>
       <c r="D463">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E463" t="s">
         <v>35</v>
@@ -12835,7 +12835,7 @@
         <v>54</v>
       </c>
       <c r="D472">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E472" t="s">
         <v>14</v>
@@ -12861,7 +12861,7 @@
         <v>54</v>
       </c>
       <c r="D473">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E473" t="s">
         <v>15</v>
@@ -13225,7 +13225,7 @@
         <v>54</v>
       </c>
       <c r="D487">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E487" t="s">
         <v>30</v>
@@ -13251,7 +13251,7 @@
         <v>54</v>
       </c>
       <c r="D488">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E488" t="s">
         <v>31</v>
@@ -13329,7 +13329,7 @@
         <v>54</v>
       </c>
       <c r="D491">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E491" t="s">
         <v>34</v>
@@ -13355,7 +13355,7 @@
         <v>54</v>
       </c>
       <c r="D492">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E492" t="s">
         <v>35</v>
@@ -13589,7 +13589,7 @@
         <v>55</v>
       </c>
       <c r="D501">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E501" t="s">
         <v>14</v>
@@ -13615,7 +13615,7 @@
         <v>55</v>
       </c>
       <c r="D502">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E502" t="s">
         <v>15</v>
@@ -13979,7 +13979,7 @@
         <v>55</v>
       </c>
       <c r="D516">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E516" t="s">
         <v>30</v>
@@ -14005,7 +14005,7 @@
         <v>55</v>
       </c>
       <c r="D517">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E517" t="s">
         <v>31</v>
@@ -14083,7 +14083,7 @@
         <v>55</v>
       </c>
       <c r="D520">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E520" t="s">
         <v>34</v>
@@ -14109,7 +14109,7 @@
         <v>55</v>
       </c>
       <c r="D521">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E521" t="s">
         <v>35</v>
@@ -14343,7 +14343,7 @@
         <v>56</v>
       </c>
       <c r="D530">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E530" t="s">
         <v>14</v>
@@ -14369,7 +14369,7 @@
         <v>56</v>
       </c>
       <c r="D531">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E531" t="s">
         <v>15</v>
@@ -14733,7 +14733,7 @@
         <v>56</v>
       </c>
       <c r="D545">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E545" t="s">
         <v>30</v>
@@ -14759,7 +14759,7 @@
         <v>56</v>
       </c>
       <c r="D546">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E546" t="s">
         <v>31</v>
@@ -14837,7 +14837,7 @@
         <v>56</v>
       </c>
       <c r="D549">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E549" t="s">
         <v>34</v>
@@ -14863,7 +14863,7 @@
         <v>56</v>
       </c>
       <c r="D550">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E550" t="s">
         <v>35</v>
@@ -15097,7 +15097,7 @@
         <v>57</v>
       </c>
       <c r="D559">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E559" t="s">
         <v>14</v>
@@ -15123,7 +15123,7 @@
         <v>57</v>
       </c>
       <c r="D560">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E560" t="s">
         <v>15</v>
@@ -15487,7 +15487,7 @@
         <v>57</v>
       </c>
       <c r="D574">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E574" t="s">
         <v>30</v>
@@ -15513,7 +15513,7 @@
         <v>57</v>
       </c>
       <c r="D575">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E575" t="s">
         <v>31</v>
@@ -15591,7 +15591,7 @@
         <v>57</v>
       </c>
       <c r="D578">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E578" t="s">
         <v>34</v>
@@ -15617,7 +15617,7 @@
         <v>57</v>
       </c>
       <c r="D579">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E579" t="s">
         <v>35</v>
@@ -15851,7 +15851,7 @@
         <v>58</v>
       </c>
       <c r="D588">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E588" t="s">
         <v>14</v>
@@ -15877,7 +15877,7 @@
         <v>58</v>
       </c>
       <c r="D589">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E589" t="s">
         <v>15</v>
@@ -16241,7 +16241,7 @@
         <v>58</v>
       </c>
       <c r="D603">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E603" t="s">
         <v>30</v>
@@ -16267,7 +16267,7 @@
         <v>58</v>
       </c>
       <c r="D604">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E604" t="s">
         <v>31</v>
@@ -16345,7 +16345,7 @@
         <v>58</v>
       </c>
       <c r="D607">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E607" t="s">
         <v>34</v>
@@ -16371,7 +16371,7 @@
         <v>58</v>
       </c>
       <c r="D608">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E608" t="s">
         <v>35</v>
@@ -16605,7 +16605,7 @@
         <v>59</v>
       </c>
       <c r="D617">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E617" t="s">
         <v>14</v>
@@ -16631,7 +16631,7 @@
         <v>59</v>
       </c>
       <c r="D618">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E618" t="s">
         <v>15</v>
@@ -16995,7 +16995,7 @@
         <v>59</v>
       </c>
       <c r="D632">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E632" t="s">
         <v>30</v>
@@ -17021,7 +17021,7 @@
         <v>59</v>
       </c>
       <c r="D633">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E633" t="s">
         <v>31</v>
@@ -17099,7 +17099,7 @@
         <v>59</v>
       </c>
       <c r="D636">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E636" t="s">
         <v>34</v>
@@ -17125,7 +17125,7 @@
         <v>59</v>
       </c>
       <c r="D637">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E637" t="s">
         <v>35</v>
@@ -17194,7 +17194,7 @@
     </row>
     <row r="640" spans="1:8">
       <c r="A640">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B640" t="s">
         <v>30</v>
@@ -17220,7 +17220,7 @@
     </row>
     <row r="641" spans="1:8">
       <c r="A641">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B641" t="s">
         <v>30</v>
@@ -17246,7 +17246,7 @@
     </row>
     <row r="642" spans="1:8">
       <c r="A642">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B642" t="s">
         <v>30</v>
@@ -17272,7 +17272,7 @@
     </row>
     <row r="643" spans="1:8">
       <c r="A643">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B643" t="s">
         <v>30</v>
@@ -17298,7 +17298,7 @@
     </row>
     <row r="644" spans="1:8">
       <c r="A644">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B644" t="s">
         <v>30</v>
@@ -17324,7 +17324,7 @@
     </row>
     <row r="645" spans="1:8">
       <c r="A645">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B645" t="s">
         <v>30</v>
@@ -17350,7 +17350,7 @@
     </row>
     <row r="646" spans="1:8">
       <c r="A646">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B646" t="s">
         <v>30</v>
@@ -17359,7 +17359,7 @@
         <v>60</v>
       </c>
       <c r="D646">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E646" t="s">
         <v>14</v>
@@ -17376,7 +17376,7 @@
     </row>
     <row r="647" spans="1:8">
       <c r="A647">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B647" t="s">
         <v>30</v>
@@ -17385,7 +17385,7 @@
         <v>60</v>
       </c>
       <c r="D647">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E647" t="s">
         <v>15</v>
@@ -17402,7 +17402,7 @@
     </row>
     <row r="648" spans="1:8">
       <c r="A648">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B648" t="s">
         <v>30</v>
@@ -17428,7 +17428,7 @@
     </row>
     <row r="649" spans="1:8">
       <c r="A649">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B649" t="s">
         <v>30</v>
@@ -17454,7 +17454,7 @@
     </row>
     <row r="650" spans="1:8">
       <c r="A650">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B650" t="s">
         <v>30</v>
@@ -17480,7 +17480,7 @@
     </row>
     <row r="651" spans="1:8">
       <c r="A651">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B651" t="s">
         <v>30</v>
@@ -17506,7 +17506,7 @@
     </row>
     <row r="652" spans="1:8">
       <c r="A652">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B652" t="s">
         <v>30</v>
@@ -17532,7 +17532,7 @@
     </row>
     <row r="653" spans="1:8">
       <c r="A653">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B653" t="s">
         <v>30</v>
@@ -17558,7 +17558,7 @@
     </row>
     <row r="654" spans="1:8">
       <c r="A654">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B654" t="s">
         <v>30</v>
@@ -17584,7 +17584,7 @@
     </row>
     <row r="655" spans="1:8">
       <c r="A655">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B655" t="s">
         <v>30</v>
@@ -17610,7 +17610,7 @@
     </row>
     <row r="656" spans="1:8">
       <c r="A656">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B656" t="s">
         <v>30</v>
@@ -17636,7 +17636,7 @@
     </row>
     <row r="657" spans="1:8">
       <c r="A657">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B657" t="s">
         <v>30</v>
@@ -17662,7 +17662,7 @@
     </row>
     <row r="658" spans="1:8">
       <c r="A658">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B658" t="s">
         <v>30</v>
@@ -17688,7 +17688,7 @@
     </row>
     <row r="659" spans="1:8">
       <c r="A659">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B659" t="s">
         <v>30</v>
@@ -17714,7 +17714,7 @@
     </row>
     <row r="660" spans="1:8">
       <c r="A660">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B660" t="s">
         <v>30</v>
@@ -17740,7 +17740,7 @@
     </row>
     <row r="661" spans="1:8">
       <c r="A661">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B661" t="s">
         <v>30</v>
@@ -17766,7 +17766,7 @@
     </row>
     <row r="662" spans="1:8">
       <c r="A662">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B662" t="s">
         <v>30</v>
@@ -17775,7 +17775,7 @@
         <v>60</v>
       </c>
       <c r="D662">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E662" t="s">
         <v>31</v>
@@ -17792,7 +17792,7 @@
     </row>
     <row r="663" spans="1:8">
       <c r="A663">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B663" t="s">
         <v>30</v>
@@ -17818,7 +17818,7 @@
     </row>
     <row r="664" spans="1:8">
       <c r="A664">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B664" t="s">
         <v>30</v>
@@ -17844,7 +17844,7 @@
     </row>
     <row r="665" spans="1:8">
       <c r="A665">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B665" t="s">
         <v>30</v>
@@ -17853,7 +17853,7 @@
         <v>60</v>
       </c>
       <c r="D665">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E665" t="s">
         <v>34</v>
@@ -17870,7 +17870,7 @@
     </row>
     <row r="666" spans="1:8">
       <c r="A666">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B666" t="s">
         <v>30</v>
@@ -17879,7 +17879,7 @@
         <v>60</v>
       </c>
       <c r="D666">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E666" t="s">
         <v>35</v>
@@ -17896,7 +17896,7 @@
     </row>
     <row r="667" spans="1:8">
       <c r="A667">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B667" t="s">
         <v>30</v>
@@ -17922,7 +17922,7 @@
     </row>
     <row r="668" spans="1:8">
       <c r="A668">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="B668" t="s">
         <v>30</v>
@@ -17948,7 +17948,7 @@
     </row>
     <row r="669" spans="1:8">
       <c r="A669">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B669" t="s">
         <v>31</v>
@@ -17974,7 +17974,7 @@
     </row>
     <row r="670" spans="1:8">
       <c r="A670">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B670" t="s">
         <v>31</v>
@@ -18000,7 +18000,7 @@
     </row>
     <row r="671" spans="1:8">
       <c r="A671">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B671" t="s">
         <v>31</v>
@@ -18026,7 +18026,7 @@
     </row>
     <row r="672" spans="1:8">
       <c r="A672">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B672" t="s">
         <v>31</v>
@@ -18052,7 +18052,7 @@
     </row>
     <row r="673" spans="1:8">
       <c r="A673">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B673" t="s">
         <v>31</v>
@@ -18078,7 +18078,7 @@
     </row>
     <row r="674" spans="1:8">
       <c r="A674">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B674" t="s">
         <v>31</v>
@@ -18104,7 +18104,7 @@
     </row>
     <row r="675" spans="1:8">
       <c r="A675">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B675" t="s">
         <v>31</v>
@@ -18113,7 +18113,7 @@
         <v>61</v>
       </c>
       <c r="D675">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E675" t="s">
         <v>14</v>
@@ -18130,7 +18130,7 @@
     </row>
     <row r="676" spans="1:8">
       <c r="A676">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B676" t="s">
         <v>31</v>
@@ -18139,7 +18139,7 @@
         <v>61</v>
       </c>
       <c r="D676">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E676" t="s">
         <v>15</v>
@@ -18156,7 +18156,7 @@
     </row>
     <row r="677" spans="1:8">
       <c r="A677">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B677" t="s">
         <v>31</v>
@@ -18182,7 +18182,7 @@
     </row>
     <row r="678" spans="1:8">
       <c r="A678">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B678" t="s">
         <v>31</v>
@@ -18208,7 +18208,7 @@
     </row>
     <row r="679" spans="1:8">
       <c r="A679">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B679" t="s">
         <v>31</v>
@@ -18234,7 +18234,7 @@
     </row>
     <row r="680" spans="1:8">
       <c r="A680">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B680" t="s">
         <v>31</v>
@@ -18260,7 +18260,7 @@
     </row>
     <row r="681" spans="1:8">
       <c r="A681">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B681" t="s">
         <v>31</v>
@@ -18286,7 +18286,7 @@
     </row>
     <row r="682" spans="1:8">
       <c r="A682">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B682" t="s">
         <v>31</v>
@@ -18312,7 +18312,7 @@
     </row>
     <row r="683" spans="1:8">
       <c r="A683">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B683" t="s">
         <v>31</v>
@@ -18338,7 +18338,7 @@
     </row>
     <row r="684" spans="1:8">
       <c r="A684">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B684" t="s">
         <v>31</v>
@@ -18364,7 +18364,7 @@
     </row>
     <row r="685" spans="1:8">
       <c r="A685">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B685" t="s">
         <v>31</v>
@@ -18390,7 +18390,7 @@
     </row>
     <row r="686" spans="1:8">
       <c r="A686">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B686" t="s">
         <v>31</v>
@@ -18416,7 +18416,7 @@
     </row>
     <row r="687" spans="1:8">
       <c r="A687">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B687" t="s">
         <v>31</v>
@@ -18442,7 +18442,7 @@
     </row>
     <row r="688" spans="1:8">
       <c r="A688">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B688" t="s">
         <v>31</v>
@@ -18468,7 +18468,7 @@
     </row>
     <row r="689" spans="1:8">
       <c r="A689">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B689" t="s">
         <v>31</v>
@@ -18494,7 +18494,7 @@
     </row>
     <row r="690" spans="1:8">
       <c r="A690">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B690" t="s">
         <v>31</v>
@@ -18520,7 +18520,7 @@
     </row>
     <row r="691" spans="1:8">
       <c r="A691">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B691" t="s">
         <v>31</v>
@@ -18529,7 +18529,7 @@
         <v>61</v>
       </c>
       <c r="D691">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E691" t="s">
         <v>30</v>
@@ -18546,7 +18546,7 @@
     </row>
     <row r="692" spans="1:8">
       <c r="A692">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B692" t="s">
         <v>31</v>
@@ -18572,7 +18572,7 @@
     </row>
     <row r="693" spans="1:8">
       <c r="A693">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B693" t="s">
         <v>31</v>
@@ -18598,7 +18598,7 @@
     </row>
     <row r="694" spans="1:8">
       <c r="A694">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B694" t="s">
         <v>31</v>
@@ -18607,7 +18607,7 @@
         <v>61</v>
       </c>
       <c r="D694">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E694" t="s">
         <v>34</v>
@@ -18624,7 +18624,7 @@
     </row>
     <row r="695" spans="1:8">
       <c r="A695">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B695" t="s">
         <v>31</v>
@@ -18633,7 +18633,7 @@
         <v>61</v>
       </c>
       <c r="D695">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E695" t="s">
         <v>35</v>
@@ -18650,7 +18650,7 @@
     </row>
     <row r="696" spans="1:8">
       <c r="A696">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B696" t="s">
         <v>31</v>
@@ -18676,7 +18676,7 @@
     </row>
     <row r="697" spans="1:8">
       <c r="A697">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="B697" t="s">
         <v>31</v>
@@ -18867,7 +18867,7 @@
         <v>62</v>
       </c>
       <c r="D704">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E704" t="s">
         <v>14</v>
@@ -18893,7 +18893,7 @@
         <v>62</v>
       </c>
       <c r="D705">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E705" t="s">
         <v>15</v>
@@ -19283,7 +19283,7 @@
         <v>62</v>
       </c>
       <c r="D720">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E720" t="s">
         <v>30</v>
@@ -19309,7 +19309,7 @@
         <v>62</v>
       </c>
       <c r="D721">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E721" t="s">
         <v>31</v>
@@ -19361,7 +19361,7 @@
         <v>62</v>
       </c>
       <c r="D723">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E723" t="s">
         <v>34</v>
@@ -19387,7 +19387,7 @@
         <v>62</v>
       </c>
       <c r="D724">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E724" t="s">
         <v>35</v>
@@ -19621,7 +19621,7 @@
         <v>63</v>
       </c>
       <c r="D733">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E733" t="s">
         <v>14</v>
@@ -19647,7 +19647,7 @@
         <v>63</v>
       </c>
       <c r="D734">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E734" t="s">
         <v>15</v>
@@ -20037,7 +20037,7 @@
         <v>63</v>
       </c>
       <c r="D749">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E749" t="s">
         <v>30</v>
@@ -20063,7 +20063,7 @@
         <v>63</v>
       </c>
       <c r="D750">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E750" t="s">
         <v>31</v>
@@ -20115,7 +20115,7 @@
         <v>63</v>
       </c>
       <c r="D752">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E752" t="s">
         <v>34</v>
@@ -20141,7 +20141,7 @@
         <v>63</v>
       </c>
       <c r="D753">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E753" t="s">
         <v>35</v>
@@ -20210,7 +20210,7 @@
     </row>
     <row r="756" spans="1:8">
       <c r="A756">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B756" t="s">
         <v>34</v>
@@ -20236,7 +20236,7 @@
     </row>
     <row r="757" spans="1:8">
       <c r="A757">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B757" t="s">
         <v>34</v>
@@ -20262,7 +20262,7 @@
     </row>
     <row r="758" spans="1:8">
       <c r="A758">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B758" t="s">
         <v>34</v>
@@ -20288,7 +20288,7 @@
     </row>
     <row r="759" spans="1:8">
       <c r="A759">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B759" t="s">
         <v>34</v>
@@ -20314,7 +20314,7 @@
     </row>
     <row r="760" spans="1:8">
       <c r="A760">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B760" t="s">
         <v>34</v>
@@ -20340,7 +20340,7 @@
     </row>
     <row r="761" spans="1:8">
       <c r="A761">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B761" t="s">
         <v>34</v>
@@ -20366,7 +20366,7 @@
     </row>
     <row r="762" spans="1:8">
       <c r="A762">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B762" t="s">
         <v>34</v>
@@ -20375,7 +20375,7 @@
         <v>64</v>
       </c>
       <c r="D762">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E762" t="s">
         <v>14</v>
@@ -20392,7 +20392,7 @@
     </row>
     <row r="763" spans="1:8">
       <c r="A763">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B763" t="s">
         <v>34</v>
@@ -20401,7 +20401,7 @@
         <v>64</v>
       </c>
       <c r="D763">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E763" t="s">
         <v>15</v>
@@ -20418,7 +20418,7 @@
     </row>
     <row r="764" spans="1:8">
       <c r="A764">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B764" t="s">
         <v>34</v>
@@ -20444,7 +20444,7 @@
     </row>
     <row r="765" spans="1:8">
       <c r="A765">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B765" t="s">
         <v>34</v>
@@ -20470,7 +20470,7 @@
     </row>
     <row r="766" spans="1:8">
       <c r="A766">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B766" t="s">
         <v>34</v>
@@ -20496,7 +20496,7 @@
     </row>
     <row r="767" spans="1:8">
       <c r="A767">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B767" t="s">
         <v>34</v>
@@ -20522,7 +20522,7 @@
     </row>
     <row r="768" spans="1:8">
       <c r="A768">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B768" t="s">
         <v>34</v>
@@ -20548,7 +20548,7 @@
     </row>
     <row r="769" spans="1:8">
       <c r="A769">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B769" t="s">
         <v>34</v>
@@ -20574,7 +20574,7 @@
     </row>
     <row r="770" spans="1:8">
       <c r="A770">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B770" t="s">
         <v>34</v>
@@ -20600,7 +20600,7 @@
     </row>
     <row r="771" spans="1:8">
       <c r="A771">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B771" t="s">
         <v>34</v>
@@ -20626,7 +20626,7 @@
     </row>
     <row r="772" spans="1:8">
       <c r="A772">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B772" t="s">
         <v>34</v>
@@ -20652,7 +20652,7 @@
     </row>
     <row r="773" spans="1:8">
       <c r="A773">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B773" t="s">
         <v>34</v>
@@ -20678,7 +20678,7 @@
     </row>
     <row r="774" spans="1:8">
       <c r="A774">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B774" t="s">
         <v>34</v>
@@ -20704,7 +20704,7 @@
     </row>
     <row r="775" spans="1:8">
       <c r="A775">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B775" t="s">
         <v>34</v>
@@ -20730,7 +20730,7 @@
     </row>
     <row r="776" spans="1:8">
       <c r="A776">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B776" t="s">
         <v>34</v>
@@ -20756,7 +20756,7 @@
     </row>
     <row r="777" spans="1:8">
       <c r="A777">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B777" t="s">
         <v>34</v>
@@ -20782,7 +20782,7 @@
     </row>
     <row r="778" spans="1:8">
       <c r="A778">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B778" t="s">
         <v>34</v>
@@ -20791,7 +20791,7 @@
         <v>64</v>
       </c>
       <c r="D778">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E778" t="s">
         <v>30</v>
@@ -20808,7 +20808,7 @@
     </row>
     <row r="779" spans="1:8">
       <c r="A779">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B779" t="s">
         <v>34</v>
@@ -20817,7 +20817,7 @@
         <v>64</v>
       </c>
       <c r="D779">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E779" t="s">
         <v>31</v>
@@ -20834,7 +20834,7 @@
     </row>
     <row r="780" spans="1:8">
       <c r="A780">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B780" t="s">
         <v>34</v>
@@ -20860,7 +20860,7 @@
     </row>
     <row r="781" spans="1:8">
       <c r="A781">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B781" t="s">
         <v>34</v>
@@ -20886,7 +20886,7 @@
     </row>
     <row r="782" spans="1:8">
       <c r="A782">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B782" t="s">
         <v>34</v>
@@ -20895,7 +20895,7 @@
         <v>64</v>
       </c>
       <c r="D782">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E782" t="s">
         <v>35</v>
@@ -20912,7 +20912,7 @@
     </row>
     <row r="783" spans="1:8">
       <c r="A783">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B783" t="s">
         <v>34</v>
@@ -20938,7 +20938,7 @@
     </row>
     <row r="784" spans="1:8">
       <c r="A784">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="B784" t="s">
         <v>34</v>
@@ -20964,7 +20964,7 @@
     </row>
     <row r="785" spans="1:8">
       <c r="A785">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B785" t="s">
         <v>35</v>
@@ -20990,7 +20990,7 @@
     </row>
     <row r="786" spans="1:8">
       <c r="A786">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B786" t="s">
         <v>35</v>
@@ -21016,7 +21016,7 @@
     </row>
     <row r="787" spans="1:8">
       <c r="A787">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B787" t="s">
         <v>35</v>
@@ -21042,7 +21042,7 @@
     </row>
     <row r="788" spans="1:8">
       <c r="A788">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B788" t="s">
         <v>35</v>
@@ -21068,7 +21068,7 @@
     </row>
     <row r="789" spans="1:8">
       <c r="A789">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B789" t="s">
         <v>35</v>
@@ -21094,7 +21094,7 @@
     </row>
     <row r="790" spans="1:8">
       <c r="A790">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B790" t="s">
         <v>35</v>
@@ -21120,7 +21120,7 @@
     </row>
     <row r="791" spans="1:8">
       <c r="A791">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B791" t="s">
         <v>35</v>
@@ -21129,7 +21129,7 @@
         <v>65</v>
       </c>
       <c r="D791">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E791" t="s">
         <v>14</v>
@@ -21146,7 +21146,7 @@
     </row>
     <row r="792" spans="1:8">
       <c r="A792">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B792" t="s">
         <v>35</v>
@@ -21155,7 +21155,7 @@
         <v>65</v>
       </c>
       <c r="D792">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E792" t="s">
         <v>15</v>
@@ -21172,7 +21172,7 @@
     </row>
     <row r="793" spans="1:8">
       <c r="A793">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B793" t="s">
         <v>35</v>
@@ -21198,7 +21198,7 @@
     </row>
     <row r="794" spans="1:8">
       <c r="A794">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B794" t="s">
         <v>35</v>
@@ -21224,7 +21224,7 @@
     </row>
     <row r="795" spans="1:8">
       <c r="A795">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B795" t="s">
         <v>35</v>
@@ -21250,7 +21250,7 @@
     </row>
     <row r="796" spans="1:8">
       <c r="A796">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B796" t="s">
         <v>35</v>
@@ -21276,7 +21276,7 @@
     </row>
     <row r="797" spans="1:8">
       <c r="A797">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B797" t="s">
         <v>35</v>
@@ -21302,7 +21302,7 @@
     </row>
     <row r="798" spans="1:8">
       <c r="A798">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B798" t="s">
         <v>35</v>
@@ -21328,7 +21328,7 @@
     </row>
     <row r="799" spans="1:8">
       <c r="A799">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B799" t="s">
         <v>35</v>
@@ -21354,7 +21354,7 @@
     </row>
     <row r="800" spans="1:8">
       <c r="A800">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B800" t="s">
         <v>35</v>
@@ -21380,7 +21380,7 @@
     </row>
     <row r="801" spans="1:8">
       <c r="A801">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B801" t="s">
         <v>35</v>
@@ -21406,7 +21406,7 @@
     </row>
     <row r="802" spans="1:8">
       <c r="A802">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B802" t="s">
         <v>35</v>
@@ -21432,7 +21432,7 @@
     </row>
     <row r="803" spans="1:8">
       <c r="A803">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B803" t="s">
         <v>35</v>
@@ -21458,7 +21458,7 @@
     </row>
     <row r="804" spans="1:8">
       <c r="A804">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B804" t="s">
         <v>35</v>
@@ -21484,7 +21484,7 @@
     </row>
     <row r="805" spans="1:8">
       <c r="A805">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B805" t="s">
         <v>35</v>
@@ -21510,7 +21510,7 @@
     </row>
     <row r="806" spans="1:8">
       <c r="A806">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B806" t="s">
         <v>35</v>
@@ -21536,7 +21536,7 @@
     </row>
     <row r="807" spans="1:8">
       <c r="A807">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B807" t="s">
         <v>35</v>
@@ -21545,7 +21545,7 @@
         <v>65</v>
       </c>
       <c r="D807">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E807" t="s">
         <v>30</v>
@@ -21562,7 +21562,7 @@
     </row>
     <row r="808" spans="1:8">
       <c r="A808">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B808" t="s">
         <v>35</v>
@@ -21571,7 +21571,7 @@
         <v>65</v>
       </c>
       <c r="D808">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E808" t="s">
         <v>31</v>
@@ -21588,7 +21588,7 @@
     </row>
     <row r="809" spans="1:8">
       <c r="A809">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B809" t="s">
         <v>35</v>
@@ -21614,7 +21614,7 @@
     </row>
     <row r="810" spans="1:8">
       <c r="A810">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B810" t="s">
         <v>35</v>
@@ -21640,7 +21640,7 @@
     </row>
     <row r="811" spans="1:8">
       <c r="A811">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B811" t="s">
         <v>35</v>
@@ -21649,7 +21649,7 @@
         <v>65</v>
       </c>
       <c r="D811">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E811" t="s">
         <v>34</v>
@@ -21666,7 +21666,7 @@
     </row>
     <row r="812" spans="1:8">
       <c r="A812">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B812" t="s">
         <v>35</v>
@@ -21692,7 +21692,7 @@
     </row>
     <row r="813" spans="1:8">
       <c r="A813">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="B813" t="s">
         <v>35</v>
@@ -21883,7 +21883,7 @@
         <v>66</v>
       </c>
       <c r="D820">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E820" t="s">
         <v>14</v>
@@ -21909,7 +21909,7 @@
         <v>66</v>
       </c>
       <c r="D821">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E821" t="s">
         <v>15</v>
@@ -22299,7 +22299,7 @@
         <v>66</v>
       </c>
       <c r="D836">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E836" t="s">
         <v>30</v>
@@ -22325,7 +22325,7 @@
         <v>66</v>
       </c>
       <c r="D837">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E837" t="s">
         <v>31</v>
@@ -22403,7 +22403,7 @@
         <v>66</v>
       </c>
       <c r="D840">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E840" t="s">
         <v>34</v>
@@ -22429,7 +22429,7 @@
         <v>66</v>
       </c>
       <c r="D841">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E841" t="s">
         <v>35</v>
@@ -22637,7 +22637,7 @@
         <v>67</v>
       </c>
       <c r="D849">
-        <v>1610612753</v>
+        <v>1610612755</v>
       </c>
       <c r="E849" t="s">
         <v>14</v>
@@ -22663,7 +22663,7 @@
         <v>67</v>
       </c>
       <c r="D850">
-        <v>1610612755</v>
+        <v>1610612753</v>
       </c>
       <c r="E850" t="s">
         <v>15</v>
@@ -23053,7 +23053,7 @@
         <v>67</v>
       </c>
       <c r="D865">
-        <v>1610612746</v>
+        <v>1610612757</v>
       </c>
       <c r="E865" t="s">
         <v>30</v>
@@ -23079,7 +23079,7 @@
         <v>67</v>
       </c>
       <c r="D866">
-        <v>1610612757</v>
+        <v>1610612746</v>
       </c>
       <c r="E866" t="s">
         <v>31</v>
@@ -23157,7 +23157,7 @@
         <v>67</v>
       </c>
       <c r="D869">
-        <v>1610612763</v>
+        <v>1610612742</v>
       </c>
       <c r="E869" t="s">
         <v>34</v>
@@ -23183,7 +23183,7 @@
         <v>67</v>
       </c>
       <c r="D870">
-        <v>1610612742</v>
+        <v>1610612763</v>
       </c>
       <c r="E870" t="s">
         <v>35</v>

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4274</v>
+        <v>0.4836</v>
       </c>
       <c r="H2">
-        <v>0.3739</v>
+        <v>0.4344</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,10 +650,10 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>0.5937</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="H3">
-        <v>0.5558999999999999</v>
+        <v>0.5251</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5325</v>
+        <v>0.5726</v>
       </c>
       <c r="H4">
-        <v>0.4917</v>
+        <v>0.5386</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -702,10 +702,10 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>0.7864</v>
+        <v>0.7849</v>
       </c>
       <c r="H5">
-        <v>0.7712</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -728,10 +728,10 @@
         <v>43</v>
       </c>
       <c r="G6">
-        <v>0.8082</v>
+        <v>0.7712</v>
       </c>
       <c r="H6">
-        <v>0.7793</v>
+        <v>0.7369</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -754,10 +754,10 @@
         <v>44</v>
       </c>
       <c r="G7">
-        <v>0.9006999999999999</v>
+        <v>0.872</v>
       </c>
       <c r="H7">
-        <v>0.8804999999999999</v>
+        <v>0.8494</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.927</v>
+        <v>0.8983</v>
       </c>
       <c r="H8">
-        <v>0.9061</v>
+        <v>0.8749</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -806,10 +806,10 @@
         <v>46</v>
       </c>
       <c r="G9">
-        <v>0.7487</v>
+        <v>0.7683</v>
       </c>
       <c r="H9">
-        <v>0.712</v>
+        <v>0.7409</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -832,10 +832,10 @@
         <v>47</v>
       </c>
       <c r="G10">
-        <v>0.8745000000000001</v>
+        <v>0.8845</v>
       </c>
       <c r="H10">
-        <v>0.8475</v>
+        <v>0.8537</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -858,10 +858,10 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>0.9798</v>
+        <v>0.9751</v>
       </c>
       <c r="H11">
-        <v>0.9752</v>
+        <v>0.969</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -884,10 +884,10 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>0.9814000000000001</v>
+        <v>0.9756</v>
       </c>
       <c r="H12">
-        <v>0.976</v>
+        <v>0.9684</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.9797</v>
+        <v>0.971</v>
       </c>
       <c r="H14">
-        <v>0.9765</v>
+        <v>0.9658</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -962,10 +962,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>0.9854000000000001</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="H15">
-        <v>0.9809</v>
+        <v>0.9755</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.6261</v>
+        <v>0.5656</v>
       </c>
       <c r="H31">
-        <v>0.5726</v>
+        <v>0.5164</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="G32">
-        <v>0.6951000000000001</v>
+        <v>0.6411</v>
       </c>
       <c r="H32">
-        <v>0.6698</v>
+        <v>0.6181</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1430,7 +1430,7 @@
         <v>41</v>
       </c>
       <c r="G33">
-        <v>0.6828</v>
+        <v>0.6842</v>
       </c>
       <c r="H33">
         <v>0.6556999999999999</v>
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.8879</v>
+        <v>0.8717</v>
       </c>
       <c r="H34">
-        <v>0.8594000000000001</v>
+        <v>0.8391999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1482,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="G35">
-        <v>0.8995</v>
+        <v>0.8646</v>
       </c>
       <c r="H35">
-        <v>0.8692</v>
+        <v>0.8312</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1508,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="G36">
-        <v>0.9500999999999999</v>
+        <v>0.913</v>
       </c>
       <c r="H36">
-        <v>0.9366</v>
+        <v>0.8939</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.9589</v>
+        <v>0.9263</v>
       </c>
       <c r="H37">
-        <v>0.9471000000000001</v>
+        <v>0.907</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.8406</v>
+        <v>0.8515</v>
       </c>
       <c r="H38">
-        <v>0.8110000000000001</v>
+        <v>0.8204</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1586,10 +1586,10 @@
         <v>47</v>
       </c>
       <c r="G39">
-        <v>0.9337</v>
+        <v>0.9255</v>
       </c>
       <c r="H39">
-        <v>0.9113</v>
+        <v>0.8994</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1638,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="G41">
-        <v>0.9881</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="H41">
-        <v>0.9838</v>
+        <v>0.9829</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1690,10 +1690,10 @@
         <v>51</v>
       </c>
       <c r="G43">
-        <v>0.9856</v>
+        <v>0.9852</v>
       </c>
       <c r="H43">
-        <v>0.981</v>
+        <v>0.9804</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -2132,10 +2132,10 @@
         <v>38</v>
       </c>
       <c r="G60">
-        <v>0.4441</v>
+        <v>0.4749</v>
       </c>
       <c r="H60">
-        <v>0.4063</v>
+        <v>0.4299</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2158,10 +2158,10 @@
         <v>39</v>
       </c>
       <c r="G61">
-        <v>0.3302</v>
+        <v>0.3819</v>
       </c>
       <c r="H61">
-        <v>0.3049</v>
+        <v>0.3589</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2184,10 +2184,10 @@
         <v>41</v>
       </c>
       <c r="G62">
-        <v>0.5058</v>
+        <v>0.5746</v>
       </c>
       <c r="H62">
-        <v>0.4677</v>
+        <v>0.5453</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2236,10 +2236,10 @@
         <v>43</v>
       </c>
       <c r="G64">
-        <v>0.7732</v>
+        <v>0.7559</v>
       </c>
       <c r="H64">
-        <v>0.7217</v>
+        <v>0.7059</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2262,10 +2262,10 @@
         <v>44</v>
       </c>
       <c r="G65">
-        <v>0.8932</v>
+        <v>0.868</v>
       </c>
       <c r="H65">
-        <v>0.8738</v>
+        <v>0.8467</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.9086</v>
+        <v>0.8844</v>
       </c>
       <c r="H66">
-        <v>0.884</v>
+        <v>0.8559</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2314,10 +2314,10 @@
         <v>46</v>
       </c>
       <c r="G67">
-        <v>0.6823</v>
+        <v>0.7441</v>
       </c>
       <c r="H67">
-        <v>0.6371</v>
+        <v>0.7068</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2340,10 +2340,10 @@
         <v>47</v>
       </c>
       <c r="G68">
-        <v>0.8704</v>
+        <v>0.887</v>
       </c>
       <c r="H68">
-        <v>0.8302</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2366,10 +2366,10 @@
         <v>48</v>
       </c>
       <c r="G69">
-        <v>0.9818</v>
+        <v>0.9813</v>
       </c>
       <c r="H69">
-        <v>0.9768</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="G70">
-        <v>0.9863</v>
+        <v>0.982</v>
       </c>
       <c r="H70">
-        <v>0.9818</v>
+        <v>0.9761</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2444,10 +2444,10 @@
         <v>51</v>
       </c>
       <c r="G72">
-        <v>0.9797</v>
+        <v>0.9751</v>
       </c>
       <c r="H72">
-        <v>0.9741</v>
+        <v>0.9677</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2470,10 +2470,10 @@
         <v>52</v>
       </c>
       <c r="G73">
-        <v>0.9875</v>
+        <v>0.9867</v>
       </c>
       <c r="H73">
-        <v>0.9835</v>
+        <v>0.9826</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.5083</v>
+        <v>0.4614</v>
       </c>
       <c r="H89">
-        <v>0.4675</v>
+        <v>0.4274</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2915,7 +2915,7 @@
         <v>0.3443</v>
       </c>
       <c r="H90">
-        <v>0.3172</v>
+        <v>0.3158</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2938,10 +2938,10 @@
         <v>40</v>
       </c>
       <c r="G91">
-        <v>0.5323</v>
+        <v>0.4547</v>
       </c>
       <c r="H91">
-        <v>0.4942</v>
+        <v>0.4254</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.8031</v>
+        <v>0.7736</v>
       </c>
       <c r="H92">
-        <v>0.7664</v>
+        <v>0.7295</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2990,10 +2990,10 @@
         <v>43</v>
       </c>
       <c r="G93">
-        <v>0.8207</v>
+        <v>0.7683</v>
       </c>
       <c r="H93">
-        <v>0.7829</v>
+        <v>0.7272</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3016,10 +3016,10 @@
         <v>44</v>
       </c>
       <c r="G94">
-        <v>0.889</v>
+        <v>0.8542</v>
       </c>
       <c r="H94">
-        <v>0.8676</v>
+        <v>0.8217</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.9024</v>
+        <v>0.8721</v>
       </c>
       <c r="H95">
-        <v>0.8764</v>
+        <v>0.8391</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3068,10 +3068,10 @@
         <v>46</v>
       </c>
       <c r="G96">
-        <v>0.6977</v>
+        <v>0.7278</v>
       </c>
       <c r="H96">
-        <v>0.6609</v>
+        <v>0.6902</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3094,10 +3094,10 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.886</v>
+        <v>0.8746</v>
       </c>
       <c r="H97">
-        <v>0.8525</v>
+        <v>0.8389</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3146,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="G99">
-        <v>0.9792</v>
+        <v>0.9785</v>
       </c>
       <c r="H99">
-        <v>0.9752999999999999</v>
+        <v>0.9745</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3640,10 +3640,10 @@
         <v>38</v>
       </c>
       <c r="G118">
-        <v>0.2288</v>
+        <v>0.23</v>
       </c>
       <c r="H118">
-        <v>0.2136</v>
+        <v>0.2151</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3666,10 +3666,10 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.1406</v>
+        <v>0.1608</v>
       </c>
       <c r="H119">
-        <v>0.1121</v>
+        <v>0.1283</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3718,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2336</v>
+        <v>0.2705</v>
       </c>
       <c r="H121">
-        <v>0.1969</v>
+        <v>0.2264</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3744,10 +3744,10 @@
         <v>43</v>
       </c>
       <c r="G122">
-        <v>0.4891</v>
+        <v>0.4611</v>
       </c>
       <c r="H122">
-        <v>0.4544</v>
+        <v>0.4272</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.6917</v>
+        <v>0.6353</v>
       </c>
       <c r="H123">
-        <v>0.6713</v>
+        <v>0.6032999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -3796,10 +3796,10 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.7459</v>
+        <v>0.6761</v>
       </c>
       <c r="H124">
-        <v>0.7054</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3822,10 +3822,10 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.455</v>
+        <v>0.5112</v>
       </c>
       <c r="H125">
-        <v>0.4118</v>
+        <v>0.4738</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3848,10 +3848,10 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.6748</v>
+        <v>0.6825</v>
       </c>
       <c r="H126">
-        <v>0.6284999999999999</v>
+        <v>0.6355</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3874,10 +3874,10 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.9606</v>
+        <v>0.9467</v>
       </c>
       <c r="H127">
-        <v>0.946</v>
+        <v>0.9277</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3900,10 +3900,10 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9589</v>
+        <v>0.9434</v>
       </c>
       <c r="H128">
-        <v>0.9403</v>
+        <v>0.9199000000000001</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3926,10 +3926,10 @@
         <v>50</v>
       </c>
       <c r="G129">
-        <v>0.9806</v>
+        <v>0.9801</v>
       </c>
       <c r="H129">
-        <v>0.9759</v>
+        <v>0.9751</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -3952,10 +3952,10 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9554</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="H130">
-        <v>0.9445</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3978,10 +3978,10 @@
         <v>52</v>
       </c>
       <c r="G131">
-        <v>0.9811</v>
+        <v>0.9734</v>
       </c>
       <c r="H131">
-        <v>0.9752999999999999</v>
+        <v>0.9649</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4394,10 +4394,10 @@
         <v>38</v>
       </c>
       <c r="G147">
-        <v>0.2207</v>
+        <v>0.2631</v>
       </c>
       <c r="H147">
-        <v>0.1918</v>
+        <v>0.2288</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4420,10 +4420,10 @@
         <v>39</v>
       </c>
       <c r="G148">
-        <v>0.1308</v>
+        <v>0.1688</v>
       </c>
       <c r="H148">
-        <v>0.1005</v>
+        <v>0.1354</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4446,10 +4446,10 @@
         <v>40</v>
       </c>
       <c r="G149">
-        <v>0.2783</v>
+        <v>0.2941</v>
       </c>
       <c r="H149">
-        <v>0.2268</v>
+        <v>0.2441</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4472,10 +4472,10 @@
         <v>41</v>
       </c>
       <c r="G150">
-        <v>0.2171</v>
+        <v>0.2728</v>
       </c>
       <c r="H150">
-        <v>0.1793</v>
+        <v>0.2317</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4498,10 +4498,10 @@
         <v>42</v>
       </c>
       <c r="G151">
-        <v>0.5456</v>
+        <v>0.5728</v>
       </c>
       <c r="H151">
-        <v>0.5109</v>
+        <v>0.5389</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4524,10 +4524,10 @@
         <v>44</v>
       </c>
       <c r="G152">
-        <v>0.6984</v>
+        <v>0.6636</v>
       </c>
       <c r="H152">
-        <v>0.6777</v>
+        <v>0.6258</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4550,10 +4550,10 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.7249</v>
+        <v>0.7306</v>
       </c>
       <c r="H153">
-        <v>0.6774</v>
+        <v>0.6905</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4576,10 +4576,10 @@
         <v>46</v>
       </c>
       <c r="G154">
-        <v>0.4563</v>
+        <v>0.5433</v>
       </c>
       <c r="H154">
-        <v>0.4238</v>
+        <v>0.504</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4602,10 +4602,10 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>0.6725</v>
+        <v>0.7155</v>
       </c>
       <c r="H155">
-        <v>0.6354</v>
+        <v>0.6715</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4628,10 +4628,10 @@
         <v>48</v>
       </c>
       <c r="G156">
-        <v>0.9594</v>
+        <v>0.951</v>
       </c>
       <c r="H156">
-        <v>0.9434</v>
+        <v>0.9308999999999999</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4654,10 +4654,10 @@
         <v>49</v>
       </c>
       <c r="G157">
-        <v>0.9578</v>
+        <v>0.9522</v>
       </c>
       <c r="H157">
-        <v>0.9437</v>
+        <v>0.9355</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4706,10 +4706,10 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9544</v>
+        <v>0.9458</v>
       </c>
       <c r="H159">
-        <v>0.9434</v>
+        <v>0.9326</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4732,10 +4732,10 @@
         <v>52</v>
       </c>
       <c r="G160">
-        <v>0.9828</v>
+        <v>0.9784</v>
       </c>
       <c r="H160">
-        <v>0.978</v>
+        <v>0.9724</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5148,10 +5148,10 @@
         <v>38</v>
       </c>
       <c r="G176">
-        <v>0.1195</v>
+        <v>0.1506</v>
       </c>
       <c r="H176">
-        <v>0.0993</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5174,10 +5174,10 @@
         <v>39</v>
       </c>
       <c r="G177">
-        <v>0.0634</v>
+        <v>0.1061</v>
       </c>
       <c r="H177">
-        <v>0.0499</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5200,10 +5200,10 @@
         <v>40</v>
       </c>
       <c r="G178">
-        <v>0.1262</v>
+        <v>0.1533</v>
       </c>
       <c r="H178">
-        <v>0.1068</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5226,10 +5226,10 @@
         <v>41</v>
       </c>
       <c r="G179">
-        <v>0.1324</v>
+        <v>0.1783</v>
       </c>
       <c r="H179">
-        <v>0.111</v>
+        <v>0.1458</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5252,10 +5252,10 @@
         <v>42</v>
       </c>
       <c r="G180">
-        <v>0.3287</v>
+        <v>0.3967</v>
       </c>
       <c r="H180">
-        <v>0.3083</v>
+        <v>0.3647</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5278,10 +5278,10 @@
         <v>43</v>
       </c>
       <c r="G181">
-        <v>0.3223</v>
+        <v>0.3742</v>
       </c>
       <c r="H181">
-        <v>0.3016</v>
+        <v>0.3364</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5304,10 +5304,10 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.5443</v>
+        <v>0.5327</v>
       </c>
       <c r="H182">
-        <v>0.4948</v>
+        <v>0.5028</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5330,10 +5330,10 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.2444</v>
+        <v>0.3893</v>
       </c>
       <c r="H183">
-        <v>0.2074</v>
+        <v>0.3422</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5356,10 +5356,10 @@
         <v>47</v>
       </c>
       <c r="G184">
-        <v>0.4789</v>
+        <v>0.5457</v>
       </c>
       <c r="H184">
-        <v>0.4236</v>
+        <v>0.4968</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5382,10 +5382,10 @@
         <v>48</v>
       </c>
       <c r="G185">
-        <v>0.9111</v>
+        <v>0.9019</v>
       </c>
       <c r="H185">
-        <v>0.8863</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5408,10 +5408,10 @@
         <v>49</v>
       </c>
       <c r="G186">
-        <v>0.8988</v>
+        <v>0.9074</v>
       </c>
       <c r="H186">
-        <v>0.874</v>
+        <v>0.8779</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5434,10 +5434,10 @@
         <v>50</v>
       </c>
       <c r="G187">
-        <v>0.9719</v>
+        <v>0.9687</v>
       </c>
       <c r="H187">
-        <v>0.9646</v>
+        <v>0.9603</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5460,10 +5460,10 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.9055</v>
+        <v>0.9013</v>
       </c>
       <c r="H188">
-        <v>0.8824</v>
+        <v>0.8757</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5486,10 +5486,10 @@
         <v>52</v>
       </c>
       <c r="G189">
-        <v>0.9691</v>
+        <v>0.9659</v>
       </c>
       <c r="H189">
-        <v>0.9622000000000001</v>
+        <v>0.9576</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -5902,10 +5902,10 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.0939</v>
+        <v>0.1251</v>
       </c>
       <c r="H205">
-        <v>0.073</v>
+        <v>0.1017</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5928,10 +5928,10 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.0529</v>
+        <v>0.093</v>
       </c>
       <c r="H206">
-        <v>0.0411</v>
+        <v>0.0737</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -5954,10 +5954,10 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.116</v>
+        <v>0.1441</v>
       </c>
       <c r="H207">
-        <v>0.0914</v>
+        <v>0.1156</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5980,10 +5980,10 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.1236</v>
+        <v>0.1609</v>
       </c>
       <c r="H208">
-        <v>0.09760000000000001</v>
+        <v>0.1279</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6006,10 +6006,10 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.2946</v>
+        <v>0.365</v>
       </c>
       <c r="H209">
-        <v>0.2541</v>
+        <v>0.3239</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6032,10 +6032,10 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.3226</v>
+        <v>0.3095</v>
       </c>
       <c r="H210">
-        <v>0.2751</v>
+        <v>0.2694</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6058,10 +6058,10 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.5052</v>
+        <v>0.4972</v>
       </c>
       <c r="H211">
-        <v>0.4557</v>
+        <v>0.4673</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -6084,10 +6084,10 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.239</v>
+        <v>0.3154</v>
       </c>
       <c r="H212">
-        <v>0.2024</v>
+        <v>0.2698</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -6110,10 +6110,10 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.4469</v>
+        <v>0.522</v>
       </c>
       <c r="H213">
-        <v>0.4072</v>
+        <v>0.4845</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -6136,10 +6136,10 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.915</v>
+        <v>0.8911</v>
       </c>
       <c r="H214">
-        <v>0.8887</v>
+        <v>0.8623</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -6162,10 +6162,10 @@
         <v>49</v>
       </c>
       <c r="G215">
-        <v>0.8947000000000001</v>
+        <v>0.8784</v>
       </c>
       <c r="H215">
-        <v>0.8715000000000001</v>
+        <v>0.8485</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -6188,10 +6188,10 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>0.9734</v>
+        <v>0.9633</v>
       </c>
       <c r="H216">
-        <v>0.9669</v>
+        <v>0.9528</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -6214,10 +6214,10 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.8931</v>
+        <v>0.8841</v>
       </c>
       <c r="H217">
-        <v>0.8707</v>
+        <v>0.8574000000000001</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -6240,10 +6240,10 @@
         <v>52</v>
       </c>
       <c r="G218">
-        <v>0.9585</v>
+        <v>0.9526</v>
       </c>
       <c r="H218">
-        <v>0.9487</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -6656,10 +6656,10 @@
         <v>38</v>
       </c>
       <c r="G234">
-        <v>0.288</v>
+        <v>0.2591</v>
       </c>
       <c r="H234">
-        <v>0.2513</v>
+        <v>0.2317</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -6682,10 +6682,10 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.189</v>
+        <v>0.1796</v>
       </c>
       <c r="H235">
-        <v>0.1594</v>
+        <v>0.1485</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -6708,10 +6708,10 @@
         <v>40</v>
       </c>
       <c r="G236">
-        <v>0.3629</v>
+        <v>0.2932</v>
       </c>
       <c r="H236">
-        <v>0.3177</v>
+        <v>0.2559</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -6734,10 +6734,10 @@
         <v>41</v>
       </c>
       <c r="G237">
-        <v>0.3391</v>
+        <v>0.3098</v>
       </c>
       <c r="H237">
-        <v>0.3023</v>
+        <v>0.2722</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -6760,10 +6760,10 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.5881999999999999</v>
+        <v>0.5262</v>
       </c>
       <c r="H238">
-        <v>0.545</v>
+        <v>0.4888</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -6786,10 +6786,10 @@
         <v>43</v>
       </c>
       <c r="G239">
-        <v>0.5762</v>
+        <v>0.496</v>
       </c>
       <c r="H239">
-        <v>0.5437</v>
+        <v>0.4567</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -6812,10 +6812,10 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.7926</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="H240">
-        <v>0.7556</v>
+        <v>0.6107</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -6838,10 +6838,10 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.7976</v>
+        <v>0.7302</v>
       </c>
       <c r="H241">
-        <v>0.761</v>
+        <v>0.6846</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -6864,10 +6864,10 @@
         <v>47</v>
       </c>
       <c r="G242">
-        <v>0.7279</v>
+        <v>0.7027</v>
       </c>
       <c r="H242">
-        <v>0.6855</v>
+        <v>0.6623</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -6890,10 +6890,10 @@
         <v>48</v>
       </c>
       <c r="G243">
-        <v>0.9717</v>
+        <v>0.9519</v>
       </c>
       <c r="H243">
-        <v>0.963</v>
+        <v>0.9399</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -6916,10 +6916,10 @@
         <v>49</v>
       </c>
       <c r="G244">
-        <v>0.9649</v>
+        <v>0.9465</v>
       </c>
       <c r="H244">
-        <v>0.9517</v>
+        <v>0.9323</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -6942,10 +6942,10 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9865</v>
+        <v>0.9827</v>
       </c>
       <c r="H245">
-        <v>0.9827</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -6968,10 +6968,10 @@
         <v>51</v>
       </c>
       <c r="G246">
-        <v>0.9678</v>
+        <v>0.9312</v>
       </c>
       <c r="H246">
-        <v>0.9603</v>
+        <v>0.9163</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -6994,10 +6994,10 @@
         <v>52</v>
       </c>
       <c r="G247">
-        <v>0.9859</v>
+        <v>0.9758</v>
       </c>
       <c r="H247">
-        <v>0.9818</v>
+        <v>0.9692</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7410,10 +7410,10 @@
         <v>38</v>
       </c>
       <c r="G263">
-        <v>0.1525</v>
+        <v>0.1463</v>
       </c>
       <c r="H263">
-        <v>0.1255</v>
+        <v>0.1155</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -7436,10 +7436,10 @@
         <v>39</v>
       </c>
       <c r="G264">
-        <v>0.0887</v>
+        <v>0.1006</v>
       </c>
       <c r="H264">
-        <v>0.0663</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7462,10 +7462,10 @@
         <v>40</v>
       </c>
       <c r="G265">
-        <v>0.1698</v>
+        <v>0.149</v>
       </c>
       <c r="H265">
-        <v>0.1296</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7488,10 +7488,10 @@
         <v>41</v>
       </c>
       <c r="G266">
-        <v>0.1475</v>
+        <v>0.1611</v>
       </c>
       <c r="H266">
-        <v>0.114</v>
+        <v>0.1254</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3715</v>
+        <v>0.3645</v>
       </c>
       <c r="H267">
-        <v>0.3252</v>
+        <v>0.3175</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7540,10 +7540,10 @@
         <v>43</v>
       </c>
       <c r="G268">
-        <v>0.3646</v>
+        <v>0.3285</v>
       </c>
       <c r="H268">
-        <v>0.3275</v>
+        <v>0.2845</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -7566,10 +7566,10 @@
         <v>44</v>
       </c>
       <c r="G269">
-        <v>0.5764</v>
+        <v>0.5032</v>
       </c>
       <c r="H269">
-        <v>0.5211</v>
+        <v>0.4543</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.5928</v>
+        <v>0.5155</v>
       </c>
       <c r="H270">
-        <v>0.5531</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7618,10 +7618,10 @@
         <v>46</v>
       </c>
       <c r="G271">
-        <v>0.3145</v>
+        <v>0.3377</v>
       </c>
       <c r="H271">
-        <v>0.2721</v>
+        <v>0.2973</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -7644,10 +7644,10 @@
         <v>48</v>
       </c>
       <c r="G272">
-        <v>0.9352</v>
+        <v>0.9044</v>
       </c>
       <c r="H272">
-        <v>0.9121</v>
+        <v>0.8724</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7670,10 +7670,10 @@
         <v>49</v>
       </c>
       <c r="G273">
-        <v>0.9141</v>
+        <v>0.8843</v>
       </c>
       <c r="H273">
-        <v>0.8925</v>
+        <v>0.8583</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7696,10 +7696,10 @@
         <v>50</v>
       </c>
       <c r="G274">
-        <v>0.972</v>
+        <v>0.9631</v>
       </c>
       <c r="H274">
-        <v>0.9655</v>
+        <v>0.9533</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7722,10 +7722,10 @@
         <v>51</v>
       </c>
       <c r="G275">
-        <v>0.9172</v>
+        <v>0.8782</v>
       </c>
       <c r="H275">
-        <v>0.8998</v>
+        <v>0.8531</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -7748,10 +7748,10 @@
         <v>52</v>
       </c>
       <c r="G276">
-        <v>0.9697</v>
+        <v>0.9599</v>
       </c>
       <c r="H276">
-        <v>0.9626</v>
+        <v>0.9506</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -8164,10 +8164,10 @@
         <v>38</v>
       </c>
       <c r="G292">
-        <v>0.0248</v>
+        <v>0.031</v>
       </c>
       <c r="H292">
-        <v>0.0202</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8216,10 +8216,10 @@
         <v>40</v>
       </c>
       <c r="G294">
-        <v>0.0232</v>
+        <v>0.0239</v>
       </c>
       <c r="H294">
-        <v>0.0182</v>
+        <v>0.0187</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.054</v>
+        <v>0.0723</v>
       </c>
       <c r="H296">
-        <v>0.0394</v>
+        <v>0.0533</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8294,10 +8294,10 @@
         <v>43</v>
       </c>
       <c r="G297">
-        <v>0.0566</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H297">
-        <v>0.0406</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -8320,10 +8320,10 @@
         <v>44</v>
       </c>
       <c r="G298">
-        <v>0.1137</v>
+        <v>0.126</v>
       </c>
       <c r="H298">
-        <v>0.08890000000000001</v>
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.1113</v>
+        <v>0.1377</v>
       </c>
       <c r="H299">
-        <v>0.08500000000000001</v>
+        <v>0.1089</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8372,10 +8372,10 @@
         <v>46</v>
       </c>
       <c r="G300">
-        <v>0.037</v>
+        <v>0.0601</v>
       </c>
       <c r="H300">
-        <v>0.0283</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -8398,10 +8398,10 @@
         <v>47</v>
       </c>
       <c r="G301">
-        <v>0.08790000000000001</v>
+        <v>0.1276</v>
       </c>
       <c r="H301">
-        <v>0.0648</v>
+        <v>0.0956</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8424,10 +8424,10 @@
         <v>49</v>
       </c>
       <c r="G302">
-        <v>0.4346</v>
+        <v>0.4656</v>
       </c>
       <c r="H302">
-        <v>0.4027</v>
+        <v>0.4329</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -8450,10 +8450,10 @@
         <v>50</v>
       </c>
       <c r="G303">
-        <v>0.7849</v>
+        <v>0.7746</v>
       </c>
       <c r="H303">
-        <v>0.7489</v>
+        <v>0.7368</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -8476,10 +8476,10 @@
         <v>51</v>
       </c>
       <c r="G304">
-        <v>0.453</v>
+        <v>0.4702</v>
       </c>
       <c r="H304">
-        <v>0.4098</v>
+        <v>0.4311</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -8918,10 +8918,10 @@
         <v>38</v>
       </c>
       <c r="G321">
-        <v>0.024</v>
+        <v>0.0316</v>
       </c>
       <c r="H321">
-        <v>0.0186</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8944,10 +8944,10 @@
         <v>39</v>
       </c>
       <c r="G322">
-        <v>0.0162</v>
+        <v>0.0171</v>
       </c>
       <c r="H322">
-        <v>0.0119</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8970,10 +8970,10 @@
         <v>40</v>
       </c>
       <c r="G323">
-        <v>0.0182</v>
+        <v>0.0239</v>
       </c>
       <c r="H323">
-        <v>0.0137</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8996,10 +8996,10 @@
         <v>41</v>
       </c>
       <c r="G324">
-        <v>0.0247</v>
+        <v>0.0255</v>
       </c>
       <c r="H324">
-        <v>0.0208</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.0597</v>
+        <v>0.0801</v>
       </c>
       <c r="H325">
-        <v>0.0411</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9048,10 +9048,10 @@
         <v>43</v>
       </c>
       <c r="G326">
-        <v>0.0563</v>
+        <v>0.0645</v>
       </c>
       <c r="H326">
-        <v>0.0422</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -9074,10 +9074,10 @@
         <v>44</v>
       </c>
       <c r="G327">
-        <v>0.126</v>
+        <v>0.1221</v>
       </c>
       <c r="H327">
-        <v>0.1012</v>
+        <v>0.0926</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -9100,10 +9100,10 @@
         <v>45</v>
       </c>
       <c r="G328">
-        <v>0.1285</v>
+        <v>0.1515</v>
       </c>
       <c r="H328">
-        <v>0.1053</v>
+        <v>0.1216</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9126,10 +9126,10 @@
         <v>46</v>
       </c>
       <c r="G329">
-        <v>0.0483</v>
+        <v>0.0677</v>
       </c>
       <c r="H329">
-        <v>0.0351</v>
+        <v>0.0535</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9152,10 +9152,10 @@
         <v>47</v>
       </c>
       <c r="G330">
-        <v>0.1075</v>
+        <v>0.1417</v>
       </c>
       <c r="H330">
-        <v>0.0859</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9178,10 +9178,10 @@
         <v>48</v>
       </c>
       <c r="G331">
-        <v>0.5973000000000001</v>
+        <v>0.5671</v>
       </c>
       <c r="H331">
-        <v>0.5654</v>
+        <v>0.5344</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.8369</v>
+        <v>0.8102</v>
       </c>
       <c r="H332">
-        <v>0.7994</v>
+        <v>0.7674</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9230,10 +9230,10 @@
         <v>51</v>
       </c>
       <c r="G333">
-        <v>0.5364</v>
+        <v>0.5203</v>
       </c>
       <c r="H333">
-        <v>0.499</v>
+        <v>0.4869</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -9256,10 +9256,10 @@
         <v>52</v>
       </c>
       <c r="G334">
-        <v>0.8195</v>
+        <v>0.8051</v>
       </c>
       <c r="H334">
-        <v>0.7851</v>
+        <v>0.7725</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -9776,10 +9776,10 @@
         <v>42</v>
       </c>
       <c r="G354">
-        <v>0.0241</v>
+        <v>0.0249</v>
       </c>
       <c r="H354">
-        <v>0.0194</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -9828,10 +9828,10 @@
         <v>44</v>
       </c>
       <c r="G356">
-        <v>0.0354</v>
+        <v>0.0397</v>
       </c>
       <c r="H356">
-        <v>0.0281</v>
+        <v>0.0313</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9854,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="G357">
-        <v>0.0331</v>
+        <v>0.0472</v>
       </c>
       <c r="H357">
-        <v>0.0266</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
+        <v>0.022</v>
+      </c>
+      <c r="H358">
         <v>0.0173</v>
-      </c>
-      <c r="H358">
-        <v>0.0135</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9906,10 +9906,10 @@
         <v>47</v>
       </c>
       <c r="G359">
-        <v>0.0345</v>
+        <v>0.0467</v>
       </c>
       <c r="H359">
-        <v>0.028</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -9932,10 +9932,10 @@
         <v>48</v>
       </c>
       <c r="G360">
-        <v>0.2511</v>
+        <v>0.2632</v>
       </c>
       <c r="H360">
-        <v>0.2151</v>
+        <v>0.2254</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.2006</v>
+        <v>0.2326</v>
       </c>
       <c r="H361">
-        <v>0.1631</v>
+        <v>0.1898</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -9984,10 +9984,10 @@
         <v>51</v>
       </c>
       <c r="G362">
-        <v>0.21</v>
+        <v>0.2268</v>
       </c>
       <c r="H362">
-        <v>0.1663</v>
+        <v>0.179</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -10010,10 +10010,10 @@
         <v>52</v>
       </c>
       <c r="G363">
-        <v>0.5125999999999999</v>
+        <v>0.5486</v>
       </c>
       <c r="H363">
-        <v>0.4669</v>
+        <v>0.5042</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.0235</v>
+        <v>0.0342</v>
       </c>
       <c r="H379">
-        <v>0.0203</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10452,10 +10452,10 @@
         <v>39</v>
       </c>
       <c r="G380">
-        <v>0.019</v>
+        <v>0.0196</v>
       </c>
       <c r="H380">
-        <v>0.0144</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -10478,10 +10478,10 @@
         <v>40</v>
       </c>
       <c r="G381">
-        <v>0.0259</v>
+        <v>0.0323</v>
       </c>
       <c r="H381">
-        <v>0.0203</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.0555</v>
+        <v>0.0708</v>
       </c>
       <c r="H383">
-        <v>0.0446</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.0566</v>
+        <v>0.0674</v>
       </c>
       <c r="H384">
-        <v>0.0456</v>
+        <v>0.0542</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.1176</v>
+        <v>0.1243</v>
       </c>
       <c r="H385">
-        <v>0.0945</v>
+        <v>0.0987</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.1293</v>
+        <v>0.1426</v>
       </c>
       <c r="H386">
-        <v>0.1069</v>
+        <v>0.1159</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10634,10 +10634,10 @@
         <v>46</v>
       </c>
       <c r="G387">
-        <v>0.0397</v>
+        <v>0.0837</v>
       </c>
       <c r="H387">
-        <v>0.0322</v>
+        <v>0.0688</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -10660,10 +10660,10 @@
         <v>47</v>
       </c>
       <c r="G388">
-        <v>0.1002</v>
+        <v>0.1469</v>
       </c>
       <c r="H388">
-        <v>0.0828</v>
+        <v>0.1218</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -10686,10 +10686,10 @@
         <v>48</v>
       </c>
       <c r="G389">
-        <v>0.5901999999999999</v>
+        <v>0.5689</v>
       </c>
       <c r="H389">
-        <v>0.547</v>
+        <v>0.5298</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -10712,10 +10712,10 @@
         <v>49</v>
       </c>
       <c r="G390">
-        <v>0.501</v>
+        <v>0.5131</v>
       </c>
       <c r="H390">
-        <v>0.4636</v>
+        <v>0.4797</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -10738,10 +10738,10 @@
         <v>50</v>
       </c>
       <c r="G391">
-        <v>0.8337</v>
+        <v>0.821</v>
       </c>
       <c r="H391">
-        <v>0.79</v>
+        <v>0.7732</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -10764,10 +10764,10 @@
         <v>52</v>
       </c>
       <c r="G392">
-        <v>0.7915</v>
+        <v>0.7778</v>
       </c>
       <c r="H392">
-        <v>0.7614</v>
+        <v>0.7497</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -11180,10 +11180,10 @@
         <v>38</v>
       </c>
       <c r="G408">
-        <v>0.0191</v>
+        <v>0.0245</v>
       </c>
       <c r="H408">
-        <v>0.0146</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11232,10 +11232,10 @@
         <v>40</v>
       </c>
       <c r="G410">
-        <v>0.0165</v>
+        <v>0.0174</v>
       </c>
       <c r="H410">
-        <v>0.0125</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -11284,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="G412">
-        <v>0.0247</v>
+        <v>0.0351</v>
       </c>
       <c r="H412">
-        <v>0.0189</v>
+        <v>0.0266</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11310,10 +11310,10 @@
         <v>43</v>
       </c>
       <c r="G413">
-        <v>0.022</v>
+        <v>0.0276</v>
       </c>
       <c r="H413">
-        <v>0.0172</v>
+        <v>0.0216</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -11336,10 +11336,10 @@
         <v>44</v>
       </c>
       <c r="G414">
-        <v>0.0378</v>
+        <v>0.0424</v>
       </c>
       <c r="H414">
-        <v>0.0309</v>
+        <v>0.0341</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -11362,10 +11362,10 @@
         <v>45</v>
       </c>
       <c r="G415">
-        <v>0.0513</v>
+        <v>0.0585</v>
       </c>
       <c r="H415">
-        <v>0.0415</v>
+        <v>0.0474</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -11388,10 +11388,10 @@
         <v>46</v>
       </c>
       <c r="G416">
-        <v>0.0182</v>
+        <v>0.0308</v>
       </c>
       <c r="H416">
-        <v>0.0141</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -11414,10 +11414,10 @@
         <v>47</v>
       </c>
       <c r="G417">
-        <v>0.0374</v>
+        <v>0.0494</v>
       </c>
       <c r="H417">
-        <v>0.0303</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -11466,10 +11466,10 @@
         <v>49</v>
       </c>
       <c r="G419">
-        <v>0.2149</v>
+        <v>0.2275</v>
       </c>
       <c r="H419">
-        <v>0.1805</v>
+        <v>0.1949</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -11492,10 +11492,10 @@
         <v>50</v>
       </c>
       <c r="G420">
-        <v>0.5331</v>
+        <v>0.4958</v>
       </c>
       <c r="H420">
-        <v>0.4874</v>
+        <v>0.4514</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -11518,10 +11518,10 @@
         <v>51</v>
       </c>
       <c r="G421">
-        <v>0.2386</v>
+        <v>0.2503</v>
       </c>
       <c r="H421">
-        <v>0.2085</v>
+        <v>0.2222</v>
       </c>
     </row>
     <row r="422" spans="1:8">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4836</v>
+        <v>0.4685</v>
       </c>
       <c r="H2">
-        <v>0.4344</v>
+        <v>0.4232</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5726</v>
+        <v>0.5687</v>
       </c>
       <c r="H4">
-        <v>0.5386</v>
+        <v>0.5336</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -702,10 +702,10 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>0.7849</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="H5">
-        <v>0.77</v>
+        <v>0.7446</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -754,10 +754,10 @@
         <v>44</v>
       </c>
       <c r="G7">
-        <v>0.872</v>
+        <v>0.8709</v>
       </c>
       <c r="H7">
-        <v>0.8494</v>
+        <v>0.8482</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.8983</v>
+        <v>0.9023</v>
       </c>
       <c r="H8">
-        <v>0.8749</v>
+        <v>0.8797</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.971</v>
+        <v>0.9716</v>
       </c>
       <c r="H14">
-        <v>0.9658</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.5656</v>
+        <v>0.5768</v>
       </c>
       <c r="H31">
-        <v>0.5164</v>
+        <v>0.5315</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.8717</v>
+        <v>0.8581</v>
       </c>
       <c r="H34">
-        <v>0.8391999999999999</v>
+        <v>0.8255</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.9263</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="H37">
-        <v>0.907</v>
+        <v>0.9091</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.8515</v>
+        <v>0.8508</v>
       </c>
       <c r="H38">
-        <v>0.8204</v>
+        <v>0.8193</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -2210,10 +2210,10 @@
         <v>42</v>
       </c>
       <c r="G63">
-        <v>0.78</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="H63">
-        <v>0.7395</v>
+        <v>0.7324000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.8844</v>
+        <v>0.8879</v>
       </c>
       <c r="H66">
-        <v>0.8559</v>
+        <v>0.8606</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2314,10 +2314,10 @@
         <v>46</v>
       </c>
       <c r="G67">
-        <v>0.7441</v>
+        <v>0.7395</v>
       </c>
       <c r="H67">
-        <v>0.7068</v>
+        <v>0.7030999999999999</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.4614</v>
+        <v>0.4664</v>
       </c>
       <c r="H89">
-        <v>0.4274</v>
+        <v>0.4313</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.7736</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="H92">
-        <v>0.7295</v>
+        <v>0.7161</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.8721</v>
+        <v>0.8782</v>
       </c>
       <c r="H95">
-        <v>0.8391</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3071,7 +3071,7 @@
         <v>0.7278</v>
       </c>
       <c r="H96">
-        <v>0.6902</v>
+        <v>0.6903</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3094,7 +3094,7 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.8746</v>
+        <v>0.8748</v>
       </c>
       <c r="H97">
         <v>0.8389</v>
@@ -3640,10 +3640,10 @@
         <v>38</v>
       </c>
       <c r="G118">
-        <v>0.23</v>
+        <v>0.2554</v>
       </c>
       <c r="H118">
-        <v>0.2151</v>
+        <v>0.2344</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3666,10 +3666,10 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.1608</v>
+        <v>0.1745</v>
       </c>
       <c r="H119">
-        <v>0.1283</v>
+        <v>0.1419</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3692,10 +3692,10 @@
         <v>40</v>
       </c>
       <c r="G120">
-        <v>0.2605</v>
+        <v>0.2676</v>
       </c>
       <c r="H120">
-        <v>0.22</v>
+        <v>0.2293</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3718,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2705</v>
+        <v>0.2839</v>
       </c>
       <c r="H121">
-        <v>0.2264</v>
+        <v>0.2384</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3744,10 +3744,10 @@
         <v>43</v>
       </c>
       <c r="G122">
-        <v>0.4611</v>
+        <v>0.4842</v>
       </c>
       <c r="H122">
-        <v>0.4272</v>
+        <v>0.4468</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.6353</v>
+        <v>0.6523</v>
       </c>
       <c r="H123">
-        <v>0.6032999999999999</v>
+        <v>0.6254999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -3796,10 +3796,10 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.6761</v>
+        <v>0.7184</v>
       </c>
       <c r="H124">
-        <v>0.635</v>
+        <v>0.6806</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3822,10 +3822,10 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.5112</v>
+        <v>0.5191</v>
       </c>
       <c r="H125">
-        <v>0.4738</v>
+        <v>0.4844</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3848,10 +3848,10 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.6825</v>
+        <v>0.7036</v>
       </c>
       <c r="H126">
-        <v>0.6355</v>
+        <v>0.6599</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3874,10 +3874,10 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.9467</v>
+        <v>0.951</v>
       </c>
       <c r="H127">
-        <v>0.9277</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3900,10 +3900,10 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9434</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="H128">
-        <v>0.9199000000000001</v>
+        <v>0.9311</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3926,7 +3926,7 @@
         <v>50</v>
       </c>
       <c r="G129">
-        <v>0.9801</v>
+        <v>0.9805</v>
       </c>
       <c r="H129">
         <v>0.9751</v>
@@ -3952,10 +3952,10 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9419999999999999</v>
+        <v>0.9469</v>
       </c>
       <c r="H130">
-        <v>0.9292</v>
+        <v>0.9347</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3978,10 +3978,10 @@
         <v>52</v>
       </c>
       <c r="G131">
-        <v>0.9734</v>
+        <v>0.9764</v>
       </c>
       <c r="H131">
-        <v>0.9649</v>
+        <v>0.9687</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4498,10 +4498,10 @@
         <v>42</v>
       </c>
       <c r="G151">
-        <v>0.5728</v>
+        <v>0.5532</v>
       </c>
       <c r="H151">
-        <v>0.5389</v>
+        <v>0.5158</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4550,10 +4550,10 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.7306</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="H153">
-        <v>0.6905</v>
+        <v>0.6991000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4576,10 +4576,10 @@
         <v>46</v>
       </c>
       <c r="G154">
-        <v>0.5433</v>
+        <v>0.543</v>
       </c>
       <c r="H154">
-        <v>0.504</v>
+        <v>0.5038</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4706,10 +4706,10 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9458</v>
+        <v>0.9472</v>
       </c>
       <c r="H159">
-        <v>0.9326</v>
+        <v>0.9339</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -5148,10 +5148,10 @@
         <v>38</v>
       </c>
       <c r="G176">
-        <v>0.1506</v>
+        <v>0.1518</v>
       </c>
       <c r="H176">
-        <v>0.128</v>
+        <v>0.1291</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5252,10 +5252,10 @@
         <v>42</v>
       </c>
       <c r="G180">
-        <v>0.3967</v>
+        <v>0.3745</v>
       </c>
       <c r="H180">
-        <v>0.3647</v>
+        <v>0.3477</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5304,10 +5304,10 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.5327</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="H182">
-        <v>0.5028</v>
+        <v>0.5113</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5330,10 +5330,10 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.3893</v>
+        <v>0.3836</v>
       </c>
       <c r="H183">
-        <v>0.3422</v>
+        <v>0.3381</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5460,10 +5460,10 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.9013</v>
+        <v>0.9015</v>
       </c>
       <c r="H188">
-        <v>0.8757</v>
+        <v>0.8759</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5902,10 +5902,10 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.1251</v>
+        <v>0.1203</v>
       </c>
       <c r="H205">
-        <v>0.1017</v>
+        <v>0.0977</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5928,10 +5928,10 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.093</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="H206">
-        <v>0.0737</v>
+        <v>0.0721</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -5954,10 +5954,10 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.1441</v>
+        <v>0.1394</v>
       </c>
       <c r="H207">
-        <v>0.1156</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5980,10 +5980,10 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.1609</v>
+        <v>0.1538</v>
       </c>
       <c r="H208">
-        <v>0.1279</v>
+        <v>0.1218</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6006,10 +6006,10 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.365</v>
+        <v>0.3194</v>
       </c>
       <c r="H209">
-        <v>0.3239</v>
+        <v>0.2816</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6032,10 +6032,10 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.3095</v>
+        <v>0.3009</v>
       </c>
       <c r="H210">
-        <v>0.2694</v>
+        <v>0.2616</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6058,10 +6058,10 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.4972</v>
+        <v>0.4887</v>
       </c>
       <c r="H211">
-        <v>0.4673</v>
+        <v>0.4572</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -6084,10 +6084,10 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.3154</v>
+        <v>0.3078</v>
       </c>
       <c r="H212">
-        <v>0.2698</v>
+        <v>0.2637</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -6110,10 +6110,10 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.522</v>
+        <v>0.5048</v>
       </c>
       <c r="H213">
-        <v>0.4845</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -6136,10 +6136,10 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.8911</v>
+        <v>0.8877</v>
       </c>
       <c r="H214">
-        <v>0.8623</v>
+        <v>0.8584000000000001</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -6188,10 +6188,10 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>0.9633</v>
+        <v>0.9616</v>
       </c>
       <c r="H216">
-        <v>0.9528</v>
+        <v>0.9508</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -6214,10 +6214,10 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.8841</v>
+        <v>0.8808</v>
       </c>
       <c r="H217">
-        <v>0.8574000000000001</v>
+        <v>0.8537</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -6240,10 +6240,10 @@
         <v>52</v>
       </c>
       <c r="G218">
-        <v>0.9526</v>
+        <v>0.9508</v>
       </c>
       <c r="H218">
-        <v>0.9415</v>
+        <v>0.9387</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -6682,10 +6682,10 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.1796</v>
+        <v>0.1807</v>
       </c>
       <c r="H235">
-        <v>0.1485</v>
+        <v>0.1492</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -6708,10 +6708,10 @@
         <v>40</v>
       </c>
       <c r="G236">
-        <v>0.2932</v>
+        <v>0.2969</v>
       </c>
       <c r="H236">
-        <v>0.2559</v>
+        <v>0.2605</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -6734,7 +6734,7 @@
         <v>41</v>
       </c>
       <c r="G237">
-        <v>0.3098</v>
+        <v>0.3097</v>
       </c>
       <c r="H237">
         <v>0.2722</v>
@@ -6760,10 +6760,10 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.5262</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="H238">
-        <v>0.4888</v>
+        <v>0.4809</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -6786,10 +6786,10 @@
         <v>43</v>
       </c>
       <c r="G239">
-        <v>0.496</v>
+        <v>0.4962</v>
       </c>
       <c r="H239">
-        <v>0.4567</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -6812,10 +6812,10 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.6578000000000001</v>
+        <v>0.6619</v>
       </c>
       <c r="H240">
-        <v>0.6107</v>
+        <v>0.6163999999999999</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -6838,10 +6838,10 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.7302</v>
+        <v>0.7363</v>
       </c>
       <c r="H241">
-        <v>0.6846</v>
+        <v>0.6922</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -6942,10 +6942,10 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9827</v>
+        <v>0.9832</v>
       </c>
       <c r="H245">
-        <v>0.978</v>
+        <v>0.9785</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -6968,10 +6968,10 @@
         <v>51</v>
       </c>
       <c r="G246">
-        <v>0.9312</v>
+        <v>0.9336</v>
       </c>
       <c r="H246">
-        <v>0.9163</v>
+        <v>0.9195</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -6994,10 +6994,10 @@
         <v>52</v>
       </c>
       <c r="G247">
-        <v>0.9758</v>
+        <v>0.9769</v>
       </c>
       <c r="H247">
-        <v>0.9692</v>
+        <v>0.9705</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7491,7 +7491,7 @@
         <v>0.1611</v>
       </c>
       <c r="H266">
-        <v>0.1254</v>
+        <v>0.1252</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3645</v>
+        <v>0.3401</v>
       </c>
       <c r="H267">
-        <v>0.3175</v>
+        <v>0.2964</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.5155</v>
+        <v>0.531</v>
       </c>
       <c r="H270">
-        <v>0.478</v>
+        <v>0.4952</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.0723</v>
+        <v>0.067</v>
       </c>
       <c r="H296">
-        <v>0.0533</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.1377</v>
+        <v>0.1416</v>
       </c>
       <c r="H299">
-        <v>0.1089</v>
+        <v>0.1123</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.0801</v>
+        <v>0.0689</v>
       </c>
       <c r="H325">
-        <v>0.0566</v>
+        <v>0.0479</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.8102</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H332">
-        <v>0.7674</v>
+        <v>0.7673</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9779,7 +9779,7 @@
         <v>0.0249</v>
       </c>
       <c r="H354">
-        <v>0.0199</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -9854,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="G357">
-        <v>0.0472</v>
+        <v>0.0492</v>
       </c>
       <c r="H357">
-        <v>0.0367</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
-        <v>0.022</v>
+        <v>0.0215</v>
       </c>
       <c r="H358">
-        <v>0.0173</v>
+        <v>0.0168</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.2326</v>
+        <v>0.2327</v>
       </c>
       <c r="H361">
-        <v>0.1898</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.0342</v>
+        <v>0.0334</v>
       </c>
       <c r="H379">
-        <v>0.029</v>
+        <v>0.0284</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.0708</v>
+        <v>0.0653</v>
       </c>
       <c r="H383">
-        <v>0.058</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.0674</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="H384">
-        <v>0.0542</v>
+        <v>0.0528</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.1243</v>
+        <v>0.1241</v>
       </c>
       <c r="H385">
-        <v>0.0987</v>
+        <v>0.0985</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.1426</v>
+        <v>0.1463</v>
       </c>
       <c r="H386">
-        <v>0.1159</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10634,10 +10634,10 @@
         <v>46</v>
       </c>
       <c r="G387">
-        <v>0.0837</v>
+        <v>0.0805</v>
       </c>
       <c r="H387">
-        <v>0.0688</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -11284,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="G412">
-        <v>0.0351</v>
+        <v>0.0313</v>
       </c>
       <c r="H412">
-        <v>0.0266</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11362,10 +11362,10 @@
         <v>45</v>
       </c>
       <c r="G415">
-        <v>0.0585</v>
+        <v>0.0613</v>
       </c>
       <c r="H415">
-        <v>0.0474</v>
+        <v>0.0492</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -11388,10 +11388,10 @@
         <v>46</v>
       </c>
       <c r="G416">
-        <v>0.0308</v>
+        <v>0.0295</v>
       </c>
       <c r="H416">
-        <v>0.0242</v>
+        <v>0.0231</v>
       </c>
     </row>
     <row r="417" spans="1:8">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4685</v>
+        <v>0.4622</v>
       </c>
       <c r="H2">
-        <v>0.4232</v>
+        <v>0.4068</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,10 +650,10 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>0.5701000000000001</v>
+        <v>0.5643</v>
       </c>
       <c r="H3">
-        <v>0.5251</v>
+        <v>0.5137</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5687</v>
+        <v>0.5412</v>
       </c>
       <c r="H4">
-        <v>0.5336</v>
+        <v>0.5011</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -702,10 +702,10 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>0.7655999999999999</v>
+        <v>0.7397</v>
       </c>
       <c r="H5">
-        <v>0.7446</v>
+        <v>0.7299</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -728,10 +728,10 @@
         <v>43</v>
       </c>
       <c r="G6">
-        <v>0.7712</v>
+        <v>0.784</v>
       </c>
       <c r="H6">
-        <v>0.7369</v>
+        <v>0.755</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -754,10 +754,10 @@
         <v>44</v>
       </c>
       <c r="G7">
-        <v>0.8709</v>
+        <v>0.8701</v>
       </c>
       <c r="H7">
-        <v>0.8482</v>
+        <v>0.8473000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.9023</v>
+        <v>0.8641</v>
       </c>
       <c r="H8">
-        <v>0.8797</v>
+        <v>0.8381999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -806,10 +806,10 @@
         <v>46</v>
       </c>
       <c r="G9">
-        <v>0.7683</v>
+        <v>0.7375</v>
       </c>
       <c r="H9">
-        <v>0.7409</v>
+        <v>0.7074</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -832,10 +832,10 @@
         <v>47</v>
       </c>
       <c r="G10">
-        <v>0.8845</v>
+        <v>0.8699</v>
       </c>
       <c r="H10">
-        <v>0.8537</v>
+        <v>0.8466</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -858,10 +858,10 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>0.9751</v>
+        <v>0.9697</v>
       </c>
       <c r="H11">
-        <v>0.969</v>
+        <v>0.9625</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -884,10 +884,10 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>0.9756</v>
+        <v>0.9704</v>
       </c>
       <c r="H12">
-        <v>0.9684</v>
+        <v>0.9623</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -910,10 +910,10 @@
         <v>50</v>
       </c>
       <c r="G13">
-        <v>0.9855</v>
+        <v>0.9846</v>
       </c>
       <c r="H13">
-        <v>0.9811</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.9716</v>
+        <v>0.9678</v>
       </c>
       <c r="H14">
-        <v>0.9666</v>
+        <v>0.9615</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -962,10 +962,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>0.9814000000000001</v>
+        <v>0.9786</v>
       </c>
       <c r="H15">
-        <v>0.9755</v>
+        <v>0.9723000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.5768</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="H31">
-        <v>0.5315</v>
+        <v>0.5377999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="G32">
-        <v>0.6411</v>
+        <v>0.6869</v>
       </c>
       <c r="H32">
-        <v>0.6181</v>
+        <v>0.6644</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1430,10 +1430,10 @@
         <v>41</v>
       </c>
       <c r="G33">
-        <v>0.6842</v>
+        <v>0.655</v>
       </c>
       <c r="H33">
-        <v>0.6556999999999999</v>
+        <v>0.6254</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.8581</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="H34">
-        <v>0.8255</v>
+        <v>0.8369</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1482,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="G35">
-        <v>0.8646</v>
+        <v>0.8817</v>
       </c>
       <c r="H35">
-        <v>0.8312</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1508,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="G36">
-        <v>0.913</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="H36">
-        <v>0.8939</v>
+        <v>0.9041</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.9278999999999999</v>
+        <v>0.9107</v>
       </c>
       <c r="H37">
-        <v>0.9091</v>
+        <v>0.8877</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.8508</v>
+        <v>0.8313</v>
       </c>
       <c r="H38">
-        <v>0.8193</v>
+        <v>0.7948</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1586,10 +1586,10 @@
         <v>47</v>
       </c>
       <c r="G39">
-        <v>0.9255</v>
+        <v>0.9264</v>
       </c>
       <c r="H39">
-        <v>0.8994</v>
+        <v>0.9025</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1612,10 +1612,10 @@
         <v>48</v>
       </c>
       <c r="G40">
-        <v>0.9856</v>
+        <v>0.9852</v>
       </c>
       <c r="H40">
-        <v>0.9814000000000001</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1638,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="G41">
-        <v>0.9874000000000001</v>
+        <v>0.9857</v>
       </c>
       <c r="H41">
-        <v>0.9829</v>
+        <v>0.9805</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1664,10 +1664,10 @@
         <v>50</v>
       </c>
       <c r="G42">
-        <v>0.9886</v>
+        <v>0.9888</v>
       </c>
       <c r="H42">
-        <v>0.9862</v>
+        <v>0.9867</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1690,10 +1690,10 @@
         <v>51</v>
       </c>
       <c r="G43">
-        <v>0.9852</v>
+        <v>0.9837</v>
       </c>
       <c r="H43">
-        <v>0.9804</v>
+        <v>0.978</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1716,10 +1716,10 @@
         <v>52</v>
       </c>
       <c r="G44">
-        <v>0.989</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="H44">
-        <v>0.9852</v>
+        <v>0.9842</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2132,10 +2132,10 @@
         <v>38</v>
       </c>
       <c r="G60">
-        <v>0.4749</v>
+        <v>0.4863</v>
       </c>
       <c r="H60">
-        <v>0.4299</v>
+        <v>0.4357</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2158,10 +2158,10 @@
         <v>39</v>
       </c>
       <c r="G61">
-        <v>0.3819</v>
+        <v>0.3356</v>
       </c>
       <c r="H61">
-        <v>0.3589</v>
+        <v>0.3131</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2184,10 +2184,10 @@
         <v>41</v>
       </c>
       <c r="G62">
-        <v>0.5746</v>
+        <v>0.5135</v>
       </c>
       <c r="H62">
-        <v>0.5453</v>
+        <v>0.4773</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2210,10 +2210,10 @@
         <v>42</v>
       </c>
       <c r="G63">
-        <v>0.7707000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="H63">
-        <v>0.7324000000000001</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2236,10 +2236,10 @@
         <v>43</v>
       </c>
       <c r="G64">
-        <v>0.7559</v>
+        <v>0.7675</v>
       </c>
       <c r="H64">
-        <v>0.7059</v>
+        <v>0.7204</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2262,10 +2262,10 @@
         <v>44</v>
       </c>
       <c r="G65">
-        <v>0.868</v>
+        <v>0.8648</v>
       </c>
       <c r="H65">
-        <v>0.8467</v>
+        <v>0.8438</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.8879</v>
+        <v>0.858</v>
       </c>
       <c r="H66">
-        <v>0.8606</v>
+        <v>0.8146</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2314,10 +2314,10 @@
         <v>46</v>
       </c>
       <c r="G67">
-        <v>0.7395</v>
+        <v>0.7343</v>
       </c>
       <c r="H67">
-        <v>0.7030999999999999</v>
+        <v>0.6968</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2340,10 +2340,10 @@
         <v>47</v>
       </c>
       <c r="G68">
-        <v>0.887</v>
+        <v>0.8801</v>
       </c>
       <c r="H68">
-        <v>0.851</v>
+        <v>0.8421999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2366,10 +2366,10 @@
         <v>48</v>
       </c>
       <c r="G69">
-        <v>0.9813</v>
+        <v>0.9796</v>
       </c>
       <c r="H69">
-        <v>0.9761</v>
+        <v>0.9729</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="G70">
-        <v>0.982</v>
+        <v>0.9767</v>
       </c>
       <c r="H70">
-        <v>0.9761</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2418,10 +2418,10 @@
         <v>50</v>
       </c>
       <c r="G71">
-        <v>0.9868</v>
+        <v>0.9871</v>
       </c>
       <c r="H71">
-        <v>0.9848</v>
+        <v>0.9847</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2444,10 +2444,10 @@
         <v>51</v>
       </c>
       <c r="G72">
-        <v>0.9751</v>
+        <v>0.9705</v>
       </c>
       <c r="H72">
-        <v>0.9677</v>
+        <v>0.9619</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2470,10 +2470,10 @@
         <v>52</v>
       </c>
       <c r="G73">
-        <v>0.9867</v>
+        <v>0.9852</v>
       </c>
       <c r="H73">
-        <v>0.9826</v>
+        <v>0.9805</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.4664</v>
+        <v>0.4989</v>
       </c>
       <c r="H89">
-        <v>0.4313</v>
+        <v>0.4588</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2912,10 +2912,10 @@
         <v>39</v>
       </c>
       <c r="G90">
-        <v>0.3443</v>
+        <v>0.3746</v>
       </c>
       <c r="H90">
-        <v>0.3158</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2938,10 +2938,10 @@
         <v>40</v>
       </c>
       <c r="G91">
-        <v>0.4547</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="H91">
-        <v>0.4254</v>
+        <v>0.4865</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.7616000000000001</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="H92">
-        <v>0.7161</v>
+        <v>0.7113</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2990,10 +2990,10 @@
         <v>43</v>
       </c>
       <c r="G93">
-        <v>0.7683</v>
+        <v>0.8015</v>
       </c>
       <c r="H93">
-        <v>0.7272</v>
+        <v>0.7648</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3016,10 +3016,10 @@
         <v>44</v>
       </c>
       <c r="G94">
-        <v>0.8542</v>
+        <v>0.8744</v>
       </c>
       <c r="H94">
-        <v>0.8217</v>
+        <v>0.8484</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.8782</v>
+        <v>0.8498</v>
       </c>
       <c r="H95">
-        <v>0.8462</v>
+        <v>0.8167</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3068,10 +3068,10 @@
         <v>46</v>
       </c>
       <c r="G96">
-        <v>0.7278</v>
+        <v>0.7306</v>
       </c>
       <c r="H96">
-        <v>0.6903</v>
+        <v>0.6913</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3094,10 +3094,10 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.8748</v>
+        <v>0.8758</v>
       </c>
       <c r="H97">
-        <v>0.8389</v>
+        <v>0.8401999999999999</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3120,10 +3120,10 @@
         <v>48</v>
       </c>
       <c r="G98">
-        <v>0.9759</v>
+        <v>0.9774</v>
       </c>
       <c r="H98">
-        <v>0.9687</v>
+        <v>0.9711</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3146,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="G99">
-        <v>0.9785</v>
+        <v>0.9771</v>
       </c>
       <c r="H99">
-        <v>0.9745</v>
+        <v>0.9716</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3172,10 +3172,10 @@
         <v>50</v>
       </c>
       <c r="G100">
-        <v>0.9832</v>
+        <v>0.9868</v>
       </c>
       <c r="H100">
-        <v>0.9792</v>
+        <v>0.9833</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3198,10 +3198,10 @@
         <v>51</v>
       </c>
       <c r="G101">
-        <v>0.9691</v>
+        <v>0.9729</v>
       </c>
       <c r="H101">
-        <v>0.9654</v>
+        <v>0.967</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3224,10 +3224,10 @@
         <v>52</v>
       </c>
       <c r="G102">
-        <v>0.9861</v>
+        <v>0.9865</v>
       </c>
       <c r="H102">
-        <v>0.9825</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3640,10 +3640,10 @@
         <v>38</v>
       </c>
       <c r="G118">
-        <v>0.2554</v>
+        <v>0.2701</v>
       </c>
       <c r="H118">
-        <v>0.2344</v>
+        <v>0.2603</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3666,10 +3666,10 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.1745</v>
+        <v>0.1631</v>
       </c>
       <c r="H119">
-        <v>0.1419</v>
+        <v>0.1326</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3692,10 +3692,10 @@
         <v>40</v>
       </c>
       <c r="G120">
-        <v>0.2676</v>
+        <v>0.285</v>
       </c>
       <c r="H120">
-        <v>0.2293</v>
+        <v>0.235</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3718,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2839</v>
+        <v>0.2887</v>
       </c>
       <c r="H121">
-        <v>0.2384</v>
+        <v>0.2495</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3744,10 +3744,10 @@
         <v>43</v>
       </c>
       <c r="G122">
-        <v>0.4842</v>
+        <v>0.5493</v>
       </c>
       <c r="H122">
-        <v>0.4468</v>
+        <v>0.516</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.6523</v>
+        <v>0.6587</v>
       </c>
       <c r="H123">
-        <v>0.6254999999999999</v>
+        <v>0.6412</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -3796,10 +3796,10 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.7184</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="H124">
-        <v>0.6806</v>
+        <v>0.5797</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3822,10 +3822,10 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.5191</v>
+        <v>0.5071</v>
       </c>
       <c r="H125">
-        <v>0.4844</v>
+        <v>0.4744</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3848,10 +3848,10 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.7036</v>
+        <v>0.6908</v>
       </c>
       <c r="H126">
-        <v>0.6599</v>
+        <v>0.6461</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3874,10 +3874,10 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.951</v>
+        <v>0.9402</v>
       </c>
       <c r="H127">
-        <v>0.9330000000000001</v>
+        <v>0.9196</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3900,10 +3900,10 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9520999999999999</v>
+        <v>0.9414</v>
       </c>
       <c r="H128">
-        <v>0.9311</v>
+        <v>0.9197</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3926,10 +3926,10 @@
         <v>50</v>
       </c>
       <c r="G129">
-        <v>0.9805</v>
+        <v>0.9786</v>
       </c>
       <c r="H129">
-        <v>0.9751</v>
+        <v>0.9721</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -3952,10 +3952,10 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9469</v>
+        <v>0.9344</v>
       </c>
       <c r="H130">
-        <v>0.9347</v>
+        <v>0.9189000000000001</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3978,10 +3978,10 @@
         <v>52</v>
       </c>
       <c r="G131">
-        <v>0.9764</v>
+        <v>0.9736</v>
       </c>
       <c r="H131">
-        <v>0.9687</v>
+        <v>0.9644</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4394,10 +4394,10 @@
         <v>38</v>
       </c>
       <c r="G147">
-        <v>0.2631</v>
+        <v>0.245</v>
       </c>
       <c r="H147">
-        <v>0.2288</v>
+        <v>0.216</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4420,10 +4420,10 @@
         <v>39</v>
       </c>
       <c r="G148">
-        <v>0.1688</v>
+        <v>0.143</v>
       </c>
       <c r="H148">
-        <v>0.1354</v>
+        <v>0.1183</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4446,10 +4446,10 @@
         <v>40</v>
       </c>
       <c r="G149">
-        <v>0.2941</v>
+        <v>0.2796</v>
       </c>
       <c r="H149">
-        <v>0.2441</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4472,10 +4472,10 @@
         <v>41</v>
       </c>
       <c r="G150">
-        <v>0.2728</v>
+        <v>0.2352</v>
       </c>
       <c r="H150">
-        <v>0.2317</v>
+        <v>0.1985</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4498,10 +4498,10 @@
         <v>42</v>
       </c>
       <c r="G151">
-        <v>0.5532</v>
+        <v>0.484</v>
       </c>
       <c r="H151">
-        <v>0.5158</v>
+        <v>0.4507</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4524,10 +4524,10 @@
         <v>44</v>
       </c>
       <c r="G152">
-        <v>0.6636</v>
+        <v>0.6502</v>
       </c>
       <c r="H152">
-        <v>0.6258</v>
+        <v>0.6101</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4550,10 +4550,10 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.7383999999999999</v>
+        <v>0.5946</v>
       </c>
       <c r="H153">
-        <v>0.6991000000000001</v>
+        <v>0.5558999999999999</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4576,10 +4576,10 @@
         <v>46</v>
       </c>
       <c r="G154">
-        <v>0.543</v>
+        <v>0.4878</v>
       </c>
       <c r="H154">
-        <v>0.5038</v>
+        <v>0.4476</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4602,10 +4602,10 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>0.7155</v>
+        <v>0.6548</v>
       </c>
       <c r="H155">
-        <v>0.6715</v>
+        <v>0.6014</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4628,10 +4628,10 @@
         <v>48</v>
       </c>
       <c r="G156">
-        <v>0.951</v>
+        <v>0.9371</v>
       </c>
       <c r="H156">
-        <v>0.9308999999999999</v>
+        <v>0.9137</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4654,10 +4654,10 @@
         <v>49</v>
       </c>
       <c r="G157">
-        <v>0.9522</v>
+        <v>0.9403</v>
       </c>
       <c r="H157">
-        <v>0.9355</v>
+        <v>0.9214</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4680,10 +4680,10 @@
         <v>50</v>
       </c>
       <c r="G158">
-        <v>0.9802</v>
+        <v>0.9795</v>
       </c>
       <c r="H158">
-        <v>0.9737</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -4706,10 +4706,10 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9472</v>
+        <v>0.9394</v>
       </c>
       <c r="H159">
-        <v>0.9339</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4732,10 +4732,10 @@
         <v>52</v>
       </c>
       <c r="G160">
-        <v>0.9784</v>
+        <v>0.9739</v>
       </c>
       <c r="H160">
-        <v>0.9724</v>
+        <v>0.9661</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5148,10 +5148,10 @@
         <v>38</v>
       </c>
       <c r="G176">
-        <v>0.1518</v>
+        <v>0.1527</v>
       </c>
       <c r="H176">
-        <v>0.1291</v>
+        <v>0.1299</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5174,10 +5174,10 @@
         <v>39</v>
       </c>
       <c r="G177">
-        <v>0.1061</v>
+        <v>0.0959</v>
       </c>
       <c r="H177">
-        <v>0.08699999999999999</v>
+        <v>0.0761</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5200,10 +5200,10 @@
         <v>40</v>
       </c>
       <c r="G178">
-        <v>0.1533</v>
+        <v>0.1562</v>
       </c>
       <c r="H178">
-        <v>0.132</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5226,10 +5226,10 @@
         <v>41</v>
       </c>
       <c r="G179">
-        <v>0.1783</v>
+        <v>0.1516</v>
       </c>
       <c r="H179">
-        <v>0.1458</v>
+        <v>0.1256</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5252,10 +5252,10 @@
         <v>42</v>
       </c>
       <c r="G180">
-        <v>0.3745</v>
+        <v>0.3588</v>
       </c>
       <c r="H180">
-        <v>0.3477</v>
+        <v>0.3413</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5278,10 +5278,10 @@
         <v>43</v>
       </c>
       <c r="G181">
-        <v>0.3742</v>
+        <v>0.3899</v>
       </c>
       <c r="H181">
-        <v>0.3364</v>
+        <v>0.3498</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5304,10 +5304,10 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.5427999999999999</v>
+        <v>0.4624</v>
       </c>
       <c r="H182">
-        <v>0.5113</v>
+        <v>0.4268</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5330,10 +5330,10 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.3836</v>
+        <v>0.3504</v>
       </c>
       <c r="H183">
-        <v>0.3381</v>
+        <v>0.3078</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5356,10 +5356,10 @@
         <v>47</v>
       </c>
       <c r="G184">
-        <v>0.5457</v>
+        <v>0.5108</v>
       </c>
       <c r="H184">
-        <v>0.4968</v>
+        <v>0.4654</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5382,10 +5382,10 @@
         <v>48</v>
       </c>
       <c r="G185">
-        <v>0.9019</v>
+        <v>0.8804</v>
       </c>
       <c r="H185">
-        <v>0.874</v>
+        <v>0.8507</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5408,10 +5408,10 @@
         <v>49</v>
       </c>
       <c r="G186">
-        <v>0.9074</v>
+        <v>0.8807</v>
       </c>
       <c r="H186">
-        <v>0.8779</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5434,10 +5434,10 @@
         <v>50</v>
       </c>
       <c r="G187">
-        <v>0.9687</v>
+        <v>0.9634</v>
       </c>
       <c r="H187">
-        <v>0.9603</v>
+        <v>0.9549</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5460,10 +5460,10 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.9015</v>
+        <v>0.8789</v>
       </c>
       <c r="H188">
-        <v>0.8759</v>
+        <v>0.8489</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5486,10 +5486,10 @@
         <v>52</v>
       </c>
       <c r="G189">
-        <v>0.9659</v>
+        <v>0.961</v>
       </c>
       <c r="H189">
-        <v>0.9576</v>
+        <v>0.9520999999999999</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -5902,10 +5902,10 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.1203</v>
+        <v>0.1618</v>
       </c>
       <c r="H205">
-        <v>0.0977</v>
+        <v>0.1359</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5928,10 +5928,10 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.09089999999999999</v>
+        <v>0.1123</v>
       </c>
       <c r="H206">
-        <v>0.0721</v>
+        <v>0.0893</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -5954,10 +5954,10 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.1394</v>
+        <v>0.1854</v>
       </c>
       <c r="H207">
-        <v>0.1121</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5980,10 +5980,10 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.1538</v>
+        <v>0.1833</v>
       </c>
       <c r="H208">
-        <v>0.1218</v>
+        <v>0.1502</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6006,10 +6006,10 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.3194</v>
+        <v>0.4203</v>
       </c>
       <c r="H209">
-        <v>0.2816</v>
+        <v>0.3846</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6032,10 +6032,10 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.3009</v>
+        <v>0.4441</v>
       </c>
       <c r="H210">
-        <v>0.2616</v>
+        <v>0.4054</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6058,10 +6058,10 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.4887</v>
+        <v>0.5732</v>
       </c>
       <c r="H211">
-        <v>0.4572</v>
+        <v>0.5376</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -6084,10 +6084,10 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.3078</v>
+        <v>0.343</v>
       </c>
       <c r="H212">
-        <v>0.2637</v>
+        <v>0.2925</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -6110,10 +6110,10 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.5048</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="H213">
-        <v>0.469</v>
+        <v>0.498</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -6136,10 +6136,10 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.8877</v>
+        <v>0.9053</v>
       </c>
       <c r="H214">
-        <v>0.8584000000000001</v>
+        <v>0.8762</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -6162,10 +6162,10 @@
         <v>49</v>
       </c>
       <c r="G215">
-        <v>0.8784</v>
+        <v>0.8902</v>
       </c>
       <c r="H215">
-        <v>0.8485</v>
+        <v>0.8605</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -6188,10 +6188,10 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>0.9616</v>
+        <v>0.967</v>
       </c>
       <c r="H216">
-        <v>0.9508</v>
+        <v>0.9558</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -6214,10 +6214,10 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.8808</v>
+        <v>0.8921</v>
       </c>
       <c r="H217">
-        <v>0.8537</v>
+        <v>0.868</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -6243,7 +6243,7 @@
         <v>0.9508</v>
       </c>
       <c r="H218">
-        <v>0.9387</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -6656,10 +6656,10 @@
         <v>38</v>
       </c>
       <c r="G234">
-        <v>0.2591</v>
+        <v>0.2926</v>
       </c>
       <c r="H234">
-        <v>0.2317</v>
+        <v>0.2625</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -6682,10 +6682,10 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.1807</v>
+        <v>0.2052</v>
       </c>
       <c r="H235">
-        <v>0.1492</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -6708,10 +6708,10 @@
         <v>40</v>
       </c>
       <c r="G236">
-        <v>0.2969</v>
+        <v>0.3032</v>
       </c>
       <c r="H236">
-        <v>0.2605</v>
+        <v>0.2657</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -6734,10 +6734,10 @@
         <v>41</v>
       </c>
       <c r="G237">
-        <v>0.3097</v>
+        <v>0.3087</v>
       </c>
       <c r="H237">
-        <v>0.2722</v>
+        <v>0.2694</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -6760,10 +6760,10 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.5155999999999999</v>
+        <v>0.5256</v>
       </c>
       <c r="H238">
-        <v>0.4809</v>
+        <v>0.4929</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -6786,10 +6786,10 @@
         <v>43</v>
       </c>
       <c r="G239">
-        <v>0.4962</v>
+        <v>0.5524</v>
       </c>
       <c r="H239">
-        <v>0.457</v>
+        <v>0.5122</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -6812,10 +6812,10 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.6619</v>
+        <v>0.6922</v>
       </c>
       <c r="H240">
-        <v>0.6163999999999999</v>
+        <v>0.6496</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -6838,10 +6838,10 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.7363</v>
+        <v>0.7075</v>
       </c>
       <c r="H241">
-        <v>0.6922</v>
+        <v>0.657</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -6890,10 +6890,10 @@
         <v>48</v>
       </c>
       <c r="G243">
-        <v>0.9519</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="H243">
-        <v>0.9399</v>
+        <v>0.9366</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -6916,10 +6916,10 @@
         <v>49</v>
       </c>
       <c r="G244">
-        <v>0.9465</v>
+        <v>0.9443</v>
       </c>
       <c r="H244">
-        <v>0.9323</v>
+        <v>0.9297</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -6942,10 +6942,10 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9832</v>
+        <v>0.9801</v>
       </c>
       <c r="H245">
-        <v>0.9785</v>
+        <v>0.9742</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -6968,10 +6968,10 @@
         <v>51</v>
       </c>
       <c r="G246">
-        <v>0.9336</v>
+        <v>0.9298</v>
       </c>
       <c r="H246">
-        <v>0.9195</v>
+        <v>0.9146</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -6994,10 +6994,10 @@
         <v>52</v>
       </c>
       <c r="G247">
-        <v>0.9769</v>
+        <v>0.9747</v>
       </c>
       <c r="H247">
-        <v>0.9705</v>
+        <v>0.9675</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7410,10 +7410,10 @@
         <v>38</v>
       </c>
       <c r="G263">
-        <v>0.1463</v>
+        <v>0.1534</v>
       </c>
       <c r="H263">
-        <v>0.1155</v>
+        <v>0.1301</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -7436,10 +7436,10 @@
         <v>39</v>
       </c>
       <c r="G264">
-        <v>0.1006</v>
+        <v>0.0975</v>
       </c>
       <c r="H264">
-        <v>0.0745</v>
+        <v>0.0736</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7462,10 +7462,10 @@
         <v>40</v>
       </c>
       <c r="G265">
-        <v>0.149</v>
+        <v>0.1578</v>
       </c>
       <c r="H265">
-        <v>0.113</v>
+        <v>0.1199</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7488,10 +7488,10 @@
         <v>41</v>
       </c>
       <c r="G266">
-        <v>0.1611</v>
+        <v>0.1598</v>
       </c>
       <c r="H266">
-        <v>0.1252</v>
+        <v>0.1242</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3401</v>
+        <v>0.3539</v>
       </c>
       <c r="H267">
-        <v>0.2964</v>
+        <v>0.3092</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7540,10 +7540,10 @@
         <v>43</v>
       </c>
       <c r="G268">
-        <v>0.3285</v>
+        <v>0.3986</v>
       </c>
       <c r="H268">
-        <v>0.2845</v>
+        <v>0.3452</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -7566,10 +7566,10 @@
         <v>44</v>
       </c>
       <c r="G269">
-        <v>0.5032</v>
+        <v>0.5346</v>
       </c>
       <c r="H269">
-        <v>0.4543</v>
+        <v>0.4892</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.531</v>
+        <v>0.502</v>
       </c>
       <c r="H270">
-        <v>0.4952</v>
+        <v>0.4652</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7644,10 +7644,10 @@
         <v>48</v>
       </c>
       <c r="G272">
-        <v>0.9044</v>
+        <v>0.9018</v>
       </c>
       <c r="H272">
-        <v>0.8724</v>
+        <v>0.8694</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7670,10 +7670,10 @@
         <v>49</v>
       </c>
       <c r="G273">
-        <v>0.8843</v>
+        <v>0.882</v>
       </c>
       <c r="H273">
-        <v>0.8583</v>
+        <v>0.8548</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7696,10 +7696,10 @@
         <v>50</v>
       </c>
       <c r="G274">
-        <v>0.9631</v>
+        <v>0.96</v>
       </c>
       <c r="H274">
-        <v>0.9533</v>
+        <v>0.9496</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7722,10 +7722,10 @@
         <v>51</v>
       </c>
       <c r="G275">
-        <v>0.8782</v>
+        <v>0.8779</v>
       </c>
       <c r="H275">
-        <v>0.8531</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -7748,10 +7748,10 @@
         <v>52</v>
       </c>
       <c r="G276">
-        <v>0.9599</v>
+        <v>0.9578</v>
       </c>
       <c r="H276">
-        <v>0.9506</v>
+        <v>0.9479</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -8164,10 +8164,10 @@
         <v>38</v>
       </c>
       <c r="G292">
-        <v>0.031</v>
+        <v>0.0375</v>
       </c>
       <c r="H292">
-        <v>0.0249</v>
+        <v>0.0303</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8190,10 +8190,10 @@
         <v>39</v>
       </c>
       <c r="G293">
-        <v>0.0186</v>
+        <v>0.0194</v>
       </c>
       <c r="H293">
-        <v>0.0144</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -8216,10 +8216,10 @@
         <v>40</v>
       </c>
       <c r="G294">
-        <v>0.0239</v>
+        <v>0.0271</v>
       </c>
       <c r="H294">
-        <v>0.0187</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -8242,10 +8242,10 @@
         <v>41</v>
       </c>
       <c r="G295">
-        <v>0.0313</v>
+        <v>0.0289</v>
       </c>
       <c r="H295">
-        <v>0.0241</v>
+        <v>0.0226</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.067</v>
+        <v>0.0804</v>
       </c>
       <c r="H296">
-        <v>0.049</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8294,10 +8294,10 @@
         <v>43</v>
       </c>
       <c r="G297">
-        <v>0.06909999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="H297">
-        <v>0.049</v>
+        <v>0.0629</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -8320,10 +8320,10 @@
         <v>44</v>
       </c>
       <c r="G298">
-        <v>0.126</v>
+        <v>0.1493</v>
       </c>
       <c r="H298">
-        <v>0.09810000000000001</v>
+        <v>0.1196</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.1416</v>
+        <v>0.1238</v>
       </c>
       <c r="H299">
-        <v>0.1123</v>
+        <v>0.09470000000000001</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8372,10 +8372,10 @@
         <v>46</v>
       </c>
       <c r="G300">
-        <v>0.0601</v>
+        <v>0.0634</v>
       </c>
       <c r="H300">
-        <v>0.0481</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -8398,10 +8398,10 @@
         <v>47</v>
       </c>
       <c r="G301">
-        <v>0.1276</v>
+        <v>0.1306</v>
       </c>
       <c r="H301">
-        <v>0.0956</v>
+        <v>0.0982</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8424,10 +8424,10 @@
         <v>49</v>
       </c>
       <c r="G302">
-        <v>0.4656</v>
+        <v>0.466</v>
       </c>
       <c r="H302">
-        <v>0.4329</v>
+        <v>0.4334</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -8450,10 +8450,10 @@
         <v>50</v>
       </c>
       <c r="G303">
-        <v>0.7746</v>
+        <v>0.7718</v>
       </c>
       <c r="H303">
-        <v>0.7368</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -8476,10 +8476,10 @@
         <v>51</v>
       </c>
       <c r="G304">
-        <v>0.4702</v>
+        <v>0.4731</v>
       </c>
       <c r="H304">
-        <v>0.4311</v>
+        <v>0.4349</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -8918,10 +8918,10 @@
         <v>38</v>
       </c>
       <c r="G321">
-        <v>0.0316</v>
+        <v>0.0377</v>
       </c>
       <c r="H321">
-        <v>0.0244</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8944,10 +8944,10 @@
         <v>39</v>
       </c>
       <c r="G322">
-        <v>0.0171</v>
+        <v>0.0195</v>
       </c>
       <c r="H322">
-        <v>0.0126</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8970,10 +8970,10 @@
         <v>40</v>
       </c>
       <c r="G323">
-        <v>0.0239</v>
+        <v>0.0307</v>
       </c>
       <c r="H323">
-        <v>0.018</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8996,10 +8996,10 @@
         <v>41</v>
       </c>
       <c r="G324">
-        <v>0.0255</v>
+        <v>0.0284</v>
       </c>
       <c r="H324">
-        <v>0.0215</v>
+        <v>0.0229</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.0689</v>
+        <v>0.0803</v>
       </c>
       <c r="H325">
-        <v>0.0479</v>
+        <v>0.0586</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9048,10 +9048,10 @@
         <v>43</v>
       </c>
       <c r="G326">
-        <v>0.0645</v>
+        <v>0.0786</v>
       </c>
       <c r="H326">
-        <v>0.0478</v>
+        <v>0.0597</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -9074,10 +9074,10 @@
         <v>44</v>
       </c>
       <c r="G327">
-        <v>0.1221</v>
+        <v>0.1505</v>
       </c>
       <c r="H327">
-        <v>0.0926</v>
+        <v>0.1193</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -9100,10 +9100,10 @@
         <v>45</v>
       </c>
       <c r="G328">
-        <v>0.1515</v>
+        <v>0.1395</v>
       </c>
       <c r="H328">
-        <v>0.1216</v>
+        <v>0.1098</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9126,10 +9126,10 @@
         <v>46</v>
       </c>
       <c r="G329">
-        <v>0.0677</v>
+        <v>0.0703</v>
       </c>
       <c r="H329">
-        <v>0.0535</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9152,10 +9152,10 @@
         <v>47</v>
       </c>
       <c r="G330">
-        <v>0.1417</v>
+        <v>0.1452</v>
       </c>
       <c r="H330">
-        <v>0.1157</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9178,10 +9178,10 @@
         <v>48</v>
       </c>
       <c r="G331">
-        <v>0.5671</v>
+        <v>0.5666</v>
       </c>
       <c r="H331">
-        <v>0.5344</v>
+        <v>0.534</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.8100000000000001</v>
+        <v>0.8012</v>
       </c>
       <c r="H332">
-        <v>0.7673</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9256,10 +9256,10 @@
         <v>52</v>
       </c>
       <c r="G334">
-        <v>0.8051</v>
+        <v>0.801</v>
       </c>
       <c r="H334">
-        <v>0.7725</v>
+        <v>0.7691</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -9672,10 +9672,10 @@
         <v>38</v>
       </c>
       <c r="G350">
-        <v>0.0189</v>
+        <v>0.02</v>
       </c>
       <c r="H350">
-        <v>0.0145</v>
+        <v>0.0154</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -9698,10 +9698,10 @@
         <v>39</v>
       </c>
       <c r="G351">
-        <v>0.0138</v>
+        <v>0.0133</v>
       </c>
       <c r="H351">
-        <v>0.0114</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -9724,10 +9724,10 @@
         <v>40</v>
       </c>
       <c r="G352">
-        <v>0.0152</v>
+        <v>0.0153</v>
       </c>
       <c r="H352">
-        <v>0.0132</v>
+        <v>0.0129</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -9750,10 +9750,10 @@
         <v>41</v>
       </c>
       <c r="G353">
-        <v>0.0208</v>
+        <v>0.0167</v>
       </c>
       <c r="H353">
-        <v>0.0168</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -9776,10 +9776,10 @@
         <v>42</v>
       </c>
       <c r="G354">
-        <v>0.0249</v>
+        <v>0.0279</v>
       </c>
       <c r="H354">
-        <v>0.0195</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -9802,10 +9802,10 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>0.0263</v>
+        <v>0.027</v>
       </c>
       <c r="H355">
-        <v>0.0198</v>
+        <v>0.0205</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -9828,10 +9828,10 @@
         <v>44</v>
       </c>
       <c r="G356">
-        <v>0.0397</v>
+        <v>0.0451</v>
       </c>
       <c r="H356">
-        <v>0.0313</v>
+        <v>0.0366</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9854,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="G357">
-        <v>0.0492</v>
+        <v>0.0442</v>
       </c>
       <c r="H357">
-        <v>0.0384</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
-        <v>0.0215</v>
+        <v>0.0258</v>
       </c>
       <c r="H358">
-        <v>0.0168</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9906,10 +9906,10 @@
         <v>47</v>
       </c>
       <c r="G359">
-        <v>0.0467</v>
+        <v>0.0504</v>
       </c>
       <c r="H359">
-        <v>0.0369</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -9932,10 +9932,10 @@
         <v>48</v>
       </c>
       <c r="G360">
-        <v>0.2632</v>
+        <v>0.2655</v>
       </c>
       <c r="H360">
-        <v>0.2254</v>
+        <v>0.2282</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.2327</v>
+        <v>0.2445</v>
       </c>
       <c r="H361">
-        <v>0.19</v>
+        <v>0.1988</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -9984,10 +9984,10 @@
         <v>51</v>
       </c>
       <c r="G362">
-        <v>0.2268</v>
+        <v>0.2368</v>
       </c>
       <c r="H362">
-        <v>0.179</v>
+        <v>0.1894</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -10010,10 +10010,10 @@
         <v>52</v>
       </c>
       <c r="G363">
-        <v>0.5486</v>
+        <v>0.555</v>
       </c>
       <c r="H363">
-        <v>0.5042</v>
+        <v>0.5109</v>
       </c>
     </row>
     <row r="364" spans="1:8">
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.0334</v>
+        <v>0.0385</v>
       </c>
       <c r="H379">
-        <v>0.0284</v>
+        <v>0.0322</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10452,10 +10452,10 @@
         <v>39</v>
       </c>
       <c r="G380">
-        <v>0.0196</v>
+        <v>0.022</v>
       </c>
       <c r="H380">
-        <v>0.0148</v>
+        <v>0.0163</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -10478,10 +10478,10 @@
         <v>40</v>
       </c>
       <c r="G381">
-        <v>0.0323</v>
+        <v>0.0381</v>
       </c>
       <c r="H381">
-        <v>0.0249</v>
+        <v>0.0295</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -10504,10 +10504,10 @@
         <v>41</v>
       </c>
       <c r="G382">
-        <v>0.0346</v>
+        <v>0.033</v>
       </c>
       <c r="H382">
-        <v>0.0309</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.0653</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="H383">
-        <v>0.0531</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.06610000000000001</v>
+        <v>0.074</v>
       </c>
       <c r="H384">
-        <v>0.0528</v>
+        <v>0.0606</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.1241</v>
+        <v>0.1511</v>
       </c>
       <c r="H385">
-        <v>0.0985</v>
+        <v>0.1211</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.1463</v>
+        <v>0.132</v>
       </c>
       <c r="H386">
-        <v>0.1192</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10634,10 +10634,10 @@
         <v>46</v>
       </c>
       <c r="G387">
-        <v>0.0805</v>
+        <v>0.0854</v>
       </c>
       <c r="H387">
-        <v>0.0664</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -10660,10 +10660,10 @@
         <v>47</v>
       </c>
       <c r="G388">
-        <v>0.1469</v>
+        <v>0.148</v>
       </c>
       <c r="H388">
-        <v>0.1218</v>
+        <v>0.1221</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -10686,10 +10686,10 @@
         <v>48</v>
       </c>
       <c r="G389">
-        <v>0.5689</v>
+        <v>0.5651</v>
       </c>
       <c r="H389">
-        <v>0.5298</v>
+        <v>0.5269</v>
       </c>
     </row>
     <row r="390" spans="1:8">
@@ -10738,10 +10738,10 @@
         <v>50</v>
       </c>
       <c r="G391">
-        <v>0.821</v>
+        <v>0.8106</v>
       </c>
       <c r="H391">
-        <v>0.7732</v>
+        <v>0.7632</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -10764,10 +10764,10 @@
         <v>52</v>
       </c>
       <c r="G392">
-        <v>0.7778</v>
+        <v>0.7763</v>
       </c>
       <c r="H392">
-        <v>0.7497</v>
+        <v>0.7485000000000001</v>
       </c>
     </row>
     <row r="393" spans="1:8">
@@ -11180,10 +11180,10 @@
         <v>38</v>
       </c>
       <c r="G408">
-        <v>0.0245</v>
+        <v>0.0277</v>
       </c>
       <c r="H408">
-        <v>0.0186</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11206,10 +11206,10 @@
         <v>39</v>
       </c>
       <c r="G409">
-        <v>0.0148</v>
+        <v>0.0158</v>
       </c>
       <c r="H409">
-        <v>0.011</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -11232,10 +11232,10 @@
         <v>40</v>
       </c>
       <c r="G410">
-        <v>0.0174</v>
+        <v>0.0195</v>
       </c>
       <c r="H410">
-        <v>0.0133</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -11258,10 +11258,10 @@
         <v>41</v>
       </c>
       <c r="G411">
-        <v>0.0175</v>
+        <v>0.0178</v>
       </c>
       <c r="H411">
-        <v>0.0139</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -11284,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="G412">
-        <v>0.0313</v>
+        <v>0.0356</v>
       </c>
       <c r="H412">
-        <v>0.0236</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11310,10 +11310,10 @@
         <v>43</v>
       </c>
       <c r="G413">
-        <v>0.0276</v>
+        <v>0.0339</v>
       </c>
       <c r="H413">
-        <v>0.0216</v>
+        <v>0.0261</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -11336,10 +11336,10 @@
         <v>44</v>
       </c>
       <c r="G414">
-        <v>0.0424</v>
+        <v>0.0479</v>
       </c>
       <c r="H414">
-        <v>0.0341</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -11362,7 +11362,7 @@
         <v>45</v>
       </c>
       <c r="G415">
-        <v>0.0613</v>
+        <v>0.061</v>
       </c>
       <c r="H415">
         <v>0.0492</v>
@@ -11388,10 +11388,10 @@
         <v>46</v>
       </c>
       <c r="G416">
-        <v>0.0295</v>
+        <v>0.0325</v>
       </c>
       <c r="H416">
-        <v>0.0231</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -11414,10 +11414,10 @@
         <v>47</v>
       </c>
       <c r="G417">
-        <v>0.0494</v>
+        <v>0.0521</v>
       </c>
       <c r="H417">
-        <v>0.0401</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="418" spans="1:8">
@@ -11466,10 +11466,10 @@
         <v>49</v>
       </c>
       <c r="G419">
-        <v>0.2275</v>
+        <v>0.2309</v>
       </c>
       <c r="H419">
-        <v>0.1949</v>
+        <v>0.199</v>
       </c>
     </row>
     <row r="420" spans="1:8">
@@ -11492,10 +11492,10 @@
         <v>50</v>
       </c>
       <c r="G420">
-        <v>0.4958</v>
+        <v>0.4891</v>
       </c>
       <c r="H420">
-        <v>0.4514</v>
+        <v>0.445</v>
       </c>
     </row>
     <row r="421" spans="1:8">
@@ -11518,10 +11518,10 @@
         <v>51</v>
       </c>
       <c r="G421">
-        <v>0.2503</v>
+        <v>0.2515</v>
       </c>
       <c r="H421">
-        <v>0.2222</v>
+        <v>0.2237</v>
       </c>
     </row>
     <row r="422" spans="1:8">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4622</v>
+        <v>0.4446</v>
       </c>
       <c r="H2">
-        <v>0.4068</v>
+        <v>0.3922</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,10 +650,10 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>0.5643</v>
+        <v>0.5484</v>
       </c>
       <c r="H3">
-        <v>0.5137</v>
+        <v>0.5008</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5412</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="H4">
-        <v>0.5011</v>
+        <v>0.4844</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -702,10 +702,10 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>0.7397</v>
+        <v>0.745</v>
       </c>
       <c r="H5">
-        <v>0.7299</v>
+        <v>0.7344000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -728,10 +728,10 @@
         <v>43</v>
       </c>
       <c r="G6">
-        <v>0.784</v>
+        <v>0.7769</v>
       </c>
       <c r="H6">
-        <v>0.755</v>
+        <v>0.7461</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -754,10 +754,10 @@
         <v>44</v>
       </c>
       <c r="G7">
-        <v>0.8701</v>
+        <v>0.8612</v>
       </c>
       <c r="H7">
-        <v>0.8473000000000001</v>
+        <v>0.8368</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.8641</v>
+        <v>0.8583</v>
       </c>
       <c r="H8">
-        <v>0.8381999999999999</v>
+        <v>0.8307</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -806,10 +806,10 @@
         <v>46</v>
       </c>
       <c r="G9">
-        <v>0.7375</v>
+        <v>0.7307</v>
       </c>
       <c r="H9">
-        <v>0.7074</v>
+        <v>0.7013</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -832,10 +832,10 @@
         <v>47</v>
       </c>
       <c r="G10">
-        <v>0.8699</v>
+        <v>0.862</v>
       </c>
       <c r="H10">
-        <v>0.8466</v>
+        <v>0.8333</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -858,10 +858,10 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>0.9697</v>
+        <v>0.9668</v>
       </c>
       <c r="H11">
-        <v>0.9625</v>
+        <v>0.9597</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -884,10 +884,10 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>0.9704</v>
+        <v>0.9617</v>
       </c>
       <c r="H12">
-        <v>0.9623</v>
+        <v>0.9513</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -913,7 +913,7 @@
         <v>0.9846</v>
       </c>
       <c r="H13">
-        <v>0.98</v>
+        <v>0.9796</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.9678</v>
+        <v>0.9669</v>
       </c>
       <c r="H14">
-        <v>0.9615</v>
+        <v>0.9608</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -962,10 +962,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>0.9786</v>
+        <v>0.9785</v>
       </c>
       <c r="H15">
-        <v>0.9723000000000001</v>
+        <v>0.973</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.5931999999999999</v>
+        <v>0.6078</v>
       </c>
       <c r="H31">
-        <v>0.5377999999999999</v>
+        <v>0.5554</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.8673999999999999</v>
+        <v>0.868</v>
       </c>
       <c r="H34">
-        <v>0.8369</v>
+        <v>0.8379</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1482,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="G35">
-        <v>0.8817</v>
+        <v>0.8832</v>
       </c>
       <c r="H35">
-        <v>0.857</v>
+        <v>0.8582</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1508,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="G36">
-        <v>0.9239000000000001</v>
+        <v>0.9227</v>
       </c>
       <c r="H36">
-        <v>0.9041</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.9107</v>
+        <v>0.9194</v>
       </c>
       <c r="H37">
-        <v>0.8877</v>
+        <v>0.8991</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.8313</v>
+        <v>0.8333</v>
       </c>
       <c r="H38">
-        <v>0.7948</v>
+        <v>0.7965</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1638,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="G41">
-        <v>0.9857</v>
+        <v>0.9833</v>
       </c>
       <c r="H41">
-        <v>0.9805</v>
+        <v>0.9772</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -2132,10 +2132,10 @@
         <v>38</v>
       </c>
       <c r="G60">
-        <v>0.4863</v>
+        <v>0.4992</v>
       </c>
       <c r="H60">
-        <v>0.4357</v>
+        <v>0.4516</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2184,10 +2184,10 @@
         <v>41</v>
       </c>
       <c r="G62">
-        <v>0.5135</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="H62">
-        <v>0.4773</v>
+        <v>0.4767</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2210,10 +2210,10 @@
         <v>42</v>
       </c>
       <c r="G63">
-        <v>0.765</v>
+        <v>0.7674</v>
       </c>
       <c r="H63">
-        <v>0.715</v>
+        <v>0.7174</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2262,10 +2262,10 @@
         <v>44</v>
       </c>
       <c r="G65">
-        <v>0.8648</v>
+        <v>0.8656</v>
       </c>
       <c r="H65">
-        <v>0.8438</v>
+        <v>0.8445</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.858</v>
+        <v>0.8648</v>
       </c>
       <c r="H66">
-        <v>0.8146</v>
+        <v>0.8269</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2340,10 +2340,10 @@
         <v>47</v>
       </c>
       <c r="G68">
-        <v>0.8801</v>
+        <v>0.8817</v>
       </c>
       <c r="H68">
-        <v>0.8421999999999999</v>
+        <v>0.8436</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="G70">
-        <v>0.9767</v>
+        <v>0.9709</v>
       </c>
       <c r="H70">
-        <v>0.9693000000000001</v>
+        <v>0.9621</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.4989</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="H89">
-        <v>0.4588</v>
+        <v>0.4854</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2938,10 +2938,10 @@
         <v>40</v>
       </c>
       <c r="G91">
-        <v>0.5227000000000001</v>
+        <v>0.5233</v>
       </c>
       <c r="H91">
-        <v>0.4865</v>
+        <v>0.4874</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.7504999999999999</v>
+        <v>0.7509</v>
       </c>
       <c r="H92">
-        <v>0.7113</v>
+        <v>0.7119</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -3016,10 +3016,10 @@
         <v>44</v>
       </c>
       <c r="G94">
-        <v>0.8744</v>
+        <v>0.8742</v>
       </c>
       <c r="H94">
-        <v>0.8484</v>
+        <v>0.851</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.8498</v>
+        <v>0.8544</v>
       </c>
       <c r="H95">
-        <v>0.8167</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3094,10 +3094,10 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.8758</v>
+        <v>0.8774</v>
       </c>
       <c r="H97">
-        <v>0.8401999999999999</v>
+        <v>0.8416</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3146,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="G99">
-        <v>0.9771</v>
+        <v>0.9735</v>
       </c>
       <c r="H99">
-        <v>0.9716</v>
+        <v>0.9666</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3227,7 +3227,7 @@
         <v>0.9865</v>
       </c>
       <c r="H102">
-        <v>0.9822</v>
+        <v>0.9825</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3640,10 +3640,10 @@
         <v>38</v>
       </c>
       <c r="G118">
-        <v>0.2701</v>
+        <v>0.2656</v>
       </c>
       <c r="H118">
-        <v>0.2603</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3666,10 +3666,10 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.1631</v>
+        <v>0.1621</v>
       </c>
       <c r="H119">
-        <v>0.1326</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3692,10 +3692,10 @@
         <v>40</v>
       </c>
       <c r="G120">
-        <v>0.285</v>
+        <v>0.2826</v>
       </c>
       <c r="H120">
-        <v>0.235</v>
+        <v>0.2326</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3718,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2887</v>
+        <v>0.2881</v>
       </c>
       <c r="H121">
-        <v>0.2495</v>
+        <v>0.2491</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.6587</v>
+        <v>0.6571</v>
       </c>
       <c r="H123">
-        <v>0.6412</v>
+        <v>0.6399</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -3796,10 +3796,10 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.6153999999999999</v>
+        <v>0.6583</v>
       </c>
       <c r="H124">
-        <v>0.5797</v>
+        <v>0.6186</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3822,10 +3822,10 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.5071</v>
+        <v>0.5031</v>
       </c>
       <c r="H125">
-        <v>0.4744</v>
+        <v>0.4691</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3848,10 +3848,10 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.6908</v>
+        <v>0.6931</v>
       </c>
       <c r="H126">
-        <v>0.6461</v>
+        <v>0.6456</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3874,10 +3874,10 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.9402</v>
+        <v>0.9419</v>
       </c>
       <c r="H127">
-        <v>0.9196</v>
+        <v>0.9218</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3900,10 +3900,10 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9414</v>
+        <v>0.9316</v>
       </c>
       <c r="H128">
-        <v>0.9197</v>
+        <v>0.9031</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3952,10 +3952,10 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9344</v>
+        <v>0.9358</v>
       </c>
       <c r="H130">
-        <v>0.9189000000000001</v>
+        <v>0.9197</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -4394,10 +4394,10 @@
         <v>38</v>
       </c>
       <c r="G147">
-        <v>0.245</v>
+        <v>0.2539</v>
       </c>
       <c r="H147">
-        <v>0.216</v>
+        <v>0.2231</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4420,10 +4420,10 @@
         <v>39</v>
       </c>
       <c r="G148">
-        <v>0.143</v>
+        <v>0.1418</v>
       </c>
       <c r="H148">
-        <v>0.1183</v>
+        <v>0.1168</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4550,10 +4550,10 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.5946</v>
+        <v>0.6063</v>
       </c>
       <c r="H153">
-        <v>0.5558999999999999</v>
+        <v>0.5652</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4654,10 +4654,10 @@
         <v>49</v>
       </c>
       <c r="G157">
-        <v>0.9403</v>
+        <v>0.9323</v>
       </c>
       <c r="H157">
-        <v>0.9214</v>
+        <v>0.9122</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4706,10 +4706,10 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9394</v>
+        <v>0.9413</v>
       </c>
       <c r="H159">
-        <v>0.926</v>
+        <v>0.9276</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4735,7 +4735,7 @@
         <v>0.9739</v>
       </c>
       <c r="H160">
-        <v>0.9661</v>
+        <v>0.9665</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5148,10 +5148,10 @@
         <v>38</v>
       </c>
       <c r="G176">
-        <v>0.1527</v>
+        <v>0.1632</v>
       </c>
       <c r="H176">
-        <v>0.1299</v>
+        <v>0.1388</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5174,10 +5174,10 @@
         <v>39</v>
       </c>
       <c r="G177">
-        <v>0.0959</v>
+        <v>0.097</v>
       </c>
       <c r="H177">
-        <v>0.0761</v>
+        <v>0.07729999999999999</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -5200,10 +5200,10 @@
         <v>40</v>
       </c>
       <c r="G178">
-        <v>0.1562</v>
+        <v>0.1555</v>
       </c>
       <c r="H178">
-        <v>0.1352</v>
+        <v>0.1344</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5226,10 +5226,10 @@
         <v>41</v>
       </c>
       <c r="G179">
-        <v>0.1516</v>
+        <v>0.149</v>
       </c>
       <c r="H179">
-        <v>0.1256</v>
+        <v>0.1258</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5252,10 +5252,10 @@
         <v>42</v>
       </c>
       <c r="G180">
-        <v>0.3588</v>
+        <v>0.3601</v>
       </c>
       <c r="H180">
-        <v>0.3413</v>
+        <v>0.3429</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5304,10 +5304,10 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.4624</v>
+        <v>0.4647</v>
       </c>
       <c r="H182">
-        <v>0.4268</v>
+        <v>0.4233</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5330,10 +5330,10 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.3504</v>
+        <v>0.3487</v>
       </c>
       <c r="H183">
-        <v>0.3078</v>
+        <v>0.3063</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5356,10 +5356,10 @@
         <v>47</v>
       </c>
       <c r="G184">
-        <v>0.5108</v>
+        <v>0.5083</v>
       </c>
       <c r="H184">
-        <v>0.4654</v>
+        <v>0.4637</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5408,10 +5408,10 @@
         <v>49</v>
       </c>
       <c r="G186">
-        <v>0.8807</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="H186">
-        <v>0.8495</v>
+        <v>0.8243</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5434,10 +5434,10 @@
         <v>50</v>
       </c>
       <c r="G187">
-        <v>0.9634</v>
+        <v>0.9637</v>
       </c>
       <c r="H187">
-        <v>0.9549</v>
+        <v>0.9553</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5460,10 +5460,10 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.8789</v>
+        <v>0.8799</v>
       </c>
       <c r="H188">
-        <v>0.8489</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5902,10 +5902,10 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.1618</v>
+        <v>0.1693</v>
       </c>
       <c r="H205">
-        <v>0.1359</v>
+        <v>0.1417</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5928,10 +5928,10 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.1123</v>
+        <v>0.1009</v>
       </c>
       <c r="H206">
-        <v>0.0893</v>
+        <v>0.0806</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -5954,10 +5954,10 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.1854</v>
+        <v>0.1731</v>
       </c>
       <c r="H207">
-        <v>0.142</v>
+        <v>0.1352</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5980,10 +5980,10 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.1833</v>
+        <v>0.1756</v>
       </c>
       <c r="H208">
-        <v>0.1502</v>
+        <v>0.1456</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6006,10 +6006,10 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.4203</v>
+        <v>0.3814</v>
       </c>
       <c r="H209">
-        <v>0.3846</v>
+        <v>0.3417</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6032,10 +6032,10 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.4441</v>
+        <v>0.4348</v>
       </c>
       <c r="H210">
-        <v>0.4054</v>
+        <v>0.3937</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6058,10 +6058,10 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.5732</v>
+        <v>0.5767</v>
       </c>
       <c r="H211">
-        <v>0.5376</v>
+        <v>0.5353</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -6084,10 +6084,10 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.343</v>
+        <v>0.3466</v>
       </c>
       <c r="H212">
-        <v>0.2925</v>
+        <v>0.2952</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -6110,10 +6110,10 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.5348000000000001</v>
+        <v>0.5451</v>
       </c>
       <c r="H213">
-        <v>0.498</v>
+        <v>0.5118</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -6136,10 +6136,10 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.9053</v>
+        <v>0.9063</v>
       </c>
       <c r="H214">
-        <v>0.8762</v>
+        <v>0.8831</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -6162,10 +6162,10 @@
         <v>49</v>
       </c>
       <c r="G215">
-        <v>0.8902</v>
+        <v>0.8627</v>
       </c>
       <c r="H215">
-        <v>0.8605</v>
+        <v>0.8355</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -6188,10 +6188,10 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>0.967</v>
+        <v>0.965</v>
       </c>
       <c r="H216">
-        <v>0.9558</v>
+        <v>0.9539</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -6214,10 +6214,10 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.8921</v>
+        <v>0.8928</v>
       </c>
       <c r="H217">
-        <v>0.868</v>
+        <v>0.8678</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -6240,10 +6240,10 @@
         <v>52</v>
       </c>
       <c r="G218">
-        <v>0.9508</v>
+        <v>0.9536</v>
       </c>
       <c r="H218">
-        <v>0.9389999999999999</v>
+        <v>0.9416</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -6656,10 +6656,10 @@
         <v>38</v>
       </c>
       <c r="G234">
-        <v>0.2926</v>
+        <v>0.2987</v>
       </c>
       <c r="H234">
-        <v>0.2625</v>
+        <v>0.2693</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -6682,10 +6682,10 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.2052</v>
+        <v>0.2035</v>
       </c>
       <c r="H235">
-        <v>0.1687</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -6760,10 +6760,10 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.5256</v>
+        <v>0.5309</v>
       </c>
       <c r="H238">
-        <v>0.4929</v>
+        <v>0.4969</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -6812,10 +6812,10 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.6922</v>
+        <v>0.6937</v>
       </c>
       <c r="H240">
-        <v>0.6496</v>
+        <v>0.6513</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -6838,10 +6838,10 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.7075</v>
+        <v>0.7048</v>
       </c>
       <c r="H241">
-        <v>0.657</v>
+        <v>0.6534</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -6916,10 +6916,10 @@
         <v>49</v>
       </c>
       <c r="G244">
-        <v>0.9443</v>
+        <v>0.9351</v>
       </c>
       <c r="H244">
-        <v>0.9297</v>
+        <v>0.9171</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -6942,10 +6942,10 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9801</v>
+        <v>0.9805</v>
       </c>
       <c r="H245">
-        <v>0.9742</v>
+        <v>0.9746</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -7410,10 +7410,10 @@
         <v>38</v>
       </c>
       <c r="G263">
-        <v>0.1534</v>
+        <v>0.1667</v>
       </c>
       <c r="H263">
-        <v>0.1301</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -7462,10 +7462,10 @@
         <v>40</v>
       </c>
       <c r="G265">
-        <v>0.1578</v>
+        <v>0.1564</v>
       </c>
       <c r="H265">
-        <v>0.1199</v>
+        <v>0.1183</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7488,10 +7488,10 @@
         <v>41</v>
       </c>
       <c r="G266">
-        <v>0.1598</v>
+        <v>0.1584</v>
       </c>
       <c r="H266">
-        <v>0.1242</v>
+        <v>0.1226</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3539</v>
+        <v>0.3544</v>
       </c>
       <c r="H267">
-        <v>0.3092</v>
+        <v>0.3069</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7566,10 +7566,10 @@
         <v>44</v>
       </c>
       <c r="G269">
-        <v>0.5346</v>
+        <v>0.5363</v>
       </c>
       <c r="H269">
-        <v>0.4892</v>
+        <v>0.4917</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.502</v>
+        <v>0.4882</v>
       </c>
       <c r="H270">
-        <v>0.4652</v>
+        <v>0.4549</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7644,10 +7644,10 @@
         <v>48</v>
       </c>
       <c r="G272">
-        <v>0.9018</v>
+        <v>0.9014</v>
       </c>
       <c r="H272">
-        <v>0.8694</v>
+        <v>0.8687</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7670,10 +7670,10 @@
         <v>49</v>
       </c>
       <c r="G273">
-        <v>0.882</v>
+        <v>0.8522</v>
       </c>
       <c r="H273">
-        <v>0.8548</v>
+        <v>0.8219</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7722,10 +7722,10 @@
         <v>51</v>
       </c>
       <c r="G275">
-        <v>0.8779</v>
+        <v>0.8786</v>
       </c>
       <c r="H275">
-        <v>0.852</v>
+        <v>0.8531</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -8164,10 +8164,10 @@
         <v>38</v>
       </c>
       <c r="G292">
-        <v>0.0375</v>
+        <v>0.0403</v>
       </c>
       <c r="H292">
-        <v>0.0303</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.0804</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="H296">
-        <v>0.0598</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.1238</v>
+        <v>0.1169</v>
       </c>
       <c r="H299">
-        <v>0.09470000000000001</v>
+        <v>0.09370000000000001</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8398,10 +8398,10 @@
         <v>47</v>
       </c>
       <c r="G301">
-        <v>0.1306</v>
+        <v>0.1313</v>
       </c>
       <c r="H301">
-        <v>0.0982</v>
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8424,10 +8424,10 @@
         <v>49</v>
       </c>
       <c r="G302">
-        <v>0.466</v>
+        <v>0.4296</v>
       </c>
       <c r="H302">
-        <v>0.4334</v>
+        <v>0.3961</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -8918,10 +8918,10 @@
         <v>38</v>
       </c>
       <c r="G321">
-        <v>0.0377</v>
+        <v>0.0487</v>
       </c>
       <c r="H321">
-        <v>0.0296</v>
+        <v>0.0383</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8944,10 +8944,10 @@
         <v>39</v>
       </c>
       <c r="G322">
-        <v>0.0195</v>
+        <v>0.0228</v>
       </c>
       <c r="H322">
-        <v>0.0143</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8970,10 +8970,10 @@
         <v>40</v>
       </c>
       <c r="G323">
-        <v>0.0307</v>
+        <v>0.0379</v>
       </c>
       <c r="H323">
-        <v>0.0233</v>
+        <v>0.0291</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8996,10 +8996,10 @@
         <v>41</v>
       </c>
       <c r="G324">
-        <v>0.0284</v>
+        <v>0.0334</v>
       </c>
       <c r="H324">
-        <v>0.0229</v>
+        <v>0.0265</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.0803</v>
+        <v>0.0969</v>
       </c>
       <c r="H325">
-        <v>0.0586</v>
+        <v>0.0684</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9048,10 +9048,10 @@
         <v>43</v>
       </c>
       <c r="G326">
-        <v>0.0786</v>
+        <v>0.0878</v>
       </c>
       <c r="H326">
-        <v>0.0597</v>
+        <v>0.0677</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -9074,10 +9074,10 @@
         <v>44</v>
       </c>
       <c r="G327">
-        <v>0.1505</v>
+        <v>0.1757</v>
       </c>
       <c r="H327">
-        <v>0.1193</v>
+        <v>0.1416</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -9100,10 +9100,10 @@
         <v>45</v>
       </c>
       <c r="G328">
-        <v>0.1395</v>
+        <v>0.1645</v>
       </c>
       <c r="H328">
-        <v>0.1098</v>
+        <v>0.1373</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9126,10 +9126,10 @@
         <v>46</v>
       </c>
       <c r="G329">
-        <v>0.0703</v>
+        <v>0.0829</v>
       </c>
       <c r="H329">
-        <v>0.0557</v>
+        <v>0.0649</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9152,10 +9152,10 @@
         <v>47</v>
       </c>
       <c r="G330">
-        <v>0.1452</v>
+        <v>0.1781</v>
       </c>
       <c r="H330">
-        <v>0.118</v>
+        <v>0.1478</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9178,10 +9178,10 @@
         <v>48</v>
       </c>
       <c r="G331">
-        <v>0.5666</v>
+        <v>0.6039</v>
       </c>
       <c r="H331">
-        <v>0.534</v>
+        <v>0.5704</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.8012</v>
+        <v>0.8267</v>
       </c>
       <c r="H332">
-        <v>0.7554999999999999</v>
+        <v>0.7881</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9230,10 +9230,10 @@
         <v>51</v>
       </c>
       <c r="G333">
-        <v>0.5203</v>
+        <v>0.591</v>
       </c>
       <c r="H333">
-        <v>0.4869</v>
+        <v>0.5467</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -9256,10 +9256,10 @@
         <v>52</v>
       </c>
       <c r="G334">
-        <v>0.801</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="H334">
-        <v>0.7691</v>
+        <v>0.8045</v>
       </c>
     </row>
     <row r="335" spans="1:8">
@@ -9672,7 +9672,7 @@
         <v>38</v>
       </c>
       <c r="G350">
-        <v>0.02</v>
+        <v>0.0204</v>
       </c>
       <c r="H350">
         <v>0.0154</v>
@@ -9828,10 +9828,10 @@
         <v>44</v>
       </c>
       <c r="G356">
-        <v>0.0451</v>
+        <v>0.0447</v>
       </c>
       <c r="H356">
-        <v>0.0366</v>
+        <v>0.0363</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9854,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="G357">
-        <v>0.0442</v>
+        <v>0.0461</v>
       </c>
       <c r="H357">
-        <v>0.033</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
-        <v>0.0258</v>
+        <v>0.0254</v>
       </c>
       <c r="H358">
-        <v>0.0199</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.2445</v>
+        <v>0.2119</v>
       </c>
       <c r="H361">
-        <v>0.1988</v>
+        <v>0.1733</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.0385</v>
+        <v>0.0392</v>
       </c>
       <c r="H379">
-        <v>0.0322</v>
+        <v>0.0331</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.08110000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="H383">
-        <v>0.06560000000000001</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.074</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="H384">
-        <v>0.0606</v>
+        <v>0.0587</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.1511</v>
+        <v>0.1505</v>
       </c>
       <c r="H385">
-        <v>0.1211</v>
+        <v>0.1201</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.132</v>
+        <v>0.1322</v>
       </c>
       <c r="H386">
-        <v>0.1079</v>
+        <v>0.1072</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10660,10 +10660,10 @@
         <v>47</v>
       </c>
       <c r="G388">
-        <v>0.148</v>
+        <v>0.1469</v>
       </c>
       <c r="H388">
-        <v>0.1221</v>
+        <v>0.1214</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -10712,10 +10712,10 @@
         <v>49</v>
       </c>
       <c r="G390">
-        <v>0.5131</v>
+        <v>0.4533</v>
       </c>
       <c r="H390">
-        <v>0.4797</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -11180,10 +11180,10 @@
         <v>38</v>
       </c>
       <c r="G408">
-        <v>0.0277</v>
+        <v>0.027</v>
       </c>
       <c r="H408">
-        <v>0.0214</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11258,7 +11258,7 @@
         <v>41</v>
       </c>
       <c r="G411">
-        <v>0.0178</v>
+        <v>0.0175</v>
       </c>
       <c r="H411">
         <v>0.0135</v>
@@ -11310,7 +11310,7 @@
         <v>43</v>
       </c>
       <c r="G413">
-        <v>0.0339</v>
+        <v>0.0335</v>
       </c>
       <c r="H413">
         <v>0.0261</v>
@@ -11362,10 +11362,10 @@
         <v>45</v>
       </c>
       <c r="G415">
-        <v>0.061</v>
+        <v>0.0584</v>
       </c>
       <c r="H415">
-        <v>0.0492</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -11466,10 +11466,10 @@
         <v>49</v>
       </c>
       <c r="G419">
-        <v>0.2309</v>
+        <v>0.1955</v>
       </c>
       <c r="H419">
-        <v>0.199</v>
+        <v>0.1648</v>
       </c>
     </row>
     <row r="420" spans="1:8">

--- a/nba/public/data/nba_series_probs.xlsx
+++ b/nba/public/data/nba_series_probs.xlsx
@@ -624,10 +624,10 @@
         <v>39</v>
       </c>
       <c r="G2">
-        <v>0.4446</v>
+        <v>0.3613</v>
       </c>
       <c r="H2">
-        <v>0.3922</v>
+        <v>0.3127</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,10 +650,10 @@
         <v>40</v>
       </c>
       <c r="G3">
-        <v>0.5484</v>
+        <v>0.4614</v>
       </c>
       <c r="H3">
-        <v>0.5008</v>
+        <v>0.4164</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -676,10 +676,10 @@
         <v>41</v>
       </c>
       <c r="G4">
-        <v>0.5145999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H4">
-        <v>0.4844</v>
+        <v>0.4966</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -702,10 +702,10 @@
         <v>42</v>
       </c>
       <c r="G5">
-        <v>0.745</v>
+        <v>0.7238</v>
       </c>
       <c r="H5">
-        <v>0.7344000000000001</v>
+        <v>0.6992</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -728,10 +728,10 @@
         <v>43</v>
       </c>
       <c r="G6">
-        <v>0.7769</v>
+        <v>0.7703</v>
       </c>
       <c r="H6">
-        <v>0.7461</v>
+        <v>0.7327</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -754,10 +754,10 @@
         <v>44</v>
       </c>
       <c r="G7">
-        <v>0.8612</v>
+        <v>0.8138</v>
       </c>
       <c r="H7">
-        <v>0.8368</v>
+        <v>0.7954</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -780,10 +780,10 @@
         <v>45</v>
       </c>
       <c r="G8">
-        <v>0.8583</v>
+        <v>0.8222</v>
       </c>
       <c r="H8">
-        <v>0.8307</v>
+        <v>0.7921</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -806,10 +806,10 @@
         <v>46</v>
       </c>
       <c r="G9">
-        <v>0.7307</v>
+        <v>0.7157</v>
       </c>
       <c r="H9">
-        <v>0.7013</v>
+        <v>0.6895</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -832,10 +832,10 @@
         <v>47</v>
       </c>
       <c r="G10">
-        <v>0.862</v>
+        <v>0.8474</v>
       </c>
       <c r="H10">
-        <v>0.8333</v>
+        <v>0.8134</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -858,10 +858,10 @@
         <v>48</v>
       </c>
       <c r="G11">
-        <v>0.9668</v>
+        <v>0.9608</v>
       </c>
       <c r="H11">
-        <v>0.9597</v>
+        <v>0.9516</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -884,10 +884,10 @@
         <v>49</v>
       </c>
       <c r="G12">
-        <v>0.9617</v>
+        <v>0.9579</v>
       </c>
       <c r="H12">
-        <v>0.9513</v>
+        <v>0.9483</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -910,10 +910,10 @@
         <v>50</v>
       </c>
       <c r="G13">
-        <v>0.9846</v>
+        <v>0.9829</v>
       </c>
       <c r="H13">
-        <v>0.9796</v>
+        <v>0.9774</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -936,10 +936,10 @@
         <v>51</v>
       </c>
       <c r="G14">
-        <v>0.9669</v>
+        <v>0.9654</v>
       </c>
       <c r="H14">
-        <v>0.9608</v>
+        <v>0.9582000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -962,10 +962,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>0.9785</v>
+        <v>0.9771</v>
       </c>
       <c r="H15">
-        <v>0.973</v>
+        <v>0.971</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1378,10 +1378,10 @@
         <v>38</v>
       </c>
       <c r="G31">
-        <v>0.6078</v>
+        <v>0.6873</v>
       </c>
       <c r="H31">
-        <v>0.5554</v>
+        <v>0.6387</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1404,10 +1404,10 @@
         <v>40</v>
       </c>
       <c r="G32">
-        <v>0.6869</v>
+        <v>0.6259</v>
       </c>
       <c r="H32">
-        <v>0.6644</v>
+        <v>0.6031</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1430,10 +1430,10 @@
         <v>41</v>
       </c>
       <c r="G33">
-        <v>0.655</v>
+        <v>0.705</v>
       </c>
       <c r="H33">
-        <v>0.6254</v>
+        <v>0.6768999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1456,10 +1456,10 @@
         <v>42</v>
       </c>
       <c r="G34">
-        <v>0.868</v>
+        <v>0.8743</v>
       </c>
       <c r="H34">
-        <v>0.8379</v>
+        <v>0.8431999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1482,10 +1482,10 @@
         <v>43</v>
       </c>
       <c r="G35">
-        <v>0.8832</v>
+        <v>0.8921</v>
       </c>
       <c r="H35">
-        <v>0.8582</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1511,7 +1511,7 @@
         <v>0.9227</v>
       </c>
       <c r="H36">
-        <v>0.903</v>
+        <v>0.9036</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1534,10 +1534,10 @@
         <v>45</v>
       </c>
       <c r="G37">
-        <v>0.9194</v>
+        <v>0.9066</v>
       </c>
       <c r="H37">
-        <v>0.8991</v>
+        <v>0.8848</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1560,10 +1560,10 @@
         <v>46</v>
       </c>
       <c r="G38">
-        <v>0.8333</v>
+        <v>0.825</v>
       </c>
       <c r="H38">
-        <v>0.7965</v>
+        <v>0.7922</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1586,10 +1586,10 @@
         <v>47</v>
       </c>
       <c r="G39">
-        <v>0.9264</v>
+        <v>0.9265</v>
       </c>
       <c r="H39">
-        <v>0.9025</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1612,10 +1612,10 @@
         <v>48</v>
       </c>
       <c r="G40">
-        <v>0.9852</v>
+        <v>0.9846</v>
       </c>
       <c r="H40">
-        <v>0.9806</v>
+        <v>0.9796</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1638,10 +1638,10 @@
         <v>49</v>
       </c>
       <c r="G41">
-        <v>0.9833</v>
+        <v>0.9825</v>
       </c>
       <c r="H41">
-        <v>0.9772</v>
+        <v>0.9762</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1664,10 +1664,10 @@
         <v>50</v>
       </c>
       <c r="G42">
-        <v>0.9888</v>
+        <v>0.9886</v>
       </c>
       <c r="H42">
-        <v>0.9867</v>
+        <v>0.9862</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1690,10 +1690,10 @@
         <v>51</v>
       </c>
       <c r="G43">
-        <v>0.9837</v>
+        <v>0.9845</v>
       </c>
       <c r="H43">
-        <v>0.978</v>
+        <v>0.9796</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1716,10 +1716,10 @@
         <v>52</v>
       </c>
       <c r="G44">
-        <v>0.9883999999999999</v>
+        <v>0.9889</v>
       </c>
       <c r="H44">
-        <v>0.9842</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -2132,10 +2132,10 @@
         <v>38</v>
       </c>
       <c r="G60">
-        <v>0.4992</v>
+        <v>0.5836</v>
       </c>
       <c r="H60">
-        <v>0.4516</v>
+        <v>0.5386</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -2158,10 +2158,10 @@
         <v>39</v>
       </c>
       <c r="G61">
-        <v>0.3356</v>
+        <v>0.3969</v>
       </c>
       <c r="H61">
-        <v>0.3131</v>
+        <v>0.3741</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -2184,10 +2184,10 @@
         <v>41</v>
       </c>
       <c r="G62">
-        <v>0.5125999999999999</v>
+        <v>0.6151</v>
       </c>
       <c r="H62">
-        <v>0.4767</v>
+        <v>0.5804</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -2210,10 +2210,10 @@
         <v>42</v>
       </c>
       <c r="G63">
-        <v>0.7674</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H63">
-        <v>0.7174</v>
+        <v>0.7859</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2236,10 +2236,10 @@
         <v>43</v>
       </c>
       <c r="G64">
-        <v>0.7675</v>
+        <v>0.8427</v>
       </c>
       <c r="H64">
-        <v>0.7204</v>
+        <v>0.8083</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -2262,10 +2262,10 @@
         <v>44</v>
       </c>
       <c r="G65">
-        <v>0.8656</v>
+        <v>0.8996</v>
       </c>
       <c r="H65">
-        <v>0.8445</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2288,10 +2288,10 @@
         <v>45</v>
       </c>
       <c r="G66">
-        <v>0.8648</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="H66">
-        <v>0.8269</v>
+        <v>0.8487</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -2314,10 +2314,10 @@
         <v>46</v>
       </c>
       <c r="G67">
-        <v>0.7343</v>
+        <v>0.7713</v>
       </c>
       <c r="H67">
-        <v>0.6968</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -2340,10 +2340,10 @@
         <v>47</v>
       </c>
       <c r="G68">
-        <v>0.8817</v>
+        <v>0.8955</v>
       </c>
       <c r="H68">
-        <v>0.8436</v>
+        <v>0.8646</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2366,10 +2366,10 @@
         <v>48</v>
       </c>
       <c r="G69">
-        <v>0.9796</v>
+        <v>0.9782</v>
       </c>
       <c r="H69">
-        <v>0.9729</v>
+        <v>0.9706</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="G70">
-        <v>0.9709</v>
+        <v>0.9748</v>
       </c>
       <c r="H70">
-        <v>0.9621</v>
+        <v>0.9663</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -2418,10 +2418,10 @@
         <v>50</v>
       </c>
       <c r="G71">
-        <v>0.9871</v>
+        <v>0.9879</v>
       </c>
       <c r="H71">
-        <v>0.9847</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -2444,10 +2444,10 @@
         <v>51</v>
       </c>
       <c r="G72">
-        <v>0.9705</v>
+        <v>0.9764</v>
       </c>
       <c r="H72">
-        <v>0.9619</v>
+        <v>0.9695</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -2470,10 +2470,10 @@
         <v>52</v>
       </c>
       <c r="G73">
-        <v>0.9852</v>
+        <v>0.9855</v>
       </c>
       <c r="H73">
-        <v>0.9805</v>
+        <v>0.9806</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -2886,10 +2886,10 @@
         <v>38</v>
       </c>
       <c r="G89">
-        <v>0.5155999999999999</v>
+        <v>0.5034</v>
       </c>
       <c r="H89">
-        <v>0.4854</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -2912,10 +2912,10 @@
         <v>39</v>
       </c>
       <c r="G90">
-        <v>0.3746</v>
+        <v>0.3231</v>
       </c>
       <c r="H90">
-        <v>0.345</v>
+        <v>0.295</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -2938,10 +2938,10 @@
         <v>40</v>
       </c>
       <c r="G91">
-        <v>0.5233</v>
+        <v>0.4196</v>
       </c>
       <c r="H91">
-        <v>0.4874</v>
+        <v>0.3849</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -2964,10 +2964,10 @@
         <v>42</v>
       </c>
       <c r="G92">
-        <v>0.7509</v>
+        <v>0.7533</v>
       </c>
       <c r="H92">
-        <v>0.7119</v>
+        <v>0.7165</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -2990,10 +2990,10 @@
         <v>43</v>
       </c>
       <c r="G93">
-        <v>0.8015</v>
+        <v>0.7588</v>
       </c>
       <c r="H93">
-        <v>0.7648</v>
+        <v>0.7181</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -3016,10 +3016,10 @@
         <v>44</v>
       </c>
       <c r="G94">
-        <v>0.8742</v>
+        <v>0.8359</v>
       </c>
       <c r="H94">
-        <v>0.851</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -3042,10 +3042,10 @@
         <v>45</v>
       </c>
       <c r="G95">
-        <v>0.8544</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="H95">
-        <v>0.8244</v>
+        <v>0.7957</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -3068,10 +3068,10 @@
         <v>46</v>
       </c>
       <c r="G96">
-        <v>0.7306</v>
+        <v>0.6835</v>
       </c>
       <c r="H96">
-        <v>0.6913</v>
+        <v>0.6429</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -3094,10 +3094,10 @@
         <v>47</v>
       </c>
       <c r="G97">
-        <v>0.8774</v>
+        <v>0.8647</v>
       </c>
       <c r="H97">
-        <v>0.8416</v>
+        <v>0.8245</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3120,10 +3120,10 @@
         <v>48</v>
       </c>
       <c r="G98">
-        <v>0.9774</v>
+        <v>0.9761</v>
       </c>
       <c r="H98">
-        <v>0.9711</v>
+        <v>0.9702</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -3146,10 +3146,10 @@
         <v>49</v>
       </c>
       <c r="G99">
-        <v>0.9735</v>
+        <v>0.9707</v>
       </c>
       <c r="H99">
-        <v>0.9666</v>
+        <v>0.962</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -3172,10 +3172,10 @@
         <v>50</v>
       </c>
       <c r="G100">
-        <v>0.9868</v>
+        <v>0.9856</v>
       </c>
       <c r="H100">
-        <v>0.9833</v>
+        <v>0.9821</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -3198,10 +3198,10 @@
         <v>51</v>
       </c>
       <c r="G101">
-        <v>0.9729</v>
+        <v>0.9721</v>
       </c>
       <c r="H101">
-        <v>0.967</v>
+        <v>0.9678</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -3224,10 +3224,10 @@
         <v>52</v>
       </c>
       <c r="G102">
-        <v>0.9865</v>
+        <v>0.986</v>
       </c>
       <c r="H102">
-        <v>0.9825</v>
+        <v>0.982</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -3640,10 +3640,10 @@
         <v>38</v>
       </c>
       <c r="G118">
-        <v>0.2656</v>
+        <v>0.3008</v>
       </c>
       <c r="H118">
-        <v>0.255</v>
+        <v>0.2762</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -3666,10 +3666,10 @@
         <v>39</v>
       </c>
       <c r="G119">
-        <v>0.1621</v>
+        <v>0.1568</v>
       </c>
       <c r="H119">
-        <v>0.132</v>
+        <v>0.1257</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -3692,10 +3692,10 @@
         <v>40</v>
       </c>
       <c r="G120">
-        <v>0.2826</v>
+        <v>0.2141</v>
       </c>
       <c r="H120">
-        <v>0.2326</v>
+        <v>0.182</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -3718,10 +3718,10 @@
         <v>41</v>
       </c>
       <c r="G121">
-        <v>0.2881</v>
+        <v>0.2835</v>
       </c>
       <c r="H121">
-        <v>0.2491</v>
+        <v>0.2467</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -3744,10 +3744,10 @@
         <v>43</v>
       </c>
       <c r="G122">
-        <v>0.5493</v>
+        <v>0.5579</v>
       </c>
       <c r="H122">
-        <v>0.516</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -3770,10 +3770,10 @@
         <v>44</v>
       </c>
       <c r="G123">
-        <v>0.6571</v>
+        <v>0.6309</v>
       </c>
       <c r="H123">
-        <v>0.6399</v>
+        <v>0.5974</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -3796,10 +3796,10 @@
         <v>45</v>
       </c>
       <c r="G124">
-        <v>0.6583</v>
+        <v>0.6091</v>
       </c>
       <c r="H124">
-        <v>0.6186</v>
+        <v>0.5699</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -3822,10 +3822,10 @@
         <v>46</v>
       </c>
       <c r="G125">
-        <v>0.5031</v>
+        <v>0.4646</v>
       </c>
       <c r="H125">
-        <v>0.4691</v>
+        <v>0.4268</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -3848,10 +3848,10 @@
         <v>47</v>
       </c>
       <c r="G126">
-        <v>0.6931</v>
+        <v>0.6821</v>
       </c>
       <c r="H126">
-        <v>0.6456</v>
+        <v>0.6321</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -3874,10 +3874,10 @@
         <v>48</v>
       </c>
       <c r="G127">
-        <v>0.9419</v>
+        <v>0.945</v>
       </c>
       <c r="H127">
-        <v>0.9218</v>
+        <v>0.9271</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -3900,10 +3900,10 @@
         <v>49</v>
       </c>
       <c r="G128">
-        <v>0.9316</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="H128">
-        <v>0.9031</v>
+        <v>0.8987000000000001</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -3926,10 +3926,10 @@
         <v>50</v>
       </c>
       <c r="G129">
-        <v>0.9786</v>
+        <v>0.9762</v>
       </c>
       <c r="H129">
-        <v>0.9721</v>
+        <v>0.9689</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -3952,10 +3952,10 @@
         <v>51</v>
       </c>
       <c r="G130">
-        <v>0.9358</v>
+        <v>0.9333</v>
       </c>
       <c r="H130">
-        <v>0.9197</v>
+        <v>0.9201</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -3978,10 +3978,10 @@
         <v>52</v>
       </c>
       <c r="G131">
-        <v>0.9736</v>
+        <v>0.97</v>
       </c>
       <c r="H131">
-        <v>0.9644</v>
+        <v>0.9617</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -4394,10 +4394,10 @@
         <v>38</v>
       </c>
       <c r="G147">
-        <v>0.2539</v>
+        <v>0.2673</v>
       </c>
       <c r="H147">
-        <v>0.2231</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -4420,10 +4420,10 @@
         <v>39</v>
       </c>
       <c r="G148">
-        <v>0.1418</v>
+        <v>0.135</v>
       </c>
       <c r="H148">
-        <v>0.1168</v>
+        <v>0.1079</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -4446,10 +4446,10 @@
         <v>40</v>
       </c>
       <c r="G149">
-        <v>0.2796</v>
+        <v>0.1917</v>
       </c>
       <c r="H149">
-        <v>0.2325</v>
+        <v>0.1573</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -4472,10 +4472,10 @@
         <v>41</v>
       </c>
       <c r="G150">
-        <v>0.2352</v>
+        <v>0.2819</v>
       </c>
       <c r="H150">
-        <v>0.1985</v>
+        <v>0.2412</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -4498,10 +4498,10 @@
         <v>42</v>
       </c>
       <c r="G151">
-        <v>0.484</v>
+        <v>0.482</v>
       </c>
       <c r="H151">
-        <v>0.4507</v>
+        <v>0.4421</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -4524,10 +4524,10 @@
         <v>44</v>
       </c>
       <c r="G152">
-        <v>0.6502</v>
+        <v>0.614</v>
       </c>
       <c r="H152">
-        <v>0.6101</v>
+        <v>0.5874</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -4550,10 +4550,10 @@
         <v>45</v>
       </c>
       <c r="G153">
-        <v>0.6063</v>
+        <v>0.5757</v>
       </c>
       <c r="H153">
-        <v>0.5652</v>
+        <v>0.5222</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -4576,10 +4576,10 @@
         <v>46</v>
       </c>
       <c r="G154">
-        <v>0.4878</v>
+        <v>0.437</v>
       </c>
       <c r="H154">
-        <v>0.4476</v>
+        <v>0.4016</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -4602,10 +4602,10 @@
         <v>47</v>
       </c>
       <c r="G155">
-        <v>0.6548</v>
+        <v>0.675</v>
       </c>
       <c r="H155">
-        <v>0.6014</v>
+        <v>0.6203</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -4628,10 +4628,10 @@
         <v>48</v>
       </c>
       <c r="G156">
-        <v>0.9371</v>
+        <v>0.9288</v>
       </c>
       <c r="H156">
-        <v>0.9137</v>
+        <v>0.9062</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -4654,10 +4654,10 @@
         <v>49</v>
       </c>
       <c r="G157">
-        <v>0.9323</v>
+        <v>0.9112</v>
       </c>
       <c r="H157">
-        <v>0.9122</v>
+        <v>0.8909</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -4680,10 +4680,10 @@
         <v>50</v>
       </c>
       <c r="G158">
-        <v>0.9795</v>
+        <v>0.9718</v>
       </c>
       <c r="H158">
-        <v>0.973</v>
+        <v>0.9639</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -4706,10 +4706,10 @@
         <v>51</v>
       </c>
       <c r="G159">
-        <v>0.9413</v>
+        <v>0.9212</v>
       </c>
       <c r="H159">
-        <v>0.9276</v>
+        <v>0.9006999999999999</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -4732,10 +4732,10 @@
         <v>52</v>
       </c>
       <c r="G160">
-        <v>0.9739</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="H160">
-        <v>0.9665</v>
+        <v>0.9617</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -5148,10 +5148,10 @@
         <v>38</v>
       </c>
       <c r="G176">
-        <v>0.1632</v>
+        <v>0.2046</v>
       </c>
       <c r="H176">
-        <v>0.1388</v>
+        <v>0.1862</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -5174,7 +5174,7 @@
         <v>39</v>
       </c>
       <c r="G177">
-        <v>0.097</v>
+        <v>0.0964</v>
       </c>
       <c r="H177">
         <v>0.07729999999999999</v>
@@ -5200,10 +5200,10 @@
         <v>40</v>
       </c>
       <c r="G178">
-        <v>0.1555</v>
+        <v>0.1185</v>
       </c>
       <c r="H178">
-        <v>0.1344</v>
+        <v>0.1004</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -5226,10 +5226,10 @@
         <v>41</v>
       </c>
       <c r="G179">
-        <v>0.149</v>
+        <v>0.192</v>
       </c>
       <c r="H179">
-        <v>0.1258</v>
+        <v>0.1641</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -5252,10 +5252,10 @@
         <v>42</v>
       </c>
       <c r="G180">
-        <v>0.3601</v>
+        <v>0.4026</v>
       </c>
       <c r="H180">
-        <v>0.3429</v>
+        <v>0.3691</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -5278,10 +5278,10 @@
         <v>43</v>
       </c>
       <c r="G181">
-        <v>0.3899</v>
+        <v>0.4126</v>
       </c>
       <c r="H181">
-        <v>0.3498</v>
+        <v>0.386</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -5304,10 +5304,10 @@
         <v>45</v>
       </c>
       <c r="G182">
-        <v>0.4647</v>
+        <v>0.5044</v>
       </c>
       <c r="H182">
-        <v>0.4233</v>
+        <v>0.4623</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -5330,10 +5330,10 @@
         <v>46</v>
       </c>
       <c r="G183">
-        <v>0.3487</v>
+        <v>0.3726</v>
       </c>
       <c r="H183">
-        <v>0.3063</v>
+        <v>0.3289</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -5356,10 +5356,10 @@
         <v>47</v>
       </c>
       <c r="G184">
-        <v>0.5083</v>
+        <v>0.545</v>
       </c>
       <c r="H184">
-        <v>0.4637</v>
+        <v>0.4976</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -5382,10 +5382,10 @@
         <v>48</v>
       </c>
       <c r="G185">
-        <v>0.8804</v>
+        <v>0.8903</v>
       </c>
       <c r="H185">
-        <v>0.8507</v>
+        <v>0.8651</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -5408,10 +5408,10 @@
         <v>49</v>
       </c>
       <c r="G186">
-        <v>0.8584000000000001</v>
+        <v>0.8706</v>
       </c>
       <c r="H186">
-        <v>0.8243</v>
+        <v>0.8399</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -5434,10 +5434,10 @@
         <v>50</v>
       </c>
       <c r="G187">
-        <v>0.9637</v>
+        <v>0.9643</v>
       </c>
       <c r="H187">
-        <v>0.9553</v>
+        <v>0.9587</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -5460,10 +5460,10 @@
         <v>51</v>
       </c>
       <c r="G188">
-        <v>0.8799</v>
+        <v>0.8753</v>
       </c>
       <c r="H188">
-        <v>0.8495</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -5486,10 +5486,10 @@
         <v>52</v>
       </c>
       <c r="G189">
-        <v>0.961</v>
+        <v>0.9623</v>
       </c>
       <c r="H189">
-        <v>0.9520999999999999</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -5902,10 +5902,10 @@
         <v>38</v>
       </c>
       <c r="G205">
-        <v>0.1693</v>
+        <v>0.2079</v>
       </c>
       <c r="H205">
-        <v>0.1417</v>
+        <v>0.1778</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -5928,10 +5928,10 @@
         <v>39</v>
       </c>
       <c r="G206">
-        <v>0.1009</v>
+        <v>0.1152</v>
       </c>
       <c r="H206">
-        <v>0.0806</v>
+        <v>0.0934</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -5954,10 +5954,10 @@
         <v>40</v>
       </c>
       <c r="G207">
-        <v>0.1731</v>
+        <v>0.1513</v>
       </c>
       <c r="H207">
-        <v>0.1352</v>
+        <v>0.1285</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -5980,10 +5980,10 @@
         <v>41</v>
       </c>
       <c r="G208">
-        <v>0.1756</v>
+        <v>0.2043</v>
       </c>
       <c r="H208">
-        <v>0.1456</v>
+        <v>0.1729</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -6006,10 +6006,10 @@
         <v>42</v>
       </c>
       <c r="G209">
-        <v>0.3814</v>
+        <v>0.4301</v>
       </c>
       <c r="H209">
-        <v>0.3417</v>
+        <v>0.3909</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -6032,10 +6032,10 @@
         <v>43</v>
       </c>
       <c r="G210">
-        <v>0.4348</v>
+        <v>0.4778</v>
       </c>
       <c r="H210">
-        <v>0.3937</v>
+        <v>0.4243</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -6058,10 +6058,10 @@
         <v>44</v>
       </c>
       <c r="G211">
-        <v>0.5767</v>
+        <v>0.5377</v>
       </c>
       <c r="H211">
-        <v>0.5353</v>
+        <v>0.4956</v>
       </c>
     </row>
     <row r="212" spans="1:8">
@@ -6084,10 +6084,10 @@
         <v>46</v>
       </c>
       <c r="G212">
-        <v>0.3466</v>
+        <v>0.3607</v>
       </c>
       <c r="H212">
-        <v>0.2952</v>
+        <v>0.3122</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -6110,10 +6110,10 @@
         <v>47</v>
       </c>
       <c r="G213">
-        <v>0.5451</v>
+        <v>0.5572</v>
       </c>
       <c r="H213">
-        <v>0.5118</v>
+        <v>0.5284</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -6136,10 +6136,10 @@
         <v>48</v>
       </c>
       <c r="G214">
-        <v>0.9063</v>
+        <v>0.9052</v>
       </c>
       <c r="H214">
-        <v>0.8831</v>
+        <v>0.8837</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -6162,10 +6162,10 @@
         <v>49</v>
       </c>
       <c r="G215">
-        <v>0.8627</v>
+        <v>0.8707</v>
       </c>
       <c r="H215">
-        <v>0.8355</v>
+        <v>0.8445</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -6188,10 +6188,10 @@
         <v>50</v>
       </c>
       <c r="G216">
-        <v>0.965</v>
+        <v>0.9638</v>
       </c>
       <c r="H216">
-        <v>0.9539</v>
+        <v>0.9517</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -6214,10 +6214,10 @@
         <v>51</v>
       </c>
       <c r="G217">
-        <v>0.8928</v>
+        <v>0.894</v>
       </c>
       <c r="H217">
-        <v>0.8678</v>
+        <v>0.8701</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -6240,10 +6240,10 @@
         <v>52</v>
       </c>
       <c r="G218">
-        <v>0.9536</v>
+        <v>0.9506</v>
       </c>
       <c r="H218">
-        <v>0.9416</v>
+        <v>0.9363</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -6656,10 +6656,10 @@
         <v>38</v>
       </c>
       <c r="G234">
-        <v>0.2987</v>
+        <v>0.3105</v>
       </c>
       <c r="H234">
-        <v>0.2693</v>
+        <v>0.2843</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -6682,10 +6682,10 @@
         <v>39</v>
       </c>
       <c r="G235">
-        <v>0.2035</v>
+        <v>0.2078</v>
       </c>
       <c r="H235">
-        <v>0.1667</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -6708,10 +6708,10 @@
         <v>40</v>
       </c>
       <c r="G236">
-        <v>0.3032</v>
+        <v>0.2661</v>
       </c>
       <c r="H236">
-        <v>0.2657</v>
+        <v>0.2287</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -6734,10 +6734,10 @@
         <v>41</v>
       </c>
       <c r="G237">
-        <v>0.3087</v>
+        <v>0.3571</v>
       </c>
       <c r="H237">
-        <v>0.2694</v>
+        <v>0.3165</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -6760,10 +6760,10 @@
         <v>42</v>
       </c>
       <c r="G238">
-        <v>0.5309</v>
+        <v>0.5732</v>
       </c>
       <c r="H238">
-        <v>0.4969</v>
+        <v>0.5354</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -6786,10 +6786,10 @@
         <v>43</v>
       </c>
       <c r="G239">
-        <v>0.5524</v>
+        <v>0.5984</v>
       </c>
       <c r="H239">
-        <v>0.5122</v>
+        <v>0.5629999999999999</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -6812,10 +6812,10 @@
         <v>44</v>
       </c>
       <c r="G240">
-        <v>0.6937</v>
+        <v>0.6711</v>
       </c>
       <c r="H240">
-        <v>0.6513</v>
+        <v>0.6274</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -6838,10 +6838,10 @@
         <v>45</v>
       </c>
       <c r="G241">
-        <v>0.7048</v>
+        <v>0.6878</v>
       </c>
       <c r="H241">
-        <v>0.6534</v>
+        <v>0.6393</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -6864,10 +6864,10 @@
         <v>47</v>
       </c>
       <c r="G242">
-        <v>0.7027</v>
+        <v>0.7184</v>
       </c>
       <c r="H242">
-        <v>0.6623</v>
+        <v>0.6816</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -6890,10 +6890,10 @@
         <v>48</v>
       </c>
       <c r="G243">
-        <v>0.9491000000000001</v>
+        <v>0.9547</v>
       </c>
       <c r="H243">
-        <v>0.9366</v>
+        <v>0.9433</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -6916,10 +6916,10 @@
         <v>49</v>
       </c>
       <c r="G244">
-        <v>0.9351</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H244">
-        <v>0.9171</v>
+        <v>0.9188</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -6942,10 +6942,10 @@
         <v>50</v>
       </c>
       <c r="G245">
-        <v>0.9805</v>
+        <v>0.9829</v>
       </c>
       <c r="H245">
-        <v>0.9746</v>
+        <v>0.9784</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -6968,10 +6968,10 @@
         <v>51</v>
       </c>
       <c r="G246">
-        <v>0.9298</v>
+        <v>0.9305</v>
       </c>
       <c r="H246">
-        <v>0.9146</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -6994,10 +6994,10 @@
         <v>52</v>
       </c>
       <c r="G247">
-        <v>0.9747</v>
+        <v>0.9758</v>
       </c>
       <c r="H247">
-        <v>0.9675</v>
+        <v>0.9692</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -7410,10 +7410,10 @@
         <v>38</v>
       </c>
       <c r="G263">
-        <v>0.1667</v>
+        <v>0.1866</v>
       </c>
       <c r="H263">
-        <v>0.138</v>
+        <v>0.1526</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -7436,10 +7436,10 @@
         <v>39</v>
       </c>
       <c r="G264">
-        <v>0.0975</v>
+        <v>0.097</v>
       </c>
       <c r="H264">
-        <v>0.0736</v>
+        <v>0.0735</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -7462,10 +7462,10 @@
         <v>40</v>
       </c>
       <c r="G265">
-        <v>0.1564</v>
+        <v>0.1354</v>
       </c>
       <c r="H265">
-        <v>0.1183</v>
+        <v>0.1045</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -7488,10 +7488,10 @@
         <v>41</v>
       </c>
       <c r="G266">
-        <v>0.1584</v>
+        <v>0.1755</v>
       </c>
       <c r="H266">
-        <v>0.1226</v>
+        <v>0.1353</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -7514,10 +7514,10 @@
         <v>42</v>
       </c>
       <c r="G267">
-        <v>0.3544</v>
+        <v>0.3679</v>
       </c>
       <c r="H267">
-        <v>0.3069</v>
+        <v>0.3179</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -7540,10 +7540,10 @@
         <v>43</v>
       </c>
       <c r="G268">
-        <v>0.3986</v>
+        <v>0.3797</v>
       </c>
       <c r="H268">
-        <v>0.3452</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -7566,10 +7566,10 @@
         <v>44</v>
       </c>
       <c r="G269">
-        <v>0.5363</v>
+        <v>0.5024</v>
       </c>
       <c r="H269">
-        <v>0.4917</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7592,10 +7592,10 @@
         <v>45</v>
       </c>
       <c r="G270">
-        <v>0.4882</v>
+        <v>0.4716</v>
       </c>
       <c r="H270">
-        <v>0.4549</v>
+        <v>0.4428</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7618,10 +7618,10 @@
         <v>46</v>
       </c>
       <c r="G271">
-        <v>0.3377</v>
+        <v>0.3184</v>
       </c>
       <c r="H271">
-        <v>0.2973</v>
+        <v>0.2816</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -7644,10 +7644,10 @@
         <v>48</v>
       </c>
       <c r="G272">
-        <v>0.9014</v>
+        <v>0.898</v>
       </c>
       <c r="H272">
-        <v>0.8687</v>
+        <v>0.8645</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7670,10 +7670,10 @@
         <v>49</v>
       </c>
       <c r="G273">
-        <v>0.8522</v>
+        <v>0.8465</v>
       </c>
       <c r="H273">
-        <v>0.8219</v>
+        <v>0.8162</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7696,10 +7696,10 @@
         <v>50</v>
       </c>
       <c r="G274">
-        <v>0.96</v>
+        <v>0.9562</v>
       </c>
       <c r="H274">
-        <v>0.9496</v>
+        <v>0.9443</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7722,10 +7722,10 @@
         <v>51</v>
       </c>
       <c r="G275">
-        <v>0.8786</v>
+        <v>0.8661</v>
       </c>
       <c r="H275">
-        <v>0.8531</v>
+        <v>0.8391</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -7748,10 +7748,10 @@
         <v>52</v>
       </c>
       <c r="G276">
-        <v>0.9578</v>
+        <v>0.9547</v>
       </c>
       <c r="H276">
-        <v>0.9479</v>
+        <v>0.9436</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -8164,10 +8164,10 @@
         <v>38</v>
       </c>
       <c r="G292">
-        <v>0.0403</v>
+        <v>0.0484</v>
       </c>
       <c r="H292">
-        <v>0.0332</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -8190,10 +8190,10 @@
         <v>39</v>
       </c>
       <c r="G293">
-        <v>0.0194</v>
+        <v>0.0204</v>
       </c>
       <c r="H293">
-        <v>0.0148</v>
+        <v>0.0154</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -8216,10 +8216,10 @@
         <v>40</v>
       </c>
       <c r="G294">
-        <v>0.0271</v>
+        <v>0.0294</v>
       </c>
       <c r="H294">
-        <v>0.0204</v>
+        <v>0.0218</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -8242,10 +8242,10 @@
         <v>41</v>
       </c>
       <c r="G295">
-        <v>0.0289</v>
+        <v>0.0298</v>
       </c>
       <c r="H295">
-        <v>0.0226</v>
+        <v>0.0239</v>
       </c>
     </row>
     <row r="296" spans="1:8">
@@ -8268,10 +8268,10 @@
         <v>42</v>
       </c>
       <c r="G296">
-        <v>0.07820000000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="H296">
-        <v>0.0581</v>
+        <v>0.055</v>
       </c>
     </row>
     <row r="297" spans="1:8">
@@ -8294,10 +8294,10 @@
         <v>43</v>
       </c>
       <c r="G297">
-        <v>0.0863</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="H297">
-        <v>0.0629</v>
+        <v>0.0712</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -8320,10 +8320,10 @@
         <v>44</v>
       </c>
       <c r="G298">
-        <v>0.1493</v>
+        <v>0.1349</v>
       </c>
       <c r="H298">
-        <v>0.1196</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -8346,10 +8346,10 @@
         <v>45</v>
       </c>
       <c r="G299">
-        <v>0.1169</v>
+        <v>0.1163</v>
       </c>
       <c r="H299">
-        <v>0.09370000000000001</v>
+        <v>0.0948</v>
       </c>
     </row>
     <row r="300" spans="1:8">
@@ -8372,10 +8372,10 @@
         <v>46</v>
       </c>
       <c r="G300">
-        <v>0.0634</v>
+        <v>0.0567</v>
       </c>
       <c r="H300">
-        <v>0.0509</v>
+        <v>0.0453</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -8398,10 +8398,10 @@
         <v>47</v>
       </c>
       <c r="G301">
-        <v>0.1313</v>
+        <v>0.1355</v>
       </c>
       <c r="H301">
-        <v>0.09859999999999999</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8424,10 +8424,10 @@
         <v>49</v>
       </c>
       <c r="G302">
-        <v>0.4296</v>
+        <v>0.43</v>
       </c>
       <c r="H302">
-        <v>0.3961</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -8450,10 +8450,10 @@
         <v>50</v>
       </c>
       <c r="G303">
-        <v>0.7718</v>
+        <v>0.7746</v>
       </c>
       <c r="H303">
-        <v>0.7345</v>
+        <v>0.7368</v>
       </c>
     </row>
     <row r="304" spans="1:8">
@@ -8918,10 +8918,10 @@
         <v>38</v>
       </c>
       <c r="G321">
-        <v>0.0487</v>
+        <v>0.0517</v>
       </c>
       <c r="H321">
-        <v>0.0383</v>
+        <v>0.0421</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -8944,10 +8944,10 @@
         <v>39</v>
       </c>
       <c r="G322">
-        <v>0.0228</v>
+        <v>0.0238</v>
       </c>
       <c r="H322">
-        <v>0.0167</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="323" spans="1:8">
@@ -8970,10 +8970,10 @@
         <v>40</v>
       </c>
       <c r="G323">
-        <v>0.0379</v>
+        <v>0.0337</v>
       </c>
       <c r="H323">
-        <v>0.0291</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -8996,10 +8996,10 @@
         <v>41</v>
       </c>
       <c r="G324">
-        <v>0.0334</v>
+        <v>0.038</v>
       </c>
       <c r="H324">
-        <v>0.0265</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -9022,10 +9022,10 @@
         <v>42</v>
       </c>
       <c r="G325">
-        <v>0.0969</v>
+        <v>0.1013</v>
       </c>
       <c r="H325">
-        <v>0.0684</v>
+        <v>0.0751</v>
       </c>
     </row>
     <row r="326" spans="1:8">
@@ -9048,10 +9048,10 @@
         <v>43</v>
       </c>
       <c r="G326">
-        <v>0.0878</v>
+        <v>0.1091</v>
       </c>
       <c r="H326">
-        <v>0.0677</v>
+        <v>0.0888</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -9074,10 +9074,10 @@
         <v>44</v>
       </c>
       <c r="G327">
-        <v>0.1757</v>
+        <v>0.1601</v>
       </c>
       <c r="H327">
-        <v>0.1416</v>
+        <v>0.1294</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -9100,10 +9100,10 @@
         <v>45</v>
       </c>
       <c r="G328">
-        <v>0.1645</v>
+        <v>0.1555</v>
       </c>
       <c r="H328">
-        <v>0.1373</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -9126,10 +9126,10 @@
         <v>46</v>
       </c>
       <c r="G329">
-        <v>0.0829</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H329">
-        <v>0.0649</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -9152,10 +9152,10 @@
         <v>47</v>
       </c>
       <c r="G330">
-        <v>0.1781</v>
+        <v>0.1838</v>
       </c>
       <c r="H330">
-        <v>0.1478</v>
+        <v>0.1535</v>
       </c>
     </row>
     <row r="331" spans="1:8">
@@ -9178,10 +9178,10 @@
         <v>48</v>
       </c>
       <c r="G331">
-        <v>0.6039</v>
+        <v>0.6042</v>
       </c>
       <c r="H331">
-        <v>0.5704</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="332" spans="1:8">
@@ -9204,10 +9204,10 @@
         <v>50</v>
       </c>
       <c r="G332">
-        <v>0.8267</v>
+        <v>0.8303</v>
       </c>
       <c r="H332">
-        <v>0.7881</v>
+        <v>0.7911</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -9230,10 +9230,10 @@
         <v>51</v>
       </c>
       <c r="G333">
-        <v>0.591</v>
+        <v>0.6029</v>
       </c>
       <c r="H333">
-        <v>0.5467</v>
+        <v>0.5568</v>
       </c>
     </row>
     <row r="334" spans="1:8">
@@ -9672,10 +9672,10 @@
         <v>38</v>
       </c>
       <c r="G350">
-        <v>0.0204</v>
+        <v>0.0226</v>
       </c>
       <c r="H350">
-        <v>0.0154</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="351" spans="1:8">
@@ -9698,10 +9698,10 @@
         <v>39</v>
       </c>
       <c r="G351">
-        <v>0.0133</v>
+        <v>0.0138</v>
       </c>
       <c r="H351">
-        <v>0.0112</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="352" spans="1:8">
@@ -9724,10 +9724,10 @@
         <v>40</v>
       </c>
       <c r="G352">
-        <v>0.0153</v>
+        <v>0.0142</v>
       </c>
       <c r="H352">
-        <v>0.0129</v>
+        <v>0.0121</v>
       </c>
     </row>
     <row r="353" spans="1:8">
@@ -9750,10 +9750,10 @@
         <v>41</v>
       </c>
       <c r="G353">
-        <v>0.0167</v>
+        <v>0.0179</v>
       </c>
       <c r="H353">
-        <v>0.0132</v>
+        <v>0.0144</v>
       </c>
     </row>
     <row r="354" spans="1:8">
@@ -9776,10 +9776,10 @@
         <v>42</v>
       </c>
       <c r="G354">
-        <v>0.0279</v>
+        <v>0.0311</v>
       </c>
       <c r="H354">
-        <v>0.0214</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="355" spans="1:8">
@@ -9802,10 +9802,10 @@
         <v>43</v>
       </c>
       <c r="G355">
-        <v>0.027</v>
+        <v>0.0361</v>
       </c>
       <c r="H355">
-        <v>0.0205</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="356" spans="1:8">
@@ -9828,10 +9828,10 @@
         <v>44</v>
       </c>
       <c r="G356">
-        <v>0.0447</v>
+        <v>0.0413</v>
       </c>
       <c r="H356">
-        <v>0.0363</v>
+        <v>0.0357</v>
       </c>
     </row>
     <row r="357" spans="1:8">
@@ -9854,10 +9854,10 @@
         <v>45</v>
       </c>
       <c r="G357">
-        <v>0.0461</v>
+        <v>0.0483</v>
       </c>
       <c r="H357">
-        <v>0.035</v>
+        <v>0.0362</v>
       </c>
     </row>
     <row r="358" spans="1:8">
@@ -9880,10 +9880,10 @@
         <v>46</v>
       </c>
       <c r="G358">
-        <v>0.0254</v>
+        <v>0.0216</v>
       </c>
       <c r="H358">
-        <v>0.0195</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -9906,10 +9906,10 @@
         <v>47</v>
       </c>
       <c r="G359">
-        <v>0.0504</v>
+        <v>0.0557</v>
       </c>
       <c r="H359">
-        <v>0.04</v>
+        <v>0.0438</v>
       </c>
     </row>
     <row r="360" spans="1:8">
@@ -9932,10 +9932,10 @@
         <v>48</v>
       </c>
       <c r="G360">
-        <v>0.2655</v>
+        <v>0.2632</v>
       </c>
       <c r="H360">
-        <v>0.2282</v>
+        <v>0.2254</v>
       </c>
     </row>
     <row r="361" spans="1:8">
@@ -9958,10 +9958,10 @@
         <v>49</v>
       </c>
       <c r="G361">
-        <v>0.2119</v>
+        <v>0.2089</v>
       </c>
       <c r="H361">
-        <v>0.1733</v>
+        <v>0.1697</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -9984,10 +9984,10 @@
         <v>51</v>
       </c>
       <c r="G362">
-        <v>0.2368</v>
+        <v>0.2341</v>
       </c>
       <c r="H362">
-        <v>0.1894</v>
+        <v>0.1852</v>
       </c>
     </row>
     <row r="363" spans="1:8">
@@ -10426,10 +10426,10 @@
         <v>38</v>
       </c>
       <c r="G379">
-        <v>0.0392</v>
+        <v>0.0418</v>
       </c>
       <c r="H379">
-        <v>0.0331</v>
+        <v>0.0346</v>
       </c>
     </row>
     <row r="380" spans="1:8">
@@ -10452,10 +10452,10 @@
         <v>39</v>
       </c>
       <c r="G380">
-        <v>0.022</v>
+        <v>0.0204</v>
       </c>
       <c r="H380">
-        <v>0.0163</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="381" spans="1:8">
@@ -10478,10 +10478,10 @@
         <v>40</v>
       </c>
       <c r="G381">
-        <v>0.0381</v>
+        <v>0.0305</v>
       </c>
       <c r="H381">
-        <v>0.0295</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="382" spans="1:8">
@@ -10504,10 +10504,10 @@
         <v>41</v>
       </c>
       <c r="G382">
-        <v>0.033</v>
+        <v>0.0322</v>
       </c>
       <c r="H382">
-        <v>0.0271</v>
+        <v>0.0279</v>
       </c>
     </row>
     <row r="383" spans="1:8">
@@ -10530,10 +10530,10 @@
         <v>42</v>
       </c>
       <c r="G383">
-        <v>0.0803</v>
+        <v>0.0799</v>
       </c>
       <c r="H383">
-        <v>0.06419999999999999</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="384" spans="1:8">
@@ -10556,10 +10556,10 @@
         <v>43</v>
       </c>
       <c r="G384">
-        <v>0.07240000000000001</v>
+        <v>0.0993</v>
       </c>
       <c r="H384">
-        <v>0.0587</v>
+        <v>0.0788</v>
       </c>
     </row>
     <row r="385" spans="1:8">
@@ -10582,10 +10582,10 @@
         <v>44</v>
       </c>
       <c r="G385">
-        <v>0.1505</v>
+        <v>0.1561</v>
       </c>
       <c r="H385">
-        <v>0.1201</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="386" spans="1:8">
@@ -10608,10 +10608,10 @@
         <v>45</v>
       </c>
       <c r="G386">
-        <v>0.1322</v>
+        <v>0.1299</v>
       </c>
       <c r="H386">
-        <v>0.1072</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="387" spans="1:8">
@@ -10634,10 +10634,10 @@
         <v>46</v>
       </c>
       <c r="G387">
-        <v>0.0854</v>
+        <v>0.0842</v>
       </c>
       <c r="H387">
-        <v>0.0702</v>
+        <v>0.06950000000000001</v>
       </c>
     </row>
     <row r="388" spans="1:8">
@@ -10660,10 +10660,10 @@
         <v>47</v>
       </c>
       <c r="G388">
-        <v>0.1469</v>
+        <v>0.1609</v>
       </c>
       <c r="H388">
-        <v>0.1214</v>
+        <v>0.1339</v>
       </c>
     </row>
     <row r="389" spans="1:8">
@@ -10712,10 +10712,10 @@
         <v>49</v>
       </c>
       <c r="G390">
-        <v>0.4533</v>
+        <v>0.4432</v>
       </c>
       <c r="H390">
-        <v>0.409</v>
+        <v>0.3971</v>
       </c>
     </row>
     <row r="391" spans="1:8">
@@ -10738,10 +10738,10 @@
         <v>50</v>
       </c>
       <c r="G391">
-        <v>0.8106</v>
+        <v>0.8148</v>
       </c>
       <c r="H391">
-        <v>0.7632</v>
+        <v>0.7659</v>
       </c>
     </row>
     <row r="392" spans="1:8">
@@ -11180,10 +11180,10 @@
         <v>38</v>
       </c>
       <c r="G408">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="H408">
-        <v>0.0215</v>
+        <v>0.0229</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -11206,10 +11206,10 @@
         <v>39</v>
       </c>
       <c r="G409">
-        <v>0.0158</v>
+        <v>0.015</v>
       </c>
       <c r="H409">
-        <v>0.0116</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="410" spans="1:8">
@@ -11232,10 +11232,10 @@
         <v>40</v>
       </c>
       <c r="G410">
-        <v>0.0195</v>
+        <v>0.0194</v>
       </c>
       <c r="H410">
-        <v>0.0148</v>
+        <v>0.0145</v>
       </c>
     </row>
     <row r="411" spans="1:8">
@@ -11258,10 +11258,10 @@
         <v>41</v>
       </c>
       <c r="G411">
-        <v>0.0175</v>
+        <v>0.018</v>
       </c>
       <c r="H411">
-        <v>0.0135</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="412" spans="1:8">
@@ -11284,10 +11284,10 @@
         <v>42</v>
       </c>
       <c r="G412">
-        <v>0.0356</v>
+        <v>0.0383</v>
       </c>
       <c r="H412">
-        <v>0.0264</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="413" spans="1:8">
@@ -11310,10 +11310,10 @@
         <v>43</v>
       </c>
       <c r="G413">
-        <v>0.0335</v>
+        <v>0.0383</v>
       </c>
       <c r="H413">
-        <v>0.0261</v>
+        <v>0.0307</v>
       </c>
     </row>
     <row r="414" spans="1:8">
@@ -11336,10 +11336,10 @@
         <v>44</v>
       </c>
       <c r="G414">
-        <v>0.0479</v>
+        <v>0.0459</v>
       </c>
       <c r="H414">
-        <v>0.039</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="415" spans="1:8">
@@ -11362,10 +11362,10 @@
         <v>45</v>
       </c>
       <c r="G415">
-        <v>0.0584</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="H415">
-        <v>0.0464</v>
+        <v>0.0494</v>
       </c>
     </row>
     <row r="416" spans="1:8">
@@ -11388,10 +11388,10 @@
         <v>46</v>
       </c>
       <c r="G416">
-        <v>0.0325</v>
+        <v>0.0308</v>
       </c>
       <c r="H416">
-        <v>0.0253</v>
+        <v>0.0242</v>
       </c>
     </row>
     <row r="417" spans="1:8">
@@ -11414,10 +11414,10 @@
         <v>47</v>
       </c>
       <c r="G417">
-        <v>0.0521</v>
+        <v>0.0564</v>
       </c>
       <c r="H417">
-        <v>0.0422</v>
+        <v>0.0453</v>
       </c>
     </row>
     <row r="418" spans="1:8">
